--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/Attachments/Bureau/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCB32303-F9E0-4111-8677-557EFE02326E}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{310313DC-AB9E-4348-9C20-2FE0689D789E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil2" sheetId="30" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="31" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1936" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="370">
   <si>
     <t>-</t>
   </si>
@@ -516,15 +516,6 @@
     <t>PLATEAU</t>
   </si>
   <si>
-    <t>CAN 2025</t>
-  </si>
-  <si>
-    <t>ITC MANDJARO</t>
-  </si>
-  <si>
-    <t>ITC(MANDJARO)</t>
-  </si>
-  <si>
     <t>CONSEIL REGIONAL DE LA MARAHOUE</t>
   </si>
   <si>
@@ -831,12 +822,6 @@
     <t>LYCEE PROFESSIONNEL METIER ENERGIES RENOUVELABLES</t>
   </si>
   <si>
-    <t>YOPOUGON LYCEE TECHNIQUE</t>
-  </si>
-  <si>
-    <t>Support IP: Correction</t>
-  </si>
-  <si>
     <t>COMPAGNIE DE TRANSFORMATION DU CAOUCHOUC IVOIRIEN</t>
   </si>
   <si>
@@ -849,12 +834,6 @@
     <t>PORT BOUET VRIDI ZONE INDUSTRIELLE</t>
   </si>
   <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BOUAKE//VOIE INCONNUE/N'GATTAKRO</t>
-  </si>
-  <si>
     <t>SYTHD260069</t>
   </si>
   <si>
@@ -921,12 +900,6 @@
     <t>MARCORY ZONE 4</t>
   </si>
   <si>
-    <t>xxxxxxxxxxxxx</t>
-  </si>
-  <si>
-    <t>DIE : Configuration IMS</t>
-  </si>
-  <si>
     <t>PC MARKET</t>
   </si>
   <si>
@@ -1102,6 +1075,66 @@
   </si>
   <si>
     <t>FOUAD GROUPE</t>
+  </si>
+  <si>
+    <t>BUVPN260022</t>
+  </si>
+  <si>
+    <t>Responsable Zone: Validation intervention</t>
+  </si>
+  <si>
+    <t>BASE AERIENN KORHOGO</t>
+  </si>
+  <si>
+    <t>FH</t>
+  </si>
+  <si>
+    <t>SYTHD260061</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie BSCS</t>
+  </si>
+  <si>
+    <t>ABIDJAN-YOPOUGON//VOIE INCONNUE/LYCEE TECHNIQUE ADMINISTRATION</t>
+  </si>
+  <si>
+    <t>SYTHD260068</t>
+  </si>
+  <si>
+    <t>BUVPN260043</t>
+  </si>
+  <si>
+    <t>BOUAKE N'GATTAKRO</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>Prestataire : Etude</t>
+  </si>
+  <si>
+    <t>BUVPN260037</t>
+  </si>
+  <si>
+    <t>BUVPN260046</t>
+  </si>
+  <si>
+    <t>BGFI SERVICE SIMAO</t>
+  </si>
+  <si>
+    <t>COCODY VALON</t>
+  </si>
+  <si>
+    <t>MARCORY</t>
+  </si>
+  <si>
+    <t>TROPICALE TRANSIT SITE TREICHVILLE IMMEUBLE EN FACR DE SOGELUX</t>
+  </si>
+  <si>
+    <t>FAMAN TRANSIT SITE TREICHVILLE EN FACE DE SOLIBRA SUR VGE</t>
+  </si>
+  <si>
+    <t>HANNYYAH TRANSIT SITE TREICHVILLE VERS NOTRE DAME</t>
   </si>
 </sst>
 </file>
@@ -1474,8 +1507,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69FB493-FFEB-40A9-8A40-ECED1B9A0D11}">
-  <dimension ref="A1:P190"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B586976-6BB4-4483-B4DB-77564AF6B97B}">
+  <dimension ref="A1:P200"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -1545,19 +1578,19 @@
         <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G2">
         <v>709899970</v>
       </c>
       <c r="H2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K2" t="s">
         <v>5</v>
@@ -1575,7 +1608,7 @@
         <v>8018371</v>
       </c>
       <c r="P2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
@@ -1645,13 +1678,13 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G4">
         <v>824923429</v>
       </c>
       <c r="H4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
@@ -1675,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
@@ -1695,13 +1728,13 @@
         <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G5">
         <v>824923429</v>
       </c>
       <c r="H5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I5" t="s">
         <v>0</v>
@@ -1725,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
@@ -1745,13 +1778,13 @@
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G6">
         <v>707269600</v>
       </c>
       <c r="H6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I6">
         <v>2753435</v>
@@ -1775,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
@@ -2286,13 +2319,13 @@
         <v>45960.452361111114</v>
       </c>
       <c r="C17">
-        <v>54241472</v>
+        <v>59297097</v>
       </c>
       <c r="D17" s="1">
-        <v>45988.651770833334</v>
+        <v>46084.659699074073</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
         <v>79</v>
@@ -2875,7 +2908,7 @@
         <v>2932569</v>
       </c>
       <c r="P28" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
@@ -2925,7 +2958,7 @@
         <v>2932569</v>
       </c>
       <c r="P29" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
@@ -3151,7 +3184,7 @@
         <v>504033918</v>
       </c>
       <c r="H34" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I34">
         <v>1814616</v>
@@ -3175,7 +3208,7 @@
         <v>1000000</v>
       </c>
       <c r="P34" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.35">
@@ -3225,7 +3258,7 @@
         <v>1000000</v>
       </c>
       <c r="P35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.35">
@@ -3275,7 +3308,7 @@
         <v>1000000</v>
       </c>
       <c r="P36" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.35">
@@ -3886,13 +3919,13 @@
         <v>46002.615995370368</v>
       </c>
       <c r="C49">
-        <v>59026386</v>
+        <v>59305652</v>
       </c>
       <c r="D49" s="1">
-        <v>46079.684884259259</v>
+        <v>46084.729594907411</v>
       </c>
       <c r="E49" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="F49" t="s">
         <v>128</v>
@@ -4275,7 +4308,7 @@
         <v>1000000</v>
       </c>
       <c r="P56" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
@@ -4325,7 +4358,7 @@
         <v>1000000</v>
       </c>
       <c r="P57" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
@@ -4375,183 +4408,183 @@
         <v>1250000</v>
       </c>
       <c r="P58" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>55476623</v>
+        <v>55490966</v>
       </c>
       <c r="B59" s="1">
-        <v>46010.646481481483</v>
+        <v>46010.764004629629</v>
       </c>
       <c r="C59">
-        <v>56108841</v>
+        <v>59265081</v>
       </c>
       <c r="D59" s="1">
-        <v>46024.572210648148</v>
+        <v>46084.416689814818</v>
       </c>
       <c r="E59" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="G59">
-        <v>707701545</v>
+        <v>707098376</v>
       </c>
       <c r="H59" t="s">
-        <v>164</v>
-      </c>
-      <c r="I59" t="s">
-        <v>0</v>
+        <v>215</v>
+      </c>
+      <c r="I59">
+        <v>1763406</v>
       </c>
       <c r="J59" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K59" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L59" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M59" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="N59" t="s">
         <v>0</v>
       </c>
-      <c r="O59" s="2">
-        <v>5324000</v>
+      <c r="O59">
+        <v>0</v>
       </c>
       <c r="P59" t="s">
-        <v>43</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>55477827</v>
+        <v>55636282</v>
       </c>
       <c r="B60" s="1">
-        <v>46010.653912037036</v>
+        <v>46014.435729166667</v>
       </c>
       <c r="C60">
-        <v>56360428</v>
+        <v>57367586</v>
       </c>
       <c r="D60" s="1">
-        <v>46030.346030092594</v>
+        <v>46049.856261574074</v>
       </c>
       <c r="E60" t="s">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="F60" t="s">
         <v>163</v>
       </c>
       <c r="G60">
-        <v>707701545</v>
+        <v>759003900</v>
       </c>
       <c r="H60" t="s">
-        <v>165</v>
+        <v>34</v>
       </c>
       <c r="I60" t="s">
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K60" t="s">
         <v>5</v>
       </c>
       <c r="L60" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M60" t="s">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="N60" t="s">
         <v>0</v>
       </c>
       <c r="O60" s="2">
-        <v>293000</v>
+        <v>918681</v>
       </c>
       <c r="P60" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>55490966</v>
+        <v>55686160</v>
       </c>
       <c r="B61" s="1">
-        <v>46010.764004629629</v>
+        <v>46015.355868055558</v>
       </c>
       <c r="C61">
-        <v>59265081</v>
+        <v>58214558</v>
       </c>
       <c r="D61" s="1">
-        <v>46084.416689814818</v>
+        <v>46065.517453703702</v>
       </c>
       <c r="E61" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F61" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="G61">
-        <v>707098376</v>
+        <v>777765287</v>
       </c>
       <c r="H61" t="s">
-        <v>218</v>
-      </c>
-      <c r="I61">
-        <v>1763406</v>
+        <v>69</v>
+      </c>
+      <c r="I61" t="s">
+        <v>0</v>
       </c>
       <c r="J61" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K61" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L61" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M61" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N61" t="s">
         <v>0</v>
       </c>
-      <c r="O61">
-        <v>0</v>
+      <c r="O61" s="2">
+        <v>850887</v>
       </c>
       <c r="P61" t="s">
-        <v>219</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>55636282</v>
+        <v>55694485</v>
       </c>
       <c r="B62" s="1">
-        <v>46014.435729166667</v>
+        <v>46015.420092592591</v>
       </c>
       <c r="C62">
-        <v>57367586</v>
+        <v>56752240</v>
       </c>
       <c r="D62" s="1">
-        <v>46049.856261574074</v>
+        <v>46037.705520833333</v>
       </c>
       <c r="E62" t="s">
-        <v>197</v>
+        <v>10</v>
       </c>
       <c r="F62" t="s">
+        <v>165</v>
+      </c>
+      <c r="G62">
+        <v>749338073</v>
+      </c>
+      <c r="H62" t="s">
         <v>166</v>
-      </c>
-      <c r="G62">
-        <v>759003900</v>
-      </c>
-      <c r="H62" t="s">
-        <v>34</v>
       </c>
       <c r="I62" t="s">
         <v>0</v>
@@ -4572,42 +4605,42 @@
         <v>0</v>
       </c>
       <c r="O62" s="2">
-        <v>918681</v>
+        <v>638462</v>
       </c>
       <c r="P62" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>55686160</v>
+        <v>56181778</v>
       </c>
       <c r="B63" s="1">
-        <v>46015.355868055558</v>
+        <v>46027.499212962961</v>
       </c>
       <c r="C63">
-        <v>58214558</v>
+        <v>59210339</v>
       </c>
       <c r="D63" s="1">
-        <v>46065.517453703702</v>
+        <v>46083.492881944447</v>
       </c>
       <c r="E63" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="F63" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G63">
-        <v>777765287</v>
+        <v>585990976</v>
       </c>
       <c r="H63" t="s">
-        <v>69</v>
-      </c>
-      <c r="I63" t="s">
-        <v>0</v>
+        <v>169</v>
+      </c>
+      <c r="I63">
+        <v>1765416</v>
       </c>
       <c r="J63" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K63" t="s">
         <v>5</v>
@@ -4622,48 +4655,48 @@
         <v>0</v>
       </c>
       <c r="O63" s="2">
-        <v>850887</v>
+        <v>3000000</v>
       </c>
       <c r="P63" t="s">
-        <v>12</v>
+        <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>55694485</v>
+        <v>56460494</v>
       </c>
       <c r="B64" s="1">
-        <v>46015.420092592591</v>
+        <v>46031.688935185186</v>
       </c>
       <c r="C64">
-        <v>56752240</v>
+        <v>58549829</v>
       </c>
       <c r="D64" s="1">
-        <v>46037.705520833333</v>
+        <v>46071.689143518517</v>
       </c>
       <c r="E64" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G64">
-        <v>749338073</v>
+        <v>758513012</v>
       </c>
       <c r="H64" t="s">
-        <v>169</v>
-      </c>
-      <c r="I64" t="s">
-        <v>0</v>
+        <v>198</v>
+      </c>
+      <c r="I64">
+        <v>1771006</v>
       </c>
       <c r="J64" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K64" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M64" t="s">
         <v>3</v>
@@ -4672,48 +4705,48 @@
         <v>0</v>
       </c>
       <c r="O64" s="2">
-        <v>638462</v>
+        <v>500000</v>
       </c>
       <c r="P64" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>56181778</v>
+        <v>56601140</v>
       </c>
       <c r="B65" s="1">
-        <v>46027.499212962961</v>
+        <v>46035.385555555556</v>
       </c>
       <c r="C65">
-        <v>59210339</v>
+        <v>58682590</v>
       </c>
       <c r="D65" s="1">
-        <v>46083.492881944447</v>
+        <v>46073.725775462961</v>
       </c>
       <c r="E65" t="s">
-        <v>197</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="G65">
-        <v>585990976</v>
+        <v>707003126</v>
       </c>
       <c r="H65" t="s">
-        <v>172</v>
-      </c>
-      <c r="I65">
-        <v>1765416</v>
+        <v>173</v>
+      </c>
+      <c r="I65" t="s">
+        <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
       </c>
       <c r="L65" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M65" t="s">
         <v>3</v>
@@ -4722,45 +4755,45 @@
         <v>0</v>
       </c>
       <c r="O65" s="2">
-        <v>3000000</v>
+        <v>7103410</v>
       </c>
       <c r="P65" t="s">
-        <v>173</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>56460494</v>
+        <v>56601982</v>
       </c>
       <c r="B66" s="1">
-        <v>46031.688935185186</v>
+        <v>46035.393611111111</v>
       </c>
       <c r="C66">
-        <v>58549829</v>
+        <v>59241374</v>
       </c>
       <c r="D66" s="1">
-        <v>46071.689143518517</v>
+        <v>46083.713761574072</v>
       </c>
       <c r="E66" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F66" t="s">
+        <v>32</v>
+      </c>
+      <c r="G66">
+        <v>707003126</v>
+      </c>
+      <c r="H66" t="s">
         <v>174</v>
       </c>
-      <c r="G66">
-        <v>758513012</v>
-      </c>
-      <c r="H66" t="s">
-        <v>201</v>
-      </c>
-      <c r="I66">
-        <v>1771006</v>
+      <c r="I66" t="s">
+        <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K66" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L66" t="s">
         <v>8</v>
@@ -4772,48 +4805,48 @@
         <v>0</v>
       </c>
       <c r="O66" s="2">
-        <v>500000</v>
+        <v>7103410</v>
       </c>
       <c r="P66" t="s">
-        <v>220</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>56601140</v>
+        <v>56603158</v>
       </c>
       <c r="B67" s="1">
-        <v>46035.385555555556</v>
+        <v>46035.405011574076</v>
       </c>
       <c r="C67">
-        <v>58682590</v>
+        <v>57145671</v>
       </c>
       <c r="D67" s="1">
-        <v>46073.725775462961</v>
+        <v>46045.510034722225</v>
       </c>
       <c r="E67" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F67" t="s">
-        <v>32</v>
+        <v>175</v>
       </c>
       <c r="G67">
-        <v>707003126</v>
+        <v>504041812</v>
       </c>
       <c r="H67" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="I67" t="s">
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
       </c>
       <c r="L67" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M67" t="s">
         <v>3</v>
@@ -4822,27 +4855,27 @@
         <v>0</v>
       </c>
       <c r="O67" s="2">
-        <v>7103410</v>
+        <v>2000000</v>
       </c>
       <c r="P67" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>56601982</v>
+        <v>56603495</v>
       </c>
       <c r="B68" s="1">
-        <v>46035.393611111111</v>
+        <v>46035.408518518518</v>
       </c>
       <c r="C68">
-        <v>59241374</v>
+        <v>58682422</v>
       </c>
       <c r="D68" s="1">
-        <v>46083.713761574072</v>
+        <v>46073.724178240744</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F68" t="s">
         <v>32</v>
@@ -4851,7 +4884,7 @@
         <v>707003126</v>
       </c>
       <c r="H68" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I68" t="s">
         <v>0</v>
@@ -4880,40 +4913,40 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>56603158</v>
+        <v>56606469</v>
       </c>
       <c r="B69" s="1">
-        <v>46035.405011574076</v>
+        <v>46035.43072916667</v>
       </c>
       <c r="C69">
-        <v>57145671</v>
+        <v>58080473</v>
       </c>
       <c r="D69" s="1">
-        <v>46045.510034722225</v>
+        <v>46063.478414351855</v>
       </c>
       <c r="E69" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F69" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G69">
         <v>504041812</v>
       </c>
       <c r="H69" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="I69" t="s">
         <v>0</v>
       </c>
       <c r="J69" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
       </c>
       <c r="L69" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M69" t="s">
         <v>3</v>
@@ -4922,36 +4955,36 @@
         <v>0</v>
       </c>
       <c r="O69" s="2">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="P69" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>56603495</v>
+        <v>56607988</v>
       </c>
       <c r="B70" s="1">
-        <v>46035.408518518518</v>
+        <v>46035.443668981483</v>
       </c>
       <c r="C70">
-        <v>58682422</v>
+        <v>58404447</v>
       </c>
       <c r="D70" s="1">
-        <v>46073.724178240744</v>
+        <v>46069.522615740738</v>
       </c>
       <c r="E70" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>175</v>
       </c>
       <c r="G70">
-        <v>707003126</v>
+        <v>504041812</v>
       </c>
       <c r="H70" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I70" t="s">
         <v>0</v>
@@ -4972,36 +5005,36 @@
         <v>0</v>
       </c>
       <c r="O70" s="2">
-        <v>7103410</v>
+        <v>2000000</v>
       </c>
       <c r="P70" t="s">
-        <v>22</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>56606469</v>
+        <v>56609018</v>
       </c>
       <c r="B71" s="1">
-        <v>46035.43072916667</v>
+        <v>46035.452465277776</v>
       </c>
       <c r="C71">
-        <v>58080473</v>
+        <v>58089216</v>
       </c>
       <c r="D71" s="1">
-        <v>46063.478414351855</v>
+        <v>46063.544803240744</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G71">
         <v>504041812</v>
       </c>
       <c r="H71" t="s">
-        <v>45</v>
+        <v>178</v>
       </c>
       <c r="I71" t="s">
         <v>0</v>
@@ -5022,30 +5055,30 @@
         <v>0</v>
       </c>
       <c r="O71" s="2">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="P71" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>56607988</v>
+        <v>56611212</v>
       </c>
       <c r="B72" s="1">
-        <v>46035.443668981483</v>
+        <v>46035.471886574072</v>
       </c>
       <c r="C72">
-        <v>58404447</v>
+        <v>57137676</v>
       </c>
       <c r="D72" s="1">
-        <v>46069.522615740738</v>
+        <v>46045.45140046296</v>
       </c>
       <c r="E72" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F72" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G72">
         <v>504041812</v>
@@ -5075,33 +5108,33 @@
         <v>2000000</v>
       </c>
       <c r="P72" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>56609018</v>
+        <v>56612479</v>
       </c>
       <c r="B73" s="1">
-        <v>46035.452465277776</v>
+        <v>46035.481446759259</v>
       </c>
       <c r="C73">
-        <v>58089216</v>
+        <v>59297612</v>
       </c>
       <c r="D73" s="1">
-        <v>46063.544803240744</v>
+        <v>46084.663553240738</v>
       </c>
       <c r="E73" t="s">
-        <v>10</v>
+        <v>351</v>
       </c>
       <c r="F73" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G73">
         <v>504041812</v>
       </c>
       <c r="H73" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I73" t="s">
         <v>0</v>
@@ -5125,27 +5158,27 @@
         <v>2000000</v>
       </c>
       <c r="P73" t="s">
-        <v>19</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>56611212</v>
+        <v>56613961</v>
       </c>
       <c r="B74" s="1">
-        <v>46035.471886574072</v>
+        <v>46035.492175925923</v>
       </c>
       <c r="C74">
-        <v>57137676</v>
+        <v>59292922</v>
       </c>
       <c r="D74" s="1">
-        <v>46045.45140046296</v>
+        <v>46084.632453703707</v>
       </c>
       <c r="E74" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
       <c r="F74" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G74">
         <v>504041812</v>
@@ -5180,28 +5213,28 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>56612479</v>
+        <v>56618123</v>
       </c>
       <c r="B75" s="1">
-        <v>46035.481446759259</v>
+        <v>46035.520821759259</v>
       </c>
       <c r="C75">
-        <v>57824193</v>
+        <v>58857998</v>
       </c>
       <c r="D75" s="1">
-        <v>46058.408449074072</v>
+        <v>46077.428530092591</v>
       </c>
       <c r="E75" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F75" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G75">
         <v>504041812</v>
       </c>
       <c r="H75" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I75" t="s">
         <v>0</v>
@@ -5225,45 +5258,45 @@
         <v>2000000</v>
       </c>
       <c r="P75" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>56613961</v>
+        <v>56675050</v>
       </c>
       <c r="B76" s="1">
-        <v>46035.492175925923</v>
+        <v>46036.516423611109</v>
       </c>
       <c r="C76">
-        <v>57137551</v>
+        <v>58216664</v>
       </c>
       <c r="D76" s="1">
-        <v>46045.450266203705</v>
+        <v>46065.536226851851</v>
       </c>
       <c r="E76" t="s">
-        <v>197</v>
+        <v>10</v>
       </c>
       <c r="F76" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="G76">
-        <v>504041812</v>
+        <v>748512613</v>
       </c>
       <c r="H76" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="I76" t="s">
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
       </c>
       <c r="L76" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M76" t="s">
         <v>3</v>
@@ -5272,36 +5305,36 @@
         <v>0</v>
       </c>
       <c r="O76" s="2">
-        <v>2000000</v>
+        <v>4362401</v>
       </c>
       <c r="P76" t="s">
-        <v>187</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>56618123</v>
+        <v>56800015</v>
       </c>
       <c r="B77" s="1">
-        <v>46035.520821759259</v>
+        <v>46038.638506944444</v>
       </c>
       <c r="C77">
-        <v>58857998</v>
+        <v>58668806</v>
       </c>
       <c r="D77" s="1">
-        <v>46077.428530092591</v>
+        <v>46073.619537037041</v>
       </c>
       <c r="E77" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F77" t="s">
+        <v>187</v>
+      </c>
+      <c r="G77">
+        <v>777748203</v>
+      </c>
+      <c r="H77" t="s">
         <v>188</v>
-      </c>
-      <c r="G77">
-        <v>504041812</v>
-      </c>
-      <c r="H77" t="s">
-        <v>189</v>
       </c>
       <c r="I77" t="s">
         <v>0</v>
@@ -5322,36 +5355,36 @@
         <v>0</v>
       </c>
       <c r="O77" s="2">
-        <v>2000000</v>
+        <v>293000</v>
       </c>
       <c r="P77" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>56675050</v>
+        <v>56970346</v>
       </c>
       <c r="B78" s="1">
-        <v>46036.516423611109</v>
+        <v>46042.557280092595</v>
       </c>
       <c r="C78">
-        <v>58216664</v>
+        <v>59242054</v>
       </c>
       <c r="D78" s="1">
-        <v>46065.536226851851</v>
+        <v>46083.719525462962</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
       </c>
       <c r="F78" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="G78">
-        <v>748512613</v>
+        <v>708667658</v>
       </c>
       <c r="H78" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="I78" t="s">
         <v>0</v>
@@ -5372,86 +5405,86 @@
         <v>0</v>
       </c>
       <c r="O78" s="2">
-        <v>4362401</v>
+        <v>2871414</v>
       </c>
       <c r="P78" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>56800015</v>
+        <v>57111758</v>
       </c>
       <c r="B79" s="1">
-        <v>46038.638506944444</v>
+        <v>46044.694849537038</v>
       </c>
       <c r="C79">
-        <v>58668806</v>
+        <v>57898966</v>
       </c>
       <c r="D79" s="1">
-        <v>46073.619537037041</v>
+        <v>46059.499050925922</v>
       </c>
       <c r="E79" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F79" t="s">
-        <v>190</v>
+        <v>106</v>
       </c>
       <c r="G79">
-        <v>777748203</v>
+        <v>171161677</v>
       </c>
       <c r="H79" t="s">
-        <v>191</v>
-      </c>
-      <c r="I79" t="s">
-        <v>0</v>
+        <v>220</v>
+      </c>
+      <c r="I79">
+        <v>1784416</v>
       </c>
       <c r="J79" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
       </c>
       <c r="L79" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M79" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N79" t="s">
         <v>0</v>
       </c>
-      <c r="O79" s="2">
-        <v>293000</v>
+      <c r="O79" t="s">
+        <v>0</v>
       </c>
       <c r="P79" t="s">
-        <v>40</v>
+        <v>221</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>56970346</v>
+        <v>57111764</v>
       </c>
       <c r="B80" s="1">
-        <v>46042.557280092595</v>
+        <v>46044.694884259261</v>
       </c>
       <c r="C80">
-        <v>59242054</v>
+        <v>57901159</v>
       </c>
       <c r="D80" s="1">
-        <v>46083.719525462962</v>
+        <v>46059.513090277775</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F80" t="s">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="G80">
-        <v>708667658</v>
+        <v>171161677</v>
       </c>
       <c r="H80" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I80" t="s">
         <v>0</v>
@@ -5466,45 +5499,45 @@
         <v>6</v>
       </c>
       <c r="M80" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N80" t="s">
         <v>0</v>
       </c>
-      <c r="O80" s="2">
-        <v>2871414</v>
+      <c r="O80">
+        <v>0</v>
       </c>
       <c r="P80" t="s">
-        <v>40</v>
+        <v>222</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>57111758</v>
+        <v>57157406</v>
       </c>
       <c r="B81" s="1">
-        <v>46044.694849537038</v>
+        <v>46045.608391203707</v>
       </c>
       <c r="C81">
-        <v>57898966</v>
+        <v>57671501</v>
       </c>
       <c r="D81" s="1">
-        <v>46059.499050925922</v>
+        <v>46055.709131944444</v>
       </c>
       <c r="E81" t="s">
         <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="G81">
-        <v>171161677</v>
+        <v>787682110</v>
       </c>
       <c r="H81" t="s">
         <v>223</v>
       </c>
       <c r="I81">
-        <v>1784416</v>
+        <v>1787266</v>
       </c>
       <c r="J81" t="s">
         <v>4</v>
@@ -5530,28 +5563,28 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>57111764</v>
+        <v>57157435</v>
       </c>
       <c r="B82" s="1">
-        <v>46044.694884259261</v>
+        <v>46045.608460648145</v>
       </c>
       <c r="C82">
-        <v>57901159</v>
+        <v>57671608</v>
       </c>
       <c r="D82" s="1">
-        <v>46059.513090277775</v>
+        <v>46055.709560185183</v>
       </c>
       <c r="E82" t="s">
         <v>16</v>
       </c>
       <c r="F82" t="s">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="G82">
-        <v>171161677</v>
+        <v>787682110</v>
       </c>
       <c r="H82" t="s">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="I82" t="s">
         <v>0</v>
@@ -5575,39 +5608,39 @@
         <v>0</v>
       </c>
       <c r="P82" t="s">
-        <v>225</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>57157406</v>
+        <v>57398181</v>
       </c>
       <c r="B83" s="1">
-        <v>46045.608391203707</v>
+        <v>46050.584374999999</v>
       </c>
       <c r="C83">
-        <v>57671501</v>
+        <v>59095417</v>
       </c>
       <c r="D83" s="1">
-        <v>46055.709131944444</v>
+        <v>46080.738333333335</v>
       </c>
       <c r="E83" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F83" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="G83">
-        <v>787682110</v>
+        <v>720631500</v>
       </c>
       <c r="H83" t="s">
         <v>226</v>
       </c>
-      <c r="I83">
-        <v>1787266</v>
+      <c r="I83" t="s">
+        <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
@@ -5616,139 +5649,139 @@
         <v>6</v>
       </c>
       <c r="M83" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N83" t="s">
         <v>0</v>
       </c>
-      <c r="O83" t="s">
-        <v>0</v>
+      <c r="O83" s="2">
+        <v>4406780</v>
       </c>
       <c r="P83" t="s">
-        <v>227</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>57157435</v>
+        <v>57651441</v>
       </c>
       <c r="B84" s="1">
-        <v>46045.608460648145</v>
+        <v>46055.58011574074</v>
       </c>
       <c r="C84">
-        <v>57671608</v>
+        <v>58955875</v>
       </c>
       <c r="D84" s="1">
-        <v>46055.709560185183</v>
+        <v>46078.639594907407</v>
       </c>
       <c r="E84" t="s">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="F84" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="G84">
-        <v>787682110</v>
+        <v>707079088</v>
       </c>
       <c r="H84" t="s">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="I84" t="s">
         <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K84" t="s">
         <v>5</v>
       </c>
       <c r="L84" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M84" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N84" t="s">
         <v>0</v>
       </c>
-      <c r="O84">
-        <v>0</v>
+      <c r="O84" t="s">
+        <v>229</v>
       </c>
       <c r="P84" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>57398181</v>
+        <v>57651441</v>
       </c>
       <c r="B85" s="1">
-        <v>46050.584374999999</v>
+        <v>46055.58011574074</v>
       </c>
       <c r="C85">
-        <v>59095417</v>
+        <v>59132755</v>
       </c>
       <c r="D85" s="1">
-        <v>46080.738333333335</v>
+        <v>46081.616689814815</v>
       </c>
       <c r="E85" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F85" t="s">
+        <v>227</v>
+      </c>
+      <c r="G85">
+        <v>707079088</v>
+      </c>
+      <c r="H85" t="s">
         <v>228</v>
       </c>
-      <c r="G85">
-        <v>720631500</v>
-      </c>
-      <c r="H85" t="s">
+      <c r="I85" t="s">
+        <v>0</v>
+      </c>
+      <c r="J85" t="s">
+        <v>18</v>
+      </c>
+      <c r="K85" t="s">
+        <v>5</v>
+      </c>
+      <c r="L85" t="s">
+        <v>8</v>
+      </c>
+      <c r="M85" t="s">
+        <v>3</v>
+      </c>
+      <c r="N85" t="s">
+        <v>0</v>
+      </c>
+      <c r="O85" t="s">
         <v>229</v>
       </c>
-      <c r="I85" t="s">
-        <v>0</v>
-      </c>
-      <c r="J85" t="s">
-        <v>13</v>
-      </c>
-      <c r="K85" t="s">
-        <v>5</v>
-      </c>
-      <c r="L85" t="s">
-        <v>6</v>
-      </c>
-      <c r="M85" t="s">
-        <v>3</v>
-      </c>
-      <c r="N85" t="s">
-        <v>0</v>
-      </c>
-      <c r="O85" s="2">
-        <v>4406780</v>
-      </c>
       <c r="P85" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>57651441</v>
+        <v>57664431</v>
       </c>
       <c r="B86" s="1">
-        <v>46055.58011574074</v>
+        <v>46055.665300925924</v>
       </c>
       <c r="C86">
-        <v>58955875</v>
+        <v>59300337</v>
       </c>
       <c r="D86" s="1">
-        <v>46078.639594907407</v>
+        <v>46084.688287037039</v>
       </c>
       <c r="E86" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
       <c r="F86" t="s">
         <v>230</v>
       </c>
       <c r="G86">
-        <v>707079088</v>
+        <v>707966030</v>
       </c>
       <c r="H86" t="s">
         <v>231</v>
@@ -5757,10 +5790,10 @@
         <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K86" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L86" t="s">
         <v>8</v>
@@ -5771,37 +5804,37 @@
       <c r="N86" t="s">
         <v>0</v>
       </c>
-      <c r="O86" t="s">
+      <c r="O86" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="P86" t="s">
         <v>232</v>
-      </c>
-      <c r="P86" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>57651441</v>
+        <v>57672103</v>
       </c>
       <c r="B87" s="1">
-        <v>46055.58011574074</v>
+        <v>46055.712083333332</v>
       </c>
       <c r="C87">
-        <v>59132755</v>
+        <v>58477217</v>
       </c>
       <c r="D87" s="1">
-        <v>46081.616689814815</v>
+        <v>46070.620787037034</v>
       </c>
       <c r="E87" t="s">
-        <v>33</v>
+        <v>194</v>
       </c>
       <c r="F87" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G87">
         <v>707079088</v>
       </c>
       <c r="H87" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I87" t="s">
         <v>0</v>
@@ -5821,93 +5854,93 @@
       <c r="N87" t="s">
         <v>0</v>
       </c>
-      <c r="O87" t="s">
-        <v>232</v>
+      <c r="O87" s="2">
+        <v>1426700</v>
       </c>
       <c r="P87" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>57664431</v>
+        <v>57692887</v>
       </c>
       <c r="B88" s="1">
-        <v>46055.665300925924</v>
+        <v>46056.394780092596</v>
       </c>
       <c r="C88">
-        <v>59202104</v>
+        <v>59278266</v>
       </c>
       <c r="D88" s="1">
-        <v>46083.433159722219</v>
+        <v>46084.516481481478</v>
       </c>
       <c r="E88" t="s">
-        <v>16</v>
+        <v>313</v>
       </c>
       <c r="F88" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G88">
-        <v>707966030</v>
+        <v>707109668</v>
       </c>
       <c r="H88" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I88" t="s">
         <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K88" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L88" t="s">
         <v>8</v>
       </c>
       <c r="M88" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N88" t="s">
         <v>0</v>
       </c>
-      <c r="O88" s="2">
-        <v>2500000</v>
+      <c r="O88" t="s">
+        <v>0</v>
       </c>
       <c r="P88" t="s">
-        <v>235</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>57672103</v>
+        <v>57692887</v>
       </c>
       <c r="B89" s="1">
-        <v>46055.712083333332</v>
+        <v>46056.394780092596</v>
       </c>
       <c r="C89">
-        <v>58477217</v>
+        <v>59278268</v>
       </c>
       <c r="D89" s="1">
-        <v>46070.620787037034</v>
+        <v>46084.516493055555</v>
       </c>
       <c r="E89" t="s">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="F89" t="s">
+        <v>235</v>
+      </c>
+      <c r="G89">
+        <v>707109668</v>
+      </c>
+      <c r="H89" t="s">
         <v>236</v>
       </c>
-      <c r="G89">
-        <v>707079088</v>
-      </c>
-      <c r="H89" t="s">
-        <v>237</v>
-      </c>
       <c r="I89" t="s">
         <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
@@ -5916,54 +5949,54 @@
         <v>8</v>
       </c>
       <c r="M89" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N89" t="s">
         <v>0</v>
       </c>
-      <c r="O89" s="2">
-        <v>1426700</v>
+      <c r="O89" t="s">
+        <v>0</v>
       </c>
       <c r="P89" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>57692887</v>
+        <v>57706849</v>
       </c>
       <c r="B90" s="1">
-        <v>46056.394780092596</v>
+        <v>46056.499166666668</v>
       </c>
       <c r="C90">
-        <v>59095550</v>
+        <v>59220431</v>
       </c>
       <c r="D90" s="1">
-        <v>46080.739837962959</v>
+        <v>46083.561423611114</v>
       </c>
       <c r="E90" t="s">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="F90" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G90">
-        <v>707109668</v>
+        <v>708086472</v>
       </c>
       <c r="H90" t="s">
-        <v>239</v>
+        <v>162</v>
       </c>
       <c r="I90" t="s">
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
       </c>
       <c r="L90" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M90" t="s">
         <v>7</v>
@@ -5971,37 +6004,37 @@
       <c r="N90" t="s">
         <v>0</v>
       </c>
-      <c r="O90" t="s">
+      <c r="O90">
         <v>0</v>
       </c>
       <c r="P90" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>57706849</v>
+        <v>57771694</v>
       </c>
       <c r="B91" s="1">
-        <v>46056.499166666668</v>
+        <v>46057.509652777779</v>
       </c>
       <c r="C91">
-        <v>59220431</v>
+        <v>58091715</v>
       </c>
       <c r="D91" s="1">
-        <v>46083.561423611114</v>
+        <v>46063.566319444442</v>
       </c>
       <c r="E91" t="s">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="F91" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G91">
-        <v>708086472</v>
+        <v>758333146</v>
       </c>
       <c r="H91" t="s">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="I91" t="s">
         <v>0</v>
@@ -6016,42 +6049,42 @@
         <v>6</v>
       </c>
       <c r="M91" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N91" t="s">
         <v>0</v>
       </c>
-      <c r="O91">
-        <v>0</v>
+      <c r="O91" s="2">
+        <v>400000</v>
       </c>
       <c r="P91" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>57771694</v>
+        <v>57773018</v>
       </c>
       <c r="B92" s="1">
-        <v>46057.509652777779</v>
+        <v>46057.517175925925</v>
       </c>
       <c r="C92">
-        <v>58091715</v>
+        <v>59290831</v>
       </c>
       <c r="D92" s="1">
-        <v>46063.566319444442</v>
+        <v>46084.619016203702</v>
       </c>
       <c r="E92" t="s">
-        <v>21</v>
+        <v>348</v>
       </c>
       <c r="F92" t="s">
-        <v>241</v>
+        <v>352</v>
       </c>
       <c r="G92">
         <v>758333146</v>
       </c>
       <c r="H92" t="s">
-        <v>242</v>
+        <v>311</v>
       </c>
       <c r="I92" t="s">
         <v>0</v>
@@ -6060,7 +6093,7 @@
         <v>13</v>
       </c>
       <c r="K92" t="s">
-        <v>5</v>
+        <v>353</v>
       </c>
       <c r="L92" t="s">
         <v>6</v>
@@ -6075,7 +6108,7 @@
         <v>400000</v>
       </c>
       <c r="P92" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.35">
@@ -6095,13 +6128,13 @@
         <v>26</v>
       </c>
       <c r="F93" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G93">
         <v>708075673</v>
       </c>
       <c r="H93" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I93" t="s">
         <v>0</v>
@@ -6136,16 +6169,16 @@
         <v>46058.589849537035</v>
       </c>
       <c r="C94">
-        <v>58975552</v>
+        <v>59287862</v>
       </c>
       <c r="D94" s="1">
-        <v>46078.883587962962</v>
+        <v>46084.599965277775</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>355</v>
       </c>
       <c r="F94" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G94">
         <v>757233377</v>
@@ -6175,7 +6208,7 @@
         <v>485500</v>
       </c>
       <c r="P94" t="s">
-        <v>27</v>
+        <v>354</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.35">
@@ -6195,13 +6228,13 @@
         <v>21</v>
       </c>
       <c r="F95" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G95">
         <v>707109668</v>
       </c>
       <c r="H95" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I95" t="s">
         <v>0</v>
@@ -6225,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="P95" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.35">
@@ -6236,16 +6269,16 @@
         <v>46058.739907407406</v>
       </c>
       <c r="C96">
-        <v>59238582</v>
+        <v>59246699</v>
       </c>
       <c r="D96" s="1">
-        <v>46083.694907407407</v>
+        <v>46083.767824074072</v>
       </c>
       <c r="E96" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F96" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G96">
         <v>575480452</v>
@@ -6275,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="P96" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.35">
@@ -6286,16 +6319,16 @@
         <v>46058.739907407406</v>
       </c>
       <c r="C97">
-        <v>59246699</v>
+        <v>59302399</v>
       </c>
       <c r="D97" s="1">
-        <v>46083.767824074072</v>
+        <v>46084.702094907407</v>
       </c>
       <c r="E97" t="s">
-        <v>33</v>
+        <v>335</v>
       </c>
       <c r="F97" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G97">
         <v>575480452</v>
@@ -6325,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="P97" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.35">
@@ -6342,7 +6375,7 @@
         <v>46080.432372685187</v>
       </c>
       <c r="E98" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F98" t="s">
         <v>153</v>
@@ -6351,7 +6384,7 @@
         <v>505980067</v>
       </c>
       <c r="H98" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I98" t="s">
         <v>0</v>
@@ -6375,7 +6408,7 @@
         <v>1002937</v>
       </c>
       <c r="P98" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.35">
@@ -6395,13 +6428,13 @@
         <v>16</v>
       </c>
       <c r="F99" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G99">
         <v>505980067</v>
       </c>
       <c r="H99" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I99">
         <v>1811806</v>
@@ -6425,7 +6458,7 @@
         <v>1388682</v>
       </c>
       <c r="P99" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.35">
@@ -6445,13 +6478,13 @@
         <v>21</v>
       </c>
       <c r="F100" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G100">
         <v>575750228</v>
       </c>
       <c r="H100" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I100" t="s">
         <v>0</v>
@@ -6495,13 +6528,13 @@
         <v>86</v>
       </c>
       <c r="F101" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G101">
         <v>708392808</v>
       </c>
       <c r="H101" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I101" t="s">
         <v>0</v>
@@ -6545,13 +6578,13 @@
         <v>21</v>
       </c>
       <c r="F102" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G102">
         <v>758224257</v>
       </c>
       <c r="H102" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I102" t="s">
         <v>0</v>
@@ -6586,13 +6619,13 @@
         <v>46063.583402777775</v>
       </c>
       <c r="C103">
-        <v>59199883</v>
+        <v>59292813</v>
       </c>
       <c r="D103" s="1">
-        <v>46083.415011574078</v>
+        <v>46084.631550925929</v>
       </c>
       <c r="E103" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F103" t="s">
         <v>47</v>
@@ -6601,7 +6634,7 @@
         <v>708086759</v>
       </c>
       <c r="H103" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I103" t="s">
         <v>0</v>
@@ -6625,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="P103" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.35">
@@ -6651,7 +6684,7 @@
         <v>708086759</v>
       </c>
       <c r="H104" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I104" t="s">
         <v>0</v>
@@ -6675,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="P104" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.35">
@@ -6701,7 +6734,7 @@
         <v>708086759</v>
       </c>
       <c r="H105" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I105" t="s">
         <v>0</v>
@@ -6725,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="P105" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.35">
@@ -6751,7 +6784,7 @@
         <v>708086759</v>
       </c>
       <c r="H106" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I106" t="s">
         <v>0</v>
@@ -6775,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="P106" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.35">
@@ -6795,13 +6828,13 @@
         <v>20</v>
       </c>
       <c r="F107" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G107">
         <v>707109668</v>
       </c>
       <c r="H107" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I107" t="s">
         <v>0</v>
@@ -6836,31 +6869,31 @@
         <v>46064.471539351849</v>
       </c>
       <c r="C108">
-        <v>59234418</v>
+        <v>59289848</v>
       </c>
       <c r="D108" s="1">
-        <v>46083.662442129629</v>
+        <v>46084.612673611111</v>
       </c>
       <c r="E108" t="s">
-        <v>269</v>
+        <v>335</v>
       </c>
       <c r="F108" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G108">
         <v>757687227</v>
       </c>
       <c r="H108" t="s">
-        <v>268</v>
-      </c>
-      <c r="I108" t="s">
-        <v>0</v>
+        <v>356</v>
+      </c>
+      <c r="I108">
+        <v>1810436</v>
       </c>
       <c r="J108" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K108" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L108" t="s">
         <v>6</v>
@@ -6875,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="P108" t="s">
-        <v>35</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.35">
@@ -6895,13 +6928,13 @@
         <v>21</v>
       </c>
       <c r="F109" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G109">
         <v>2722418166</v>
       </c>
       <c r="H109" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I109" t="s">
         <v>0</v>
@@ -6936,13 +6969,13 @@
         <v>46064.520543981482</v>
       </c>
       <c r="C110">
-        <v>59212080</v>
+        <v>59286573</v>
       </c>
       <c r="D110" s="1">
-        <v>46083.504467592589</v>
+        <v>46084.588842592595</v>
       </c>
       <c r="E110" t="s">
-        <v>29</v>
+        <v>335</v>
       </c>
       <c r="F110" t="s">
         <v>24</v>
@@ -6951,7 +6984,7 @@
         <v>779491369</v>
       </c>
       <c r="H110" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="I110" t="s">
         <v>0</v>
@@ -6960,7 +6993,7 @@
         <v>18</v>
       </c>
       <c r="K110" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L110" t="s">
         <v>8</v>
@@ -6975,7 +7008,7 @@
         <v>2000000</v>
       </c>
       <c r="P110" t="s">
-        <v>27</v>
+        <v>358</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.35">
@@ -6995,13 +7028,13 @@
         <v>21</v>
       </c>
       <c r="F111" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G111">
         <v>2721271444</v>
       </c>
       <c r="H111" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I111" t="s">
         <v>0</v>
@@ -7036,28 +7069,28 @@
         <v>46064.629108796296</v>
       </c>
       <c r="C112">
-        <v>59242483</v>
+        <v>59285100</v>
       </c>
       <c r="D112" s="1">
-        <v>46083.722986111112</v>
+        <v>46084.573321759257</v>
       </c>
       <c r="E112" t="s">
-        <v>269</v>
+        <v>335</v>
       </c>
       <c r="F112" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G112">
         <v>504001081</v>
       </c>
       <c r="H112" t="s">
-        <v>275</v>
-      </c>
-      <c r="I112">
-        <v>1814806</v>
+        <v>359</v>
+      </c>
+      <c r="I112" t="s">
+        <v>0</v>
       </c>
       <c r="J112" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K112" t="s">
         <v>9</v>
@@ -7066,7 +7099,7 @@
         <v>6</v>
       </c>
       <c r="M112" t="s">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="N112" t="s">
         <v>0</v>
@@ -7075,7 +7108,7 @@
         <v>0</v>
       </c>
       <c r="P112" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.35">
@@ -7095,7 +7128,7 @@
         <v>21</v>
       </c>
       <c r="F113" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G113">
         <v>504041812</v>
@@ -7145,7 +7178,7 @@
         <v>21</v>
       </c>
       <c r="F114" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G114">
         <v>707501026</v>
@@ -7192,16 +7225,16 @@
         <v>46069.532650462963</v>
       </c>
       <c r="E115" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F115" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G115">
         <v>504041812</v>
       </c>
       <c r="H115" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I115" t="s">
         <v>0</v>
@@ -7225,7 +7258,7 @@
         <v>2000000</v>
       </c>
       <c r="P115" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.35">
@@ -7245,13 +7278,13 @@
         <v>33</v>
       </c>
       <c r="F116" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="G116">
         <v>504001081</v>
       </c>
       <c r="H116" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="I116">
         <v>1810836</v>
@@ -7275,7 +7308,7 @@
         <v>0</v>
       </c>
       <c r="P116" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.35">
@@ -7286,22 +7319,22 @@
         <v>46064.700439814813</v>
       </c>
       <c r="C117">
-        <v>59246828</v>
+        <v>59282926</v>
       </c>
       <c r="D117" s="1">
-        <v>46083.769409722219</v>
+        <v>46084.553611111114</v>
       </c>
       <c r="E117" t="s">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="F117" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="G117">
         <v>504001081</v>
       </c>
       <c r="H117" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="I117">
         <v>1810836</v>
@@ -7325,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.35">
@@ -7345,13 +7378,13 @@
         <v>21</v>
       </c>
       <c r="F118" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G118">
         <v>3365190695</v>
       </c>
       <c r="H118" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="I118" t="s">
         <v>0</v>
@@ -7375,7 +7408,7 @@
         <v>600000</v>
       </c>
       <c r="P118" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.35">
@@ -7386,22 +7419,22 @@
         <v>46065.449108796296</v>
       </c>
       <c r="C119">
-        <v>59239902</v>
+        <v>59299112</v>
       </c>
       <c r="D119" s="1">
-        <v>46083.704340277778</v>
+        <v>46084.675844907404</v>
       </c>
       <c r="E119" t="s">
-        <v>21</v>
+        <v>313</v>
       </c>
       <c r="F119" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="G119">
         <v>504001081</v>
       </c>
       <c r="H119" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="I119" t="s">
         <v>0</v>
@@ -7410,7 +7443,7 @@
         <v>13</v>
       </c>
       <c r="K119" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L119" t="s">
         <v>6</v>
@@ -7425,33 +7458,33 @@
         <v>0</v>
       </c>
       <c r="P119" t="s">
-        <v>35</v>
+        <v>360</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120">
-        <v>58227435</v>
+        <v>58205267</v>
       </c>
       <c r="B120" s="1">
-        <v>46065.628240740742</v>
+        <v>46065.449108796296</v>
       </c>
       <c r="C120">
-        <v>59202194</v>
+        <v>59300372</v>
       </c>
       <c r="D120" s="1">
-        <v>46083.433807870373</v>
+        <v>46084.688136574077</v>
       </c>
       <c r="E120" t="s">
-        <v>16</v>
+        <v>361</v>
       </c>
       <c r="F120" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="G120">
         <v>504001081</v>
       </c>
       <c r="H120" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="I120" t="s">
         <v>0</v>
@@ -7460,7 +7493,7 @@
         <v>13</v>
       </c>
       <c r="K120" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L120" t="s">
         <v>6</v>
@@ -7475,33 +7508,33 @@
         <v>0</v>
       </c>
       <c r="P120" t="s">
-        <v>27</v>
+        <v>360</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121">
-        <v>58272102</v>
+        <v>58227435</v>
       </c>
       <c r="B121" s="1">
-        <v>46066.506493055553</v>
+        <v>46065.628240740742</v>
       </c>
       <c r="C121">
-        <v>59200672</v>
+        <v>59202194</v>
       </c>
       <c r="D121" s="1">
-        <v>46083.421655092592</v>
+        <v>46083.433807870373</v>
       </c>
       <c r="E121" t="s">
         <v>16</v>
       </c>
       <c r="F121" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="G121">
-        <v>707338900</v>
+        <v>504001081</v>
       </c>
       <c r="H121" t="s">
-        <v>162</v>
+        <v>280</v>
       </c>
       <c r="I121" t="s">
         <v>0</v>
@@ -7510,7 +7543,7 @@
         <v>13</v>
       </c>
       <c r="K121" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L121" t="s">
         <v>6</v>
@@ -7521,37 +7554,37 @@
       <c r="N121" t="s">
         <v>0</v>
       </c>
-      <c r="O121" s="2">
-        <v>750000</v>
+      <c r="O121">
+        <v>0</v>
       </c>
       <c r="P121" t="s">
-        <v>289</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>58274609</v>
+        <v>58272102</v>
       </c>
       <c r="B122" s="1">
-        <v>46066.525011574071</v>
+        <v>46066.506493055553</v>
       </c>
       <c r="C122">
-        <v>59264178</v>
+        <v>59200672</v>
       </c>
       <c r="D122" s="1">
-        <v>46084.406759259262</v>
+        <v>46083.421655092592</v>
       </c>
       <c r="E122" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F122" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G122">
-        <v>2722480700</v>
+        <v>707338900</v>
       </c>
       <c r="H122" t="s">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="I122" t="s">
         <v>0</v>
@@ -7560,7 +7593,7 @@
         <v>13</v>
       </c>
       <c r="K122" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L122" t="s">
         <v>6</v>
@@ -7572,48 +7605,48 @@
         <v>0</v>
       </c>
       <c r="O122" s="2">
-        <v>522590</v>
+        <v>750000</v>
       </c>
       <c r="P122" t="s">
-        <v>43</v>
+        <v>282</v>
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123">
-        <v>58276534</v>
+        <v>58274609</v>
       </c>
       <c r="B123" s="1">
-        <v>46066.539675925924</v>
+        <v>46066.525011574071</v>
       </c>
       <c r="C123">
-        <v>59213687</v>
+        <v>59264178</v>
       </c>
       <c r="D123" s="1">
-        <v>46083.515196759261</v>
+        <v>46084.406759259262</v>
       </c>
       <c r="E123" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="F123" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G123">
-        <v>777308038</v>
+        <v>2722480700</v>
       </c>
       <c r="H123" t="s">
-        <v>292</v>
+        <v>45</v>
       </c>
       <c r="I123" t="s">
         <v>0</v>
       </c>
       <c r="J123" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K123" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="L123" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M123" t="s">
         <v>3</v>
@@ -7621,46 +7654,46 @@
       <c r="N123" t="s">
         <v>0</v>
       </c>
-      <c r="O123" t="s">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>2723489370</v>
+      <c r="O123" s="2">
+        <v>522590</v>
+      </c>
+      <c r="P123" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124">
-        <v>58407509</v>
+        <v>58276534</v>
       </c>
       <c r="B124" s="1">
-        <v>46069.545914351853</v>
+        <v>46066.539675925924</v>
       </c>
       <c r="C124">
-        <v>59257892</v>
+        <v>59213687</v>
       </c>
       <c r="D124" s="1">
-        <v>46084.33421296296</v>
+        <v>46083.515196759261</v>
       </c>
       <c r="E124" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="F124" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="G124">
-        <v>709213314</v>
+        <v>777308038</v>
       </c>
       <c r="H124" t="s">
-        <v>162</v>
+        <v>285</v>
       </c>
       <c r="I124" t="s">
         <v>0</v>
       </c>
       <c r="J124" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="K124" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L124" t="s">
         <v>2</v>
@@ -7674,40 +7707,40 @@
       <c r="O124" t="s">
         <v>0</v>
       </c>
-      <c r="P124" t="s">
-        <v>36</v>
+      <c r="P124">
+        <v>2723489370</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125">
-        <v>58420580</v>
+        <v>58407509</v>
       </c>
       <c r="B125" s="1">
-        <v>46069.648148148146</v>
+        <v>46069.545914351853</v>
       </c>
       <c r="C125">
-        <v>59241630</v>
+        <v>59257892</v>
       </c>
       <c r="D125" s="1">
-        <v>46083.715162037035</v>
+        <v>46084.33421296296</v>
       </c>
       <c r="E125" t="s">
         <v>21</v>
       </c>
       <c r="F125" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="G125">
-        <v>749857975</v>
+        <v>709213314</v>
       </c>
       <c r="H125" t="s">
-        <v>295</v>
+        <v>162</v>
       </c>
       <c r="I125" t="s">
         <v>0</v>
       </c>
       <c r="J125" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="K125" t="s">
         <v>1</v>
@@ -7725,33 +7758,33 @@
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126">
-        <v>58476260</v>
+        <v>58420580</v>
       </c>
       <c r="B126" s="1">
-        <v>46070.61273148148</v>
+        <v>46069.648148148146</v>
       </c>
       <c r="C126">
-        <v>59229324</v>
+        <v>59241630</v>
       </c>
       <c r="D126" s="1">
-        <v>46083.62572916667</v>
+        <v>46083.715162037035</v>
       </c>
       <c r="E126" t="s">
-        <v>299</v>
+        <v>21</v>
       </c>
       <c r="F126" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="G126">
-        <v>708526165</v>
+        <v>749857975</v>
       </c>
       <c r="H126" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I126" t="s">
         <v>0</v>
@@ -7775,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>298</v>
+        <v>35</v>
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.35">
@@ -7786,22 +7819,22 @@
         <v>46070.61273148148</v>
       </c>
       <c r="C127">
-        <v>59229320</v>
+        <v>59291043</v>
       </c>
       <c r="D127" s="1">
-        <v>46083.625717592593</v>
+        <v>46084.62027777778</v>
       </c>
       <c r="E127" t="s">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="F127" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="G127">
         <v>708526165</v>
       </c>
       <c r="H127" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="I127" t="s">
         <v>0</v>
@@ -7810,7 +7843,7 @@
         <v>25</v>
       </c>
       <c r="K127" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L127" t="s">
         <v>2</v>
@@ -7825,7 +7858,7 @@
         <v>0</v>
       </c>
       <c r="P127" t="s">
-        <v>298</v>
+        <v>260</v>
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.35">
@@ -7845,13 +7878,13 @@
         <v>21</v>
       </c>
       <c r="F128" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="G128">
         <v>767154815</v>
       </c>
       <c r="H128" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="I128" t="s">
         <v>0</v>
@@ -7875,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="P128" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.35">
@@ -7886,16 +7919,16 @@
         <v>46072.455555555556</v>
       </c>
       <c r="C129">
-        <v>59227820</v>
+        <v>59244907</v>
       </c>
       <c r="D129" s="1">
-        <v>46083.616736111115</v>
+        <v>46083.744629629633</v>
       </c>
       <c r="E129" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F129" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="G129">
         <v>707965430</v>
@@ -7910,7 +7943,7 @@
         <v>25</v>
       </c>
       <c r="K129" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L129" t="s">
         <v>2</v>
@@ -7924,8 +7957,8 @@
       <c r="O129" t="s">
         <v>0</v>
       </c>
-      <c r="P129" t="s">
-        <v>40</v>
+      <c r="P129">
+        <v>2722229950</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.35">
@@ -7936,16 +7969,16 @@
         <v>46072.455555555556</v>
       </c>
       <c r="C130">
-        <v>59244907</v>
+        <v>59299403</v>
       </c>
       <c r="D130" s="1">
-        <v>46083.744629629633</v>
+        <v>46084.678333333337</v>
       </c>
       <c r="E130" t="s">
-        <v>33</v>
+        <v>351</v>
       </c>
       <c r="F130" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="G130">
         <v>707965430</v>
@@ -7960,7 +7993,7 @@
         <v>25</v>
       </c>
       <c r="K130" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L130" t="s">
         <v>2</v>
@@ -7974,8 +8007,8 @@
       <c r="O130" t="s">
         <v>0</v>
       </c>
-      <c r="P130" t="s">
-        <v>40</v>
+      <c r="P130">
+        <v>2722229950</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.35">
@@ -7995,13 +8028,13 @@
         <v>21</v>
       </c>
       <c r="F131" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="G131">
         <v>709574114</v>
       </c>
       <c r="H131" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="I131" t="s">
         <v>0</v>
@@ -8042,10 +8075,10 @@
         <v>46083.67386574074</v>
       </c>
       <c r="E132" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F132" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="G132">
         <v>759250737</v>
@@ -8095,7 +8128,7 @@
         <v>21</v>
       </c>
       <c r="F133" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="G133">
         <v>759250737</v>
@@ -8145,7 +8178,7 @@
         <v>21</v>
       </c>
       <c r="F134" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="G134">
         <v>759250737</v>
@@ -8175,7 +8208,7 @@
         <v>0</v>
       </c>
       <c r="P134" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.35">
@@ -8192,10 +8225,10 @@
         <v>46083.555219907408</v>
       </c>
       <c r="E135" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F135" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="G135">
         <v>759250737</v>
@@ -8245,7 +8278,7 @@
         <v>21</v>
       </c>
       <c r="F136" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="G136">
         <v>759250737</v>
@@ -8295,13 +8328,13 @@
         <v>21</v>
       </c>
       <c r="F137" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="G137">
         <v>708193864</v>
       </c>
       <c r="H137" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="I137" t="s">
         <v>0</v>
@@ -8345,13 +8378,13 @@
         <v>21</v>
       </c>
       <c r="F138" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="G138">
         <v>767093390</v>
       </c>
       <c r="H138" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I138" t="s">
         <v>0</v>
@@ -8392,16 +8425,16 @@
         <v>46083.634050925924</v>
       </c>
       <c r="E139" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F139" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="G139">
         <v>102224907</v>
       </c>
       <c r="H139" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="I139" t="s">
         <v>0</v>
@@ -8442,16 +8475,16 @@
         <v>46083.684444444443</v>
       </c>
       <c r="E140" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F140" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="G140">
         <v>749994094</v>
       </c>
       <c r="H140" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="I140" t="s">
         <v>0</v>
@@ -8475,7 +8508,7 @@
         <v>2000000</v>
       </c>
       <c r="P140" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.35">
@@ -8495,13 +8528,13 @@
         <v>21</v>
       </c>
       <c r="F141" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="G141">
         <v>556374989</v>
       </c>
       <c r="H141" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="I141" t="s">
         <v>0</v>
@@ -8545,13 +8578,13 @@
         <v>21</v>
       </c>
       <c r="F142" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="G142">
         <v>586654060</v>
       </c>
       <c r="H142" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="I142" t="s">
         <v>0</v>
@@ -8595,13 +8628,13 @@
         <v>21</v>
       </c>
       <c r="F143" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="G143">
         <v>708086472</v>
       </c>
       <c r="H143" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="I143">
         <v>1825816</v>
@@ -8642,16 +8675,16 @@
         <v>46083.68540509259</v>
       </c>
       <c r="E144" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F144" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G144">
         <v>708086472</v>
       </c>
       <c r="H144" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I144" t="s">
         <v>0</v>
@@ -8695,13 +8728,13 @@
         <v>33</v>
       </c>
       <c r="F145" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G145">
         <v>708086472</v>
       </c>
       <c r="H145" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="I145" t="s">
         <v>0</v>
@@ -8725,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="P145" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.35">
@@ -8736,22 +8769,22 @@
         <v>46076.670810185184</v>
       </c>
       <c r="C146">
-        <v>59266530</v>
+        <v>59299539</v>
       </c>
       <c r="D146" s="1">
-        <v>46084.429166666669</v>
+        <v>46084.679537037038</v>
       </c>
       <c r="E146" t="s">
-        <v>269</v>
+        <v>29</v>
       </c>
       <c r="F146" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G146">
         <v>708086472</v>
       </c>
       <c r="H146" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="I146" t="s">
         <v>0</v>
@@ -8775,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="P146" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.35">
@@ -8792,16 +8825,16 @@
         <v>46084.392627314817</v>
       </c>
       <c r="E147" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="F147" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G147">
         <v>708086472</v>
       </c>
       <c r="H147" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="I147" t="s">
         <v>0</v>
@@ -8845,13 +8878,13 @@
         <v>20</v>
       </c>
       <c r="F148" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G148">
         <v>708086472</v>
       </c>
       <c r="H148" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="I148" t="s">
         <v>0</v>
@@ -8895,13 +8928,13 @@
         <v>21</v>
       </c>
       <c r="F149" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="G149">
         <v>708086472</v>
       </c>
       <c r="H149" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="I149">
         <v>1825416</v>
@@ -8945,13 +8978,13 @@
         <v>21</v>
       </c>
       <c r="F150" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="G150">
         <v>708086472</v>
       </c>
       <c r="H150" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I150">
         <v>1825206</v>
@@ -8986,16 +9019,16 @@
         <v>46076.679837962962</v>
       </c>
       <c r="C151">
-        <v>59241891</v>
+        <v>59245117</v>
       </c>
       <c r="D151" s="1">
-        <v>46083.717824074076</v>
+        <v>46083.746898148151</v>
       </c>
       <c r="E151" t="s">
-        <v>269</v>
+        <v>33</v>
       </c>
       <c r="F151" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G151">
         <v>708086472</v>
@@ -9010,7 +9043,7 @@
         <v>18</v>
       </c>
       <c r="K151" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L151" t="s">
         <v>8</v>
@@ -9025,7 +9058,7 @@
         <v>543324</v>
       </c>
       <c r="P151" t="s">
-        <v>12</v>
+        <v>362</v>
       </c>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.35">
@@ -9036,16 +9069,16 @@
         <v>46076.679837962962</v>
       </c>
       <c r="C152">
-        <v>59245117</v>
+        <v>59285687</v>
       </c>
       <c r="D152" s="1">
-        <v>46083.746898148151</v>
+        <v>46084.578483796293</v>
       </c>
       <c r="E152" t="s">
-        <v>33</v>
+        <v>335</v>
       </c>
       <c r="F152" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G152">
         <v>708086472</v>
@@ -9060,7 +9093,7 @@
         <v>18</v>
       </c>
       <c r="K152" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L152" t="s">
         <v>8</v>
@@ -9075,7 +9108,7 @@
         <v>543324</v>
       </c>
       <c r="P152" t="s">
-        <v>12</v>
+        <v>362</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.35">
@@ -9095,13 +9128,13 @@
         <v>21</v>
       </c>
       <c r="F153" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="G153">
         <v>748377555</v>
       </c>
       <c r="H153" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="I153" t="s">
         <v>0</v>
@@ -9125,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="P153" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.35">
@@ -9142,16 +9175,16 @@
         <v>46084.401979166665</v>
       </c>
       <c r="E154" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="F154" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="G154">
         <v>748377555</v>
       </c>
       <c r="H154" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="I154" t="s">
         <v>0</v>
@@ -9160,7 +9193,7 @@
         <v>18</v>
       </c>
       <c r="K154" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L154" t="s">
         <v>8</v>
@@ -9175,7 +9208,7 @@
         <v>5324000</v>
       </c>
       <c r="P154" t="s">
-        <v>35</v>
+        <v>363</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.35">
@@ -9186,22 +9219,22 @@
         <v>46077.398726851854</v>
       </c>
       <c r="C155">
-        <v>59263648</v>
+        <v>59304742</v>
       </c>
       <c r="D155" s="1">
-        <v>46084.401979166665</v>
+        <v>46084.722280092596</v>
       </c>
       <c r="E155" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="F155" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="G155">
         <v>748377555</v>
       </c>
       <c r="H155" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="I155" t="s">
         <v>0</v>
@@ -9210,7 +9243,7 @@
         <v>18</v>
       </c>
       <c r="K155" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L155" t="s">
         <v>8</v>
@@ -9225,7 +9258,7 @@
         <v>5324000</v>
       </c>
       <c r="P155" t="s">
-        <v>35</v>
+        <v>363</v>
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.35">
@@ -9245,7 +9278,7 @@
         <v>76</v>
       </c>
       <c r="F156" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="G156">
         <v>748377555</v>
@@ -9295,7 +9328,7 @@
         <v>76</v>
       </c>
       <c r="F157" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="G157">
         <v>748377555</v>
@@ -9345,13 +9378,13 @@
         <v>76</v>
       </c>
       <c r="F158" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="G158">
         <v>748377555</v>
       </c>
       <c r="H158" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="I158" t="s">
         <v>0</v>
@@ -9395,13 +9428,13 @@
         <v>76</v>
       </c>
       <c r="F159" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="G159">
         <v>748377555</v>
       </c>
       <c r="H159" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="I159" t="s">
         <v>0</v>
@@ -9445,13 +9478,13 @@
         <v>76</v>
       </c>
       <c r="F160" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="G160">
         <v>748377555</v>
       </c>
       <c r="H160" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="I160" t="s">
         <v>0</v>
@@ -9495,13 +9528,13 @@
         <v>76</v>
       </c>
       <c r="F161" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="G161">
         <v>748377555</v>
       </c>
       <c r="H161" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="I161" t="s">
         <v>0</v>
@@ -9525,7 +9558,7 @@
         <v>5324000</v>
       </c>
       <c r="P161" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
     </row>
     <row r="162" spans="1:16" x14ac:dyDescent="0.35">
@@ -9545,13 +9578,13 @@
         <v>76</v>
       </c>
       <c r="F162" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="G162">
         <v>748377555</v>
       </c>
       <c r="H162" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="I162" t="s">
         <v>0</v>
@@ -9595,13 +9628,13 @@
         <v>76</v>
       </c>
       <c r="F163" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="G163">
         <v>748377555</v>
       </c>
       <c r="H163" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="I163" t="s">
         <v>0</v>
@@ -9645,13 +9678,13 @@
         <v>76</v>
       </c>
       <c r="F164" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G164">
         <v>748377555</v>
       </c>
       <c r="H164" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="I164" t="s">
         <v>0</v>
@@ -9675,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="P164" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="165" spans="1:16" x14ac:dyDescent="0.35">
@@ -9695,13 +9728,13 @@
         <v>76</v>
       </c>
       <c r="F165" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G165">
         <v>748377555</v>
       </c>
       <c r="H165" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="I165" t="s">
         <v>0</v>
@@ -9745,13 +9778,13 @@
         <v>76</v>
       </c>
       <c r="F166" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G166">
         <v>748377507</v>
       </c>
       <c r="H166" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="I166" t="s">
         <v>0</v>
@@ -9795,13 +9828,13 @@
         <v>76</v>
       </c>
       <c r="F167" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G167">
         <v>748377507</v>
       </c>
       <c r="H167" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="I167" t="s">
         <v>0</v>
@@ -9845,13 +9878,13 @@
         <v>76</v>
       </c>
       <c r="F168" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G168">
         <v>748377555</v>
       </c>
       <c r="H168" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="I168" t="s">
         <v>0</v>
@@ -9875,7 +9908,7 @@
         <v>0</v>
       </c>
       <c r="P168" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.35">
@@ -9895,13 +9928,13 @@
         <v>76</v>
       </c>
       <c r="F169" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G169">
         <v>748377555</v>
       </c>
       <c r="H169" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="I169" t="s">
         <v>0</v>
@@ -9945,13 +9978,13 @@
         <v>76</v>
       </c>
       <c r="F170" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G170">
         <v>748377555</v>
       </c>
       <c r="H170" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="I170" t="s">
         <v>0</v>
@@ -9995,13 +10028,13 @@
         <v>76</v>
       </c>
       <c r="F171" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="G171">
         <v>748377555</v>
       </c>
       <c r="H171" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="I171" t="s">
         <v>0</v>
@@ -10036,22 +10069,22 @@
         <v>46077.724490740744</v>
       </c>
       <c r="C172">
-        <v>59247429</v>
+        <v>59294681</v>
       </c>
       <c r="D172" s="1">
-        <v>46083.776296296295</v>
+        <v>46084.643576388888</v>
       </c>
       <c r="E172" t="s">
-        <v>344</v>
+        <v>86</v>
       </c>
       <c r="F172" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="G172">
         <v>707966030</v>
       </c>
       <c r="H172" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="I172">
         <v>1828806</v>
@@ -10075,7 +10108,7 @@
         <v>2400000</v>
       </c>
       <c r="P172" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.35">
@@ -10092,16 +10125,16 @@
         <v>46084.424537037034</v>
       </c>
       <c r="E173" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F173" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="G173">
         <v>708641473</v>
       </c>
       <c r="H173" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="I173" t="s">
         <v>0</v>
@@ -10125,7 +10158,7 @@
         <v>0</v>
       </c>
       <c r="P173" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.35">
@@ -10136,22 +10169,22 @@
         <v>46078.472939814812</v>
       </c>
       <c r="C174">
-        <v>59234437</v>
+        <v>59305391</v>
       </c>
       <c r="D174" s="1">
-        <v>46083.662291666667</v>
+        <v>46084.727511574078</v>
       </c>
       <c r="E174" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F174" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="G174">
         <v>502787892</v>
       </c>
       <c r="H174" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="I174" t="s">
         <v>0</v>
@@ -10174,8 +10207,8 @@
       <c r="O174" t="s">
         <v>0</v>
       </c>
-      <c r="P174" t="s">
-        <v>82</v>
+      <c r="P174">
+        <v>2722229955</v>
       </c>
     </row>
     <row r="175" spans="1:16" x14ac:dyDescent="0.35">
@@ -10186,22 +10219,22 @@
         <v>46078.611458333333</v>
       </c>
       <c r="C175">
-        <v>59232537</v>
+        <v>59290449</v>
       </c>
       <c r="D175" s="1">
-        <v>46083.648726851854</v>
+        <v>46084.616898148146</v>
       </c>
       <c r="E175" t="s">
-        <v>299</v>
+        <v>29</v>
       </c>
       <c r="F175" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="G175">
         <v>709565662</v>
       </c>
       <c r="H175" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="I175" t="s">
         <v>0</v>
@@ -10225,33 +10258,33 @@
         <v>0</v>
       </c>
       <c r="P175" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176">
-        <v>58951364</v>
+        <v>58952151</v>
       </c>
       <c r="B176" s="1">
-        <v>46078.611458333333</v>
+        <v>46078.615104166667</v>
       </c>
       <c r="C176">
-        <v>59232533</v>
+        <v>59290426</v>
       </c>
       <c r="D176" s="1">
-        <v>46083.648715277777</v>
+        <v>46084.616666666669</v>
       </c>
       <c r="E176" t="s">
-        <v>269</v>
+        <v>86</v>
       </c>
       <c r="F176" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="G176">
         <v>709565662</v>
       </c>
       <c r="H176" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="I176" t="s">
         <v>0</v>
@@ -10274,46 +10307,46 @@
       <c r="O176" t="s">
         <v>0</v>
       </c>
-      <c r="P176" t="s">
-        <v>332</v>
+      <c r="P176">
+        <v>2721712030</v>
       </c>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177">
-        <v>58952151</v>
+        <v>58959238</v>
       </c>
       <c r="B177" s="1">
-        <v>46078.615104166667</v>
+        <v>46078.665532407409</v>
       </c>
       <c r="C177">
-        <v>59231347</v>
+        <v>59295526</v>
       </c>
       <c r="D177" s="1">
-        <v>46083.641064814816</v>
+        <v>46084.649004629631</v>
       </c>
       <c r="E177" t="s">
-        <v>299</v>
+        <v>199</v>
       </c>
       <c r="F177" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="G177">
-        <v>709565662</v>
+        <v>708641473</v>
       </c>
       <c r="H177" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="I177" t="s">
         <v>0</v>
       </c>
       <c r="J177" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="K177" t="s">
         <v>5</v>
       </c>
       <c r="L177" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M177" t="s">
         <v>3</v>
@@ -10321,52 +10354,52 @@
       <c r="N177" t="s">
         <v>0</v>
       </c>
-      <c r="O177" t="s">
-        <v>0</v>
-      </c>
-      <c r="P177">
-        <v>2721712030</v>
+      <c r="O177" s="2">
+        <v>850000</v>
+      </c>
+      <c r="P177" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178">
-        <v>58952151</v>
+        <v>58963630</v>
       </c>
       <c r="B178" s="1">
-        <v>46078.615104166667</v>
+        <v>46078.697002314817</v>
       </c>
       <c r="C178">
-        <v>59231345</v>
+        <v>59280973</v>
       </c>
       <c r="D178" s="1">
-        <v>46083.641064814816</v>
+        <v>46084.538611111115</v>
       </c>
       <c r="E178" t="s">
-        <v>269</v>
+        <v>361</v>
       </c>
       <c r="F178" t="s">
-        <v>348</v>
+        <v>50</v>
       </c>
       <c r="G178">
-        <v>709565662</v>
+        <v>747726344</v>
       </c>
       <c r="H178" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="I178" t="s">
         <v>0</v>
       </c>
       <c r="J178" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="K178" t="s">
         <v>5</v>
       </c>
       <c r="L178" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M178" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N178" t="s">
         <v>0</v>
@@ -10374,34 +10407,34 @@
       <c r="O178" t="s">
         <v>0</v>
       </c>
-      <c r="P178">
-        <v>2721712030</v>
+      <c r="P178" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179">
-        <v>58959238</v>
+        <v>58963646</v>
       </c>
       <c r="B179" s="1">
-        <v>46078.665532407409</v>
+        <v>46078.697048611109</v>
       </c>
       <c r="C179">
-        <v>58961094</v>
+        <v>59281151</v>
       </c>
       <c r="D179" s="1">
-        <v>46078.6797337963</v>
+        <v>46084.540462962963</v>
       </c>
       <c r="E179" t="s">
-        <v>115</v>
+        <v>361</v>
       </c>
       <c r="F179" t="s">
-        <v>345</v>
+        <v>50</v>
       </c>
       <c r="G179">
-        <v>708641473</v>
+        <v>747726344</v>
       </c>
       <c r="H179" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="I179" t="s">
         <v>0</v>
@@ -10416,57 +10449,57 @@
         <v>6</v>
       </c>
       <c r="M179" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N179" t="s">
         <v>0</v>
       </c>
-      <c r="O179" s="2">
-        <v>850000</v>
+      <c r="O179">
+        <v>0</v>
       </c>
       <c r="P179" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180">
-        <v>58963630</v>
+        <v>59019541</v>
       </c>
       <c r="B180" s="1">
-        <v>46078.697002314817</v>
+        <v>46079.637060185189</v>
       </c>
       <c r="C180">
-        <v>58964242</v>
+        <v>59222474</v>
       </c>
       <c r="D180" s="1">
-        <v>46078.701423611114</v>
+        <v>46083.577013888891</v>
       </c>
       <c r="E180" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="F180" t="s">
-        <v>50</v>
+        <v>343</v>
       </c>
       <c r="G180">
-        <v>747726344</v>
+        <v>747111735</v>
       </c>
       <c r="H180" t="s">
-        <v>351</v>
+        <v>285</v>
       </c>
       <c r="I180" t="s">
         <v>0</v>
       </c>
       <c r="J180" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K180" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L180" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N180" t="s">
         <v>0</v>
@@ -10475,33 +10508,33 @@
         <v>0</v>
       </c>
       <c r="P180" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181">
-        <v>58963646</v>
+        <v>59027644</v>
       </c>
       <c r="B181" s="1">
-        <v>46078.697048611109</v>
+        <v>46079.69427083333</v>
       </c>
       <c r="C181">
-        <v>58964315</v>
+        <v>59296472</v>
       </c>
       <c r="D181" s="1">
-        <v>46078.70208333333</v>
+        <v>46084.655115740738</v>
       </c>
       <c r="E181" t="s">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="F181" t="s">
-        <v>50</v>
+        <v>343</v>
       </c>
       <c r="G181">
-        <v>747726344</v>
+        <v>747111735</v>
       </c>
       <c r="H181" t="s">
-        <v>351</v>
+        <v>285</v>
       </c>
       <c r="I181" t="s">
         <v>0</v>
@@ -10516,54 +10549,54 @@
         <v>6</v>
       </c>
       <c r="M181" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N181" t="s">
         <v>0</v>
       </c>
-      <c r="O181">
-        <v>0</v>
+      <c r="O181" s="2">
+        <v>1500000</v>
       </c>
       <c r="P181" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182">
-        <v>59019541</v>
+        <v>59027644</v>
       </c>
       <c r="B182" s="1">
-        <v>46079.637060185189</v>
+        <v>46079.69427083333</v>
       </c>
       <c r="C182">
-        <v>59222474</v>
+        <v>59027679</v>
       </c>
       <c r="D182" s="1">
-        <v>46083.577013888891</v>
+        <v>46079.694490740738</v>
       </c>
       <c r="E182" t="s">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="F182" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="G182">
         <v>747111735</v>
       </c>
       <c r="H182" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="I182" t="s">
         <v>0</v>
       </c>
       <c r="J182" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K182" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L182" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M182" t="s">
         <v>3</v>
@@ -10571,49 +10604,49 @@
       <c r="N182" t="s">
         <v>0</v>
       </c>
-      <c r="O182" t="s">
-        <v>0</v>
+      <c r="O182" s="2">
+        <v>1500000</v>
       </c>
       <c r="P182" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183">
-        <v>59027644</v>
+        <v>59078958</v>
       </c>
       <c r="B183" s="1">
-        <v>46079.69427083333</v>
+        <v>46080.616597222222</v>
       </c>
       <c r="C183">
-        <v>59027679</v>
+        <v>59248335</v>
       </c>
       <c r="D183" s="1">
-        <v>46079.694490740738</v>
+        <v>46083.791724537034</v>
       </c>
       <c r="E183" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="F183" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="G183">
-        <v>747111735</v>
+        <v>779273099</v>
       </c>
       <c r="H183" t="s">
-        <v>292</v>
+        <v>345</v>
       </c>
       <c r="I183" t="s">
         <v>0</v>
       </c>
       <c r="J183" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K183" t="s">
         <v>5</v>
       </c>
       <c r="L183" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M183" t="s">
         <v>3</v>
@@ -10621,49 +10654,49 @@
       <c r="N183" t="s">
         <v>0</v>
       </c>
-      <c r="O183" s="2">
-        <v>1500000</v>
+      <c r="O183">
+        <v>0</v>
       </c>
       <c r="P183" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184">
-        <v>59027644</v>
+        <v>59078958</v>
       </c>
       <c r="B184" s="1">
-        <v>46079.69427083333</v>
+        <v>46080.616597222222</v>
       </c>
       <c r="C184">
-        <v>59053461</v>
+        <v>59281355</v>
       </c>
       <c r="D184" s="1">
-        <v>46080.431747685187</v>
+        <v>46084.542303240742</v>
       </c>
       <c r="E184" t="s">
-        <v>115</v>
+        <v>361</v>
       </c>
       <c r="F184" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="G184">
-        <v>747111735</v>
+        <v>779273099</v>
       </c>
       <c r="H184" t="s">
-        <v>292</v>
+        <v>345</v>
       </c>
       <c r="I184" t="s">
         <v>0</v>
       </c>
       <c r="J184" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K184" t="s">
         <v>5</v>
       </c>
       <c r="L184" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M184" t="s">
         <v>3</v>
@@ -10671,49 +10704,49 @@
       <c r="N184" t="s">
         <v>0</v>
       </c>
-      <c r="O184" s="2">
-        <v>1500000</v>
+      <c r="O184">
+        <v>0</v>
       </c>
       <c r="P184" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185">
-        <v>59078958</v>
+        <v>59207750</v>
       </c>
       <c r="B185" s="1">
-        <v>46080.616597222222</v>
+        <v>46083.476817129631</v>
       </c>
       <c r="C185">
-        <v>59248335</v>
+        <v>59207793</v>
       </c>
       <c r="D185" s="1">
-        <v>46083.791724537034</v>
+        <v>46083.476736111108</v>
       </c>
       <c r="E185" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="F185" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="G185">
-        <v>779273099</v>
+        <v>758501635</v>
       </c>
       <c r="H185" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="I185" t="s">
         <v>0</v>
       </c>
       <c r="J185" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K185" t="s">
         <v>5</v>
       </c>
       <c r="L185" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M185" t="s">
         <v>3</v>
@@ -10721,49 +10754,49 @@
       <c r="N185" t="s">
         <v>0</v>
       </c>
-      <c r="O185">
-        <v>0</v>
+      <c r="O185" s="2">
+        <v>1000000</v>
       </c>
       <c r="P185" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186">
-        <v>59078958</v>
+        <v>59207750</v>
       </c>
       <c r="B186" s="1">
-        <v>46080.616597222222</v>
+        <v>46083.476817129631</v>
       </c>
       <c r="C186">
-        <v>59091971</v>
+        <v>59302142</v>
       </c>
       <c r="D186" s="1">
-        <v>46080.70516203704</v>
+        <v>46084.699861111112</v>
       </c>
       <c r="E186" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="F186" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="G186">
-        <v>779273099</v>
+        <v>758501635</v>
       </c>
       <c r="H186" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="I186" t="s">
         <v>0</v>
       </c>
       <c r="J186" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K186" t="s">
         <v>5</v>
       </c>
       <c r="L186" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M186" t="s">
         <v>3</v>
@@ -10771,37 +10804,37 @@
       <c r="N186" t="s">
         <v>0</v>
       </c>
-      <c r="O186">
-        <v>0</v>
+      <c r="O186" s="2">
+        <v>1000000</v>
       </c>
       <c r="P186" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187">
-        <v>59207750</v>
+        <v>59248227</v>
       </c>
       <c r="B187" s="1">
-        <v>46083.476817129631</v>
+        <v>46083.789641203701</v>
       </c>
       <c r="C187">
-        <v>59216010</v>
+        <v>59248264</v>
       </c>
       <c r="D187" s="1">
-        <v>46083.531458333331</v>
+        <v>46083.789861111109</v>
       </c>
       <c r="E187" t="s">
-        <v>357</v>
+        <v>114</v>
       </c>
       <c r="F187" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="G187">
-        <v>758501635</v>
+        <v>707478577</v>
       </c>
       <c r="H187" t="s">
-        <v>356</v>
+        <v>290</v>
       </c>
       <c r="I187" t="s">
         <v>0</v>
@@ -10822,36 +10855,36 @@
         <v>0</v>
       </c>
       <c r="O187" s="2">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="P187" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188">
-        <v>59207750</v>
+        <v>59248227</v>
       </c>
       <c r="B188" s="1">
-        <v>46083.476817129631</v>
+        <v>46083.789641203701</v>
       </c>
       <c r="C188">
-        <v>59207793</v>
+        <v>59281686</v>
       </c>
       <c r="D188" s="1">
-        <v>46083.476736111108</v>
+        <v>46084.545277777775</v>
       </c>
       <c r="E188" t="s">
-        <v>114</v>
+        <v>361</v>
       </c>
       <c r="F188" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="G188">
-        <v>758501635</v>
+        <v>707478577</v>
       </c>
       <c r="H188" t="s">
-        <v>356</v>
+        <v>290</v>
       </c>
       <c r="I188" t="s">
         <v>0</v>
@@ -10872,48 +10905,48 @@
         <v>0</v>
       </c>
       <c r="O188" s="2">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="P188" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189">
-        <v>59248227</v>
+        <v>59278285</v>
       </c>
       <c r="B189" s="1">
-        <v>46083.789641203701</v>
+        <v>46084.516597222224</v>
       </c>
       <c r="C189">
-        <v>59248264</v>
+        <v>59278324</v>
       </c>
       <c r="D189" s="1">
-        <v>46083.789861111109</v>
+        <v>46084.517141203702</v>
       </c>
       <c r="E189" t="s">
         <v>114</v>
       </c>
       <c r="F189" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="G189">
-        <v>707478577</v>
+        <v>759651079</v>
       </c>
       <c r="H189" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="I189" t="s">
         <v>0</v>
       </c>
       <c r="J189" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K189" t="s">
         <v>5</v>
       </c>
       <c r="L189" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M189" t="s">
         <v>3</v>
@@ -10922,7 +10955,7 @@
         <v>0</v>
       </c>
       <c r="O189" s="2">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="P189" t="s">
         <v>0</v>
@@ -10930,59 +10963,556 @@
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190">
-        <v>59248227</v>
+        <v>59278285</v>
       </c>
       <c r="B190" s="1">
-        <v>46083.789641203701</v>
+        <v>46084.516597222224</v>
       </c>
       <c r="C190">
-        <v>59248262</v>
+        <v>59279167</v>
       </c>
       <c r="D190" s="1">
-        <v>46083.789861111109</v>
+        <v>46084.52306712963</v>
       </c>
       <c r="E190" t="s">
+        <v>115</v>
+      </c>
+      <c r="F190" t="s">
+        <v>364</v>
+      </c>
+      <c r="G190">
+        <v>759651079</v>
+      </c>
+      <c r="H190" t="s">
+        <v>365</v>
+      </c>
+      <c r="I190" t="s">
+        <v>0</v>
+      </c>
+      <c r="J190" t="s">
+        <v>18</v>
+      </c>
+      <c r="K190" t="s">
+        <v>5</v>
+      </c>
+      <c r="L190" t="s">
+        <v>8</v>
+      </c>
+      <c r="M190" t="s">
+        <v>3</v>
+      </c>
+      <c r="N190" t="s">
+        <v>0</v>
+      </c>
+      <c r="O190" s="2">
+        <v>500000</v>
+      </c>
+      <c r="P190" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A191">
+        <v>59278925</v>
+      </c>
+      <c r="B191" s="1">
+        <v>46084.521053240744</v>
+      </c>
+      <c r="C191">
+        <v>59278967</v>
+      </c>
+      <c r="D191" s="1">
+        <v>46084.521597222221</v>
+      </c>
+      <c r="E191" t="s">
+        <v>114</v>
+      </c>
+      <c r="F191" t="s">
+        <v>364</v>
+      </c>
+      <c r="G191">
+        <v>759651079</v>
+      </c>
+      <c r="H191" t="s">
+        <v>366</v>
+      </c>
+      <c r="I191" t="s">
+        <v>0</v>
+      </c>
+      <c r="J191" t="s">
+        <v>18</v>
+      </c>
+      <c r="K191" t="s">
+        <v>5</v>
+      </c>
+      <c r="L191" t="s">
+        <v>8</v>
+      </c>
+      <c r="M191" t="s">
+        <v>3</v>
+      </c>
+      <c r="N191" t="s">
+        <v>0</v>
+      </c>
+      <c r="O191" s="2">
+        <v>500000</v>
+      </c>
+      <c r="P191" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A192">
+        <v>59278925</v>
+      </c>
+      <c r="B192" s="1">
+        <v>46084.521053240744</v>
+      </c>
+      <c r="C192">
+        <v>59279458</v>
+      </c>
+      <c r="D192" s="1">
+        <v>46084.525254629632</v>
+      </c>
+      <c r="E192" t="s">
+        <v>115</v>
+      </c>
+      <c r="F192" t="s">
+        <v>364</v>
+      </c>
+      <c r="G192">
+        <v>759651079</v>
+      </c>
+      <c r="H192" t="s">
+        <v>366</v>
+      </c>
+      <c r="I192" t="s">
+        <v>0</v>
+      </c>
+      <c r="J192" t="s">
+        <v>18</v>
+      </c>
+      <c r="K192" t="s">
+        <v>5</v>
+      </c>
+      <c r="L192" t="s">
+        <v>8</v>
+      </c>
+      <c r="M192" t="s">
+        <v>3</v>
+      </c>
+      <c r="N192" t="s">
+        <v>0</v>
+      </c>
+      <c r="O192" s="2">
+        <v>500000</v>
+      </c>
+      <c r="P192" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A193">
+        <v>59300338</v>
+      </c>
+      <c r="B193" s="1">
+        <v>46084.687997685185</v>
+      </c>
+      <c r="C193">
+        <v>59305297</v>
+      </c>
+      <c r="D193" s="1">
+        <v>46084.7268287037</v>
+      </c>
+      <c r="E193" t="s">
+        <v>41</v>
+      </c>
+      <c r="F193" t="s">
+        <v>302</v>
+      </c>
+      <c r="G193">
+        <v>545254325</v>
+      </c>
+      <c r="H193" t="s">
+        <v>367</v>
+      </c>
+      <c r="I193" t="s">
+        <v>0</v>
+      </c>
+      <c r="J193" t="s">
+        <v>18</v>
+      </c>
+      <c r="K193" t="s">
+        <v>5</v>
+      </c>
+      <c r="L193" t="s">
+        <v>8</v>
+      </c>
+      <c r="M193" t="s">
+        <v>3</v>
+      </c>
+      <c r="N193" t="s">
+        <v>0</v>
+      </c>
+      <c r="O193" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="P193" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A194">
+        <v>59300338</v>
+      </c>
+      <c r="B194" s="1">
+        <v>46084.687997685185</v>
+      </c>
+      <c r="C194">
+        <v>59305312</v>
+      </c>
+      <c r="D194" s="1">
+        <v>46084.726921296293</v>
+      </c>
+      <c r="E194" t="s">
+        <v>115</v>
+      </c>
+      <c r="F194" t="s">
+        <v>302</v>
+      </c>
+      <c r="G194">
+        <v>545254325</v>
+      </c>
+      <c r="H194" t="s">
+        <v>367</v>
+      </c>
+      <c r="I194" t="s">
+        <v>0</v>
+      </c>
+      <c r="J194" t="s">
+        <v>18</v>
+      </c>
+      <c r="K194" t="s">
+        <v>5</v>
+      </c>
+      <c r="L194" t="s">
+        <v>8</v>
+      </c>
+      <c r="M194" t="s">
+        <v>3</v>
+      </c>
+      <c r="N194" t="s">
+        <v>0</v>
+      </c>
+      <c r="O194" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="P194" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A195">
+        <v>59301114</v>
+      </c>
+      <c r="B195" s="1">
+        <v>46084.692615740743</v>
+      </c>
+      <c r="C195">
+        <v>59305430</v>
+      </c>
+      <c r="D195" s="1">
+        <v>46084.727731481478</v>
+      </c>
+      <c r="E195" t="s">
+        <v>115</v>
+      </c>
+      <c r="F195" t="s">
+        <v>302</v>
+      </c>
+      <c r="G195">
+        <v>788872393</v>
+      </c>
+      <c r="H195" t="s">
+        <v>368</v>
+      </c>
+      <c r="I195" t="s">
+        <v>0</v>
+      </c>
+      <c r="J195" t="s">
+        <v>18</v>
+      </c>
+      <c r="K195" t="s">
+        <v>5</v>
+      </c>
+      <c r="L195" t="s">
+        <v>8</v>
+      </c>
+      <c r="M195" t="s">
+        <v>3</v>
+      </c>
+      <c r="N195" t="s">
+        <v>0</v>
+      </c>
+      <c r="O195" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="P195" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A196">
+        <v>59301114</v>
+      </c>
+      <c r="B196" s="1">
+        <v>46084.692615740743</v>
+      </c>
+      <c r="C196">
+        <v>59305377</v>
+      </c>
+      <c r="D196" s="1">
+        <v>46084.727418981478</v>
+      </c>
+      <c r="E196" t="s">
+        <v>41</v>
+      </c>
+      <c r="F196" t="s">
+        <v>302</v>
+      </c>
+      <c r="G196">
+        <v>788872393</v>
+      </c>
+      <c r="H196" t="s">
+        <v>368</v>
+      </c>
+      <c r="I196" t="s">
+        <v>0</v>
+      </c>
+      <c r="J196" t="s">
+        <v>18</v>
+      </c>
+      <c r="K196" t="s">
+        <v>5</v>
+      </c>
+      <c r="L196" t="s">
+        <v>8</v>
+      </c>
+      <c r="M196" t="s">
+        <v>3</v>
+      </c>
+      <c r="N196" t="s">
+        <v>0</v>
+      </c>
+      <c r="O196" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="P196" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A197">
+        <v>59301554</v>
+      </c>
+      <c r="B197" s="1">
+        <v>46084.695763888885</v>
+      </c>
+      <c r="C197">
+        <v>59305276</v>
+      </c>
+      <c r="D197" s="1">
+        <v>46084.726585648146</v>
+      </c>
+      <c r="E197" t="s">
+        <v>115</v>
+      </c>
+      <c r="F197" t="s">
+        <v>302</v>
+      </c>
+      <c r="G197">
+        <v>777654212</v>
+      </c>
+      <c r="H197" t="s">
+        <v>369</v>
+      </c>
+      <c r="I197" t="s">
+        <v>0</v>
+      </c>
+      <c r="J197" t="s">
+        <v>18</v>
+      </c>
+      <c r="K197" t="s">
+        <v>5</v>
+      </c>
+      <c r="L197" t="s">
+        <v>8</v>
+      </c>
+      <c r="M197" t="s">
+        <v>3</v>
+      </c>
+      <c r="N197" t="s">
+        <v>0</v>
+      </c>
+      <c r="O197" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="P197" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A198">
+        <v>59301554</v>
+      </c>
+      <c r="B198" s="1">
+        <v>46084.695763888885</v>
+      </c>
+      <c r="C198">
+        <v>59305521</v>
+      </c>
+      <c r="D198" s="1">
+        <v>46084.72859953704</v>
+      </c>
+      <c r="E198" t="s">
+        <v>41</v>
+      </c>
+      <c r="F198" t="s">
+        <v>302</v>
+      </c>
+      <c r="G198">
+        <v>777654212</v>
+      </c>
+      <c r="H198" t="s">
+        <v>369</v>
+      </c>
+      <c r="I198" t="s">
+        <v>0</v>
+      </c>
+      <c r="J198" t="s">
+        <v>18</v>
+      </c>
+      <c r="K198" t="s">
+        <v>5</v>
+      </c>
+      <c r="L198" t="s">
+        <v>8</v>
+      </c>
+      <c r="M198" t="s">
+        <v>3</v>
+      </c>
+      <c r="N198" t="s">
+        <v>0</v>
+      </c>
+      <c r="O198" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="P198" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A199">
+        <v>59308240</v>
+      </c>
+      <c r="B199" s="1">
+        <v>46084.755844907406</v>
+      </c>
+      <c r="C199">
+        <v>59308268</v>
+      </c>
+      <c r="D199" s="1">
+        <v>46084.756122685183</v>
+      </c>
+      <c r="E199" t="s">
         <v>42</v>
       </c>
-      <c r="F190" t="s">
-        <v>358</v>
-      </c>
-      <c r="G190">
-        <v>707478577</v>
-      </c>
-      <c r="H190" t="s">
-        <v>297</v>
-      </c>
-      <c r="I190" t="s">
-        <v>0</v>
-      </c>
-      <c r="J190" t="s">
-        <v>13</v>
-      </c>
-      <c r="K190" t="s">
-        <v>5</v>
-      </c>
-      <c r="L190" t="s">
-        <v>6</v>
-      </c>
-      <c r="M190" t="s">
-        <v>3</v>
-      </c>
-      <c r="N190" t="s">
-        <v>0</v>
-      </c>
-      <c r="O190" s="2">
-        <v>800000</v>
-      </c>
-      <c r="P190" t="s">
+      <c r="F199" t="s">
+        <v>24</v>
+      </c>
+      <c r="G199">
+        <v>707865499</v>
+      </c>
+      <c r="H199" t="s">
+        <v>200</v>
+      </c>
+      <c r="I199" t="s">
+        <v>0</v>
+      </c>
+      <c r="J199" t="s">
+        <v>18</v>
+      </c>
+      <c r="K199" t="s">
+        <v>5</v>
+      </c>
+      <c r="L199" t="s">
+        <v>8</v>
+      </c>
+      <c r="M199" t="s">
+        <v>3</v>
+      </c>
+      <c r="N199" t="s">
+        <v>0</v>
+      </c>
+      <c r="O199" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="P199" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A200">
+        <v>59308240</v>
+      </c>
+      <c r="B200" s="1">
+        <v>46084.755844907406</v>
+      </c>
+      <c r="C200">
+        <v>59308269</v>
+      </c>
+      <c r="D200" s="1">
+        <v>46084.75613425926</v>
+      </c>
+      <c r="E200" t="s">
+        <v>114</v>
+      </c>
+      <c r="F200" t="s">
+        <v>24</v>
+      </c>
+      <c r="G200">
+        <v>707865499</v>
+      </c>
+      <c r="H200" t="s">
+        <v>200</v>
+      </c>
+      <c r="I200" t="s">
+        <v>0</v>
+      </c>
+      <c r="J200" t="s">
+        <v>18</v>
+      </c>
+      <c r="K200" t="s">
+        <v>5</v>
+      </c>
+      <c r="L200" t="s">
+        <v>8</v>
+      </c>
+      <c r="M200" t="s">
+        <v>3</v>
+      </c>
+      <c r="N200" t="s">
+        <v>0</v>
+      </c>
+      <c r="O200" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="P200" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Helvetica 75 Bold"&amp;8&amp;KED7D31 Orange Restricted</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XZRS8771\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B0A922-E109-44F8-91BD-BC57BF209E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9FA39B-3460-4B0F-ADCB-1E9CE6E2430B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{10E1CAFB-183C-41AD-83DF-DC9DE0E28769}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$V$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$V$158</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="333">
   <si>
     <t>ID DOSSIER</t>
   </si>
@@ -765,18 +765,6 @@
   </si>
   <si>
     <t>TREICHVILLE ZONE 3 EN FACE DE CFAO</t>
-  </si>
-  <si>
-    <t>PRIMORIS</t>
-  </si>
-  <si>
-    <t>ABIDJAN-YOPOUGON//VOIE INCONNUE/ZONE INDUSTRIELLE</t>
-  </si>
-  <si>
-    <t>SYTHD260073</t>
-  </si>
-  <si>
-    <t>BO Homologation: Mise en service GAIA</t>
   </si>
   <si>
     <t>FOUAD GROUPE</t>
@@ -12225,7 +12213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91676046-DC9A-418C-A539-44748F9868EB}">
-  <dimension ref="A1:V159"/>
+  <dimension ref="A1:V158"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -12294,19 +12282,19 @@
         <v>16</v>
       </c>
       <c r="R1" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="V1" s="6" t="s">
         <v>332</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="52" x14ac:dyDescent="0.35">
@@ -17103,7 +17091,7 @@
         <v>500000</v>
       </c>
       <c r="R67" s="7">
-        <f t="shared" ref="R67:R130" ca="1" si="1">NETWORKDAYS(B67,TODAY())</f>
+        <f t="shared" ref="R67:R129" ca="1" si="1">NETWORKDAYS(B67,TODAY())</f>
         <v>20</v>
       </c>
       <c r="S67" s="7" t="str">
@@ -19605,36 +19593,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:22" ht="91" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
-        <v>59027644</v>
+        <v>59248227</v>
       </c>
       <c r="B102" s="4">
-        <v>46079.69427083333</v>
+        <v>46083.789641203701</v>
       </c>
       <c r="C102" s="3">
-        <v>60198153</v>
+        <v>60031670</v>
       </c>
       <c r="D102" s="4">
-        <v>46100.676203703704</v>
+        <v>46098.408229166664</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>241</v>
       </c>
       <c r="G102" s="3">
-        <v>747111735</v>
+        <v>707478577</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="I102" s="3">
-        <v>1833216</v>
+      <c r="I102" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>36</v>
@@ -19655,11 +19643,11 @@
         <v>19</v>
       </c>
       <c r="Q102" s="5">
-        <v>1500000</v>
+        <v>800000</v>
       </c>
       <c r="R102" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S102" s="7" t="str">
         <f>VLOOKUP(A102,[1]Feuil1!$A:$V,19,FALSE)</f>
@@ -19680,40 +19668,40 @@
     </row>
     <row r="103" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
-        <v>59248227</v>
+        <v>59278285</v>
       </c>
       <c r="B103" s="4">
-        <v>46083.789641203701</v>
+        <v>46084.516597222224</v>
       </c>
       <c r="C103" s="3">
-        <v>60031670</v>
+        <v>60042845</v>
       </c>
       <c r="D103" s="4">
-        <v>46098.408229166664</v>
+        <v>46098.495370370372</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>141</v>
       </c>
       <c r="F103" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G103" s="3">
+        <v>759651079</v>
+      </c>
+      <c r="H103" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G103" s="3">
-        <v>707478577</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>246</v>
-      </c>
       <c r="I103" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K103" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="M103" s="3" t="s">
         <v>23</v>
@@ -19722,17 +19710,17 @@
         <v>117</v>
       </c>
       <c r="O103" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P103" s="3" t="s">
         <v>19</v>
       </c>
       <c r="Q103" s="5">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="R103" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S103" s="7" t="str">
         <f>VLOOKUP(A103,[1]Feuil1!$A:$V,19,FALSE)</f>
@@ -19753,28 +19741,28 @@
     </row>
     <row r="104" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
-        <v>59278285</v>
+        <v>59278925</v>
       </c>
       <c r="B104" s="4">
-        <v>46084.516597222224</v>
+        <v>46084.521053240744</v>
       </c>
       <c r="C104" s="3">
-        <v>60042845</v>
+        <v>60110317</v>
       </c>
       <c r="D104" s="4">
-        <v>46098.495370370372</v>
+        <v>46099.500092592592</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>141</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G104" s="3">
         <v>759651079</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>19</v>
@@ -19795,7 +19783,7 @@
         <v>117</v>
       </c>
       <c r="O104" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P104" s="3" t="s">
         <v>19</v>
@@ -19824,30 +19812,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:22" ht="52" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:22" ht="78" x14ac:dyDescent="0.35">
       <c r="A105" s="3">
-        <v>59278925</v>
+        <v>59300338</v>
       </c>
       <c r="B105" s="4">
-        <v>46084.521053240744</v>
+        <v>46084.687997685185</v>
       </c>
       <c r="C105" s="3">
-        <v>60110317</v>
+        <v>60194598</v>
       </c>
       <c r="D105" s="4">
-        <v>46099.500092592592</v>
+        <v>46100.648078703707</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>248</v>
+        <v>203</v>
       </c>
       <c r="G105" s="3">
-        <v>759651079</v>
+        <v>545254325</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>19</v>
@@ -19856,7 +19844,7 @@
         <v>35</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L105" s="3" t="s">
         <v>29</v>
@@ -19865,16 +19853,16 @@
         <v>23</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="O105" s="3" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="P105" s="3" t="s">
         <v>19</v>
       </c>
       <c r="Q105" s="5">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="R105" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -19899,28 +19887,28 @@
     </row>
     <row r="106" spans="1:22" ht="78" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
-        <v>59300338</v>
+        <v>59301114</v>
       </c>
       <c r="B106" s="4">
-        <v>46084.687997685185</v>
+        <v>46084.692615740743</v>
       </c>
       <c r="C106" s="3">
-        <v>60194598</v>
+        <v>60197211</v>
       </c>
       <c r="D106" s="4">
-        <v>46100.648078703707</v>
+        <v>46100.666875000003</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>203</v>
       </c>
       <c r="G106" s="3">
-        <v>545254325</v>
+        <v>788872393</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>19</v>
@@ -19938,7 +19926,7 @@
         <v>23</v>
       </c>
       <c r="N106" s="3" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="O106" s="3" t="s">
         <v>222</v>
@@ -19970,30 +19958,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:22" ht="78" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:22" ht="65" x14ac:dyDescent="0.35">
       <c r="A107" s="3">
-        <v>59301114</v>
+        <v>59301554</v>
       </c>
       <c r="B107" s="4">
-        <v>46084.692615740743</v>
+        <v>46084.695763888885</v>
       </c>
       <c r="C107" s="3">
-        <v>60197211</v>
+        <v>60163155</v>
       </c>
       <c r="D107" s="4">
-        <v>46100.666875000003</v>
+        <v>46100.417083333334</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>203</v>
       </c>
       <c r="G107" s="3">
-        <v>788872393</v>
+        <v>777654212</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>19</v>
@@ -20011,10 +19999,10 @@
         <v>23</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="O107" s="3" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="P107" s="3" t="s">
         <v>19</v>
@@ -20043,30 +20031,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:22" ht="65" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
-        <v>59301554</v>
+        <v>59308240</v>
       </c>
       <c r="B108" s="4">
-        <v>46084.695763888885</v>
+        <v>46084.755844907406</v>
       </c>
       <c r="C108" s="3">
-        <v>60163155</v>
+        <v>60195577</v>
       </c>
       <c r="D108" s="4">
-        <v>46100.417083333334</v>
+        <v>46100.654699074075</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>203</v>
+        <v>253</v>
       </c>
       <c r="G108" s="3">
-        <v>777654212</v>
+        <v>707865499</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>19</v>
@@ -20087,7 +20075,7 @@
         <v>30</v>
       </c>
       <c r="O108" s="3" t="s">
-        <v>256</v>
+        <v>56</v>
       </c>
       <c r="P108" s="3" t="s">
         <v>19</v>
@@ -20103,9 +20091,9 @@
         <f>VLOOKUP(A108,[1]Feuil1!$A:$V,19,FALSE)</f>
         <v>Non</v>
       </c>
-      <c r="T108" s="7" t="e">
+      <c r="T108" s="7" t="str">
         <f>VLOOKUP(A108,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>#N/A</v>
+        <v xml:space="preserve">CLIENT </v>
       </c>
       <c r="U108" s="7" t="str">
         <f>VLOOKUP(A108,[1]Feuil1!$A:$V,21,FALSE)</f>
@@ -20116,30 +20104,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:22" ht="26" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:22" ht="65" x14ac:dyDescent="0.35">
       <c r="A109" s="3">
-        <v>59308240</v>
+        <v>59309764</v>
       </c>
       <c r="B109" s="4">
-        <v>46084.755844907406</v>
+        <v>46084.777083333334</v>
       </c>
       <c r="C109" s="3">
-        <v>60195577</v>
+        <v>60021725</v>
       </c>
       <c r="D109" s="4">
-        <v>46100.654699074075</v>
+        <v>46097.886493055557</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>221</v>
+        <v>44</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G109" s="3">
-        <v>707865499</v>
+        <v>708164102</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>209</v>
+        <v>254</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>19</v>
@@ -20160,7 +20148,7 @@
         <v>30</v>
       </c>
       <c r="O109" s="3" t="s">
-        <v>56</v>
+        <v>252</v>
       </c>
       <c r="P109" s="3" t="s">
         <v>19</v>
@@ -20176,9 +20164,9 @@
         <f>VLOOKUP(A109,[1]Feuil1!$A:$V,19,FALSE)</f>
         <v>Non</v>
       </c>
-      <c r="T109" s="7" t="str">
+      <c r="T109" s="7" t="e">
         <f>VLOOKUP(A109,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v xml:space="preserve">CLIENT </v>
+        <v>#N/A</v>
       </c>
       <c r="U109" s="7" t="str">
         <f>VLOOKUP(A109,[1]Feuil1!$A:$V,21,FALSE)</f>
@@ -20189,57 +20177,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:22" ht="65" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A110" s="3">
-        <v>59309764</v>
+        <v>59312351</v>
       </c>
       <c r="B110" s="4">
-        <v>46084.777083333334</v>
+        <v>46084.824178240742</v>
       </c>
       <c r="C110" s="3">
-        <v>60021725</v>
+        <v>60192773</v>
       </c>
       <c r="D110" s="4">
-        <v>46097.886493055557</v>
+        <v>46100.638124999998</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>44</v>
+        <v>255</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>257</v>
+        <v>48</v>
       </c>
       <c r="G110" s="3">
-        <v>708164102</v>
+        <v>749928277</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M110" s="3" t="s">
         <v>23</v>
       </c>
       <c r="N110" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O110" s="3" t="s">
-        <v>256</v>
+        <v>117</v>
+      </c>
+      <c r="O110" s="3">
+        <v>2721252525</v>
       </c>
       <c r="P110" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q110" s="5">
-        <v>2000000</v>
+      <c r="Q110" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R110" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -20262,51 +20250,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:22" ht="26" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:22" ht="91" x14ac:dyDescent="0.35">
       <c r="A111" s="3">
-        <v>59312351</v>
+        <v>59374776</v>
       </c>
       <c r="B111" s="4">
-        <v>46084.824178240742</v>
+        <v>46085.757662037038</v>
       </c>
       <c r="C111" s="3">
-        <v>60192773</v>
+        <v>60185369</v>
       </c>
       <c r="D111" s="4">
-        <v>46100.638124999998</v>
+        <v>46100.585393518515</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>259</v>
+        <v>51</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>48</v>
+        <v>256</v>
       </c>
       <c r="G111" s="3">
-        <v>749928277</v>
+        <v>747726344</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="O111" s="3">
-        <v>2721252525</v>
+        <v>30</v>
+      </c>
+      <c r="O111" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="P111" s="3" t="s">
         <v>19</v>
@@ -20316,7 +20304,7 @@
       </c>
       <c r="R111" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S111" s="7" t="str">
         <f>VLOOKUP(A111,[1]Feuil1!$A:$V,19,FALSE)</f>
@@ -20335,61 +20323,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:22" ht="91" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A112" s="3">
-        <v>59374776</v>
+        <v>59406146</v>
       </c>
       <c r="B112" s="4">
-        <v>46085.757662037038</v>
+        <v>46086.506643518522</v>
       </c>
       <c r="C112" s="3">
-        <v>60185369</v>
+        <v>59426353</v>
       </c>
       <c r="D112" s="4">
-        <v>46100.585393518515</v>
+        <v>46086.658784722225</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>51</v>
+        <v>207</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G112" s="3">
-        <v>747726344</v>
+        <v>709136702</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>19</v>
+        <v>156</v>
+      </c>
+      <c r="I112" s="3">
+        <v>1843656</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="N112" s="3" t="s">
         <v>30</v>
       </c>
       <c r="O112" s="3" t="s">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="P112" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q112" s="3" t="s">
-        <v>19</v>
+      <c r="Q112" s="3">
+        <v>0</v>
       </c>
       <c r="R112" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S112" s="7" t="str">
         <f>VLOOKUP(A112,[1]Feuil1!$A:$V,19,FALSE)</f>
@@ -20410,22 +20398,22 @@
     </row>
     <row r="113" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A113" s="3">
-        <v>59406146</v>
+        <v>59406937</v>
       </c>
       <c r="B113" s="4">
-        <v>46086.506643518522</v>
+        <v>46086.512870370374</v>
       </c>
       <c r="C113" s="3">
-        <v>59426353</v>
+        <v>59428327</v>
       </c>
       <c r="D113" s="4">
-        <v>46086.658784722225</v>
+        <v>46086.673530092594</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>207</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G113" s="3">
         <v>709136702</v>
@@ -20434,7 +20422,7 @@
         <v>156</v>
       </c>
       <c r="I113" s="3">
-        <v>1843656</v>
+        <v>1843676</v>
       </c>
       <c r="J113" s="3" t="s">
         <v>95</v>
@@ -20483,43 +20471,43 @@
     </row>
     <row r="114" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A114" s="3">
-        <v>59406937</v>
+        <v>59409078</v>
       </c>
       <c r="B114" s="4">
-        <v>46086.512870370374</v>
+        <v>46086.529247685183</v>
       </c>
       <c r="C114" s="3">
-        <v>59428327</v>
+        <v>59427283</v>
       </c>
       <c r="D114" s="4">
-        <v>46086.673530092594</v>
+        <v>46086.665729166663</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>207</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G114" s="3">
-        <v>709136702</v>
+        <v>709140938</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>156</v>
       </c>
       <c r="I114" s="3">
-        <v>1843676</v>
+        <v>0</v>
       </c>
       <c r="J114" s="3" t="s">
         <v>95</v>
       </c>
       <c r="K114" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L114" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="N114" s="3" t="s">
         <v>30</v>
@@ -20530,8 +20518,8 @@
       <c r="P114" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q114" s="3">
-        <v>0</v>
+      <c r="Q114" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R114" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -20556,25 +20544,25 @@
     </row>
     <row r="115" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A115" s="3">
-        <v>59409078</v>
+        <v>59409752</v>
       </c>
       <c r="B115" s="4">
-        <v>46086.529247685183</v>
+        <v>46086.534502314818</v>
       </c>
       <c r="C115" s="3">
-        <v>59427283</v>
+        <v>59429000</v>
       </c>
       <c r="D115" s="4">
-        <v>46086.665729166663</v>
+        <v>46086.676817129628</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>207</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G115" s="3">
-        <v>709140938</v>
+        <v>758700193</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>156</v>
@@ -20592,7 +20580,7 @@
         <v>22</v>
       </c>
       <c r="M115" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="N115" s="3" t="s">
         <v>30</v>
@@ -20629,49 +20617,49 @@
     </row>
     <row r="116" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A116" s="3">
-        <v>59409752</v>
+        <v>59410212</v>
       </c>
       <c r="B116" s="4">
-        <v>46086.534502314818</v>
+        <v>46086.537708333337</v>
       </c>
       <c r="C116" s="3">
-        <v>59429000</v>
+        <v>59835857</v>
       </c>
       <c r="D116" s="4">
-        <v>46086.676817129628</v>
+        <v>46093.728726851848</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>207</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G116" s="3">
-        <v>758700193</v>
+        <v>789018789</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I116" s="3">
-        <v>0</v>
+      <c r="I116" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="J116" s="3" t="s">
         <v>95</v>
       </c>
       <c r="K116" s="3" t="s">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="L116" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M116" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="N116" s="3" t="s">
         <v>30</v>
       </c>
       <c r="O116" s="3" t="s">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="P116" s="3" t="s">
         <v>19</v>
@@ -20700,51 +20688,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:22" ht="26" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A117" s="3">
-        <v>59410212</v>
+        <v>59410843</v>
       </c>
       <c r="B117" s="4">
-        <v>46086.537708333337</v>
+        <v>46086.542870370373</v>
       </c>
       <c r="C117" s="3">
-        <v>59835857</v>
+        <v>59429922</v>
       </c>
       <c r="D117" s="4">
-        <v>46093.728726851848</v>
+        <v>46086.682488425926</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>207</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G117" s="3">
-        <v>789018789</v>
+        <v>758700193</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>19</v>
+        <v>265</v>
+      </c>
+      <c r="I117" s="3">
+        <v>0</v>
       </c>
       <c r="J117" s="3" t="s">
         <v>95</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>267</v>
+        <v>21</v>
       </c>
       <c r="L117" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M117" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="N117" s="3" t="s">
         <v>30</v>
       </c>
       <c r="O117" s="3" t="s">
-        <v>222</v>
+        <v>19</v>
       </c>
       <c r="P117" s="3" t="s">
         <v>19</v>
@@ -20773,33 +20761,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:22" ht="52" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A118" s="3">
-        <v>59410843</v>
+        <v>59414411</v>
       </c>
       <c r="B118" s="4">
-        <v>46086.542870370373</v>
+        <v>46086.57104166667</v>
       </c>
       <c r="C118" s="3">
-        <v>59429922</v>
+        <v>59430460</v>
       </c>
       <c r="D118" s="4">
-        <v>46086.682488425926</v>
+        <v>46086.686412037037</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>207</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G118" s="3">
-        <v>758700193</v>
+        <v>566473307</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I118" s="3">
-        <v>0</v>
+        <v>1841606</v>
       </c>
       <c r="J118" s="3" t="s">
         <v>95</v>
@@ -20822,8 +20810,8 @@
       <c r="P118" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q118" s="3" t="s">
-        <v>19</v>
+      <c r="Q118" s="3">
+        <v>0</v>
       </c>
       <c r="R118" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -20846,33 +20834,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:22" ht="39" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A119" s="3">
-        <v>59414411</v>
+        <v>59417066</v>
       </c>
       <c r="B119" s="4">
-        <v>46086.57104166667</v>
+        <v>46086.594525462962</v>
       </c>
       <c r="C119" s="3">
-        <v>59430460</v>
+        <v>59431339</v>
       </c>
       <c r="D119" s="4">
-        <v>46086.686412037037</v>
+        <v>46086.692337962966</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>207</v>
       </c>
       <c r="F119" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G119" s="3">
+        <v>709565662</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="I119" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="G119" s="3">
-        <v>566473307</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="I119" s="3">
-        <v>1841606</v>
       </c>
       <c r="J119" s="3" t="s">
         <v>95</v>
@@ -20919,36 +20907,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:22" ht="52" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:22" ht="65" x14ac:dyDescent="0.35">
       <c r="A120" s="3">
-        <v>59417066</v>
+        <v>59427337</v>
       </c>
       <c r="B120" s="4">
-        <v>46086.594525462962</v>
+        <v>46086.666180555556</v>
       </c>
       <c r="C120" s="3">
-        <v>59431339</v>
+        <v>60189892</v>
       </c>
       <c r="D120" s="4">
-        <v>46086.692337962966</v>
+        <v>46100.618032407408</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>207</v>
+        <v>123</v>
       </c>
       <c r="F120" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G120" s="3">
+        <v>708326247</v>
+      </c>
+      <c r="H120" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="G120" s="3">
-        <v>709565662</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="I120" s="3" t="s">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="K120" s="3" t="s">
         <v>21</v>
@@ -20960,16 +20948,16 @@
         <v>23</v>
       </c>
       <c r="N120" s="3" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="O120" s="3" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="P120" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q120" s="3">
-        <v>0</v>
+      <c r="Q120" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R120" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -20992,91 +20980,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:22" ht="65" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A121" s="3">
-        <v>59427337</v>
+        <v>59464660</v>
       </c>
       <c r="B121" s="4">
-        <v>46086.666180555556</v>
+        <v>46087.421030092592</v>
       </c>
       <c r="C121" s="3">
-        <v>60189892</v>
+        <v>59688131</v>
       </c>
       <c r="D121" s="4">
-        <v>46100.618032407408</v>
+        <v>46091.589421296296</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>275</v>
+        <v>126</v>
       </c>
       <c r="G121" s="3">
-        <v>708326247</v>
+        <v>554235979</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>276</v>
+        <v>209</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="N121" s="3" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="O121" s="3" t="s">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="P121" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q121" s="3" t="s">
-        <v>19</v>
+      <c r="Q121" s="3">
+        <v>0</v>
       </c>
       <c r="R121" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S121" s="7" t="str">
         <f>VLOOKUP(A121,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>Non</v>
-      </c>
-      <c r="T121" s="7" t="e">
+        <v>NON</v>
+      </c>
+      <c r="T121" s="7">
         <f>VLOOKUP(A121,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="U121" s="7" t="str">
         <f>VLOOKUP(A121,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="V121" s="7">
+        <v>Projet ingénierie</v>
+      </c>
+      <c r="V121" s="7" t="str">
         <f>VLOOKUP(A121,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>0</v>
+        <v>Projet</v>
       </c>
     </row>
     <row r="122" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A122" s="3">
-        <v>59464660</v>
+        <v>59465071</v>
       </c>
       <c r="B122" s="4">
-        <v>46087.421030092592</v>
+        <v>46087.424062500002</v>
       </c>
       <c r="C122" s="3">
-        <v>59688131</v>
+        <v>59643075</v>
       </c>
       <c r="D122" s="4">
-        <v>46091.589421296296</v>
+        <v>46090.709768518522</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>207</v>
@@ -21088,7 +21076,7 @@
         <v>554235979</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>209</v>
+        <v>273</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>19</v>
@@ -21138,30 +21126,30 @@
         <v>Projet</v>
       </c>
     </row>
-    <row r="123" spans="1:22" ht="26" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A123" s="3">
-        <v>59465071</v>
+        <v>59466514</v>
       </c>
       <c r="B123" s="4">
-        <v>46087.424062500002</v>
+        <v>46087.436643518522</v>
       </c>
       <c r="C123" s="3">
-        <v>59643075</v>
+        <v>60021703</v>
       </c>
       <c r="D123" s="4">
-        <v>46090.709768518522</v>
+        <v>46097.883842592593</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>126</v>
+        <v>274</v>
       </c>
       <c r="G123" s="3">
-        <v>554235979</v>
+        <v>141679210</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>19</v>
@@ -21182,13 +21170,13 @@
         <v>30</v>
       </c>
       <c r="O123" s="3" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="P123" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q123" s="3">
-        <v>0</v>
+      <c r="Q123" s="5">
+        <v>3213390</v>
       </c>
       <c r="R123" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -21196,57 +21184,57 @@
       </c>
       <c r="S123" s="7" t="str">
         <f>VLOOKUP(A123,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>NON</v>
-      </c>
-      <c r="T123" s="7">
+        <v>Non</v>
+      </c>
+      <c r="T123" s="7" t="str">
         <f>VLOOKUP(A123,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>0</v>
+        <v xml:space="preserve">CLIENT </v>
       </c>
       <c r="U123" s="7" t="str">
         <f>VLOOKUP(A123,[1]Feuil1!$A:$V,21,FALSE)</f>
         <v>Projet ingénierie</v>
       </c>
-      <c r="V123" s="7" t="str">
+      <c r="V123" s="7">
         <f>VLOOKUP(A123,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>Projet</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:22" ht="39" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A124" s="3">
-        <v>59466514</v>
+        <v>59466778</v>
       </c>
       <c r="B124" s="4">
-        <v>46087.436643518522</v>
+        <v>46087.438715277778</v>
       </c>
       <c r="C124" s="3">
-        <v>60021703</v>
+        <v>59497069</v>
       </c>
       <c r="D124" s="4">
-        <v>46097.883842592593</v>
+        <v>46087.666539351849</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>44</v>
+        <v>207</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>278</v>
+        <v>126</v>
       </c>
       <c r="G124" s="3">
-        <v>141679210</v>
+        <v>554235979</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="I124" s="3" t="s">
-        <v>19</v>
+        <v>121</v>
+      </c>
+      <c r="I124" s="3">
+        <v>0</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="M124" s="3" t="s">
         <v>37</v>
@@ -21255,13 +21243,13 @@
         <v>30</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="P124" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q124" s="5">
-        <v>3213390</v>
+      <c r="Q124" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R124" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -21269,33 +21257,33 @@
       </c>
       <c r="S124" s="7" t="str">
         <f>VLOOKUP(A124,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>Non</v>
-      </c>
-      <c r="T124" s="7" t="str">
+        <v>NON</v>
+      </c>
+      <c r="T124" s="7">
         <f>VLOOKUP(A124,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v xml:space="preserve">CLIENT </v>
+        <v>0</v>
       </c>
       <c r="U124" s="7" t="str">
         <f>VLOOKUP(A124,[1]Feuil1!$A:$V,21,FALSE)</f>
         <v>Projet ingénierie</v>
       </c>
-      <c r="V124" s="7">
+      <c r="V124" s="7" t="str">
         <f>VLOOKUP(A124,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>0</v>
+        <v>Projet</v>
       </c>
     </row>
     <row r="125" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A125" s="3">
-        <v>59466778</v>
+        <v>59468518</v>
       </c>
       <c r="B125" s="4">
-        <v>46087.438715277778</v>
+        <v>46087.450266203705</v>
       </c>
       <c r="C125" s="3">
-        <v>59497069</v>
+        <v>59646678</v>
       </c>
       <c r="D125" s="4">
-        <v>46087.666539351849</v>
+        <v>46090.740671296298</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>207</v>
@@ -21307,10 +21295,10 @@
         <v>554235979</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I125" s="3">
-        <v>0</v>
+        <v>209</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="J125" s="3" t="s">
         <v>95</v>
@@ -21322,13 +21310,13 @@
         <v>22</v>
       </c>
       <c r="M125" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="N125" s="3" t="s">
         <v>30</v>
       </c>
       <c r="O125" s="3" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="P125" s="3" t="s">
         <v>19</v>
@@ -21359,16 +21347,16 @@
     </row>
     <row r="126" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A126" s="3">
-        <v>59468518</v>
+        <v>59469589</v>
       </c>
       <c r="B126" s="4">
-        <v>46087.450266203705</v>
+        <v>46087.458460648151</v>
       </c>
       <c r="C126" s="3">
-        <v>59646678</v>
+        <v>59646039</v>
       </c>
       <c r="D126" s="4">
-        <v>46090.740671296298</v>
+        <v>46090.733263888891</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>207</v>
@@ -21401,7 +21389,7 @@
         <v>30</v>
       </c>
       <c r="O126" s="3" t="s">
-        <v>56</v>
+        <v>235</v>
       </c>
       <c r="P126" s="3" t="s">
         <v>19</v>
@@ -21423,43 +21411,43 @@
       </c>
       <c r="U126" s="7" t="str">
         <f>VLOOKUP(A126,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v>Projet ingénierie</v>
+        <v>Doublon</v>
       </c>
       <c r="V126" s="7" t="str">
         <f>VLOOKUP(A126,[1]Feuil1!$A:$V,22,FALSE)</f>
         <v>Projet</v>
       </c>
     </row>
-    <row r="127" spans="1:22" ht="26" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A127" s="3">
-        <v>59469589</v>
+        <v>59480507</v>
       </c>
       <c r="B127" s="4">
-        <v>46087.458460648151</v>
+        <v>46087.544247685182</v>
       </c>
       <c r="C127" s="3">
-        <v>59646039</v>
+        <v>60031786</v>
       </c>
       <c r="D127" s="4">
-        <v>46090.733263888891</v>
+        <v>46098.409074074072</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>126</v>
+        <v>275</v>
       </c>
       <c r="G127" s="3">
-        <v>554235979</v>
+        <v>708547070</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="K127" s="3" t="s">
         <v>21</v>
@@ -21471,10 +21459,10 @@
         <v>23</v>
       </c>
       <c r="N127" s="3" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>235</v>
+        <v>56</v>
       </c>
       <c r="P127" s="3" t="s">
         <v>19</v>
@@ -21488,72 +21476,72 @@
       </c>
       <c r="S127" s="7" t="str">
         <f>VLOOKUP(A127,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>NON</v>
-      </c>
-      <c r="T127" s="7">
+        <v>Non</v>
+      </c>
+      <c r="T127" s="7" t="str">
         <f>VLOOKUP(A127,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>0</v>
+        <v>OCI</v>
       </c>
       <c r="U127" s="7" t="str">
         <f>VLOOKUP(A127,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v>Doublon</v>
-      </c>
-      <c r="V127" s="7" t="str">
+        <v>Projet ingénierie</v>
+      </c>
+      <c r="V127" s="7">
         <f>VLOOKUP(A127,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>Projet</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:22" ht="39" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A128" s="3">
-        <v>59480507</v>
+        <v>59495473</v>
       </c>
       <c r="B128" s="4">
-        <v>46087.544247685182</v>
+        <v>46087.653935185182</v>
       </c>
       <c r="C128" s="3">
-        <v>60031786</v>
+        <v>59644603</v>
       </c>
       <c r="D128" s="4">
-        <v>46098.409074074072</v>
+        <v>46090.722048611111</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>280</v>
+        <v>207</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G128" s="3">
-        <v>708547070</v>
+        <v>506727287</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>213</v>
+        <v>278</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="M128" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="N128" s="3" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="P128" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q128" s="3" t="s">
-        <v>19</v>
+      <c r="Q128" s="3">
+        <v>0</v>
       </c>
       <c r="R128" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -21561,72 +21549,72 @@
       </c>
       <c r="S128" s="7" t="str">
         <f>VLOOKUP(A128,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>Non</v>
-      </c>
-      <c r="T128" s="7" t="str">
+        <v>NON</v>
+      </c>
+      <c r="T128" s="7">
         <f>VLOOKUP(A128,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>OCI</v>
+        <v>0</v>
       </c>
       <c r="U128" s="7" t="str">
         <f>VLOOKUP(A128,[1]Feuil1!$A:$V,21,FALSE)</f>
         <v>Projet ingénierie</v>
       </c>
-      <c r="V128" s="7">
+      <c r="V128" s="7" t="str">
         <f>VLOOKUP(A128,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>0</v>
+        <v>Projet</v>
       </c>
     </row>
-    <row r="129" spans="1:22" ht="26" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A129" s="3">
-        <v>59495473</v>
+        <v>59495495</v>
       </c>
       <c r="B129" s="4">
-        <v>46087.653935185182</v>
+        <v>46087.654039351852</v>
       </c>
       <c r="C129" s="3">
-        <v>59644603</v>
+        <v>60103608</v>
       </c>
       <c r="D129" s="4">
-        <v>46090.722048611111</v>
+        <v>46099.451018518521</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>207</v>
+        <v>280</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G129" s="3">
-        <v>506727287</v>
+        <v>757019000</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>282</v>
+        <v>156</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K129" s="3" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="N129" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="O129" s="3" t="s">
-        <v>19</v>
+      <c r="O129" s="3">
+        <v>2720219740</v>
       </c>
       <c r="P129" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q129" s="3">
-        <v>0</v>
+      <c r="Q129" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R129" s="7">
         <f t="shared" ca="1" si="1"/>
@@ -21634,118 +21622,118 @@
       </c>
       <c r="S129" s="7" t="str">
         <f>VLOOKUP(A129,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>NON</v>
-      </c>
-      <c r="T129" s="7">
+        <v>Non</v>
+      </c>
+      <c r="T129" s="7" t="str">
         <f>VLOOKUP(A129,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>0</v>
+        <v>OCI</v>
       </c>
       <c r="U129" s="7" t="str">
         <f>VLOOKUP(A129,[1]Feuil1!$A:$V,21,FALSE)</f>
         <v>Projet ingénierie</v>
       </c>
-      <c r="V129" s="7" t="str">
+      <c r="V129" s="7">
         <f>VLOOKUP(A129,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>Projet</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:22" ht="39" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A130" s="3">
-        <v>59495495</v>
+        <v>59498233</v>
       </c>
       <c r="B130" s="4">
-        <v>46087.654039351852</v>
+        <v>46087.67423611111</v>
       </c>
       <c r="C130" s="3">
-        <v>60103608</v>
+        <v>59693004</v>
       </c>
       <c r="D130" s="4">
-        <v>46099.451018518521</v>
+        <v>46091.627928240741</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>284</v>
+        <v>105</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G130" s="3">
-        <v>757019000</v>
+        <v>606727287</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>96</v>
+        <v>281</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="M130" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="N130" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="O130" s="3">
-        <v>2720219740</v>
+      <c r="O130" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="P130" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q130" s="3" t="s">
-        <v>19</v>
+      <c r="Q130" s="3">
+        <v>0</v>
       </c>
       <c r="R130" s="7">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ref="R130:R158" ca="1" si="2">NETWORKDAYS(B130,TODAY())</f>
         <v>10</v>
       </c>
       <c r="S130" s="7" t="str">
         <f>VLOOKUP(A130,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>Non</v>
-      </c>
-      <c r="T130" s="7" t="str">
+        <v>NON</v>
+      </c>
+      <c r="T130" s="7">
         <f>VLOOKUP(A130,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>OCI</v>
+        <v>0</v>
       </c>
       <c r="U130" s="7" t="str">
         <f>VLOOKUP(A130,[1]Feuil1!$A:$V,21,FALSE)</f>
         <v>Projet ingénierie</v>
       </c>
-      <c r="V130" s="7">
+      <c r="V130" s="7" t="str">
         <f>VLOOKUP(A130,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>0</v>
+        <v>Projet</v>
       </c>
     </row>
-    <row r="131" spans="1:22" ht="52" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:22" ht="65" x14ac:dyDescent="0.35">
       <c r="A131" s="3">
-        <v>59498233</v>
+        <v>59537755</v>
       </c>
       <c r="B131" s="4">
-        <v>46087.67423611111</v>
+        <v>46088.586631944447</v>
       </c>
       <c r="C131" s="3">
-        <v>59693004</v>
+        <v>59807640</v>
       </c>
       <c r="D131" s="4">
-        <v>46091.627928240741</v>
+        <v>46093.511296296296</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G131" s="3">
-        <v>606727287</v>
+        <v>556331131</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>103</v>
+        <v>282</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>19</v>
@@ -21754,7 +21742,7 @@
         <v>27</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L131" s="3" t="s">
         <v>47</v>
@@ -21775,8 +21763,8 @@
         <v>0</v>
       </c>
       <c r="R131" s="7">
-        <f t="shared" ref="R131:R159" ca="1" si="2">NETWORKDAYS(B131,TODAY())</f>
-        <v>10</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>9</v>
       </c>
       <c r="S131" s="7" t="str">
         <f>VLOOKUP(A131,[1]Feuil1!$A:$V,19,FALSE)</f>
@@ -21788,58 +21776,56 @@
       </c>
       <c r="U131" s="7" t="str">
         <f>VLOOKUP(A131,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v>Projet ingénierie</v>
+        <v>PROJET LTE</v>
       </c>
       <c r="V131" s="7" t="str">
         <f>VLOOKUP(A131,[1]Feuil1!$A:$V,22,FALSE)</f>
         <v>Projet</v>
       </c>
     </row>
-    <row r="132" spans="1:22" ht="65" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A132" s="3">
-        <v>59537755</v>
+        <v>59538099</v>
       </c>
       <c r="B132" s="4">
-        <v>46088.586631944447</v>
+        <v>46088.590717592589</v>
       </c>
       <c r="C132" s="3">
-        <v>59807640</v>
+        <v>60033812</v>
       </c>
       <c r="D132" s="4">
-        <v>46093.511296296296</v>
+        <v>46098.426782407405</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G132" s="3">
-        <v>556331131</v>
+        <v>566473307</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K132" s="3" t="s">
-        <v>287</v>
+        <v>42</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="M132" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N132" s="3" t="s">
-        <v>30</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N132" s="3"/>
       <c r="O132" s="3" t="s">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="P132" s="3" t="s">
         <v>19</v>
@@ -21853,45 +21839,45 @@
       </c>
       <c r="S132" s="7" t="str">
         <f>VLOOKUP(A132,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>NON</v>
-      </c>
-      <c r="T132" s="7">
+        <v>non</v>
+      </c>
+      <c r="T132" s="7" t="str">
         <f>VLOOKUP(A132,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>0</v>
+        <v>non</v>
       </c>
       <c r="U132" s="7" t="str">
         <f>VLOOKUP(A132,[1]Feuil1!$A:$V,21,FALSE)</f>
         <v>PROJET LTE</v>
       </c>
-      <c r="V132" s="7" t="str">
+      <c r="V132" s="7">
         <f>VLOOKUP(A132,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>Projet</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A133" s="3">
-        <v>59538099</v>
+        <v>59538597</v>
       </c>
       <c r="B133" s="4">
-        <v>46088.590717592589</v>
+        <v>46088.598194444443</v>
       </c>
       <c r="C133" s="3">
-        <v>60033812</v>
+        <v>60030833</v>
       </c>
       <c r="D133" s="4">
-        <v>46098.426782407405</v>
+        <v>46098.40320601852</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G133" s="3">
         <v>566473307</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>19</v>
@@ -21910,7 +21896,7 @@
       </c>
       <c r="N133" s="3"/>
       <c r="O133" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="P133" s="3" t="s">
         <v>19</v>
@@ -21939,49 +21925,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:22" ht="26" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A134" s="3">
-        <v>59538597</v>
+        <v>59541145</v>
       </c>
       <c r="B134" s="4">
-        <v>46088.598194444443</v>
+        <v>46088.634837962964</v>
       </c>
       <c r="C134" s="3">
-        <v>60030833</v>
+        <v>59799803</v>
       </c>
       <c r="D134" s="4">
-        <v>46098.40320601852</v>
+        <v>46093.453530092593</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="F134" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G134" s="3">
+        <v>546008131</v>
+      </c>
+      <c r="H134" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="G134" s="3">
-        <v>566473307</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="I134" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>42</v>
+        <v>283</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="M134" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N134" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="N134" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="O134" s="3" t="s">
-        <v>289</v>
+        <v>19</v>
       </c>
       <c r="P134" s="3" t="s">
         <v>19</v>
@@ -21995,45 +21983,45 @@
       </c>
       <c r="S134" s="7" t="str">
         <f>VLOOKUP(A134,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>non</v>
-      </c>
-      <c r="T134" s="7" t="str">
+        <v>NON</v>
+      </c>
+      <c r="T134" s="7">
         <f>VLOOKUP(A134,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>non</v>
+        <v>0</v>
       </c>
       <c r="U134" s="7" t="str">
         <f>VLOOKUP(A134,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v>PROJET LTE</v>
-      </c>
-      <c r="V134" s="7">
+        <v>Projet ingénierie</v>
+      </c>
+      <c r="V134" s="7" t="str">
         <f>VLOOKUP(A134,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>0</v>
+        <v>Projet</v>
       </c>
     </row>
-    <row r="135" spans="1:22" ht="52" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:22" ht="65" x14ac:dyDescent="0.35">
       <c r="A135" s="3">
-        <v>59541145</v>
+        <v>59606122</v>
       </c>
       <c r="B135" s="4">
-        <v>46088.634837962964</v>
+        <v>46090.447604166664</v>
       </c>
       <c r="C135" s="3">
-        <v>59799803</v>
+        <v>59682305</v>
       </c>
       <c r="D135" s="4">
-        <v>46093.453530092593</v>
+        <v>46091.541701388887</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>105</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G135" s="3">
-        <v>546008131</v>
+        <v>708454305</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>19</v>
@@ -22042,7 +22030,7 @@
         <v>27</v>
       </c>
       <c r="K135" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L135" s="3" t="s">
         <v>47</v>
@@ -22083,30 +22071,30 @@
         <v>Projet</v>
       </c>
     </row>
-    <row r="136" spans="1:22" ht="65" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A136" s="3">
-        <v>59606122</v>
+        <v>59615935</v>
       </c>
       <c r="B136" s="4">
-        <v>46090.447604166664</v>
+        <v>46090.512303240743</v>
       </c>
       <c r="C136" s="3">
-        <v>59682305</v>
+        <v>60052243</v>
       </c>
       <c r="D136" s="4">
-        <v>46091.541701388887</v>
+        <v>46098.565104166664</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G136" s="3">
-        <v>708454305</v>
+        <v>767081456</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>19</v>
@@ -22115,19 +22103,19 @@
         <v>27</v>
       </c>
       <c r="K136" s="3" t="s">
-        <v>287</v>
+        <v>42</v>
       </c>
       <c r="L136" s="3" t="s">
         <v>47</v>
       </c>
       <c r="M136" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="N136" s="3" t="s">
         <v>30</v>
       </c>
       <c r="O136" s="3" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="P136" s="3" t="s">
         <v>19</v>
@@ -22141,57 +22129,57 @@
       </c>
       <c r="S136" s="7" t="str">
         <f>VLOOKUP(A136,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>NON</v>
-      </c>
-      <c r="T136" s="7">
+        <v>Non</v>
+      </c>
+      <c r="T136" s="7" t="str">
         <f>VLOOKUP(A136,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>0</v>
+        <v>OCI</v>
       </c>
       <c r="U136" s="7" t="str">
         <f>VLOOKUP(A136,[1]Feuil1!$A:$V,21,FALSE)</f>
         <v>Projet ingénierie</v>
       </c>
-      <c r="V136" s="7" t="str">
+      <c r="V136" s="7">
         <f>VLOOKUP(A136,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>Projet</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:22" ht="39" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:22" ht="208" x14ac:dyDescent="0.35">
       <c r="A137" s="3">
-        <v>59615935</v>
+        <v>59684312</v>
       </c>
       <c r="B137" s="4">
-        <v>46090.512303240743</v>
+        <v>46091.557453703703</v>
       </c>
       <c r="C137" s="3">
-        <v>60052243</v>
+        <v>59736324</v>
       </c>
       <c r="D137" s="4">
-        <v>46098.565104166664</v>
+        <v>46092.496296296296</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>221</v>
+        <v>295</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G137" s="3">
-        <v>767081456</v>
+        <v>3130227350</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="K137" s="3" t="s">
         <v>42</v>
       </c>
       <c r="L137" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="M137" s="3" t="s">
         <v>23</v>
@@ -22200,17 +22188,17 @@
         <v>30</v>
       </c>
       <c r="O137" s="3" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="P137" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q137" s="3">
-        <v>0</v>
+      <c r="Q137" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R137" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S137" s="7" t="str">
         <f>VLOOKUP(A137,[1]Feuil1!$A:$V,19,FALSE)</f>
@@ -22218,7 +22206,7 @@
       </c>
       <c r="T137" s="7" t="str">
         <f>VLOOKUP(A137,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>OCI</v>
+        <v xml:space="preserve">CLIENT </v>
       </c>
       <c r="U137" s="7" t="str">
         <f>VLOOKUP(A137,[1]Feuil1!$A:$V,21,FALSE)</f>
@@ -22229,45 +22217,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:22" ht="208" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A138" s="3">
-        <v>59684312</v>
+        <v>59706056</v>
       </c>
       <c r="B138" s="4">
-        <v>46091.557453703703</v>
+        <v>46091.727199074077</v>
       </c>
       <c r="C138" s="3">
-        <v>59736324</v>
+        <v>59799692</v>
       </c>
       <c r="D138" s="4">
-        <v>46092.496296296296</v>
+        <v>46093.453136574077</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>297</v>
+        <v>208</v>
       </c>
       <c r="G138" s="3">
-        <v>3130227350</v>
+        <v>708086472</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>298</v>
+        <v>107</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="K138" s="3" t="s">
-        <v>42</v>
+        <v>281</v>
       </c>
       <c r="L138" s="3" t="s">
         <v>29</v>
       </c>
       <c r="M138" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="N138" s="3" t="s">
         <v>30</v>
@@ -22278,8 +22266,8 @@
       <c r="P138" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q138" s="3" t="s">
-        <v>19</v>
+      <c r="Q138" s="3">
+        <v>0</v>
       </c>
       <c r="R138" s="7">
         <f t="shared" ca="1" si="2"/>
@@ -22287,36 +22275,36 @@
       </c>
       <c r="S138" s="7" t="str">
         <f>VLOOKUP(A138,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>Non</v>
-      </c>
-      <c r="T138" s="7" t="str">
+        <v>NON</v>
+      </c>
+      <c r="T138" s="7">
         <f>VLOOKUP(A138,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v xml:space="preserve">CLIENT </v>
+        <v>0</v>
       </c>
       <c r="U138" s="7" t="str">
         <f>VLOOKUP(A138,[1]Feuil1!$A:$V,21,FALSE)</f>
         <v>Projet ingénierie</v>
       </c>
-      <c r="V138" s="7">
+      <c r="V138" s="7" t="str">
         <f>VLOOKUP(A138,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>0</v>
+        <v>Projet</v>
       </c>
     </row>
-    <row r="139" spans="1:22" ht="52" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A139" s="3">
-        <v>59706056</v>
+        <v>59706490</v>
       </c>
       <c r="B139" s="4">
-        <v>46091.727199074077</v>
+        <v>46091.731006944443</v>
       </c>
       <c r="C139" s="3">
-        <v>59799692</v>
+        <v>59799753</v>
       </c>
       <c r="D139" s="4">
-        <v>46093.453136574077</v>
+        <v>46093.4530787037</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>105</v>
+        <v>296</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>208</v>
@@ -22325,7 +22313,7 @@
         <v>708086472</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>107</v>
+        <v>212</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>19</v>
@@ -22334,7 +22322,7 @@
         <v>35</v>
       </c>
       <c r="K139" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L139" s="3" t="s">
         <v>29</v>
@@ -22346,7 +22334,7 @@
         <v>30</v>
       </c>
       <c r="O139" s="3" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="P139" s="3" t="s">
         <v>19</v>
@@ -22377,19 +22365,19 @@
     </row>
     <row r="140" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A140" s="3">
-        <v>59706490</v>
+        <v>59706900</v>
       </c>
       <c r="B140" s="4">
-        <v>46091.731006944443</v>
+        <v>46091.734016203707</v>
       </c>
       <c r="C140" s="3">
-        <v>59799753</v>
+        <v>59799641</v>
       </c>
       <c r="D140" s="4">
-        <v>46093.4530787037</v>
+        <v>46093.452222222222</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>208</v>
@@ -22398,7 +22386,7 @@
         <v>708086472</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>19</v>
@@ -22407,7 +22395,7 @@
         <v>35</v>
       </c>
       <c r="K140" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="L140" s="3" t="s">
         <v>29</v>
@@ -22419,7 +22407,7 @@
         <v>30</v>
       </c>
       <c r="O140" s="3" t="s">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="P140" s="3" t="s">
         <v>19</v>
@@ -22441,49 +22429,49 @@
       </c>
       <c r="U140" s="7" t="str">
         <f>VLOOKUP(A140,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v>Projet ingénierie</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="V140" s="7" t="str">
         <f>VLOOKUP(A140,[1]Feuil1!$A:$V,22,FALSE)</f>
         <v>Projet</v>
       </c>
     </row>
-    <row r="141" spans="1:22" ht="39" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A141" s="3">
-        <v>59706900</v>
+        <v>59793967</v>
       </c>
       <c r="B141" s="4">
-        <v>46091.734016203707</v>
+        <v>46093.406724537039</v>
       </c>
       <c r="C141" s="3">
-        <v>59799641</v>
+        <v>60109623</v>
       </c>
       <c r="D141" s="4">
-        <v>46093.452222222222</v>
+        <v>46099.495104166665</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>300</v>
+        <v>221</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>208</v>
+        <v>297</v>
       </c>
       <c r="G141" s="3">
-        <v>708086472</v>
+        <v>506727287</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>213</v>
+        <v>278</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K141" s="3" t="s">
-        <v>285</v>
+        <v>42</v>
       </c>
       <c r="L141" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="M141" s="3" t="s">
         <v>37</v>
@@ -22492,7 +22480,7 @@
         <v>30</v>
       </c>
       <c r="O141" s="3" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="P141" s="3" t="s">
         <v>19</v>
@@ -22502,7 +22490,7 @@
       </c>
       <c r="R141" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S141" s="7" t="str">
         <f>VLOOKUP(A141,[1]Feuil1!$A:$V,19,FALSE)</f>
@@ -22521,30 +22509,30 @@
         <v>Projet</v>
       </c>
     </row>
-    <row r="142" spans="1:22" ht="26" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:22" ht="91" x14ac:dyDescent="0.35">
       <c r="A142" s="3">
-        <v>59793967</v>
+        <v>59801109</v>
       </c>
       <c r="B142" s="4">
-        <v>46093.406724537039</v>
+        <v>46093.464594907404</v>
       </c>
       <c r="C142" s="3">
-        <v>60109623</v>
+        <v>60196153</v>
       </c>
       <c r="D142" s="4">
-        <v>46099.495104166665</v>
+        <v>46100.659583333334</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>221</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G142" s="3">
-        <v>506727287</v>
+        <v>709173657</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>19</v>
@@ -22565,7 +22553,7 @@
         <v>30</v>
       </c>
       <c r="O142" s="3" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="P142" s="3" t="s">
         <v>19</v>
@@ -22579,45 +22567,45 @@
       </c>
       <c r="S142" s="7" t="str">
         <f>VLOOKUP(A142,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>NON</v>
-      </c>
-      <c r="T142" s="7">
+        <v>Non</v>
+      </c>
+      <c r="T142" s="7" t="str">
         <f>VLOOKUP(A142,[1]Feuil1!$A:$V,20,FALSE)</f>
+        <v xml:space="preserve">CLIENT </v>
+      </c>
+      <c r="U142" s="7">
+        <f>VLOOKUP(A142,[1]Feuil1!$A:$V,21,FALSE)</f>
         <v>0</v>
-      </c>
-      <c r="U142" s="7" t="str">
-        <f>VLOOKUP(A142,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v xml:space="preserve"> </v>
       </c>
       <c r="V142" s="7" t="str">
         <f>VLOOKUP(A142,[1]Feuil1!$A:$V,22,FALSE)</f>
         <v>Projet</v>
       </c>
     </row>
-    <row r="143" spans="1:22" ht="91" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:22" ht="65" x14ac:dyDescent="0.35">
       <c r="A143" s="3">
-        <v>59801109</v>
+        <v>59813505</v>
       </c>
       <c r="B143" s="4">
-        <v>46093.464594907404</v>
+        <v>46093.557256944441</v>
       </c>
       <c r="C143" s="3">
-        <v>60196153</v>
+        <v>60136980</v>
       </c>
       <c r="D143" s="4">
-        <v>46100.659583333334</v>
+        <v>46099.706805555557</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>221</v>
+        <v>302</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G143" s="3">
-        <v>709173657</v>
+        <v>706727287</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>19</v>
@@ -22626,7 +22614,7 @@
         <v>27</v>
       </c>
       <c r="K143" s="3" t="s">
-        <v>42</v>
+        <v>283</v>
       </c>
       <c r="L143" s="3" t="s">
         <v>47</v>
@@ -22635,10 +22623,10 @@
         <v>37</v>
       </c>
       <c r="N143" s="3" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="O143" s="3" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="P143" s="3" t="s">
         <v>19</v>
@@ -22652,54 +22640,54 @@
       </c>
       <c r="S143" s="7" t="str">
         <f>VLOOKUP(A143,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>Non</v>
-      </c>
-      <c r="T143" s="7" t="str">
+        <v>NON</v>
+      </c>
+      <c r="T143" s="7">
         <f>VLOOKUP(A143,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v xml:space="preserve">CLIENT </v>
-      </c>
-      <c r="U143" s="7">
+        <v>0</v>
+      </c>
+      <c r="U143" s="7" t="str">
         <f>VLOOKUP(A143,[1]Feuil1!$A:$V,21,FALSE)</f>
+        <v>Projet ingénierie</v>
+      </c>
+      <c r="V143" s="7">
+        <f>VLOOKUP(A143,[1]Feuil1!$A:$V,22,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="V143" s="7" t="str">
-        <f>VLOOKUP(A143,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>Projet</v>
-      </c>
     </row>
-    <row r="144" spans="1:22" ht="65" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:22" ht="78" x14ac:dyDescent="0.35">
       <c r="A144" s="3">
-        <v>59813505</v>
+        <v>59816396</v>
       </c>
       <c r="B144" s="4">
-        <v>46093.557256944441</v>
+        <v>46093.580590277779</v>
       </c>
       <c r="C144" s="3">
-        <v>60136980</v>
+        <v>60137506</v>
       </c>
       <c r="D144" s="4">
-        <v>46099.706805555557</v>
+        <v>46099.711053240739</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="F144" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G144" s="3">
+        <v>506727287</v>
+      </c>
+      <c r="H144" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="G144" s="3">
-        <v>706727287</v>
-      </c>
-      <c r="H144" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="I144" s="3" t="s">
-        <v>19</v>
+      <c r="I144" s="3">
+        <v>1848446</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="K144" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L144" s="3" t="s">
         <v>47</v>
@@ -22711,7 +22699,7 @@
         <v>117</v>
       </c>
       <c r="O144" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="P144" s="3" t="s">
         <v>19</v>
@@ -22740,39 +22728,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:22" ht="78" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A145" s="3">
-        <v>59816396</v>
+        <v>59820678</v>
       </c>
       <c r="B145" s="4">
-        <v>46093.580590277779</v>
+        <v>46093.612222222226</v>
       </c>
       <c r="C145" s="3">
-        <v>60137506</v>
+        <v>60139442</v>
       </c>
       <c r="D145" s="4">
-        <v>46099.711053240739</v>
+        <v>46099.725694444445</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G145" s="3">
         <v>506727287</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="I145" s="3">
-        <v>1848446</v>
+        <v>306</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="K145" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L145" s="3" t="s">
         <v>47</v>
@@ -22784,7 +22772,7 @@
         <v>117</v>
       </c>
       <c r="O145" s="3" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="P145" s="3" t="s">
         <v>19</v>
@@ -22815,28 +22803,28 @@
     </row>
     <row r="146" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A146" s="3">
-        <v>59820678</v>
+        <v>59821965</v>
       </c>
       <c r="B146" s="4">
-        <v>46093.612222222226</v>
+        <v>46093.621331018519</v>
       </c>
       <c r="C146" s="3">
-        <v>60139442</v>
+        <v>60033589</v>
       </c>
       <c r="D146" s="4">
-        <v>46099.725694444445</v>
+        <v>46098.424780092595</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>306</v>
+        <v>105</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G146" s="3">
-        <v>506727287</v>
+        <v>101383885</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>310</v>
+        <v>156</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>19</v>
@@ -22845,16 +22833,16 @@
         <v>27</v>
       </c>
       <c r="K146" s="3" t="s">
-        <v>287</v>
+        <v>42</v>
       </c>
       <c r="L146" s="3" t="s">
         <v>47</v>
       </c>
       <c r="M146" s="3" t="s">
-        <v>37</v>
+        <v>308</v>
       </c>
       <c r="N146" s="3" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="O146" s="3" t="s">
         <v>19</v>
@@ -22862,8 +22850,8 @@
       <c r="P146" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q146" s="3">
-        <v>0</v>
+      <c r="Q146" s="5">
+        <v>3000000</v>
       </c>
       <c r="R146" s="7">
         <f t="shared" ca="1" si="2"/>
@@ -22871,45 +22859,45 @@
       </c>
       <c r="S146" s="7" t="str">
         <f>VLOOKUP(A146,[1]Feuil1!$A:$V,19,FALSE)</f>
+        <v>Non</v>
+      </c>
+      <c r="T146" s="7" t="str">
+        <f>VLOOKUP(A146,[1]Feuil1!$A:$V,20,FALSE)</f>
         <v>NON</v>
-      </c>
-      <c r="T146" s="7">
-        <f>VLOOKUP(A146,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>0</v>
       </c>
       <c r="U146" s="7" t="str">
         <f>VLOOKUP(A146,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v>Projet ingénierie</v>
+        <v>EVENT REGUL</v>
       </c>
       <c r="V146" s="7">
         <f>VLOOKUP(A146,[1]Feuil1!$A:$V,22,FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:22" ht="52" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:22" ht="65" x14ac:dyDescent="0.35">
       <c r="A147" s="3">
-        <v>59821965</v>
+        <v>59824550</v>
       </c>
       <c r="B147" s="4">
-        <v>46093.621331018519</v>
+        <v>46093.6405787037</v>
       </c>
       <c r="C147" s="3">
-        <v>60033589</v>
+        <v>59859139</v>
       </c>
       <c r="D147" s="4">
-        <v>46098.424780092595</v>
+        <v>46094.429143518515</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G147" s="3">
-        <v>101383885</v>
+        <v>506727287</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>156</v>
+        <v>310</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>19</v>
@@ -22924,7 +22912,7 @@
         <v>47</v>
       </c>
       <c r="M147" s="3" t="s">
-        <v>312</v>
+        <v>37</v>
       </c>
       <c r="N147" s="3" t="s">
         <v>30</v>
@@ -22935,8 +22923,8 @@
       <c r="P147" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q147" s="5">
-        <v>3000000</v>
+      <c r="Q147" s="3">
+        <v>0</v>
       </c>
       <c r="R147" s="7">
         <f t="shared" ca="1" si="2"/>
@@ -22944,72 +22932,72 @@
       </c>
       <c r="S147" s="7" t="str">
         <f>VLOOKUP(A147,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>Non</v>
-      </c>
-      <c r="T147" s="7" t="str">
+        <v>NON</v>
+      </c>
+      <c r="T147" s="7">
         <f>VLOOKUP(A147,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>NON</v>
+        <v>0</v>
       </c>
       <c r="U147" s="7" t="str">
         <f>VLOOKUP(A147,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v>EVENT REGUL</v>
+        <v>Projet ingénierie</v>
       </c>
       <c r="V147" s="7">
         <f>VLOOKUP(A147,[1]Feuil1!$A:$V,22,FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:22" ht="65" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A148" s="3">
-        <v>59824550</v>
+        <v>59834036</v>
       </c>
       <c r="B148" s="4">
-        <v>46093.6405787037</v>
+        <v>46093.713761574072</v>
       </c>
       <c r="C148" s="3">
-        <v>59859139</v>
+        <v>60133383</v>
       </c>
       <c r="D148" s="4">
-        <v>46094.429143518515</v>
+        <v>46099.680173611108</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G148" s="3">
-        <v>506727287</v>
+        <v>787309090</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>314</v>
+        <v>121</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K148" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L148" s="3" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="M148" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="N148" s="3" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="O148" s="3" t="s">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="P148" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q148" s="3">
-        <v>0</v>
+      <c r="Q148" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R148" s="7">
         <f t="shared" ca="1" si="2"/>
@@ -23017,15 +23005,15 @@
       </c>
       <c r="S148" s="7" t="str">
         <f>VLOOKUP(A148,[1]Feuil1!$A:$V,19,FALSE)</f>
+        <v>Non</v>
+      </c>
+      <c r="T148" s="7" t="str">
+        <f>VLOOKUP(A148,[1]Feuil1!$A:$V,20,FALSE)</f>
         <v>NON</v>
       </c>
-      <c r="T148" s="7">
-        <f>VLOOKUP(A148,[1]Feuil1!$A:$V,20,FALSE)</f>
+      <c r="U148" s="7">
+        <f>VLOOKUP(A148,[1]Feuil1!$A:$V,21,FALSE)</f>
         <v>0</v>
-      </c>
-      <c r="U148" s="7" t="str">
-        <f>VLOOKUP(A148,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v>Projet ingénierie</v>
       </c>
       <c r="V148" s="7">
         <f>VLOOKUP(A148,[1]Feuil1!$A:$V,22,FALSE)</f>
@@ -23034,28 +23022,28 @@
     </row>
     <row r="149" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A149" s="3">
-        <v>59834036</v>
+        <v>59888143</v>
       </c>
       <c r="B149" s="4">
-        <v>46093.713761574072</v>
+        <v>46094.646597222221</v>
       </c>
       <c r="C149" s="3">
-        <v>60133383</v>
+        <v>60162137</v>
       </c>
       <c r="D149" s="4">
-        <v>46099.680173611108</v>
+        <v>46100.409004629626</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G149" s="3">
-        <v>787309090</v>
+        <v>708858866</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>121</v>
+        <v>313</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>19</v>
@@ -23073,10 +23061,10 @@
         <v>23</v>
       </c>
       <c r="N149" s="3" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="O149" s="3" t="s">
-        <v>222</v>
+        <v>146</v>
       </c>
       <c r="P149" s="3" t="s">
         <v>19</v>
@@ -23086,61 +23074,61 @@
       </c>
       <c r="R149" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="S149" s="7" t="str">
+        <v>5</v>
+      </c>
+      <c r="S149" s="7" t="e">
         <f>VLOOKUP(A149,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>Non</v>
-      </c>
-      <c r="T149" s="7" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="T149" s="7" t="e">
         <f>VLOOKUP(A149,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>NON</v>
-      </c>
-      <c r="U149" s="7">
+        <v>#N/A</v>
+      </c>
+      <c r="U149" s="7" t="e">
         <f>VLOOKUP(A149,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="V149" s="7">
+        <v>#N/A</v>
+      </c>
+      <c r="V149" s="7" t="e">
         <f>VLOOKUP(A149,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
-    <row r="150" spans="1:22" ht="52" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A150" s="3">
-        <v>59888143</v>
+        <v>59889656</v>
       </c>
       <c r="B150" s="4">
-        <v>46094.646597222221</v>
+        <v>46094.657060185185</v>
       </c>
       <c r="C150" s="3">
-        <v>60162137</v>
+        <v>60199357</v>
       </c>
       <c r="D150" s="4">
-        <v>46100.409004629626</v>
+        <v>46100.685902777775</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>44</v>
+        <v>179</v>
       </c>
       <c r="F150" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G150" s="3">
+        <v>709813123</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J150" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="G150" s="3">
-        <v>708858866</v>
-      </c>
-      <c r="H150" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="I150" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J150" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="K150" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L150" s="3" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="M150" s="3" t="s">
         <v>23</v>
@@ -23154,8 +23142,8 @@
       <c r="P150" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q150" s="3" t="s">
-        <v>19</v>
+      <c r="Q150" s="5">
+        <v>600000</v>
       </c>
       <c r="R150" s="7">
         <f t="shared" ca="1" si="2"/>
@@ -23180,34 +23168,34 @@
     </row>
     <row r="151" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A151" s="3">
-        <v>59889656</v>
+        <v>59894743</v>
       </c>
       <c r="B151" s="4">
-        <v>46094.657060185185</v>
+        <v>46094.687673611108</v>
       </c>
       <c r="C151" s="3">
-        <v>60199357</v>
+        <v>60193377</v>
       </c>
       <c r="D151" s="4">
-        <v>46100.685902777775</v>
+        <v>46100.641863425924</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G151" s="3">
-        <v>709813123</v>
+        <v>759668146</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>319</v>
+        <v>121</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>320</v>
+        <v>27</v>
       </c>
       <c r="K151" s="3" t="s">
         <v>42</v>
@@ -23216,19 +23204,19 @@
         <v>47</v>
       </c>
       <c r="M151" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="N151" s="3" t="s">
         <v>30</v>
       </c>
       <c r="O151" s="3" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="P151" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q151" s="5">
-        <v>600000</v>
+      <c r="Q151" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R151" s="7">
         <f t="shared" ca="1" si="2"/>
@@ -23251,36 +23239,36 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="152" spans="1:22" ht="26" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:22" ht="78" x14ac:dyDescent="0.35">
       <c r="A152" s="3">
-        <v>59894743</v>
+        <v>59894758</v>
       </c>
       <c r="B152" s="4">
-        <v>46094.687673611108</v>
+        <v>46094.687719907408</v>
       </c>
       <c r="C152" s="3">
-        <v>60193377</v>
+        <v>60202861</v>
       </c>
       <c r="D152" s="4">
-        <v>46100.641863425924</v>
+        <v>46100.711192129631</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G152" s="3">
         <v>759668146</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I152" s="3" t="s">
-        <v>19</v>
+        <v>318</v>
+      </c>
+      <c r="I152" s="3">
+        <v>1849216</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="K152" s="3" t="s">
         <v>42</v>
@@ -23289,19 +23277,19 @@
         <v>47</v>
       </c>
       <c r="M152" s="3" t="s">
-        <v>37</v>
+        <v>173</v>
       </c>
       <c r="N152" s="3" t="s">
         <v>30</v>
       </c>
       <c r="O152" s="3" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="P152" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q152" s="3" t="s">
-        <v>19</v>
+      <c r="Q152" s="5">
+        <v>1000000</v>
       </c>
       <c r="R152" s="7">
         <f t="shared" ca="1" si="2"/>
@@ -23324,61 +23312,61 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="153" spans="1:22" ht="78" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:22" ht="65" x14ac:dyDescent="0.35">
       <c r="A153" s="3">
-        <v>59894758</v>
+        <v>60025705</v>
       </c>
       <c r="B153" s="4">
-        <v>46094.687719907408</v>
+        <v>46098.34920138889</v>
       </c>
       <c r="C153" s="3">
-        <v>60202861</v>
+        <v>60165414</v>
       </c>
       <c r="D153" s="4">
-        <v>46100.711192129631</v>
+        <v>46100.437986111108</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="F153" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G153" s="3">
+        <v>704080021</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="I153" s="3">
+        <v>1849206</v>
+      </c>
+      <c r="J153" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K153" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="G153" s="3">
-        <v>759668146</v>
-      </c>
-      <c r="H153" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="I153" s="3">
-        <v>1849216</v>
-      </c>
-      <c r="J153" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K153" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="L153" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="M153" s="3" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="N153" s="3" t="s">
         <v>30</v>
       </c>
       <c r="O153" s="3" t="s">
-        <v>98</v>
+        <v>322</v>
       </c>
       <c r="P153" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q153" s="5">
-        <v>1000000</v>
+      <c r="Q153" s="3">
+        <v>0</v>
       </c>
       <c r="R153" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S153" s="7" t="e">
         <f>VLOOKUP(A153,[1]Feuil1!$A:$V,19,FALSE)</f>
@@ -23397,51 +23385,51 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="154" spans="1:22" ht="65" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A154" s="3">
-        <v>60025705</v>
+        <v>60026486</v>
       </c>
       <c r="B154" s="4">
-        <v>46098.34920138889</v>
+        <v>46098.36173611111</v>
       </c>
       <c r="C154" s="3">
-        <v>60165414</v>
+        <v>60121930</v>
       </c>
       <c r="D154" s="4">
-        <v>46100.437986111108</v>
+        <v>46099.594039351854</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>184</v>
+        <v>105</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
       <c r="G154" s="3">
-        <v>704080021</v>
+        <v>506727287</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="I154" s="3">
-        <v>1849206</v>
+        <v>103</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="J154" s="3" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K154" s="3" t="s">
-        <v>325</v>
+        <v>283</v>
       </c>
       <c r="L154" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="M154" s="3" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N154" s="3" t="s">
         <v>30</v>
       </c>
       <c r="O154" s="3" t="s">
-        <v>326</v>
+        <v>19</v>
       </c>
       <c r="P154" s="3" t="s">
         <v>19</v>
@@ -23472,46 +23460,46 @@
     </row>
     <row r="155" spans="1:22" ht="52" x14ac:dyDescent="0.35">
       <c r="A155" s="3">
-        <v>60026486</v>
+        <v>60084243</v>
       </c>
       <c r="B155" s="4">
-        <v>46098.36173611111</v>
+        <v>46098.817627314813</v>
       </c>
       <c r="C155" s="3">
-        <v>60121930</v>
+        <v>60105219</v>
       </c>
       <c r="D155" s="4">
-        <v>46099.594039351854</v>
+        <v>46099.462893518517</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>105</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="G155" s="3">
-        <v>506727287</v>
+        <v>707708502</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I155" s="3" t="s">
-        <v>19</v>
+        <v>121</v>
+      </c>
+      <c r="I155" s="3">
+        <v>0</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K155" s="3" t="s">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="L155" s="3" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="M155" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="N155" s="3" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="O155" s="3" t="s">
         <v>19</v>
@@ -23519,8 +23507,8 @@
       <c r="P155" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q155" s="3">
-        <v>0</v>
+      <c r="Q155" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R155" s="7">
         <f t="shared" ca="1" si="2"/>
@@ -23543,33 +23531,33 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="156" spans="1:22" ht="52" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:22" ht="26" x14ac:dyDescent="0.35">
       <c r="A156" s="3">
-        <v>60084243</v>
+        <v>60154802</v>
       </c>
       <c r="B156" s="4">
-        <v>46098.817627314813</v>
+        <v>46100.305405092593</v>
       </c>
       <c r="C156" s="3">
-        <v>60105219</v>
+        <v>60191170</v>
       </c>
       <c r="D156" s="4">
-        <v>46099.462893518517</v>
+        <v>46100.626759259256</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>327</v>
+        <v>67</v>
       </c>
       <c r="G156" s="3">
-        <v>707708502</v>
+        <v>707225975</v>
       </c>
       <c r="H156" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I156" s="3">
-        <v>0</v>
+      <c r="I156" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="J156" s="3" t="s">
         <v>20</v>
@@ -23584,10 +23572,10 @@
         <v>23</v>
       </c>
       <c r="N156" s="3" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="O156" s="3" t="s">
-        <v>19</v>
+        <v>324</v>
       </c>
       <c r="P156" s="3" t="s">
         <v>19</v>
@@ -23597,7 +23585,7 @@
       </c>
       <c r="R156" s="7">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S156" s="7" t="e">
         <f>VLOOKUP(A156,[1]Feuil1!$A:$V,19,FALSE)</f>
@@ -23616,57 +23604,57 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="157" spans="1:22" ht="26" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:22" ht="65" x14ac:dyDescent="0.35">
       <c r="A157" s="3">
-        <v>60154802</v>
+        <v>60162087</v>
       </c>
       <c r="B157" s="4">
-        <v>46100.305405092593</v>
+        <v>46100.408645833333</v>
       </c>
       <c r="C157" s="3">
-        <v>60191170</v>
+        <v>60164327</v>
       </c>
       <c r="D157" s="4">
-        <v>46100.626759259256</v>
+        <v>46100.428159722222</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>207</v>
+        <v>326</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>67</v>
+        <v>325</v>
       </c>
       <c r="G157" s="3">
-        <v>707225975</v>
+        <v>757271671</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K157" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L157" s="3" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="M157" s="3" t="s">
-        <v>23</v>
+        <v>308</v>
       </c>
       <c r="N157" s="3" t="s">
         <v>30</v>
       </c>
       <c r="O157" s="3" t="s">
-        <v>328</v>
+        <v>19</v>
       </c>
       <c r="P157" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q157" s="3" t="s">
-        <v>19</v>
+      <c r="Q157" s="5">
+        <v>400000</v>
       </c>
       <c r="R157" s="7">
         <f t="shared" ca="1" si="2"/>
@@ -23689,45 +23677,45 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="158" spans="1:22" ht="65" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:22" ht="39" x14ac:dyDescent="0.35">
       <c r="A158" s="3">
-        <v>60162087</v>
+        <v>60190035</v>
       </c>
       <c r="B158" s="4">
-        <v>46100.408645833333</v>
+        <v>46100.619201388887</v>
       </c>
       <c r="C158" s="3">
-        <v>60164327</v>
+        <v>60194911</v>
       </c>
       <c r="D158" s="4">
-        <v>46100.428159722222</v>
+        <v>46100.650335648148</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G158" s="3">
-        <v>757271671</v>
+        <v>708142290</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J158" s="3" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="K158" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="L158" s="3" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="M158" s="3" t="s">
-        <v>312</v>
+        <v>23</v>
       </c>
       <c r="N158" s="3" t="s">
         <v>30</v>
@@ -23738,8 +23726,8 @@
       <c r="P158" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q158" s="5">
-        <v>400000</v>
+      <c r="Q158" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="R158" s="7">
         <f t="shared" ca="1" si="2"/>
@@ -23762,81 +23750,8 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="159" spans="1:22" ht="39" x14ac:dyDescent="0.35">
-      <c r="A159" s="3">
-        <v>60190035</v>
-      </c>
-      <c r="B159" s="4">
-        <v>46100.619201388887</v>
-      </c>
-      <c r="C159" s="3">
-        <v>60194911</v>
-      </c>
-      <c r="D159" s="4">
-        <v>46100.650335648148</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F159" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G159" s="3">
-        <v>708142290</v>
-      </c>
-      <c r="H159" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I159" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J159" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K159" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L159" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M159" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N159" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O159" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P159" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q159" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="R159" s="7">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="S159" s="7" t="e">
-        <f>VLOOKUP(A159,[1]Feuil1!$A:$V,19,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="T159" s="7" t="e">
-        <f>VLOOKUP(A159,[1]Feuil1!$A:$V,20,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="U159" s="7" t="e">
-        <f>VLOOKUP(A159,[1]Feuil1!$A:$V,21,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="V159" s="7" t="e">
-        <f>VLOOKUP(A159,[1]Feuil1!$A:$V,22,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V159" xr:uid="{91676046-DC9A-418C-A539-44748F9868EB}"/>
+  <autoFilter ref="A1:V158" xr:uid="{91676046-DC9A-418C-A539-44748F9868EB}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/Attachments/Bureau/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B9A3CC5-1FDD-4F3D-A54D-E25D7A9C98CA}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E29467CA-F562-427F-A28D-49B4C01DCDF7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil2" sheetId="38" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="39" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil2!$A$1:$Q$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$Q$147</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="309">
   <si>
     <t>-</t>
   </si>
@@ -320,12 +320,6 @@
     <t>ABOISSO</t>
   </si>
   <si>
-    <t>NANO</t>
-  </si>
-  <si>
-    <t>YOPOUGON ANDOKOI</t>
-  </si>
-  <si>
     <t>AGILITY BUSINESS PARKS COTE D’IVOIRE</t>
   </si>
   <si>
@@ -518,9 +512,6 @@
     <t>MANCALA</t>
   </si>
   <si>
-    <t>MINISTERE DE LA DEFENSE</t>
-  </si>
-  <si>
     <t>MFI CI (SODEXAM)</t>
   </si>
   <si>
@@ -710,9 +701,6 @@
     <t>ANYAMA</t>
   </si>
   <si>
-    <t>EUROFIND PARTICIPATION</t>
-  </si>
-  <si>
     <t>radio</t>
   </si>
   <si>
@@ -764,9 +752,6 @@
     <t>BUVPN260039</t>
   </si>
   <si>
-    <t>GI : 1841846</t>
-  </si>
-  <si>
     <t>VIPNET</t>
   </si>
   <si>
@@ -779,18 +764,12 @@
     <t>SYTHD260018</t>
   </si>
   <si>
-    <t>Support IP: Correction</t>
-  </si>
-  <si>
     <t>BUVPN260055</t>
   </si>
   <si>
     <t>BUVPN260056</t>
   </si>
   <si>
-    <t>Support IP: Config Eq Acces</t>
-  </si>
-  <si>
     <t>BUVPN240108</t>
   </si>
   <si>
@@ -827,36 +806,18 @@
     <t>SECO TREICHVILLE</t>
   </si>
   <si>
-    <t>SYNELIA GROUP AFRIQUE</t>
-  </si>
-  <si>
     <t>STE DGTCP</t>
   </si>
   <si>
     <t>PLATEAU EN FACE DU PALAIS DE JUSTICE</t>
   </si>
   <si>
-    <t>AMOAMAN &amp; ASSOCIES</t>
-  </si>
-  <si>
-    <t>COCODY RIVIEA 3</t>
-  </si>
-  <si>
-    <t>LSI Gold</t>
-  </si>
-  <si>
     <t>MAXAM CI</t>
   </si>
   <si>
-    <t>radio_lte</t>
-  </si>
-  <si>
     <t>BUVPN250061</t>
   </si>
   <si>
-    <t>SIE : Affectation des ressources</t>
-  </si>
-  <si>
     <t>SOCIETE GEZA EXPERTISE</t>
   </si>
   <si>
@@ -869,9 +830,6 @@
     <t>SYTHD260081</t>
   </si>
   <si>
-    <t>Technicien zone: Intervention</t>
-  </si>
-  <si>
     <t>BUVPN260063</t>
   </si>
   <si>
@@ -887,27 +845,9 @@
     <t>DIAWALA//VOIE INCONNUE/SECO DIAWALA 05 06 72 72 87</t>
   </si>
   <si>
-    <t>SYTHD260082</t>
-  </si>
-  <si>
     <t>ABIDJAN-COCODY//VOIE INCONNUE/M.ME SARA LOBOGNON</t>
   </si>
   <si>
-    <t>SOGENA COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>ABIDJAN-MARCORY//VOIE INCONNUE/ZONE 4</t>
-  </si>
-  <si>
-    <t>BUVPN260059</t>
-  </si>
-  <si>
-    <t>ROYAL INVESTISSEMENT INTERNATIONAL</t>
-  </si>
-  <si>
-    <t>SYTHD260083</t>
-  </si>
-  <si>
     <t>INSTITUT CARDIOLOGIE BOUAKE</t>
   </si>
   <si>
@@ -920,9 +860,6 @@
     <t>1.000.000</t>
   </si>
   <si>
-    <t>SIE: Pilote</t>
-  </si>
-  <si>
     <t>TREICHVILLE ZONE 4</t>
   </si>
   <si>
@@ -951,6 +888,84 @@
   </si>
   <si>
     <t>TREICHVILLE BATIMENT RIMCO</t>
+  </si>
+  <si>
+    <t>Transmission Plans Equipe Numerisation</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU//VOIE INCONNUE/EXT A : POP DJOLIBA REPUBLIQUE</t>
+  </si>
+  <si>
+    <t>SYTHD260072</t>
+  </si>
+  <si>
+    <t>KORHOGO//VOIE INCONNUE/BASE AERIENN KORHOGO</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie BSCS</t>
+  </si>
+  <si>
+    <t>Responsable Zone: Validation intervention</t>
+  </si>
+  <si>
+    <t>DJIGUI SHIPPING SITE TREICHVILLE CHU</t>
+  </si>
+  <si>
+    <t>BUVPN260057</t>
+  </si>
+  <si>
+    <t>BUVPN260061</t>
+  </si>
+  <si>
+    <t>BUVPN260066</t>
+  </si>
+  <si>
+    <t>xxxxxx</t>
+  </si>
+  <si>
+    <t>xxxxxxxxxxxxxxx</t>
+  </si>
+  <si>
+    <t>Etude Suspendu</t>
+  </si>
+  <si>
+    <t>BBF : Validation Etude</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>SYTHD260085</t>
+  </si>
+  <si>
+    <t>SYTHD260080</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>ECART SERVICES IVOIRY COAST</t>
+  </si>
+  <si>
+    <t>BAD</t>
+  </si>
+  <si>
+    <t>PORT BOUET RADUISON BLU</t>
+  </si>
+  <si>
+    <t>IP Delivery: Validation information</t>
+  </si>
+  <si>
+    <t>SOCIETE DE MECANIQUE GENERALE</t>
+  </si>
+  <si>
+    <t>MARCORY BOULEVARD PHILIPPE YACE BATIMENT 7504 AU RDC</t>
+  </si>
+  <si>
+    <t>PRESIDENCE DE LA REPUBLIQUE</t>
+  </si>
+  <si>
+    <t>PLATEAU IMMEUBLE DJEKANOU</t>
   </si>
 </sst>
 </file>
@@ -1334,8 +1349,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6112C32D-301C-49EC-A409-207BDCA453AB}">
-  <dimension ref="A1:Q146"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F241F63F-8CA3-4680-8FA3-BC3B4E36762D}">
+  <dimension ref="A1:Q147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
@@ -1379,7 +1394,7 @@
         <v>61</v>
       </c>
       <c r="N1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O1" t="s">
         <v>62</v>
@@ -1393,28 +1408,28 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>60472385</v>
+        <v>44970444</v>
       </c>
       <c r="B2" s="2">
-        <v>46106.535451388889</v>
+        <v>45798.444131944445</v>
       </c>
       <c r="C2">
-        <v>60472432</v>
+        <v>57086157</v>
       </c>
       <c r="D2" s="2">
-        <v>46106.53565972222</v>
+        <v>46044.497789351852</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>302</v>
+        <v>93</v>
       </c>
       <c r="G2">
-        <v>504001081</v>
+        <v>777545168</v>
       </c>
       <c r="H2" t="s">
-        <v>303</v>
+        <v>94</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
@@ -1431,96 +1446,93 @@
       <c r="M2" t="s">
         <v>3</v>
       </c>
-      <c r="N2" t="s">
-        <v>198</v>
-      </c>
       <c r="O2" t="s">
         <v>0</v>
       </c>
       <c r="P2" t="s">
         <v>0</v>
       </c>
-      <c r="Q2" t="s">
-        <v>0</v>
+      <c r="Q2">
+        <v>2723489300</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>60463210</v>
+        <v>48847621</v>
       </c>
       <c r="B3" s="2">
-        <v>46106.455092592594</v>
+        <v>45882.483449074076</v>
       </c>
       <c r="C3">
-        <v>60463244</v>
+        <v>60094807</v>
       </c>
       <c r="D3" s="2">
-        <v>46106.455324074072</v>
+        <v>46099.377268518518</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="G3">
-        <v>708086472</v>
+        <v>749194205</v>
       </c>
       <c r="H3" t="s">
-        <v>92</v>
+        <v>238</v>
       </c>
       <c r="I3" t="s">
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s">
-        <v>5</v>
+        <v>239</v>
       </c>
       <c r="L3" t="s">
         <v>8</v>
       </c>
       <c r="M3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O3" t="s">
         <v>0</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="s">
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>60461778</v>
+        <v>51760632</v>
       </c>
       <c r="B4" s="2">
-        <v>46106.443009259259</v>
+        <v>45938.521469907406</v>
       </c>
       <c r="C4">
-        <v>60461820</v>
+        <v>59332667</v>
       </c>
       <c r="D4" s="2">
-        <v>46106.443240740744</v>
+        <v>46085.453263888892</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="F4" t="s">
-        <v>170</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>708086472</v>
+        <v>556999292</v>
       </c>
       <c r="H4" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
@@ -1529,51 +1541,51 @@
         <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L4" t="s">
         <v>8</v>
       </c>
       <c r="M4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O4" t="s">
         <v>0</v>
       </c>
-      <c r="P4" s="1">
-        <v>780000</v>
+      <c r="P4" t="s">
+        <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>60461761</v>
+        <v>52448985</v>
       </c>
       <c r="B5" s="2">
-        <v>46106.442974537036</v>
+        <v>45952.656354166669</v>
       </c>
       <c r="C5">
-        <v>60461814</v>
+        <v>60421537</v>
       </c>
       <c r="D5" s="2">
-        <v>46106.443206018521</v>
+        <v>46105.662175925929</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="G5">
-        <v>708086472</v>
+        <v>708086759</v>
       </c>
       <c r="H5" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="I5" t="s">
         <v>0</v>
@@ -1591,7 +1603,7 @@
         <v>7</v>
       </c>
       <c r="N5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O5" t="s">
         <v>0</v>
@@ -1600,145 +1612,145 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>60458148</v>
+        <v>52561777</v>
       </c>
       <c r="B6" s="2">
-        <v>46106.41574074074</v>
+        <v>45954.649918981479</v>
       </c>
       <c r="C6">
-        <v>60458184</v>
+        <v>60344171</v>
       </c>
       <c r="D6" s="2">
-        <v>46106.415960648148</v>
+        <v>46104.526550925926</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="G6">
-        <v>708086472</v>
+        <v>708086759</v>
       </c>
       <c r="H6" t="s">
-        <v>239</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K6" t="s">
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O6" t="s">
         <v>0</v>
       </c>
-      <c r="P6" s="1">
-        <v>580000</v>
+      <c r="P6" t="s">
+        <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>60458135</v>
+        <v>52691553</v>
       </c>
       <c r="B7" s="2">
-        <v>46106.415694444448</v>
+        <v>45958.456122685187</v>
       </c>
       <c r="C7">
-        <v>60458178</v>
+        <v>59242377</v>
       </c>
       <c r="D7" s="2">
-        <v>46106.415902777779</v>
+        <v>46083.722071759257</v>
       </c>
       <c r="E7" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="G7">
-        <v>708086472</v>
+        <v>708473548</v>
       </c>
       <c r="H7" t="s">
-        <v>239</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M7" t="s">
         <v>7</v>
       </c>
       <c r="N7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O7" t="s">
         <v>0</v>
       </c>
-      <c r="P7" t="s">
-        <v>0</v>
+      <c r="P7" s="1">
+        <v>1000000</v>
       </c>
       <c r="Q7" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>60423011</v>
+        <v>52778382</v>
       </c>
       <c r="B8" s="2">
-        <v>46105.672754629632</v>
+        <v>45959.67696759259</v>
       </c>
       <c r="C8">
-        <v>60423045</v>
+        <v>55073470</v>
       </c>
       <c r="D8" s="2">
-        <v>46105.672974537039</v>
+        <v>46003.678194444445</v>
       </c>
       <c r="E8" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>300</v>
+        <v>45</v>
       </c>
       <c r="G8">
-        <v>787670708</v>
+        <v>708086759</v>
       </c>
       <c r="H8" t="s">
-        <v>301</v>
-      </c>
-      <c r="I8" t="s">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="I8">
+        <v>2788625</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K8" t="s">
         <v>5</v>
@@ -1747,204 +1759,204 @@
         <v>8</v>
       </c>
       <c r="M8" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O8" t="s">
         <v>0</v>
       </c>
-      <c r="P8" s="1">
-        <v>293000</v>
+      <c r="P8" t="s">
+        <v>0</v>
       </c>
       <c r="Q8" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>60422373</v>
+        <v>52808171</v>
       </c>
       <c r="B9" s="2">
-        <v>46105.667442129627</v>
+        <v>45960.452361111114</v>
       </c>
       <c r="C9">
-        <v>60422419</v>
+        <v>59829408</v>
       </c>
       <c r="D9" s="2">
-        <v>46105.667766203704</v>
+        <v>46093.677152777775</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="G9">
-        <v>787670708</v>
+        <v>709738605</v>
       </c>
       <c r="H9" t="s">
-        <v>301</v>
-      </c>
-      <c r="I9" t="s">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="I9">
+        <v>2793645</v>
       </c>
       <c r="J9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M9" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="N9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O9" t="s">
         <v>0</v>
       </c>
-      <c r="P9" s="1">
-        <v>5324000</v>
+      <c r="P9" t="s">
+        <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>60416636</v>
+        <v>53702282</v>
       </c>
       <c r="B10" s="2">
-        <v>46105.623402777775</v>
+        <v>45978.671550925923</v>
       </c>
       <c r="C10">
-        <v>60416673</v>
+        <v>54614316</v>
       </c>
       <c r="D10" s="2">
-        <v>46105.62363425926</v>
+        <v>45995.632673611108</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>299</v>
+        <v>44</v>
       </c>
       <c r="G10">
-        <v>172818143</v>
+        <v>778036533</v>
       </c>
       <c r="H10" t="s">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M10" t="s">
         <v>3</v>
       </c>
       <c r="N10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O10" t="s">
         <v>0</v>
       </c>
-      <c r="P10" s="1">
-        <v>500000</v>
+      <c r="P10" t="s">
+        <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>60410207</v>
+        <v>53749839</v>
       </c>
       <c r="B11" s="2">
-        <v>46105.573414351849</v>
+        <v>45979.600694444445</v>
       </c>
       <c r="C11">
-        <v>60410238</v>
+        <v>57266013</v>
       </c>
       <c r="D11" s="2">
-        <v>46105.573645833334</v>
+        <v>46048.492129629631</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>298</v>
+        <v>80</v>
       </c>
       <c r="G11">
-        <v>709254356</v>
+        <v>703333988</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M11" t="s">
         <v>3</v>
       </c>
       <c r="N11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O11" t="s">
         <v>0</v>
       </c>
       <c r="P11" s="1">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
       <c r="Q11" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>60399905</v>
+        <v>53790357</v>
       </c>
       <c r="B12" s="2">
-        <v>46105.484120370369</v>
+        <v>45980.438298611109</v>
       </c>
       <c r="C12">
-        <v>60454828</v>
+        <v>60457171</v>
       </c>
       <c r="D12" s="2">
-        <v>46106.376134259262</v>
+        <v>46106.402766203704</v>
       </c>
       <c r="E12" t="s">
-        <v>293</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="G12">
-        <v>504001081</v>
+        <v>708336404</v>
       </c>
       <c r="H12" t="s">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="I12" t="s">
         <v>0</v>
@@ -1953,7 +1965,7 @@
         <v>13</v>
       </c>
       <c r="K12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L12" t="s">
         <v>6</v>
@@ -1962,219 +1974,219 @@
         <v>3</v>
       </c>
       <c r="N12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O12" t="s">
         <v>0</v>
       </c>
       <c r="P12" s="1">
-        <v>1000000</v>
+        <v>4430307</v>
       </c>
       <c r="Q12" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>60395491</v>
+        <v>53899369</v>
       </c>
       <c r="B13" s="2">
-        <v>46105.449062500003</v>
+        <v>45981.827430555553</v>
       </c>
       <c r="C13">
-        <v>60428541</v>
+        <v>55146678</v>
       </c>
       <c r="D13" s="2">
-        <v>46105.707268518519</v>
+        <v>46005.762916666667</v>
       </c>
       <c r="E13" t="s">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>295</v>
+        <v>32</v>
       </c>
       <c r="G13">
-        <v>767747841</v>
+        <v>707003126</v>
       </c>
       <c r="H13" t="s">
-        <v>194</v>
-      </c>
-      <c r="I13">
+        <v>83</v>
+      </c>
+      <c r="I13" t="s">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K13" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M13" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N13" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O13" t="s">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13" t="s">
-        <v>176</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>60358121</v>
+        <v>54178346</v>
       </c>
       <c r="B14" s="2">
-        <v>46104.633344907408</v>
+        <v>45987.646099537036</v>
       </c>
       <c r="C14">
-        <v>60454891</v>
+        <v>59755436</v>
       </c>
       <c r="D14" s="2">
-        <v>46106.376828703702</v>
+        <v>46092.631111111114</v>
       </c>
       <c r="E14" t="s">
-        <v>293</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>290</v>
+        <v>71</v>
       </c>
       <c r="G14">
-        <v>504001081</v>
+        <v>757323203</v>
       </c>
       <c r="H14" t="s">
-        <v>294</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M14" t="s">
         <v>3</v>
       </c>
       <c r="N14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O14" t="s">
         <v>0</v>
       </c>
-      <c r="P14" s="1">
-        <v>500000</v>
+      <c r="P14" t="s">
+        <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>60356605</v>
+        <v>54449048</v>
       </c>
       <c r="B15" s="2">
-        <v>46104.623726851853</v>
+        <v>45992.706157407411</v>
       </c>
       <c r="C15">
-        <v>60454988</v>
+        <v>56341749</v>
       </c>
       <c r="D15" s="2">
-        <v>46106.377615740741</v>
+        <v>46029.685115740744</v>
       </c>
       <c r="E15" t="s">
-        <v>293</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>290</v>
+        <v>42</v>
       </c>
       <c r="G15">
-        <v>504001081</v>
+        <v>708086759</v>
       </c>
       <c r="H15" t="s">
-        <v>291</v>
+        <v>87</v>
       </c>
       <c r="I15" t="s">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M15" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N15" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>60190035</v>
+        <v>54793554</v>
       </c>
       <c r="B16" s="2">
-        <v>46100.619201388887</v>
+        <v>45999.637916666667</v>
       </c>
       <c r="C16">
-        <v>60387805</v>
+        <v>59895786</v>
       </c>
       <c r="D16" s="2">
-        <v>46105.371874999997</v>
+        <v>46094.6953125</v>
       </c>
       <c r="E16" t="s">
-        <v>191</v>
+        <v>261</v>
       </c>
       <c r="F16" t="s">
-        <v>289</v>
+        <v>71</v>
       </c>
       <c r="G16">
-        <v>708142290</v>
+        <v>757323203</v>
       </c>
       <c r="H16" t="s">
-        <v>67</v>
+        <v>260</v>
       </c>
       <c r="I16" t="s">
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="K16" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M16" t="s">
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O16" t="s">
         <v>0</v>
@@ -2183,304 +2195,304 @@
         <v>0</v>
       </c>
       <c r="Q16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>60162087</v>
+        <v>54967903</v>
       </c>
       <c r="B17" s="2">
-        <v>46100.408645833333</v>
+        <v>46002.459837962961</v>
       </c>
       <c r="C17">
-        <v>60465399</v>
+        <v>59197300</v>
       </c>
       <c r="D17" s="2">
-        <v>46106.474826388891</v>
+        <v>46083.390844907408</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>287</v>
+        <v>97</v>
       </c>
       <c r="G17">
-        <v>757271671</v>
+        <v>504033918</v>
       </c>
       <c r="H17" t="s">
+        <v>129</v>
+      </c>
+      <c r="I17">
+        <v>1814616</v>
+      </c>
+      <c r="J17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" t="s">
+        <v>84</v>
+      </c>
+      <c r="N17" t="s">
+        <v>196</v>
+      </c>
+      <c r="O17" t="s">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="Q17" t="s">
         <v>130</v>
-      </c>
-      <c r="I17" t="s">
-        <v>0</v>
-      </c>
-      <c r="J17" t="s">
-        <v>13</v>
-      </c>
-      <c r="K17" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" t="s">
-        <v>6</v>
-      </c>
-      <c r="M17" t="s">
-        <v>38</v>
-      </c>
-      <c r="N17" t="s">
-        <v>199</v>
-      </c>
-      <c r="O17" t="s">
-        <v>0</v>
-      </c>
-      <c r="P17" s="1">
-        <v>400000</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>60154802</v>
+        <v>54970719</v>
       </c>
       <c r="B18" s="2">
-        <v>46100.305405092593</v>
+        <v>46002.47859953704</v>
       </c>
       <c r="C18">
-        <v>60420668</v>
+        <v>56201571</v>
       </c>
       <c r="D18" s="2">
-        <v>46105.653217592589</v>
+        <v>46027.649004629631</v>
       </c>
       <c r="E18" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="G18">
-        <v>707225975</v>
+        <v>504033918</v>
       </c>
       <c r="H18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" t="s">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="I18">
+        <v>2843545</v>
       </c>
       <c r="J18" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K18" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="L18" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M18" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="N18" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O18" t="s">
         <v>0</v>
       </c>
-      <c r="P18" t="s">
-        <v>0</v>
+      <c r="P18" s="1">
+        <v>1000000</v>
       </c>
       <c r="Q18" t="s">
-        <v>169</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>60084243</v>
+        <v>54973689</v>
       </c>
       <c r="B19" s="2">
-        <v>46098.817627314813</v>
+        <v>46002.496215277781</v>
       </c>
       <c r="C19">
-        <v>60465270</v>
+        <v>60458793</v>
       </c>
       <c r="D19" s="2">
-        <v>46106.473298611112</v>
+        <v>46106.421805555554</v>
       </c>
       <c r="E19" t="s">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>272</v>
+        <v>90</v>
       </c>
       <c r="G19">
-        <v>707708502</v>
+        <v>789916125</v>
       </c>
       <c r="H19" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19">
+        <v>91</v>
+      </c>
+      <c r="I19" t="s">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K19" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="L19" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M19" t="s">
         <v>3</v>
       </c>
       <c r="N19" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O19" t="s">
         <v>0</v>
       </c>
-      <c r="P19" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>2722487090</v>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>60026486</v>
+        <v>55104019</v>
       </c>
       <c r="B20" s="2">
-        <v>46098.36173611111</v>
+        <v>46004.469606481478</v>
       </c>
       <c r="C20">
-        <v>60121930</v>
+        <v>56566265</v>
       </c>
       <c r="D20" s="2">
-        <v>46099.594039351854</v>
+        <v>46034.582673611112</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>251</v>
+        <v>89</v>
       </c>
       <c r="G20">
-        <v>506727287</v>
+        <v>504033918</v>
       </c>
       <c r="H20" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="I20" t="s">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>226</v>
+        <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M20" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N20" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O20" t="s">
         <v>0</v>
       </c>
-      <c r="P20">
-        <v>0</v>
+      <c r="P20" s="1">
+        <v>4000000</v>
       </c>
       <c r="Q20" t="s">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>60025705</v>
+        <v>55105103</v>
       </c>
       <c r="B21" s="2">
-        <v>46098.34920138889</v>
+        <v>46004.481180555558</v>
       </c>
       <c r="C21">
-        <v>60165414</v>
+        <v>56940307</v>
       </c>
       <c r="D21" s="2">
-        <v>46100.437986111108</v>
+        <v>46041.803784722222</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>284</v>
+        <v>89</v>
       </c>
       <c r="G21">
-        <v>704080021</v>
+        <v>504033918</v>
       </c>
       <c r="H21" t="s">
-        <v>285</v>
-      </c>
-      <c r="I21">
-        <v>1849206</v>
+        <v>101</v>
+      </c>
+      <c r="I21" t="s">
+        <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K21" t="s">
-        <v>269</v>
+        <v>5</v>
       </c>
       <c r="L21" t="s">
         <v>8</v>
       </c>
       <c r="M21" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O21" t="s">
         <v>0</v>
       </c>
-      <c r="P21">
-        <v>0</v>
+      <c r="P21" s="1">
+        <v>1500000</v>
       </c>
       <c r="Q21" t="s">
-        <v>286</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>59894758</v>
+        <v>55636282</v>
       </c>
       <c r="B22" s="2">
-        <v>46094.687719907408</v>
+        <v>46014.435729166667</v>
       </c>
       <c r="C22">
-        <v>60454354</v>
+        <v>57367586</v>
       </c>
       <c r="D22" s="2">
-        <v>46106.369768518518</v>
+        <v>46049.856261574074</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="F22" t="s">
-        <v>268</v>
+        <v>104</v>
       </c>
       <c r="G22">
-        <v>759668146</v>
+        <v>759003900</v>
       </c>
       <c r="H22" t="s">
-        <v>283</v>
-      </c>
-      <c r="I22">
-        <v>1849216</v>
+        <v>33</v>
+      </c>
+      <c r="I22" t="s">
+        <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
@@ -2489,45 +2501,45 @@
         <v>6</v>
       </c>
       <c r="M22" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N22" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O22" t="s">
         <v>0</v>
       </c>
       <c r="P22" s="1">
-        <v>1000000</v>
+        <v>918681</v>
       </c>
       <c r="Q22" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>59894743</v>
+        <v>55686160</v>
       </c>
       <c r="B23" s="2">
-        <v>46094.687673611108</v>
+        <v>46015.355868055558</v>
       </c>
       <c r="C23">
-        <v>60454133</v>
+        <v>60490199</v>
       </c>
       <c r="D23" s="2">
-        <v>46106.366770833331</v>
+        <v>46106.680219907408</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>268</v>
+        <v>105</v>
       </c>
       <c r="G23">
-        <v>759668146</v>
+        <v>777765287</v>
       </c>
       <c r="H23" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I23" t="s">
         <v>0</v>
@@ -2542,51 +2554,51 @@
         <v>6</v>
       </c>
       <c r="M23" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N23" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O23" t="s">
         <v>0</v>
       </c>
-      <c r="P23" t="s">
-        <v>0</v>
+      <c r="P23" s="1">
+        <v>850887</v>
       </c>
       <c r="Q23" t="s">
-        <v>35</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>59889656</v>
+        <v>55694485</v>
       </c>
       <c r="B24" s="2">
-        <v>46094.657060185185</v>
+        <v>46015.420092592591</v>
       </c>
       <c r="C24">
-        <v>60349423</v>
+        <v>56752240</v>
       </c>
       <c r="D24" s="2">
-        <v>46104.569618055553</v>
+        <v>46037.705520833333</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>265</v>
+        <v>106</v>
       </c>
       <c r="G24">
-        <v>709813123</v>
+        <v>749338073</v>
       </c>
       <c r="H24" t="s">
-        <v>266</v>
+        <v>107</v>
       </c>
       <c r="I24" t="s">
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>267</v>
+        <v>13</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
@@ -2598,525 +2610,525 @@
         <v>3</v>
       </c>
       <c r="N24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O24" t="s">
         <v>0</v>
       </c>
       <c r="P24" s="1">
-        <v>600000</v>
+        <v>638462</v>
       </c>
       <c r="Q24" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>59888143</v>
+        <v>56181778</v>
       </c>
       <c r="B25" s="2">
-        <v>46094.646597222221</v>
+        <v>46027.499212962961</v>
       </c>
       <c r="C25">
-        <v>60470514</v>
+        <v>59210339</v>
       </c>
       <c r="D25" s="2">
-        <v>46106.519421296296</v>
+        <v>46083.492881944447</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="F25" t="s">
-        <v>263</v>
+        <v>109</v>
       </c>
       <c r="G25">
-        <v>708858866</v>
+        <v>585990976</v>
       </c>
       <c r="H25" t="s">
-        <v>264</v>
-      </c>
-      <c r="I25" t="s">
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="I25">
+        <v>1765416</v>
       </c>
       <c r="J25" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K25" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="L25" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M25" t="s">
         <v>3</v>
       </c>
       <c r="N25" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O25" t="s">
         <v>0</v>
       </c>
-      <c r="P25" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>2720219745</v>
+      <c r="P25" s="1">
+        <v>3000000</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>59834036</v>
+        <v>56601982</v>
       </c>
       <c r="B26" s="2">
-        <v>46093.713761574072</v>
+        <v>46035.393611111111</v>
       </c>
       <c r="C26">
-        <v>60389783</v>
+        <v>60341610</v>
       </c>
       <c r="D26" s="2">
-        <v>46105.397777777776</v>
+        <v>46104.501319444447</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>262</v>
+        <v>32</v>
       </c>
       <c r="G26">
-        <v>787309090</v>
+        <v>707003126</v>
       </c>
       <c r="H26" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="I26" t="s">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K26" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L26" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M26" t="s">
         <v>3</v>
       </c>
       <c r="N26" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O26" t="s">
         <v>0</v>
       </c>
-      <c r="P26" t="s">
-        <v>0</v>
+      <c r="P26" s="1">
+        <v>7103410</v>
       </c>
       <c r="Q26" t="s">
-        <v>176</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>59824550</v>
+        <v>56603495</v>
       </c>
       <c r="B27" s="2">
-        <v>46093.6405787037</v>
+        <v>46035.408518518518</v>
       </c>
       <c r="C27">
-        <v>59859139</v>
+        <v>59831107</v>
       </c>
       <c r="D27" s="2">
-        <v>46094.429143518515</v>
+        <v>46093.691342592596</v>
       </c>
       <c r="E27" t="s">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>260</v>
+        <v>32</v>
       </c>
       <c r="G27">
-        <v>506727287</v>
+        <v>707003126</v>
       </c>
       <c r="H27" t="s">
-        <v>261</v>
+        <v>115</v>
       </c>
       <c r="I27" t="s">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
       </c>
       <c r="L27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M27" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N27" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O27" t="s">
         <v>0</v>
       </c>
-      <c r="P27">
-        <v>0</v>
+      <c r="P27" s="1">
+        <v>7103410</v>
       </c>
       <c r="Q27" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>59821965</v>
+        <v>56606469</v>
       </c>
       <c r="B28" s="2">
-        <v>46093.621331018519</v>
+        <v>46035.43072916667</v>
       </c>
       <c r="C28">
-        <v>60472420</v>
+        <v>60527398</v>
       </c>
       <c r="D28" s="2">
-        <v>46106.535543981481</v>
+        <v>46107.458136574074</v>
       </c>
       <c r="E28" t="s">
-        <v>29</v>
+        <v>283</v>
       </c>
       <c r="F28" t="s">
-        <v>259</v>
+        <v>114</v>
       </c>
       <c r="G28">
-        <v>101383885</v>
+        <v>504041812</v>
       </c>
       <c r="H28" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="I28" t="s">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
       </c>
       <c r="L28" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M28" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="N28" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O28" t="s">
         <v>0</v>
       </c>
       <c r="P28" s="1">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q28" t="s">
-        <v>282</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>59820678</v>
+        <v>56607988</v>
       </c>
       <c r="B29" s="2">
-        <v>46093.612222222226</v>
+        <v>46035.443668981483</v>
       </c>
       <c r="C29">
-        <v>60208764</v>
+        <v>58404447</v>
       </c>
       <c r="D29" s="2">
-        <v>46100.766909722224</v>
+        <v>46069.522615740738</v>
       </c>
       <c r="E29" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="F29" t="s">
-        <v>257</v>
+        <v>114</v>
       </c>
       <c r="G29">
-        <v>506727287</v>
+        <v>504041812</v>
       </c>
       <c r="H29" t="s">
-        <v>258</v>
+        <v>116</v>
       </c>
       <c r="I29" t="s">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K29" t="s">
-        <v>226</v>
+        <v>5</v>
       </c>
       <c r="L29" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M29" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N29" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O29" t="s">
         <v>0</v>
       </c>
-      <c r="P29">
-        <v>0</v>
+      <c r="P29" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q29" t="s">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>59816396</v>
+        <v>56609018</v>
       </c>
       <c r="B30" s="2">
-        <v>46093.580590277779</v>
+        <v>46035.452465277776</v>
       </c>
       <c r="C30">
-        <v>60137506</v>
+        <v>60165633</v>
       </c>
       <c r="D30" s="2">
-        <v>46099.711053240739</v>
+        <v>46100.43891203704</v>
       </c>
       <c r="E30" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>256</v>
+        <v>114</v>
       </c>
       <c r="G30">
-        <v>506727287</v>
+        <v>504041812</v>
       </c>
       <c r="H30" t="s">
-        <v>281</v>
-      </c>
-      <c r="I30">
-        <v>1848446</v>
+        <v>117</v>
+      </c>
+      <c r="I30" t="s">
+        <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K30" t="s">
-        <v>226</v>
+        <v>5</v>
       </c>
       <c r="L30" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M30" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N30" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O30" t="s">
         <v>0</v>
       </c>
-      <c r="P30">
-        <v>0</v>
+      <c r="P30" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q30" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>59813505</v>
+        <v>56611212</v>
       </c>
       <c r="B31" s="2">
-        <v>46093.557256944441</v>
+        <v>46035.471886574072</v>
       </c>
       <c r="C31">
-        <v>60137642</v>
+        <v>57137676</v>
       </c>
       <c r="D31" s="2">
-        <v>46099.71303240741</v>
+        <v>46045.45140046296</v>
       </c>
       <c r="E31" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="F31" t="s">
-        <v>254</v>
+        <v>118</v>
       </c>
       <c r="G31">
-        <v>706727287</v>
+        <v>504041812</v>
       </c>
       <c r="H31" t="s">
-        <v>255</v>
+        <v>119</v>
       </c>
       <c r="I31" t="s">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K31" t="s">
-        <v>226</v>
+        <v>5</v>
       </c>
       <c r="L31" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M31" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O31" t="s">
         <v>0</v>
       </c>
-      <c r="P31">
-        <v>0</v>
+      <c r="P31" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q31" t="s">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>59801109</v>
+        <v>56612479</v>
       </c>
       <c r="B32" s="2">
-        <v>46093.464594907404</v>
+        <v>46035.481446759259</v>
       </c>
       <c r="C32">
-        <v>60426371</v>
+        <v>60101226</v>
       </c>
       <c r="D32" s="2">
-        <v>46105.695104166669</v>
+        <v>46099.43613425926</v>
       </c>
       <c r="E32" t="s">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="F32" t="s">
-        <v>252</v>
+        <v>118</v>
       </c>
       <c r="G32">
-        <v>709173657</v>
+        <v>504041812</v>
       </c>
       <c r="H32" t="s">
-        <v>253</v>
+        <v>121</v>
       </c>
       <c r="I32" t="s">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
       </c>
       <c r="L32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M32" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N32" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O32" t="s">
         <v>0</v>
       </c>
-      <c r="P32">
-        <v>0</v>
+      <c r="P32" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q32" t="s">
-        <v>73</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>59793967</v>
+        <v>56613961</v>
       </c>
       <c r="B33" s="2">
-        <v>46093.406724537039</v>
+        <v>46035.492175925923</v>
       </c>
       <c r="C33">
-        <v>60225840</v>
+        <v>59754685</v>
       </c>
       <c r="D33" s="2">
-        <v>46101.328912037039</v>
+        <v>46092.626307870371</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="F33" t="s">
-        <v>251</v>
+        <v>118</v>
       </c>
       <c r="G33">
-        <v>506727287</v>
+        <v>504041812</v>
       </c>
       <c r="H33" t="s">
-        <v>222</v>
+        <v>122</v>
       </c>
       <c r="I33" t="s">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
       </c>
       <c r="L33" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M33" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N33" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O33" t="s">
         <v>0</v>
       </c>
-      <c r="P33">
-        <v>0</v>
+      <c r="P33" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q33" t="s">
-        <v>35</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>59684312</v>
+        <v>56618123</v>
       </c>
       <c r="B34" s="2">
-        <v>46091.557453703703</v>
+        <v>46035.520821759259</v>
       </c>
       <c r="C34">
-        <v>59736324</v>
+        <v>59311833</v>
       </c>
       <c r="D34" s="2">
-        <v>46092.496296296296</v>
+        <v>46084.811782407407</v>
       </c>
       <c r="E34" t="s">
-        <v>238</v>
+        <v>127</v>
       </c>
       <c r="F34" t="s">
-        <v>235</v>
+        <v>124</v>
       </c>
       <c r="G34">
-        <v>3130227350</v>
+        <v>504041812</v>
       </c>
       <c r="H34" t="s">
-        <v>236</v>
-      </c>
-      <c r="I34" t="s">
-        <v>0</v>
+        <v>197</v>
+      </c>
+      <c r="I34">
+        <v>1775236</v>
       </c>
       <c r="J34" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
@@ -3128,42 +3140,42 @@
         <v>3</v>
       </c>
       <c r="N34" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O34" t="s">
         <v>0</v>
       </c>
-      <c r="P34" t="s">
-        <v>0</v>
+      <c r="P34" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q34" t="s">
-        <v>0</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>59615935</v>
+        <v>56675050</v>
       </c>
       <c r="B35" s="2">
-        <v>46090.512303240743</v>
+        <v>46036.516423611109</v>
       </c>
       <c r="C35">
-        <v>60393405</v>
+        <v>58216664</v>
       </c>
       <c r="D35" s="2">
-        <v>46105.432800925926</v>
+        <v>46065.536226851851</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>233</v>
+        <v>131</v>
       </c>
       <c r="G35">
-        <v>767081456</v>
+        <v>748512613</v>
       </c>
       <c r="H35" t="s">
-        <v>234</v>
+        <v>132</v>
       </c>
       <c r="I35" t="s">
         <v>0</v>
@@ -3181,42 +3193,42 @@
         <v>3</v>
       </c>
       <c r="N35" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O35" t="s">
         <v>0</v>
       </c>
-      <c r="P35">
-        <v>0</v>
+      <c r="P35" s="1">
+        <v>4362401</v>
       </c>
       <c r="Q35" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>59606122</v>
+        <v>56970346</v>
       </c>
       <c r="B36" s="2">
-        <v>46090.447604166664</v>
+        <v>46042.557280092595</v>
       </c>
       <c r="C36">
-        <v>59682305</v>
+        <v>59242054</v>
       </c>
       <c r="D36" s="2">
-        <v>46091.541701388887</v>
+        <v>46083.719525462962</v>
       </c>
       <c r="E36" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>231</v>
+        <v>125</v>
       </c>
       <c r="G36">
-        <v>708454305</v>
+        <v>708667658</v>
       </c>
       <c r="H36" t="s">
-        <v>232</v>
+        <v>126</v>
       </c>
       <c r="I36" t="s">
         <v>0</v>
@@ -3225,51 +3237,51 @@
         <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>226</v>
+        <v>5</v>
       </c>
       <c r="L36" t="s">
         <v>6</v>
       </c>
       <c r="M36" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N36" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O36" t="s">
         <v>0</v>
       </c>
-      <c r="P36">
-        <v>0</v>
+      <c r="P36" s="1">
+        <v>2871414</v>
       </c>
       <c r="Q36" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>59541145</v>
+        <v>57398181</v>
       </c>
       <c r="B37" s="2">
-        <v>46088.634837962964</v>
+        <v>46050.584374999999</v>
       </c>
       <c r="C37">
-        <v>59799803</v>
+        <v>60344342</v>
       </c>
       <c r="D37" s="2">
-        <v>46093.453530092593</v>
+        <v>46104.528900462959</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>229</v>
+        <v>133</v>
       </c>
       <c r="G37">
-        <v>546008131</v>
+        <v>720631500</v>
       </c>
       <c r="H37" t="s">
-        <v>230</v>
+        <v>134</v>
       </c>
       <c r="I37" t="s">
         <v>0</v>
@@ -3278,51 +3290,51 @@
         <v>13</v>
       </c>
       <c r="K37" t="s">
-        <v>226</v>
+        <v>5</v>
       </c>
       <c r="L37" t="s">
         <v>6</v>
       </c>
       <c r="M37" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N37" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O37" t="s">
         <v>0</v>
       </c>
-      <c r="P37">
-        <v>0</v>
+      <c r="P37" s="1">
+        <v>4406780</v>
       </c>
       <c r="Q37" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>59538597</v>
+        <v>57651441</v>
       </c>
       <c r="B38" s="2">
-        <v>46088.598194444443</v>
+        <v>46055.58011574074</v>
       </c>
       <c r="C38">
-        <v>60030833</v>
+        <v>58955875</v>
       </c>
       <c r="D38" s="2">
-        <v>46098.40320601852</v>
+        <v>46078.639594907407</v>
       </c>
       <c r="E38" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="F38" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="G38">
-        <v>566473307</v>
+        <v>707079088</v>
       </c>
       <c r="H38" t="s">
-        <v>228</v>
+        <v>136</v>
       </c>
       <c r="I38" t="s">
         <v>0</v>
@@ -3339,40 +3351,43 @@
       <c r="M38" t="s">
         <v>3</v>
       </c>
+      <c r="N38" t="s">
+        <v>196</v>
+      </c>
       <c r="O38" t="s">
         <v>0</v>
       </c>
-      <c r="P38">
-        <v>0</v>
+      <c r="P38" t="s">
+        <v>137</v>
       </c>
       <c r="Q38" t="s">
-        <v>250</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>59538099</v>
+        <v>57672103</v>
       </c>
       <c r="B39" s="2">
-        <v>46088.590717592589</v>
+        <v>46055.712083333332</v>
       </c>
       <c r="C39">
-        <v>60033812</v>
+        <v>58477217</v>
       </c>
       <c r="D39" s="2">
-        <v>46098.426782407405</v>
+        <v>46070.620787037034</v>
       </c>
       <c r="E39" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="F39" t="s">
-        <v>227</v>
+        <v>138</v>
       </c>
       <c r="G39">
-        <v>566473307</v>
+        <v>707079088</v>
       </c>
       <c r="H39" t="s">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="I39" t="s">
         <v>0</v>
@@ -3389,93 +3404,96 @@
       <c r="M39" t="s">
         <v>3</v>
       </c>
+      <c r="N39" t="s">
+        <v>196</v>
+      </c>
       <c r="O39" t="s">
         <v>0</v>
       </c>
-      <c r="P39">
-        <v>0</v>
+      <c r="P39" s="1">
+        <v>1426700</v>
       </c>
       <c r="Q39" t="s">
-        <v>250</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>59537755</v>
+        <v>57692887</v>
       </c>
       <c r="B40" s="2">
-        <v>46088.586631944447</v>
+        <v>46056.394780092596</v>
       </c>
       <c r="C40">
-        <v>59807640</v>
+        <v>60516591</v>
       </c>
       <c r="D40" s="2">
-        <v>46093.511296296296</v>
+        <v>46107.377708333333</v>
       </c>
       <c r="E40" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>225</v>
+        <v>140</v>
       </c>
       <c r="G40">
-        <v>556331131</v>
+        <v>707109668</v>
       </c>
       <c r="H40" t="s">
-        <v>225</v>
-      </c>
-      <c r="I40" t="s">
-        <v>0</v>
+        <v>284</v>
+      </c>
+      <c r="I40">
+        <v>1798816</v>
       </c>
       <c r="J40" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K40" t="s">
-        <v>226</v>
+        <v>5</v>
       </c>
       <c r="L40" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M40" t="s">
         <v>7</v>
       </c>
       <c r="N40" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O40" t="s">
         <v>0</v>
       </c>
-      <c r="P40">
+      <c r="P40" t="s">
         <v>0</v>
       </c>
       <c r="Q40" t="s">
-        <v>0</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>59498233</v>
+        <v>57706849</v>
       </c>
       <c r="B41" s="2">
-        <v>46087.67423611111</v>
+        <v>46056.499166666668</v>
       </c>
       <c r="C41">
-        <v>59693004</v>
+        <v>59767932</v>
       </c>
       <c r="D41" s="2">
-        <v>46091.627928240741</v>
+        <v>46092.721273148149</v>
       </c>
       <c r="E41" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>221</v>
+        <v>142</v>
       </c>
       <c r="G41">
-        <v>606727287</v>
+        <v>708086472</v>
       </c>
       <c r="H41" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="I41" t="s">
         <v>0</v>
@@ -3484,7 +3502,7 @@
         <v>13</v>
       </c>
       <c r="K41" t="s">
-        <v>224</v>
+        <v>5</v>
       </c>
       <c r="L41" t="s">
         <v>6</v>
@@ -3493,7 +3511,7 @@
         <v>7</v>
       </c>
       <c r="N41" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O41" t="s">
         <v>0</v>
@@ -3502,263 +3520,263 @@
         <v>0</v>
       </c>
       <c r="Q41" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>59495495</v>
+        <v>57773018</v>
       </c>
       <c r="B42" s="2">
-        <v>46087.654039351852</v>
+        <v>46057.517175925925</v>
       </c>
       <c r="C42">
-        <v>60103608</v>
+        <v>60593118</v>
       </c>
       <c r="D42" s="2">
-        <v>46099.451018518521</v>
+        <v>46108.403668981482</v>
       </c>
       <c r="E42" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="F42" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="G42">
-        <v>757019000</v>
+        <v>758333146</v>
       </c>
       <c r="H42" t="s">
-        <v>105</v>
-      </c>
-      <c r="I42" t="s">
-        <v>0</v>
+        <v>286</v>
+      </c>
+      <c r="I42">
+        <v>1805046</v>
       </c>
       <c r="J42" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K42" t="s">
-        <v>1</v>
+        <v>187</v>
       </c>
       <c r="L42" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M42" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="N42" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="O42" t="s">
         <v>0</v>
       </c>
-      <c r="P42" t="s">
-        <v>0</v>
+      <c r="P42" s="1">
+        <v>400000</v>
       </c>
       <c r="Q42" t="s">
-        <v>73</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>59495473</v>
+        <v>57849095</v>
       </c>
       <c r="B43" s="2">
-        <v>46087.653935185182</v>
+        <v>46058.603668981479</v>
       </c>
       <c r="C43">
-        <v>59644603</v>
+        <v>60388868</v>
       </c>
       <c r="D43" s="2">
-        <v>46090.722048611111</v>
+        <v>46105.385023148148</v>
       </c>
       <c r="E43" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="F43" t="s">
-        <v>221</v>
+        <v>140</v>
       </c>
       <c r="G43">
-        <v>506727287</v>
+        <v>707109668</v>
       </c>
       <c r="H43" t="s">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="I43" t="s">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
       </c>
       <c r="L43" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M43" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N43" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O43" t="s">
         <v>0</v>
       </c>
-      <c r="P43">
+      <c r="P43" t="s">
         <v>0</v>
       </c>
       <c r="Q43" t="s">
-        <v>0</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>59480507</v>
+        <v>57899728</v>
       </c>
       <c r="B44" s="2">
-        <v>46087.544247685182</v>
+        <v>46059.503668981481</v>
       </c>
       <c r="C44">
-        <v>60031786</v>
+        <v>59053570</v>
       </c>
       <c r="D44" s="2">
-        <v>46098.409074074072</v>
+        <v>46080.432372685187</v>
       </c>
       <c r="E44" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="F44" t="s">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="G44">
-        <v>708547070</v>
+        <v>505980067</v>
       </c>
       <c r="H44" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="I44" t="s">
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K44" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L44" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M44" t="s">
         <v>3</v>
       </c>
       <c r="N44" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O44" t="s">
         <v>0</v>
       </c>
-      <c r="P44" t="s">
-        <v>0</v>
+      <c r="P44" s="1">
+        <v>1002937</v>
       </c>
       <c r="Q44" t="s">
-        <v>35</v>
+        <v>145</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>59469589</v>
+        <v>58055656</v>
       </c>
       <c r="B45" s="2">
-        <v>46087.458460648151</v>
+        <v>46062.760023148148</v>
       </c>
       <c r="C45">
-        <v>59646039</v>
+        <v>60340320</v>
       </c>
       <c r="D45" s="2">
-        <v>46090.733263888891</v>
+        <v>46104.489583333336</v>
       </c>
       <c r="E45" t="s">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="G45">
-        <v>554235979</v>
+        <v>758224257</v>
       </c>
       <c r="H45" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="I45" t="s">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L45" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M45" t="s">
         <v>3</v>
       </c>
       <c r="N45" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O45" t="s">
         <v>0</v>
       </c>
-      <c r="P45" t="s">
-        <v>0</v>
+      <c r="P45" s="1">
+        <v>1800000</v>
       </c>
       <c r="Q45" t="s">
-        <v>169</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>59468518</v>
+        <v>58093827</v>
       </c>
       <c r="B46" s="2">
-        <v>46087.450266203705</v>
+        <v>46063.583402777775</v>
       </c>
       <c r="C46">
-        <v>59646678</v>
+        <v>59486282</v>
       </c>
       <c r="D46" s="2">
-        <v>46090.740671296298</v>
+        <v>46087.591932870368</v>
       </c>
       <c r="E46" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="G46">
-        <v>554235979</v>
+        <v>708086759</v>
       </c>
       <c r="H46" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="I46" t="s">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K46" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L46" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M46" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N46" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O46" t="s">
         <v>0</v>
@@ -3767,157 +3785,157 @@
         <v>0</v>
       </c>
       <c r="Q46" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>59466778</v>
+        <v>58093843</v>
       </c>
       <c r="B47" s="2">
-        <v>46087.438715277778</v>
+        <v>46063.583460648151</v>
       </c>
       <c r="C47">
-        <v>59497069</v>
+        <v>58667700</v>
       </c>
       <c r="D47" s="2">
-        <v>46087.666539351849</v>
+        <v>46073.611655092594</v>
       </c>
       <c r="E47" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="G47">
-        <v>554235979</v>
+        <v>708086759</v>
       </c>
       <c r="H47" t="s">
-        <v>43</v>
-      </c>
-      <c r="I47">
+        <v>148</v>
+      </c>
+      <c r="I47" t="s">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K47" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L47" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M47" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N47" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O47" t="s">
         <v>0</v>
       </c>
-      <c r="P47" t="s">
+      <c r="P47">
         <v>0</v>
       </c>
       <c r="Q47" t="s">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>59466514</v>
+        <v>58096775</v>
       </c>
       <c r="B48" s="2">
-        <v>46087.436643518522</v>
+        <v>46063.603263888886</v>
       </c>
       <c r="C48">
-        <v>60021703</v>
+        <v>58655959</v>
       </c>
       <c r="D48" s="2">
-        <v>46097.883842592593</v>
+        <v>46073.525740740741</v>
       </c>
       <c r="E48" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F48" t="s">
-        <v>219</v>
+        <v>45</v>
       </c>
       <c r="G48">
-        <v>141679210</v>
+        <v>708086759</v>
       </c>
       <c r="H48" t="s">
-        <v>218</v>
+        <v>148</v>
       </c>
       <c r="I48" t="s">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
       </c>
       <c r="L48" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M48" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N48" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O48" t="s">
         <v>0</v>
       </c>
-      <c r="P48" s="1">
-        <v>3213390</v>
+      <c r="P48">
+        <v>0</v>
       </c>
       <c r="Q48" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>59465071</v>
+        <v>58144220</v>
       </c>
       <c r="B49" s="2">
-        <v>46087.424062500002</v>
+        <v>46064.478425925925</v>
       </c>
       <c r="C49">
-        <v>59643075</v>
+        <v>60604436</v>
       </c>
       <c r="D49" s="2">
-        <v>46090.709768518522</v>
+        <v>46108.484652777777</v>
       </c>
       <c r="E49" t="s">
-        <v>191</v>
+        <v>288</v>
       </c>
       <c r="F49" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="G49">
-        <v>554235979</v>
+        <v>2722418166</v>
       </c>
       <c r="H49" t="s">
-        <v>218</v>
+        <v>112</v>
       </c>
       <c r="I49" t="s">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K49" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L49" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M49" t="s">
         <v>7</v>
       </c>
       <c r="N49" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O49" t="s">
         <v>0</v>
@@ -3926,33 +3944,33 @@
         <v>0</v>
       </c>
       <c r="Q49" t="s">
-        <v>0</v>
+        <v>263</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>59464660</v>
+        <v>58151683</v>
       </c>
       <c r="B50" s="2">
-        <v>46087.421030092592</v>
+        <v>46064.532222222224</v>
       </c>
       <c r="C50">
-        <v>59688131</v>
+        <v>60402173</v>
       </c>
       <c r="D50" s="2">
-        <v>46091.589421296296</v>
+        <v>46105.501574074071</v>
       </c>
       <c r="E50" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="F50" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="G50">
-        <v>554235979</v>
+        <v>2721271444</v>
       </c>
       <c r="H50" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="I50" t="s">
         <v>0</v>
@@ -3967,275 +3985,275 @@
         <v>6</v>
       </c>
       <c r="M50" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N50" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O50" t="s">
         <v>0</v>
       </c>
-      <c r="P50">
-        <v>0</v>
+      <c r="P50" s="1">
+        <v>1495965</v>
       </c>
       <c r="Q50" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>59417066</v>
+        <v>58166885</v>
       </c>
       <c r="B51" s="2">
-        <v>46086.594525462962</v>
+        <v>46064.649965277778</v>
       </c>
       <c r="C51">
-        <v>59431339</v>
+        <v>59811530</v>
       </c>
       <c r="D51" s="2">
-        <v>46086.692337962966</v>
+        <v>46093.540775462963</v>
       </c>
       <c r="E51" t="s">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="G51">
-        <v>709565662</v>
+        <v>504041812</v>
       </c>
       <c r="H51" t="s">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="I51" t="s">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K51" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L51" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M51" t="s">
         <v>3</v>
       </c>
       <c r="N51" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O51" t="s">
         <v>0</v>
       </c>
-      <c r="P51">
-        <v>0</v>
+      <c r="P51" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q51" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>59414411</v>
+        <v>58168004</v>
       </c>
       <c r="B52" s="2">
-        <v>46086.57104166667</v>
+        <v>46064.657037037039</v>
       </c>
       <c r="C52">
-        <v>59430460</v>
+        <v>60360622</v>
       </c>
       <c r="D52" s="2">
-        <v>46086.686412037037</v>
+        <v>46104.652754629627</v>
       </c>
       <c r="E52" t="s">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="F52" t="s">
-        <v>214</v>
+        <v>114</v>
       </c>
       <c r="G52">
-        <v>566473307</v>
+        <v>504041812</v>
       </c>
       <c r="H52" t="s">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="I52">
-        <v>1841606</v>
+        <v>1811236</v>
       </c>
       <c r="J52" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="K52" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L52" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M52" t="s">
         <v>3</v>
       </c>
       <c r="N52" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O52" t="s">
         <v>0</v>
       </c>
-      <c r="P52">
-        <v>0</v>
+      <c r="P52" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q52" t="s">
-        <v>0</v>
+        <v>265</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>59410843</v>
+        <v>58274609</v>
       </c>
       <c r="B53" s="2">
-        <v>46086.542870370373</v>
+        <v>46066.525011574071</v>
       </c>
       <c r="C53">
-        <v>59429922</v>
+        <v>59264178</v>
       </c>
       <c r="D53" s="2">
-        <v>46086.682488425926</v>
+        <v>46084.406759259262</v>
       </c>
       <c r="E53" t="s">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c r="G53">
-        <v>758700193</v>
+        <v>2722480700</v>
       </c>
       <c r="H53" t="s">
-        <v>213</v>
-      </c>
-      <c r="I53">
+        <v>43</v>
+      </c>
+      <c r="I53" t="s">
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K53" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L53" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M53" t="s">
         <v>3</v>
       </c>
       <c r="N53" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O53" t="s">
         <v>0</v>
       </c>
-      <c r="P53" t="s">
-        <v>0</v>
+      <c r="P53" s="1">
+        <v>522590</v>
       </c>
       <c r="Q53" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>59410212</v>
+        <v>58626822</v>
       </c>
       <c r="B54" s="2">
-        <v>46086.537708333337</v>
+        <v>46072.810324074075</v>
       </c>
       <c r="C54">
-        <v>59835857</v>
+        <v>59811821</v>
       </c>
       <c r="D54" s="2">
-        <v>46093.728726851848</v>
+        <v>46093.543773148151</v>
       </c>
       <c r="E54" t="s">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="G54">
-        <v>789018789</v>
+        <v>709574114</v>
       </c>
       <c r="H54" t="s">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="I54" t="s">
         <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K54" t="s">
-        <v>211</v>
+        <v>5</v>
       </c>
       <c r="L54" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M54" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N54" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O54" t="s">
         <v>0</v>
       </c>
-      <c r="P54" t="s">
-        <v>0</v>
+      <c r="P54" s="1">
+        <v>445307</v>
       </c>
       <c r="Q54" t="s">
-        <v>176</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>59409752</v>
+        <v>58635645</v>
       </c>
       <c r="B55" s="2">
-        <v>46086.534502314818</v>
+        <v>46073.372395833336</v>
       </c>
       <c r="C55">
-        <v>59429000</v>
+        <v>59752855</v>
       </c>
       <c r="D55" s="2">
-        <v>46086.676817129628</v>
+        <v>46092.614201388889</v>
       </c>
       <c r="E55" t="s">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="G55">
-        <v>758700193</v>
+        <v>759250737</v>
       </c>
       <c r="H55" t="s">
-        <v>105</v>
-      </c>
-      <c r="I55">
+        <v>28</v>
+      </c>
+      <c r="I55" t="s">
         <v>0</v>
       </c>
       <c r="J55" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K55" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L55" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M55" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N55" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O55" t="s">
         <v>0</v>
@@ -4244,95 +4262,95 @@
         <v>0</v>
       </c>
       <c r="Q55" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>59409078</v>
+        <v>58635674</v>
       </c>
       <c r="B56" s="2">
-        <v>46086.529247685183</v>
+        <v>46073.372488425928</v>
       </c>
       <c r="C56">
-        <v>59427283</v>
+        <v>60160137</v>
       </c>
       <c r="D56" s="2">
-        <v>46086.665729166663</v>
+        <v>46100.389884259261</v>
       </c>
       <c r="E56" t="s">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="G56">
-        <v>709140938</v>
+        <v>759250737</v>
       </c>
       <c r="H56" t="s">
-        <v>105</v>
-      </c>
-      <c r="I56">
+        <v>28</v>
+      </c>
+      <c r="I56" t="s">
         <v>0</v>
       </c>
       <c r="J56" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K56" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L56" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M56" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N56" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O56" t="s">
         <v>0</v>
       </c>
-      <c r="P56" t="s">
-        <v>0</v>
+      <c r="P56" s="1">
+        <v>500000</v>
       </c>
       <c r="Q56" t="s">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>59406937</v>
+        <v>58642079</v>
       </c>
       <c r="B57" s="2">
-        <v>46086.512870370374</v>
+        <v>46073.425034722219</v>
       </c>
       <c r="C57">
-        <v>59428327</v>
+        <v>59755320</v>
       </c>
       <c r="D57" s="2">
-        <v>46086.673530092594</v>
+        <v>46092.630370370367</v>
       </c>
       <c r="E57" t="s">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="G57">
-        <v>709136702</v>
+        <v>759250737</v>
       </c>
       <c r="H57" t="s">
-        <v>105</v>
-      </c>
-      <c r="I57">
-        <v>1843676</v>
+        <v>28</v>
+      </c>
+      <c r="I57" t="s">
+        <v>0</v>
       </c>
       <c r="J57" t="s">
         <v>85</v>
       </c>
       <c r="K57" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L57" t="s">
         <v>2</v>
@@ -4341,95 +4359,95 @@
         <v>3</v>
       </c>
       <c r="N57" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O57" t="s">
         <v>0</v>
       </c>
-      <c r="P57">
+      <c r="P57" t="s">
         <v>0</v>
       </c>
       <c r="Q57" t="s">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>59406146</v>
+        <v>58649804</v>
       </c>
       <c r="B58" s="2">
-        <v>46086.506643518522</v>
+        <v>46073.479305555556</v>
       </c>
       <c r="C58">
-        <v>59426353</v>
+        <v>59753122</v>
       </c>
       <c r="D58" s="2">
-        <v>46086.658784722225</v>
+        <v>46092.615983796299</v>
       </c>
       <c r="E58" t="s">
-        <v>191</v>
+        <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="G58">
-        <v>709136702</v>
+        <v>759250737</v>
       </c>
       <c r="H58" t="s">
-        <v>105</v>
-      </c>
-      <c r="I58">
-        <v>1843656</v>
+        <v>28</v>
+      </c>
+      <c r="I58" t="s">
+        <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K58" t="s">
         <v>5</v>
       </c>
       <c r="L58" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M58" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N58" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O58" t="s">
         <v>0</v>
       </c>
-      <c r="P58">
+      <c r="P58" t="s">
         <v>0</v>
       </c>
       <c r="Q58" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>59374776</v>
+        <v>58649837</v>
       </c>
       <c r="B59" s="2">
-        <v>46085.757662037038</v>
+        <v>46073.479409722226</v>
       </c>
       <c r="C59">
-        <v>60185369</v>
+        <v>59753844</v>
       </c>
       <c r="D59" s="2">
-        <v>46100.585393518515</v>
+        <v>46092.619826388887</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="G59">
-        <v>747726344</v>
+        <v>759250737</v>
       </c>
       <c r="H59" t="s">
-        <v>205</v>
+        <v>28</v>
       </c>
       <c r="I59" t="s">
         <v>0</v>
@@ -4444,98 +4462,98 @@
         <v>6</v>
       </c>
       <c r="M59" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N59" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O59" t="s">
         <v>0</v>
       </c>
-      <c r="P59" t="s">
-        <v>0</v>
+      <c r="P59" s="1">
+        <v>500000</v>
       </c>
       <c r="Q59" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>59309764</v>
+        <v>58650374</v>
       </c>
       <c r="B60" s="2">
-        <v>46084.777083333334</v>
+        <v>46073.483518518522</v>
       </c>
       <c r="C60">
-        <v>60432246</v>
+        <v>60467780</v>
       </c>
       <c r="D60" s="2">
-        <v>46105.737245370372</v>
+        <v>46106.494745370372</v>
       </c>
       <c r="E60" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="F60" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="G60">
-        <v>708164102</v>
+        <v>708193864</v>
       </c>
       <c r="H60" t="s">
-        <v>203</v>
+        <v>163</v>
       </c>
       <c r="I60" t="s">
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K60" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L60" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M60" t="s">
         <v>3</v>
       </c>
       <c r="N60" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="O60" t="s">
         <v>0</v>
       </c>
-      <c r="P60" s="1">
-        <v>2000000</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>202</v>
+      <c r="P60" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>2722229765</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>59308240</v>
+        <v>58797846</v>
       </c>
       <c r="B61" s="2">
-        <v>46084.755844907406</v>
+        <v>46076.510104166664</v>
       </c>
       <c r="C61">
-        <v>60408206</v>
+        <v>60565096</v>
       </c>
       <c r="D61" s="2">
-        <v>46105.552349537036</v>
+        <v>46107.733611111114</v>
       </c>
       <c r="E61" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F61" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="G61">
-        <v>707865499</v>
+        <v>102224907</v>
       </c>
       <c r="H61" t="s">
-        <v>130</v>
+        <v>289</v>
       </c>
       <c r="I61" t="s">
         <v>0</v>
@@ -4544,7 +4562,7 @@
         <v>18</v>
       </c>
       <c r="K61" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L61" t="s">
         <v>8</v>
@@ -4553,7 +4571,7 @@
         <v>3</v>
       </c>
       <c r="N61" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O61" t="s">
         <v>0</v>
@@ -4562,33 +4580,33 @@
         <v>2000000</v>
       </c>
       <c r="Q61" t="s">
-        <v>176</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>59301554</v>
+        <v>58808846</v>
       </c>
       <c r="B62" s="2">
-        <v>46084.695763888885</v>
+        <v>46076.586747685185</v>
       </c>
       <c r="C62">
-        <v>60404424</v>
+        <v>60488514</v>
       </c>
       <c r="D62" s="2">
-        <v>46105.51835648148</v>
+        <v>46106.663819444446</v>
       </c>
       <c r="E62" t="s">
-        <v>191</v>
+        <v>74</v>
       </c>
       <c r="F62" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G62">
-        <v>777654212</v>
+        <v>749994094</v>
       </c>
       <c r="H62" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="I62" t="s">
         <v>0</v>
@@ -4606,7 +4624,7 @@
         <v>3</v>
       </c>
       <c r="N62" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="O62" t="s">
         <v>0</v>
@@ -4615,33 +4633,33 @@
         <v>2000000</v>
       </c>
       <c r="Q62" t="s">
-        <v>73</v>
+        <v>290</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>59300338</v>
+        <v>58821537</v>
       </c>
       <c r="B63" s="2">
-        <v>46084.687997685185</v>
+        <v>46076.664479166669</v>
       </c>
       <c r="C63">
-        <v>60334904</v>
+        <v>60409857</v>
       </c>
       <c r="D63" s="2">
-        <v>46104.445138888892</v>
+        <v>46105.569016203706</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
+        <v>188</v>
       </c>
       <c r="F63" t="s">
         <v>167</v>
       </c>
       <c r="G63">
-        <v>545254325</v>
+        <v>708086472</v>
       </c>
       <c r="H63" t="s">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="I63" t="s">
         <v>0</v>
@@ -4650,51 +4668,51 @@
         <v>18</v>
       </c>
       <c r="K63" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L63" t="s">
         <v>8</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N63" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O63" t="s">
         <v>0</v>
       </c>
-      <c r="P63" s="1">
-        <v>2000000</v>
+      <c r="P63" t="s">
+        <v>0</v>
       </c>
       <c r="Q63" t="s">
-        <v>280</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>59278925</v>
+        <v>58821553</v>
       </c>
       <c r="B64" s="2">
-        <v>46084.521053240744</v>
+        <v>46076.664525462962</v>
       </c>
       <c r="C64">
-        <v>60397473</v>
+        <v>59998536</v>
       </c>
       <c r="D64" s="2">
-        <v>46105.464074074072</v>
+        <v>46097.435590277775</v>
       </c>
       <c r="E64" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="F64" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="G64">
-        <v>759651079</v>
+        <v>708086472</v>
       </c>
       <c r="H64" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="I64" t="s">
         <v>0</v>
@@ -4709,45 +4727,45 @@
         <v>8</v>
       </c>
       <c r="M64" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N64" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O64" t="s">
         <v>0</v>
       </c>
       <c r="P64" s="1">
-        <v>500000</v>
+        <v>705000</v>
       </c>
       <c r="Q64" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>59278285</v>
+        <v>58822576</v>
       </c>
       <c r="B65" s="2">
-        <v>46084.516597222224</v>
+        <v>46076.670810185184</v>
       </c>
       <c r="C65">
-        <v>60396888</v>
+        <v>59375318</v>
       </c>
       <c r="D65" s="2">
-        <v>46105.459768518522</v>
+        <v>46085.763622685183</v>
       </c>
       <c r="E65" t="s">
         <v>16</v>
       </c>
       <c r="F65" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="G65">
-        <v>759651079</v>
+        <v>708086472</v>
       </c>
       <c r="H65" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="I65" t="s">
         <v>0</v>
@@ -4756,122 +4774,122 @@
         <v>18</v>
       </c>
       <c r="K65" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L65" t="s">
         <v>8</v>
       </c>
       <c r="M65" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N65" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O65" t="s">
         <v>0</v>
       </c>
-      <c r="P65" s="1">
-        <v>500000</v>
+      <c r="P65" t="s">
+        <v>0</v>
       </c>
       <c r="Q65" t="s">
-        <v>247</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>58963646</v>
+        <v>58822595</v>
       </c>
       <c r="B66" s="2">
-        <v>46078.697048611109</v>
+        <v>46076.670856481483</v>
       </c>
       <c r="C66">
-        <v>60185453</v>
+        <v>60208557</v>
       </c>
       <c r="D66" s="2">
-        <v>46100.586238425924</v>
+        <v>46100.764618055553</v>
       </c>
       <c r="E66" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F66" t="s">
-        <v>48</v>
+        <v>167</v>
       </c>
       <c r="G66">
-        <v>747726344</v>
+        <v>708086472</v>
       </c>
       <c r="H66" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="I66" t="s">
         <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K66" t="s">
         <v>5</v>
       </c>
       <c r="L66" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M66" t="s">
         <v>14</v>
       </c>
       <c r="N66" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O66" t="s">
         <v>0</v>
       </c>
-      <c r="P66">
-        <v>0</v>
+      <c r="P66" s="1">
+        <v>1150000</v>
       </c>
       <c r="Q66" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>58963630</v>
+        <v>58856498</v>
       </c>
       <c r="B67" s="2">
-        <v>46078.697002314817</v>
+        <v>46077.418171296296</v>
       </c>
       <c r="C67">
-        <v>60167087</v>
+        <v>60184731</v>
       </c>
       <c r="D67" s="2">
-        <v>46100.449837962966</v>
+        <v>46100.579618055555</v>
       </c>
       <c r="E67" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F67" t="s">
-        <v>48</v>
+        <v>169</v>
       </c>
       <c r="G67">
-        <v>747726344</v>
+        <v>748377555</v>
       </c>
       <c r="H67" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="I67" t="s">
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
       </c>
       <c r="L67" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M67" t="s">
         <v>7</v>
       </c>
       <c r="N67" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="O67" t="s">
         <v>0</v>
@@ -4880,139 +4898,139 @@
         <v>0</v>
       </c>
       <c r="Q67" t="s">
-        <v>27</v>
+        <v>258</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>58959238</v>
+        <v>58860531</v>
       </c>
       <c r="B68" s="2">
-        <v>46078.665532407409</v>
+        <v>46077.446631944447</v>
       </c>
       <c r="C68">
-        <v>60163938</v>
+        <v>60225679</v>
       </c>
       <c r="D68" s="2">
-        <v>46100.423773148148</v>
+        <v>46101.312939814816</v>
       </c>
       <c r="E68" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F68" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="G68">
-        <v>708641473</v>
+        <v>748377555</v>
       </c>
       <c r="H68" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="I68" t="s">
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
       </c>
       <c r="L68" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M68" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N68" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O68" t="s">
         <v>0</v>
       </c>
-      <c r="P68" s="1">
-        <v>850000</v>
+      <c r="P68" t="s">
+        <v>0</v>
       </c>
       <c r="Q68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>58925987</v>
+        <v>58860538</v>
       </c>
       <c r="B69" s="2">
-        <v>46078.434814814813</v>
+        <v>46077.446666666663</v>
       </c>
       <c r="C69">
-        <v>60163873</v>
+        <v>60551848</v>
       </c>
       <c r="D69" s="2">
-        <v>46100.423101851855</v>
+        <v>46107.634930555556</v>
       </c>
       <c r="E69" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F69" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="G69">
-        <v>708641473</v>
+        <v>748377555</v>
       </c>
       <c r="H69" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="I69" t="s">
         <v>0</v>
       </c>
       <c r="J69" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K69" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L69" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M69" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N69" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O69" t="s">
         <v>0</v>
       </c>
-      <c r="P69" t="s">
-        <v>0</v>
+      <c r="P69" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q69" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>58892481</v>
+        <v>58862661</v>
       </c>
       <c r="B70" s="2">
-        <v>46077.688344907408</v>
+        <v>46077.461805555555</v>
       </c>
       <c r="C70">
-        <v>60413667</v>
+        <v>60042646</v>
       </c>
       <c r="D70" s="2">
-        <v>46105.602303240739</v>
+        <v>46098.494629629633</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G70">
         <v>748377555</v>
       </c>
       <c r="H70" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="I70" t="s">
         <v>0</v>
@@ -5027,45 +5045,45 @@
         <v>8</v>
       </c>
       <c r="M70" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N70" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O70" t="s">
         <v>0</v>
       </c>
-      <c r="P70" s="1">
-        <v>5324000</v>
+      <c r="P70" t="s">
+        <v>0</v>
       </c>
       <c r="Q70" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>58892468</v>
+        <v>58862680</v>
       </c>
       <c r="B71" s="2">
-        <v>46077.688321759262</v>
+        <v>46077.461828703701</v>
       </c>
       <c r="C71">
-        <v>60414369</v>
+        <v>60043590</v>
       </c>
       <c r="D71" s="2">
-        <v>46105.607986111114</v>
+        <v>46098.501527777778</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G71">
         <v>748377555</v>
       </c>
       <c r="H71" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="I71" t="s">
         <v>0</v>
@@ -5080,45 +5098,45 @@
         <v>8</v>
       </c>
       <c r="M71" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N71" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O71" t="s">
         <v>0</v>
       </c>
-      <c r="P71" t="s">
-        <v>0</v>
+      <c r="P71" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q71" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>58889883</v>
+        <v>58868849</v>
       </c>
       <c r="B72" s="2">
-        <v>46077.670601851853</v>
+        <v>46077.501203703701</v>
       </c>
       <c r="C72">
-        <v>60328639</v>
+        <v>60416909</v>
       </c>
       <c r="D72" s="2">
-        <v>46104.393576388888</v>
+        <v>46105.625150462962</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F72" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G72">
         <v>748377555</v>
       </c>
       <c r="H72" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I72" t="s">
         <v>0</v>
@@ -5133,45 +5151,45 @@
         <v>8</v>
       </c>
       <c r="M72" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N72" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O72" t="s">
         <v>0</v>
       </c>
-      <c r="P72" s="1">
-        <v>5324000</v>
+      <c r="P72" t="s">
+        <v>0</v>
       </c>
       <c r="Q72" t="s">
-        <v>73</v>
+        <v>178</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>58889872</v>
+        <v>58868860</v>
       </c>
       <c r="B73" s="2">
-        <v>46077.670567129629</v>
+        <v>46077.501238425924</v>
       </c>
       <c r="C73">
-        <v>60225565</v>
+        <v>60340792</v>
       </c>
       <c r="D73" s="2">
-        <v>46101.301990740743</v>
+        <v>46104.493530092594</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G73">
         <v>748377555</v>
       </c>
       <c r="H73" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I73" t="s">
         <v>0</v>
@@ -5186,45 +5204,45 @@
         <v>8</v>
       </c>
       <c r="M73" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N73" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O73" t="s">
         <v>0</v>
       </c>
-      <c r="P73" t="s">
-        <v>0</v>
+      <c r="P73" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q73" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>58885259</v>
+        <v>58885251</v>
       </c>
       <c r="B74" s="2">
-        <v>46077.638657407406</v>
+        <v>46077.63863425926</v>
       </c>
       <c r="C74">
-        <v>60373389</v>
+        <v>60408762</v>
       </c>
       <c r="D74" s="2">
-        <v>46104.751145833332</v>
+        <v>46105.557326388887</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G74">
         <v>748377507</v>
       </c>
       <c r="H74" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I74" t="s">
         <v>0</v>
@@ -5239,45 +5257,45 @@
         <v>8</v>
       </c>
       <c r="M74" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N74" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O74" t="s">
         <v>0</v>
       </c>
-      <c r="P74" s="1">
-        <v>5324000</v>
+      <c r="P74" t="s">
+        <v>0</v>
       </c>
       <c r="Q74" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>58885251</v>
+        <v>58885259</v>
       </c>
       <c r="B75" s="2">
-        <v>46077.63863425926</v>
+        <v>46077.638657407406</v>
       </c>
       <c r="C75">
-        <v>60408762</v>
+        <v>60373389</v>
       </c>
       <c r="D75" s="2">
-        <v>46105.557326388887</v>
+        <v>46104.751145833332</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G75">
         <v>748377507</v>
       </c>
       <c r="H75" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I75" t="s">
         <v>0</v>
@@ -5292,39 +5310,39 @@
         <v>8</v>
       </c>
       <c r="M75" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N75" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O75" t="s">
         <v>0</v>
       </c>
-      <c r="P75" t="s">
-        <v>0</v>
+      <c r="P75" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q75" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>58868860</v>
+        <v>58889872</v>
       </c>
       <c r="B76" s="2">
-        <v>46077.501238425924</v>
+        <v>46077.670567129629</v>
       </c>
       <c r="C76">
-        <v>60340792</v>
+        <v>60225565</v>
       </c>
       <c r="D76" s="2">
-        <v>46104.493530092594</v>
+        <v>46101.301990740743</v>
       </c>
       <c r="E76" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F76" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G76">
         <v>748377555</v>
@@ -5345,39 +5363,39 @@
         <v>8</v>
       </c>
       <c r="M76" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N76" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O76" t="s">
         <v>0</v>
       </c>
-      <c r="P76" s="1">
-        <v>5324000</v>
+      <c r="P76" t="s">
+        <v>0</v>
       </c>
       <c r="Q76" t="s">
-        <v>73</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>58868849</v>
+        <v>58889883</v>
       </c>
       <c r="B77" s="2">
-        <v>46077.501203703701</v>
+        <v>46077.670601851853</v>
       </c>
       <c r="C77">
-        <v>60416909</v>
+        <v>60328639</v>
       </c>
       <c r="D77" s="2">
-        <v>46105.625150462962</v>
+        <v>46104.393576388888</v>
       </c>
       <c r="E77" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F77" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G77">
         <v>748377555</v>
@@ -5398,45 +5416,45 @@
         <v>8</v>
       </c>
       <c r="M77" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N77" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O77" t="s">
         <v>0</v>
       </c>
-      <c r="P77" t="s">
-        <v>0</v>
+      <c r="P77" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q77" t="s">
-        <v>181</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>58862680</v>
+        <v>58892468</v>
       </c>
       <c r="B78" s="2">
-        <v>46077.461828703701</v>
+        <v>46077.688321759262</v>
       </c>
       <c r="C78">
-        <v>60043590</v>
+        <v>60414369</v>
       </c>
       <c r="D78" s="2">
-        <v>46098.501527777778</v>
+        <v>46105.607986111114</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
       </c>
       <c r="F78" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G78">
         <v>748377555</v>
       </c>
       <c r="H78" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I78" t="s">
         <v>0</v>
@@ -5451,45 +5469,45 @@
         <v>8</v>
       </c>
       <c r="M78" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N78" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O78" t="s">
         <v>0</v>
       </c>
-      <c r="P78" s="1">
-        <v>5324000</v>
+      <c r="P78" t="s">
+        <v>0</v>
       </c>
       <c r="Q78" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>58862661</v>
+        <v>58892481</v>
       </c>
       <c r="B79" s="2">
-        <v>46077.461805555555</v>
+        <v>46077.688344907408</v>
       </c>
       <c r="C79">
-        <v>60042646</v>
+        <v>60413667</v>
       </c>
       <c r="D79" s="2">
-        <v>46098.494629629633</v>
+        <v>46105.602303240739</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
       </c>
       <c r="F79" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G79">
         <v>748377555</v>
       </c>
       <c r="H79" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I79" t="s">
         <v>0</v>
@@ -5504,63 +5522,63 @@
         <v>8</v>
       </c>
       <c r="M79" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N79" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O79" t="s">
         <v>0</v>
       </c>
-      <c r="P79" t="s">
-        <v>0</v>
+      <c r="P79" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q79" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>58860531</v>
+        <v>58925987</v>
       </c>
       <c r="B80" s="2">
-        <v>46077.446631944447</v>
+        <v>46078.434814814813</v>
       </c>
       <c r="C80">
-        <v>60225679</v>
+        <v>60163873</v>
       </c>
       <c r="D80" s="2">
-        <v>46101.312939814816</v>
+        <v>46100.423101851855</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="G80">
-        <v>748377555</v>
+        <v>708641473</v>
       </c>
       <c r="H80" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="I80" t="s">
         <v>0</v>
       </c>
       <c r="J80" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K80" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L80" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M80" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N80" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O80" t="s">
         <v>0</v>
@@ -5569,192 +5587,192 @@
         <v>0</v>
       </c>
       <c r="Q80" t="s">
-        <v>35</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>58856498</v>
+        <v>58959238</v>
       </c>
       <c r="B81" s="2">
-        <v>46077.418171296296</v>
+        <v>46078.665532407409</v>
       </c>
       <c r="C81">
-        <v>60184731</v>
+        <v>60163938</v>
       </c>
       <c r="D81" s="2">
-        <v>46100.579618055555</v>
+        <v>46100.423773148148</v>
       </c>
       <c r="E81" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F81" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G81">
-        <v>748377555</v>
+        <v>708641473</v>
       </c>
       <c r="H81" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="I81" t="s">
         <v>0</v>
       </c>
       <c r="J81" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K81" t="s">
         <v>5</v>
       </c>
       <c r="L81" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M81" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N81" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O81" t="s">
         <v>0</v>
       </c>
-      <c r="P81" t="s">
-        <v>0</v>
+      <c r="P81" s="1">
+        <v>850000</v>
       </c>
       <c r="Q81" t="s">
-        <v>270</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>58822595</v>
+        <v>58963630</v>
       </c>
       <c r="B82" s="2">
-        <v>46076.670856481483</v>
+        <v>46078.697002314817</v>
       </c>
       <c r="C82">
-        <v>60208557</v>
+        <v>60167087</v>
       </c>
       <c r="D82" s="2">
-        <v>46100.764618055553</v>
+        <v>46100.449837962966</v>
       </c>
       <c r="E82" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F82" t="s">
-        <v>170</v>
+        <v>48</v>
       </c>
       <c r="G82">
-        <v>708086472</v>
+        <v>747726344</v>
       </c>
       <c r="H82" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="I82" t="s">
         <v>0</v>
       </c>
       <c r="J82" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
       </c>
       <c r="L82" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M82" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N82" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O82" t="s">
         <v>0</v>
       </c>
-      <c r="P82" s="1">
-        <v>1150000</v>
+      <c r="P82" t="s">
+        <v>0</v>
       </c>
       <c r="Q82" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>58822576</v>
+        <v>58963646</v>
       </c>
       <c r="B83" s="2">
-        <v>46076.670810185184</v>
+        <v>46078.697048611109</v>
       </c>
       <c r="C83">
-        <v>59375318</v>
+        <v>60185453</v>
       </c>
       <c r="D83" s="2">
-        <v>46085.763622685183</v>
+        <v>46100.586238425924</v>
       </c>
       <c r="E83" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F83" t="s">
-        <v>170</v>
+        <v>48</v>
       </c>
       <c r="G83">
-        <v>708086472</v>
+        <v>747726344</v>
       </c>
       <c r="H83" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="I83" t="s">
         <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K83" t="s">
         <v>5</v>
       </c>
       <c r="L83" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M83" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N83" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O83" t="s">
         <v>0</v>
       </c>
-      <c r="P83" t="s">
+      <c r="P83">
         <v>0</v>
       </c>
       <c r="Q83" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>58821553</v>
+        <v>59278285</v>
       </c>
       <c r="B84" s="2">
-        <v>46076.664525462962</v>
+        <v>46084.516597222224</v>
       </c>
       <c r="C84">
-        <v>59998536</v>
+        <v>60396888</v>
       </c>
       <c r="D84" s="2">
-        <v>46097.435590277775</v>
+        <v>46105.459768518522</v>
       </c>
       <c r="E84" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="F84" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="G84">
-        <v>708086472</v>
+        <v>759651079</v>
       </c>
       <c r="H84" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="I84" t="s">
         <v>0</v>
@@ -5769,45 +5787,45 @@
         <v>8</v>
       </c>
       <c r="M84" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N84" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O84" t="s">
         <v>0</v>
       </c>
       <c r="P84" s="1">
-        <v>705000</v>
+        <v>500000</v>
       </c>
       <c r="Q84" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>58821537</v>
+        <v>59278925</v>
       </c>
       <c r="B85" s="2">
-        <v>46076.664479166669</v>
+        <v>46084.521053240744</v>
       </c>
       <c r="C85">
-        <v>60409857</v>
+        <v>60397473</v>
       </c>
       <c r="D85" s="2">
-        <v>46105.569016203706</v>
+        <v>46105.464074074072</v>
       </c>
       <c r="E85" t="s">
+        <v>16</v>
+      </c>
+      <c r="F85" t="s">
+        <v>189</v>
+      </c>
+      <c r="G85">
+        <v>759651079</v>
+      </c>
+      <c r="H85" t="s">
         <v>191</v>
-      </c>
-      <c r="F85" t="s">
-        <v>170</v>
-      </c>
-      <c r="G85">
-        <v>708086472</v>
-      </c>
-      <c r="H85" t="s">
-        <v>130</v>
       </c>
       <c r="I85" t="s">
         <v>0</v>
@@ -5816,51 +5834,51 @@
         <v>18</v>
       </c>
       <c r="K85" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L85" t="s">
         <v>8</v>
       </c>
       <c r="M85" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N85" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O85" t="s">
         <v>0</v>
       </c>
-      <c r="P85" t="s">
-        <v>0</v>
+      <c r="P85" s="1">
+        <v>500000</v>
       </c>
       <c r="Q85" t="s">
-        <v>176</v>
+        <v>242</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>58808846</v>
+        <v>59300338</v>
       </c>
       <c r="B86" s="2">
-        <v>46076.586747685185</v>
+        <v>46084.687997685185</v>
       </c>
       <c r="C86">
-        <v>60368622</v>
+        <v>60558677</v>
       </c>
       <c r="D86" s="2">
-        <v>46104.709988425922</v>
+        <v>46107.684594907405</v>
       </c>
       <c r="E86" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="F86" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G86">
-        <v>749994094</v>
+        <v>545254325</v>
       </c>
       <c r="H86" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="I86" t="s">
         <v>0</v>
@@ -5869,7 +5887,7 @@
         <v>18</v>
       </c>
       <c r="K86" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L86" t="s">
         <v>8</v>
@@ -5878,7 +5896,7 @@
         <v>3</v>
       </c>
       <c r="N86" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O86" t="s">
         <v>0</v>
@@ -5887,210 +5905,210 @@
         <v>2000000</v>
       </c>
       <c r="Q86" t="s">
-        <v>169</v>
+        <v>266</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>58650374</v>
+        <v>59301554</v>
       </c>
       <c r="B87" s="2">
-        <v>46073.483518518522</v>
+        <v>46084.695763888885</v>
       </c>
       <c r="C87">
-        <v>60467780</v>
+        <v>60611241</v>
       </c>
       <c r="D87" s="2">
-        <v>46106.494745370372</v>
+        <v>46108.537268518521</v>
       </c>
       <c r="E87" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="F87" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G87">
-        <v>708193864</v>
+        <v>777654212</v>
       </c>
       <c r="H87" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="I87" t="s">
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K87" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="L87" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M87" t="s">
         <v>3</v>
       </c>
       <c r="N87" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O87" t="s">
         <v>0</v>
       </c>
-      <c r="P87" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q87">
-        <v>2722229765</v>
+      <c r="P87" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>58649837</v>
+        <v>59308240</v>
       </c>
       <c r="B88" s="2">
-        <v>46073.479409722226</v>
+        <v>46084.755844907406</v>
       </c>
       <c r="C88">
-        <v>59753844</v>
+        <v>60617360</v>
       </c>
       <c r="D88" s="2">
-        <v>46092.619826388887</v>
+        <v>46108.594525462962</v>
       </c>
       <c r="E88" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="F88" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="G88">
-        <v>759250737</v>
+        <v>707865499</v>
       </c>
       <c r="H88" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="I88" t="s">
         <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K88" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L88" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M88" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N88" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O88" t="s">
         <v>0</v>
       </c>
       <c r="P88" s="1">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="Q88" t="s">
-        <v>181</v>
+        <v>292</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>58649804</v>
+        <v>59309764</v>
       </c>
       <c r="B89" s="2">
-        <v>46073.479305555556</v>
+        <v>46084.777083333334</v>
       </c>
       <c r="C89">
-        <v>59753122</v>
+        <v>60432246</v>
       </c>
       <c r="D89" s="2">
-        <v>46092.615983796299</v>
+        <v>46105.737245370372</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
       </c>
       <c r="F89" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="G89">
-        <v>759250737</v>
+        <v>708164102</v>
       </c>
       <c r="H89" t="s">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="I89" t="s">
         <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
       </c>
       <c r="L89" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M89" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N89" t="s">
+        <v>196</v>
+      </c>
+      <c r="O89" t="s">
+        <v>0</v>
+      </c>
+      <c r="P89" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="Q89" t="s">
         <v>199</v>
-      </c>
-      <c r="O89" t="s">
-        <v>0</v>
-      </c>
-      <c r="P89" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>58642079</v>
+        <v>59374776</v>
       </c>
       <c r="B90" s="2">
-        <v>46073.425034722219</v>
+        <v>46085.757662037038</v>
       </c>
       <c r="C90">
-        <v>59755320</v>
+        <v>60185369</v>
       </c>
       <c r="D90" s="2">
-        <v>46092.630370370367</v>
+        <v>46100.585393518515</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
       </c>
       <c r="F90" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="G90">
-        <v>759250737</v>
+        <v>747726344</v>
       </c>
       <c r="H90" t="s">
-        <v>28</v>
+        <v>202</v>
       </c>
       <c r="I90" t="s">
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K90" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L90" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M90" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N90" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O90" t="s">
         <v>0</v>
@@ -6099,192 +6117,192 @@
         <v>0</v>
       </c>
       <c r="Q90" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>58635674</v>
+        <v>59406146</v>
       </c>
       <c r="B91" s="2">
-        <v>46073.372488425928</v>
+        <v>46086.506643518522</v>
       </c>
       <c r="C91">
-        <v>60160137</v>
+        <v>60600544</v>
       </c>
       <c r="D91" s="2">
-        <v>46100.389884259261</v>
+        <v>46108.458136574074</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
       </c>
       <c r="F91" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="G91">
-        <v>759250737</v>
+        <v>709136702</v>
       </c>
       <c r="H91" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="I91" t="s">
         <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
       </c>
       <c r="L91" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M91" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N91" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O91" t="s">
         <v>0</v>
       </c>
-      <c r="P91" s="1">
-        <v>500000</v>
+      <c r="P91">
+        <v>0</v>
       </c>
       <c r="Q91" t="s">
-        <v>73</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>58635645</v>
+        <v>59406937</v>
       </c>
       <c r="B92" s="2">
-        <v>46073.372395833336</v>
+        <v>46086.512870370374</v>
       </c>
       <c r="C92">
-        <v>59752855</v>
+        <v>60616367</v>
       </c>
       <c r="D92" s="2">
-        <v>46092.614201388889</v>
+        <v>46108.587060185186</v>
       </c>
       <c r="E92" t="s">
-        <v>10</v>
+        <v>283</v>
       </c>
       <c r="F92" t="s">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="G92">
-        <v>759250737</v>
+        <v>709136702</v>
       </c>
       <c r="H92" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="I92" t="s">
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M92" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N92" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O92" t="s">
         <v>0</v>
       </c>
-      <c r="P92" t="s">
+      <c r="P92">
         <v>0</v>
       </c>
       <c r="Q92" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>58626822</v>
+        <v>59409078</v>
       </c>
       <c r="B93" s="2">
-        <v>46072.810324074075</v>
+        <v>46086.529247685183</v>
       </c>
       <c r="C93">
-        <v>59811821</v>
+        <v>60600044</v>
       </c>
       <c r="D93" s="2">
-        <v>46093.543773148151</v>
+        <v>46108.453865740739</v>
       </c>
       <c r="E93" t="s">
         <v>10</v>
       </c>
       <c r="F93" t="s">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="G93">
-        <v>709574114</v>
+        <v>709140938</v>
       </c>
       <c r="H93" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="I93" t="s">
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="K93" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L93" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M93" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N93" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O93" t="s">
         <v>0</v>
       </c>
-      <c r="P93" s="1">
-        <v>445307</v>
+      <c r="P93" t="s">
+        <v>0</v>
       </c>
       <c r="Q93" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>58407509</v>
+        <v>59409752</v>
       </c>
       <c r="B94" s="2">
-        <v>46069.545914351853</v>
+        <v>46086.534502314818</v>
       </c>
       <c r="C94">
-        <v>60340196</v>
+        <v>60600716</v>
       </c>
       <c r="D94" s="2">
-        <v>46104.488530092596</v>
+        <v>46108.459768518522</v>
       </c>
       <c r="E94" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="F94" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="G94">
-        <v>709213314</v>
+        <v>758700193</v>
       </c>
       <c r="H94" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I94" t="s">
         <v>0</v>
@@ -6302,7 +6320,7 @@
         <v>3</v>
       </c>
       <c r="N94" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O94" t="s">
         <v>0</v>
@@ -6311,263 +6329,263 @@
         <v>0</v>
       </c>
       <c r="Q94" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>58274609</v>
+        <v>59410212</v>
       </c>
       <c r="B95" s="2">
-        <v>46066.525011574071</v>
+        <v>46086.537708333337</v>
       </c>
       <c r="C95">
-        <v>59264178</v>
+        <v>59835857</v>
       </c>
       <c r="D95" s="2">
-        <v>46084.406759259262</v>
+        <v>46093.728726851848</v>
       </c>
       <c r="E95" t="s">
-        <v>10</v>
+        <v>188</v>
       </c>
       <c r="F95" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="G95">
-        <v>2722480700</v>
+        <v>789018789</v>
       </c>
       <c r="H95" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="I95" t="s">
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="K95" t="s">
-        <v>5</v>
+        <v>208</v>
       </c>
       <c r="L95" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M95" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N95" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O95" t="s">
         <v>0</v>
       </c>
-      <c r="P95" s="1">
-        <v>522590</v>
+      <c r="P95" t="s">
+        <v>0</v>
       </c>
       <c r="Q95" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>58168004</v>
+        <v>59410843</v>
       </c>
       <c r="B96" s="2">
-        <v>46064.657037037039</v>
+        <v>46086.542870370373</v>
       </c>
       <c r="C96">
-        <v>60360622</v>
+        <v>60526566</v>
       </c>
       <c r="D96" s="2">
-        <v>46104.652754629627</v>
+        <v>46107.452592592592</v>
       </c>
       <c r="E96" t="s">
-        <v>129</v>
+        <v>295</v>
       </c>
       <c r="F96" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="G96">
-        <v>504041812</v>
+        <v>758700193</v>
       </c>
       <c r="H96" t="s">
-        <v>278</v>
-      </c>
-      <c r="I96">
-        <v>1811236</v>
+        <v>210</v>
+      </c>
+      <c r="I96" t="s">
+        <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="K96" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L96" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M96" t="s">
         <v>3</v>
       </c>
       <c r="N96" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O96" t="s">
         <v>0</v>
       </c>
-      <c r="P96" s="1">
-        <v>2000000</v>
+      <c r="P96" t="s">
+        <v>0</v>
       </c>
       <c r="Q96" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>58166885</v>
+        <v>59414411</v>
       </c>
       <c r="B97" s="2">
-        <v>46064.649965277778</v>
+        <v>46086.57104166667</v>
       </c>
       <c r="C97">
-        <v>59811530</v>
+        <v>60601081</v>
       </c>
       <c r="D97" s="2">
-        <v>46093.540775462963</v>
+        <v>46108.462025462963</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>116</v>
+        <v>211</v>
       </c>
       <c r="G97">
-        <v>504041812</v>
+        <v>566473307</v>
       </c>
       <c r="H97" t="s">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="I97" t="s">
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K97" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L97" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M97" t="s">
         <v>3</v>
       </c>
       <c r="N97" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O97" t="s">
         <v>0</v>
       </c>
-      <c r="P97" s="1">
-        <v>2000000</v>
+      <c r="P97">
+        <v>0</v>
       </c>
       <c r="Q97" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>58151683</v>
+        <v>59417066</v>
       </c>
       <c r="B98" s="2">
-        <v>46064.532222222224</v>
+        <v>46086.594525462962</v>
       </c>
       <c r="C98">
-        <v>60402173</v>
+        <v>60589286</v>
       </c>
       <c r="D98" s="2">
-        <v>46105.501574074071</v>
+        <v>46108.367418981485</v>
       </c>
       <c r="E98" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F98" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="G98">
-        <v>2721271444</v>
+        <v>709565662</v>
       </c>
       <c r="H98" t="s">
-        <v>156</v>
+        <v>214</v>
       </c>
       <c r="I98" t="s">
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="K98" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M98" t="s">
         <v>3</v>
       </c>
       <c r="N98" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O98" t="s">
         <v>0</v>
       </c>
-      <c r="P98" s="1">
-        <v>1495965</v>
+      <c r="P98">
+        <v>0</v>
       </c>
       <c r="Q98" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>58144220</v>
+        <v>59464660</v>
       </c>
       <c r="B99" s="2">
-        <v>46064.478425925925</v>
+        <v>46087.421030092592</v>
       </c>
       <c r="C99">
-        <v>60455803</v>
+        <v>60601930</v>
       </c>
       <c r="D99" s="2">
-        <v>46106.387337962966</v>
+        <v>46108.467233796298</v>
       </c>
       <c r="E99" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F99" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="G99">
-        <v>2722418166</v>
+        <v>554235979</v>
       </c>
       <c r="H99" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I99" t="s">
         <v>0</v>
       </c>
       <c r="J99" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K99" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L99" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M99" t="s">
         <v>7</v>
       </c>
       <c r="N99" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O99" t="s">
         <v>0</v>
@@ -6576,51 +6594,51 @@
         <v>0</v>
       </c>
       <c r="Q99" t="s">
-        <v>277</v>
+        <v>34</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>58096775</v>
+        <v>59465071</v>
       </c>
       <c r="B100" s="2">
-        <v>46063.603263888886</v>
+        <v>46087.424062500002</v>
       </c>
       <c r="C100">
-        <v>58655959</v>
+        <v>60531474</v>
       </c>
       <c r="D100" s="2">
-        <v>46073.525740740741</v>
+        <v>46107.489861111113</v>
       </c>
       <c r="E100" t="s">
-        <v>16</v>
+        <v>295</v>
       </c>
       <c r="F100" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="G100">
-        <v>708086759</v>
+        <v>554235979</v>
       </c>
       <c r="H100" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="I100" t="s">
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M100" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N100" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O100" t="s">
         <v>0</v>
@@ -6629,33 +6647,33 @@
         <v>0</v>
       </c>
       <c r="Q100" t="s">
-        <v>153</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>58093843</v>
+        <v>59466514</v>
       </c>
       <c r="B101" s="2">
-        <v>46063.583460648151</v>
+        <v>46087.436643518522</v>
       </c>
       <c r="C101">
-        <v>58667700</v>
+        <v>60602589</v>
       </c>
       <c r="D101" s="2">
-        <v>46073.611655092594</v>
+        <v>46108.472187500003</v>
       </c>
       <c r="E101" t="s">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="F101" t="s">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="G101">
-        <v>708086759</v>
+        <v>141679210</v>
       </c>
       <c r="H101" t="s">
-        <v>150</v>
+        <v>215</v>
       </c>
       <c r="I101" t="s">
         <v>0</v>
@@ -6670,63 +6688,63 @@
         <v>6</v>
       </c>
       <c r="M101" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N101" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O101" t="s">
         <v>0</v>
       </c>
-      <c r="P101">
-        <v>0</v>
+      <c r="P101" s="1">
+        <v>3213390</v>
       </c>
       <c r="Q101" t="s">
-        <v>152</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>58093827</v>
+        <v>59466778</v>
       </c>
       <c r="B102" s="2">
-        <v>46063.583402777775</v>
+        <v>46087.438715277778</v>
       </c>
       <c r="C102">
-        <v>59486282</v>
+        <v>60553947</v>
       </c>
       <c r="D102" s="2">
-        <v>46087.591932870368</v>
+        <v>46107.648668981485</v>
       </c>
       <c r="E102" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="F102" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="G102">
-        <v>708086759</v>
+        <v>554235979</v>
       </c>
       <c r="H102" t="s">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="I102" t="s">
         <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="K102" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L102" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M102" t="s">
         <v>7</v>
       </c>
       <c r="N102" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O102" t="s">
         <v>0</v>
@@ -6735,157 +6753,157 @@
         <v>0</v>
       </c>
       <c r="Q102" t="s">
-        <v>151</v>
+        <v>294</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>58055656</v>
+        <v>59468518</v>
       </c>
       <c r="B103" s="2">
-        <v>46062.760023148148</v>
+        <v>46087.450266203705</v>
       </c>
       <c r="C103">
-        <v>60340320</v>
+        <v>60601750</v>
       </c>
       <c r="D103" s="2">
-        <v>46104.489583333336</v>
+        <v>46108.466053240743</v>
       </c>
       <c r="E103" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F103" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="G103">
-        <v>758224257</v>
+        <v>554235979</v>
       </c>
       <c r="H103" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="I103" t="s">
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="K103" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L103" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M103" t="s">
         <v>3</v>
       </c>
       <c r="N103" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O103" t="s">
         <v>0</v>
       </c>
-      <c r="P103" s="1">
-        <v>1800000</v>
+      <c r="P103" t="s">
+        <v>0</v>
       </c>
       <c r="Q103" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>57899728</v>
+        <v>59469589</v>
       </c>
       <c r="B104" s="2">
-        <v>46059.503668981481</v>
+        <v>46087.458460648151</v>
       </c>
       <c r="C104">
-        <v>59053570</v>
+        <v>60601477</v>
       </c>
       <c r="D104" s="2">
-        <v>46080.432372685187</v>
+        <v>46108.464641203704</v>
       </c>
       <c r="E104" t="s">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="F104" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G104">
-        <v>505980067</v>
+        <v>554235979</v>
       </c>
       <c r="H104" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="I104" t="s">
         <v>0</v>
       </c>
       <c r="J104" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="K104" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L104" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M104" t="s">
         <v>3</v>
       </c>
       <c r="N104" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O104" t="s">
         <v>0</v>
       </c>
-      <c r="P104" s="1">
-        <v>1002937</v>
+      <c r="P104" t="s">
+        <v>0</v>
       </c>
       <c r="Q104" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>57849095</v>
+        <v>59480507</v>
       </c>
       <c r="B105" s="2">
-        <v>46058.603668981479</v>
+        <v>46087.544247685182</v>
       </c>
       <c r="C105">
-        <v>60388868</v>
+        <v>60564140</v>
       </c>
       <c r="D105" s="2">
-        <v>46105.385023148148</v>
+        <v>46107.723194444443</v>
       </c>
       <c r="E105" t="s">
-        <v>16</v>
+        <v>155</v>
       </c>
       <c r="F105" t="s">
-        <v>142</v>
+        <v>217</v>
       </c>
       <c r="G105">
-        <v>707109668</v>
+        <v>708547070</v>
       </c>
       <c r="H105" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="I105" t="s">
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K105" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L105" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M105" t="s">
         <v>3</v>
       </c>
       <c r="N105" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O105" t="s">
         <v>0</v>
@@ -6894,33 +6912,33 @@
         <v>0</v>
       </c>
       <c r="Q105" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>57773018</v>
+        <v>59495473</v>
       </c>
       <c r="B106" s="2">
-        <v>46057.517175925925</v>
+        <v>46087.653935185182</v>
       </c>
       <c r="C106">
-        <v>60394430</v>
+        <v>60551423</v>
       </c>
       <c r="D106" s="2">
-        <v>46105.441655092596</v>
+        <v>46107.631689814814</v>
       </c>
       <c r="E106" t="s">
-        <v>276</v>
+        <v>21</v>
       </c>
       <c r="F106" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="G106">
-        <v>758333146</v>
+        <v>506727287</v>
       </c>
       <c r="H106" t="s">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="I106" t="s">
         <v>0</v>
@@ -6929,51 +6947,51 @@
         <v>13</v>
       </c>
       <c r="K106" t="s">
-        <v>190</v>
+        <v>5</v>
       </c>
       <c r="L106" t="s">
         <v>6</v>
       </c>
       <c r="M106" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N106" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O106" t="s">
         <v>0</v>
       </c>
-      <c r="P106" s="1">
-        <v>400000</v>
+      <c r="P106">
+        <v>0</v>
       </c>
       <c r="Q106" t="s">
-        <v>237</v>
+        <v>297</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>57706849</v>
+        <v>59498233</v>
       </c>
       <c r="B107" s="2">
-        <v>46056.499166666668</v>
+        <v>46087.67423611111</v>
       </c>
       <c r="C107">
-        <v>59767932</v>
+        <v>59693004</v>
       </c>
       <c r="D107" s="2">
-        <v>46092.721273148149</v>
+        <v>46091.627928240741</v>
       </c>
       <c r="E107" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F107" t="s">
-        <v>144</v>
+        <v>218</v>
       </c>
       <c r="G107">
-        <v>708086472</v>
+        <v>606727287</v>
       </c>
       <c r="H107" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="I107" t="s">
         <v>0</v>
@@ -6982,7 +7000,7 @@
         <v>13</v>
       </c>
       <c r="K107" t="s">
-        <v>5</v>
+        <v>220</v>
       </c>
       <c r="L107" t="s">
         <v>6</v>
@@ -6991,7 +7009,7 @@
         <v>7</v>
       </c>
       <c r="N107" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O107" t="s">
         <v>0</v>
@@ -7000,86 +7018,86 @@
         <v>0</v>
       </c>
       <c r="Q107" t="s">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>57692887</v>
+        <v>59537755</v>
       </c>
       <c r="B108" s="2">
-        <v>46056.394780092596</v>
+        <v>46088.586631944447</v>
       </c>
       <c r="C108">
-        <v>60356178</v>
+        <v>59807640</v>
       </c>
       <c r="D108" s="2">
-        <v>46104.621365740742</v>
+        <v>46093.511296296296</v>
       </c>
       <c r="E108" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="F108" t="s">
-        <v>142</v>
+        <v>221</v>
       </c>
       <c r="G108">
-        <v>707109668</v>
+        <v>556331131</v>
       </c>
       <c r="H108" t="s">
-        <v>143</v>
+        <v>221</v>
       </c>
       <c r="I108" t="s">
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K108" t="s">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="L108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M108" t="s">
         <v>7</v>
       </c>
       <c r="N108" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O108" t="s">
         <v>0</v>
       </c>
-      <c r="P108" t="s">
+      <c r="P108">
         <v>0</v>
       </c>
       <c r="Q108" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>57672103</v>
+        <v>59538099</v>
       </c>
       <c r="B109" s="2">
-        <v>46055.712083333332</v>
+        <v>46088.590717592589</v>
       </c>
       <c r="C109">
-        <v>58477217</v>
+        <v>60033812</v>
       </c>
       <c r="D109" s="2">
-        <v>46070.620787037034</v>
+        <v>46098.426782407405</v>
       </c>
       <c r="E109" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="F109" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="G109">
-        <v>707079088</v>
+        <v>566473307</v>
       </c>
       <c r="H109" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="I109" t="s">
         <v>0</v>
@@ -7096,43 +7114,40 @@
       <c r="M109" t="s">
         <v>3</v>
       </c>
-      <c r="N109" t="s">
-        <v>199</v>
-      </c>
       <c r="O109" t="s">
         <v>0</v>
       </c>
-      <c r="P109" s="1">
-        <v>1426700</v>
+      <c r="P109">
+        <v>0</v>
       </c>
       <c r="Q109" t="s">
-        <v>34</v>
+        <v>243</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110">
-        <v>57651441</v>
+        <v>59538597</v>
       </c>
       <c r="B110" s="2">
-        <v>46055.58011574074</v>
+        <v>46088.598194444443</v>
       </c>
       <c r="C110">
-        <v>58955875</v>
+        <v>60030833</v>
       </c>
       <c r="D110" s="2">
-        <v>46078.639594907407</v>
+        <v>46098.40320601852</v>
       </c>
       <c r="E110" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="F110" t="s">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="G110">
-        <v>707079088</v>
+        <v>566473307</v>
       </c>
       <c r="H110" t="s">
-        <v>138</v>
+        <v>224</v>
       </c>
       <c r="I110" t="s">
         <v>0</v>
@@ -7149,43 +7164,40 @@
       <c r="M110" t="s">
         <v>3</v>
       </c>
-      <c r="N110" t="s">
-        <v>199</v>
-      </c>
       <c r="O110" t="s">
         <v>0</v>
       </c>
-      <c r="P110" t="s">
-        <v>139</v>
+      <c r="P110">
+        <v>0</v>
       </c>
       <c r="Q110" t="s">
-        <v>39</v>
+        <v>243</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111">
-        <v>57398181</v>
+        <v>59541145</v>
       </c>
       <c r="B111" s="2">
-        <v>46050.584374999999</v>
+        <v>46088.634837962964</v>
       </c>
       <c r="C111">
-        <v>60344342</v>
+        <v>59799803</v>
       </c>
       <c r="D111" s="2">
-        <v>46104.528900462959</v>
+        <v>46093.453530092593</v>
       </c>
       <c r="E111" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F111" t="s">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="G111">
-        <v>720631500</v>
+        <v>546008131</v>
       </c>
       <c r="H111" t="s">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="I111" t="s">
         <v>0</v>
@@ -7194,51 +7206,51 @@
         <v>13</v>
       </c>
       <c r="K111" t="s">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="L111" t="s">
         <v>6</v>
       </c>
       <c r="M111" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N111" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O111" t="s">
         <v>0</v>
       </c>
-      <c r="P111" s="1">
-        <v>4406780</v>
+      <c r="P111">
+        <v>0</v>
       </c>
       <c r="Q111" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112">
-        <v>56970346</v>
+        <v>59606122</v>
       </c>
       <c r="B112" s="2">
-        <v>46042.557280092595</v>
+        <v>46090.447604166664</v>
       </c>
       <c r="C112">
-        <v>59242054</v>
+        <v>59682305</v>
       </c>
       <c r="D112" s="2">
-        <v>46083.719525462962</v>
+        <v>46091.541701388887</v>
       </c>
       <c r="E112" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F112" t="s">
-        <v>127</v>
+        <v>227</v>
       </c>
       <c r="G112">
-        <v>708667658</v>
+        <v>708454305</v>
       </c>
       <c r="H112" t="s">
-        <v>128</v>
+        <v>228</v>
       </c>
       <c r="I112" t="s">
         <v>0</v>
@@ -7247,51 +7259,51 @@
         <v>13</v>
       </c>
       <c r="K112" t="s">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="L112" t="s">
         <v>6</v>
       </c>
       <c r="M112" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N112" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O112" t="s">
         <v>0</v>
       </c>
-      <c r="P112" s="1">
-        <v>2871414</v>
+      <c r="P112">
+        <v>0</v>
       </c>
       <c r="Q112" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113">
-        <v>56675050</v>
+        <v>59615935</v>
       </c>
       <c r="B113" s="2">
-        <v>46036.516423611109</v>
+        <v>46090.512303240743</v>
       </c>
       <c r="C113">
-        <v>58216664</v>
+        <v>60393405</v>
       </c>
       <c r="D113" s="2">
-        <v>46065.536226851851</v>
+        <v>46105.432800925926</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
       </c>
       <c r="F113" t="s">
-        <v>133</v>
+        <v>229</v>
       </c>
       <c r="G113">
-        <v>748512613</v>
+        <v>767081456</v>
       </c>
       <c r="H113" t="s">
-        <v>134</v>
+        <v>230</v>
       </c>
       <c r="I113" t="s">
         <v>0</v>
@@ -7309,48 +7321,48 @@
         <v>3</v>
       </c>
       <c r="N113" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O113" t="s">
         <v>0</v>
       </c>
-      <c r="P113" s="1">
-        <v>4362401</v>
+      <c r="P113">
+        <v>0</v>
       </c>
       <c r="Q113" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114">
-        <v>56618123</v>
+        <v>59684312</v>
       </c>
       <c r="B114" s="2">
-        <v>46035.520821759259</v>
+        <v>46091.557453703703</v>
       </c>
       <c r="C114">
-        <v>59311833</v>
+        <v>59736324</v>
       </c>
       <c r="D114" s="2">
-        <v>46084.811782407407</v>
+        <v>46092.496296296296</v>
       </c>
       <c r="E114" t="s">
-        <v>129</v>
+        <v>234</v>
       </c>
       <c r="F114" t="s">
-        <v>126</v>
+        <v>231</v>
       </c>
       <c r="G114">
-        <v>504041812</v>
+        <v>3130227350</v>
       </c>
       <c r="H114" t="s">
-        <v>200</v>
-      </c>
-      <c r="I114">
-        <v>1775236</v>
+        <v>232</v>
+      </c>
+      <c r="I114" t="s">
+        <v>0</v>
       </c>
       <c r="J114" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
@@ -7362,466 +7374,466 @@
         <v>3</v>
       </c>
       <c r="N114" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O114" t="s">
         <v>0</v>
       </c>
-      <c r="P114" s="1">
-        <v>2000000</v>
+      <c r="P114" t="s">
+        <v>0</v>
       </c>
       <c r="Q114" t="s">
-        <v>201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115">
-        <v>56613961</v>
+        <v>59793967</v>
       </c>
       <c r="B115" s="2">
-        <v>46035.492175925923</v>
+        <v>46093.406724537039</v>
       </c>
       <c r="C115">
-        <v>59754685</v>
+        <v>60225840</v>
       </c>
       <c r="D115" s="2">
-        <v>46092.626307870371</v>
+        <v>46101.328912037039</v>
       </c>
       <c r="E115" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="F115" t="s">
-        <v>120</v>
+        <v>244</v>
       </c>
       <c r="G115">
-        <v>504041812</v>
+        <v>506727287</v>
       </c>
       <c r="H115" t="s">
-        <v>124</v>
+        <v>219</v>
       </c>
       <c r="I115" t="s">
         <v>0</v>
       </c>
       <c r="J115" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K115" t="s">
         <v>5</v>
       </c>
       <c r="L115" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M115" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N115" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O115" t="s">
         <v>0</v>
       </c>
-      <c r="P115" s="1">
-        <v>2000000</v>
+      <c r="P115">
+        <v>0</v>
       </c>
       <c r="Q115" t="s">
-        <v>125</v>
+        <v>35</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116">
-        <v>56612479</v>
+        <v>59801109</v>
       </c>
       <c r="B116" s="2">
-        <v>46035.481446759259</v>
+        <v>46093.464594907404</v>
       </c>
       <c r="C116">
-        <v>60101226</v>
+        <v>60611654</v>
       </c>
       <c r="D116" s="2">
-        <v>46099.43613425926</v>
+        <v>46108.541504629633</v>
       </c>
       <c r="E116" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="F116" t="s">
-        <v>120</v>
+        <v>245</v>
       </c>
       <c r="G116">
-        <v>504041812</v>
+        <v>709173657</v>
       </c>
       <c r="H116" t="s">
-        <v>123</v>
+        <v>246</v>
       </c>
       <c r="I116" t="s">
         <v>0</v>
       </c>
       <c r="J116" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K116" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L116" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M116" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N116" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O116" t="s">
         <v>0</v>
       </c>
-      <c r="P116" s="1">
-        <v>2000000</v>
+      <c r="P116">
+        <v>0</v>
       </c>
       <c r="Q116" t="s">
-        <v>188</v>
+        <v>298</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117">
-        <v>56611212</v>
+        <v>59813505</v>
       </c>
       <c r="B117" s="2">
-        <v>46035.471886574072</v>
+        <v>46093.557256944441</v>
       </c>
       <c r="C117">
-        <v>57137676</v>
+        <v>60137642</v>
       </c>
       <c r="D117" s="2">
-        <v>46045.45140046296</v>
+        <v>46099.71303240741</v>
       </c>
       <c r="E117" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="F117" t="s">
-        <v>120</v>
+        <v>247</v>
       </c>
       <c r="G117">
-        <v>504041812</v>
+        <v>706727287</v>
       </c>
       <c r="H117" t="s">
-        <v>121</v>
+        <v>248</v>
       </c>
       <c r="I117" t="s">
         <v>0</v>
       </c>
       <c r="J117" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K117" t="s">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="L117" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M117" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N117" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="O117" t="s">
         <v>0</v>
       </c>
-      <c r="P117" s="1">
-        <v>2000000</v>
+      <c r="P117">
+        <v>0</v>
       </c>
       <c r="Q117" t="s">
-        <v>122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118">
-        <v>56609018</v>
+        <v>59816396</v>
       </c>
       <c r="B118" s="2">
-        <v>46035.452465277776</v>
+        <v>46093.580590277779</v>
       </c>
       <c r="C118">
-        <v>60165633</v>
+        <v>60137506</v>
       </c>
       <c r="D118" s="2">
-        <v>46100.43891203704</v>
+        <v>46099.711053240739</v>
       </c>
       <c r="E118" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="F118" t="s">
-        <v>116</v>
+        <v>249</v>
       </c>
       <c r="G118">
-        <v>504041812</v>
+        <v>506727287</v>
       </c>
       <c r="H118" t="s">
-        <v>119</v>
-      </c>
-      <c r="I118" t="s">
-        <v>0</v>
+        <v>267</v>
+      </c>
+      <c r="I118">
+        <v>1848446</v>
       </c>
       <c r="J118" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K118" t="s">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="L118" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M118" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N118" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="O118" t="s">
         <v>0</v>
       </c>
-      <c r="P118" s="1">
-        <v>2000000</v>
+      <c r="P118">
+        <v>0</v>
       </c>
       <c r="Q118" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119">
-        <v>56607988</v>
+        <v>59820678</v>
       </c>
       <c r="B119" s="2">
-        <v>46035.443668981483</v>
+        <v>46093.612222222226</v>
       </c>
       <c r="C119">
-        <v>58404447</v>
+        <v>60208764</v>
       </c>
       <c r="D119" s="2">
-        <v>46069.522615740738</v>
+        <v>46100.766909722224</v>
       </c>
       <c r="E119" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="F119" t="s">
-        <v>116</v>
+        <v>250</v>
       </c>
       <c r="G119">
-        <v>504041812</v>
+        <v>506727287</v>
       </c>
       <c r="H119" t="s">
-        <v>118</v>
+        <v>251</v>
       </c>
       <c r="I119" t="s">
         <v>0</v>
       </c>
       <c r="J119" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K119" t="s">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="L119" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M119" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N119" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O119" t="s">
         <v>0</v>
       </c>
-      <c r="P119" s="1">
-        <v>2000000</v>
+      <c r="P119">
+        <v>0</v>
       </c>
       <c r="Q119" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120">
-        <v>56603495</v>
+        <v>59821965</v>
       </c>
       <c r="B120" s="2">
-        <v>46035.408518518518</v>
+        <v>46093.621331018519</v>
       </c>
       <c r="C120">
-        <v>59831107</v>
+        <v>60495824</v>
       </c>
       <c r="D120" s="2">
-        <v>46093.691342592596</v>
+        <v>46106.725034722222</v>
       </c>
       <c r="E120" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="F120" t="s">
-        <v>32</v>
+        <v>252</v>
       </c>
       <c r="G120">
-        <v>707003126</v>
+        <v>101383885</v>
       </c>
       <c r="H120" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="I120" t="s">
         <v>0</v>
       </c>
       <c r="J120" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K120" t="s">
         <v>5</v>
       </c>
       <c r="L120" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M120" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="N120" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O120" t="s">
         <v>0</v>
       </c>
       <c r="P120" s="1">
-        <v>7103410</v>
+        <v>3000000</v>
       </c>
       <c r="Q120" t="s">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121">
-        <v>56601982</v>
+        <v>59824550</v>
       </c>
       <c r="B121" s="2">
-        <v>46035.393611111111</v>
+        <v>46093.6405787037</v>
       </c>
       <c r="C121">
-        <v>60341610</v>
+        <v>60530213</v>
       </c>
       <c r="D121" s="2">
-        <v>46104.501319444447</v>
+        <v>46107.478576388887</v>
       </c>
       <c r="E121" t="s">
-        <v>10</v>
+        <v>296</v>
       </c>
       <c r="F121" t="s">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="G121">
-        <v>707003126</v>
+        <v>506727287</v>
       </c>
       <c r="H121" t="s">
-        <v>115</v>
+        <v>254</v>
       </c>
       <c r="I121" t="s">
         <v>0</v>
       </c>
       <c r="J121" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K121" t="s">
         <v>5</v>
       </c>
       <c r="L121" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M121" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N121" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O121" t="s">
         <v>0</v>
       </c>
-      <c r="P121" s="1">
-        <v>7103410</v>
+      <c r="P121">
+        <v>0</v>
       </c>
       <c r="Q121" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>56181778</v>
+        <v>59888143</v>
       </c>
       <c r="B122" s="2">
-        <v>46027.499212962961</v>
+        <v>46094.646597222221</v>
       </c>
       <c r="C122">
-        <v>59210339</v>
+        <v>60622376</v>
       </c>
       <c r="D122" s="2">
-        <v>46083.492881944447</v>
+        <v>46108.63175925926</v>
       </c>
       <c r="E122" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="F122" t="s">
-        <v>111</v>
+        <v>255</v>
       </c>
       <c r="G122">
-        <v>585990976</v>
+        <v>708858866</v>
       </c>
       <c r="H122" t="s">
-        <v>112</v>
-      </c>
-      <c r="I122">
-        <v>1765416</v>
+        <v>256</v>
+      </c>
+      <c r="I122" t="s">
+        <v>0</v>
       </c>
       <c r="J122" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K122" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L122" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M122" t="s">
         <v>3</v>
       </c>
       <c r="N122" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O122" t="s">
         <v>0</v>
       </c>
-      <c r="P122" s="1">
-        <v>3000000</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>113</v>
+      <c r="P122" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>2720219745</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123">
-        <v>55694485</v>
+        <v>59894743</v>
       </c>
       <c r="B123" s="2">
-        <v>46015.420092592591</v>
+        <v>46094.687673611108</v>
       </c>
       <c r="C123">
-        <v>56752240</v>
+        <v>60454133</v>
       </c>
       <c r="D123" s="2">
-        <v>46037.705520833333</v>
+        <v>46106.366770833331</v>
       </c>
       <c r="E123" t="s">
         <v>10</v>
       </c>
       <c r="F123" t="s">
-        <v>108</v>
+        <v>257</v>
       </c>
       <c r="G123">
-        <v>749338073</v>
+        <v>759668146</v>
       </c>
       <c r="H123" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="I123" t="s">
         <v>0</v>
@@ -7836,98 +7848,98 @@
         <v>6</v>
       </c>
       <c r="M123" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N123" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O123" t="s">
         <v>0</v>
       </c>
-      <c r="P123" s="1">
-        <v>638462</v>
+      <c r="P123" t="s">
+        <v>0</v>
       </c>
       <c r="Q123" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124">
-        <v>55686160</v>
+        <v>59894758</v>
       </c>
       <c r="B124" s="2">
-        <v>46015.355868055558</v>
+        <v>46094.687719907408</v>
       </c>
       <c r="C124">
-        <v>60471780</v>
+        <v>60616207</v>
       </c>
       <c r="D124" s="2">
-        <v>46106.530613425923</v>
+        <v>46108.585763888892</v>
       </c>
       <c r="E124" t="s">
-        <v>246</v>
+        <v>74</v>
       </c>
       <c r="F124" t="s">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="G124">
-        <v>777765287</v>
+        <v>759668146</v>
       </c>
       <c r="H124" t="s">
-        <v>67</v>
-      </c>
-      <c r="I124" t="s">
-        <v>0</v>
+        <v>268</v>
+      </c>
+      <c r="I124">
+        <v>1849216</v>
       </c>
       <c r="J124" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K124" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L124" t="s">
         <v>6</v>
       </c>
       <c r="M124" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N124" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O124" t="s">
         <v>0</v>
       </c>
       <c r="P124" s="1">
-        <v>850887</v>
+        <v>1000000</v>
       </c>
       <c r="Q124" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125">
-        <v>55636282</v>
+        <v>60026486</v>
       </c>
       <c r="B125" s="2">
-        <v>46014.435729166667</v>
+        <v>46098.36173611111</v>
       </c>
       <c r="C125">
-        <v>57367586</v>
+        <v>60121930</v>
       </c>
       <c r="D125" s="2">
-        <v>46049.856261574074</v>
+        <v>46099.594039351854</v>
       </c>
       <c r="E125" t="s">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="F125" t="s">
-        <v>106</v>
+        <v>244</v>
       </c>
       <c r="G125">
-        <v>759003900</v>
+        <v>506727287</v>
       </c>
       <c r="H125" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="I125" t="s">
         <v>0</v>
@@ -7936,157 +7948,157 @@
         <v>13</v>
       </c>
       <c r="K125" t="s">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="L125" t="s">
         <v>6</v>
       </c>
       <c r="M125" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N125" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O125" t="s">
         <v>0</v>
       </c>
-      <c r="P125" s="1">
-        <v>918681</v>
+      <c r="P125">
+        <v>0</v>
       </c>
       <c r="Q125" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126">
-        <v>55105103</v>
+        <v>60084243</v>
       </c>
       <c r="B126" s="2">
-        <v>46004.481180555558</v>
+        <v>46098.817627314813</v>
       </c>
       <c r="C126">
-        <v>56940307</v>
+        <v>60622487</v>
       </c>
       <c r="D126" s="2">
-        <v>46041.803784722222</v>
+        <v>46108.632453703707</v>
       </c>
       <c r="E126" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F126" t="s">
-        <v>89</v>
+        <v>259</v>
       </c>
       <c r="G126">
-        <v>504033918</v>
+        <v>707708502</v>
       </c>
       <c r="H126" t="s">
-        <v>103</v>
-      </c>
-      <c r="I126" t="s">
+        <v>43</v>
+      </c>
+      <c r="I126">
         <v>0</v>
       </c>
       <c r="J126" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K126" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L126" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M126" t="s">
         <v>3</v>
       </c>
       <c r="N126" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O126" t="s">
         <v>0</v>
       </c>
-      <c r="P126" s="1">
-        <v>1500000</v>
-      </c>
-      <c r="Q126" t="s">
-        <v>12</v>
+      <c r="P126" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>2722487090</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127">
-        <v>55104019</v>
+        <v>60154802</v>
       </c>
       <c r="B127" s="2">
-        <v>46004.469606481478</v>
+        <v>46100.305405092593</v>
       </c>
       <c r="C127">
-        <v>56566265</v>
+        <v>60613032</v>
       </c>
       <c r="D127" s="2">
-        <v>46034.582673611112</v>
+        <v>46108.555520833332</v>
       </c>
       <c r="E127" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F127" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="G127">
-        <v>504033918</v>
+        <v>707225975</v>
       </c>
       <c r="H127" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I127" t="s">
         <v>0</v>
       </c>
       <c r="J127" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K127" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L127" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M127" t="s">
         <v>3</v>
       </c>
       <c r="N127" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O127" t="s">
         <v>0</v>
       </c>
-      <c r="P127" s="1">
-        <v>4000000</v>
-      </c>
-      <c r="Q127" t="s">
-        <v>73</v>
+      <c r="P127" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>2722520140</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128">
-        <v>54992969</v>
+        <v>60190035</v>
       </c>
       <c r="B128" s="2">
-        <v>46002.631724537037</v>
+        <v>46100.619201388887</v>
       </c>
       <c r="C128">
-        <v>56675990</v>
+        <v>60600359</v>
       </c>
       <c r="D128" s="2">
-        <v>46036.52447916667</v>
+        <v>46108.456620370373</v>
       </c>
       <c r="E128" t="s">
-        <v>26</v>
+        <v>296</v>
       </c>
       <c r="F128" t="s">
-        <v>93</v>
+        <v>269</v>
       </c>
       <c r="G128">
-        <v>2723535999</v>
+        <v>708142290</v>
       </c>
       <c r="H128" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="I128" t="s">
         <v>0</v>
@@ -8095,7 +8107,7 @@
         <v>85</v>
       </c>
       <c r="K128" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L128" t="s">
         <v>2</v>
@@ -8103,40 +8115,43 @@
       <c r="M128" t="s">
         <v>3</v>
       </c>
+      <c r="N128" t="s">
+        <v>196</v>
+      </c>
       <c r="O128" t="s">
         <v>0</v>
       </c>
       <c r="P128" t="s">
         <v>0</v>
       </c>
-      <c r="Q128">
-        <v>2723489320</v>
+      <c r="Q128" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129">
-        <v>54973689</v>
+        <v>60356605</v>
       </c>
       <c r="B129" s="2">
-        <v>46002.496215277781</v>
+        <v>46104.623726851853</v>
       </c>
       <c r="C129">
-        <v>60458793</v>
+        <v>60604386</v>
       </c>
       <c r="D129" s="2">
-        <v>46106.421805555554</v>
+        <v>46108.484166666669</v>
       </c>
       <c r="E129" t="s">
-        <v>20</v>
+        <v>296</v>
       </c>
       <c r="F129" t="s">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="G129">
-        <v>789916125</v>
+        <v>504001081</v>
       </c>
       <c r="H129" t="s">
-        <v>91</v>
+        <v>271</v>
       </c>
       <c r="I129" t="s">
         <v>0</v>
@@ -8154,201 +8169,201 @@
         <v>3</v>
       </c>
       <c r="N129" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O129" t="s">
         <v>0</v>
       </c>
-      <c r="P129">
-        <v>0</v>
+      <c r="P129" t="s">
+        <v>272</v>
       </c>
       <c r="Q129" t="s">
-        <v>37</v>
+        <v>166</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130">
-        <v>54970719</v>
+        <v>60358121</v>
       </c>
       <c r="B130" s="2">
-        <v>46002.47859953704</v>
+        <v>46104.633344907408</v>
       </c>
       <c r="C130">
-        <v>56201571</v>
+        <v>60603382</v>
       </c>
       <c r="D130" s="2">
-        <v>46027.649004629631</v>
+        <v>46108.477407407408</v>
       </c>
       <c r="E130" t="s">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="F130" t="s">
-        <v>99</v>
+        <v>270</v>
       </c>
       <c r="G130">
-        <v>504033918</v>
+        <v>504001081</v>
       </c>
       <c r="H130" t="s">
-        <v>100</v>
-      </c>
-      <c r="I130">
-        <v>2843545</v>
+        <v>273</v>
+      </c>
+      <c r="I130" t="s">
+        <v>0</v>
       </c>
       <c r="J130" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K130" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L130" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M130" t="s">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="N130" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O130" t="s">
         <v>0</v>
       </c>
       <c r="P130" s="1">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="Q130" t="s">
-        <v>101</v>
+        <v>297</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131">
-        <v>54967903</v>
+        <v>60395491</v>
       </c>
       <c r="B131" s="2">
-        <v>46002.459837962961</v>
+        <v>46105.449062500003</v>
       </c>
       <c r="C131">
-        <v>59197300</v>
+        <v>60600791</v>
       </c>
       <c r="D131" s="2">
-        <v>46083.390844907408</v>
+        <v>46108.460127314815</v>
       </c>
       <c r="E131" t="s">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c r="F131" t="s">
-        <v>99</v>
+        <v>274</v>
       </c>
       <c r="G131">
-        <v>504033918</v>
+        <v>767747841</v>
       </c>
       <c r="H131" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="I131">
-        <v>1814616</v>
+        <v>0</v>
       </c>
       <c r="J131" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K131" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L131" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M131" t="s">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="N131" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O131" t="s">
         <v>0</v>
       </c>
-      <c r="P131" s="1">
-        <v>1000000</v>
+      <c r="P131" t="s">
+        <v>0</v>
       </c>
       <c r="Q131" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132">
-        <v>54793554</v>
+        <v>60399905</v>
       </c>
       <c r="B132" s="2">
-        <v>45999.637916666667</v>
+        <v>46105.484120370369</v>
       </c>
       <c r="C132">
-        <v>59895786</v>
+        <v>60603082</v>
       </c>
       <c r="D132" s="2">
-        <v>46094.6953125</v>
+        <v>46108.474965277775</v>
       </c>
       <c r="E132" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="F132" t="s">
-        <v>71</v>
+        <v>275</v>
       </c>
       <c r="G132">
-        <v>757323203</v>
+        <v>504001081</v>
       </c>
       <c r="H132" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I132" t="s">
         <v>0</v>
       </c>
       <c r="J132" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K132" t="s">
         <v>5</v>
       </c>
       <c r="L132" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M132" t="s">
         <v>3</v>
       </c>
       <c r="N132" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O132" t="s">
         <v>0</v>
       </c>
-      <c r="P132" t="s">
-        <v>0</v>
+      <c r="P132" s="1">
+        <v>1000000</v>
       </c>
       <c r="Q132" t="s">
-        <v>181</v>
+        <v>41</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133">
-        <v>54449048</v>
+        <v>60410207</v>
       </c>
       <c r="B133" s="2">
-        <v>45992.706157407411</v>
+        <v>46105.573414351849</v>
       </c>
       <c r="C133">
-        <v>56341749</v>
+        <v>60520322</v>
       </c>
       <c r="D133" s="2">
-        <v>46029.685115740744</v>
+        <v>46107.405590277776</v>
       </c>
       <c r="E133" t="s">
-        <v>10</v>
+        <v>188</v>
       </c>
       <c r="F133" t="s">
-        <v>42</v>
+        <v>277</v>
       </c>
       <c r="G133">
-        <v>708086759</v>
+        <v>709254356</v>
       </c>
       <c r="H133" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="I133" t="s">
         <v>0</v>
@@ -8363,98 +8378,98 @@
         <v>8</v>
       </c>
       <c r="M133" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N133" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O133" t="s">
         <v>0</v>
       </c>
-      <c r="P133" t="s">
-        <v>0</v>
+      <c r="P133" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q133" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134">
-        <v>54178346</v>
+        <v>60416636</v>
       </c>
       <c r="B134" s="2">
-        <v>45987.646099537036</v>
+        <v>46105.623402777775</v>
       </c>
       <c r="C134">
-        <v>59755436</v>
+        <v>60519385</v>
       </c>
       <c r="D134" s="2">
-        <v>46092.631111111114</v>
+        <v>46107.397152777776</v>
       </c>
       <c r="E134" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="F134" t="s">
-        <v>71</v>
+        <v>278</v>
       </c>
       <c r="G134">
-        <v>757323203</v>
+        <v>172818143</v>
       </c>
       <c r="H134" t="s">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="I134" t="s">
         <v>0</v>
       </c>
       <c r="J134" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
       </c>
       <c r="L134" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M134" t="s">
         <v>3</v>
       </c>
       <c r="N134" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O134" t="s">
         <v>0</v>
       </c>
-      <c r="P134" t="s">
-        <v>0</v>
+      <c r="P134" s="1">
+        <v>500000</v>
       </c>
       <c r="Q134" t="s">
-        <v>98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A135">
-        <v>53899369</v>
+        <v>60422373</v>
       </c>
       <c r="B135" s="2">
-        <v>45981.827430555553</v>
+        <v>46105.667442129627</v>
       </c>
       <c r="C135">
-        <v>55146678</v>
+        <v>60616433</v>
       </c>
       <c r="D135" s="2">
-        <v>46005.762916666667</v>
+        <v>46108.587754629632</v>
       </c>
       <c r="E135" t="s">
-        <v>10</v>
+        <v>283</v>
       </c>
       <c r="F135" t="s">
-        <v>32</v>
+        <v>279</v>
       </c>
       <c r="G135">
-        <v>707003126</v>
+        <v>787670708</v>
       </c>
       <c r="H135" t="s">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c r="I135" t="s">
         <v>0</v>
@@ -8469,210 +8484,210 @@
         <v>6</v>
       </c>
       <c r="M135" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="N135" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O135" t="s">
         <v>0</v>
       </c>
-      <c r="P135">
-        <v>0</v>
+      <c r="P135" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q135" t="s">
-        <v>37</v>
+        <v>297</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A136">
-        <v>53790357</v>
+        <v>60423011</v>
       </c>
       <c r="B136" s="2">
-        <v>45980.438298611109</v>
+        <v>46105.672754629632</v>
       </c>
       <c r="C136">
-        <v>60457171</v>
+        <v>60616386</v>
       </c>
       <c r="D136" s="2">
-        <v>46106.402766203704</v>
+        <v>46108.587326388886</v>
       </c>
       <c r="E136" t="s">
-        <v>10</v>
+        <v>283</v>
       </c>
       <c r="F136" t="s">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="G136">
-        <v>708336404</v>
+        <v>787670708</v>
       </c>
       <c r="H136" t="s">
-        <v>78</v>
+        <v>280</v>
       </c>
       <c r="I136" t="s">
         <v>0</v>
       </c>
       <c r="J136" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K136" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L136" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M136" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="N136" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O136" t="s">
         <v>0</v>
       </c>
       <c r="P136" s="1">
-        <v>4430307</v>
+        <v>293000</v>
       </c>
       <c r="Q136" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A137">
-        <v>53749839</v>
+        <v>60458135</v>
       </c>
       <c r="B137" s="2">
-        <v>45979.600694444445</v>
+        <v>46106.415694444448</v>
       </c>
       <c r="C137">
-        <v>57266013</v>
+        <v>60458178</v>
       </c>
       <c r="D137" s="2">
-        <v>46048.492129629631</v>
+        <v>46106.415902777779</v>
       </c>
       <c r="E137" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="F137" t="s">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="G137">
-        <v>703333988</v>
+        <v>708086472</v>
       </c>
       <c r="H137" t="s">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="I137" t="s">
         <v>0</v>
       </c>
       <c r="J137" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K137" t="s">
         <v>5</v>
       </c>
       <c r="L137" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M137" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N137" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O137" t="s">
         <v>0</v>
       </c>
-      <c r="P137" s="1">
-        <v>10000000</v>
+      <c r="P137" t="s">
+        <v>0</v>
       </c>
       <c r="Q137" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A138">
-        <v>53702282</v>
+        <v>60458148</v>
       </c>
       <c r="B138" s="2">
-        <v>45978.671550925923</v>
+        <v>46106.41574074074</v>
       </c>
       <c r="C138">
-        <v>54614316</v>
+        <v>60458184</v>
       </c>
       <c r="D138" s="2">
-        <v>45995.632673611108</v>
+        <v>46106.415960648148</v>
       </c>
       <c r="E138" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="F138" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="G138">
-        <v>778036533</v>
+        <v>708086472</v>
       </c>
       <c r="H138" t="s">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="I138" t="s">
         <v>0</v>
       </c>
       <c r="J138" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K138" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L138" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M138" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N138" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O138" t="s">
         <v>0</v>
       </c>
-      <c r="P138" t="s">
-        <v>0</v>
+      <c r="P138" s="1">
+        <v>580000</v>
       </c>
       <c r="Q138" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A139">
-        <v>52808171</v>
+        <v>60461761</v>
       </c>
       <c r="B139" s="2">
-        <v>45960.452361111114</v>
+        <v>46106.442974537036</v>
       </c>
       <c r="C139">
-        <v>59829408</v>
+        <v>60461814</v>
       </c>
       <c r="D139" s="2">
-        <v>46093.677152777775</v>
+        <v>46106.443206018521</v>
       </c>
       <c r="E139" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="F139" t="s">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="G139">
-        <v>709738605</v>
+        <v>708086472</v>
       </c>
       <c r="H139" t="s">
-        <v>76</v>
-      </c>
-      <c r="I139">
-        <v>2793645</v>
+        <v>107</v>
+      </c>
+      <c r="I139" t="s">
+        <v>0</v>
       </c>
       <c r="J139" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K139" t="s">
         <v>5</v>
@@ -8684,7 +8699,7 @@
         <v>7</v>
       </c>
       <c r="N139" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O139" t="s">
         <v>0</v>
@@ -8693,39 +8708,39 @@
         <v>0</v>
       </c>
       <c r="Q139" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A140">
-        <v>52778382</v>
+        <v>60461778</v>
       </c>
       <c r="B140" s="2">
-        <v>45959.67696759259</v>
+        <v>46106.443009259259</v>
       </c>
       <c r="C140">
-        <v>55073470</v>
+        <v>60461820</v>
       </c>
       <c r="D140" s="2">
-        <v>46003.678194444445</v>
+        <v>46106.443240740744</v>
       </c>
       <c r="E140" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="F140" t="s">
-        <v>45</v>
+        <v>167</v>
       </c>
       <c r="G140">
-        <v>708086759</v>
+        <v>708086472</v>
       </c>
       <c r="H140" t="s">
-        <v>72</v>
-      </c>
-      <c r="I140">
-        <v>2788625</v>
+        <v>107</v>
+      </c>
+      <c r="I140" t="s">
+        <v>0</v>
       </c>
       <c r="J140" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K140" t="s">
         <v>5</v>
@@ -8734,116 +8749,116 @@
         <v>8</v>
       </c>
       <c r="M140" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N140" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O140" t="s">
         <v>0</v>
       </c>
-      <c r="P140" t="s">
-        <v>0</v>
+      <c r="P140" s="1">
+        <v>780000</v>
       </c>
       <c r="Q140" t="s">
-        <v>35</v>
+        <v>300</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A141">
-        <v>52691553</v>
+        <v>60463210</v>
       </c>
       <c r="B141" s="2">
-        <v>45958.456122685187</v>
+        <v>46106.455092592594</v>
       </c>
       <c r="C141">
-        <v>59242377</v>
+        <v>60463244</v>
       </c>
       <c r="D141" s="2">
-        <v>46083.722071759257</v>
+        <v>46106.455324074072</v>
       </c>
       <c r="E141" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="F141" t="s">
-        <v>68</v>
+        <v>167</v>
       </c>
       <c r="G141">
-        <v>708473548</v>
+        <v>708086472</v>
       </c>
       <c r="H141" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="I141" t="s">
         <v>0</v>
       </c>
       <c r="J141" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K141" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L141" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M141" t="s">
         <v>7</v>
       </c>
       <c r="N141" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O141" t="s">
         <v>0</v>
       </c>
-      <c r="P141" s="1">
-        <v>1000000</v>
+      <c r="P141">
+        <v>0</v>
       </c>
       <c r="Q141" t="s">
-        <v>75</v>
+        <v>178</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A142">
-        <v>52561777</v>
+        <v>60472385</v>
       </c>
       <c r="B142" s="2">
-        <v>45954.649918981479</v>
+        <v>46106.535451388889</v>
       </c>
       <c r="C142">
-        <v>60344171</v>
+        <v>60601451</v>
       </c>
       <c r="D142" s="2">
-        <v>46104.526550925926</v>
+        <v>46108.464375000003</v>
       </c>
       <c r="E142" t="s">
-        <v>10</v>
+        <v>296</v>
       </c>
       <c r="F142" t="s">
-        <v>65</v>
+        <v>281</v>
       </c>
       <c r="G142">
-        <v>708086759</v>
+        <v>504001081</v>
       </c>
       <c r="H142" t="s">
-        <v>66</v>
+        <v>282</v>
       </c>
       <c r="I142" t="s">
         <v>0</v>
       </c>
       <c r="J142" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K142" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L142" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M142" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N142" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O142" t="s">
         <v>0</v>
@@ -8852,51 +8867,51 @@
         <v>0</v>
       </c>
       <c r="Q142" t="s">
-        <v>12</v>
+        <v>166</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A143">
-        <v>52448985</v>
+        <v>60486510</v>
       </c>
       <c r="B143" s="2">
-        <v>45952.656354166669</v>
+        <v>46106.647210648145</v>
       </c>
       <c r="C143">
-        <v>60421537</v>
+        <v>60601070</v>
       </c>
       <c r="D143" s="2">
-        <v>46105.662175925929</v>
+        <v>46108.461956018517</v>
       </c>
       <c r="E143" t="s">
-        <v>21</v>
+        <v>296</v>
       </c>
       <c r="F143" t="s">
-        <v>46</v>
+        <v>301</v>
       </c>
       <c r="G143">
-        <v>708086759</v>
+        <v>710060780</v>
       </c>
       <c r="H143" t="s">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="I143" t="s">
         <v>0</v>
       </c>
       <c r="J143" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K143" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L143" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M143" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N143" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O143" t="s">
         <v>0</v>
@@ -8905,104 +8920,104 @@
         <v>0</v>
       </c>
       <c r="Q143" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A144">
-        <v>51760632</v>
+        <v>60573620</v>
       </c>
       <c r="B144" s="2">
-        <v>45938.521469907406</v>
+        <v>46107.848483796297</v>
       </c>
       <c r="C144">
-        <v>59332667</v>
+        <v>60590960</v>
       </c>
       <c r="D144" s="2">
-        <v>46085.453263888892</v>
+        <v>46108.386261574073</v>
       </c>
       <c r="E144" t="s">
-        <v>129</v>
+        <v>304</v>
       </c>
       <c r="F144" t="s">
-        <v>36</v>
+        <v>302</v>
       </c>
       <c r="G144">
-        <v>556999292</v>
+        <v>575750228</v>
       </c>
       <c r="H144" t="s">
-        <v>97</v>
+        <v>303</v>
       </c>
       <c r="I144" t="s">
         <v>0</v>
       </c>
       <c r="J144" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K144" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L144" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M144" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="N144" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O144" t="s">
         <v>0</v>
       </c>
-      <c r="P144" t="s">
-        <v>0</v>
+      <c r="P144" s="1">
+        <v>802977</v>
       </c>
       <c r="Q144" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A145">
-        <v>48847621</v>
+        <v>60589306</v>
       </c>
       <c r="B145" s="2">
-        <v>45882.483449074076</v>
+        <v>46108.367638888885</v>
       </c>
       <c r="C145">
-        <v>60094807</v>
+        <v>60590899</v>
       </c>
       <c r="D145" s="2">
-        <v>46099.377268518518</v>
+        <v>46108.385578703703</v>
       </c>
       <c r="E145" t="s">
-        <v>16</v>
+        <v>304</v>
       </c>
       <c r="F145" t="s">
-        <v>242</v>
+        <v>305</v>
       </c>
       <c r="G145">
-        <v>749194205</v>
+        <v>707040612</v>
       </c>
       <c r="H145" t="s">
-        <v>243</v>
-      </c>
-      <c r="I145" t="s">
+        <v>306</v>
+      </c>
+      <c r="I145">
         <v>0</v>
       </c>
       <c r="J145" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K145" t="s">
-        <v>244</v>
+        <v>1</v>
       </c>
       <c r="L145" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M145" t="s">
         <v>3</v>
       </c>
       <c r="N145" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O145" t="s">
         <v>0</v>
@@ -9011,33 +9026,33 @@
         <v>0</v>
       </c>
       <c r="Q145" t="s">
-        <v>245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A146">
-        <v>44970444</v>
+        <v>60611946</v>
       </c>
       <c r="B146" s="2">
-        <v>45798.444131944445</v>
+        <v>46108.544236111113</v>
       </c>
       <c r="C146">
-        <v>57086157</v>
+        <v>60611970</v>
       </c>
       <c r="D146" s="2">
-        <v>46044.497789351852</v>
+        <v>46108.54446759259</v>
       </c>
       <c r="E146" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F146" t="s">
-        <v>95</v>
+        <v>307</v>
       </c>
       <c r="G146">
-        <v>777545168</v>
+        <v>707812141</v>
       </c>
       <c r="H146" t="s">
-        <v>96</v>
+        <v>308</v>
       </c>
       <c r="I146" t="s">
         <v>0</v>
@@ -9054,22 +9069,74 @@
       <c r="M146" t="s">
         <v>3</v>
       </c>
+      <c r="N146" t="s">
+        <v>195</v>
+      </c>
       <c r="O146" t="s">
         <v>0</v>
       </c>
       <c r="P146" t="s">
         <v>0</v>
       </c>
-      <c r="Q146">
-        <v>2723489300</v>
+      <c r="Q146" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>60612374</v>
+      </c>
+      <c r="B147" s="2">
+        <v>46108.549409722225</v>
+      </c>
+      <c r="C147">
+        <v>60612392</v>
+      </c>
+      <c r="D147" s="2">
+        <v>46108.549618055556</v>
+      </c>
+      <c r="E147" t="s">
+        <v>40</v>
+      </c>
+      <c r="F147" t="s">
+        <v>307</v>
+      </c>
+      <c r="G147">
+        <v>707812141</v>
+      </c>
+      <c r="H147" t="s">
+        <v>308</v>
+      </c>
+      <c r="I147" t="s">
+        <v>0</v>
+      </c>
+      <c r="J147" t="s">
+        <v>25</v>
+      </c>
+      <c r="K147" t="s">
+        <v>1</v>
+      </c>
+      <c r="L147" t="s">
+        <v>2</v>
+      </c>
+      <c r="M147" t="s">
+        <v>3</v>
+      </c>
+      <c r="N147" t="s">
+        <v>195</v>
+      </c>
+      <c r="O147" t="s">
+        <v>0</v>
+      </c>
+      <c r="P147" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q146" xr:uid="{6112C32D-301C-49EC-A409-207BDCA453AB}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q146">
-      <sortCondition descending="1" ref="A1:A146"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:Q147" xr:uid="{F241F63F-8CA3-4680-8FA3-BC3B4E36762D}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/Attachments/Bureau/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E29467CA-F562-427F-A28D-49B4C01DCDF7}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B7A57EB-5BF4-43F9-BED3-9CFE8EAF1C49}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="39" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="40" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$Q$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil2!$A$1:$S$137</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="299">
   <si>
     <t>-</t>
   </si>
@@ -161,9 +161,6 @@
     <t>XXXXXXX</t>
   </si>
   <si>
-    <t>BO Homologation: Saisie GAIA</t>
-  </si>
-  <si>
     <t>XXXXXXXXX</t>
   </si>
   <si>
@@ -527,18 +524,9 @@
     <t>ZENITH BANK COTE D4IVOIRE</t>
   </si>
   <si>
-    <t>STE SINOAFRICK AUTO SARL</t>
-  </si>
-  <si>
-    <t>COCODY RIVIERA 2</t>
-  </si>
-  <si>
     <t>DIRECTION GENERALE DES DOUANES</t>
   </si>
   <si>
-    <t>GREENWAYS TRANSIT SITE PORT BOUET VRIDI ZONE DIGUE</t>
-  </si>
-  <si>
     <t>XXXXXXXXXXXXX</t>
   </si>
   <si>
@@ -599,27 +587,15 @@
     <t>BUVPN260022</t>
   </si>
   <si>
-    <t>BASE AERIENN KORHOGO</t>
-  </si>
-  <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>Prestataire : Etude</t>
   </si>
   <si>
     <t>BGFI SERVICE SIMAO</t>
   </si>
   <si>
-    <t>COCODY VALON</t>
-  </si>
-  <si>
     <t>MARCORY</t>
   </si>
   <si>
-    <t>TROPICALE TRANSIT SITE TREICHVILLE IMMEUBLE EN FACR DE SOGELUX</t>
-  </si>
-  <si>
     <t>HANNYYAH TRANSIT SITE TREICHVILLE VERS NOTRE DAME</t>
   </si>
   <si>
@@ -740,9 +716,6 @@
     <t>DIA 20Mbps Ext A : PoP ICA REPUBLIQUE Ext B : 7,avenue Nogues,Immeuble BSIC,5eme et Abidjan 01 BP 5754 7 AV.Nogues 8X8J+QX Abidjan, COTE D IVOIRE</t>
   </si>
   <si>
-    <t>SYTHD260075</t>
-  </si>
-  <si>
     <t>Manager Trafic et Projets : Affectation responsable projet</t>
   </si>
   <si>
@@ -764,9 +737,6 @@
     <t>SYTHD260018</t>
   </si>
   <si>
-    <t>BUVPN260055</t>
-  </si>
-  <si>
     <t>BUVPN260056</t>
   </si>
   <si>
@@ -797,30 +767,18 @@
     <t>SECO FERKE</t>
   </si>
   <si>
-    <t>IFM</t>
-  </si>
-  <si>
     <t>SECO TREICHVILLE (BACKUP DU SYTHD230357 )</t>
   </si>
   <si>
     <t>SECO TREICHVILLE</t>
   </si>
   <si>
-    <t>STE DGTCP</t>
-  </si>
-  <si>
-    <t>PLATEAU EN FACE DU PALAIS DE JUSTICE</t>
-  </si>
-  <si>
     <t>MAXAM CI</t>
   </si>
   <si>
     <t>BUVPN250061</t>
   </si>
   <si>
-    <t>SOCIETE GEZA EXPERTISE</t>
-  </si>
-  <si>
     <t>EXT A: DC Nsia Vallons EXT B: DC NSIA MAINONE AU VITB 2Gbps backhaul</t>
   </si>
   <si>
@@ -830,24 +788,15 @@
     <t>SYTHD260081</t>
   </si>
   <si>
-    <t>BUVPN260063</t>
-  </si>
-  <si>
     <t>DIMBOKRO//VOIE INCONNUE/DIMBOKRO</t>
   </si>
   <si>
     <t>BUVPN260060</t>
   </si>
   <si>
-    <t>BUVPN260062</t>
-  </si>
-  <si>
     <t>DIAWALA//VOIE INCONNUE/SECO DIAWALA 05 06 72 72 87</t>
   </si>
   <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/M.ME SARA LOBOGNON</t>
-  </si>
-  <si>
     <t>INSTITUT CARDIOLOGIE BOUAKE</t>
   </si>
   <si>
@@ -878,12 +827,6 @@
     <t>PROJET POLE AGRO INDUSTRIEL DANS LE NORD</t>
   </si>
   <si>
-    <t>DEMANDE INTERNE PROJET FESTIVAL YAKRO YÔFÊ 9</t>
-  </si>
-  <si>
-    <t>YAMOUSSOUKRO/ STADE CKB YAKRO</t>
-  </si>
-  <si>
     <t>YESHI GROUPE COTE D'IVOIRE</t>
   </si>
   <si>
@@ -899,27 +842,12 @@
     <t>SYTHD260072</t>
   </si>
   <si>
-    <t>KORHOGO//VOIE INCONNUE/BASE AERIENN KORHOGO</t>
-  </si>
-  <si>
-    <t>BO Homologation: Saisie BSCS</t>
-  </si>
-  <si>
-    <t>Responsable Zone: Validation intervention</t>
-  </si>
-  <si>
     <t>DJIGUI SHIPPING SITE TREICHVILLE CHU</t>
   </si>
   <si>
-    <t>BUVPN260057</t>
-  </si>
-  <si>
     <t>BUVPN260061</t>
   </si>
   <si>
-    <t>BUVPN260066</t>
-  </si>
-  <si>
     <t>xxxxxx</t>
   </si>
   <si>
@@ -935,12 +863,6 @@
     <t>XXXXXXXXXXXXXXX</t>
   </si>
   <si>
-    <t>SYTHD260085</t>
-  </si>
-  <si>
-    <t>SYTHD260080</t>
-  </si>
-  <si>
     <t>XXXXXXXXXXXXXXXXX</t>
   </si>
   <si>
@@ -953,9 +875,6 @@
     <t>PORT BOUET RADUISON BLU</t>
   </si>
   <si>
-    <t>IP Delivery: Validation information</t>
-  </si>
-  <si>
     <t>SOCIETE DE MECANIQUE GENERALE</t>
   </si>
   <si>
@@ -966,6 +885,57 @@
   </si>
   <si>
     <t>PLATEAU IMMEUBLE DJEKANOU</t>
+  </si>
+  <si>
+    <t>SYTHD260087</t>
+  </si>
+  <si>
+    <t>Saisie ASCOM</t>
+  </si>
+  <si>
+    <t>Technicien zone: Intervention</t>
+  </si>
+  <si>
+    <t>Realisation Ctrl Conformite</t>
+  </si>
+  <si>
+    <t>Support IP: Correction</t>
+  </si>
+  <si>
+    <t>BUVPN260069</t>
+  </si>
+  <si>
+    <t>AGENCE OCI 2PLTX ENA</t>
+  </si>
+  <si>
+    <t>DALOA//VOIE INCONNUE/DALOA</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>BUVPN260068</t>
+  </si>
+  <si>
+    <t>EUROFIND PARTICIPATION</t>
+  </si>
+  <si>
+    <t>Support IP: Config Eq Acces</t>
+  </si>
+  <si>
+    <t>xxx</t>
+  </si>
+  <si>
+    <t>ECOTI SA</t>
+  </si>
+  <si>
+    <t>YOPOUGON</t>
+  </si>
+  <si>
+    <t>CREDAF GROUP</t>
+  </si>
+  <si>
+    <t>MARCORY ZONE 4</t>
   </si>
 </sst>
 </file>
@@ -1349,87 +1319,87 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F241F63F-8CA3-4680-8FA3-BC3B4E36762D}">
-  <dimension ref="A1:Q147"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C722EAFD-41F1-49B4-A0A6-ACE76096AA41}">
+  <dimension ref="A1:Q137"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>56</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>57</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>58</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>59</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>60</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
+        <v>186</v>
+      </c>
+      <c r="O1" t="s">
         <v>61</v>
       </c>
-      <c r="N1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>62</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>63</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>44970444</v>
+        <v>60760104</v>
       </c>
       <c r="B2" s="2">
-        <v>45798.444131944445</v>
+        <v>46111.598865740743</v>
       </c>
       <c r="C2">
-        <v>57086157</v>
+        <v>60800769</v>
       </c>
       <c r="D2" s="2">
-        <v>46044.497789351852</v>
+        <v>46112.401261574072</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="F2" t="s">
-        <v>93</v>
+        <v>297</v>
       </c>
       <c r="G2">
-        <v>777545168</v>
+        <v>708187511</v>
       </c>
       <c r="H2" t="s">
-        <v>94</v>
+        <v>298</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
@@ -1446,40 +1416,43 @@
       <c r="M2" t="s">
         <v>3</v>
       </c>
+      <c r="N2" t="s">
+        <v>188</v>
+      </c>
       <c r="O2" t="s">
         <v>0</v>
       </c>
-      <c r="P2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>2723489300</v>
+      <c r="P2" s="1">
+        <v>150000</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>48847621</v>
+        <v>60748674</v>
       </c>
       <c r="B3" s="2">
-        <v>45882.483449074076</v>
+        <v>46111.511504629627</v>
       </c>
       <c r="C3">
-        <v>60094807</v>
+        <v>60748765</v>
       </c>
       <c r="D3" s="2">
-        <v>46099.377268518518</v>
+        <v>46111.511828703704</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="F3" t="s">
-        <v>237</v>
+        <v>295</v>
       </c>
       <c r="G3">
-        <v>749194205</v>
+        <v>767791237</v>
       </c>
       <c r="H3" t="s">
-        <v>238</v>
+        <v>296</v>
       </c>
       <c r="I3" t="s">
         <v>0</v>
@@ -1488,69 +1461,69 @@
         <v>13</v>
       </c>
       <c r="K3" t="s">
-        <v>239</v>
+        <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O3" t="s">
         <v>0</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3" t="s">
-        <v>240</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>51760632</v>
+        <v>60612374</v>
       </c>
       <c r="B4" s="2">
-        <v>45938.521469907406</v>
+        <v>46108.549409722225</v>
       </c>
       <c r="C4">
-        <v>59332667</v>
+        <v>60832789</v>
       </c>
       <c r="D4" s="2">
-        <v>46085.453263888892</v>
+        <v>46112.642962962964</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>280</v>
       </c>
       <c r="G4">
-        <v>556999292</v>
+        <v>707812141</v>
       </c>
       <c r="H4" t="s">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="I4" t="s">
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N4" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O4" t="s">
         <v>0</v>
@@ -1559,51 +1532,51 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>52448985</v>
+        <v>60611946</v>
       </c>
       <c r="B5" s="2">
-        <v>45952.656354166669</v>
+        <v>46108.544236111113</v>
       </c>
       <c r="C5">
-        <v>60421537</v>
+        <v>60836344</v>
       </c>
       <c r="D5" s="2">
-        <v>46105.662175925929</v>
+        <v>46112.669745370367</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>280</v>
       </c>
       <c r="G5">
-        <v>708086759</v>
+        <v>707812141</v>
       </c>
       <c r="H5" t="s">
-        <v>47</v>
+        <v>281</v>
       </c>
       <c r="I5" t="s">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N5" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O5" t="s">
         <v>0</v>
@@ -1612,51 +1585,51 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>15</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>52561777</v>
+        <v>60589306</v>
       </c>
       <c r="B6" s="2">
-        <v>45954.649918981479</v>
+        <v>46108.367638888885</v>
       </c>
       <c r="C6">
-        <v>60344171</v>
+        <v>60811477</v>
       </c>
       <c r="D6" s="2">
-        <v>46104.526550925926</v>
+        <v>46112.481712962966</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>278</v>
       </c>
       <c r="G6">
-        <v>708086759</v>
+        <v>707040612</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>279</v>
       </c>
       <c r="I6" t="s">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N6" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O6" t="s">
         <v>0</v>
@@ -1665,33 +1638,33 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>52691553</v>
+        <v>60573620</v>
       </c>
       <c r="B7" s="2">
-        <v>45958.456122685187</v>
+        <v>46107.848483796297</v>
       </c>
       <c r="C7">
-        <v>59242377</v>
+        <v>60573635</v>
       </c>
       <c r="D7" s="2">
-        <v>46083.722071759257</v>
+        <v>46107.848703703705</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>276</v>
       </c>
       <c r="G7">
-        <v>708473548</v>
+        <v>575750228</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>277</v>
       </c>
       <c r="I7" t="s">
         <v>0</v>
@@ -1700,122 +1673,122 @@
         <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L7" t="s">
         <v>6</v>
       </c>
       <c r="M7" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="N7" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O7" t="s">
         <v>0</v>
       </c>
       <c r="P7" s="1">
-        <v>1000000</v>
+        <v>802977</v>
       </c>
       <c r="Q7" t="s">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>52778382</v>
+        <v>60486510</v>
       </c>
       <c r="B8" s="2">
-        <v>45959.67696759259</v>
+        <v>46106.647210648145</v>
       </c>
       <c r="C8">
-        <v>55073470</v>
+        <v>60735668</v>
       </c>
       <c r="D8" s="2">
-        <v>46003.678194444445</v>
+        <v>46111.416516203702</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>275</v>
       </c>
       <c r="G8">
-        <v>708086759</v>
+        <v>710060780</v>
       </c>
       <c r="H8" t="s">
+        <v>184</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>2</v>
+      </c>
+      <c r="M8" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" t="s">
+        <v>188</v>
+      </c>
+      <c r="O8" t="s">
+        <v>0</v>
+      </c>
+      <c r="P8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="s">
         <v>72</v>
-      </c>
-      <c r="I8">
-        <v>2788625</v>
-      </c>
-      <c r="J8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N8" t="s">
-        <v>196</v>
-      </c>
-      <c r="O8" t="s">
-        <v>0</v>
-      </c>
-      <c r="P8" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>52808171</v>
+        <v>60472385</v>
       </c>
       <c r="B9" s="2">
-        <v>45960.452361111114</v>
+        <v>46106.535451388889</v>
       </c>
       <c r="C9">
-        <v>59829408</v>
+        <v>60799241</v>
       </c>
       <c r="D9" s="2">
-        <v>46093.677152777775</v>
+        <v>46112.384131944447</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="G9">
-        <v>709738605</v>
+        <v>504001081</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9">
-        <v>2793645</v>
+        <v>263</v>
+      </c>
+      <c r="I9" t="s">
+        <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M9" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N9" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O9" t="s">
         <v>0</v>
@@ -1824,251 +1797,251 @@
         <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>77</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>53702282</v>
+        <v>60463210</v>
       </c>
       <c r="B10" s="2">
-        <v>45978.671550925923</v>
+        <v>46106.455092592594</v>
       </c>
       <c r="C10">
-        <v>54614316</v>
+        <v>60749996</v>
       </c>
       <c r="D10" s="2">
-        <v>45995.632673611108</v>
+        <v>46111.519606481481</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>163</v>
       </c>
       <c r="G10">
-        <v>778036533</v>
+        <v>708086472</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M10" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N10" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="O10" t="s">
         <v>0</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>53749839</v>
+        <v>60461778</v>
       </c>
       <c r="B11" s="2">
-        <v>45979.600694444445</v>
+        <v>46106.443009259259</v>
       </c>
       <c r="C11">
-        <v>57266013</v>
+        <v>60769067</v>
       </c>
       <c r="D11" s="2">
-        <v>46048.492129629631</v>
+        <v>46111.661840277775</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="G11">
-        <v>703333988</v>
+        <v>708086472</v>
       </c>
       <c r="H11" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="I11" t="s">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M11" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N11" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O11" t="s">
         <v>0</v>
       </c>
       <c r="P11" s="1">
-        <v>10000000</v>
+        <v>780000</v>
       </c>
       <c r="Q11" t="s">
-        <v>12</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>53790357</v>
+        <v>60461761</v>
       </c>
       <c r="B12" s="2">
-        <v>45980.438298611109</v>
+        <v>46106.442974537036</v>
       </c>
       <c r="C12">
-        <v>60457171</v>
+        <v>60771687</v>
       </c>
       <c r="D12" s="2">
-        <v>46106.402766203704</v>
+        <v>46111.678715277776</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="G12">
-        <v>708336404</v>
+        <v>708086472</v>
       </c>
       <c r="H12" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="I12" t="s">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M12" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N12" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O12" t="s">
         <v>0</v>
       </c>
-      <c r="P12" s="1">
-        <v>4430307</v>
+      <c r="P12" t="s">
+        <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>39</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>53899369</v>
+        <v>60458148</v>
       </c>
       <c r="B13" s="2">
-        <v>45981.827430555553</v>
+        <v>46106.41574074074</v>
       </c>
       <c r="C13">
-        <v>55146678</v>
+        <v>60800389</v>
       </c>
       <c r="D13" s="2">
-        <v>46005.762916666667</v>
+        <v>46112.397928240738</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="G13">
-        <v>707003126</v>
+        <v>708086472</v>
       </c>
       <c r="H13" t="s">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="I13" t="s">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M13" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N13" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O13" t="s">
         <v>0</v>
       </c>
-      <c r="P13">
-        <v>0</v>
+      <c r="P13" s="1">
+        <v>580000</v>
       </c>
       <c r="Q13" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>54178346</v>
+        <v>60458135</v>
       </c>
       <c r="B14" s="2">
-        <v>45987.646099537036</v>
+        <v>46106.415694444448</v>
       </c>
       <c r="C14">
-        <v>59755436</v>
+        <v>60799562</v>
       </c>
       <c r="D14" s="2">
-        <v>46092.631111111114</v>
+        <v>46112.388206018521</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>71</v>
+        <v>163</v>
       </c>
       <c r="G14">
-        <v>757323203</v>
+        <v>708086472</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>226</v>
       </c>
       <c r="I14" t="s">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -2077,10 +2050,10 @@
         <v>8</v>
       </c>
       <c r="M14" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N14" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O14" t="s">
         <v>0</v>
@@ -2089,92 +2062,92 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>96</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>54449048</v>
+        <v>60416636</v>
       </c>
       <c r="B15" s="2">
-        <v>45992.706157407411</v>
+        <v>46105.623402777775</v>
       </c>
       <c r="C15">
-        <v>56341749</v>
+        <v>60758513</v>
       </c>
       <c r="D15" s="2">
-        <v>46029.685115740744</v>
+        <v>46111.586331018516</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>272</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>261</v>
       </c>
       <c r="G15">
-        <v>708086759</v>
+        <v>172818143</v>
       </c>
       <c r="H15" t="s">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="I15" t="s">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M15" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N15" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O15" t="s">
         <v>0</v>
       </c>
-      <c r="P15" t="s">
-        <v>0</v>
+      <c r="P15" s="1">
+        <v>500000</v>
       </c>
       <c r="Q15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>54793554</v>
+        <v>60410207</v>
       </c>
       <c r="B16" s="2">
-        <v>45999.637916666667</v>
+        <v>46105.573414351849</v>
       </c>
       <c r="C16">
-        <v>59895786</v>
+        <v>60758829</v>
       </c>
       <c r="D16" s="2">
-        <v>46094.6953125</v>
+        <v>46111.589050925926</v>
       </c>
       <c r="E16" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>260</v>
       </c>
       <c r="G16">
-        <v>757323203</v>
+        <v>709254356</v>
       </c>
       <c r="H16" t="s">
-        <v>260</v>
+        <v>102</v>
       </c>
       <c r="I16" t="s">
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -2186,60 +2159,60 @@
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O16" t="s">
         <v>0</v>
       </c>
-      <c r="P16" t="s">
-        <v>0</v>
+      <c r="P16" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q16" t="s">
-        <v>178</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>54967903</v>
+        <v>60399905</v>
       </c>
       <c r="B17" s="2">
-        <v>46002.459837962961</v>
+        <v>46105.484120370369</v>
       </c>
       <c r="C17">
-        <v>59197300</v>
+        <v>60603082</v>
       </c>
       <c r="D17" s="2">
-        <v>46083.390844907408</v>
+        <v>46108.474965277775</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="F17" t="s">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="G17">
-        <v>504033918</v>
+        <v>504001081</v>
       </c>
       <c r="H17" t="s">
-        <v>129</v>
-      </c>
-      <c r="I17">
-        <v>1814616</v>
+        <v>259</v>
+      </c>
+      <c r="I17" t="s">
+        <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
       </c>
       <c r="L17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M17" t="s">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="N17" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O17" t="s">
         <v>0</v>
@@ -2248,86 +2221,86 @@
         <v>1000000</v>
       </c>
       <c r="Q17" t="s">
-        <v>130</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>54970719</v>
+        <v>60395491</v>
       </c>
       <c r="B18" s="2">
-        <v>46002.47859953704</v>
+        <v>46105.449062500003</v>
       </c>
       <c r="C18">
-        <v>56201571</v>
+        <v>60735521</v>
       </c>
       <c r="D18" s="2">
-        <v>46027.649004629631</v>
+        <v>46111.41542824074</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>257</v>
       </c>
       <c r="G18">
-        <v>504033918</v>
+        <v>767747841</v>
       </c>
       <c r="H18" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="I18">
-        <v>2843545</v>
+        <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K18" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M18" t="s">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="N18" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O18" t="s">
         <v>0</v>
       </c>
-      <c r="P18" s="1">
-        <v>1000000</v>
+      <c r="P18" t="s">
+        <v>0</v>
       </c>
       <c r="Q18" t="s">
-        <v>99</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>54973689</v>
+        <v>60358121</v>
       </c>
       <c r="B19" s="2">
-        <v>46002.496215277781</v>
+        <v>46104.633344907408</v>
       </c>
       <c r="C19">
-        <v>60458793</v>
+        <v>60740064</v>
       </c>
       <c r="D19" s="2">
-        <v>46106.421805555554</v>
+        <v>46111.450486111113</v>
       </c>
       <c r="E19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>253</v>
       </c>
       <c r="G19">
-        <v>789916125</v>
+        <v>504001081</v>
       </c>
       <c r="H19" t="s">
-        <v>91</v>
+        <v>256</v>
       </c>
       <c r="I19" t="s">
         <v>0</v>
@@ -2345,201 +2318,201 @@
         <v>3</v>
       </c>
       <c r="N19" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O19" t="s">
         <v>0</v>
       </c>
-      <c r="P19">
-        <v>0</v>
+      <c r="P19" s="1">
+        <v>500000</v>
       </c>
       <c r="Q19" t="s">
-        <v>37</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>55104019</v>
+        <v>60356605</v>
       </c>
       <c r="B20" s="2">
-        <v>46004.469606481478</v>
+        <v>46104.623726851853</v>
       </c>
       <c r="C20">
-        <v>56566265</v>
+        <v>60604386</v>
       </c>
       <c r="D20" s="2">
-        <v>46034.582673611112</v>
+        <v>46108.484166666669</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>272</v>
       </c>
       <c r="F20" t="s">
-        <v>89</v>
+        <v>253</v>
       </c>
       <c r="G20">
-        <v>504033918</v>
+        <v>504001081</v>
       </c>
       <c r="H20" t="s">
-        <v>31</v>
+        <v>254</v>
       </c>
       <c r="I20" t="s">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M20" t="s">
         <v>3</v>
       </c>
       <c r="N20" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O20" t="s">
         <v>0</v>
       </c>
-      <c r="P20" s="1">
-        <v>4000000</v>
+      <c r="P20" t="s">
+        <v>255</v>
       </c>
       <c r="Q20" t="s">
-        <v>73</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>55105103</v>
+        <v>60190035</v>
       </c>
       <c r="B21" s="2">
-        <v>46004.481180555558</v>
+        <v>46100.619201388887</v>
       </c>
       <c r="C21">
-        <v>56940307</v>
+        <v>60735565</v>
       </c>
       <c r="D21" s="2">
-        <v>46041.803784722222</v>
+        <v>46111.41574074074</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>89</v>
+        <v>252</v>
       </c>
       <c r="G21">
-        <v>504033918</v>
+        <v>708142290</v>
       </c>
       <c r="H21" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="I21" t="s">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="K21" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M21" t="s">
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O21" t="s">
         <v>0</v>
       </c>
-      <c r="P21" s="1">
-        <v>1500000</v>
+      <c r="P21" t="s">
+        <v>0</v>
       </c>
       <c r="Q21" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>55636282</v>
+        <v>60154802</v>
       </c>
       <c r="B22" s="2">
-        <v>46014.435729166667</v>
+        <v>46100.305405092593</v>
       </c>
       <c r="C22">
-        <v>57367586</v>
+        <v>60732475</v>
       </c>
       <c r="D22" s="2">
-        <v>46049.856261574074</v>
+        <v>46111.385648148149</v>
       </c>
       <c r="E22" t="s">
-        <v>127</v>
+        <v>293</v>
       </c>
       <c r="F22" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="G22">
-        <v>759003900</v>
+        <v>707225975</v>
       </c>
       <c r="H22" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I22" t="s">
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K22" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L22" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M22" t="s">
         <v>3</v>
       </c>
       <c r="N22" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O22" t="s">
         <v>0</v>
       </c>
-      <c r="P22" s="1">
-        <v>918681</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>108</v>
+      <c r="P22" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>2722520140</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>55686160</v>
+        <v>60026486</v>
       </c>
       <c r="B23" s="2">
-        <v>46015.355868055558</v>
+        <v>46098.36173611111</v>
       </c>
       <c r="C23">
-        <v>60490199</v>
+        <v>60121930</v>
       </c>
       <c r="D23" s="2">
-        <v>46106.680219907408</v>
+        <v>46099.594039351854</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F23" t="s">
-        <v>105</v>
+        <v>234</v>
       </c>
       <c r="G23">
-        <v>777765287</v>
+        <v>506727287</v>
       </c>
       <c r="H23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I23" t="s">
         <v>0</v>
@@ -2548,51 +2521,51 @@
         <v>13</v>
       </c>
       <c r="K23" t="s">
-        <v>5</v>
+        <v>214</v>
       </c>
       <c r="L23" t="s">
         <v>6</v>
       </c>
       <c r="M23" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N23" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O23" t="s">
         <v>0</v>
       </c>
-      <c r="P23" s="1">
-        <v>850887</v>
+      <c r="P23">
+        <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>55694485</v>
+        <v>59894743</v>
       </c>
       <c r="B24" s="2">
-        <v>46015.420092592591</v>
+        <v>46094.687673611108</v>
       </c>
       <c r="C24">
-        <v>56752240</v>
+        <v>60454133</v>
       </c>
       <c r="D24" s="2">
-        <v>46037.705520833333</v>
+        <v>46106.366770833331</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>106</v>
+        <v>244</v>
       </c>
       <c r="G24">
-        <v>749338073</v>
+        <v>759668146</v>
       </c>
       <c r="H24" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="I24" t="s">
         <v>0</v>
@@ -2607,51 +2580,51 @@
         <v>6</v>
       </c>
       <c r="M24" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N24" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O24" t="s">
         <v>0</v>
       </c>
-      <c r="P24" s="1">
-        <v>638462</v>
+      <c r="P24" t="s">
+        <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>56181778</v>
+        <v>59824550</v>
       </c>
       <c r="B25" s="2">
-        <v>46027.499212962961</v>
+        <v>46093.6405787037</v>
       </c>
       <c r="C25">
-        <v>59210339</v>
+        <v>60733506</v>
       </c>
       <c r="D25" s="2">
-        <v>46083.492881944447</v>
+        <v>46111.394432870373</v>
       </c>
       <c r="E25" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>109</v>
+        <v>242</v>
       </c>
       <c r="G25">
-        <v>585990976</v>
+        <v>506727287</v>
       </c>
       <c r="H25" t="s">
-        <v>110</v>
-      </c>
-      <c r="I25">
-        <v>1765416</v>
+        <v>243</v>
+      </c>
+      <c r="I25" t="s">
+        <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
@@ -2660,316 +2633,316 @@
         <v>6</v>
       </c>
       <c r="M25" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N25" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O25" t="s">
         <v>0</v>
       </c>
-      <c r="P25" s="1">
-        <v>3000000</v>
+      <c r="P25">
+        <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>56601982</v>
+        <v>59820678</v>
       </c>
       <c r="B26" s="2">
-        <v>46035.393611111111</v>
+        <v>46093.612222222226</v>
       </c>
       <c r="C26">
-        <v>60341610</v>
+        <v>60208764</v>
       </c>
       <c r="D26" s="2">
-        <v>46104.501319444447</v>
+        <v>46100.766909722224</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>240</v>
       </c>
       <c r="G26">
-        <v>707003126</v>
+        <v>506727287</v>
       </c>
       <c r="H26" t="s">
-        <v>113</v>
+        <v>241</v>
       </c>
       <c r="I26" t="s">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K26" t="s">
-        <v>5</v>
+        <v>214</v>
       </c>
       <c r="L26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M26" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N26" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="O26" t="s">
         <v>0</v>
       </c>
-      <c r="P26" s="1">
-        <v>7103410</v>
+      <c r="P26">
+        <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>56603495</v>
+        <v>59816396</v>
       </c>
       <c r="B27" s="2">
-        <v>46035.408518518518</v>
+        <v>46093.580590277779</v>
       </c>
       <c r="C27">
-        <v>59831107</v>
+        <v>60137506</v>
       </c>
       <c r="D27" s="2">
-        <v>46093.691342592596</v>
+        <v>46099.711053240739</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>239</v>
       </c>
       <c r="G27">
-        <v>707003126</v>
+        <v>506727287</v>
       </c>
       <c r="H27" t="s">
-        <v>115</v>
-      </c>
-      <c r="I27" t="s">
-        <v>0</v>
+        <v>251</v>
+      </c>
+      <c r="I27">
+        <v>1848446</v>
       </c>
       <c r="J27" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K27" t="s">
-        <v>5</v>
+        <v>214</v>
       </c>
       <c r="L27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M27" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N27" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="O27" t="s">
         <v>0</v>
       </c>
-      <c r="P27" s="1">
-        <v>7103410</v>
+      <c r="P27">
+        <v>0</v>
       </c>
       <c r="Q27" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>56606469</v>
+        <v>59813505</v>
       </c>
       <c r="B28" s="2">
-        <v>46035.43072916667</v>
+        <v>46093.557256944441</v>
       </c>
       <c r="C28">
-        <v>60527398</v>
+        <v>60137642</v>
       </c>
       <c r="D28" s="2">
-        <v>46107.458136574074</v>
+        <v>46099.71303240741</v>
       </c>
       <c r="E28" t="s">
-        <v>283</v>
+        <v>154</v>
       </c>
       <c r="F28" t="s">
-        <v>114</v>
+        <v>237</v>
       </c>
       <c r="G28">
-        <v>504041812</v>
+        <v>706727287</v>
       </c>
       <c r="H28" t="s">
-        <v>43</v>
+        <v>238</v>
       </c>
       <c r="I28" t="s">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K28" t="s">
-        <v>5</v>
+        <v>214</v>
       </c>
       <c r="L28" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M28" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N28" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="O28" t="s">
         <v>0</v>
       </c>
-      <c r="P28" s="1">
-        <v>1000000</v>
+      <c r="P28">
+        <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>56607988</v>
+        <v>59801109</v>
       </c>
       <c r="B29" s="2">
-        <v>46035.443668981483</v>
+        <v>46093.464594907404</v>
       </c>
       <c r="C29">
-        <v>58404447</v>
+        <v>60635513</v>
       </c>
       <c r="D29" s="2">
-        <v>46069.522615740738</v>
+        <v>46108.727754629632</v>
       </c>
       <c r="E29" t="s">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s">
-        <v>114</v>
+        <v>235</v>
       </c>
       <c r="G29">
-        <v>504041812</v>
+        <v>709173657</v>
       </c>
       <c r="H29" t="s">
-        <v>116</v>
+        <v>236</v>
       </c>
       <c r="I29" t="s">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K29" t="s">
         <v>5</v>
       </c>
       <c r="L29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M29" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N29" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="O29" t="s">
         <v>0</v>
       </c>
-      <c r="P29" s="1">
-        <v>2000000</v>
+      <c r="P29">
+        <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>56609018</v>
+        <v>59793967</v>
       </c>
       <c r="B30" s="2">
-        <v>46035.452465277776</v>
+        <v>46093.406724537039</v>
       </c>
       <c r="C30">
-        <v>60165633</v>
+        <v>60225840</v>
       </c>
       <c r="D30" s="2">
-        <v>46100.43891203704</v>
+        <v>46101.328912037039</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F30" t="s">
-        <v>114</v>
+        <v>234</v>
       </c>
       <c r="G30">
-        <v>504041812</v>
+        <v>506727287</v>
       </c>
       <c r="H30" t="s">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
       </c>
       <c r="L30" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M30" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N30" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O30" t="s">
         <v>0</v>
       </c>
-      <c r="P30" s="1">
-        <v>2000000</v>
+      <c r="P30">
+        <v>0</v>
       </c>
       <c r="Q30" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>56611212</v>
+        <v>59684312</v>
       </c>
       <c r="B31" s="2">
-        <v>46035.471886574072</v>
+        <v>46091.557453703703</v>
       </c>
       <c r="C31">
-        <v>57137676</v>
+        <v>59736324</v>
       </c>
       <c r="D31" s="2">
-        <v>46045.45140046296</v>
+        <v>46092.496296296296</v>
       </c>
       <c r="E31" t="s">
-        <v>127</v>
+        <v>225</v>
       </c>
       <c r="F31" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="G31">
-        <v>504041812</v>
+        <v>3130227350</v>
       </c>
       <c r="H31" t="s">
-        <v>119</v>
+        <v>224</v>
       </c>
       <c r="I31" t="s">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
@@ -2981,307 +2954,301 @@
         <v>3</v>
       </c>
       <c r="N31" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O31" t="s">
         <v>0</v>
       </c>
-      <c r="P31" s="1">
-        <v>2000000</v>
+      <c r="P31" t="s">
+        <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>56612479</v>
+        <v>59615935</v>
       </c>
       <c r="B32" s="2">
-        <v>46035.481446759259</v>
+        <v>46090.512303240743</v>
       </c>
       <c r="C32">
-        <v>60101226</v>
+        <v>60393405</v>
       </c>
       <c r="D32" s="2">
-        <v>46099.43613425926</v>
+        <v>46105.432800925926</v>
       </c>
       <c r="E32" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>118</v>
+        <v>221</v>
       </c>
       <c r="G32">
-        <v>504041812</v>
+        <v>767081456</v>
       </c>
       <c r="H32" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="I32" t="s">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
       </c>
       <c r="L32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M32" t="s">
         <v>3</v>
       </c>
       <c r="N32" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O32" t="s">
         <v>0</v>
       </c>
-      <c r="P32" s="1">
-        <v>2000000</v>
+      <c r="P32">
+        <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>56613961</v>
+        <v>59606122</v>
       </c>
       <c r="B33" s="2">
-        <v>46035.492175925923</v>
+        <v>46090.447604166664</v>
       </c>
       <c r="C33">
-        <v>59754685</v>
+        <v>59682305</v>
       </c>
       <c r="D33" s="2">
-        <v>46092.626307870371</v>
+        <v>46091.541701388887</v>
       </c>
       <c r="E33" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="F33" t="s">
-        <v>118</v>
+        <v>219</v>
       </c>
       <c r="G33">
-        <v>504041812</v>
+        <v>708454305</v>
       </c>
       <c r="H33" t="s">
-        <v>122</v>
+        <v>220</v>
       </c>
       <c r="I33" t="s">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K33" t="s">
-        <v>5</v>
+        <v>214</v>
       </c>
       <c r="L33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N33" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O33" t="s">
         <v>0</v>
       </c>
-      <c r="P33" s="1">
-        <v>2000000</v>
+      <c r="P33">
+        <v>0</v>
       </c>
       <c r="Q33" t="s">
-        <v>123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>56618123</v>
+        <v>59541145</v>
       </c>
       <c r="B34" s="2">
-        <v>46035.520821759259</v>
+        <v>46088.634837962964</v>
       </c>
       <c r="C34">
-        <v>59311833</v>
+        <v>59799803</v>
       </c>
       <c r="D34" s="2">
-        <v>46084.811782407407</v>
+        <v>46093.453530092593</v>
       </c>
       <c r="E34" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="F34" t="s">
-        <v>124</v>
+        <v>217</v>
       </c>
       <c r="G34">
-        <v>504041812</v>
+        <v>546008131</v>
       </c>
       <c r="H34" t="s">
-        <v>197</v>
-      </c>
-      <c r="I34">
-        <v>1775236</v>
+        <v>218</v>
+      </c>
+      <c r="I34" t="s">
+        <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K34" t="s">
-        <v>5</v>
+        <v>214</v>
       </c>
       <c r="L34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M34" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N34" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O34" t="s">
         <v>0</v>
       </c>
-      <c r="P34" s="1">
-        <v>2000000</v>
+      <c r="P34">
+        <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>56675050</v>
+        <v>59538597</v>
       </c>
       <c r="B35" s="2">
-        <v>46036.516423611109</v>
+        <v>46088.598194444443</v>
       </c>
       <c r="C35">
-        <v>58216664</v>
+        <v>60030833</v>
       </c>
       <c r="D35" s="2">
-        <v>46065.536226851851</v>
+        <v>46098.40320601852</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>131</v>
+        <v>215</v>
       </c>
       <c r="G35">
-        <v>748512613</v>
+        <v>566473307</v>
       </c>
       <c r="H35" t="s">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="I35" t="s">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K35" t="s">
         <v>5</v>
       </c>
       <c r="L35" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M35" t="s">
         <v>3</v>
       </c>
-      <c r="N35" t="s">
-        <v>196</v>
-      </c>
       <c r="O35" t="s">
         <v>0</v>
       </c>
-      <c r="P35" s="1">
-        <v>4362401</v>
+      <c r="P35">
+        <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>22</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>56970346</v>
+        <v>59538099</v>
       </c>
       <c r="B36" s="2">
-        <v>46042.557280092595</v>
+        <v>46088.590717592589</v>
       </c>
       <c r="C36">
-        <v>59242054</v>
+        <v>60033812</v>
       </c>
       <c r="D36" s="2">
-        <v>46083.719525462962</v>
+        <v>46098.426782407405</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>125</v>
+        <v>215</v>
       </c>
       <c r="G36">
-        <v>708667658</v>
+        <v>566473307</v>
       </c>
       <c r="H36" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="I36" t="s">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K36" t="s">
         <v>5</v>
       </c>
       <c r="L36" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M36" t="s">
         <v>3</v>
       </c>
-      <c r="N36" t="s">
-        <v>196</v>
-      </c>
       <c r="O36" t="s">
         <v>0</v>
       </c>
-      <c r="P36" s="1">
-        <v>2871414</v>
+      <c r="P36">
+        <v>0</v>
       </c>
       <c r="Q36" t="s">
-        <v>39</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>57398181</v>
+        <v>59537755</v>
       </c>
       <c r="B37" s="2">
-        <v>46050.584374999999</v>
+        <v>46088.586631944447</v>
       </c>
       <c r="C37">
-        <v>60344342</v>
+        <v>59807640</v>
       </c>
       <c r="D37" s="2">
-        <v>46104.528900462959</v>
+        <v>46093.511296296296</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="F37" t="s">
-        <v>133</v>
+        <v>213</v>
       </c>
       <c r="G37">
-        <v>720631500</v>
+        <v>556331131</v>
       </c>
       <c r="H37" t="s">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="I37" t="s">
         <v>0</v>
@@ -3290,369 +3257,369 @@
         <v>13</v>
       </c>
       <c r="K37" t="s">
-        <v>5</v>
+        <v>214</v>
       </c>
       <c r="L37" t="s">
         <v>6</v>
       </c>
       <c r="M37" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N37" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O37" t="s">
         <v>0</v>
       </c>
-      <c r="P37" s="1">
-        <v>4406780</v>
+      <c r="P37">
+        <v>0</v>
       </c>
       <c r="Q37" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>57651441</v>
+        <v>59498233</v>
       </c>
       <c r="B38" s="2">
-        <v>46055.58011574074</v>
+        <v>46087.67423611111</v>
       </c>
       <c r="C38">
-        <v>58955875</v>
+        <v>59693004</v>
       </c>
       <c r="D38" s="2">
-        <v>46078.639594907407</v>
+        <v>46091.627928240741</v>
       </c>
       <c r="E38" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="F38" t="s">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="G38">
-        <v>707079088</v>
+        <v>606727287</v>
       </c>
       <c r="H38" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="I38" t="s">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K38" t="s">
-        <v>5</v>
+        <v>212</v>
       </c>
       <c r="L38" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M38" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N38" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O38" t="s">
         <v>0</v>
       </c>
-      <c r="P38" t="s">
-        <v>137</v>
+      <c r="P38">
+        <v>0</v>
       </c>
       <c r="Q38" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>57672103</v>
+        <v>59495495</v>
       </c>
       <c r="B39" s="2">
-        <v>46055.712083333332</v>
+        <v>46087.654039351852</v>
       </c>
       <c r="C39">
-        <v>58477217</v>
+        <v>60763956</v>
       </c>
       <c r="D39" s="2">
-        <v>46070.620787037034</v>
+        <v>46111.629756944443</v>
       </c>
       <c r="E39" t="s">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="F39" t="s">
-        <v>138</v>
+        <v>292</v>
       </c>
       <c r="G39">
-        <v>707079088</v>
+        <v>757019000</v>
       </c>
       <c r="H39" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="I39" t="s">
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K39" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L39" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M39" t="s">
         <v>3</v>
       </c>
       <c r="N39" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="O39" t="s">
         <v>0</v>
       </c>
-      <c r="P39" s="1">
-        <v>1426700</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>34</v>
+      <c r="P39" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>2720219740</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>57692887</v>
+        <v>59495473</v>
       </c>
       <c r="B40" s="2">
-        <v>46056.394780092596</v>
+        <v>46087.653935185182</v>
       </c>
       <c r="C40">
-        <v>60516591</v>
+        <v>60551423</v>
       </c>
       <c r="D40" s="2">
-        <v>46107.377708333333</v>
+        <v>46107.631689814814</v>
       </c>
       <c r="E40" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="G40">
-        <v>707109668</v>
+        <v>506727287</v>
       </c>
       <c r="H40" t="s">
-        <v>284</v>
-      </c>
-      <c r="I40">
-        <v>1798816</v>
+        <v>211</v>
+      </c>
+      <c r="I40" t="s">
+        <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K40" t="s">
         <v>5</v>
       </c>
       <c r="L40" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M40" t="s">
         <v>7</v>
       </c>
       <c r="N40" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O40" t="s">
         <v>0</v>
       </c>
-      <c r="P40" t="s">
+      <c r="P40">
         <v>0</v>
       </c>
       <c r="Q40" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>57706849</v>
+        <v>59480507</v>
       </c>
       <c r="B41" s="2">
-        <v>46056.499166666668</v>
+        <v>46087.544247685182</v>
       </c>
       <c r="C41">
-        <v>59767932</v>
+        <v>60564140</v>
       </c>
       <c r="D41" s="2">
-        <v>46092.721273148149</v>
+        <v>46107.723194444443</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="F41" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G41">
-        <v>708086472</v>
+        <v>708547070</v>
       </c>
       <c r="H41" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K41" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L41" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M41" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N41" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O41" t="s">
         <v>0</v>
       </c>
-      <c r="P41">
+      <c r="P41" t="s">
         <v>0</v>
       </c>
       <c r="Q41" t="s">
-        <v>34</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>57773018</v>
+        <v>59466778</v>
       </c>
       <c r="B42" s="2">
-        <v>46057.517175925925</v>
+        <v>46087.438715277778</v>
       </c>
       <c r="C42">
-        <v>60593118</v>
+        <v>60800786</v>
       </c>
       <c r="D42" s="2">
-        <v>46108.403668981482</v>
+        <v>46112.401354166665</v>
       </c>
       <c r="E42" t="s">
-        <v>287</v>
+        <v>182</v>
       </c>
       <c r="F42" t="s">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="G42">
-        <v>758333146</v>
+        <v>554235979</v>
       </c>
       <c r="H42" t="s">
-        <v>286</v>
-      </c>
-      <c r="I42">
-        <v>1805046</v>
+        <v>42</v>
+      </c>
+      <c r="I42" t="s">
+        <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="K42" t="s">
-        <v>187</v>
+        <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M42" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="N42" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O42" t="s">
         <v>0</v>
       </c>
-      <c r="P42" s="1">
-        <v>400000</v>
+      <c r="P42" t="s">
+        <v>0</v>
       </c>
       <c r="Q42" t="s">
-        <v>233</v>
+        <v>270</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>57849095</v>
+        <v>59466514</v>
       </c>
       <c r="B43" s="2">
-        <v>46058.603668981479</v>
+        <v>46087.436643518522</v>
       </c>
       <c r="C43">
-        <v>60388868</v>
+        <v>60757517</v>
       </c>
       <c r="D43" s="2">
-        <v>46105.385023148148</v>
+        <v>46111.579236111109</v>
       </c>
       <c r="E43" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="G43">
-        <v>707109668</v>
+        <v>141679210</v>
       </c>
       <c r="H43" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="I43" t="s">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
       </c>
       <c r="L43" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M43" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N43" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O43" t="s">
         <v>0</v>
       </c>
-      <c r="P43" t="s">
-        <v>0</v>
+      <c r="P43" s="1">
+        <v>3213390</v>
       </c>
       <c r="Q43" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>57899728</v>
+        <v>59465071</v>
       </c>
       <c r="B44" s="2">
-        <v>46059.503668981481</v>
+        <v>46087.424062500002</v>
       </c>
       <c r="C44">
-        <v>59053570</v>
+        <v>60531474</v>
       </c>
       <c r="D44" s="2">
-        <v>46080.432372685187</v>
+        <v>46107.489861111113</v>
       </c>
       <c r="E44" t="s">
-        <v>127</v>
+        <v>271</v>
       </c>
       <c r="F44" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="G44">
-        <v>505980067</v>
+        <v>554235979</v>
       </c>
       <c r="H44" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
       <c r="I44" t="s">
         <v>0</v>
@@ -3664,48 +3631,48 @@
         <v>5</v>
       </c>
       <c r="L44" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M44" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N44" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O44" t="s">
         <v>0</v>
       </c>
-      <c r="P44" s="1">
-        <v>1002937</v>
+      <c r="P44">
+        <v>0</v>
       </c>
       <c r="Q44" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>58055656</v>
+        <v>59464660</v>
       </c>
       <c r="B45" s="2">
-        <v>46062.760023148148</v>
+        <v>46087.421030092592</v>
       </c>
       <c r="C45">
-        <v>60340320</v>
+        <v>60780173</v>
       </c>
       <c r="D45" s="2">
-        <v>46104.489583333336</v>
+        <v>46111.728275462963</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="F45" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="G45">
-        <v>758224257</v>
+        <v>554235979</v>
       </c>
       <c r="H45" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="I45" t="s">
         <v>0</v>
@@ -3714,122 +3681,122 @@
         <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L45" t="s">
         <v>6</v>
       </c>
       <c r="M45" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N45" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O45" t="s">
         <v>0</v>
       </c>
-      <c r="P45" s="1">
-        <v>1800000</v>
+      <c r="P45">
+        <v>0</v>
       </c>
       <c r="Q45" t="s">
-        <v>15</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>58093827</v>
+        <v>59417066</v>
       </c>
       <c r="B46" s="2">
-        <v>46063.583402777775</v>
+        <v>46086.594525462962</v>
       </c>
       <c r="C46">
-        <v>59486282</v>
+        <v>60589286</v>
       </c>
       <c r="D46" s="2">
-        <v>46087.591932870368</v>
+        <v>46108.367418981485</v>
       </c>
       <c r="E46" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="G46">
-        <v>708086759</v>
+        <v>709565662</v>
       </c>
       <c r="H46" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="I46" t="s">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="K46" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L46" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M46" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N46" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O46" t="s">
         <v>0</v>
       </c>
-      <c r="P46" t="s">
+      <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>58093843</v>
+        <v>59414411</v>
       </c>
       <c r="B47" s="2">
-        <v>46063.583460648151</v>
+        <v>46086.57104166667</v>
       </c>
       <c r="C47">
-        <v>58667700</v>
+        <v>60601081</v>
       </c>
       <c r="D47" s="2">
-        <v>46073.611655092594</v>
+        <v>46108.462025462963</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>45</v>
+        <v>203</v>
       </c>
       <c r="G47">
-        <v>708086759</v>
+        <v>566473307</v>
       </c>
       <c r="H47" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="I47" t="s">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="K47" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L47" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M47" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N47" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O47" t="s">
         <v>0</v>
@@ -3838,351 +3805,351 @@
         <v>0</v>
       </c>
       <c r="Q47" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>58096775</v>
+        <v>59410843</v>
       </c>
       <c r="B48" s="2">
-        <v>46063.603263888886</v>
+        <v>46086.542870370373</v>
       </c>
       <c r="C48">
-        <v>58655959</v>
+        <v>60526566</v>
       </c>
       <c r="D48" s="2">
-        <v>46073.525740740741</v>
+        <v>46107.452592592592</v>
       </c>
       <c r="E48" t="s">
-        <v>16</v>
+        <v>271</v>
       </c>
       <c r="F48" t="s">
-        <v>45</v>
+        <v>201</v>
       </c>
       <c r="G48">
-        <v>708086759</v>
+        <v>758700193</v>
       </c>
       <c r="H48" t="s">
-        <v>148</v>
+        <v>202</v>
       </c>
       <c r="I48" t="s">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L48" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N48" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O48" t="s">
         <v>0</v>
       </c>
-      <c r="P48">
+      <c r="P48" t="s">
         <v>0</v>
       </c>
       <c r="Q48" t="s">
-        <v>151</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>58144220</v>
+        <v>59410212</v>
       </c>
       <c r="B49" s="2">
-        <v>46064.478425925925</v>
+        <v>46086.537708333337</v>
       </c>
       <c r="C49">
-        <v>60604436</v>
+        <v>59835857</v>
       </c>
       <c r="D49" s="2">
-        <v>46108.484652777777</v>
+        <v>46093.728726851848</v>
       </c>
       <c r="E49" t="s">
-        <v>288</v>
+        <v>182</v>
       </c>
       <c r="F49" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="G49">
-        <v>2722418166</v>
+        <v>789018789</v>
       </c>
       <c r="H49" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="I49" t="s">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="L49" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M49" t="s">
         <v>7</v>
       </c>
       <c r="N49" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O49" t="s">
         <v>0</v>
       </c>
-      <c r="P49">
+      <c r="P49" t="s">
         <v>0</v>
       </c>
       <c r="Q49" t="s">
-        <v>263</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>58151683</v>
+        <v>59409752</v>
       </c>
       <c r="B50" s="2">
-        <v>46064.532222222224</v>
+        <v>46086.534502314818</v>
       </c>
       <c r="C50">
-        <v>60402173</v>
+        <v>60600716</v>
       </c>
       <c r="D50" s="2">
-        <v>46105.501574074071</v>
+        <v>46108.459768518522</v>
       </c>
       <c r="E50" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="G50">
-        <v>2721271444</v>
+        <v>758700193</v>
       </c>
       <c r="H50" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="I50" t="s">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L50" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M50" t="s">
         <v>3</v>
       </c>
       <c r="N50" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O50" t="s">
         <v>0</v>
       </c>
-      <c r="P50" s="1">
-        <v>1495965</v>
+      <c r="P50" t="s">
+        <v>0</v>
       </c>
       <c r="Q50" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>58166885</v>
+        <v>59409078</v>
       </c>
       <c r="B51" s="2">
-        <v>46064.649965277778</v>
+        <v>46086.529247685183</v>
       </c>
       <c r="C51">
-        <v>59811530</v>
+        <v>60600044</v>
       </c>
       <c r="D51" s="2">
-        <v>46093.540775462963</v>
+        <v>46108.453865740739</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="G51">
-        <v>504041812</v>
+        <v>709140938</v>
       </c>
       <c r="H51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I51" t="s">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="K51" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L51" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M51" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N51" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O51" t="s">
         <v>0</v>
       </c>
-      <c r="P51" s="1">
-        <v>2000000</v>
+      <c r="P51" t="s">
+        <v>0</v>
       </c>
       <c r="Q51" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>58168004</v>
+        <v>59406937</v>
       </c>
       <c r="B52" s="2">
-        <v>46064.657037037039</v>
+        <v>46086.512870370374</v>
       </c>
       <c r="C52">
-        <v>60360622</v>
+        <v>60809404</v>
       </c>
       <c r="D52" s="2">
-        <v>46104.652754629627</v>
+        <v>46112.464097222219</v>
       </c>
       <c r="E52" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="F52" t="s">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="G52">
-        <v>504041812</v>
+        <v>709136702</v>
       </c>
       <c r="H52" t="s">
-        <v>264</v>
-      </c>
-      <c r="I52">
-        <v>1811236</v>
+        <v>102</v>
+      </c>
+      <c r="I52" t="s">
+        <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L52" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M52" t="s">
         <v>3</v>
       </c>
       <c r="N52" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O52" t="s">
         <v>0</v>
       </c>
-      <c r="P52" s="1">
-        <v>2000000</v>
+      <c r="P52">
+        <v>0</v>
       </c>
       <c r="Q52" t="s">
-        <v>265</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>58274609</v>
+        <v>59406146</v>
       </c>
       <c r="B53" s="2">
-        <v>46066.525011574071</v>
+        <v>46086.506643518522</v>
       </c>
       <c r="C53">
-        <v>59264178</v>
+        <v>60600544</v>
       </c>
       <c r="D53" s="2">
-        <v>46084.406759259262</v>
+        <v>46108.458136574074</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="G53">
-        <v>2722480700</v>
+        <v>709136702</v>
       </c>
       <c r="H53" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="I53" t="s">
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="K53" t="s">
         <v>5</v>
       </c>
       <c r="L53" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M53" t="s">
         <v>3</v>
       </c>
       <c r="N53" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O53" t="s">
         <v>0</v>
       </c>
-      <c r="P53" s="1">
-        <v>522590</v>
+      <c r="P53">
+        <v>0</v>
       </c>
       <c r="Q53" t="s">
-        <v>41</v>
+        <v>269</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>58626822</v>
+        <v>59374776</v>
       </c>
       <c r="B54" s="2">
-        <v>46072.810324074075</v>
+        <v>46085.757662037038</v>
       </c>
       <c r="C54">
-        <v>59811821</v>
+        <v>60837598</v>
       </c>
       <c r="D54" s="2">
-        <v>46093.543773148151</v>
+        <v>46112.678761574076</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F54" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="G54">
-        <v>709574114</v>
+        <v>747726344</v>
       </c>
       <c r="H54" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="I54" t="s">
         <v>0</v>
@@ -4197,45 +4164,45 @@
         <v>6</v>
       </c>
       <c r="M54" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N54" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O54" t="s">
         <v>0</v>
       </c>
-      <c r="P54" s="1">
-        <v>445307</v>
+      <c r="P54" t="s">
+        <v>0</v>
       </c>
       <c r="Q54" t="s">
-        <v>35</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>58635645</v>
+        <v>59309764</v>
       </c>
       <c r="B55" s="2">
-        <v>46073.372395833336</v>
+        <v>46084.777083333334</v>
       </c>
       <c r="C55">
-        <v>59752855</v>
+        <v>60432246</v>
       </c>
       <c r="D55" s="2">
-        <v>46092.614201388889</v>
+        <v>46105.737245370372</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>159</v>
+        <v>24</v>
       </c>
       <c r="G55">
-        <v>759250737</v>
+        <v>708164102</v>
       </c>
       <c r="H55" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="I55" t="s">
         <v>0</v>
@@ -4250,45 +4217,45 @@
         <v>8</v>
       </c>
       <c r="M55" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N55" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O55" t="s">
         <v>0</v>
       </c>
-      <c r="P55" t="s">
-        <v>0</v>
+      <c r="P55" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q55" t="s">
-        <v>41</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>58635674</v>
+        <v>59308240</v>
       </c>
       <c r="B56" s="2">
-        <v>46073.372488425928</v>
+        <v>46084.755844907406</v>
       </c>
       <c r="C56">
-        <v>60160137</v>
+        <v>60837666</v>
       </c>
       <c r="D56" s="2">
-        <v>46100.389884259261</v>
+        <v>46112.679131944446</v>
       </c>
       <c r="E56" t="s">
-        <v>10</v>
+        <v>264</v>
       </c>
       <c r="F56" t="s">
-        <v>159</v>
+        <v>24</v>
       </c>
       <c r="G56">
-        <v>759250737</v>
+        <v>707865499</v>
       </c>
       <c r="H56" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="I56" t="s">
         <v>0</v>
@@ -4303,151 +4270,151 @@
         <v>8</v>
       </c>
       <c r="M56" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N56" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O56" t="s">
         <v>0</v>
       </c>
       <c r="P56" s="1">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="Q56" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>58642079</v>
+        <v>59301554</v>
       </c>
       <c r="B57" s="2">
-        <v>46073.425034722219</v>
+        <v>46084.695763888885</v>
       </c>
       <c r="C57">
-        <v>59755320</v>
+        <v>60762717</v>
       </c>
       <c r="D57" s="2">
-        <v>46092.630370370367</v>
+        <v>46111.617106481484</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F57" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G57">
-        <v>759250737</v>
+        <v>777654212</v>
       </c>
       <c r="H57" t="s">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="I57" t="s">
         <v>0</v>
       </c>
       <c r="J57" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K57" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L57" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M57" t="s">
         <v>3</v>
       </c>
       <c r="N57" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="O57" t="s">
         <v>0</v>
       </c>
-      <c r="P57" t="s">
-        <v>0</v>
+      <c r="P57" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q57" t="s">
-        <v>160</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>58649804</v>
+        <v>59278925</v>
       </c>
       <c r="B58" s="2">
-        <v>46073.479305555556</v>
+        <v>46084.521053240744</v>
       </c>
       <c r="C58">
-        <v>59753122</v>
+        <v>60811998</v>
       </c>
       <c r="D58" s="2">
-        <v>46092.615983796299</v>
+        <v>46112.484432870369</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F58" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="G58">
-        <v>759250737</v>
+        <v>759651079</v>
       </c>
       <c r="H58" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="I58" t="s">
         <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K58" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L58" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M58" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N58" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="O58" t="s">
         <v>0</v>
       </c>
-      <c r="P58" t="s">
-        <v>0</v>
+      <c r="P58" s="1">
+        <v>500000</v>
       </c>
       <c r="Q58" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>58649837</v>
+        <v>58963646</v>
       </c>
       <c r="B59" s="2">
-        <v>46073.479409722226</v>
+        <v>46078.697048611109</v>
       </c>
       <c r="C59">
-        <v>59753844</v>
+        <v>60806549</v>
       </c>
       <c r="D59" s="2">
-        <v>46092.619826388887</v>
+        <v>46112.445474537039</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="F59" t="s">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="G59">
-        <v>759250737</v>
+        <v>747726344</v>
       </c>
       <c r="H59" t="s">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="I59" t="s">
         <v>0</v>
@@ -4465,60 +4432,60 @@
         <v>14</v>
       </c>
       <c r="N59" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O59" t="s">
         <v>0</v>
       </c>
-      <c r="P59" s="1">
-        <v>500000</v>
+      <c r="P59">
+        <v>0</v>
       </c>
       <c r="Q59" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>58650374</v>
+        <v>58963630</v>
       </c>
       <c r="B60" s="2">
-        <v>46073.483518518522</v>
+        <v>46078.697002314817</v>
       </c>
       <c r="C60">
-        <v>60467780</v>
+        <v>60167087</v>
       </c>
       <c r="D60" s="2">
-        <v>46106.494745370372</v>
+        <v>46100.449837962966</v>
       </c>
       <c r="E60" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="G60">
-        <v>708193864</v>
+        <v>747726344</v>
       </c>
       <c r="H60" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="I60" t="s">
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K60" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="L60" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M60" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N60" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O60" t="s">
         <v>0</v>
@@ -4526,58 +4493,58 @@
       <c r="P60" t="s">
         <v>0</v>
       </c>
-      <c r="Q60">
-        <v>2722229765</v>
+      <c r="Q60" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>58797846</v>
+        <v>58959238</v>
       </c>
       <c r="B61" s="2">
-        <v>46076.510104166664</v>
+        <v>46078.665532407409</v>
       </c>
       <c r="C61">
-        <v>60565096</v>
+        <v>60163938</v>
       </c>
       <c r="D61" s="2">
-        <v>46107.733611111114</v>
+        <v>46100.423773148148</v>
       </c>
       <c r="E61" t="s">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="F61" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="G61">
-        <v>102224907</v>
+        <v>708641473</v>
       </c>
       <c r="H61" t="s">
-        <v>289</v>
+        <v>179</v>
       </c>
       <c r="I61" t="s">
         <v>0</v>
       </c>
       <c r="J61" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
       </c>
       <c r="L61" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M61" t="s">
         <v>3</v>
       </c>
       <c r="N61" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O61" t="s">
         <v>0</v>
       </c>
       <c r="P61" s="1">
-        <v>2000000</v>
+        <v>850000</v>
       </c>
       <c r="Q61" t="s">
         <v>34</v>
@@ -4585,81 +4552,81 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>58808846</v>
+        <v>58925987</v>
       </c>
       <c r="B62" s="2">
-        <v>46076.586747685185</v>
+        <v>46078.434814814813</v>
       </c>
       <c r="C62">
-        <v>60488514</v>
+        <v>60163873</v>
       </c>
       <c r="D62" s="2">
-        <v>46106.663819444446</v>
+        <v>46100.423101851855</v>
       </c>
       <c r="E62" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="G62">
-        <v>749994094</v>
+        <v>708641473</v>
       </c>
       <c r="H62" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="I62" t="s">
         <v>0</v>
       </c>
       <c r="J62" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K62" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L62" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M62" t="s">
         <v>3</v>
       </c>
       <c r="N62" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O62" t="s">
         <v>0</v>
       </c>
-      <c r="P62" s="1">
-        <v>2000000</v>
+      <c r="P62" t="s">
+        <v>0</v>
       </c>
       <c r="Q62" t="s">
-        <v>290</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>58821537</v>
+        <v>58892481</v>
       </c>
       <c r="B63" s="2">
-        <v>46076.664479166669</v>
+        <v>46077.688344907408</v>
       </c>
       <c r="C63">
-        <v>60409857</v>
+        <v>60413667</v>
       </c>
       <c r="D63" s="2">
-        <v>46105.569016203706</v>
+        <v>46105.602303240739</v>
       </c>
       <c r="E63" t="s">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G63">
-        <v>708086472</v>
+        <v>748377555</v>
       </c>
       <c r="H63" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="I63" t="s">
         <v>0</v>
@@ -4674,45 +4641,45 @@
         <v>8</v>
       </c>
       <c r="M63" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N63" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O63" t="s">
         <v>0</v>
       </c>
-      <c r="P63" t="s">
-        <v>0</v>
+      <c r="P63" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q63" t="s">
-        <v>173</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>58821553</v>
+        <v>58892468</v>
       </c>
       <c r="B64" s="2">
-        <v>46076.664525462962</v>
+        <v>46077.688321759262</v>
       </c>
       <c r="C64">
-        <v>59998536</v>
+        <v>60414369</v>
       </c>
       <c r="D64" s="2">
-        <v>46097.435590277775</v>
+        <v>46105.607986111114</v>
       </c>
       <c r="E64" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="F64" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G64">
-        <v>708086472</v>
+        <v>748377555</v>
       </c>
       <c r="H64" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="I64" t="s">
         <v>0</v>
@@ -4721,57 +4688,57 @@
         <v>18</v>
       </c>
       <c r="K64" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L64" t="s">
         <v>8</v>
       </c>
       <c r="M64" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N64" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O64" t="s">
         <v>0</v>
       </c>
-      <c r="P64" s="1">
-        <v>705000</v>
+      <c r="P64" t="s">
+        <v>0</v>
       </c>
       <c r="Q64" t="s">
-        <v>236</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>58822576</v>
+        <v>58889883</v>
       </c>
       <c r="B65" s="2">
-        <v>46076.670810185184</v>
+        <v>46077.670601851853</v>
       </c>
       <c r="C65">
-        <v>59375318</v>
+        <v>60803412</v>
       </c>
       <c r="D65" s="2">
-        <v>46085.763622685183</v>
+        <v>46112.421851851854</v>
       </c>
       <c r="E65" t="s">
-        <v>16</v>
+        <v>286</v>
       </c>
       <c r="F65" t="s">
-        <v>167</v>
+        <v>288</v>
       </c>
       <c r="G65">
-        <v>708086472</v>
+        <v>748377555</v>
       </c>
       <c r="H65" t="s">
-        <v>168</v>
-      </c>
-      <c r="I65" t="s">
-        <v>0</v>
+        <v>289</v>
+      </c>
+      <c r="I65">
+        <v>1827246</v>
       </c>
       <c r="J65" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K65" t="s">
         <v>5</v>
@@ -4780,45 +4747,45 @@
         <v>8</v>
       </c>
       <c r="M65" t="s">
-        <v>7</v>
+        <v>290</v>
       </c>
       <c r="N65" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O65" t="s">
         <v>0</v>
       </c>
-      <c r="P65" t="s">
-        <v>0</v>
+      <c r="P65" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q65" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>58822595</v>
+        <v>58889872</v>
       </c>
       <c r="B66" s="2">
-        <v>46076.670856481483</v>
+        <v>46077.670567129629</v>
       </c>
       <c r="C66">
-        <v>60208557</v>
+        <v>60819226</v>
       </c>
       <c r="D66" s="2">
-        <v>46100.764618055553</v>
+        <v>46112.544432870367</v>
       </c>
       <c r="E66" t="s">
-        <v>16</v>
+        <v>286</v>
       </c>
       <c r="F66" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G66">
-        <v>708086472</v>
+        <v>748377555</v>
       </c>
       <c r="H66" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="I66" t="s">
         <v>0</v>
@@ -4833,45 +4800,45 @@
         <v>8</v>
       </c>
       <c r="M66" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N66" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O66" t="s">
         <v>0</v>
       </c>
-      <c r="P66" s="1">
-        <v>1150000</v>
+      <c r="P66" t="s">
+        <v>0</v>
       </c>
       <c r="Q66" t="s">
-        <v>73</v>
+        <v>287</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>58856498</v>
+        <v>58885259</v>
       </c>
       <c r="B67" s="2">
-        <v>46077.418171296296</v>
+        <v>46077.638657407406</v>
       </c>
       <c r="C67">
-        <v>60184731</v>
+        <v>60373389</v>
       </c>
       <c r="D67" s="2">
-        <v>46100.579618055555</v>
+        <v>46104.751145833332</v>
       </c>
       <c r="E67" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G67">
-        <v>748377555</v>
+        <v>748377507</v>
       </c>
       <c r="H67" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I67" t="s">
         <v>0</v>
@@ -4886,51 +4853,51 @@
         <v>8</v>
       </c>
       <c r="M67" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N67" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O67" t="s">
         <v>0</v>
       </c>
-      <c r="P67" t="s">
-        <v>0</v>
+      <c r="P67" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q67" t="s">
-        <v>258</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>58860531</v>
+        <v>58885251</v>
       </c>
       <c r="B68" s="2">
-        <v>46077.446631944447</v>
+        <v>46077.63863425926</v>
       </c>
       <c r="C68">
-        <v>60225679</v>
+        <v>60408762</v>
       </c>
       <c r="D68" s="2">
-        <v>46101.312939814816</v>
+        <v>46105.557326388887</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F68" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G68">
-        <v>748377555</v>
+        <v>748377507</v>
       </c>
       <c r="H68" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I68" t="s">
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
@@ -4942,7 +4909,7 @@
         <v>7</v>
       </c>
       <c r="N68" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O68" t="s">
         <v>0</v>
@@ -4951,39 +4918,39 @@
         <v>0</v>
       </c>
       <c r="Q68" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>58860538</v>
+        <v>58868860</v>
       </c>
       <c r="B69" s="2">
-        <v>46077.446666666663</v>
+        <v>46077.501238425924</v>
       </c>
       <c r="C69">
-        <v>60551848</v>
+        <v>60764693</v>
       </c>
       <c r="D69" s="2">
-        <v>46107.634930555556</v>
+        <v>46111.635648148149</v>
       </c>
       <c r="E69" t="s">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="F69" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G69">
         <v>748377555</v>
       </c>
       <c r="H69" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I69" t="s">
         <v>0</v>
       </c>
       <c r="J69" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
@@ -4995,7 +4962,7 @@
         <v>14</v>
       </c>
       <c r="N69" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O69" t="s">
         <v>0</v>
@@ -5004,33 +4971,33 @@
         <v>5324000</v>
       </c>
       <c r="Q69" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>58862661</v>
+        <v>58868849</v>
       </c>
       <c r="B70" s="2">
-        <v>46077.461805555555</v>
+        <v>46077.501203703701</v>
       </c>
       <c r="C70">
-        <v>60042646</v>
+        <v>60416909</v>
       </c>
       <c r="D70" s="2">
-        <v>46098.494629629633</v>
+        <v>46105.625150462962</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G70">
         <v>748377555</v>
       </c>
       <c r="H70" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I70" t="s">
         <v>0</v>
@@ -5048,7 +5015,7 @@
         <v>7</v>
       </c>
       <c r="N70" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O70" t="s">
         <v>0</v>
@@ -5057,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="Q70" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
@@ -5077,13 +5044,13 @@
         <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G71">
         <v>748377555</v>
       </c>
       <c r="H71" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="I71" t="s">
         <v>0</v>
@@ -5101,7 +5068,7 @@
         <v>14</v>
       </c>
       <c r="N71" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O71" t="s">
         <v>0</v>
@@ -5115,28 +5082,28 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>58868849</v>
+        <v>58862661</v>
       </c>
       <c r="B72" s="2">
-        <v>46077.501203703701</v>
+        <v>46077.461805555555</v>
       </c>
       <c r="C72">
-        <v>60416909</v>
+        <v>60042646</v>
       </c>
       <c r="D72" s="2">
-        <v>46105.625150462962</v>
+        <v>46098.494629629633</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
       </c>
       <c r="F72" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G72">
         <v>748377555</v>
       </c>
       <c r="H72" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="I72" t="s">
         <v>0</v>
@@ -5154,7 +5121,7 @@
         <v>7</v>
       </c>
       <c r="N72" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O72" t="s">
         <v>0</v>
@@ -5163,39 +5130,39 @@
         <v>0</v>
       </c>
       <c r="Q72" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>58868860</v>
+        <v>58860538</v>
       </c>
       <c r="B73" s="2">
-        <v>46077.501238425924</v>
+        <v>46077.446666666663</v>
       </c>
       <c r="C73">
-        <v>60340792</v>
+        <v>60749284</v>
       </c>
       <c r="D73" s="2">
-        <v>46104.493530092594</v>
+        <v>46111.515370370369</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="G73">
         <v>748377555</v>
       </c>
       <c r="H73" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="I73" t="s">
         <v>0</v>
       </c>
       <c r="J73" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
@@ -5207,7 +5174,7 @@
         <v>14</v>
       </c>
       <c r="N73" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O73" t="s">
         <v>0</v>
@@ -5216,39 +5183,39 @@
         <v>5324000</v>
       </c>
       <c r="Q73" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>58885251</v>
+        <v>58860531</v>
       </c>
       <c r="B74" s="2">
-        <v>46077.63863425926</v>
+        <v>46077.446631944447</v>
       </c>
       <c r="C74">
-        <v>60408762</v>
+        <v>60749153</v>
       </c>
       <c r="D74" s="2">
-        <v>46105.557326388887</v>
+        <v>46111.514351851853</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="G74">
-        <v>748377507</v>
+        <v>748377555</v>
       </c>
       <c r="H74" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="I74" t="s">
         <v>0</v>
       </c>
       <c r="J74" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
@@ -5260,7 +5227,7 @@
         <v>7</v>
       </c>
       <c r="N74" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O74" t="s">
         <v>0</v>
@@ -5269,33 +5236,33 @@
         <v>0</v>
       </c>
       <c r="Q74" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>58885259</v>
+        <v>58856498</v>
       </c>
       <c r="B75" s="2">
-        <v>46077.638657407406</v>
+        <v>46077.418171296296</v>
       </c>
       <c r="C75">
-        <v>60373389</v>
+        <v>60800011</v>
       </c>
       <c r="D75" s="2">
-        <v>46104.751145833332</v>
+        <v>46112.393784722219</v>
       </c>
       <c r="E75" t="s">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="F75" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="G75">
-        <v>748377507</v>
+        <v>748377555</v>
       </c>
       <c r="H75" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="I75" t="s">
         <v>0</v>
@@ -5310,45 +5277,45 @@
         <v>8</v>
       </c>
       <c r="M75" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N75" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O75" t="s">
         <v>0</v>
       </c>
-      <c r="P75" s="1">
-        <v>5324000</v>
+      <c r="P75" t="s">
+        <v>0</v>
       </c>
       <c r="Q75" t="s">
-        <v>34</v>
+        <v>245</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>58889872</v>
+        <v>58822595</v>
       </c>
       <c r="B76" s="2">
-        <v>46077.670567129629</v>
+        <v>46076.670856481483</v>
       </c>
       <c r="C76">
-        <v>60225565</v>
+        <v>60208557</v>
       </c>
       <c r="D76" s="2">
-        <v>46101.301990740743</v>
+        <v>46100.764618055553</v>
       </c>
       <c r="E76" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="G76">
-        <v>748377555</v>
+        <v>708086472</v>
       </c>
       <c r="H76" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="I76" t="s">
         <v>0</v>
@@ -5363,45 +5330,45 @@
         <v>8</v>
       </c>
       <c r="M76" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N76" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O76" t="s">
         <v>0</v>
       </c>
-      <c r="P76" t="s">
-        <v>0</v>
+      <c r="P76" s="1">
+        <v>1150000</v>
       </c>
       <c r="Q76" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>58889883</v>
+        <v>58822576</v>
       </c>
       <c r="B77" s="2">
-        <v>46077.670601851853</v>
+        <v>46076.670810185184</v>
       </c>
       <c r="C77">
-        <v>60328639</v>
+        <v>59375318</v>
       </c>
       <c r="D77" s="2">
-        <v>46104.393576388888</v>
+        <v>46085.763622685183</v>
       </c>
       <c r="E77" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="G77">
-        <v>748377555</v>
+        <v>708086472</v>
       </c>
       <c r="H77" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="I77" t="s">
         <v>0</v>
@@ -5416,45 +5383,45 @@
         <v>8</v>
       </c>
       <c r="M77" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N77" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O77" t="s">
         <v>0</v>
       </c>
-      <c r="P77" s="1">
-        <v>5324000</v>
+      <c r="P77" t="s">
+        <v>0</v>
       </c>
       <c r="Q77" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>58892468</v>
+        <v>58821553</v>
       </c>
       <c r="B78" s="2">
-        <v>46077.688321759262</v>
+        <v>46076.664525462962</v>
       </c>
       <c r="C78">
-        <v>60414369</v>
+        <v>59998536</v>
       </c>
       <c r="D78" s="2">
-        <v>46105.607986111114</v>
+        <v>46097.435590277775</v>
       </c>
       <c r="E78" t="s">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="F78" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="G78">
-        <v>748377555</v>
+        <v>708086472</v>
       </c>
       <c r="H78" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="I78" t="s">
         <v>0</v>
@@ -5463,51 +5430,51 @@
         <v>18</v>
       </c>
       <c r="K78" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L78" t="s">
         <v>8</v>
       </c>
       <c r="M78" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N78" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O78" t="s">
         <v>0</v>
       </c>
-      <c r="P78" t="s">
-        <v>0</v>
+      <c r="P78" s="1">
+        <v>705000</v>
       </c>
       <c r="Q78" t="s">
-        <v>39</v>
+        <v>227</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>58892481</v>
+        <v>58821537</v>
       </c>
       <c r="B79" s="2">
-        <v>46077.688344907408</v>
+        <v>46076.664479166669</v>
       </c>
       <c r="C79">
-        <v>60413667</v>
+        <v>60802217</v>
       </c>
       <c r="D79" s="2">
-        <v>46105.602303240739</v>
+        <v>46112.413530092592</v>
       </c>
       <c r="E79" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F79" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="G79">
-        <v>748377555</v>
+        <v>708086472</v>
       </c>
       <c r="H79" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="I79" t="s">
         <v>0</v>
@@ -5522,98 +5489,98 @@
         <v>8</v>
       </c>
       <c r="M79" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N79" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O79" t="s">
         <v>0</v>
       </c>
-      <c r="P79" s="1">
-        <v>5324000</v>
+      <c r="P79" t="s">
+        <v>0</v>
       </c>
       <c r="Q79" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>58925987</v>
+        <v>58797846</v>
       </c>
       <c r="B80" s="2">
-        <v>46078.434814814813</v>
+        <v>46076.510104166664</v>
       </c>
       <c r="C80">
-        <v>60163873</v>
+        <v>60820437</v>
       </c>
       <c r="D80" s="2">
-        <v>46100.423101851855</v>
+        <v>46112.554594907408</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="F80" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="G80">
-        <v>708641473</v>
+        <v>102224907</v>
       </c>
       <c r="H80" t="s">
-        <v>182</v>
+        <v>267</v>
       </c>
       <c r="I80" t="s">
         <v>0</v>
       </c>
       <c r="J80" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K80" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L80" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M80" t="s">
         <v>3</v>
       </c>
       <c r="N80" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O80" t="s">
         <v>0</v>
       </c>
-      <c r="P80" t="s">
-        <v>0</v>
+      <c r="P80" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q80" t="s">
-        <v>166</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>58959238</v>
+        <v>58649837</v>
       </c>
       <c r="B81" s="2">
-        <v>46078.665532407409</v>
+        <v>46073.479409722226</v>
       </c>
       <c r="C81">
-        <v>60163938</v>
+        <v>59753844</v>
       </c>
       <c r="D81" s="2">
-        <v>46100.423773148148</v>
+        <v>46092.619826388887</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
       </c>
       <c r="F81" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="G81">
-        <v>708641473</v>
+        <v>759250737</v>
       </c>
       <c r="H81" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="I81" t="s">
         <v>0</v>
@@ -5628,45 +5595,45 @@
         <v>6</v>
       </c>
       <c r="M81" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N81" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O81" t="s">
         <v>0</v>
       </c>
       <c r="P81" s="1">
-        <v>850000</v>
+        <v>500000</v>
       </c>
       <c r="Q81" t="s">
-        <v>34</v>
+        <v>174</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>58963630</v>
+        <v>58649804</v>
       </c>
       <c r="B82" s="2">
-        <v>46078.697002314817</v>
+        <v>46073.479305555556</v>
       </c>
       <c r="C82">
-        <v>60167087</v>
+        <v>59753122</v>
       </c>
       <c r="D82" s="2">
-        <v>46100.449837962966</v>
+        <v>46092.615983796299</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
       </c>
       <c r="F82" t="s">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="G82">
-        <v>747726344</v>
+        <v>759250737</v>
       </c>
       <c r="H82" t="s">
-        <v>184</v>
+        <v>28</v>
       </c>
       <c r="I82" t="s">
         <v>0</v>
@@ -5684,7 +5651,7 @@
         <v>7</v>
       </c>
       <c r="N82" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O82" t="s">
         <v>0</v>
@@ -5693,86 +5660,86 @@
         <v>0</v>
       </c>
       <c r="Q82" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>58963646</v>
+        <v>58642079</v>
       </c>
       <c r="B83" s="2">
-        <v>46078.697048611109</v>
+        <v>46073.425034722219</v>
       </c>
       <c r="C83">
-        <v>60185453</v>
+        <v>59755320</v>
       </c>
       <c r="D83" s="2">
-        <v>46100.586238425924</v>
+        <v>46092.630370370367</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
       </c>
       <c r="F83" t="s">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="G83">
-        <v>747726344</v>
+        <v>759250737</v>
       </c>
       <c r="H83" t="s">
-        <v>184</v>
+        <v>28</v>
       </c>
       <c r="I83" t="s">
         <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="K83" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L83" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M83" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N83" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O83" t="s">
         <v>0</v>
       </c>
-      <c r="P83">
+      <c r="P83" t="s">
         <v>0</v>
       </c>
       <c r="Q83" t="s">
-        <v>34</v>
+        <v>159</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>59278285</v>
+        <v>58635674</v>
       </c>
       <c r="B84" s="2">
-        <v>46084.516597222224</v>
+        <v>46073.372488425928</v>
       </c>
       <c r="C84">
-        <v>60396888</v>
+        <v>60160137</v>
       </c>
       <c r="D84" s="2">
-        <v>46105.459768518522</v>
+        <v>46100.389884259261</v>
       </c>
       <c r="E84" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F84" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="G84">
-        <v>759651079</v>
+        <v>759250737</v>
       </c>
       <c r="H84" t="s">
-        <v>190</v>
+        <v>28</v>
       </c>
       <c r="I84" t="s">
         <v>0</v>
@@ -5781,16 +5748,16 @@
         <v>18</v>
       </c>
       <c r="K84" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L84" t="s">
         <v>8</v>
       </c>
       <c r="M84" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N84" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O84" t="s">
         <v>0</v>
@@ -5799,33 +5766,33 @@
         <v>500000</v>
       </c>
       <c r="Q84" t="s">
-        <v>241</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>59278925</v>
+        <v>58635645</v>
       </c>
       <c r="B85" s="2">
-        <v>46084.521053240744</v>
+        <v>46073.372395833336</v>
       </c>
       <c r="C85">
-        <v>60397473</v>
+        <v>59752855</v>
       </c>
       <c r="D85" s="2">
-        <v>46105.464074074072</v>
+        <v>46092.614201388889</v>
       </c>
       <c r="E85" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F85" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="G85">
-        <v>759651079</v>
+        <v>759250737</v>
       </c>
       <c r="H85" t="s">
-        <v>191</v>
+        <v>28</v>
       </c>
       <c r="I85" t="s">
         <v>0</v>
@@ -5834,166 +5801,166 @@
         <v>18</v>
       </c>
       <c r="K85" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L85" t="s">
         <v>8</v>
       </c>
       <c r="M85" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N85" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O85" t="s">
         <v>0</v>
       </c>
-      <c r="P85" s="1">
-        <v>500000</v>
+      <c r="P85" t="s">
+        <v>0</v>
       </c>
       <c r="Q85" t="s">
-        <v>242</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>59300338</v>
+        <v>58626822</v>
       </c>
       <c r="B86" s="2">
-        <v>46084.687997685185</v>
+        <v>46072.810324074075</v>
       </c>
       <c r="C86">
-        <v>60558677</v>
+        <v>59811821</v>
       </c>
       <c r="D86" s="2">
-        <v>46107.684594907405</v>
+        <v>46093.543773148151</v>
       </c>
       <c r="E86" t="s">
-        <v>283</v>
+        <v>10</v>
       </c>
       <c r="F86" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G86">
-        <v>545254325</v>
+        <v>709574114</v>
       </c>
       <c r="H86" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="I86" t="s">
         <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K86" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L86" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M86" t="s">
         <v>3</v>
       </c>
       <c r="N86" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O86" t="s">
         <v>0</v>
       </c>
       <c r="P86" s="1">
-        <v>2000000</v>
+        <v>445307</v>
       </c>
       <c r="Q86" t="s">
-        <v>266</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>59301554</v>
+        <v>58274609</v>
       </c>
       <c r="B87" s="2">
-        <v>46084.695763888885</v>
+        <v>46066.525011574071</v>
       </c>
       <c r="C87">
-        <v>60611241</v>
+        <v>59264178</v>
       </c>
       <c r="D87" s="2">
-        <v>46108.537268518521</v>
+        <v>46084.406759259262</v>
       </c>
       <c r="E87" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F87" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G87">
-        <v>777654212</v>
+        <v>2722480700</v>
       </c>
       <c r="H87" t="s">
-        <v>193</v>
+        <v>42</v>
       </c>
       <c r="I87" t="s">
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K87" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L87" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M87" t="s">
         <v>3</v>
       </c>
       <c r="N87" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O87" t="s">
         <v>0</v>
       </c>
       <c r="P87" s="1">
-        <v>2000000</v>
+        <v>522590</v>
       </c>
       <c r="Q87" t="s">
-        <v>291</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>59308240</v>
+        <v>58168004</v>
       </c>
       <c r="B88" s="2">
-        <v>46084.755844907406</v>
+        <v>46064.657037037039</v>
       </c>
       <c r="C88">
-        <v>60617360</v>
+        <v>60360622</v>
       </c>
       <c r="D88" s="2">
-        <v>46108.594525462962</v>
+        <v>46104.652754629627</v>
       </c>
       <c r="E88" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="F88" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="G88">
-        <v>707865499</v>
+        <v>504041812</v>
       </c>
       <c r="H88" t="s">
-        <v>128</v>
-      </c>
-      <c r="I88" t="s">
-        <v>0</v>
+        <v>249</v>
+      </c>
+      <c r="I88">
+        <v>1811236</v>
       </c>
       <c r="J88" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K88" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L88" t="s">
         <v>8</v>
@@ -6002,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="N88" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O88" t="s">
         <v>0</v>
@@ -6011,33 +5978,33 @@
         <v>2000000</v>
       </c>
       <c r="Q88" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>59309764</v>
+        <v>58166885</v>
       </c>
       <c r="B89" s="2">
-        <v>46084.777083333334</v>
+        <v>46064.649965277778</v>
       </c>
       <c r="C89">
-        <v>60432246</v>
+        <v>59811530</v>
       </c>
       <c r="D89" s="2">
-        <v>46105.737245370372</v>
+        <v>46093.540775462963</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
       </c>
       <c r="F89" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="G89">
-        <v>708164102</v>
+        <v>504041812</v>
       </c>
       <c r="H89" t="s">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I89" t="s">
         <v>0</v>
@@ -6055,7 +6022,7 @@
         <v>3</v>
       </c>
       <c r="N89" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O89" t="s">
         <v>0</v>
@@ -6064,33 +6031,33 @@
         <v>2000000</v>
       </c>
       <c r="Q89" t="s">
-        <v>199</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>59374776</v>
+        <v>58151683</v>
       </c>
       <c r="B90" s="2">
-        <v>46085.757662037038</v>
+        <v>46064.532222222224</v>
       </c>
       <c r="C90">
-        <v>60185369</v>
+        <v>60402173</v>
       </c>
       <c r="D90" s="2">
-        <v>46100.585393518515</v>
+        <v>46105.501574074071</v>
       </c>
       <c r="E90" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F90" t="s">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="G90">
-        <v>747726344</v>
+        <v>2721271444</v>
       </c>
       <c r="H90" t="s">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="I90" t="s">
         <v>0</v>
@@ -6105,63 +6072,63 @@
         <v>6</v>
       </c>
       <c r="M90" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N90" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O90" t="s">
         <v>0</v>
       </c>
-      <c r="P90" t="s">
-        <v>0</v>
+      <c r="P90" s="1">
+        <v>1495965</v>
       </c>
       <c r="Q90" t="s">
-        <v>166</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>59406146</v>
+        <v>58144220</v>
       </c>
       <c r="B91" s="2">
-        <v>46086.506643518522</v>
+        <v>46064.478425925925</v>
       </c>
       <c r="C91">
-        <v>60600544</v>
+        <v>60834741</v>
       </c>
       <c r="D91" s="2">
-        <v>46108.458136574074</v>
+        <v>46112.656956018516</v>
       </c>
       <c r="E91" t="s">
-        <v>10</v>
+        <v>285</v>
       </c>
       <c r="F91" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="G91">
-        <v>709136702</v>
+        <v>2722418166</v>
       </c>
       <c r="H91" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="I91" t="s">
         <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K91" t="s">
         <v>5</v>
       </c>
       <c r="L91" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M91" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N91" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="O91" t="s">
         <v>0</v>
@@ -6170,51 +6137,51 @@
         <v>0</v>
       </c>
       <c r="Q91" t="s">
-        <v>293</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>59406937</v>
+        <v>58096775</v>
       </c>
       <c r="B92" s="2">
-        <v>46086.512870370374</v>
+        <v>46063.603263888886</v>
       </c>
       <c r="C92">
-        <v>60616367</v>
+        <v>58655959</v>
       </c>
       <c r="D92" s="2">
-        <v>46108.587060185186</v>
+        <v>46073.525740740741</v>
       </c>
       <c r="E92" t="s">
-        <v>283</v>
+        <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>204</v>
+        <v>44</v>
       </c>
       <c r="G92">
-        <v>709136702</v>
+        <v>708086759</v>
       </c>
       <c r="H92" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="I92" t="s">
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K92" t="s">
         <v>5</v>
       </c>
       <c r="L92" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M92" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N92" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O92" t="s">
         <v>0</v>
@@ -6223,104 +6190,104 @@
         <v>0</v>
       </c>
       <c r="Q92" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>59409078</v>
+        <v>58093843</v>
       </c>
       <c r="B93" s="2">
-        <v>46086.529247685183</v>
+        <v>46063.583460648151</v>
       </c>
       <c r="C93">
-        <v>60600044</v>
+        <v>58667700</v>
       </c>
       <c r="D93" s="2">
-        <v>46108.453865740739</v>
+        <v>46073.611655092594</v>
       </c>
       <c r="E93" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>205</v>
+        <v>44</v>
       </c>
       <c r="G93">
-        <v>709140938</v>
+        <v>708086759</v>
       </c>
       <c r="H93" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="I93" t="s">
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K93" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L93" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M93" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N93" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O93" t="s">
         <v>0</v>
       </c>
-      <c r="P93" t="s">
+      <c r="P93">
         <v>0</v>
       </c>
       <c r="Q93" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>59409752</v>
+        <v>58093827</v>
       </c>
       <c r="B94" s="2">
-        <v>46086.534502314818</v>
+        <v>46063.583402777775</v>
       </c>
       <c r="C94">
-        <v>60600716</v>
+        <v>59486282</v>
       </c>
       <c r="D94" s="2">
-        <v>46108.459768518522</v>
+        <v>46087.591932870368</v>
       </c>
       <c r="E94" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>206</v>
+        <v>44</v>
       </c>
       <c r="G94">
-        <v>758700193</v>
+        <v>708086759</v>
       </c>
       <c r="H94" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="I94" t="s">
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K94" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L94" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M94" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N94" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O94" t="s">
         <v>0</v>
@@ -6329,210 +6296,210 @@
         <v>0</v>
       </c>
       <c r="Q94" t="s">
-        <v>73</v>
+        <v>148</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>59410212</v>
+        <v>58055656</v>
       </c>
       <c r="B95" s="2">
-        <v>46086.537708333337</v>
+        <v>46062.760023148148</v>
       </c>
       <c r="C95">
-        <v>59835857</v>
+        <v>60340320</v>
       </c>
       <c r="D95" s="2">
-        <v>46093.728726851848</v>
+        <v>46104.489583333336</v>
       </c>
       <c r="E95" t="s">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="F95" t="s">
-        <v>207</v>
+        <v>145</v>
       </c>
       <c r="G95">
-        <v>789018789</v>
+        <v>758224257</v>
       </c>
       <c r="H95" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="I95" t="s">
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K95" t="s">
-        <v>208</v>
+        <v>5</v>
       </c>
       <c r="L95" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M95" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N95" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O95" t="s">
         <v>0</v>
       </c>
-      <c r="P95" t="s">
-        <v>0</v>
+      <c r="P95" s="1">
+        <v>1800000</v>
       </c>
       <c r="Q95" t="s">
-        <v>173</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>59410843</v>
+        <v>57899728</v>
       </c>
       <c r="B96" s="2">
-        <v>46086.542870370373</v>
+        <v>46059.503668981481</v>
       </c>
       <c r="C96">
-        <v>60526566</v>
+        <v>60814923</v>
       </c>
       <c r="D96" s="2">
-        <v>46107.452592592592</v>
+        <v>46112.504664351851</v>
       </c>
       <c r="E96" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="F96" t="s">
-        <v>209</v>
+        <v>99</v>
       </c>
       <c r="G96">
-        <v>758700193</v>
+        <v>505980067</v>
       </c>
       <c r="H96" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="I96" t="s">
         <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K96" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L96" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M96" t="s">
         <v>3</v>
       </c>
       <c r="N96" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O96" t="s">
         <v>0</v>
       </c>
-      <c r="P96" t="s">
-        <v>0</v>
+      <c r="P96" s="1">
+        <v>1002937</v>
       </c>
       <c r="Q96" t="s">
-        <v>294</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>59414411</v>
+        <v>57849095</v>
       </c>
       <c r="B97" s="2">
-        <v>46086.57104166667</v>
+        <v>46058.603668981479</v>
       </c>
       <c r="C97">
-        <v>60601081</v>
+        <v>60388868</v>
       </c>
       <c r="D97" s="2">
-        <v>46108.462025462963</v>
+        <v>46105.385023148148</v>
       </c>
       <c r="E97" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F97" t="s">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="G97">
-        <v>566473307</v>
+        <v>707109668</v>
       </c>
       <c r="H97" t="s">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="I97" t="s">
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="K97" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L97" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M97" t="s">
         <v>3</v>
       </c>
       <c r="N97" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O97" t="s">
         <v>0</v>
       </c>
-      <c r="P97">
+      <c r="P97" t="s">
         <v>0</v>
       </c>
       <c r="Q97" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>59417066</v>
+        <v>57706849</v>
       </c>
       <c r="B98" s="2">
-        <v>46086.594525462962</v>
+        <v>46056.499166666668</v>
       </c>
       <c r="C98">
-        <v>60589286</v>
+        <v>59767932</v>
       </c>
       <c r="D98" s="2">
-        <v>46108.367418981485</v>
+        <v>46092.721273148149</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
       </c>
       <c r="F98" t="s">
-        <v>213</v>
+        <v>141</v>
       </c>
       <c r="G98">
-        <v>709565662</v>
+        <v>708086472</v>
       </c>
       <c r="H98" t="s">
-        <v>214</v>
+        <v>102</v>
       </c>
       <c r="I98" t="s">
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K98" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L98" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M98" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N98" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O98" t="s">
         <v>0</v>
@@ -6541,563 +6508,563 @@
         <v>0</v>
       </c>
       <c r="Q98" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>59464660</v>
+        <v>57692887</v>
       </c>
       <c r="B99" s="2">
-        <v>46087.421030092592</v>
+        <v>46056.394780092596</v>
       </c>
       <c r="C99">
-        <v>60601930</v>
+        <v>60516591</v>
       </c>
       <c r="D99" s="2">
-        <v>46108.467233796298</v>
+        <v>46107.377708333333</v>
       </c>
       <c r="E99" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F99" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="G99">
-        <v>554235979</v>
+        <v>707109668</v>
       </c>
       <c r="H99" t="s">
-        <v>128</v>
-      </c>
-      <c r="I99" t="s">
-        <v>0</v>
+        <v>265</v>
+      </c>
+      <c r="I99">
+        <v>1798816</v>
       </c>
       <c r="J99" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K99" t="s">
         <v>5</v>
       </c>
       <c r="L99" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M99" t="s">
         <v>7</v>
       </c>
       <c r="N99" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O99" t="s">
         <v>0</v>
       </c>
-      <c r="P99">
+      <c r="P99" t="s">
         <v>0</v>
       </c>
       <c r="Q99" t="s">
-        <v>34</v>
+        <v>266</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>59465071</v>
+        <v>57672103</v>
       </c>
       <c r="B100" s="2">
-        <v>46087.424062500002</v>
+        <v>46055.712083333332</v>
       </c>
       <c r="C100">
-        <v>60531474</v>
+        <v>58477217</v>
       </c>
       <c r="D100" s="2">
-        <v>46107.489861111113</v>
+        <v>46070.620787037034</v>
       </c>
       <c r="E100" t="s">
-        <v>295</v>
+        <v>126</v>
       </c>
       <c r="F100" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="G100">
-        <v>554235979</v>
+        <v>707079088</v>
       </c>
       <c r="H100" t="s">
-        <v>215</v>
+        <v>138</v>
       </c>
       <c r="I100" t="s">
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M100" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N100" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O100" t="s">
         <v>0</v>
       </c>
-      <c r="P100">
-        <v>0</v>
+      <c r="P100" s="1">
+        <v>1426700</v>
       </c>
       <c r="Q100" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>59466514</v>
+        <v>57651441</v>
       </c>
       <c r="B101" s="2">
-        <v>46087.436643518522</v>
+        <v>46055.58011574074</v>
       </c>
       <c r="C101">
-        <v>60602589</v>
+        <v>58955875</v>
       </c>
       <c r="D101" s="2">
-        <v>46108.472187500003</v>
+        <v>46078.639594907407</v>
       </c>
       <c r="E101" t="s">
-        <v>296</v>
+        <v>126</v>
       </c>
       <c r="F101" t="s">
-        <v>216</v>
+        <v>134</v>
       </c>
       <c r="G101">
-        <v>141679210</v>
+        <v>707079088</v>
       </c>
       <c r="H101" t="s">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="I101" t="s">
         <v>0</v>
       </c>
       <c r="J101" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K101" t="s">
         <v>5</v>
       </c>
       <c r="L101" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M101" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N101" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O101" t="s">
         <v>0</v>
       </c>
-      <c r="P101" s="1">
-        <v>3213390</v>
+      <c r="P101" t="s">
+        <v>136</v>
       </c>
       <c r="Q101" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>59466778</v>
+        <v>57398181</v>
       </c>
       <c r="B102" s="2">
-        <v>46087.438715277778</v>
+        <v>46050.584374999999</v>
       </c>
       <c r="C102">
-        <v>60553947</v>
+        <v>60344342</v>
       </c>
       <c r="D102" s="2">
-        <v>46107.648668981485</v>
+        <v>46104.528900462959</v>
       </c>
       <c r="E102" t="s">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="F102" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="G102">
-        <v>554235979</v>
+        <v>720631500</v>
       </c>
       <c r="H102" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="I102" t="s">
         <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K102" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L102" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M102" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N102" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O102" t="s">
         <v>0</v>
       </c>
-      <c r="P102" t="s">
-        <v>0</v>
+      <c r="P102" s="1">
+        <v>4406780</v>
       </c>
       <c r="Q102" t="s">
-        <v>294</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>59468518</v>
+        <v>56970346</v>
       </c>
       <c r="B103" s="2">
-        <v>46087.450266203705</v>
+        <v>46042.557280092595</v>
       </c>
       <c r="C103">
-        <v>60601750</v>
+        <v>59242054</v>
       </c>
       <c r="D103" s="2">
-        <v>46108.466053240743</v>
+        <v>46083.719525462962</v>
       </c>
       <c r="E103" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F103" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G103">
-        <v>554235979</v>
+        <v>708667658</v>
       </c>
       <c r="H103" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I103" t="s">
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K103" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L103" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M103" t="s">
         <v>3</v>
       </c>
       <c r="N103" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O103" t="s">
         <v>0</v>
       </c>
-      <c r="P103" t="s">
-        <v>0</v>
+      <c r="P103" s="1">
+        <v>2871414</v>
       </c>
       <c r="Q103" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>59469589</v>
+        <v>56675050</v>
       </c>
       <c r="B104" s="2">
-        <v>46087.458460648151</v>
+        <v>46036.516423611109</v>
       </c>
       <c r="C104">
-        <v>60601477</v>
+        <v>58216664</v>
       </c>
       <c r="D104" s="2">
-        <v>46108.464641203704</v>
+        <v>46065.536226851851</v>
       </c>
       <c r="E104" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F104" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G104">
-        <v>554235979</v>
+        <v>748512613</v>
       </c>
       <c r="H104" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I104" t="s">
         <v>0</v>
       </c>
       <c r="J104" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K104" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L104" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M104" t="s">
         <v>3</v>
       </c>
       <c r="N104" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O104" t="s">
         <v>0</v>
       </c>
-      <c r="P104" t="s">
-        <v>0</v>
+      <c r="P104" s="1">
+        <v>4362401</v>
       </c>
       <c r="Q104" t="s">
-        <v>166</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>59480507</v>
+        <v>56618123</v>
       </c>
       <c r="B105" s="2">
-        <v>46087.544247685182</v>
+        <v>46035.520821759259</v>
       </c>
       <c r="C105">
-        <v>60564140</v>
+        <v>59311833</v>
       </c>
       <c r="D105" s="2">
-        <v>46107.723194444443</v>
+        <v>46084.811782407407</v>
       </c>
       <c r="E105" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="F105" t="s">
-        <v>217</v>
+        <v>123</v>
       </c>
       <c r="G105">
-        <v>708547070</v>
+        <v>504041812</v>
       </c>
       <c r="H105" t="s">
-        <v>92</v>
-      </c>
-      <c r="I105" t="s">
-        <v>0</v>
+        <v>189</v>
+      </c>
+      <c r="I105">
+        <v>1775236</v>
       </c>
       <c r="J105" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K105" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L105" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M105" t="s">
         <v>3</v>
       </c>
       <c r="N105" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O105" t="s">
         <v>0</v>
       </c>
-      <c r="P105" t="s">
-        <v>0</v>
+      <c r="P105" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q105" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>59495473</v>
+        <v>56613961</v>
       </c>
       <c r="B106" s="2">
-        <v>46087.653935185182</v>
+        <v>46035.492175925923</v>
       </c>
       <c r="C106">
-        <v>60551423</v>
+        <v>59754685</v>
       </c>
       <c r="D106" s="2">
-        <v>46107.631689814814</v>
+        <v>46092.626307870371</v>
       </c>
       <c r="E106" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="F106" t="s">
-        <v>218</v>
+        <v>117</v>
       </c>
       <c r="G106">
-        <v>506727287</v>
+        <v>504041812</v>
       </c>
       <c r="H106" t="s">
-        <v>219</v>
+        <v>121</v>
       </c>
       <c r="I106" t="s">
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M106" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N106" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O106" t="s">
         <v>0</v>
       </c>
-      <c r="P106">
-        <v>0</v>
+      <c r="P106" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q106" t="s">
-        <v>297</v>
+        <v>122</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>59498233</v>
+        <v>56612479</v>
       </c>
       <c r="B107" s="2">
-        <v>46087.67423611111</v>
+        <v>46035.481446759259</v>
       </c>
       <c r="C107">
-        <v>59693004</v>
+        <v>60101226</v>
       </c>
       <c r="D107" s="2">
-        <v>46091.627928240741</v>
+        <v>46099.43613425926</v>
       </c>
       <c r="E107" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="F107" t="s">
-        <v>218</v>
+        <v>117</v>
       </c>
       <c r="G107">
-        <v>606727287</v>
+        <v>504041812</v>
       </c>
       <c r="H107" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="I107" t="s">
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K107" t="s">
-        <v>220</v>
+        <v>5</v>
       </c>
       <c r="L107" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M107" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N107" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O107" t="s">
         <v>0</v>
       </c>
-      <c r="P107">
-        <v>0</v>
+      <c r="P107" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q107" t="s">
-        <v>0</v>
+        <v>181</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>59537755</v>
+        <v>56611212</v>
       </c>
       <c r="B108" s="2">
-        <v>46088.586631944447</v>
+        <v>46035.471886574072</v>
       </c>
       <c r="C108">
-        <v>59807640</v>
+        <v>57137676</v>
       </c>
       <c r="D108" s="2">
-        <v>46093.511296296296</v>
+        <v>46045.45140046296</v>
       </c>
       <c r="E108" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="F108" t="s">
-        <v>221</v>
+        <v>117</v>
       </c>
       <c r="G108">
-        <v>556331131</v>
+        <v>504041812</v>
       </c>
       <c r="H108" t="s">
-        <v>221</v>
+        <v>118</v>
       </c>
       <c r="I108" t="s">
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K108" t="s">
-        <v>222</v>
+        <v>5</v>
       </c>
       <c r="L108" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M108" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N108" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O108" t="s">
         <v>0</v>
       </c>
-      <c r="P108">
-        <v>0</v>
+      <c r="P108" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q108" t="s">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>59538099</v>
+        <v>56609018</v>
       </c>
       <c r="B109" s="2">
-        <v>46088.590717592589</v>
+        <v>46035.452465277776</v>
       </c>
       <c r="C109">
-        <v>60033812</v>
+        <v>60165633</v>
       </c>
       <c r="D109" s="2">
-        <v>46098.426782407405</v>
+        <v>46100.43891203704</v>
       </c>
       <c r="E109" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F109" t="s">
-        <v>223</v>
+        <v>113</v>
       </c>
       <c r="G109">
-        <v>566473307</v>
+        <v>504041812</v>
       </c>
       <c r="H109" t="s">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="I109" t="s">
         <v>0</v>
@@ -7114,40 +7081,43 @@
       <c r="M109" t="s">
         <v>3</v>
       </c>
+      <c r="N109" t="s">
+        <v>188</v>
+      </c>
       <c r="O109" t="s">
         <v>0</v>
       </c>
-      <c r="P109">
-        <v>0</v>
+      <c r="P109" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q109" t="s">
-        <v>243</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110">
-        <v>59538597</v>
+        <v>56607988</v>
       </c>
       <c r="B110" s="2">
-        <v>46088.598194444443</v>
+        <v>46035.443668981483</v>
       </c>
       <c r="C110">
-        <v>60030833</v>
+        <v>58404447</v>
       </c>
       <c r="D110" s="2">
-        <v>46098.40320601852</v>
+        <v>46069.522615740738</v>
       </c>
       <c r="E110" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="F110" t="s">
-        <v>223</v>
+        <v>113</v>
       </c>
       <c r="G110">
-        <v>566473307</v>
+        <v>504041812</v>
       </c>
       <c r="H110" t="s">
-        <v>224</v>
+        <v>115</v>
       </c>
       <c r="I110" t="s">
         <v>0</v>
@@ -7164,252 +7134,255 @@
       <c r="M110" t="s">
         <v>3</v>
       </c>
+      <c r="N110" t="s">
+        <v>188</v>
+      </c>
       <c r="O110" t="s">
         <v>0</v>
       </c>
-      <c r="P110">
-        <v>0</v>
+      <c r="P110" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q110" t="s">
-        <v>243</v>
+        <v>107</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111">
-        <v>59541145</v>
+        <v>56606469</v>
       </c>
       <c r="B111" s="2">
-        <v>46088.634837962964</v>
+        <v>46035.43072916667</v>
       </c>
       <c r="C111">
-        <v>59799803</v>
+        <v>60100048</v>
       </c>
       <c r="D111" s="2">
-        <v>46093.453530092593</v>
+        <v>46099.427060185182</v>
       </c>
       <c r="E111" t="s">
-        <v>20</v>
+        <v>283</v>
       </c>
       <c r="F111" t="s">
-        <v>225</v>
+        <v>113</v>
       </c>
       <c r="G111">
-        <v>546008131</v>
+        <v>504041812</v>
       </c>
       <c r="H111" t="s">
-        <v>226</v>
+        <v>42</v>
       </c>
       <c r="I111" t="s">
         <v>0</v>
       </c>
       <c r="J111" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K111" t="s">
-        <v>222</v>
+        <v>5</v>
       </c>
       <c r="L111" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M111" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N111" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O111" t="s">
         <v>0</v>
       </c>
-      <c r="P111">
-        <v>0</v>
+      <c r="P111" s="1">
+        <v>1000000</v>
       </c>
       <c r="Q111" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112">
-        <v>59606122</v>
+        <v>56603495</v>
       </c>
       <c r="B112" s="2">
-        <v>46090.447604166664</v>
+        <v>46035.408518518518</v>
       </c>
       <c r="C112">
-        <v>59682305</v>
+        <v>59831107</v>
       </c>
       <c r="D112" s="2">
-        <v>46091.541701388887</v>
+        <v>46093.691342592596</v>
       </c>
       <c r="E112" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F112" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="G112">
-        <v>708454305</v>
+        <v>707003126</v>
       </c>
       <c r="H112" t="s">
-        <v>228</v>
+        <v>114</v>
       </c>
       <c r="I112" t="s">
         <v>0</v>
       </c>
       <c r="J112" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K112" t="s">
-        <v>222</v>
+        <v>5</v>
       </c>
       <c r="L112" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M112" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N112" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O112" t="s">
         <v>0</v>
       </c>
-      <c r="P112">
-        <v>0</v>
+      <c r="P112" s="1">
+        <v>7103410</v>
       </c>
       <c r="Q112" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113">
-        <v>59615935</v>
+        <v>56601982</v>
       </c>
       <c r="B113" s="2">
-        <v>46090.512303240743</v>
+        <v>46035.393611111111</v>
       </c>
       <c r="C113">
-        <v>60393405</v>
+        <v>60341610</v>
       </c>
       <c r="D113" s="2">
-        <v>46105.432800925926</v>
+        <v>46104.501319444447</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
       </c>
       <c r="F113" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="G113">
-        <v>767081456</v>
+        <v>707003126</v>
       </c>
       <c r="H113" t="s">
-        <v>230</v>
+        <v>112</v>
       </c>
       <c r="I113" t="s">
         <v>0</v>
       </c>
       <c r="J113" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K113" t="s">
         <v>5</v>
       </c>
       <c r="L113" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M113" t="s">
         <v>3</v>
       </c>
       <c r="N113" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O113" t="s">
         <v>0</v>
       </c>
-      <c r="P113">
-        <v>0</v>
+      <c r="P113" s="1">
+        <v>7103410</v>
       </c>
       <c r="Q113" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114">
-        <v>59684312</v>
+        <v>56181778</v>
       </c>
       <c r="B114" s="2">
-        <v>46091.557453703703</v>
+        <v>46027.499212962961</v>
       </c>
       <c r="C114">
-        <v>59736324</v>
+        <v>59210339</v>
       </c>
       <c r="D114" s="2">
-        <v>46092.496296296296</v>
+        <v>46083.492881944447</v>
       </c>
       <c r="E114" t="s">
-        <v>234</v>
+        <v>126</v>
       </c>
       <c r="F114" t="s">
-        <v>231</v>
+        <v>108</v>
       </c>
       <c r="G114">
-        <v>3130227350</v>
+        <v>585990976</v>
       </c>
       <c r="H114" t="s">
-        <v>232</v>
-      </c>
-      <c r="I114" t="s">
-        <v>0</v>
+        <v>109</v>
+      </c>
+      <c r="I114">
+        <v>1765416</v>
       </c>
       <c r="J114" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K114" t="s">
         <v>5</v>
       </c>
       <c r="L114" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M114" t="s">
         <v>3</v>
       </c>
       <c r="N114" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O114" t="s">
         <v>0</v>
       </c>
-      <c r="P114" t="s">
-        <v>0</v>
+      <c r="P114" s="1">
+        <v>3000000</v>
       </c>
       <c r="Q114" t="s">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115">
-        <v>59793967</v>
+        <v>55694485</v>
       </c>
       <c r="B115" s="2">
-        <v>46093.406724537039</v>
+        <v>46015.420092592591</v>
       </c>
       <c r="C115">
-        <v>60225840</v>
+        <v>56752240</v>
       </c>
       <c r="D115" s="2">
-        <v>46101.328912037039</v>
+        <v>46037.705520833333</v>
       </c>
       <c r="E115" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F115" t="s">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="G115">
-        <v>506727287</v>
+        <v>749338073</v>
       </c>
       <c r="H115" t="s">
-        <v>219</v>
+        <v>106</v>
       </c>
       <c r="I115" t="s">
         <v>0</v>
@@ -7424,45 +7397,45 @@
         <v>6</v>
       </c>
       <c r="M115" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N115" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O115" t="s">
         <v>0</v>
       </c>
-      <c r="P115">
-        <v>0</v>
+      <c r="P115" s="1">
+        <v>638462</v>
       </c>
       <c r="Q115" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116">
-        <v>59801109</v>
+        <v>55686160</v>
       </c>
       <c r="B116" s="2">
-        <v>46093.464594907404</v>
+        <v>46015.355868055558</v>
       </c>
       <c r="C116">
-        <v>60611654</v>
+        <v>60490199</v>
       </c>
       <c r="D116" s="2">
-        <v>46108.541504629633</v>
+        <v>46106.680219907408</v>
       </c>
       <c r="E116" t="s">
         <v>29</v>
       </c>
       <c r="F116" t="s">
-        <v>245</v>
+        <v>104</v>
       </c>
       <c r="G116">
-        <v>709173657</v>
+        <v>777765287</v>
       </c>
       <c r="H116" t="s">
-        <v>246</v>
+        <v>66</v>
       </c>
       <c r="I116" t="s">
         <v>0</v>
@@ -7471,51 +7444,51 @@
         <v>13</v>
       </c>
       <c r="K116" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L116" t="s">
         <v>6</v>
       </c>
       <c r="M116" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N116" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O116" t="s">
         <v>0</v>
       </c>
-      <c r="P116">
-        <v>0</v>
+      <c r="P116" s="1">
+        <v>850887</v>
       </c>
       <c r="Q116" t="s">
-        <v>298</v>
+        <v>248</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117">
-        <v>59813505</v>
+        <v>55636282</v>
       </c>
       <c r="B117" s="2">
-        <v>46093.557256944441</v>
+        <v>46014.435729166667</v>
       </c>
       <c r="C117">
-        <v>60137642</v>
+        <v>57367586</v>
       </c>
       <c r="D117" s="2">
-        <v>46099.71303240741</v>
+        <v>46049.856261574074</v>
       </c>
       <c r="E117" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="F117" t="s">
-        <v>247</v>
+        <v>103</v>
       </c>
       <c r="G117">
-        <v>706727287</v>
+        <v>759003900</v>
       </c>
       <c r="H117" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
       <c r="I117" t="s">
         <v>0</v>
@@ -7524,157 +7497,157 @@
         <v>13</v>
       </c>
       <c r="K117" t="s">
-        <v>222</v>
+        <v>5</v>
       </c>
       <c r="L117" t="s">
         <v>6</v>
       </c>
       <c r="M117" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N117" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O117" t="s">
         <v>0</v>
       </c>
-      <c r="P117">
-        <v>0</v>
+      <c r="P117" s="1">
+        <v>918681</v>
       </c>
       <c r="Q117" t="s">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118">
-        <v>59816396</v>
+        <v>55105103</v>
       </c>
       <c r="B118" s="2">
-        <v>46093.580590277779</v>
+        <v>46004.481180555558</v>
       </c>
       <c r="C118">
-        <v>60137506</v>
+        <v>56940307</v>
       </c>
       <c r="D118" s="2">
-        <v>46099.711053240739</v>
+        <v>46041.803784722222</v>
       </c>
       <c r="E118" t="s">
-        <v>155</v>
+        <v>16</v>
       </c>
       <c r="F118" t="s">
-        <v>249</v>
+        <v>88</v>
       </c>
       <c r="G118">
-        <v>506727287</v>
+        <v>504033918</v>
       </c>
       <c r="H118" t="s">
-        <v>267</v>
-      </c>
-      <c r="I118">
-        <v>1848446</v>
+        <v>100</v>
+      </c>
+      <c r="I118" t="s">
+        <v>0</v>
       </c>
       <c r="J118" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K118" t="s">
-        <v>222</v>
+        <v>5</v>
       </c>
       <c r="L118" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M118" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N118" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="O118" t="s">
         <v>0</v>
       </c>
-      <c r="P118">
-        <v>0</v>
+      <c r="P118" s="1">
+        <v>1500000</v>
       </c>
       <c r="Q118" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119">
-        <v>59820678</v>
+        <v>55104019</v>
       </c>
       <c r="B119" s="2">
-        <v>46093.612222222226</v>
+        <v>46004.469606481478</v>
       </c>
       <c r="C119">
-        <v>60208764</v>
+        <v>56566265</v>
       </c>
       <c r="D119" s="2">
-        <v>46100.766909722224</v>
+        <v>46034.582673611112</v>
       </c>
       <c r="E119" t="s">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="F119" t="s">
-        <v>250</v>
+        <v>88</v>
       </c>
       <c r="G119">
-        <v>506727287</v>
+        <v>504033918</v>
       </c>
       <c r="H119" t="s">
-        <v>251</v>
+        <v>31</v>
       </c>
       <c r="I119" t="s">
         <v>0</v>
       </c>
       <c r="J119" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K119" t="s">
-        <v>222</v>
+        <v>5</v>
       </c>
       <c r="L119" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M119" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N119" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O119" t="s">
         <v>0</v>
       </c>
-      <c r="P119">
-        <v>0</v>
+      <c r="P119" s="1">
+        <v>4000000</v>
       </c>
       <c r="Q119" t="s">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120">
-        <v>59821965</v>
+        <v>54973689</v>
       </c>
       <c r="B120" s="2">
-        <v>46093.621331018519</v>
+        <v>46002.496215277781</v>
       </c>
       <c r="C120">
-        <v>60495824</v>
+        <v>60812547</v>
       </c>
       <c r="D120" s="2">
-        <v>46106.725034722222</v>
+        <v>46112.487685185188</v>
       </c>
       <c r="E120" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="F120" t="s">
-        <v>252</v>
+        <v>89</v>
       </c>
       <c r="G120">
-        <v>101383885</v>
+        <v>789916125</v>
       </c>
       <c r="H120" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="I120" t="s">
         <v>0</v>
@@ -7689,169 +7662,169 @@
         <v>6</v>
       </c>
       <c r="M120" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="N120" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="O120" t="s">
         <v>0</v>
       </c>
-      <c r="P120" s="1">
-        <v>3000000</v>
+      <c r="P120">
+        <v>0</v>
       </c>
       <c r="Q120" t="s">
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121">
-        <v>59824550</v>
+        <v>54970719</v>
       </c>
       <c r="B121" s="2">
-        <v>46093.6405787037</v>
+        <v>46002.47859953704</v>
       </c>
       <c r="C121">
-        <v>60530213</v>
+        <v>56201571</v>
       </c>
       <c r="D121" s="2">
-        <v>46107.478576388887</v>
+        <v>46027.649004629631</v>
       </c>
       <c r="E121" t="s">
-        <v>296</v>
+        <v>16</v>
       </c>
       <c r="F121" t="s">
-        <v>253</v>
+        <v>96</v>
       </c>
       <c r="G121">
-        <v>506727287</v>
+        <v>504033918</v>
       </c>
       <c r="H121" t="s">
-        <v>254</v>
-      </c>
-      <c r="I121" t="s">
-        <v>0</v>
+        <v>97</v>
+      </c>
+      <c r="I121">
+        <v>2843545</v>
       </c>
       <c r="J121" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K121" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L121" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M121" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="N121" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O121" t="s">
         <v>0</v>
       </c>
-      <c r="P121">
-        <v>0</v>
+      <c r="P121" s="1">
+        <v>1000000</v>
       </c>
       <c r="Q121" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>59888143</v>
+        <v>54967903</v>
       </c>
       <c r="B122" s="2">
-        <v>46094.646597222221</v>
+        <v>46002.459837962961</v>
       </c>
       <c r="C122">
-        <v>60622376</v>
+        <v>59197300</v>
       </c>
       <c r="D122" s="2">
-        <v>46108.63175925926</v>
+        <v>46083.390844907408</v>
       </c>
       <c r="E122" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F122" t="s">
-        <v>255</v>
+        <v>96</v>
       </c>
       <c r="G122">
-        <v>708858866</v>
+        <v>504033918</v>
       </c>
       <c r="H122" t="s">
-        <v>256</v>
-      </c>
-      <c r="I122" t="s">
-        <v>0</v>
+        <v>128</v>
+      </c>
+      <c r="I122">
+        <v>1814616</v>
       </c>
       <c r="J122" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K122" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="L122" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M122" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="N122" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O122" t="s">
         <v>0</v>
       </c>
-      <c r="P122" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q122">
-        <v>2720219745</v>
+      <c r="P122" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123">
-        <v>59894743</v>
+        <v>54793554</v>
       </c>
       <c r="B123" s="2">
-        <v>46094.687673611108</v>
+        <v>45999.637916666667</v>
       </c>
       <c r="C123">
-        <v>60454133</v>
+        <v>59895786</v>
       </c>
       <c r="D123" s="2">
-        <v>46106.366770833331</v>
+        <v>46094.6953125</v>
       </c>
       <c r="E123" t="s">
-        <v>10</v>
+        <v>247</v>
       </c>
       <c r="F123" t="s">
-        <v>257</v>
+        <v>70</v>
       </c>
       <c r="G123">
-        <v>759668146</v>
+        <v>757323203</v>
       </c>
       <c r="H123" t="s">
-        <v>43</v>
+        <v>246</v>
       </c>
       <c r="I123" t="s">
         <v>0</v>
       </c>
       <c r="J123" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K123" t="s">
         <v>5</v>
       </c>
       <c r="L123" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M123" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N123" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O123" t="s">
         <v>0</v>
@@ -7860,422 +7833,422 @@
         <v>0</v>
       </c>
       <c r="Q123" t="s">
-        <v>35</v>
+        <v>174</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124">
-        <v>59894758</v>
+        <v>54449048</v>
       </c>
       <c r="B124" s="2">
-        <v>46094.687719907408</v>
+        <v>45992.706157407411</v>
       </c>
       <c r="C124">
-        <v>60616207</v>
+        <v>56341749</v>
       </c>
       <c r="D124" s="2">
-        <v>46108.585763888892</v>
+        <v>46029.685115740744</v>
       </c>
       <c r="E124" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="F124" t="s">
-        <v>257</v>
+        <v>41</v>
       </c>
       <c r="G124">
-        <v>759668146</v>
+        <v>708086759</v>
       </c>
       <c r="H124" t="s">
-        <v>268</v>
-      </c>
-      <c r="I124">
-        <v>1849216</v>
+        <v>86</v>
+      </c>
+      <c r="I124" t="s">
+        <v>0</v>
       </c>
       <c r="J124" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K124" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L124" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M124" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N124" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O124" t="s">
         <v>0</v>
       </c>
-      <c r="P124" s="1">
-        <v>1000000</v>
+      <c r="P124" t="s">
+        <v>0</v>
       </c>
       <c r="Q124" t="s">
-        <v>299</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125">
-        <v>60026486</v>
+        <v>54178346</v>
       </c>
       <c r="B125" s="2">
-        <v>46098.36173611111</v>
+        <v>45987.646099537036</v>
       </c>
       <c r="C125">
-        <v>60121930</v>
+        <v>59755436</v>
       </c>
       <c r="D125" s="2">
-        <v>46099.594039351854</v>
+        <v>46092.631111111114</v>
       </c>
       <c r="E125" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>244</v>
+        <v>70</v>
       </c>
       <c r="G125">
-        <v>506727287</v>
+        <v>757323203</v>
       </c>
       <c r="H125" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="I125" t="s">
         <v>0</v>
       </c>
       <c r="J125" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K125" t="s">
-        <v>222</v>
+        <v>5</v>
       </c>
       <c r="L125" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M125" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N125" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O125" t="s">
         <v>0</v>
       </c>
-      <c r="P125">
+      <c r="P125" t="s">
         <v>0</v>
       </c>
       <c r="Q125" t="s">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126">
-        <v>60084243</v>
+        <v>53899369</v>
       </c>
       <c r="B126" s="2">
-        <v>46098.817627314813</v>
+        <v>45981.827430555553</v>
       </c>
       <c r="C126">
-        <v>60622487</v>
+        <v>55146678</v>
       </c>
       <c r="D126" s="2">
-        <v>46108.632453703707</v>
+        <v>46005.762916666667</v>
       </c>
       <c r="E126" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F126" t="s">
-        <v>259</v>
+        <v>32</v>
       </c>
       <c r="G126">
-        <v>707708502</v>
+        <v>707003126</v>
       </c>
       <c r="H126" t="s">
-        <v>43</v>
-      </c>
-      <c r="I126">
+        <v>82</v>
+      </c>
+      <c r="I126" t="s">
         <v>0</v>
       </c>
       <c r="J126" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K126" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="L126" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M126" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N126" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O126" t="s">
         <v>0</v>
       </c>
-      <c r="P126" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>2722487090</v>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127">
-        <v>60154802</v>
+        <v>53790357</v>
       </c>
       <c r="B127" s="2">
-        <v>46100.305405092593</v>
+        <v>45980.438298611109</v>
       </c>
       <c r="C127">
-        <v>60613032</v>
+        <v>60457171</v>
       </c>
       <c r="D127" s="2">
-        <v>46108.555520833332</v>
+        <v>46106.402766203704</v>
       </c>
       <c r="E127" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F127" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="G127">
-        <v>707225975</v>
+        <v>708336404</v>
       </c>
       <c r="H127" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="I127" t="s">
         <v>0</v>
       </c>
       <c r="J127" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K127" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="L127" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M127" t="s">
         <v>3</v>
       </c>
       <c r="N127" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O127" t="s">
         <v>0</v>
       </c>
-      <c r="P127" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>2722520140</v>
+      <c r="P127" s="1">
+        <v>4430307</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128">
-        <v>60190035</v>
+        <v>53749839</v>
       </c>
       <c r="B128" s="2">
-        <v>46100.619201388887</v>
+        <v>45979.600694444445</v>
       </c>
       <c r="C128">
-        <v>60600359</v>
+        <v>60751264</v>
       </c>
       <c r="D128" s="2">
-        <v>46108.456620370373</v>
+        <v>46111.528391203705</v>
       </c>
       <c r="E128" t="s">
-        <v>296</v>
+        <v>10</v>
       </c>
       <c r="F128" t="s">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="G128">
-        <v>708142290</v>
+        <v>703333988</v>
       </c>
       <c r="H128" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="I128" t="s">
         <v>0</v>
       </c>
       <c r="J128" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="K128" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L128" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M128" t="s">
         <v>3</v>
       </c>
       <c r="N128" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O128" t="s">
         <v>0</v>
       </c>
-      <c r="P128" t="s">
-        <v>0</v>
+      <c r="P128" s="1">
+        <v>10000000</v>
       </c>
       <c r="Q128" t="s">
-        <v>173</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129">
-        <v>60356605</v>
+        <v>53702282</v>
       </c>
       <c r="B129" s="2">
-        <v>46104.623726851853</v>
+        <v>45978.671550925923</v>
       </c>
       <c r="C129">
-        <v>60604386</v>
+        <v>54614316</v>
       </c>
       <c r="D129" s="2">
-        <v>46108.484166666669</v>
+        <v>45995.632673611108</v>
       </c>
       <c r="E129" t="s">
-        <v>296</v>
+        <v>10</v>
       </c>
       <c r="F129" t="s">
-        <v>270</v>
+        <v>43</v>
       </c>
       <c r="G129">
-        <v>504001081</v>
+        <v>778036533</v>
       </c>
       <c r="H129" t="s">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="I129" t="s">
         <v>0</v>
       </c>
       <c r="J129" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K129" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L129" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M129" t="s">
         <v>3</v>
       </c>
       <c r="N129" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O129" t="s">
         <v>0</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="s">
-        <v>166</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130">
-        <v>60358121</v>
+        <v>52808171</v>
       </c>
       <c r="B130" s="2">
-        <v>46104.633344907408</v>
+        <v>45960.452361111114</v>
       </c>
       <c r="C130">
-        <v>60603382</v>
+        <v>59829408</v>
       </c>
       <c r="D130" s="2">
-        <v>46108.477407407408</v>
+        <v>46093.677152777775</v>
       </c>
       <c r="E130" t="s">
-        <v>296</v>
+        <v>10</v>
       </c>
       <c r="F130" t="s">
-        <v>270</v>
+        <v>69</v>
       </c>
       <c r="G130">
-        <v>504001081</v>
+        <v>709738605</v>
       </c>
       <c r="H130" t="s">
-        <v>273</v>
-      </c>
-      <c r="I130" t="s">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="I130">
+        <v>2793645</v>
       </c>
       <c r="J130" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K130" t="s">
         <v>5</v>
       </c>
       <c r="L130" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M130" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N130" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O130" t="s">
         <v>0</v>
       </c>
-      <c r="P130" s="1">
-        <v>500000</v>
+      <c r="P130" t="s">
+        <v>0</v>
       </c>
       <c r="Q130" t="s">
-        <v>297</v>
+        <v>76</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131">
-        <v>60395491</v>
+        <v>52778382</v>
       </c>
       <c r="B131" s="2">
-        <v>46105.449062500003</v>
+        <v>45959.67696759259</v>
       </c>
       <c r="C131">
-        <v>60600791</v>
+        <v>55073470</v>
       </c>
       <c r="D131" s="2">
-        <v>46108.460127314815</v>
+        <v>46003.678194444445</v>
       </c>
       <c r="E131" t="s">
-        <v>296</v>
+        <v>10</v>
       </c>
       <c r="F131" t="s">
-        <v>274</v>
+        <v>44</v>
       </c>
       <c r="G131">
-        <v>767747841</v>
+        <v>708086759</v>
       </c>
       <c r="H131" t="s">
-        <v>191</v>
+        <v>71</v>
       </c>
       <c r="I131">
-        <v>0</v>
+        <v>2788625</v>
       </c>
       <c r="J131" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K131" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L131" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M131" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="N131" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O131" t="s">
         <v>0</v>
@@ -8284,33 +8257,33 @@
         <v>0</v>
       </c>
       <c r="Q131" t="s">
-        <v>173</v>
+        <v>35</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132">
-        <v>60399905</v>
+        <v>52691553</v>
       </c>
       <c r="B132" s="2">
-        <v>46105.484120370369</v>
+        <v>45958.456122685187</v>
       </c>
       <c r="C132">
-        <v>60603082</v>
+        <v>59242377</v>
       </c>
       <c r="D132" s="2">
-        <v>46108.474965277775</v>
+        <v>46083.722071759257</v>
       </c>
       <c r="E132" t="s">
-        <v>296</v>
+        <v>10</v>
       </c>
       <c r="F132" t="s">
-        <v>275</v>
+        <v>67</v>
       </c>
       <c r="G132">
-        <v>504001081</v>
+        <v>708473548</v>
       </c>
       <c r="H132" t="s">
-        <v>276</v>
+        <v>68</v>
       </c>
       <c r="I132" t="s">
         <v>0</v>
@@ -8319,16 +8292,16 @@
         <v>13</v>
       </c>
       <c r="K132" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L132" t="s">
         <v>6</v>
       </c>
       <c r="M132" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N132" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O132" t="s">
         <v>0</v>
@@ -8337,263 +8310,260 @@
         <v>1000000</v>
       </c>
       <c r="Q132" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133">
-        <v>60410207</v>
+        <v>52561777</v>
       </c>
       <c r="B133" s="2">
-        <v>46105.573414351849</v>
+        <v>45954.649918981479</v>
       </c>
       <c r="C133">
-        <v>60520322</v>
+        <v>60344171</v>
       </c>
       <c r="D133" s="2">
-        <v>46107.405590277776</v>
+        <v>46104.526550925926</v>
       </c>
       <c r="E133" t="s">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="F133" t="s">
-        <v>277</v>
+        <v>64</v>
       </c>
       <c r="G133">
-        <v>709254356</v>
+        <v>708086759</v>
       </c>
       <c r="H133" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="I133" t="s">
         <v>0</v>
       </c>
       <c r="J133" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K133" t="s">
         <v>5</v>
       </c>
       <c r="L133" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M133" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N133" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O133" t="s">
         <v>0</v>
       </c>
-      <c r="P133" s="1">
-        <v>2000000</v>
+      <c r="P133" t="s">
+        <v>0</v>
       </c>
       <c r="Q133" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134">
-        <v>60416636</v>
+        <v>52448985</v>
       </c>
       <c r="B134" s="2">
-        <v>46105.623402777775</v>
+        <v>45952.656354166669</v>
       </c>
       <c r="C134">
-        <v>60519385</v>
+        <v>60421537</v>
       </c>
       <c r="D134" s="2">
-        <v>46107.397152777776</v>
+        <v>46105.662175925929</v>
       </c>
       <c r="E134" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="F134" t="s">
-        <v>278</v>
+        <v>45</v>
       </c>
       <c r="G134">
-        <v>172818143</v>
+        <v>708086759</v>
       </c>
       <c r="H134" t="s">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="I134" t="s">
         <v>0</v>
       </c>
       <c r="J134" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K134" t="s">
         <v>5</v>
       </c>
       <c r="L134" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M134" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N134" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O134" t="s">
         <v>0</v>
       </c>
-      <c r="P134" s="1">
-        <v>500000</v>
+      <c r="P134" t="s">
+        <v>0</v>
       </c>
       <c r="Q134" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A135">
-        <v>60422373</v>
+        <v>51760632</v>
       </c>
       <c r="B135" s="2">
-        <v>46105.667442129627</v>
+        <v>45938.521469907406</v>
       </c>
       <c r="C135">
-        <v>60616433</v>
+        <v>59332667</v>
       </c>
       <c r="D135" s="2">
-        <v>46108.587754629632</v>
+        <v>46085.453263888892</v>
       </c>
       <c r="E135" t="s">
-        <v>283</v>
+        <v>126</v>
       </c>
       <c r="F135" t="s">
-        <v>279</v>
+        <v>36</v>
       </c>
       <c r="G135">
-        <v>787670708</v>
+        <v>556999292</v>
       </c>
       <c r="H135" t="s">
-        <v>280</v>
+        <v>94</v>
       </c>
       <c r="I135" t="s">
         <v>0</v>
       </c>
       <c r="J135" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K135" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L135" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M135" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="N135" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O135" t="s">
         <v>0</v>
       </c>
-      <c r="P135" s="1">
-        <v>5324000</v>
+      <c r="P135" t="s">
+        <v>0</v>
       </c>
       <c r="Q135" t="s">
-        <v>297</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A136">
-        <v>60423011</v>
+        <v>48847621</v>
       </c>
       <c r="B136" s="2">
-        <v>46105.672754629632</v>
+        <v>45882.483449074076</v>
       </c>
       <c r="C136">
-        <v>60616386</v>
+        <v>60094807</v>
       </c>
       <c r="D136" s="2">
-        <v>46108.587326388886</v>
+        <v>46099.377268518518</v>
       </c>
       <c r="E136" t="s">
-        <v>283</v>
+        <v>16</v>
       </c>
       <c r="F136" t="s">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="G136">
-        <v>787670708</v>
+        <v>749194205</v>
       </c>
       <c r="H136" t="s">
-        <v>280</v>
+        <v>229</v>
       </c>
       <c r="I136" t="s">
         <v>0</v>
       </c>
       <c r="J136" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K136" t="s">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="L136" t="s">
         <v>8</v>
       </c>
       <c r="M136" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="N136" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O136" t="s">
         <v>0</v>
       </c>
-      <c r="P136" s="1">
-        <v>293000</v>
+      <c r="P136" t="s">
+        <v>0</v>
       </c>
       <c r="Q136" t="s">
-        <v>41</v>
+        <v>231</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A137">
-        <v>60458135</v>
+        <v>44970444</v>
       </c>
       <c r="B137" s="2">
-        <v>46106.415694444448</v>
+        <v>45798.444131944445</v>
       </c>
       <c r="C137">
-        <v>60458178</v>
+        <v>57086157</v>
       </c>
       <c r="D137" s="2">
-        <v>46106.415902777779</v>
+        <v>46044.497789351852</v>
       </c>
       <c r="E137" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="F137" t="s">
-        <v>167</v>
+        <v>92</v>
       </c>
       <c r="G137">
-        <v>708086472</v>
+        <v>777545168</v>
       </c>
       <c r="H137" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c r="I137" t="s">
         <v>0</v>
       </c>
       <c r="J137" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K137" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L137" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M137" t="s">
-        <v>7</v>
-      </c>
-      <c r="N137" t="s">
-        <v>196</v>
+        <v>3</v>
       </c>
       <c r="O137" t="s">
         <v>0</v>
@@ -8601,542 +8571,16 @@
       <c r="P137" t="s">
         <v>0</v>
       </c>
-      <c r="Q137" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A138">
-        <v>60458148</v>
-      </c>
-      <c r="B138" s="2">
-        <v>46106.41574074074</v>
-      </c>
-      <c r="C138">
-        <v>60458184</v>
-      </c>
-      <c r="D138" s="2">
-        <v>46106.415960648148</v>
-      </c>
-      <c r="E138" t="s">
-        <v>88</v>
-      </c>
-      <c r="F138" t="s">
-        <v>167</v>
-      </c>
-      <c r="G138">
-        <v>708086472</v>
-      </c>
-      <c r="H138" t="s">
-        <v>235</v>
-      </c>
-      <c r="I138" t="s">
-        <v>0</v>
-      </c>
-      <c r="J138" t="s">
-        <v>18</v>
-      </c>
-      <c r="K138" t="s">
-        <v>5</v>
-      </c>
-      <c r="L138" t="s">
-        <v>8</v>
-      </c>
-      <c r="M138" t="s">
-        <v>14</v>
-      </c>
-      <c r="N138" t="s">
-        <v>196</v>
-      </c>
-      <c r="O138" t="s">
-        <v>0</v>
-      </c>
-      <c r="P138" s="1">
-        <v>580000</v>
-      </c>
-      <c r="Q138" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A139">
-        <v>60461761</v>
-      </c>
-      <c r="B139" s="2">
-        <v>46106.442974537036</v>
-      </c>
-      <c r="C139">
-        <v>60461814</v>
-      </c>
-      <c r="D139" s="2">
-        <v>46106.443206018521</v>
-      </c>
-      <c r="E139" t="s">
-        <v>88</v>
-      </c>
-      <c r="F139" t="s">
-        <v>167</v>
-      </c>
-      <c r="G139">
-        <v>708086472</v>
-      </c>
-      <c r="H139" t="s">
-        <v>107</v>
-      </c>
-      <c r="I139" t="s">
-        <v>0</v>
-      </c>
-      <c r="J139" t="s">
-        <v>18</v>
-      </c>
-      <c r="K139" t="s">
-        <v>5</v>
-      </c>
-      <c r="L139" t="s">
-        <v>8</v>
-      </c>
-      <c r="M139" t="s">
-        <v>7</v>
-      </c>
-      <c r="N139" t="s">
-        <v>196</v>
-      </c>
-      <c r="O139" t="s">
-        <v>0</v>
-      </c>
-      <c r="P139" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A140">
-        <v>60461778</v>
-      </c>
-      <c r="B140" s="2">
-        <v>46106.443009259259</v>
-      </c>
-      <c r="C140">
-        <v>60461820</v>
-      </c>
-      <c r="D140" s="2">
-        <v>46106.443240740744</v>
-      </c>
-      <c r="E140" t="s">
-        <v>88</v>
-      </c>
-      <c r="F140" t="s">
-        <v>167</v>
-      </c>
-      <c r="G140">
-        <v>708086472</v>
-      </c>
-      <c r="H140" t="s">
-        <v>107</v>
-      </c>
-      <c r="I140" t="s">
-        <v>0</v>
-      </c>
-      <c r="J140" t="s">
-        <v>18</v>
-      </c>
-      <c r="K140" t="s">
-        <v>5</v>
-      </c>
-      <c r="L140" t="s">
-        <v>8</v>
-      </c>
-      <c r="M140" t="s">
-        <v>14</v>
-      </c>
-      <c r="N140" t="s">
-        <v>196</v>
-      </c>
-      <c r="O140" t="s">
-        <v>0</v>
-      </c>
-      <c r="P140" s="1">
-        <v>780000</v>
-      </c>
-      <c r="Q140" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A141">
-        <v>60463210</v>
-      </c>
-      <c r="B141" s="2">
-        <v>46106.455092592594</v>
-      </c>
-      <c r="C141">
-        <v>60463244</v>
-      </c>
-      <c r="D141" s="2">
-        <v>46106.455324074072</v>
-      </c>
-      <c r="E141" t="s">
-        <v>88</v>
-      </c>
-      <c r="F141" t="s">
-        <v>167</v>
-      </c>
-      <c r="G141">
-        <v>708086472</v>
-      </c>
-      <c r="H141" t="s">
-        <v>92</v>
-      </c>
-      <c r="I141" t="s">
-        <v>0</v>
-      </c>
-      <c r="J141" t="s">
-        <v>18</v>
-      </c>
-      <c r="K141" t="s">
-        <v>5</v>
-      </c>
-      <c r="L141" t="s">
-        <v>8</v>
-      </c>
-      <c r="M141" t="s">
-        <v>7</v>
-      </c>
-      <c r="N141" t="s">
-        <v>196</v>
-      </c>
-      <c r="O141" t="s">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A142">
-        <v>60472385</v>
-      </c>
-      <c r="B142" s="2">
-        <v>46106.535451388889</v>
-      </c>
-      <c r="C142">
-        <v>60601451</v>
-      </c>
-      <c r="D142" s="2">
-        <v>46108.464375000003</v>
-      </c>
-      <c r="E142" t="s">
-        <v>296</v>
-      </c>
-      <c r="F142" t="s">
-        <v>281</v>
-      </c>
-      <c r="G142">
-        <v>504001081</v>
-      </c>
-      <c r="H142" t="s">
-        <v>282</v>
-      </c>
-      <c r="I142" t="s">
-        <v>0</v>
-      </c>
-      <c r="J142" t="s">
-        <v>25</v>
-      </c>
-      <c r="K142" t="s">
-        <v>1</v>
-      </c>
-      <c r="L142" t="s">
-        <v>2</v>
-      </c>
-      <c r="M142" t="s">
-        <v>3</v>
-      </c>
-      <c r="N142" t="s">
-        <v>196</v>
-      </c>
-      <c r="O142" t="s">
-        <v>0</v>
-      </c>
-      <c r="P142" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A143">
-        <v>60486510</v>
-      </c>
-      <c r="B143" s="2">
-        <v>46106.647210648145</v>
-      </c>
-      <c r="C143">
-        <v>60601070</v>
-      </c>
-      <c r="D143" s="2">
-        <v>46108.461956018517</v>
-      </c>
-      <c r="E143" t="s">
-        <v>296</v>
-      </c>
-      <c r="F143" t="s">
-        <v>301</v>
-      </c>
-      <c r="G143">
-        <v>710060780</v>
-      </c>
-      <c r="H143" t="s">
-        <v>191</v>
-      </c>
-      <c r="I143" t="s">
-        <v>0</v>
-      </c>
-      <c r="J143" t="s">
-        <v>85</v>
-      </c>
-      <c r="K143" t="s">
-        <v>1</v>
-      </c>
-      <c r="L143" t="s">
-        <v>2</v>
-      </c>
-      <c r="M143" t="s">
-        <v>3</v>
-      </c>
-      <c r="N143" t="s">
-        <v>196</v>
-      </c>
-      <c r="O143" t="s">
-        <v>0</v>
-      </c>
-      <c r="P143" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q143" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A144">
-        <v>60573620</v>
-      </c>
-      <c r="B144" s="2">
-        <v>46107.848483796297</v>
-      </c>
-      <c r="C144">
-        <v>60590960</v>
-      </c>
-      <c r="D144" s="2">
-        <v>46108.386261574073</v>
-      </c>
-      <c r="E144" t="s">
-        <v>304</v>
-      </c>
-      <c r="F144" t="s">
-        <v>302</v>
-      </c>
-      <c r="G144">
-        <v>575750228</v>
-      </c>
-      <c r="H144" t="s">
-        <v>303</v>
-      </c>
-      <c r="I144" t="s">
-        <v>0</v>
-      </c>
-      <c r="J144" t="s">
-        <v>13</v>
-      </c>
-      <c r="K144" t="s">
-        <v>5</v>
-      </c>
-      <c r="L144" t="s">
-        <v>6</v>
-      </c>
-      <c r="M144" t="s">
-        <v>38</v>
-      </c>
-      <c r="N144" t="s">
-        <v>196</v>
-      </c>
-      <c r="O144" t="s">
-        <v>0</v>
-      </c>
-      <c r="P144" s="1">
-        <v>802977</v>
-      </c>
-      <c r="Q144" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A145">
-        <v>60589306</v>
-      </c>
-      <c r="B145" s="2">
-        <v>46108.367638888885</v>
-      </c>
-      <c r="C145">
-        <v>60590899</v>
-      </c>
-      <c r="D145" s="2">
-        <v>46108.385578703703</v>
-      </c>
-      <c r="E145" t="s">
-        <v>304</v>
-      </c>
-      <c r="F145" t="s">
-        <v>305</v>
-      </c>
-      <c r="G145">
-        <v>707040612</v>
-      </c>
-      <c r="H145" t="s">
-        <v>306</v>
-      </c>
-      <c r="I145">
-        <v>0</v>
-      </c>
-      <c r="J145" t="s">
-        <v>25</v>
-      </c>
-      <c r="K145" t="s">
-        <v>1</v>
-      </c>
-      <c r="L145" t="s">
-        <v>2</v>
-      </c>
-      <c r="M145" t="s">
-        <v>3</v>
-      </c>
-      <c r="N145" t="s">
-        <v>196</v>
-      </c>
-      <c r="O145" t="s">
-        <v>0</v>
-      </c>
-      <c r="P145" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q145" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A146">
-        <v>60611946</v>
-      </c>
-      <c r="B146" s="2">
-        <v>46108.544236111113</v>
-      </c>
-      <c r="C146">
-        <v>60611970</v>
-      </c>
-      <c r="D146" s="2">
-        <v>46108.54446759259</v>
-      </c>
-      <c r="E146" t="s">
-        <v>40</v>
-      </c>
-      <c r="F146" t="s">
-        <v>307</v>
-      </c>
-      <c r="G146">
-        <v>707812141</v>
-      </c>
-      <c r="H146" t="s">
-        <v>308</v>
-      </c>
-      <c r="I146" t="s">
-        <v>0</v>
-      </c>
-      <c r="J146" t="s">
-        <v>25</v>
-      </c>
-      <c r="K146" t="s">
-        <v>1</v>
-      </c>
-      <c r="L146" t="s">
-        <v>2</v>
-      </c>
-      <c r="M146" t="s">
-        <v>3</v>
-      </c>
-      <c r="N146" t="s">
-        <v>195</v>
-      </c>
-      <c r="O146" t="s">
-        <v>0</v>
-      </c>
-      <c r="P146" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147">
-        <v>60612374</v>
-      </c>
-      <c r="B147" s="2">
-        <v>46108.549409722225</v>
-      </c>
-      <c r="C147">
-        <v>60612392</v>
-      </c>
-      <c r="D147" s="2">
-        <v>46108.549618055556</v>
-      </c>
-      <c r="E147" t="s">
-        <v>40</v>
-      </c>
-      <c r="F147" t="s">
-        <v>307</v>
-      </c>
-      <c r="G147">
-        <v>707812141</v>
-      </c>
-      <c r="H147" t="s">
-        <v>308</v>
-      </c>
-      <c r="I147" t="s">
-        <v>0</v>
-      </c>
-      <c r="J147" t="s">
-        <v>25</v>
-      </c>
-      <c r="K147" t="s">
-        <v>1</v>
-      </c>
-      <c r="L147" t="s">
-        <v>2</v>
-      </c>
-      <c r="M147" t="s">
-        <v>3</v>
-      </c>
-      <c r="N147" t="s">
-        <v>195</v>
-      </c>
-      <c r="O147" t="s">
-        <v>0</v>
-      </c>
-      <c r="P147" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q147" t="s">
-        <v>0</v>
+      <c r="Q137">
+        <v>2723489300</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q147" xr:uid="{F241F63F-8CA3-4680-8FA3-BC3B4E36762D}"/>
+  <autoFilter ref="A1:S137" xr:uid="{C722EAFD-41F1-49B4-A0A6-ACE76096AA41}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S160">
+      <sortCondition descending="1" ref="A1"/>
+    </sortState>
+  </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/Attachments/Bureau/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{713C870A-8DD6-409B-8ABD-7513E6CFDA26}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4022EB28-11E6-4DF8-8646-C905C5BE5E84}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Feuil2" sheetId="42" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil2!$A$1:$Q$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil2!$A$1:$Q$165</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="350">
   <si>
     <t>-</t>
   </si>
@@ -686,9 +686,6 @@
     <t>Etude Suspendu</t>
   </si>
   <si>
-    <t>BBF : Validation Etude</t>
-  </si>
-  <si>
     <t>XXXXXXXXXXXXXXX</t>
   </si>
   <si>
@@ -872,9 +869,6 @@
     <t>SYTHD260114</t>
   </si>
   <si>
-    <t>Planification Ctrl Conformite</t>
-  </si>
-  <si>
     <t>Support IP: Correction</t>
   </si>
   <si>
@@ -947,12 +941,6 @@
     <t>2720254300B</t>
   </si>
   <si>
-    <t>BO Homologation: Saisie GAIA LSI</t>
-  </si>
-  <si>
-    <t>IP Delivery: Validation information</t>
-  </si>
-  <si>
     <t>SODEXAM</t>
   </si>
   <si>
@@ -1095,9 +1083,6 @@
   </si>
   <si>
     <t>BO Homologation: Saisie GAIA</t>
-  </si>
-  <si>
-    <t>SIE: Pilote</t>
   </si>
   <si>
     <t>STE PLACE AFRICA</t>
@@ -1147,7 +1132,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1488,7 +1493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA2681BA-26CD-4DFD-AC27-AFE67B62DFC2}">
-  <dimension ref="A1:Q176"/>
+  <dimension ref="A1:Q165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
@@ -1608,7 +1613,7 @@
         <v>46132.531863425924</v>
       </c>
       <c r="E3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F3" t="s">
         <v>36</v>
@@ -2138,7 +2143,7 @@
         <v>46119.680300925924</v>
       </c>
       <c r="E13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F13" t="s">
         <v>87</v>
@@ -2403,7 +2408,7 @@
         <v>46099.427060185182</v>
       </c>
       <c r="E18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F18" t="s">
         <v>95</v>
@@ -2545,7 +2550,7 @@
         <v>2000000</v>
       </c>
       <c r="Q20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
@@ -2562,7 +2567,7 @@
         <v>46114.40011574074</v>
       </c>
       <c r="E21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F21" t="s">
         <v>99</v>
@@ -2942,7 +2947,7 @@
         <v>707079088</v>
       </c>
       <c r="H28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I28">
         <v>1801436</v>
@@ -2969,7 +2974,7 @@
         <v>1426700</v>
       </c>
       <c r="Q28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
@@ -2986,7 +2991,7 @@
         <v>46132.4299537037</v>
       </c>
       <c r="E29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F29" t="s">
         <v>116</v>
@@ -3092,7 +3097,7 @@
         <v>46132.426712962966</v>
       </c>
       <c r="E31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F31" t="s">
         <v>116</v>
@@ -3154,7 +3159,7 @@
         <v>758224257</v>
       </c>
       <c r="H32" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I32" t="s">
         <v>0</v>
@@ -3357,7 +3362,7 @@
         <v>46129.531180555554</v>
       </c>
       <c r="E36" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F36" t="s">
         <v>125</v>
@@ -3366,7 +3371,7 @@
         <v>2721271444</v>
       </c>
       <c r="H36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I36">
         <v>1813406</v>
@@ -3393,7 +3398,7 @@
         <v>1495965</v>
       </c>
       <c r="Q36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
@@ -3446,7 +3451,7 @@
         <v>2000000</v>
       </c>
       <c r="Q37" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
@@ -3510,13 +3515,13 @@
         <v>46066.525011574071</v>
       </c>
       <c r="C39">
-        <v>61899989</v>
+        <v>61919908</v>
       </c>
       <c r="D39" s="2">
-        <v>46132.374884259261</v>
+        <v>46132.515613425923</v>
       </c>
       <c r="E39" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F39" t="s">
         <v>127</v>
@@ -3552,33 +3557,33 @@
         <v>522590</v>
       </c>
       <c r="Q39" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>58274609</v>
+        <v>58626822</v>
       </c>
       <c r="B40" s="2">
-        <v>46066.525011574071</v>
+        <v>46072.810324074075</v>
       </c>
       <c r="C40">
-        <v>61919908</v>
+        <v>59811821</v>
       </c>
       <c r="D40" s="2">
-        <v>46132.515613425923</v>
+        <v>46093.543773148151</v>
       </c>
       <c r="E40" t="s">
-        <v>278</v>
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G40">
-        <v>2722480700</v>
+        <v>709574114</v>
       </c>
       <c r="H40" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="I40" t="s">
         <v>0</v>
@@ -3587,7 +3592,7 @@
         <v>13</v>
       </c>
       <c r="K40" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L40" t="s">
         <v>6</v>
@@ -3602,77 +3607,77 @@
         <v>0</v>
       </c>
       <c r="P40" s="1">
-        <v>522590</v>
+        <v>445307</v>
       </c>
       <c r="Q40" t="s">
-        <v>276</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>58626822</v>
+        <v>58635645</v>
       </c>
       <c r="B41" s="2">
-        <v>46072.810324074075</v>
+        <v>46073.372395833336</v>
       </c>
       <c r="C41">
-        <v>59811821</v>
+        <v>61788801</v>
       </c>
       <c r="D41" s="2">
-        <v>46093.543773148151</v>
+        <v>46129.771238425928</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G41">
-        <v>709574114</v>
+        <v>759250737</v>
       </c>
       <c r="H41" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="I41" t="s">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K41" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L41" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M41" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O41" t="s">
         <v>0</v>
       </c>
-      <c r="P41" s="1">
-        <v>445307</v>
+      <c r="P41" t="s">
+        <v>0</v>
       </c>
       <c r="Q41" t="s">
-        <v>35</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>58635645</v>
+        <v>58635674</v>
       </c>
       <c r="B42" s="2">
-        <v>46073.372395833336</v>
+        <v>46073.372488425928</v>
       </c>
       <c r="C42">
-        <v>61788801</v>
+        <v>61783488</v>
       </c>
       <c r="D42" s="2">
-        <v>46129.771238425928</v>
+        <v>46129.732662037037</v>
       </c>
       <c r="E42" t="s">
         <v>65</v>
@@ -3699,7 +3704,7 @@
         <v>8</v>
       </c>
       <c r="M42" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N42" t="s">
         <v>156</v>
@@ -3707,25 +3712,25 @@
       <c r="O42" t="s">
         <v>0</v>
       </c>
-      <c r="P42" t="s">
-        <v>0</v>
+      <c r="P42" s="1">
+        <v>500000</v>
       </c>
       <c r="Q42" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>58635674</v>
+        <v>58642079</v>
       </c>
       <c r="B43" s="2">
-        <v>46073.372488425928</v>
+        <v>46073.425034722219</v>
       </c>
       <c r="C43">
-        <v>61783488</v>
+        <v>61795445</v>
       </c>
       <c r="D43" s="2">
-        <v>46129.732662037037</v>
+        <v>46129.869398148148</v>
       </c>
       <c r="E43" t="s">
         <v>65</v>
@@ -3743,16 +3748,16 @@
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="K43" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="L43" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M43" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N43" t="s">
         <v>156</v>
@@ -3760,31 +3765,31 @@
       <c r="O43" t="s">
         <v>0</v>
       </c>
-      <c r="P43" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>225</v>
+      <c r="P43" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>2720218600</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>58642079</v>
+        <v>58649804</v>
       </c>
       <c r="B44" s="2">
-        <v>46073.425034722219</v>
+        <v>46073.479305555556</v>
       </c>
       <c r="C44">
-        <v>61795445</v>
+        <v>61794069</v>
       </c>
       <c r="D44" s="2">
-        <v>46129.869398148148</v>
+        <v>46129.840405092589</v>
       </c>
       <c r="E44" t="s">
         <v>65</v>
       </c>
       <c r="F44" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G44">
         <v>759250737</v>
@@ -3796,16 +3801,16 @@
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="K44" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="L44" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M44" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N44" t="s">
         <v>156</v>
@@ -3816,22 +3821,22 @@
       <c r="P44" t="s">
         <v>0</v>
       </c>
-      <c r="Q44">
-        <v>2720218600</v>
+      <c r="Q44" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>58649804</v>
+        <v>58649837</v>
       </c>
       <c r="B45" s="2">
-        <v>46073.479305555556</v>
+        <v>46073.479409722226</v>
       </c>
       <c r="C45">
-        <v>61794069</v>
+        <v>61780798</v>
       </c>
       <c r="D45" s="2">
-        <v>46129.840405092589</v>
+        <v>46129.7108912037</v>
       </c>
       <c r="E45" t="s">
         <v>65</v>
@@ -3858,7 +3863,7 @@
         <v>6</v>
       </c>
       <c r="M45" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N45" t="s">
         <v>156</v>
@@ -3866,8 +3871,8 @@
       <c r="O45" t="s">
         <v>0</v>
       </c>
-      <c r="P45" t="s">
-        <v>0</v>
+      <c r="P45" s="1">
+        <v>500000</v>
       </c>
       <c r="Q45" t="s">
         <v>226</v>
@@ -3875,52 +3880,52 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>58649837</v>
+        <v>58797846</v>
       </c>
       <c r="B46" s="2">
-        <v>46073.479409722226</v>
+        <v>46076.510104166664</v>
       </c>
       <c r="C46">
-        <v>61780798</v>
+        <v>61338699</v>
       </c>
       <c r="D46" s="2">
-        <v>46129.7108912037</v>
+        <v>46122.390069444446</v>
       </c>
       <c r="E46" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="F46" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G46">
-        <v>759250737</v>
+        <v>102224907</v>
       </c>
       <c r="H46" t="s">
-        <v>28</v>
+        <v>211</v>
       </c>
       <c r="I46" t="s">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K46" t="s">
         <v>9</v>
       </c>
       <c r="L46" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M46" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O46" t="s">
         <v>0</v>
       </c>
       <c r="P46" s="1">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="Q46" t="s">
         <v>227</v>
@@ -3928,28 +3933,28 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>58797846</v>
+        <v>58821537</v>
       </c>
       <c r="B47" s="2">
-        <v>46076.510104166664</v>
+        <v>46076.664479166669</v>
       </c>
       <c r="C47">
-        <v>61338699</v>
+        <v>61633411</v>
       </c>
       <c r="D47" s="2">
-        <v>46122.390069444446</v>
+        <v>46127.672071759262</v>
       </c>
       <c r="E47" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G47">
-        <v>102224907</v>
+        <v>708086472</v>
       </c>
       <c r="H47" t="s">
-        <v>211</v>
+        <v>107</v>
       </c>
       <c r="I47" t="s">
         <v>0</v>
@@ -3958,13 +3963,13 @@
         <v>18</v>
       </c>
       <c r="K47" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L47" t="s">
         <v>8</v>
       </c>
       <c r="M47" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N47" t="s">
         <v>157</v>
@@ -3972,28 +3977,28 @@
       <c r="O47" t="s">
         <v>0</v>
       </c>
-      <c r="P47" s="1">
-        <v>2000000</v>
+      <c r="P47" t="s">
+        <v>0</v>
       </c>
       <c r="Q47" t="s">
-        <v>228</v>
+        <v>277</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>58821537</v>
+        <v>58821553</v>
       </c>
       <c r="B48" s="2">
-        <v>46076.664479166669</v>
+        <v>46076.664525462962</v>
       </c>
       <c r="C48">
-        <v>61633411</v>
+        <v>61922665</v>
       </c>
       <c r="D48" s="2">
-        <v>46127.672071759262</v>
+        <v>46132.535636574074</v>
       </c>
       <c r="E48" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="F48" t="s">
         <v>134</v>
@@ -4011,13 +4016,13 @@
         <v>18</v>
       </c>
       <c r="K48" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L48" t="s">
         <v>8</v>
       </c>
       <c r="M48" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N48" t="s">
         <v>157</v>
@@ -4025,28 +4030,28 @@
       <c r="O48" t="s">
         <v>0</v>
       </c>
-      <c r="P48" t="s">
-        <v>0</v>
+      <c r="P48" s="1">
+        <v>705000</v>
       </c>
       <c r="Q48" t="s">
-        <v>279</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>58821553</v>
+        <v>58822576</v>
       </c>
       <c r="B49" s="2">
-        <v>46076.664525462962</v>
+        <v>46076.670810185184</v>
       </c>
       <c r="C49">
-        <v>61922665</v>
+        <v>59375318</v>
       </c>
       <c r="D49" s="2">
-        <v>46132.535636574074</v>
+        <v>46085.763622685183</v>
       </c>
       <c r="E49" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="F49" t="s">
         <v>134</v>
@@ -4055,7 +4060,7 @@
         <v>708086472</v>
       </c>
       <c r="H49" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="I49" t="s">
         <v>0</v>
@@ -4064,13 +4069,13 @@
         <v>18</v>
       </c>
       <c r="K49" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L49" t="s">
         <v>8</v>
       </c>
       <c r="M49" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N49" t="s">
         <v>157</v>
@@ -4078,25 +4083,25 @@
       <c r="O49" t="s">
         <v>0</v>
       </c>
-      <c r="P49" s="1">
-        <v>705000</v>
+      <c r="P49" t="s">
+        <v>0</v>
       </c>
       <c r="Q49" t="s">
-        <v>188</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>58822576</v>
+        <v>58822595</v>
       </c>
       <c r="B50" s="2">
-        <v>46076.670810185184</v>
+        <v>46076.670856481483</v>
       </c>
       <c r="C50">
-        <v>59375318</v>
+        <v>60208557</v>
       </c>
       <c r="D50" s="2">
-        <v>46085.763622685183</v>
+        <v>46100.764618055553</v>
       </c>
       <c r="E50" t="s">
         <v>16</v>
@@ -4123,7 +4128,7 @@
         <v>8</v>
       </c>
       <c r="M50" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N50" t="s">
         <v>157</v>
@@ -4131,37 +4136,37 @@
       <c r="O50" t="s">
         <v>0</v>
       </c>
-      <c r="P50" t="s">
-        <v>0</v>
+      <c r="P50" s="1">
+        <v>1150000</v>
       </c>
       <c r="Q50" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>58822595</v>
+        <v>58856498</v>
       </c>
       <c r="B51" s="2">
-        <v>46076.670856481483</v>
+        <v>46077.418171296296</v>
       </c>
       <c r="C51">
-        <v>60208557</v>
+        <v>60800011</v>
       </c>
       <c r="D51" s="2">
-        <v>46100.764618055553</v>
+        <v>46112.393784722219</v>
       </c>
       <c r="E51" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F51" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G51">
-        <v>708086472</v>
+        <v>748377555</v>
       </c>
       <c r="H51" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I51" t="s">
         <v>0</v>
@@ -4176,7 +4181,7 @@
         <v>8</v>
       </c>
       <c r="M51" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N51" t="s">
         <v>157</v>
@@ -4184,43 +4189,43 @@
       <c r="O51" t="s">
         <v>0</v>
       </c>
-      <c r="P51" s="1">
-        <v>1150000</v>
+      <c r="P51" t="s">
+        <v>0</v>
       </c>
       <c r="Q51" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>58856498</v>
+        <v>58860531</v>
       </c>
       <c r="B52" s="2">
-        <v>46077.418171296296</v>
+        <v>46077.446631944447</v>
       </c>
       <c r="C52">
-        <v>60800011</v>
+        <v>60749153</v>
       </c>
       <c r="D52" s="2">
-        <v>46112.393784722219</v>
+        <v>46111.514351851853</v>
       </c>
       <c r="E52" t="s">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G52">
         <v>748377555</v>
       </c>
       <c r="H52" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I52" t="s">
         <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
@@ -4241,21 +4246,21 @@
         <v>0</v>
       </c>
       <c r="Q52" t="s">
-        <v>200</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>58860531</v>
+        <v>58860538</v>
       </c>
       <c r="B53" s="2">
-        <v>46077.446631944447</v>
+        <v>46077.446666666663</v>
       </c>
       <c r="C53">
-        <v>60749153</v>
+        <v>60749284</v>
       </c>
       <c r="D53" s="2">
-        <v>46111.514351851853</v>
+        <v>46111.515370370369</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
@@ -4282,7 +4287,7 @@
         <v>8</v>
       </c>
       <c r="M53" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N53" t="s">
         <v>157</v>
@@ -4290,43 +4295,43 @@
       <c r="O53" t="s">
         <v>0</v>
       </c>
-      <c r="P53" t="s">
-        <v>0</v>
+      <c r="P53" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q53" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>58860538</v>
+        <v>58862661</v>
       </c>
       <c r="B54" s="2">
-        <v>46077.446666666663</v>
+        <v>46077.461805555555</v>
       </c>
       <c r="C54">
-        <v>60749284</v>
+        <v>60042646</v>
       </c>
       <c r="D54" s="2">
-        <v>46111.515370370369</v>
+        <v>46098.494629629633</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G54">
         <v>748377555</v>
       </c>
       <c r="H54" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I54" t="s">
         <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
@@ -4335,7 +4340,7 @@
         <v>8</v>
       </c>
       <c r="M54" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N54" t="s">
         <v>157</v>
@@ -4343,25 +4348,25 @@
       <c r="O54" t="s">
         <v>0</v>
       </c>
-      <c r="P54" s="1">
-        <v>5324000</v>
+      <c r="P54" t="s">
+        <v>0</v>
       </c>
       <c r="Q54" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>58862661</v>
+        <v>58862680</v>
       </c>
       <c r="B55" s="2">
-        <v>46077.461805555555</v>
+        <v>46077.461828703701</v>
       </c>
       <c r="C55">
-        <v>60042646</v>
+        <v>60043590</v>
       </c>
       <c r="D55" s="2">
-        <v>46098.494629629633</v>
+        <v>46098.501527777778</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
@@ -4388,7 +4393,7 @@
         <v>8</v>
       </c>
       <c r="M55" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N55" t="s">
         <v>157</v>
@@ -4396,37 +4401,37 @@
       <c r="O55" t="s">
         <v>0</v>
       </c>
-      <c r="P55" t="s">
-        <v>0</v>
+      <c r="P55" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q55" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>58862680</v>
+        <v>58868849</v>
       </c>
       <c r="B56" s="2">
-        <v>46077.461828703701</v>
+        <v>46077.501203703701</v>
       </c>
       <c r="C56">
-        <v>60043590</v>
+        <v>61617687</v>
       </c>
       <c r="D56" s="2">
-        <v>46098.501527777778</v>
+        <v>46127.557233796295</v>
       </c>
       <c r="E56" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F56" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G56">
         <v>748377555</v>
       </c>
       <c r="H56" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I56" t="s">
         <v>0</v>
@@ -4441,7 +4446,7 @@
         <v>8</v>
       </c>
       <c r="M56" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N56" t="s">
         <v>157</v>
@@ -4449,37 +4454,37 @@
       <c r="O56" t="s">
         <v>0</v>
       </c>
-      <c r="P56" s="1">
-        <v>5324000</v>
+      <c r="P56" t="s">
+        <v>0</v>
       </c>
       <c r="Q56" t="s">
-        <v>37</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>58868849</v>
+        <v>58885251</v>
       </c>
       <c r="B57" s="2">
-        <v>46077.501203703701</v>
+        <v>46077.63863425926</v>
       </c>
       <c r="C57">
-        <v>61617687</v>
+        <v>60408762</v>
       </c>
       <c r="D57" s="2">
-        <v>46127.557233796295</v>
+        <v>46105.557326388887</v>
       </c>
       <c r="E57" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
         <v>143</v>
       </c>
       <c r="G57">
-        <v>748377555</v>
+        <v>748377507</v>
       </c>
       <c r="H57" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I57" t="s">
         <v>0</v>
@@ -4506,21 +4511,21 @@
         <v>0</v>
       </c>
       <c r="Q57" t="s">
-        <v>280</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>58885251</v>
+        <v>58885259</v>
       </c>
       <c r="B58" s="2">
-        <v>46077.63863425926</v>
+        <v>46077.638657407406</v>
       </c>
       <c r="C58">
-        <v>60408762</v>
+        <v>60373389</v>
       </c>
       <c r="D58" s="2">
-        <v>46105.557326388887</v>
+        <v>46104.751145833332</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -4547,7 +4552,7 @@
         <v>8</v>
       </c>
       <c r="M58" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N58" t="s">
         <v>157</v>
@@ -4555,37 +4560,37 @@
       <c r="O58" t="s">
         <v>0</v>
       </c>
-      <c r="P58" t="s">
-        <v>0</v>
+      <c r="P58" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q58" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>58885259</v>
+        <v>58889872</v>
       </c>
       <c r="B59" s="2">
-        <v>46077.638657407406</v>
+        <v>46077.670567129629</v>
       </c>
       <c r="C59">
-        <v>60373389</v>
+        <v>60850352</v>
       </c>
       <c r="D59" s="2">
-        <v>46104.751145833332</v>
+        <v>46112.792870370373</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F59" t="s">
         <v>143</v>
       </c>
       <c r="G59">
-        <v>748377507</v>
+        <v>748377555</v>
       </c>
       <c r="H59" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I59" t="s">
         <v>0</v>
@@ -4600,36 +4605,36 @@
         <v>8</v>
       </c>
       <c r="M59" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N59" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O59" t="s">
         <v>0</v>
       </c>
-      <c r="P59" s="1">
-        <v>5324000</v>
+      <c r="P59" t="s">
+        <v>0</v>
       </c>
       <c r="Q59" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>58889872</v>
+        <v>58892468</v>
       </c>
       <c r="B60" s="2">
-        <v>46077.670567129629</v>
+        <v>46077.688321759262</v>
       </c>
       <c r="C60">
-        <v>60850352</v>
+        <v>60414369</v>
       </c>
       <c r="D60" s="2">
-        <v>46112.792870370373</v>
+        <v>46105.607986111114</v>
       </c>
       <c r="E60" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F60" t="s">
         <v>143</v>
@@ -4638,7 +4643,7 @@
         <v>748377555</v>
       </c>
       <c r="H60" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I60" t="s">
         <v>0</v>
@@ -4656,7 +4661,7 @@
         <v>7</v>
       </c>
       <c r="N60" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O60" t="s">
         <v>0</v>
@@ -4665,21 +4670,21 @@
         <v>0</v>
       </c>
       <c r="Q60" t="s">
-        <v>140</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>58892468</v>
+        <v>58892481</v>
       </c>
       <c r="B61" s="2">
-        <v>46077.688321759262</v>
+        <v>46077.688344907408</v>
       </c>
       <c r="C61">
-        <v>60414369</v>
+        <v>60413667</v>
       </c>
       <c r="D61" s="2">
-        <v>46105.607986111114</v>
+        <v>46105.602303240739</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -4706,7 +4711,7 @@
         <v>8</v>
       </c>
       <c r="M61" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N61" t="s">
         <v>157</v>
@@ -4714,52 +4719,52 @@
       <c r="O61" t="s">
         <v>0</v>
       </c>
-      <c r="P61" t="s">
-        <v>0</v>
+      <c r="P61" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q61" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>58892481</v>
+        <v>58925987</v>
       </c>
       <c r="B62" s="2">
-        <v>46077.688344907408</v>
+        <v>46078.434814814813</v>
       </c>
       <c r="C62">
-        <v>60413667</v>
+        <v>60163873</v>
       </c>
       <c r="D62" s="2">
-        <v>46105.602303240739</v>
+        <v>46100.423101851855</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G62">
-        <v>748377555</v>
+        <v>708641473</v>
       </c>
       <c r="H62" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I62" t="s">
         <v>0</v>
       </c>
       <c r="J62" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K62" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L62" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M62" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N62" t="s">
         <v>157</v>
@@ -4767,25 +4772,25 @@
       <c r="O62" t="s">
         <v>0</v>
       </c>
-      <c r="P62" s="1">
-        <v>5324000</v>
+      <c r="P62" t="s">
+        <v>0</v>
       </c>
       <c r="Q62" t="s">
-        <v>84</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>58925987</v>
+        <v>58959238</v>
       </c>
       <c r="B63" s="2">
-        <v>46078.434814814813</v>
+        <v>46078.665532407409</v>
       </c>
       <c r="C63">
-        <v>60163873</v>
+        <v>60163938</v>
       </c>
       <c r="D63" s="2">
-        <v>46100.423101851855</v>
+        <v>46100.423773148148</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -4797,19 +4802,19 @@
         <v>708641473</v>
       </c>
       <c r="H63" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I63" t="s">
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K63" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M63" t="s">
         <v>3</v>
@@ -4820,37 +4825,37 @@
       <c r="O63" t="s">
         <v>0</v>
       </c>
-      <c r="P63" t="s">
-        <v>0</v>
+      <c r="P63" s="1">
+        <v>850000</v>
       </c>
       <c r="Q63" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>58959238</v>
+        <v>58963630</v>
       </c>
       <c r="B64" s="2">
-        <v>46078.665532407409</v>
+        <v>46078.697002314817</v>
       </c>
       <c r="C64">
-        <v>60163938</v>
+        <v>60167087</v>
       </c>
       <c r="D64" s="2">
-        <v>46100.423773148148</v>
+        <v>46100.449837962966</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
       </c>
       <c r="F64" t="s">
-        <v>149</v>
+        <v>44</v>
       </c>
       <c r="G64">
-        <v>708641473</v>
+        <v>747726344</v>
       </c>
       <c r="H64" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I64" t="s">
         <v>0</v>
@@ -4865,7 +4870,7 @@
         <v>6</v>
       </c>
       <c r="M64" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N64" t="s">
         <v>157</v>
@@ -4873,28 +4878,28 @@
       <c r="O64" t="s">
         <v>0</v>
       </c>
-      <c r="P64" s="1">
-        <v>850000</v>
+      <c r="P64" t="s">
+        <v>0</v>
       </c>
       <c r="Q64" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>58963630</v>
+        <v>58963646</v>
       </c>
       <c r="B65" s="2">
-        <v>46078.697002314817</v>
+        <v>46078.697048611109</v>
       </c>
       <c r="C65">
-        <v>60167087</v>
+        <v>61620936</v>
       </c>
       <c r="D65" s="2">
-        <v>46100.449837962966</v>
+        <v>46127.58321759259</v>
       </c>
       <c r="E65" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="F65" t="s">
         <v>44</v>
@@ -4912,13 +4917,13 @@
         <v>13</v>
       </c>
       <c r="K65" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L65" t="s">
         <v>6</v>
       </c>
       <c r="M65" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N65" t="s">
         <v>157</v>
@@ -4926,52 +4931,52 @@
       <c r="O65" t="s">
         <v>0</v>
       </c>
-      <c r="P65" t="s">
+      <c r="P65">
         <v>0</v>
       </c>
       <c r="Q65" t="s">
-        <v>27</v>
+        <v>279</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>58963646</v>
+        <v>59309764</v>
       </c>
       <c r="B66" s="2">
-        <v>46078.697048611109</v>
+        <v>46084.777083333334</v>
       </c>
       <c r="C66">
-        <v>61620936</v>
+        <v>61274969</v>
       </c>
       <c r="D66" s="2">
-        <v>46127.58321759259</v>
+        <v>46121.432256944441</v>
       </c>
       <c r="E66" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="F66" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="G66">
-        <v>747726344</v>
+        <v>708164102</v>
       </c>
       <c r="H66" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="I66" t="s">
         <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K66" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L66" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M66" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N66" t="s">
         <v>157</v>
@@ -4979,49 +4984,49 @@
       <c r="O66" t="s">
         <v>0</v>
       </c>
-      <c r="P66">
-        <v>0</v>
+      <c r="P66" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q66" t="s">
-        <v>281</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>59309764</v>
+        <v>59406146</v>
       </c>
       <c r="B67" s="2">
-        <v>46084.777083333334</v>
+        <v>46086.506643518522</v>
       </c>
       <c r="C67">
-        <v>61274969</v>
+        <v>60600544</v>
       </c>
       <c r="D67" s="2">
-        <v>46121.432256944441</v>
+        <v>46108.458136574074</v>
       </c>
       <c r="E67" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="G67">
-        <v>708164102</v>
+        <v>709136702</v>
       </c>
       <c r="H67" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="I67" t="s">
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
       </c>
       <c r="L67" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M67" t="s">
         <v>3</v>
@@ -5032,31 +5037,31 @@
       <c r="O67" t="s">
         <v>0</v>
       </c>
-      <c r="P67" s="1">
-        <v>2000000</v>
+      <c r="P67">
+        <v>0</v>
       </c>
       <c r="Q67" t="s">
-        <v>160</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>59406146</v>
+        <v>59406937</v>
       </c>
       <c r="B68" s="2">
-        <v>46086.506643518522</v>
+        <v>46086.512870370374</v>
       </c>
       <c r="C68">
-        <v>60600544</v>
+        <v>61477853</v>
       </c>
       <c r="D68" s="2">
-        <v>46108.458136574074</v>
+        <v>46125.457789351851</v>
       </c>
       <c r="E68" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F68" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G68">
         <v>709136702</v>
@@ -5071,7 +5076,7 @@
         <v>75</v>
       </c>
       <c r="K68" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L68" t="s">
         <v>2</v>
@@ -5080,7 +5085,7 @@
         <v>3</v>
       </c>
       <c r="N68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O68" t="s">
         <v>0</v>
@@ -5089,30 +5094,30 @@
         <v>0</v>
       </c>
       <c r="Q68" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>59406937</v>
+        <v>59409078</v>
       </c>
       <c r="B69" s="2">
-        <v>46086.512870370374</v>
+        <v>46086.529247685183</v>
       </c>
       <c r="C69">
-        <v>61477853</v>
+        <v>60600044</v>
       </c>
       <c r="D69" s="2">
-        <v>46125.457789351851</v>
+        <v>46108.453865740739</v>
       </c>
       <c r="E69" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="F69" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G69">
-        <v>709136702</v>
+        <v>709140938</v>
       </c>
       <c r="H69" t="s">
         <v>85</v>
@@ -5124,48 +5129,48 @@
         <v>75</v>
       </c>
       <c r="K69" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L69" t="s">
         <v>2</v>
       </c>
       <c r="M69" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N69" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O69" t="s">
         <v>0</v>
       </c>
-      <c r="P69">
+      <c r="P69" t="s">
         <v>0</v>
       </c>
       <c r="Q69" t="s">
-        <v>229</v>
+        <v>39</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>59409078</v>
+        <v>59409752</v>
       </c>
       <c r="B70" s="2">
-        <v>46086.529247685183</v>
+        <v>46086.534502314818</v>
       </c>
       <c r="C70">
-        <v>60600044</v>
+        <v>60600716</v>
       </c>
       <c r="D70" s="2">
-        <v>46108.453865740739</v>
+        <v>46108.459768518522</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G70">
-        <v>709140938</v>
+        <v>758700193</v>
       </c>
       <c r="H70" t="s">
         <v>85</v>
@@ -5183,7 +5188,7 @@
         <v>2</v>
       </c>
       <c r="M70" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N70" t="s">
         <v>157</v>
@@ -5195,30 +5200,30 @@
         <v>0</v>
       </c>
       <c r="Q70" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>59409752</v>
+        <v>59410212</v>
       </c>
       <c r="B71" s="2">
-        <v>46086.534502314818</v>
+        <v>46086.537708333337</v>
       </c>
       <c r="C71">
-        <v>60600716</v>
+        <v>61919232</v>
       </c>
       <c r="D71" s="2">
-        <v>46108.459768518522</v>
+        <v>46132.511064814818</v>
       </c>
       <c r="E71" t="s">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="F71" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G71">
-        <v>758700193</v>
+        <v>789018789</v>
       </c>
       <c r="H71" t="s">
         <v>85</v>
@@ -5230,16 +5235,16 @@
         <v>75</v>
       </c>
       <c r="K71" t="s">
-        <v>1</v>
+        <v>167</v>
       </c>
       <c r="L71" t="s">
         <v>2</v>
       </c>
       <c r="M71" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N71" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O71" t="s">
         <v>0</v>
@@ -5248,33 +5253,33 @@
         <v>0</v>
       </c>
       <c r="Q71" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>59410212</v>
+        <v>59410843</v>
       </c>
       <c r="B72" s="2">
-        <v>46086.537708333337</v>
+        <v>46086.542870370373</v>
       </c>
       <c r="C72">
-        <v>61919232</v>
+        <v>60526566</v>
       </c>
       <c r="D72" s="2">
-        <v>46132.511064814818</v>
+        <v>46107.452592592592</v>
       </c>
       <c r="E72" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F72" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G72">
-        <v>789018789</v>
+        <v>758700193</v>
       </c>
       <c r="H72" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="I72" t="s">
         <v>0</v>
@@ -5283,16 +5288,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="L72" t="s">
         <v>2</v>
       </c>
       <c r="M72" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N72" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O72" t="s">
         <v>0</v>
@@ -5301,33 +5306,33 @@
         <v>0</v>
       </c>
       <c r="Q72" t="s">
-        <v>133</v>
+        <v>213</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>59410843</v>
+        <v>59414411</v>
       </c>
       <c r="B73" s="2">
-        <v>46086.542870370373</v>
+        <v>46086.57104166667</v>
       </c>
       <c r="C73">
-        <v>60526566</v>
+        <v>60601081</v>
       </c>
       <c r="D73" s="2">
-        <v>46107.452592592592</v>
+        <v>46108.462025462963</v>
       </c>
       <c r="E73" t="s">
-        <v>214</v>
+        <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G73">
-        <v>758700193</v>
+        <v>566473307</v>
       </c>
       <c r="H73" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I73" t="s">
         <v>0</v>
@@ -5350,37 +5355,37 @@
       <c r="O73" t="s">
         <v>0</v>
       </c>
-      <c r="P73" t="s">
+      <c r="P73">
         <v>0</v>
       </c>
       <c r="Q73" t="s">
-        <v>213</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>59414411</v>
+        <v>59417066</v>
       </c>
       <c r="B74" s="2">
-        <v>46086.57104166667</v>
+        <v>46086.594525462962</v>
       </c>
       <c r="C74">
-        <v>60601081</v>
+        <v>60589286</v>
       </c>
       <c r="D74" s="2">
-        <v>46108.462025462963</v>
+        <v>46108.367418981485</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G74">
-        <v>566473307</v>
+        <v>709565662</v>
       </c>
       <c r="H74" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I74" t="s">
         <v>0</v>
@@ -5407,48 +5412,48 @@
         <v>0</v>
       </c>
       <c r="Q74" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>59417066</v>
+        <v>59464660</v>
       </c>
       <c r="B75" s="2">
-        <v>46086.594525462962</v>
+        <v>46087.421030092592</v>
       </c>
       <c r="C75">
-        <v>60589286</v>
+        <v>61911893</v>
       </c>
       <c r="D75" s="2">
-        <v>46108.367418981485</v>
+        <v>46132.462372685186</v>
       </c>
       <c r="E75" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F75" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="G75">
-        <v>709565662</v>
+        <v>554235979</v>
       </c>
       <c r="H75" t="s">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="I75" t="s">
         <v>0</v>
       </c>
       <c r="J75" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="K75" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L75" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M75" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N75" t="s">
         <v>157</v>
@@ -5460,24 +5465,24 @@
         <v>0</v>
       </c>
       <c r="Q75" t="s">
-        <v>140</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>59464660</v>
+        <v>59465071</v>
       </c>
       <c r="B76" s="2">
-        <v>46087.421030092592</v>
+        <v>46087.424062500002</v>
       </c>
       <c r="C76">
-        <v>61911893</v>
+        <v>60531474</v>
       </c>
       <c r="D76" s="2">
-        <v>46132.462372685186</v>
+        <v>46107.489861111113</v>
       </c>
       <c r="E76" t="s">
-        <v>16</v>
+        <v>214</v>
       </c>
       <c r="F76" t="s">
         <v>99</v>
@@ -5486,7 +5491,7 @@
         <v>554235979</v>
       </c>
       <c r="H76" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="I76" t="s">
         <v>0</v>
@@ -5495,7 +5500,7 @@
         <v>13</v>
       </c>
       <c r="K76" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L76" t="s">
         <v>6</v>
@@ -5513,30 +5518,30 @@
         <v>0</v>
       </c>
       <c r="Q76" t="s">
-        <v>230</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>59465071</v>
+        <v>59466514</v>
       </c>
       <c r="B77" s="2">
-        <v>46087.424062500002</v>
+        <v>46087.436643518522</v>
       </c>
       <c r="C77">
-        <v>60531474</v>
+        <v>61596367</v>
       </c>
       <c r="D77" s="2">
-        <v>46107.489861111113</v>
+        <v>46127.401516203703</v>
       </c>
       <c r="E77" t="s">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="F77" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="G77">
-        <v>554235979</v>
+        <v>141679210</v>
       </c>
       <c r="H77" t="s">
         <v>174</v>
@@ -5562,143 +5567,143 @@
       <c r="O77" t="s">
         <v>0</v>
       </c>
-      <c r="P77">
-        <v>0</v>
+      <c r="P77" s="1">
+        <v>3213390</v>
       </c>
       <c r="Q77" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>59466514</v>
+        <v>59480507</v>
       </c>
       <c r="B78" s="2">
-        <v>46087.436643518522</v>
+        <v>46087.544247685182</v>
       </c>
       <c r="C78">
-        <v>61596367</v>
+        <v>60564140</v>
       </c>
       <c r="D78" s="2">
-        <v>46127.401516203703</v>
+        <v>46107.723194444443</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="F78" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G78">
-        <v>141679210</v>
+        <v>708547070</v>
       </c>
       <c r="H78" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="I78" t="s">
         <v>0</v>
       </c>
       <c r="J78" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K78" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O78" t="s">
         <v>0</v>
       </c>
-      <c r="P78" s="1">
-        <v>3213390</v>
+      <c r="P78" t="s">
+        <v>0</v>
       </c>
       <c r="Q78" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>59480507</v>
+        <v>59495473</v>
       </c>
       <c r="B79" s="2">
-        <v>46087.544247685182</v>
+        <v>46087.653935185182</v>
       </c>
       <c r="C79">
-        <v>60564140</v>
+        <v>61777147</v>
       </c>
       <c r="D79" s="2">
-        <v>46107.723194444443</v>
+        <v>46129.682083333333</v>
       </c>
       <c r="E79" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="F79" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G79">
-        <v>708547070</v>
+        <v>506727287</v>
       </c>
       <c r="H79" t="s">
-        <v>79</v>
+        <v>178</v>
       </c>
       <c r="I79" t="s">
         <v>0</v>
       </c>
       <c r="J79" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K79" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L79" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M79" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O79" t="s">
         <v>0</v>
       </c>
-      <c r="P79" t="s">
+      <c r="P79">
         <v>0</v>
       </c>
       <c r="Q79" t="s">
-        <v>140</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>59495473</v>
+        <v>59498233</v>
       </c>
       <c r="B80" s="2">
-        <v>46087.653935185182</v>
+        <v>46087.67423611111</v>
       </c>
       <c r="C80">
-        <v>61777147</v>
+        <v>59693004</v>
       </c>
       <c r="D80" s="2">
-        <v>46129.682083333333</v>
+        <v>46091.627928240741</v>
       </c>
       <c r="E80" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="F80" t="s">
         <v>177</v>
       </c>
       <c r="G80">
-        <v>506727287</v>
+        <v>606727287</v>
       </c>
       <c r="H80" t="s">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="I80" t="s">
         <v>0</v>
@@ -5707,7 +5712,7 @@
         <v>13</v>
       </c>
       <c r="K80" t="s">
-        <v>5</v>
+        <v>179</v>
       </c>
       <c r="L80" t="s">
         <v>6</v>
@@ -5725,42 +5730,42 @@
         <v>0</v>
       </c>
       <c r="Q80" t="s">
-        <v>216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>59498233</v>
+        <v>59537755</v>
       </c>
       <c r="B81" s="2">
-        <v>46087.67423611111</v>
+        <v>46088.586631944447</v>
       </c>
       <c r="C81">
-        <v>59693004</v>
+        <v>61591841</v>
       </c>
       <c r="D81" s="2">
-        <v>46091.627928240741</v>
+        <v>46127.35796296296</v>
       </c>
       <c r="E81" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="F81" t="s">
-        <v>177</v>
+        <v>280</v>
       </c>
       <c r="G81">
-        <v>606727287</v>
+        <v>556331131</v>
       </c>
       <c r="H81" t="s">
-        <v>61</v>
-      </c>
-      <c r="I81" t="s">
-        <v>0</v>
+        <v>230</v>
+      </c>
+      <c r="I81">
+        <v>1843236</v>
       </c>
       <c r="J81" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K81" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L81" t="s">
         <v>6</v>
@@ -5778,39 +5783,39 @@
         <v>0</v>
       </c>
       <c r="Q81" t="s">
-        <v>0</v>
+        <v>281</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>59537755</v>
+        <v>59541145</v>
       </c>
       <c r="B82" s="2">
-        <v>46088.586631944447</v>
+        <v>46088.634837962964</v>
       </c>
       <c r="C82">
-        <v>61591841</v>
+        <v>61385056</v>
       </c>
       <c r="D82" s="2">
-        <v>46127.35796296296</v>
+        <v>46122.772777777776</v>
       </c>
       <c r="E82" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="F82" t="s">
-        <v>282</v>
+        <v>181</v>
       </c>
       <c r="G82">
-        <v>556331131</v>
+        <v>546008131</v>
       </c>
       <c r="H82" t="s">
-        <v>231</v>
-      </c>
-      <c r="I82">
-        <v>1843236</v>
+        <v>182</v>
+      </c>
+      <c r="I82" t="s">
+        <v>0</v>
       </c>
       <c r="J82" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K82" t="s">
         <v>180</v>
@@ -5831,39 +5836,39 @@
         <v>0</v>
       </c>
       <c r="Q82" t="s">
-        <v>283</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>59541145</v>
+        <v>59606122</v>
       </c>
       <c r="B83" s="2">
-        <v>46088.634837962964</v>
+        <v>46090.447604166664</v>
       </c>
       <c r="C83">
-        <v>61385056</v>
+        <v>61897702</v>
       </c>
       <c r="D83" s="2">
-        <v>46122.772777777776</v>
+        <v>46132.349363425928</v>
       </c>
       <c r="E83" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="F83" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G83">
-        <v>546008131</v>
+        <v>708454305</v>
       </c>
       <c r="H83" t="s">
-        <v>182</v>
-      </c>
-      <c r="I83" t="s">
-        <v>0</v>
+        <v>282</v>
+      </c>
+      <c r="I83">
+        <v>1842206</v>
       </c>
       <c r="J83" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K83" t="s">
         <v>180</v>
@@ -5884,48 +5889,48 @@
         <v>0</v>
       </c>
       <c r="Q83" t="s">
-        <v>38</v>
+        <v>283</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>59606122</v>
+        <v>59615935</v>
       </c>
       <c r="B84" s="2">
-        <v>46090.447604166664</v>
+        <v>46090.512303240743</v>
       </c>
       <c r="C84">
-        <v>61897702</v>
+        <v>60393405</v>
       </c>
       <c r="D84" s="2">
-        <v>46132.349363425928</v>
+        <v>46105.432800925926</v>
       </c>
       <c r="E84" t="s">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="F84" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G84">
-        <v>708454305</v>
+        <v>767081456</v>
       </c>
       <c r="H84" t="s">
-        <v>284</v>
-      </c>
-      <c r="I84">
-        <v>1842206</v>
+        <v>185</v>
+      </c>
+      <c r="I84" t="s">
+        <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K84" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="L84" t="s">
         <v>6</v>
       </c>
       <c r="M84" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N84" t="s">
         <v>157</v>
@@ -5937,45 +5942,45 @@
         <v>0</v>
       </c>
       <c r="Q84" t="s">
-        <v>285</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>59615935</v>
+        <v>59684312</v>
       </c>
       <c r="B85" s="2">
-        <v>46090.512303240743</v>
+        <v>46091.557453703703</v>
       </c>
       <c r="C85">
-        <v>60393405</v>
+        <v>61372120</v>
       </c>
       <c r="D85" s="2">
-        <v>46105.432800925926</v>
+        <v>46122.663078703707</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
       </c>
       <c r="F85" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G85">
-        <v>767081456</v>
+        <v>3130227350</v>
       </c>
       <c r="H85" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I85" t="s">
         <v>0</v>
       </c>
       <c r="J85" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
       </c>
       <c r="L85" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M85" t="s">
         <v>3</v>
@@ -5986,52 +5991,52 @@
       <c r="O85" t="s">
         <v>0</v>
       </c>
-      <c r="P85">
+      <c r="P85" t="s">
         <v>0</v>
       </c>
       <c r="Q85" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>59684312</v>
+        <v>59793967</v>
       </c>
       <c r="B86" s="2">
-        <v>46091.557453703703</v>
+        <v>46093.406724537039</v>
       </c>
       <c r="C86">
-        <v>61372120</v>
+        <v>61919676</v>
       </c>
       <c r="D86" s="2">
-        <v>46122.663078703707</v>
+        <v>46132.513668981483</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="F86" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G86">
-        <v>3130227350</v>
+        <v>506727287</v>
       </c>
       <c r="H86" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I86" t="s">
         <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K86" t="s">
         <v>5</v>
       </c>
       <c r="L86" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M86" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N86" t="s">
         <v>157</v>
@@ -6039,37 +6044,37 @@
       <c r="O86" t="s">
         <v>0</v>
       </c>
-      <c r="P86" t="s">
+      <c r="P86">
         <v>0</v>
       </c>
       <c r="Q86" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>59793967</v>
+        <v>59801109</v>
       </c>
       <c r="B87" s="2">
-        <v>46093.406724537039</v>
+        <v>46093.464594907404</v>
       </c>
       <c r="C87">
-        <v>61919676</v>
+        <v>61169240</v>
       </c>
       <c r="D87" s="2">
-        <v>46132.513668981483</v>
+        <v>46119.558657407404</v>
       </c>
       <c r="E87" t="s">
-        <v>219</v>
+        <v>106</v>
       </c>
       <c r="F87" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G87">
-        <v>506727287</v>
+        <v>709173657</v>
       </c>
       <c r="H87" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="I87" t="s">
         <v>0</v>
@@ -6078,7 +6083,7 @@
         <v>13</v>
       </c>
       <c r="K87" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L87" t="s">
         <v>6</v>
@@ -6096,33 +6101,33 @@
         <v>0</v>
       </c>
       <c r="Q87" t="s">
-        <v>22</v>
+        <v>231</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>59801109</v>
+        <v>59813505</v>
       </c>
       <c r="B88" s="2">
-        <v>46093.464594907404</v>
+        <v>46093.557256944441</v>
       </c>
       <c r="C88">
-        <v>61169240</v>
+        <v>60137642</v>
       </c>
       <c r="D88" s="2">
-        <v>46119.558657407404</v>
+        <v>46099.71303240741</v>
       </c>
       <c r="E88" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="F88" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G88">
-        <v>709173657</v>
+        <v>706727287</v>
       </c>
       <c r="H88" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I88" t="s">
         <v>0</v>
@@ -6131,7 +6136,7 @@
         <v>13</v>
       </c>
       <c r="K88" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="L88" t="s">
         <v>6</v>
@@ -6140,7 +6145,7 @@
         <v>7</v>
       </c>
       <c r="N88" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O88" t="s">
         <v>0</v>
@@ -6149,39 +6154,39 @@
         <v>0</v>
       </c>
       <c r="Q88" t="s">
-        <v>232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>59813505</v>
+        <v>59816396</v>
       </c>
       <c r="B89" s="2">
-        <v>46093.557256944441</v>
+        <v>46093.580590277779</v>
       </c>
       <c r="C89">
-        <v>60137642</v>
+        <v>60137506</v>
       </c>
       <c r="D89" s="2">
-        <v>46099.71303240741</v>
+        <v>46099.711053240739</v>
       </c>
       <c r="E89" t="s">
         <v>126</v>
       </c>
       <c r="F89" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G89">
-        <v>706727287</v>
+        <v>506727287</v>
       </c>
       <c r="H89" t="s">
-        <v>193</v>
-      </c>
-      <c r="I89" t="s">
-        <v>0</v>
+        <v>203</v>
+      </c>
+      <c r="I89">
+        <v>1848446</v>
       </c>
       <c r="J89" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K89" t="s">
         <v>180</v>
@@ -6202,39 +6207,39 @@
         <v>0</v>
       </c>
       <c r="Q89" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>59816396</v>
+        <v>59820678</v>
       </c>
       <c r="B90" s="2">
-        <v>46093.580590277779</v>
+        <v>46093.612222222226</v>
       </c>
       <c r="C90">
-        <v>60137506</v>
+        <v>60208764</v>
       </c>
       <c r="D90" s="2">
-        <v>46099.711053240739</v>
+        <v>46100.766909722224</v>
       </c>
       <c r="E90" t="s">
         <v>126</v>
       </c>
       <c r="F90" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G90">
         <v>506727287</v>
       </c>
       <c r="H90" t="s">
-        <v>203</v>
-      </c>
-      <c r="I90">
-        <v>1848446</v>
+        <v>196</v>
+      </c>
+      <c r="I90" t="s">
+        <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K90" t="s">
         <v>180</v>
@@ -6255,33 +6260,33 @@
         <v>0</v>
       </c>
       <c r="Q90" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>59820678</v>
+        <v>59824550</v>
       </c>
       <c r="B91" s="2">
-        <v>46093.612222222226</v>
+        <v>46093.6405787037</v>
       </c>
       <c r="C91">
-        <v>60208764</v>
+        <v>61172877</v>
       </c>
       <c r="D91" s="2">
-        <v>46100.766909722224</v>
+        <v>46119.586805555555</v>
       </c>
       <c r="E91" t="s">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="F91" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G91">
         <v>506727287</v>
       </c>
       <c r="H91" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I91" t="s">
         <v>0</v>
@@ -6290,7 +6295,7 @@
         <v>13</v>
       </c>
       <c r="K91" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="L91" t="s">
         <v>6</v>
@@ -6299,7 +6304,7 @@
         <v>7</v>
       </c>
       <c r="N91" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O91" t="s">
         <v>0</v>
@@ -6308,33 +6313,33 @@
         <v>0</v>
       </c>
       <c r="Q91" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>59824550</v>
+        <v>59894743</v>
       </c>
       <c r="B92" s="2">
-        <v>46093.6405787037</v>
+        <v>46094.687673611108</v>
       </c>
       <c r="C92">
-        <v>61172877</v>
+        <v>60454133</v>
       </c>
       <c r="D92" s="2">
-        <v>46119.586805555555</v>
+        <v>46106.366770833331</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
       </c>
       <c r="F92" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G92">
-        <v>506727287</v>
+        <v>759668146</v>
       </c>
       <c r="H92" t="s">
-        <v>198</v>
+        <v>41</v>
       </c>
       <c r="I92" t="s">
         <v>0</v>
@@ -6357,37 +6362,37 @@
       <c r="O92" t="s">
         <v>0</v>
       </c>
-      <c r="P92">
+      <c r="P92" t="s">
         <v>0</v>
       </c>
       <c r="Q92" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>59894743</v>
+        <v>60026486</v>
       </c>
       <c r="B93" s="2">
-        <v>46094.687673611108</v>
+        <v>46098.36173611111</v>
       </c>
       <c r="C93">
-        <v>60454133</v>
+        <v>61477149</v>
       </c>
       <c r="D93" s="2">
-        <v>46106.366770833331</v>
+        <v>46125.453912037039</v>
       </c>
       <c r="E93" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F93" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="G93">
-        <v>759668146</v>
+        <v>506727287</v>
       </c>
       <c r="H93" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="I93" t="s">
         <v>0</v>
@@ -6396,7 +6401,7 @@
         <v>13</v>
       </c>
       <c r="K93" t="s">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="L93" t="s">
         <v>6</v>
@@ -6410,34 +6415,34 @@
       <c r="O93" t="s">
         <v>0</v>
       </c>
-      <c r="P93" t="s">
+      <c r="P93">
         <v>0</v>
       </c>
       <c r="Q93" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>60026486</v>
+        <v>60190035</v>
       </c>
       <c r="B94" s="2">
-        <v>46098.36173611111</v>
+        <v>46100.619201388887</v>
       </c>
       <c r="C94">
-        <v>61477149</v>
+        <v>61896785</v>
       </c>
       <c r="D94" s="2">
-        <v>46125.453912037039</v>
+        <v>46132.320810185185</v>
       </c>
       <c r="E94" t="s">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="F94" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="G94">
-        <v>506727287</v>
+        <v>708142290</v>
       </c>
       <c r="H94" t="s">
         <v>61</v>
@@ -6446,16 +6451,16 @@
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="K94" t="s">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="L94" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M94" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N94" t="s">
         <v>157</v>
@@ -6463,49 +6468,49 @@
       <c r="O94" t="s">
         <v>0</v>
       </c>
-      <c r="P94">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>19</v>
+      <c r="P94" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>2731640000</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>60190035</v>
+        <v>60356605</v>
       </c>
       <c r="B95" s="2">
-        <v>46100.619201388887</v>
+        <v>46104.623726851853</v>
       </c>
       <c r="C95">
-        <v>61896785</v>
+        <v>61596028</v>
       </c>
       <c r="D95" s="2">
-        <v>46132.320810185185</v>
+        <v>46127.398611111108</v>
       </c>
       <c r="E95" t="s">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="F95" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G95">
-        <v>708142290</v>
+        <v>504001081</v>
       </c>
       <c r="H95" t="s">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="I95" t="s">
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="K95" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="L95" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M95" t="s">
         <v>3</v>
@@ -6517,36 +6522,36 @@
         <v>0</v>
       </c>
       <c r="P95" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q95">
-        <v>2731640000</v>
+        <v>207</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>60356605</v>
+        <v>60399905</v>
       </c>
       <c r="B96" s="2">
-        <v>46104.623726851853</v>
+        <v>46105.484120370369</v>
       </c>
       <c r="C96">
-        <v>61596028</v>
+        <v>61785058</v>
       </c>
       <c r="D96" s="2">
-        <v>46127.398611111108</v>
+        <v>46129.746782407405</v>
       </c>
       <c r="E96" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F96" t="s">
-        <v>205</v>
+        <v>284</v>
       </c>
       <c r="G96">
         <v>504001081</v>
       </c>
       <c r="H96" t="s">
-        <v>206</v>
+        <v>285</v>
       </c>
       <c r="I96" t="s">
         <v>0</v>
@@ -6569,37 +6574,37 @@
       <c r="O96" t="s">
         <v>0</v>
       </c>
-      <c r="P96" t="s">
-        <v>207</v>
+      <c r="P96" s="1">
+        <v>1000000</v>
       </c>
       <c r="Q96" t="s">
-        <v>133</v>
+        <v>286</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>60399905</v>
+        <v>60416636</v>
       </c>
       <c r="B97" s="2">
-        <v>46105.484120370369</v>
+        <v>46105.623402777775</v>
       </c>
       <c r="C97">
-        <v>61785058</v>
+        <v>61795593</v>
       </c>
       <c r="D97" s="2">
-        <v>46129.746782407405</v>
+        <v>46129.873715277776</v>
       </c>
       <c r="E97" t="s">
-        <v>16</v>
+        <v>273</v>
       </c>
       <c r="F97" t="s">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="G97">
-        <v>504001081</v>
+        <v>172818143</v>
       </c>
       <c r="H97" t="s">
-        <v>287</v>
+        <v>135</v>
       </c>
       <c r="I97" t="s">
         <v>0</v>
@@ -6617,98 +6622,98 @@
         <v>3</v>
       </c>
       <c r="N97" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O97" t="s">
         <v>0</v>
       </c>
       <c r="P97" s="1">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="Q97" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>60416636</v>
+        <v>60458135</v>
       </c>
       <c r="B98" s="2">
-        <v>46105.623402777775</v>
+        <v>46106.415694444448</v>
       </c>
       <c r="C98">
-        <v>61795593</v>
+        <v>60953112</v>
       </c>
       <c r="D98" s="2">
-        <v>46129.873715277776</v>
+        <v>46114.564641203702</v>
       </c>
       <c r="E98" t="s">
-        <v>274</v>
+        <v>29</v>
       </c>
       <c r="F98" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="G98">
-        <v>172818143</v>
+        <v>708086472</v>
       </c>
       <c r="H98" t="s">
-        <v>135</v>
-      </c>
-      <c r="I98" t="s">
-        <v>0</v>
+        <v>233</v>
+      </c>
+      <c r="I98">
+        <v>1887906</v>
       </c>
       <c r="J98" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
       </c>
       <c r="L98" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M98" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="N98" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O98" t="s">
         <v>0</v>
       </c>
-      <c r="P98" s="1">
-        <v>500000</v>
+      <c r="P98" t="s">
+        <v>0</v>
       </c>
       <c r="Q98" t="s">
-        <v>289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>60458135</v>
+        <v>60458148</v>
       </c>
       <c r="B99" s="2">
-        <v>46106.415694444448</v>
+        <v>46106.41574074074</v>
       </c>
       <c r="C99">
-        <v>60953112</v>
+        <v>61737681</v>
       </c>
       <c r="D99" s="2">
-        <v>46114.564641203702</v>
+        <v>46129.39471064815</v>
       </c>
       <c r="E99" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F99" t="s">
-        <v>233</v>
+        <v>134</v>
       </c>
       <c r="G99">
         <v>708086472</v>
       </c>
       <c r="H99" t="s">
-        <v>234</v>
+        <v>288</v>
       </c>
       <c r="I99">
-        <v>1887906</v>
+        <v>1887866</v>
       </c>
       <c r="J99" t="s">
         <v>23</v>
@@ -6720,7 +6725,7 @@
         <v>8</v>
       </c>
       <c r="M99" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N99" t="s">
         <v>157</v>
@@ -6728,28 +6733,28 @@
       <c r="O99" t="s">
         <v>0</v>
       </c>
-      <c r="P99" t="s">
-        <v>0</v>
+      <c r="P99" s="1">
+        <v>580000</v>
       </c>
       <c r="Q99" t="s">
-        <v>0</v>
+        <v>289</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>60458148</v>
+        <v>60461761</v>
       </c>
       <c r="B100" s="2">
-        <v>46106.41574074074</v>
+        <v>46106.442974537036</v>
       </c>
       <c r="C100">
-        <v>61737681</v>
+        <v>60953978</v>
       </c>
       <c r="D100" s="2">
-        <v>46129.39471064815</v>
+        <v>46114.571631944447</v>
       </c>
       <c r="E100" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F100" t="s">
         <v>134</v>
@@ -6758,13 +6763,13 @@
         <v>708086472</v>
       </c>
       <c r="H100" t="s">
-        <v>290</v>
-      </c>
-      <c r="I100">
-        <v>1887866</v>
+        <v>89</v>
+      </c>
+      <c r="I100" t="s">
+        <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
@@ -6773,7 +6778,7 @@
         <v>8</v>
       </c>
       <c r="M100" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N100" t="s">
         <v>157</v>
@@ -6781,28 +6786,28 @@
       <c r="O100" t="s">
         <v>0</v>
       </c>
-      <c r="P100" s="1">
-        <v>580000</v>
+      <c r="P100" t="s">
+        <v>0</v>
       </c>
       <c r="Q100" t="s">
-        <v>291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>60461761</v>
+        <v>60461778</v>
       </c>
       <c r="B101" s="2">
-        <v>46106.442974537036</v>
+        <v>46106.443009259259</v>
       </c>
       <c r="C101">
-        <v>60953978</v>
+        <v>61918277</v>
       </c>
       <c r="D101" s="2">
-        <v>46114.571631944447</v>
+        <v>46132.506296296298</v>
       </c>
       <c r="E101" t="s">
-        <v>29</v>
+        <v>265</v>
       </c>
       <c r="F101" t="s">
         <v>134</v>
@@ -6826,7 +6831,7 @@
         <v>8</v>
       </c>
       <c r="M101" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N101" t="s">
         <v>157</v>
@@ -6834,28 +6839,28 @@
       <c r="O101" t="s">
         <v>0</v>
       </c>
-      <c r="P101" t="s">
-        <v>0</v>
+      <c r="P101" s="1">
+        <v>780000</v>
       </c>
       <c r="Q101" t="s">
-        <v>0</v>
+        <v>290</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>60461778</v>
+        <v>60463210</v>
       </c>
       <c r="B102" s="2">
-        <v>46106.443009259259</v>
+        <v>46106.455092592594</v>
       </c>
       <c r="C102">
-        <v>61918277</v>
+        <v>61926742</v>
       </c>
       <c r="D102" s="2">
-        <v>46132.506296296298</v>
+        <v>46132.566296296296</v>
       </c>
       <c r="E102" t="s">
-        <v>266</v>
+        <v>16</v>
       </c>
       <c r="F102" t="s">
         <v>134</v>
@@ -6864,7 +6869,7 @@
         <v>708086472</v>
       </c>
       <c r="H102" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I102" t="s">
         <v>0</v>
@@ -6879,7 +6884,7 @@
         <v>8</v>
       </c>
       <c r="M102" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N102" t="s">
         <v>157</v>
@@ -6887,52 +6892,52 @@
       <c r="O102" t="s">
         <v>0</v>
       </c>
-      <c r="P102" s="1">
-        <v>780000</v>
+      <c r="P102">
+        <v>0</v>
       </c>
       <c r="Q102" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>60463210</v>
+        <v>60486510</v>
       </c>
       <c r="B103" s="2">
-        <v>46106.455092592594</v>
+        <v>46106.647210648145</v>
       </c>
       <c r="C103">
-        <v>61926742</v>
+        <v>61909851</v>
       </c>
       <c r="D103" s="2">
-        <v>46132.566296296296</v>
+        <v>46132.449282407404</v>
       </c>
       <c r="E103" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F103" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="G103">
-        <v>708086472</v>
+        <v>710060780</v>
       </c>
       <c r="H103" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="I103" t="s">
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="K103" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L103" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M103" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N103" t="s">
         <v>157</v>
@@ -6940,52 +6945,52 @@
       <c r="O103" t="s">
         <v>0</v>
       </c>
-      <c r="P103">
+      <c r="P103" t="s">
         <v>0</v>
       </c>
       <c r="Q103" t="s">
-        <v>293</v>
+        <v>64</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>60486510</v>
+        <v>60748674</v>
       </c>
       <c r="B104" s="2">
-        <v>46106.647210648145</v>
+        <v>46111.511504629627</v>
       </c>
       <c r="C104">
-        <v>61909851</v>
+        <v>61760840</v>
       </c>
       <c r="D104" s="2">
-        <v>46132.449282407404</v>
+        <v>46129.562777777777</v>
       </c>
       <c r="E104" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F104" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G104">
-        <v>710060780</v>
+        <v>767791237</v>
       </c>
       <c r="H104" t="s">
-        <v>154</v>
+        <v>221</v>
       </c>
       <c r="I104" t="s">
         <v>0</v>
       </c>
       <c r="J104" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="K104" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L104" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M104" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N104" t="s">
         <v>157</v>
@@ -6993,52 +6998,52 @@
       <c r="O104" t="s">
         <v>0</v>
       </c>
-      <c r="P104" t="s">
+      <c r="P104">
         <v>0</v>
       </c>
       <c r="Q104" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>60748674</v>
+        <v>60760104</v>
       </c>
       <c r="B105" s="2">
-        <v>46111.511504629627</v>
+        <v>46111.598865740743</v>
       </c>
       <c r="C105">
-        <v>61760840</v>
+        <v>60973678</v>
       </c>
       <c r="D105" s="2">
-        <v>46129.562777777777</v>
+        <v>46114.718564814815</v>
       </c>
       <c r="E105" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F105" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G105">
-        <v>767791237</v>
+        <v>708187511</v>
       </c>
       <c r="H105" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I105" t="s">
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K105" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L105" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M105" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N105" t="s">
         <v>157</v>
@@ -7046,96 +7051,96 @@
       <c r="O105" t="s">
         <v>0</v>
       </c>
-      <c r="P105">
-        <v>0</v>
+      <c r="P105" s="1">
+        <v>150000</v>
       </c>
       <c r="Q105" t="s">
-        <v>145</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>60760104</v>
+        <v>60845648</v>
       </c>
       <c r="B106" s="2">
-        <v>46111.598865740743</v>
+        <v>46112.741215277776</v>
       </c>
       <c r="C106">
-        <v>60973678</v>
+        <v>61782693</v>
       </c>
       <c r="D106" s="2">
-        <v>46114.718564814815</v>
+        <v>46129.726678240739</v>
       </c>
       <c r="E106" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F106" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G106">
-        <v>708187511</v>
+        <v>707204274</v>
       </c>
       <c r="H106" t="s">
-        <v>224</v>
-      </c>
-      <c r="I106" t="s">
-        <v>0</v>
+        <v>234</v>
+      </c>
+      <c r="I106">
+        <v>1853956</v>
       </c>
       <c r="J106" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K106" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M106" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N106" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O106" t="s">
         <v>0</v>
       </c>
-      <c r="P106" s="1">
-        <v>150000</v>
+      <c r="P106" t="s">
+        <v>0</v>
       </c>
       <c r="Q106" t="s">
-        <v>38</v>
+        <v>292</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>60845648</v>
+        <v>60845660</v>
       </c>
       <c r="B107" s="2">
-        <v>46112.741215277776</v>
+        <v>46112.741261574076</v>
       </c>
       <c r="C107">
-        <v>61782693</v>
+        <v>61901967</v>
       </c>
       <c r="D107" s="2">
-        <v>46129.726678240739</v>
+        <v>46132.392962962964</v>
       </c>
       <c r="E107" t="s">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="F107" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G107">
         <v>707204274</v>
       </c>
       <c r="H107" t="s">
-        <v>235</v>
-      </c>
-      <c r="I107">
-        <v>1853956</v>
+        <v>236</v>
+      </c>
+      <c r="I107" t="s">
+        <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K107" t="s">
         <v>5</v>
@@ -7144,45 +7149,45 @@
         <v>8</v>
       </c>
       <c r="M107" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N107" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O107" t="s">
         <v>0</v>
       </c>
-      <c r="P107" t="s">
-        <v>0</v>
+      <c r="P107" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q107" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>60845660</v>
+        <v>60972166</v>
       </c>
       <c r="B108" s="2">
-        <v>46112.741261574076</v>
+        <v>46114.708020833335</v>
       </c>
       <c r="C108">
-        <v>61901967</v>
+        <v>61551594</v>
       </c>
       <c r="D108" s="2">
-        <v>46132.392962962964</v>
+        <v>46126.548171296294</v>
       </c>
       <c r="E108" t="s">
-        <v>29</v>
+        <v>214</v>
       </c>
       <c r="F108" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G108">
-        <v>707204274</v>
+        <v>160128782</v>
       </c>
       <c r="H108" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I108" t="s">
         <v>0</v>
@@ -7197,7 +7202,7 @@
         <v>8</v>
       </c>
       <c r="M108" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N108" t="s">
         <v>157</v>
@@ -7206,36 +7211,36 @@
         <v>0</v>
       </c>
       <c r="P108" s="1">
-        <v>5324000</v>
+        <v>800000</v>
       </c>
       <c r="Q108" t="s">
-        <v>295</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>60972166</v>
+        <v>60991432</v>
       </c>
       <c r="B109" s="2">
-        <v>46114.708020833335</v>
+        <v>46115.387835648151</v>
       </c>
       <c r="C109">
-        <v>61551594</v>
+        <v>61698030</v>
       </c>
       <c r="D109" s="2">
-        <v>46126.548171296294</v>
+        <v>46128.625925925924</v>
       </c>
       <c r="E109" t="s">
-        <v>214</v>
+        <v>65</v>
       </c>
       <c r="F109" t="s">
-        <v>238</v>
+        <v>112</v>
       </c>
       <c r="G109">
-        <v>160128782</v>
+        <v>707079088</v>
       </c>
       <c r="H109" t="s">
-        <v>239</v>
+        <v>85</v>
       </c>
       <c r="I109" t="s">
         <v>0</v>
@@ -7253,13 +7258,13 @@
         <v>3</v>
       </c>
       <c r="N109" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O109" t="s">
         <v>0</v>
       </c>
       <c r="P109" s="1">
-        <v>800000</v>
+        <v>1600000</v>
       </c>
       <c r="Q109" t="s">
         <v>34</v>
@@ -7267,52 +7272,52 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110">
-        <v>60991432</v>
+        <v>61157877</v>
       </c>
       <c r="B110" s="2">
-        <v>46115.387835648151</v>
+        <v>46119.475821759261</v>
       </c>
       <c r="C110">
-        <v>61698030</v>
+        <v>61510897</v>
       </c>
       <c r="D110" s="2">
-        <v>46128.625925925924</v>
+        <v>46125.702361111114</v>
       </c>
       <c r="E110" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="F110" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="G110">
-        <v>707079088</v>
+        <v>700726215</v>
       </c>
       <c r="H110" t="s">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="I110" t="s">
         <v>0</v>
       </c>
       <c r="J110" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K110" t="s">
         <v>5</v>
       </c>
       <c r="L110" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M110" t="s">
         <v>3</v>
       </c>
       <c r="N110" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O110" t="s">
         <v>0</v>
       </c>
       <c r="P110" s="1">
-        <v>1600000</v>
+        <v>500000</v>
       </c>
       <c r="Q110" t="s">
         <v>34</v>
@@ -7320,40 +7325,40 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111">
-        <v>61157877</v>
+        <v>61183418</v>
       </c>
       <c r="B111" s="2">
-        <v>46119.475821759261</v>
+        <v>46119.659594907411</v>
       </c>
       <c r="C111">
-        <v>61510897</v>
+        <v>61686421</v>
       </c>
       <c r="D111" s="2">
-        <v>46125.702361111114</v>
+        <v>46128.540682870371</v>
       </c>
       <c r="E111" t="s">
-        <v>10</v>
+        <v>265</v>
       </c>
       <c r="F111" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G111">
-        <v>700726215</v>
+        <v>707241025</v>
       </c>
       <c r="H111" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I111" t="s">
         <v>0</v>
       </c>
       <c r="J111" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K111" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L111" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M111" t="s">
         <v>3</v>
@@ -7364,49 +7369,49 @@
       <c r="O111" t="s">
         <v>0</v>
       </c>
-      <c r="P111" s="1">
-        <v>500000</v>
+      <c r="P111" t="s">
+        <v>0</v>
       </c>
       <c r="Q111" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112">
-        <v>61183418</v>
+        <v>61220151</v>
       </c>
       <c r="B112" s="2">
-        <v>46119.659594907411</v>
+        <v>46120.483217592591</v>
       </c>
       <c r="C112">
-        <v>61686421</v>
+        <v>61565396</v>
       </c>
       <c r="D112" s="2">
-        <v>46128.540682870371</v>
+        <v>46126.645810185182</v>
       </c>
       <c r="E112" t="s">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="F112" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="G112">
-        <v>707241025</v>
+        <v>708086759</v>
       </c>
       <c r="H112" t="s">
-        <v>243</v>
+        <v>121</v>
       </c>
       <c r="I112" t="s">
         <v>0</v>
       </c>
       <c r="J112" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K112" t="s">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="L112" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M112" t="s">
         <v>3</v>
@@ -7417,46 +7422,46 @@
       <c r="O112" t="s">
         <v>0</v>
       </c>
-      <c r="P112" t="s">
+      <c r="P112">
         <v>0</v>
       </c>
       <c r="Q112" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113">
-        <v>61220151</v>
+        <v>61220160</v>
       </c>
       <c r="B113" s="2">
-        <v>46120.483217592591</v>
+        <v>46120.483368055553</v>
       </c>
       <c r="C113">
-        <v>61565396</v>
+        <v>61742545</v>
       </c>
       <c r="D113" s="2">
-        <v>46126.645810185182</v>
+        <v>46129.436898148146</v>
       </c>
       <c r="E113" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="F113" t="s">
-        <v>43</v>
+        <v>243</v>
       </c>
       <c r="G113">
-        <v>708086759</v>
+        <v>102571205</v>
       </c>
       <c r="H113" t="s">
-        <v>121</v>
+        <v>244</v>
       </c>
       <c r="I113" t="s">
         <v>0</v>
       </c>
       <c r="J113" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K113" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="L113" t="s">
         <v>8</v>
@@ -7470,49 +7475,49 @@
       <c r="O113" t="s">
         <v>0</v>
       </c>
-      <c r="P113">
-        <v>0</v>
+      <c r="P113" s="1">
+        <v>5000000</v>
       </c>
       <c r="Q113" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114">
-        <v>61220160</v>
+        <v>61220566</v>
       </c>
       <c r="B114" s="2">
-        <v>46120.483368055553</v>
+        <v>46120.490034722221</v>
       </c>
       <c r="C114">
-        <v>61742545</v>
+        <v>61565070</v>
       </c>
       <c r="D114" s="2">
-        <v>46129.436898148146</v>
+        <v>46126.643611111111</v>
       </c>
       <c r="E114" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="F114" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="G114">
-        <v>102571205</v>
+        <v>708086759</v>
       </c>
       <c r="H114" t="s">
-        <v>245</v>
+        <v>121</v>
       </c>
       <c r="I114" t="s">
         <v>0</v>
       </c>
       <c r="J114" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K114" t="s">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="L114" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M114" t="s">
         <v>3</v>
@@ -7523,52 +7528,52 @@
       <c r="O114" t="s">
         <v>0</v>
       </c>
-      <c r="P114" s="1">
-        <v>5000000</v>
+      <c r="P114">
+        <v>0</v>
       </c>
       <c r="Q114" t="s">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115">
-        <v>61220566</v>
+        <v>61238771</v>
       </c>
       <c r="B115" s="2">
-        <v>46120.490034722221</v>
+        <v>46120.619884259257</v>
       </c>
       <c r="C115">
-        <v>61565070</v>
+        <v>61742178</v>
       </c>
       <c r="D115" s="2">
-        <v>46126.643611111111</v>
+        <v>46129.434178240743</v>
       </c>
       <c r="E115" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F115" t="s">
-        <v>43</v>
+        <v>245</v>
       </c>
       <c r="G115">
-        <v>708086759</v>
+        <v>709666018</v>
       </c>
       <c r="H115" t="s">
-        <v>121</v>
+        <v>246</v>
       </c>
       <c r="I115" t="s">
         <v>0</v>
       </c>
       <c r="J115" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="K115" t="s">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="L115" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M115" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N115" t="s">
         <v>157</v>
@@ -7576,37 +7581,37 @@
       <c r="O115" t="s">
         <v>0</v>
       </c>
-      <c r="P115">
+      <c r="P115" t="s">
         <v>0</v>
       </c>
       <c r="Q115" t="s">
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116">
-        <v>61238771</v>
+        <v>61239047</v>
       </c>
       <c r="B116" s="2">
-        <v>46120.619884259257</v>
+        <v>46120.622071759259</v>
       </c>
       <c r="C116">
-        <v>61742178</v>
+        <v>61906404</v>
       </c>
       <c r="D116" s="2">
-        <v>46129.434178240743</v>
+        <v>46132.425625000003</v>
       </c>
       <c r="E116" t="s">
-        <v>10</v>
+        <v>276</v>
       </c>
       <c r="F116" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G116">
-        <v>709666018</v>
+        <v>103381121</v>
       </c>
       <c r="H116" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I116" t="s">
         <v>0</v>
@@ -7615,7 +7620,7 @@
         <v>75</v>
       </c>
       <c r="K116" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L116" t="s">
         <v>2</v>
@@ -7629,37 +7634,37 @@
       <c r="O116" t="s">
         <v>0</v>
       </c>
-      <c r="P116" t="s">
+      <c r="P116">
         <v>0</v>
       </c>
       <c r="Q116" t="s">
-        <v>140</v>
+        <v>294</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117">
-        <v>61239047</v>
+        <v>61239287</v>
       </c>
       <c r="B117" s="2">
-        <v>46120.622071759259</v>
+        <v>46120.623703703706</v>
       </c>
       <c r="C117">
-        <v>61906404</v>
+        <v>61749741</v>
       </c>
       <c r="D117" s="2">
-        <v>46132.425625000003</v>
+        <v>46129.483819444446</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>10</v>
       </c>
       <c r="F117" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G117">
-        <v>103381121</v>
+        <v>769218598</v>
       </c>
       <c r="H117" t="s">
-        <v>249</v>
+        <v>85</v>
       </c>
       <c r="I117" t="s">
         <v>0</v>
@@ -7668,7 +7673,7 @@
         <v>75</v>
       </c>
       <c r="K117" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L117" t="s">
         <v>2</v>
@@ -7682,34 +7687,34 @@
       <c r="O117" t="s">
         <v>0</v>
       </c>
-      <c r="P117">
+      <c r="P117" t="s">
         <v>0</v>
       </c>
       <c r="Q117" t="s">
-        <v>296</v>
+        <v>133</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118">
-        <v>61239287</v>
+        <v>61239330</v>
       </c>
       <c r="B118" s="2">
-        <v>46120.623703703706</v>
+        <v>46120.62395833333</v>
       </c>
       <c r="C118">
-        <v>61749741</v>
+        <v>61664549</v>
       </c>
       <c r="D118" s="2">
-        <v>46129.483819444446</v>
+        <v>46128.389027777775</v>
       </c>
       <c r="E118" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F118" t="s">
-        <v>250</v>
+        <v>134</v>
       </c>
       <c r="G118">
-        <v>769218598</v>
+        <v>708086472</v>
       </c>
       <c r="H118" t="s">
         <v>85</v>
@@ -7739,33 +7744,33 @@
         <v>0</v>
       </c>
       <c r="Q118" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119">
-        <v>61239330</v>
+        <v>61240327</v>
       </c>
       <c r="B119" s="2">
-        <v>46120.62395833333</v>
+        <v>46120.631747685184</v>
       </c>
       <c r="C119">
-        <v>61664549</v>
+        <v>61667960</v>
       </c>
       <c r="D119" s="2">
-        <v>46128.389027777775</v>
+        <v>46128.415625000001</v>
       </c>
       <c r="E119" t="s">
         <v>21</v>
       </c>
       <c r="F119" t="s">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="G119">
-        <v>708086472</v>
+        <v>103381121</v>
       </c>
       <c r="H119" t="s">
-        <v>85</v>
+        <v>248</v>
       </c>
       <c r="I119" t="s">
         <v>0</v>
@@ -7788,37 +7793,37 @@
       <c r="O119" t="s">
         <v>0</v>
       </c>
-      <c r="P119" t="s">
+      <c r="P119">
         <v>0</v>
       </c>
       <c r="Q119" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120">
-        <v>61240327</v>
+        <v>61240462</v>
       </c>
       <c r="B120" s="2">
-        <v>46120.631747685184</v>
+        <v>46120.632835648146</v>
       </c>
       <c r="C120">
-        <v>61667960</v>
+        <v>61905847</v>
       </c>
       <c r="D120" s="2">
-        <v>46128.415625000001</v>
+        <v>46132.421574074076</v>
       </c>
       <c r="E120" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="F120" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G120">
-        <v>103381121</v>
+        <v>769218598</v>
       </c>
       <c r="H120" t="s">
-        <v>249</v>
+        <v>85</v>
       </c>
       <c r="I120" t="s">
         <v>0</v>
@@ -7827,7 +7832,7 @@
         <v>75</v>
       </c>
       <c r="K120" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L120" t="s">
         <v>2</v>
@@ -7841,31 +7846,31 @@
       <c r="O120" t="s">
         <v>0</v>
       </c>
-      <c r="P120">
+      <c r="P120" t="s">
         <v>0</v>
       </c>
       <c r="Q120" t="s">
-        <v>39</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121">
-        <v>61240462</v>
+        <v>61241295</v>
       </c>
       <c r="B121" s="2">
-        <v>46120.632835648146</v>
+        <v>46120.637986111113</v>
       </c>
       <c r="C121">
-        <v>61905847</v>
+        <v>61904451</v>
       </c>
       <c r="D121" s="2">
-        <v>46132.421574074076</v>
+        <v>46132.411168981482</v>
       </c>
       <c r="E121" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F121" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G121">
         <v>769218598</v>
@@ -7898,33 +7903,33 @@
         <v>0</v>
       </c>
       <c r="Q121" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>61241295</v>
+        <v>61242033</v>
       </c>
       <c r="B122" s="2">
-        <v>46120.637986111113</v>
+        <v>46120.643912037034</v>
       </c>
       <c r="C122">
-        <v>61904451</v>
+        <v>61743482</v>
       </c>
       <c r="D122" s="2">
-        <v>46132.411168981482</v>
+        <v>46129.442071759258</v>
       </c>
       <c r="E122" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="F122" t="s">
         <v>250</v>
       </c>
       <c r="G122">
-        <v>769218598</v>
+        <v>747636152</v>
       </c>
       <c r="H122" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="I122" t="s">
         <v>0</v>
@@ -7933,7 +7938,7 @@
         <v>75</v>
       </c>
       <c r="K122" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L122" t="s">
         <v>2</v>
@@ -7947,37 +7952,37 @@
       <c r="O122" t="s">
         <v>0</v>
       </c>
-      <c r="P122" t="s">
+      <c r="P122">
         <v>0</v>
       </c>
       <c r="Q122" t="s">
-        <v>298</v>
+        <v>133</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123">
-        <v>61242033</v>
+        <v>61242255</v>
       </c>
       <c r="B123" s="2">
-        <v>46120.643912037034</v>
+        <v>46120.645127314812</v>
       </c>
       <c r="C123">
-        <v>61743482</v>
+        <v>61919677</v>
       </c>
       <c r="D123" s="2">
-        <v>46129.442071759258</v>
+        <v>46132.513680555552</v>
       </c>
       <c r="E123" t="s">
-        <v>21</v>
+        <v>265</v>
       </c>
       <c r="F123" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G123">
-        <v>747636152</v>
+        <v>769218598</v>
       </c>
       <c r="H123" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I123" t="s">
         <v>0</v>
@@ -7986,7 +7991,7 @@
         <v>75</v>
       </c>
       <c r="K123" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L123" t="s">
         <v>2</v>
@@ -8000,37 +8005,37 @@
       <c r="O123" t="s">
         <v>0</v>
       </c>
-      <c r="P123">
+      <c r="P123" t="s">
         <v>0</v>
       </c>
       <c r="Q123" t="s">
-        <v>133</v>
+        <v>297</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124">
-        <v>61242255</v>
+        <v>61243441</v>
       </c>
       <c r="B124" s="2">
-        <v>46120.645127314812</v>
+        <v>46120.652592592596</v>
       </c>
       <c r="C124">
-        <v>61919677</v>
+        <v>61667044</v>
       </c>
       <c r="D124" s="2">
-        <v>46132.513680555552</v>
+        <v>46128.40902777778</v>
       </c>
       <c r="E124" t="s">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="F124" t="s">
         <v>250</v>
       </c>
       <c r="G124">
-        <v>769218598</v>
+        <v>747636152</v>
       </c>
       <c r="H124" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="I124" t="s">
         <v>0</v>
@@ -8039,7 +8044,7 @@
         <v>75</v>
       </c>
       <c r="K124" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L124" t="s">
         <v>2</v>
@@ -8053,49 +8058,49 @@
       <c r="O124" t="s">
         <v>0</v>
       </c>
-      <c r="P124" t="s">
+      <c r="P124">
         <v>0</v>
       </c>
       <c r="Q124" t="s">
-        <v>299</v>
+        <v>35</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125">
-        <v>61243441</v>
+        <v>61243727</v>
       </c>
       <c r="B125" s="2">
-        <v>46120.652592592596</v>
+        <v>46120.654999999999</v>
       </c>
       <c r="C125">
-        <v>61667044</v>
+        <v>61661110</v>
       </c>
       <c r="D125" s="2">
-        <v>46128.40902777778</v>
+        <v>46128.349027777775</v>
       </c>
       <c r="E125" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="F125" t="s">
         <v>251</v>
       </c>
       <c r="G125">
-        <v>747636152</v>
+        <v>707974053</v>
       </c>
       <c r="H125" t="s">
-        <v>107</v>
+        <v>252</v>
       </c>
       <c r="I125" t="s">
         <v>0</v>
       </c>
       <c r="J125" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="K125" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L125" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M125" t="s">
         <v>7</v>
@@ -8110,80 +8115,80 @@
         <v>0</v>
       </c>
       <c r="Q125" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126">
-        <v>61243727</v>
+        <v>61244524</v>
       </c>
       <c r="B126" s="2">
-        <v>46120.654999999999</v>
+        <v>46120.66065972222</v>
       </c>
       <c r="C126">
-        <v>61661110</v>
+        <v>61898472</v>
       </c>
       <c r="D126" s="2">
-        <v>46128.349027777775</v>
+        <v>46132.359768518516</v>
       </c>
       <c r="E126" t="s">
-        <v>214</v>
+        <v>265</v>
       </c>
       <c r="F126" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G126">
-        <v>707974053</v>
+        <v>757818829</v>
       </c>
       <c r="H126" t="s">
-        <v>253</v>
+        <v>85</v>
       </c>
       <c r="I126" t="s">
         <v>0</v>
       </c>
       <c r="J126" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="K126" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L126" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M126" t="s">
         <v>7</v>
       </c>
       <c r="N126" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O126" t="s">
         <v>0</v>
       </c>
-      <c r="P126">
+      <c r="P126" t="s">
         <v>0</v>
       </c>
       <c r="Q126" t="s">
-        <v>37</v>
+        <v>298</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127">
-        <v>61244524</v>
+        <v>61245220</v>
       </c>
       <c r="B127" s="2">
-        <v>46120.66065972222</v>
+        <v>46120.666134259256</v>
       </c>
       <c r="C127">
-        <v>61898472</v>
+        <v>61905058</v>
       </c>
       <c r="D127" s="2">
-        <v>46132.359768518516</v>
+        <v>46132.415659722225</v>
       </c>
       <c r="E127" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F127" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G127">
         <v>757818829</v>
@@ -8207,7 +8212,7 @@
         <v>7</v>
       </c>
       <c r="N127" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O127" t="s">
         <v>0</v>
@@ -8216,33 +8221,33 @@
         <v>0</v>
       </c>
       <c r="Q127" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128">
-        <v>61245220</v>
+        <v>61246231</v>
       </c>
       <c r="B128" s="2">
-        <v>46120.666134259256</v>
+        <v>46120.673449074071</v>
       </c>
       <c r="C128">
-        <v>61905058</v>
+        <v>61739144</v>
       </c>
       <c r="D128" s="2">
-        <v>46132.415659722225</v>
+        <v>46129.408194444448</v>
       </c>
       <c r="E128" t="s">
-        <v>278</v>
+        <v>10</v>
       </c>
       <c r="F128" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G128">
         <v>757818829</v>
       </c>
       <c r="H128" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="I128" t="s">
         <v>0</v>
@@ -8251,7 +8256,7 @@
         <v>75</v>
       </c>
       <c r="K128" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L128" t="s">
         <v>2</v>
@@ -8269,30 +8274,30 @@
         <v>0</v>
       </c>
       <c r="Q128" t="s">
-        <v>301</v>
+        <v>35</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129">
-        <v>61246231</v>
+        <v>61248751</v>
       </c>
       <c r="B129" s="2">
-        <v>46120.673449074071</v>
+        <v>46120.692800925928</v>
       </c>
       <c r="C129">
-        <v>61739144</v>
+        <v>61667255</v>
       </c>
       <c r="D129" s="2">
-        <v>46129.408194444448</v>
+        <v>46128.41065972222</v>
       </c>
       <c r="E129" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F129" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G129">
-        <v>757818829</v>
+        <v>747636152</v>
       </c>
       <c r="H129" t="s">
         <v>154</v>
@@ -8318,55 +8323,55 @@
       <c r="O129" t="s">
         <v>0</v>
       </c>
-      <c r="P129" t="s">
+      <c r="P129">
         <v>0</v>
       </c>
       <c r="Q129" t="s">
-        <v>35</v>
+        <v>215</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130">
-        <v>61248751</v>
+        <v>61254924</v>
       </c>
       <c r="B130" s="2">
-        <v>46120.692800925928</v>
+        <v>46120.74763888889</v>
       </c>
       <c r="C130">
-        <v>61667255</v>
+        <v>61737877</v>
       </c>
       <c r="D130" s="2">
-        <v>46128.41065972222</v>
+        <v>46129.396273148152</v>
       </c>
       <c r="E130" t="s">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="F130" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G130">
-        <v>747636152</v>
+        <v>757818829</v>
       </c>
       <c r="H130" t="s">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="I130" t="s">
         <v>0</v>
       </c>
       <c r="J130" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="K130" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L130" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M130" t="s">
         <v>7</v>
       </c>
       <c r="N130" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O130" t="s">
         <v>0</v>
@@ -8375,27 +8380,27 @@
         <v>0</v>
       </c>
       <c r="Q130" t="s">
-        <v>216</v>
+        <v>140</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131">
-        <v>61254924</v>
+        <v>61255381</v>
       </c>
       <c r="B131" s="2">
-        <v>46120.74763888889</v>
+        <v>46120.752291666664</v>
       </c>
       <c r="C131">
-        <v>61737877</v>
+        <v>61767294</v>
       </c>
       <c r="D131" s="2">
-        <v>46129.396273148152</v>
+        <v>46129.614317129628</v>
       </c>
       <c r="E131" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F131" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G131">
         <v>757818829</v>
@@ -8428,33 +8433,33 @@
         <v>0</v>
       </c>
       <c r="Q131" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132">
-        <v>61255381</v>
+        <v>61255901</v>
       </c>
       <c r="B132" s="2">
-        <v>46120.752291666664</v>
+        <v>46120.75712962963</v>
       </c>
       <c r="C132">
-        <v>61767294</v>
+        <v>61777545</v>
       </c>
       <c r="D132" s="2">
-        <v>46129.614317129628</v>
+        <v>46129.684988425928</v>
       </c>
       <c r="E132" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F132" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G132">
         <v>757818829</v>
       </c>
       <c r="H132" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="I132" t="s">
         <v>0</v>
@@ -8481,33 +8486,33 @@
         <v>0</v>
       </c>
       <c r="Q132" t="s">
-        <v>35</v>
+        <v>216</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133">
-        <v>61255901</v>
+        <v>61256462</v>
       </c>
       <c r="B133" s="2">
-        <v>46120.75712962963</v>
+        <v>46120.762939814813</v>
       </c>
       <c r="C133">
-        <v>61777545</v>
+        <v>61660450</v>
       </c>
       <c r="D133" s="2">
-        <v>46129.684988425928</v>
+        <v>46128.337118055555</v>
       </c>
       <c r="E133" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F133" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G133">
         <v>757818829</v>
       </c>
       <c r="H133" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="I133" t="s">
         <v>0</v>
@@ -8525,7 +8530,7 @@
         <v>7</v>
       </c>
       <c r="N133" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O133" t="s">
         <v>0</v>
@@ -8534,21 +8539,21 @@
         <v>0</v>
       </c>
       <c r="Q133" t="s">
-        <v>217</v>
+        <v>39</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134">
-        <v>61256462</v>
+        <v>61315991</v>
       </c>
       <c r="B134" s="2">
-        <v>46120.762939814813</v>
+        <v>46121.743379629632</v>
       </c>
       <c r="C134">
-        <v>61660450</v>
+        <v>61480791</v>
       </c>
       <c r="D134" s="2">
-        <v>46128.337118055555</v>
+        <v>46125.478912037041</v>
       </c>
       <c r="E134" t="s">
         <v>214</v>
@@ -8557,25 +8562,25 @@
         <v>254</v>
       </c>
       <c r="G134">
-        <v>757818829</v>
+        <v>778495680</v>
       </c>
       <c r="H134" t="s">
-        <v>41</v>
-      </c>
-      <c r="I134" t="s">
+        <v>255</v>
+      </c>
+      <c r="I134">
         <v>0</v>
       </c>
       <c r="J134" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K134" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L134" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M134" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N134" t="s">
         <v>157</v>
@@ -8583,49 +8588,49 @@
       <c r="O134" t="s">
         <v>0</v>
       </c>
-      <c r="P134">
+      <c r="P134" t="s">
         <v>0</v>
       </c>
       <c r="Q134" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A135">
-        <v>61315991</v>
+        <v>61317028</v>
       </c>
       <c r="B135" s="2">
-        <v>46121.743379629632</v>
+        <v>46121.753101851849</v>
       </c>
       <c r="C135">
-        <v>61480791</v>
+        <v>61771450</v>
       </c>
       <c r="D135" s="2">
-        <v>46125.478912037041</v>
+        <v>46129.645810185182</v>
       </c>
       <c r="E135" t="s">
-        <v>214</v>
+        <v>29</v>
       </c>
       <c r="F135" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G135">
-        <v>778495680</v>
+        <v>4414839740</v>
       </c>
       <c r="H135" t="s">
-        <v>256</v>
-      </c>
-      <c r="I135">
+        <v>257</v>
+      </c>
+      <c r="I135" t="s">
         <v>0</v>
       </c>
       <c r="J135" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K135" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L135" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M135" t="s">
         <v>3</v>
@@ -8640,33 +8645,33 @@
         <v>0</v>
       </c>
       <c r="Q135" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A136">
-        <v>61317028</v>
+        <v>61336527</v>
       </c>
       <c r="B136" s="2">
-        <v>46121.753101851849</v>
+        <v>46122.368761574071</v>
       </c>
       <c r="C136">
-        <v>61771450</v>
+        <v>61479619</v>
       </c>
       <c r="D136" s="2">
-        <v>46129.645810185182</v>
+        <v>46125.4690625</v>
       </c>
       <c r="E136" t="s">
-        <v>29</v>
+        <v>214</v>
       </c>
       <c r="F136" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G136">
-        <v>4414839740</v>
+        <v>778495680</v>
       </c>
       <c r="H136" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I136" t="s">
         <v>0</v>
@@ -8675,7 +8680,7 @@
         <v>13</v>
       </c>
       <c r="K136" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L136" t="s">
         <v>6</v>
@@ -8689,37 +8694,37 @@
       <c r="O136" t="s">
         <v>0</v>
       </c>
-      <c r="P136" t="s">
-        <v>0</v>
+      <c r="P136" s="1">
+        <v>1679940</v>
       </c>
       <c r="Q136" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A137">
-        <v>61336527</v>
+        <v>61474571</v>
       </c>
       <c r="B137" s="2">
-        <v>46122.368761574071</v>
+        <v>46125.437488425923</v>
       </c>
       <c r="C137">
-        <v>61479619</v>
+        <v>61919301</v>
       </c>
       <c r="D137" s="2">
-        <v>46125.4690625</v>
+        <v>46132.511481481481</v>
       </c>
       <c r="E137" t="s">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="F137" t="s">
         <v>259</v>
       </c>
       <c r="G137">
-        <v>778495680</v>
+        <v>707974053</v>
       </c>
       <c r="H137" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="I137" t="s">
         <v>0</v>
@@ -8734,7 +8739,7 @@
         <v>6</v>
       </c>
       <c r="M137" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N137" t="s">
         <v>157</v>
@@ -8742,31 +8747,31 @@
       <c r="O137" t="s">
         <v>0</v>
       </c>
-      <c r="P137" s="1">
-        <v>1679940</v>
+      <c r="P137">
+        <v>0</v>
       </c>
       <c r="Q137" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A138">
-        <v>61474571</v>
+        <v>61475299</v>
       </c>
       <c r="B138" s="2">
-        <v>46125.437488425923</v>
+        <v>46125.442372685182</v>
       </c>
       <c r="C138">
-        <v>61919301</v>
+        <v>61740285</v>
       </c>
       <c r="D138" s="2">
-        <v>46132.511481481481</v>
+        <v>46129.416886574072</v>
       </c>
       <c r="E138" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F138" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G138">
         <v>707974053</v>
@@ -8804,22 +8809,22 @@
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A139">
-        <v>61475299</v>
+        <v>61475818</v>
       </c>
       <c r="B139" s="2">
-        <v>46125.442372685182</v>
+        <v>46125.445914351854</v>
       </c>
       <c r="C139">
-        <v>61578769</v>
+        <v>61919107</v>
       </c>
       <c r="D139" s="2">
-        <v>46126.756122685183</v>
+        <v>46132.510324074072</v>
       </c>
       <c r="E139" t="s">
-        <v>302</v>
+        <v>21</v>
       </c>
       <c r="F139" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G139">
         <v>707974053</v>
@@ -8843,7 +8848,7 @@
         <v>7</v>
       </c>
       <c r="N139" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O139" t="s">
         <v>0</v>
@@ -8857,43 +8862,43 @@
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A140">
-        <v>61475299</v>
+        <v>61481328</v>
       </c>
       <c r="B140" s="2">
-        <v>46125.442372685182</v>
+        <v>46125.483310185184</v>
       </c>
       <c r="C140">
-        <v>61740285</v>
+        <v>61481390</v>
       </c>
       <c r="D140" s="2">
-        <v>46129.416886574072</v>
+        <v>46125.483553240738</v>
       </c>
       <c r="E140" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="F140" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G140">
-        <v>707974053</v>
+        <v>708448800</v>
       </c>
       <c r="H140" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I140" t="s">
         <v>0</v>
       </c>
       <c r="J140" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K140" t="s">
         <v>5</v>
       </c>
       <c r="L140" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M140" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N140" t="s">
         <v>157</v>
@@ -8901,37 +8906,37 @@
       <c r="O140" t="s">
         <v>0</v>
       </c>
-      <c r="P140">
-        <v>0</v>
+      <c r="P140" s="1">
+        <v>500000</v>
       </c>
       <c r="Q140" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A141">
-        <v>61475818</v>
+        <v>61504448</v>
       </c>
       <c r="B141" s="2">
-        <v>46125.445914351854</v>
+        <v>46125.648935185185</v>
       </c>
       <c r="C141">
-        <v>61919107</v>
+        <v>61919673</v>
       </c>
       <c r="D141" s="2">
-        <v>46132.510324074072</v>
+        <v>46132.513668981483</v>
       </c>
       <c r="E141" t="s">
         <v>21</v>
       </c>
       <c r="F141" t="s">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="G141">
-        <v>707974053</v>
+        <v>707234610</v>
       </c>
       <c r="H141" t="s">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="I141" t="s">
         <v>0</v>
@@ -8946,151 +8951,151 @@
         <v>6</v>
       </c>
       <c r="M141" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N141" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O141" t="s">
         <v>0</v>
       </c>
-      <c r="P141">
-        <v>0</v>
+      <c r="P141" s="1">
+        <v>3070672</v>
       </c>
       <c r="Q141" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A142">
-        <v>61481328</v>
+        <v>61506362</v>
       </c>
       <c r="B142" s="2">
-        <v>46125.483310185184</v>
+        <v>46125.660844907405</v>
       </c>
       <c r="C142">
-        <v>61481390</v>
+        <v>61771189</v>
       </c>
       <c r="D142" s="2">
-        <v>46125.483553240738</v>
+        <v>46129.643310185187</v>
       </c>
       <c r="E142" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="F142" t="s">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="G142">
-        <v>708448800</v>
+        <v>707906003</v>
       </c>
       <c r="H142" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="I142" t="s">
         <v>0</v>
       </c>
       <c r="J142" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K142" t="s">
         <v>5</v>
       </c>
       <c r="L142" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M142" t="s">
         <v>3</v>
       </c>
       <c r="N142" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O142" t="s">
         <v>0</v>
       </c>
       <c r="P142" s="1">
-        <v>500000</v>
+        <v>1218934</v>
       </c>
       <c r="Q142" t="s">
-        <v>0</v>
+        <v>304</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A143">
-        <v>61481328</v>
+        <v>61507701</v>
       </c>
       <c r="B143" s="2">
-        <v>46125.483310185184</v>
+        <v>46125.672951388886</v>
       </c>
       <c r="C143">
-        <v>61482285</v>
+        <v>61919760</v>
       </c>
       <c r="D143" s="2">
-        <v>46125.48909722222</v>
+        <v>46132.514444444445</v>
       </c>
       <c r="E143" t="s">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="F143" t="s">
-        <v>264</v>
+        <v>305</v>
       </c>
       <c r="G143">
-        <v>708448800</v>
+        <v>707906003</v>
       </c>
       <c r="H143" t="s">
-        <v>265</v>
+        <v>306</v>
       </c>
       <c r="I143" t="s">
         <v>0</v>
       </c>
       <c r="J143" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K143" t="s">
         <v>5</v>
       </c>
       <c r="L143" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M143" t="s">
         <v>3</v>
       </c>
       <c r="N143" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O143" t="s">
         <v>0</v>
       </c>
       <c r="P143" s="1">
-        <v>500000</v>
+        <v>596888</v>
       </c>
       <c r="Q143" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A144">
-        <v>61504448</v>
+        <v>61509436</v>
       </c>
       <c r="B144" s="2">
-        <v>46125.648935185185</v>
+        <v>46125.688043981485</v>
       </c>
       <c r="C144">
-        <v>61919673</v>
+        <v>61925159</v>
       </c>
       <c r="D144" s="2">
-        <v>46132.513668981483</v>
+        <v>46132.555532407408</v>
       </c>
       <c r="E144" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F144" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G144">
-        <v>707234610</v>
+        <v>707906003</v>
       </c>
       <c r="H144" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I144" t="s">
         <v>0</v>
@@ -9099,7 +9104,7 @@
         <v>13</v>
       </c>
       <c r="K144" t="s">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="L144" t="s">
         <v>6</v>
@@ -9108,95 +9113,95 @@
         <v>3</v>
       </c>
       <c r="N144" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O144" t="s">
         <v>0</v>
       </c>
       <c r="P144" s="1">
-        <v>3070672</v>
+        <v>3850000</v>
       </c>
       <c r="Q144" t="s">
-        <v>12</v>
+        <v>309</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A145">
-        <v>61506362</v>
+        <v>61509953</v>
       </c>
       <c r="B145" s="2">
-        <v>46125.660844907405</v>
+        <v>46125.694004629629</v>
       </c>
       <c r="C145">
-        <v>61771189</v>
+        <v>61741899</v>
       </c>
       <c r="D145" s="2">
-        <v>46129.643310185187</v>
+        <v>46129.432303240741</v>
       </c>
       <c r="E145" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F145" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G145">
-        <v>707906003</v>
+        <v>759379440</v>
       </c>
       <c r="H145" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I145" t="s">
         <v>0</v>
       </c>
       <c r="J145" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K145" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L145" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M145" t="s">
         <v>3</v>
       </c>
       <c r="N145" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O145" t="s">
         <v>0</v>
       </c>
-      <c r="P145" s="1">
-        <v>1218934</v>
+      <c r="P145" t="s">
+        <v>0</v>
       </c>
       <c r="Q145" t="s">
-        <v>308</v>
+        <v>140</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A146">
-        <v>61507701</v>
+        <v>61510116</v>
       </c>
       <c r="B146" s="2">
-        <v>46125.672951388886</v>
+        <v>46125.695775462962</v>
       </c>
       <c r="C146">
-        <v>61919760</v>
+        <v>61915558</v>
       </c>
       <c r="D146" s="2">
-        <v>46132.514444444445</v>
+        <v>46132.48715277778</v>
       </c>
       <c r="E146" t="s">
-        <v>21</v>
+        <v>265</v>
       </c>
       <c r="F146" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G146">
         <v>707906003</v>
       </c>
       <c r="H146" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I146" t="s">
         <v>0</v>
@@ -9205,7 +9210,7 @@
         <v>13</v>
       </c>
       <c r="K146" t="s">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="L146" t="s">
         <v>6</v>
@@ -9220,36 +9225,36 @@
         <v>0</v>
       </c>
       <c r="P146" s="1">
-        <v>596888</v>
+        <v>3850000</v>
       </c>
       <c r="Q146" t="s">
-        <v>22</v>
+        <v>314</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A147">
-        <v>61509436</v>
+        <v>61532855</v>
       </c>
       <c r="B147" s="2">
-        <v>46125.688043981485</v>
+        <v>46126.417708333334</v>
       </c>
       <c r="C147">
-        <v>61925159</v>
+        <v>61709870</v>
       </c>
       <c r="D147" s="2">
-        <v>46132.555532407408</v>
+        <v>46128.70685185185</v>
       </c>
       <c r="E147" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="F147" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="G147">
         <v>707906003</v>
       </c>
       <c r="H147" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="I147" t="s">
         <v>0</v>
@@ -9276,45 +9281,45 @@
         <v>3850000</v>
       </c>
       <c r="Q147" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A148">
-        <v>61509953</v>
+        <v>61541433</v>
       </c>
       <c r="B148" s="2">
-        <v>46125.694004629629</v>
+        <v>46126.476643518516</v>
       </c>
       <c r="C148">
-        <v>61741899</v>
+        <v>61916549</v>
       </c>
       <c r="D148" s="2">
-        <v>46129.432303240741</v>
+        <v>46132.494756944441</v>
       </c>
       <c r="E148" t="s">
-        <v>21</v>
+        <v>265</v>
       </c>
       <c r="F148" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G148">
-        <v>759379440</v>
+        <v>707192452</v>
       </c>
       <c r="H148" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="I148" t="s">
         <v>0</v>
       </c>
       <c r="J148" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K148" t="s">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="L148" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M148" t="s">
         <v>3</v>
@@ -9325,46 +9330,46 @@
       <c r="O148" t="s">
         <v>0</v>
       </c>
-      <c r="P148" t="s">
-        <v>0</v>
+      <c r="P148" s="1">
+        <v>3850000</v>
       </c>
       <c r="Q148" t="s">
-        <v>140</v>
+        <v>319</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A149">
-        <v>61510116</v>
+        <v>61552809</v>
       </c>
       <c r="B149" s="2">
-        <v>46125.695775462962</v>
+        <v>46126.558298611111</v>
       </c>
       <c r="C149">
-        <v>61915558</v>
+        <v>61912287</v>
       </c>
       <c r="D149" s="2">
-        <v>46132.48715277778</v>
+        <v>46132.465173611112</v>
       </c>
       <c r="E149" t="s">
-        <v>266</v>
+        <v>16</v>
       </c>
       <c r="F149" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="G149">
-        <v>707906003</v>
+        <v>707494870</v>
       </c>
       <c r="H149" t="s">
-        <v>317</v>
-      </c>
-      <c r="I149" t="s">
-        <v>0</v>
+        <v>321</v>
+      </c>
+      <c r="I149">
+        <v>1889896</v>
       </c>
       <c r="J149" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K149" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="L149" t="s">
         <v>6</v>
@@ -9379,48 +9384,48 @@
         <v>0</v>
       </c>
       <c r="P149" s="1">
-        <v>3850000</v>
+        <v>755590</v>
       </c>
       <c r="Q149" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A150">
-        <v>61532855</v>
+        <v>61560663</v>
       </c>
       <c r="B150" s="2">
-        <v>46126.417708333334</v>
+        <v>46126.615729166668</v>
       </c>
       <c r="C150">
-        <v>61709870</v>
+        <v>61560717</v>
       </c>
       <c r="D150" s="2">
-        <v>46128.70685185185</v>
+        <v>46126.615960648145</v>
       </c>
       <c r="E150" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="F150" t="s">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="G150">
-        <v>707906003</v>
+        <v>707984429</v>
       </c>
       <c r="H150" t="s">
-        <v>319</v>
+        <v>109</v>
       </c>
       <c r="I150" t="s">
         <v>0</v>
       </c>
       <c r="J150" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K150" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="L150" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M150" t="s">
         <v>3</v>
@@ -9432,95 +9437,95 @@
         <v>0</v>
       </c>
       <c r="P150" s="1">
-        <v>3850000</v>
+        <v>2984038</v>
       </c>
       <c r="Q150" t="s">
-        <v>320</v>
+        <v>27</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A151">
-        <v>61541433</v>
+        <v>61565561</v>
       </c>
       <c r="B151" s="2">
-        <v>46126.476643518516</v>
+        <v>46126.646979166668</v>
       </c>
       <c r="C151">
-        <v>61916549</v>
+        <v>61643933</v>
       </c>
       <c r="D151" s="2">
-        <v>46132.494756944441</v>
+        <v>46127.748055555552</v>
       </c>
       <c r="E151" t="s">
-        <v>266</v>
+        <v>29</v>
       </c>
       <c r="F151" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="G151">
-        <v>707192452</v>
+        <v>708616558</v>
       </c>
       <c r="H151" t="s">
-        <v>322</v>
-      </c>
-      <c r="I151" t="s">
-        <v>0</v>
+        <v>323</v>
+      </c>
+      <c r="I151">
+        <v>1889906</v>
       </c>
       <c r="J151" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K151" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="L151" t="s">
         <v>6</v>
       </c>
       <c r="M151" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="N151" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O151" t="s">
         <v>0</v>
       </c>
       <c r="P151" s="1">
-        <v>3850000</v>
+        <v>605000</v>
       </c>
       <c r="Q151" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A152">
-        <v>61552809</v>
+        <v>61572859</v>
       </c>
       <c r="B152" s="2">
-        <v>46126.558298611111</v>
+        <v>46126.69866898148</v>
       </c>
       <c r="C152">
-        <v>61912287</v>
+        <v>61572893</v>
       </c>
       <c r="D152" s="2">
-        <v>46132.465173611112</v>
+        <v>46126.698900462965</v>
       </c>
       <c r="E152" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="F152" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G152">
-        <v>707494870</v>
+        <v>153679707</v>
       </c>
       <c r="H152" t="s">
-        <v>325</v>
-      </c>
-      <c r="I152">
-        <v>1889896</v>
+        <v>326</v>
+      </c>
+      <c r="I152" t="s">
+        <v>0</v>
       </c>
       <c r="J152" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K152" t="s">
         <v>5</v>
@@ -9529,7 +9534,7 @@
         <v>6</v>
       </c>
       <c r="M152" t="s">
-        <v>3</v>
+        <v>327</v>
       </c>
       <c r="N152" t="s">
         <v>157</v>
@@ -9538,48 +9543,48 @@
         <v>0</v>
       </c>
       <c r="P152" s="1">
-        <v>755590</v>
+        <v>752977</v>
       </c>
       <c r="Q152" t="s">
-        <v>326</v>
+        <v>34</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A153">
-        <v>61560663</v>
+        <v>61580430</v>
       </c>
       <c r="B153" s="2">
-        <v>46126.615729166668</v>
+        <v>46126.776585648149</v>
       </c>
       <c r="C153">
-        <v>61923204</v>
+        <v>61924001</v>
       </c>
       <c r="D153" s="2">
-        <v>46132.539780092593</v>
+        <v>46132.544791666667</v>
       </c>
       <c r="E153" t="s">
-        <v>215</v>
+        <v>65</v>
       </c>
       <c r="F153" t="s">
-        <v>254</v>
+        <v>328</v>
       </c>
       <c r="G153">
-        <v>707984429</v>
+        <v>716283828</v>
       </c>
       <c r="H153" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="I153" t="s">
         <v>0</v>
       </c>
       <c r="J153" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K153" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L153" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M153" t="s">
         <v>3</v>
@@ -9591,48 +9596,48 @@
         <v>0</v>
       </c>
       <c r="P153" s="1">
-        <v>2984038</v>
+        <v>2188000</v>
       </c>
       <c r="Q153" t="s">
-        <v>27</v>
+        <v>329</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A154">
-        <v>61560663</v>
+        <v>61608637</v>
       </c>
       <c r="B154" s="2">
-        <v>46126.615729166668</v>
+        <v>46127.491550925923</v>
       </c>
       <c r="C154">
-        <v>61560717</v>
+        <v>61677257</v>
       </c>
       <c r="D154" s="2">
-        <v>46126.615960648145</v>
+        <v>46128.483958333331</v>
       </c>
       <c r="E154" t="s">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="F154" t="s">
-        <v>254</v>
+        <v>330</v>
       </c>
       <c r="G154">
-        <v>707984429</v>
+        <v>702455701</v>
       </c>
       <c r="H154" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="I154" t="s">
         <v>0</v>
       </c>
       <c r="J154" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K154" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L154" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M154" t="s">
         <v>3</v>
@@ -9643,43 +9648,43 @@
       <c r="O154" t="s">
         <v>0</v>
       </c>
-      <c r="P154" s="1">
-        <v>2984038</v>
+      <c r="P154" t="s">
+        <v>0</v>
       </c>
       <c r="Q154" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A155">
-        <v>61565561</v>
+        <v>61620138</v>
       </c>
       <c r="B155" s="2">
-        <v>46126.646979166668</v>
+        <v>46127.578287037039</v>
       </c>
       <c r="C155">
-        <v>61643933</v>
+        <v>61620187</v>
       </c>
       <c r="D155" s="2">
-        <v>46127.748055555552</v>
+        <v>46127.578622685185</v>
       </c>
       <c r="E155" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="F155" t="s">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="G155">
-        <v>708616558</v>
+        <v>758051301</v>
       </c>
       <c r="H155" t="s">
-        <v>327</v>
-      </c>
-      <c r="I155">
-        <v>1889906</v>
+        <v>332</v>
+      </c>
+      <c r="I155" t="s">
+        <v>0</v>
       </c>
       <c r="J155" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K155" t="s">
         <v>5</v>
@@ -9688,45 +9693,45 @@
         <v>6</v>
       </c>
       <c r="M155" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="N155" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O155" t="s">
         <v>0</v>
       </c>
-      <c r="P155" s="1">
-        <v>605000</v>
+      <c r="P155">
+        <v>0</v>
       </c>
       <c r="Q155" t="s">
-        <v>328</v>
+        <v>34</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A156">
-        <v>61572859</v>
+        <v>61622459</v>
       </c>
       <c r="B156" s="2">
-        <v>46126.69866898148</v>
+        <v>46127.59584490741</v>
       </c>
       <c r="C156">
-        <v>61916933</v>
+        <v>61622517</v>
       </c>
       <c r="D156" s="2">
-        <v>46132.497407407405</v>
+        <v>46127.596087962964</v>
       </c>
       <c r="E156" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="F156" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G156">
-        <v>153679707</v>
+        <v>758051301</v>
       </c>
       <c r="H156" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I156" t="s">
         <v>0</v>
@@ -9735,13 +9740,13 @@
         <v>13</v>
       </c>
       <c r="K156" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L156" t="s">
         <v>6</v>
       </c>
       <c r="M156" t="s">
-        <v>331</v>
+        <v>7</v>
       </c>
       <c r="N156" t="s">
         <v>157</v>
@@ -9749,99 +9754,99 @@
       <c r="O156" t="s">
         <v>0</v>
       </c>
-      <c r="P156" s="1">
-        <v>752977</v>
+      <c r="P156">
+        <v>0</v>
       </c>
       <c r="Q156" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A157">
-        <v>61572859</v>
+        <v>61644382</v>
       </c>
       <c r="B157" s="2">
-        <v>46126.69866898148</v>
+        <v>46127.754131944443</v>
       </c>
       <c r="C157">
-        <v>61572893</v>
+        <v>61796029</v>
       </c>
       <c r="D157" s="2">
-        <v>46126.698900462965</v>
+        <v>46129.887523148151</v>
       </c>
       <c r="E157" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F157" t="s">
-        <v>329</v>
+        <v>130</v>
       </c>
       <c r="G157">
-        <v>153679707</v>
+        <v>759250737</v>
       </c>
       <c r="H157" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I157" t="s">
         <v>0</v>
       </c>
       <c r="J157" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K157" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L157" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M157" t="s">
-        <v>331</v>
+        <v>3</v>
       </c>
       <c r="N157" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O157" t="s">
         <v>0</v>
       </c>
       <c r="P157" s="1">
-        <v>752977</v>
+        <v>1680307</v>
       </c>
       <c r="Q157" t="s">
-        <v>34</v>
+        <v>334</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A158">
-        <v>61580430</v>
+        <v>61671472</v>
       </c>
       <c r="B158" s="2">
-        <v>46126.776585648149</v>
+        <v>46128.441168981481</v>
       </c>
       <c r="C158">
-        <v>61924001</v>
+        <v>61671494</v>
       </c>
       <c r="D158" s="2">
-        <v>46132.544791666667</v>
+        <v>46128.441423611112</v>
       </c>
       <c r="E158" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F158" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G158">
-        <v>716283828</v>
+        <v>717033324</v>
       </c>
       <c r="H158" t="s">
-        <v>28</v>
+        <v>336</v>
       </c>
       <c r="I158" t="s">
         <v>0</v>
       </c>
       <c r="J158" t="s">
-        <v>13</v>
+        <v>337</v>
       </c>
       <c r="K158" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L158" t="s">
         <v>6</v>
@@ -9856,38 +9861,38 @@
         <v>0</v>
       </c>
       <c r="P158" s="1">
-        <v>2188000</v>
+        <v>700000</v>
       </c>
       <c r="Q158" t="s">
-        <v>333</v>
+        <v>38</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A159">
-        <v>61608637</v>
+        <v>61700587</v>
       </c>
       <c r="B159" s="2">
-        <v>46127.491550925923</v>
+        <v>46128.642256944448</v>
       </c>
       <c r="C159">
-        <v>61677257</v>
+        <v>61771508</v>
       </c>
       <c r="D159" s="2">
-        <v>46128.483958333331</v>
+        <v>46129.646238425928</v>
       </c>
       <c r="E159" t="s">
-        <v>214</v>
+        <v>153</v>
       </c>
       <c r="F159" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G159">
-        <v>702455701</v>
+        <v>747568798</v>
       </c>
       <c r="H159" t="s">
-        <v>41</v>
-      </c>
-      <c r="I159" t="s">
+        <v>339</v>
+      </c>
+      <c r="I159">
         <v>0</v>
       </c>
       <c r="J159" t="s">
@@ -9912,45 +9917,45 @@
         <v>0</v>
       </c>
       <c r="Q159" t="s">
-        <v>160</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A160">
-        <v>61620138</v>
+        <v>61702223</v>
       </c>
       <c r="B160" s="2">
-        <v>46127.578287037039</v>
+        <v>46128.654027777775</v>
       </c>
       <c r="C160">
-        <v>61620187</v>
+        <v>61742252</v>
       </c>
       <c r="D160" s="2">
-        <v>46127.578622685185</v>
+        <v>46129.434965277775</v>
       </c>
       <c r="E160" t="s">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="F160" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G160">
-        <v>758051301</v>
+        <v>747568798</v>
       </c>
       <c r="H160" t="s">
-        <v>336</v>
+        <v>223</v>
       </c>
       <c r="I160" t="s">
         <v>0</v>
       </c>
       <c r="J160" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K160" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L160" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M160" t="s">
         <v>3</v>
@@ -9961,49 +9966,49 @@
       <c r="O160" t="s">
         <v>0</v>
       </c>
-      <c r="P160">
+      <c r="P160" t="s">
         <v>0</v>
       </c>
       <c r="Q160" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A161">
-        <v>61620138</v>
+        <v>61702838</v>
       </c>
       <c r="B161" s="2">
-        <v>46127.578287037039</v>
+        <v>46128.658946759257</v>
       </c>
       <c r="C161">
-        <v>61764713</v>
+        <v>61741603</v>
       </c>
       <c r="D161" s="2">
-        <v>46129.595717592594</v>
+        <v>46129.430300925924</v>
       </c>
       <c r="E161" t="s">
         <v>153</v>
       </c>
       <c r="F161" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G161">
-        <v>758051301</v>
+        <v>747568798</v>
       </c>
       <c r="H161" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I161" t="s">
         <v>0</v>
       </c>
       <c r="J161" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K161" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L161" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M161" t="s">
         <v>3</v>
@@ -10014,90 +10019,87 @@
       <c r="O161" t="s">
         <v>0</v>
       </c>
-      <c r="P161">
+      <c r="P161" t="s">
         <v>0</v>
       </c>
       <c r="Q161" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A162">
-        <v>61622459</v>
+        <v>61710072</v>
       </c>
       <c r="B162" s="2">
-        <v>46127.59584490741</v>
+        <v>46128.708032407405</v>
       </c>
       <c r="C162">
-        <v>61622517</v>
+        <v>61899663</v>
       </c>
       <c r="D162" s="2">
-        <v>46127.596087962964</v>
+        <v>46132.371770833335</v>
       </c>
       <c r="E162" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="F162" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="G162">
-        <v>758051301</v>
+        <v>584425796</v>
       </c>
       <c r="H162" t="s">
-        <v>336</v>
-      </c>
-      <c r="I162" t="s">
+        <v>342</v>
+      </c>
+      <c r="I162">
         <v>0</v>
       </c>
       <c r="J162" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K162" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L162" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M162" t="s">
-        <v>7</v>
-      </c>
-      <c r="N162" t="s">
-        <v>157</v>
+        <v>3</v>
       </c>
       <c r="O162" t="s">
         <v>0</v>
       </c>
-      <c r="P162">
-        <v>0</v>
-      </c>
-      <c r="Q162" t="s">
-        <v>38</v>
+      <c r="P162" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q162">
+        <v>2721711717</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A163">
-        <v>61622459</v>
+        <v>61828334</v>
       </c>
       <c r="B163" s="2">
-        <v>46127.59584490741</v>
+        <v>46130.562754629631</v>
       </c>
       <c r="C163">
-        <v>61795290</v>
+        <v>61828369</v>
       </c>
       <c r="D163" s="2">
-        <v>46129.864305555559</v>
+        <v>46130.562974537039</v>
       </c>
       <c r="E163" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="F163" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="G163">
-        <v>758051301</v>
+        <v>747309803</v>
       </c>
       <c r="H163" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="I163" t="s">
         <v>0</v>
@@ -10106,63 +10108,63 @@
         <v>13</v>
       </c>
       <c r="K163" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L163" t="s">
         <v>6</v>
       </c>
       <c r="M163" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N163" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O163" t="s">
         <v>0</v>
       </c>
-      <c r="P163">
-        <v>0</v>
+      <c r="P163" s="1">
+        <v>1000000</v>
       </c>
       <c r="Q163" t="s">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A164">
-        <v>61644382</v>
+        <v>61915874</v>
       </c>
       <c r="B164" s="2">
-        <v>46127.754131944443</v>
+        <v>46132.488715277781</v>
       </c>
       <c r="C164">
-        <v>61796029</v>
+        <v>61915957</v>
       </c>
       <c r="D164" s="2">
-        <v>46129.887523148151</v>
+        <v>46132.489004629628</v>
       </c>
       <c r="E164" t="s">
-        <v>65</v>
+        <v>347</v>
       </c>
       <c r="F164" t="s">
-        <v>130</v>
+        <v>345</v>
       </c>
       <c r="G164">
-        <v>759250737</v>
+        <v>554356255</v>
       </c>
       <c r="H164" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="I164" t="s">
         <v>0</v>
       </c>
       <c r="J164" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K164" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L164" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M164" t="s">
         <v>3</v>
@@ -10173,649 +10175,72 @@
       <c r="O164" t="s">
         <v>0</v>
       </c>
-      <c r="P164" s="1">
-        <v>1680307</v>
+      <c r="P164" t="s">
+        <v>0</v>
       </c>
       <c r="Q164" t="s">
-        <v>338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A165">
-        <v>61671472</v>
+        <v>61918089</v>
       </c>
       <c r="B165" s="2">
-        <v>46128.441168981481</v>
+        <v>46132.504675925928</v>
       </c>
       <c r="C165">
-        <v>61922008</v>
+        <v>61918735</v>
       </c>
       <c r="D165" s="2">
-        <v>46132.531412037039</v>
+        <v>46132.508819444447</v>
       </c>
       <c r="E165" t="s">
-        <v>215</v>
+        <v>347</v>
       </c>
       <c r="F165" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="G165">
-        <v>717033324</v>
+        <v>554356255</v>
       </c>
       <c r="H165" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="I165" t="s">
         <v>0</v>
       </c>
       <c r="J165" t="s">
-        <v>341</v>
+        <v>25</v>
       </c>
       <c r="K165" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L165" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M165" t="s">
         <v>3</v>
       </c>
       <c r="N165" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O165" t="s">
         <v>0</v>
       </c>
-      <c r="P165" s="1">
-        <v>700000</v>
+      <c r="P165" t="s">
+        <v>0</v>
       </c>
       <c r="Q165" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A166">
-        <v>61671472</v>
-      </c>
-      <c r="B166" s="2">
-        <v>46128.441168981481</v>
-      </c>
-      <c r="C166">
-        <v>61671494</v>
-      </c>
-      <c r="D166" s="2">
-        <v>46128.441423611112</v>
-      </c>
-      <c r="E166" t="s">
-        <v>77</v>
-      </c>
-      <c r="F166" t="s">
-        <v>339</v>
-      </c>
-      <c r="G166">
-        <v>717033324</v>
-      </c>
-      <c r="H166" t="s">
-        <v>340</v>
-      </c>
-      <c r="I166" t="s">
-        <v>0</v>
-      </c>
-      <c r="J166" t="s">
-        <v>341</v>
-      </c>
-      <c r="K166" t="s">
-        <v>5</v>
-      </c>
-      <c r="L166" t="s">
-        <v>6</v>
-      </c>
-      <c r="M166" t="s">
-        <v>3</v>
-      </c>
-      <c r="N166" t="s">
-        <v>157</v>
-      </c>
-      <c r="O166" t="s">
-        <v>0</v>
-      </c>
-      <c r="P166" s="1">
-        <v>700000</v>
-      </c>
-      <c r="Q166" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A167">
-        <v>61700587</v>
-      </c>
-      <c r="B167" s="2">
-        <v>46128.642256944448</v>
-      </c>
-      <c r="C167">
-        <v>61771508</v>
-      </c>
-      <c r="D167" s="2">
-        <v>46129.646238425928</v>
-      </c>
-      <c r="E167" t="s">
-        <v>153</v>
-      </c>
-      <c r="F167" t="s">
-        <v>342</v>
-      </c>
-      <c r="G167">
-        <v>747568798</v>
-      </c>
-      <c r="H167" t="s">
-        <v>343</v>
-      </c>
-      <c r="I167">
-        <v>0</v>
-      </c>
-      <c r="J167" t="s">
-        <v>25</v>
-      </c>
-      <c r="K167" t="s">
-        <v>1</v>
-      </c>
-      <c r="L167" t="s">
-        <v>2</v>
-      </c>
-      <c r="M167" t="s">
-        <v>3</v>
-      </c>
-      <c r="N167" t="s">
-        <v>157</v>
-      </c>
-      <c r="O167" t="s">
-        <v>0</v>
-      </c>
-      <c r="P167" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q167" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A168">
-        <v>61702223</v>
-      </c>
-      <c r="B168" s="2">
-        <v>46128.654027777775</v>
-      </c>
-      <c r="C168">
-        <v>61742252</v>
-      </c>
-      <c r="D168" s="2">
-        <v>46129.434965277775</v>
-      </c>
-      <c r="E168" t="s">
-        <v>153</v>
-      </c>
-      <c r="F168" t="s">
-        <v>342</v>
-      </c>
-      <c r="G168">
-        <v>747568798</v>
-      </c>
-      <c r="H168" t="s">
-        <v>224</v>
-      </c>
-      <c r="I168" t="s">
-        <v>0</v>
-      </c>
-      <c r="J168" t="s">
-        <v>25</v>
-      </c>
-      <c r="K168" t="s">
-        <v>1</v>
-      </c>
-      <c r="L168" t="s">
-        <v>2</v>
-      </c>
-      <c r="M168" t="s">
-        <v>3</v>
-      </c>
-      <c r="N168" t="s">
-        <v>157</v>
-      </c>
-      <c r="O168" t="s">
-        <v>0</v>
-      </c>
-      <c r="P168" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q168" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A169">
-        <v>61702838</v>
-      </c>
-      <c r="B169" s="2">
-        <v>46128.658946759257</v>
-      </c>
-      <c r="C169">
-        <v>61741603</v>
-      </c>
-      <c r="D169" s="2">
-        <v>46129.430300925924</v>
-      </c>
-      <c r="E169" t="s">
-        <v>153</v>
-      </c>
-      <c r="F169" t="s">
-        <v>342</v>
-      </c>
-      <c r="G169">
-        <v>747568798</v>
-      </c>
-      <c r="H169" t="s">
-        <v>344</v>
-      </c>
-      <c r="I169" t="s">
-        <v>0</v>
-      </c>
-      <c r="J169" t="s">
-        <v>25</v>
-      </c>
-      <c r="K169" t="s">
-        <v>1</v>
-      </c>
-      <c r="L169" t="s">
-        <v>2</v>
-      </c>
-      <c r="M169" t="s">
-        <v>3</v>
-      </c>
-      <c r="N169" t="s">
-        <v>157</v>
-      </c>
-      <c r="O169" t="s">
-        <v>0</v>
-      </c>
-      <c r="P169" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q169" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A170">
-        <v>61710072</v>
-      </c>
-      <c r="B170" s="2">
-        <v>46128.708032407405</v>
-      </c>
-      <c r="C170">
-        <v>61899663</v>
-      </c>
-      <c r="D170" s="2">
-        <v>46132.371770833335</v>
-      </c>
-      <c r="E170" t="s">
-        <v>29</v>
-      </c>
-      <c r="F170" t="s">
-        <v>345</v>
-      </c>
-      <c r="G170">
-        <v>584425796</v>
-      </c>
-      <c r="H170" t="s">
-        <v>346</v>
-      </c>
-      <c r="I170">
-        <v>0</v>
-      </c>
-      <c r="J170" t="s">
-        <v>25</v>
-      </c>
-      <c r="K170" t="s">
-        <v>1</v>
-      </c>
-      <c r="L170" t="s">
-        <v>2</v>
-      </c>
-      <c r="M170" t="s">
-        <v>3</v>
-      </c>
-      <c r="O170" t="s">
-        <v>0</v>
-      </c>
-      <c r="P170" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q170">
-        <v>2721711717</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A171">
-        <v>61828334</v>
-      </c>
-      <c r="B171" s="2">
-        <v>46130.562754629631</v>
-      </c>
-      <c r="C171">
-        <v>61828369</v>
-      </c>
-      <c r="D171" s="2">
-        <v>46130.562974537039</v>
-      </c>
-      <c r="E171" t="s">
-        <v>77</v>
-      </c>
-      <c r="F171" t="s">
-        <v>347</v>
-      </c>
-      <c r="G171">
-        <v>747309803</v>
-      </c>
-      <c r="H171" t="s">
-        <v>348</v>
-      </c>
-      <c r="I171" t="s">
-        <v>0</v>
-      </c>
-      <c r="J171" t="s">
-        <v>13</v>
-      </c>
-      <c r="K171" t="s">
-        <v>5</v>
-      </c>
-      <c r="L171" t="s">
-        <v>6</v>
-      </c>
-      <c r="M171" t="s">
-        <v>3</v>
-      </c>
-      <c r="N171" t="s">
-        <v>157</v>
-      </c>
-      <c r="O171" t="s">
-        <v>0</v>
-      </c>
-      <c r="P171" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="Q171" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A172">
-        <v>61828334</v>
-      </c>
-      <c r="B172" s="2">
-        <v>46130.562754629631</v>
-      </c>
-      <c r="C172">
-        <v>61911266</v>
-      </c>
-      <c r="D172" s="2">
-        <v>46132.459131944444</v>
-      </c>
-      <c r="E172" t="s">
-        <v>303</v>
-      </c>
-      <c r="F172" t="s">
-        <v>347</v>
-      </c>
-      <c r="G172">
-        <v>747309803</v>
-      </c>
-      <c r="H172" t="s">
-        <v>348</v>
-      </c>
-      <c r="I172" t="s">
-        <v>0</v>
-      </c>
-      <c r="J172" t="s">
-        <v>13</v>
-      </c>
-      <c r="K172" t="s">
-        <v>5</v>
-      </c>
-      <c r="L172" t="s">
-        <v>6</v>
-      </c>
-      <c r="M172" t="s">
-        <v>3</v>
-      </c>
-      <c r="N172" t="s">
-        <v>157</v>
-      </c>
-      <c r="O172" t="s">
-        <v>0</v>
-      </c>
-      <c r="P172" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="Q172" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A173">
-        <v>61915874</v>
-      </c>
-      <c r="B173" s="2">
-        <v>46132.488715277781</v>
-      </c>
-      <c r="C173">
-        <v>61915957</v>
-      </c>
-      <c r="D173" s="2">
-        <v>46132.489004629628</v>
-      </c>
-      <c r="E173" t="s">
-        <v>351</v>
-      </c>
-      <c r="F173" t="s">
-        <v>349</v>
-      </c>
-      <c r="G173">
-        <v>554356255</v>
-      </c>
-      <c r="H173" t="s">
-        <v>350</v>
-      </c>
-      <c r="I173" t="s">
-        <v>0</v>
-      </c>
-      <c r="J173" t="s">
-        <v>25</v>
-      </c>
-      <c r="K173" t="s">
-        <v>1</v>
-      </c>
-      <c r="L173" t="s">
-        <v>2</v>
-      </c>
-      <c r="M173" t="s">
-        <v>3</v>
-      </c>
-      <c r="N173" t="s">
-        <v>156</v>
-      </c>
-      <c r="O173" t="s">
-        <v>0</v>
-      </c>
-      <c r="P173" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q173" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A174">
-        <v>61915874</v>
-      </c>
-      <c r="B174" s="2">
-        <v>46132.488715277781</v>
-      </c>
-      <c r="C174">
-        <v>61918678</v>
-      </c>
-      <c r="D174" s="2">
-        <v>46132.508576388886</v>
-      </c>
-      <c r="E174" t="s">
-        <v>352</v>
-      </c>
-      <c r="F174" t="s">
-        <v>349</v>
-      </c>
-      <c r="G174">
-        <v>554356255</v>
-      </c>
-      <c r="H174" t="s">
-        <v>350</v>
-      </c>
-      <c r="I174" t="s">
-        <v>0</v>
-      </c>
-      <c r="J174" t="s">
-        <v>25</v>
-      </c>
-      <c r="K174" t="s">
-        <v>1</v>
-      </c>
-      <c r="L174" t="s">
-        <v>2</v>
-      </c>
-      <c r="M174" t="s">
-        <v>3</v>
-      </c>
-      <c r="N174" t="s">
-        <v>157</v>
-      </c>
-      <c r="O174" t="s">
-        <v>0</v>
-      </c>
-      <c r="P174" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q174" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A175">
-        <v>61918089</v>
-      </c>
-      <c r="B175" s="2">
-        <v>46132.504675925928</v>
-      </c>
-      <c r="C175">
-        <v>61918735</v>
-      </c>
-      <c r="D175" s="2">
-        <v>46132.508819444447</v>
-      </c>
-      <c r="E175" t="s">
-        <v>351</v>
-      </c>
-      <c r="F175" t="s">
-        <v>353</v>
-      </c>
-      <c r="G175">
-        <v>554356255</v>
-      </c>
-      <c r="H175" t="s">
-        <v>354</v>
-      </c>
-      <c r="I175" t="s">
-        <v>0</v>
-      </c>
-      <c r="J175" t="s">
-        <v>25</v>
-      </c>
-      <c r="K175" t="s">
-        <v>1</v>
-      </c>
-      <c r="L175" t="s">
-        <v>2</v>
-      </c>
-      <c r="M175" t="s">
-        <v>3</v>
-      </c>
-      <c r="N175" t="s">
-        <v>156</v>
-      </c>
-      <c r="O175" t="s">
-        <v>0</v>
-      </c>
-      <c r="P175" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q175" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A176">
-        <v>61918089</v>
-      </c>
-      <c r="B176" s="2">
-        <v>46132.504675925928</v>
-      </c>
-      <c r="C176">
-        <v>61921414</v>
-      </c>
-      <c r="D176" s="2">
-        <v>46132.527141203704</v>
-      </c>
-      <c r="E176" t="s">
-        <v>303</v>
-      </c>
-      <c r="F176" t="s">
-        <v>353</v>
-      </c>
-      <c r="G176">
-        <v>554356255</v>
-      </c>
-      <c r="H176" t="s">
-        <v>354</v>
-      </c>
-      <c r="I176" t="s">
-        <v>0</v>
-      </c>
-      <c r="J176" t="s">
-        <v>25</v>
-      </c>
-      <c r="K176" t="s">
-        <v>1</v>
-      </c>
-      <c r="L176" t="s">
-        <v>2</v>
-      </c>
-      <c r="M176" t="s">
-        <v>3</v>
-      </c>
-      <c r="N176" t="s">
-        <v>157</v>
-      </c>
-      <c r="O176" t="s">
-        <v>0</v>
-      </c>
-      <c r="P176" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q176" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q176" xr:uid="{CA2681BA-26CD-4DFD-AC27-AFE67B62DFC2}"/>
+  <autoFilter ref="A1:Q165" xr:uid="{CA2681BA-26CD-4DFD-AC27-AFE67B62DFC2}"/>
   <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8C4BF8E-3AE3-4BAB-BF24-81370C088FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EE0F6FB-9E4C-436C-8AD1-54C1E6767FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{62435644-B5E9-416E-8248-44E175926A31}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8795E28B-8E72-455D-9364-4AA2911E250B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$Q$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$Q$124</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="309">
   <si>
     <t>AGILITY BUSINESS PARKS COTE D’IVOIRE</t>
   </si>
@@ -218,15 +218,21 @@
     <t>GOULIA</t>
   </si>
   <si>
+    <t>Encours</t>
+  </si>
+  <si>
     <t>xxxx</t>
   </si>
   <si>
+    <t>Responsable Zone: Coordination etude et travaux</t>
+  </si>
+  <si>
+    <t>SAMAGO</t>
+  </si>
+  <si>
     <t>Prestataire : Travaux</t>
   </si>
   <si>
-    <t>SAMAGO</t>
-  </si>
-  <si>
     <t>QUIPUX AFRIQUE</t>
   </si>
   <si>
@@ -263,441 +269,438 @@
     <t>BUVPN260034</t>
   </si>
   <si>
-    <t>MOTA ENGIL COTE D'IVOIRE MINING</t>
+    <t>MOTA ENGIL MINING LAFIGUE</t>
+  </si>
+  <si>
+    <t>DABAKALA//VOIE INCONNUE/M. AKOUE 07 48 51 26 13</t>
+  </si>
+  <si>
+    <t>SYTHD260132</t>
+  </si>
+  <si>
+    <t>Support IP: Correction</t>
+  </si>
+  <si>
+    <t>STE INTERNATIONALE D'ASSURANCE MULTIRISQUES</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU AVENUE HOUDAI</t>
+  </si>
+  <si>
+    <t>EMPIRE CIMENT CI</t>
+  </si>
+  <si>
+    <t>M'BRAGO</t>
+  </si>
+  <si>
+    <t>XXXXXXXXX</t>
+  </si>
+  <si>
+    <t>NSIA BANQUE</t>
+  </si>
+  <si>
+    <t>BONDOUKOU</t>
+  </si>
+  <si>
+    <t>1.635.147</t>
+  </si>
+  <si>
+    <t>STE MUGEFCI</t>
+  </si>
+  <si>
+    <t>PLATEAU</t>
+  </si>
+  <si>
+    <t>Cordonnateur Prestatataire: Affectation Technicien</t>
+  </si>
+  <si>
+    <t>Transmission Plans Equipe Numerisation</t>
+  </si>
+  <si>
+    <t>MAIRIE DE NIABLE</t>
+  </si>
+  <si>
+    <t>NIABLE A LA MAIRIE</t>
+  </si>
+  <si>
+    <t>xxxxx</t>
+  </si>
+  <si>
+    <t>TAABO LAMTO</t>
+  </si>
+  <si>
+    <t>xxxxxx</t>
+  </si>
+  <si>
+    <t>KONG</t>
+  </si>
+  <si>
+    <t>Responsable Zone: Validation pour intervention</t>
+  </si>
+  <si>
+    <t>MFI CI (SODEXAM)</t>
+  </si>
+  <si>
+    <t>PORT POUET ZONE AEROPORTUAIRE</t>
+  </si>
+  <si>
+    <t>ZENITH BANK COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>ABIDJAN PLATEAU</t>
+  </si>
+  <si>
+    <t>BUVPN260078</t>
+  </si>
+  <si>
+    <t>Principale (avec backup)</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DES DOUANES</t>
+  </si>
+  <si>
+    <t>DJIGUI SHIPPING SITE TREICHVILLE CHU</t>
+  </si>
+  <si>
+    <t>BUVPN260070</t>
+  </si>
+  <si>
+    <t>Support IP: Config Eq Acces</t>
+  </si>
+  <si>
+    <t>OCI PCCI 2</t>
+  </si>
+  <si>
+    <t>ABIDJAN TREICHVILLE</t>
+  </si>
+  <si>
+    <t>BUVPN250061</t>
+  </si>
+  <si>
+    <t>DEMANDE INTERNE FRANCHISE MANKONO</t>
+  </si>
+  <si>
+    <t>MONKONO</t>
+  </si>
+  <si>
+    <t>VPNLL</t>
+  </si>
+  <si>
+    <t>OCI</t>
+  </si>
+  <si>
+    <t>Franchise Gagnoa</t>
+  </si>
+  <si>
+    <t>BUVPN260077</t>
+  </si>
+  <si>
+    <t>MAIRIE DE OUELLE</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>OUELLE QT MAIRIE</t>
+  </si>
+  <si>
+    <t>AGL</t>
+  </si>
+  <si>
+    <t>TREICHVILLE ZONE 3 EN FACE DE CFAO</t>
+  </si>
+  <si>
+    <t>SYTHD260133</t>
+  </si>
+  <si>
+    <t>SYTHD260093</t>
+  </si>
+  <si>
+    <t>UBA</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>STE SIB</t>
+  </si>
+  <si>
+    <t>cuivre</t>
+  </si>
+  <si>
+    <t>AIR CI</t>
+  </si>
+  <si>
+    <t>TREICHVILLE ZONE AEROPORTUAIRE</t>
+  </si>
+  <si>
+    <t>xxxxxxxxxxxxxxx</t>
+  </si>
+  <si>
+    <t>Etude Suspendu</t>
+  </si>
+  <si>
+    <t>CORIS BANK (BACKUP DU 2722223530 )</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY 2 PLATEAUX</t>
+  </si>
+  <si>
+    <t>BICICI PLATEAU (BACKUP DU 2720242424 )</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>GRAND BASSAM</t>
+  </si>
+  <si>
+    <t>PLANETPHARMA EXPORT CI</t>
+  </si>
+  <si>
+    <t>SYTHD260122</t>
+  </si>
+  <si>
+    <t>Technicien zone: Intervention</t>
+  </si>
+  <si>
+    <t>SUD COMOE CAOUTCHOU</t>
+  </si>
+  <si>
+    <t>ABOISSO</t>
+  </si>
+  <si>
+    <t>OFI, OLAM IVOIRE</t>
+  </si>
+  <si>
+    <t>ANYAMA</t>
+  </si>
+  <si>
+    <t>OLAM AGRI RUBBER COTE D'IVOIRE ANIASSUE</t>
+  </si>
+  <si>
+    <t>ANIASSUE//VOIE INCONNUE/M. N'GUESSAN THIERRY0556331131</t>
+  </si>
+  <si>
+    <t>radio_fh</t>
+  </si>
+  <si>
+    <t>SYTHD260100</t>
+  </si>
+  <si>
+    <t>MANTRA IVOIRE SA</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/VRIDI 05 46 00 81 31</t>
+  </si>
+  <si>
+    <t>FO</t>
+  </si>
+  <si>
+    <t>SYTHD260131</t>
+  </si>
+  <si>
+    <t>OLAM COCOA PROCESSING CI SAN PEDRO</t>
+  </si>
+  <si>
+    <t>SAN-PEDRO//VOIE INCONNUE/ZONE INDUSTRIELLE 0708454305</t>
+  </si>
+  <si>
+    <t>SYTHD260102</t>
+  </si>
+  <si>
+    <t>CADESA</t>
+  </si>
+  <si>
+    <t>SASSANDRA SAGO ADEBEM</t>
+  </si>
+  <si>
+    <t>GNX</t>
+  </si>
+  <si>
+    <t>DIA 20Mbps Ext A : PoP ICA REPUBLIQUE Ext B : 7,avenue Nogues,Immeuble BSIC,5eme et Abidjan 01 BP 5754 7 AV.Nogues 8X8J+QX Abidjan, COTE D IVOIRE</t>
+  </si>
+  <si>
+    <t>OFI OLAM IVOIRE</t>
+  </si>
+  <si>
+    <t>SECO OUANGOLO (BACKUP DU SYTHD220080)</t>
+  </si>
+  <si>
+    <t>SECO OUANGOLO</t>
+  </si>
+  <si>
+    <t>Ingenieur Projet: Suspension Travaux DOB</t>
+  </si>
+  <si>
+    <t>SECO DIAWALA (BACKUP DU SYTHD220089   )</t>
+  </si>
+  <si>
+    <t>DIAWALA//VOIE INCONNUE/SECO DIAWALA 05 06 72 72 87</t>
+  </si>
+  <si>
+    <t>SECO FERKE (BACKUP DU SYTHD220118 )</t>
+  </si>
+  <si>
+    <t>SECO FERKE</t>
+  </si>
+  <si>
+    <t>SECO TREICHVILLE (BACKUP DU SYTHD230357 )</t>
+  </si>
+  <si>
+    <t>SECO TREICHVILLE</t>
+  </si>
+  <si>
+    <t>MAXAM CI</t>
+  </si>
+  <si>
+    <t>BOUAKE</t>
+  </si>
+  <si>
+    <t>SYTHD260101</t>
+  </si>
+  <si>
+    <t>Responsable Zone: Validation intervention</t>
+  </si>
+  <si>
+    <t>RIMCO</t>
+  </si>
+  <si>
+    <t>TREICHVILLE ZONE 3</t>
+  </si>
+  <si>
+    <t>1.000.000</t>
+  </si>
+  <si>
+    <t>ECOTI SA</t>
+  </si>
+  <si>
+    <t>YOPOUGON</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>BGFIBANK</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT BOUET BGFIBANK AEROPORT</t>
+  </si>
+  <si>
+    <t>SOLIBRA</t>
+  </si>
+  <si>
+    <t>YOPOUGON PK26</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie GAIA</t>
+  </si>
+  <si>
+    <t>STE LONACI</t>
+  </si>
+  <si>
+    <t>Siège MARCORY BIETRY</t>
+  </si>
+  <si>
+    <t>ftto_virage</t>
+  </si>
+  <si>
+    <t>2721599900B</t>
+  </si>
+  <si>
+    <t>CNPS</t>
+  </si>
+  <si>
+    <t>2720252050B</t>
+  </si>
+  <si>
+    <t>STE COMPAGNIE IVOIRIENNE D'ELECTRICITE DTET</t>
+  </si>
+  <si>
+    <t>TREICHVILLE</t>
+  </si>
+  <si>
+    <t>STE CFAO RETAIL</t>
+  </si>
+  <si>
+    <t>PORT_BOUET_ZONE_AEROPORTUAIRE</t>
+  </si>
+  <si>
+    <t>AFG BANK</t>
+  </si>
+  <si>
+    <t>2720306200B</t>
+  </si>
+  <si>
+    <t>MARCORY</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>xxxxxxx</t>
+  </si>
+  <si>
+    <t>MILLENIUM INDUSTRIE</t>
+  </si>
+  <si>
+    <t>BONOUA ZONE INDUSTRIELLE</t>
+  </si>
+  <si>
+    <t>MILLENIUM INDUSTRIE CI</t>
+  </si>
+  <si>
+    <t>CFAO RETAIL</t>
+  </si>
+  <si>
+    <t>SDA_RCI_MARCORY</t>
+  </si>
+  <si>
+    <t>COCODY_LAS_PALMAS</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie GAIA LSI</t>
+  </si>
+  <si>
+    <t>SDA_RCI_ANGRE</t>
+  </si>
+  <si>
+    <t>ECOBANK COCODY RIVIERA</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/RIVIERA 0708448800</t>
+  </si>
+  <si>
+    <t>BUVPN260088</t>
+  </si>
+  <si>
+    <t>SODEXAM</t>
+  </si>
+  <si>
+    <t>TABOU Aérodrome</t>
+  </si>
+  <si>
+    <t>SODEXAM BONDOUKOU STATION METEOROLOGIQUE</t>
+  </si>
+  <si>
+    <t>BONDOUKOU STATION METEOROLOGIQUE</t>
+  </si>
+  <si>
+    <t>SYTHD260115</t>
+  </si>
+  <si>
+    <t>INSTITUT HOTELIER FEH KESSE</t>
+  </si>
+  <si>
+    <t>MAN SAINTE THERESE EXTENTION</t>
   </si>
   <si>
     <t>DABAKALA</t>
   </si>
   <si>
-    <t>SYTHD260132</t>
-  </si>
-  <si>
-    <t>Support IP: Correction</t>
-  </si>
-  <si>
-    <t>STE INTERNATIONALE D'ASSURANCE MULTIRISQUES</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PLATEAU AVENUE HOUDAI</t>
-  </si>
-  <si>
-    <t>EMPIRE CIMENT CI</t>
-  </si>
-  <si>
-    <t>M'BRAGO</t>
-  </si>
-  <si>
-    <t>XXXXXXXXX</t>
-  </si>
-  <si>
-    <t>NSIA BANQUE</t>
-  </si>
-  <si>
-    <t>BONDOUKOU</t>
-  </si>
-  <si>
-    <t>1.635.147</t>
-  </si>
-  <si>
-    <t>STE MUGEFCI</t>
-  </si>
-  <si>
-    <t>PLATEAU</t>
-  </si>
-  <si>
-    <t>Encours</t>
-  </si>
-  <si>
-    <t>Cordonnateur Prestatataire: Affectation Technicien</t>
-  </si>
-  <si>
-    <t>MAIRIE DE NIABLE</t>
-  </si>
-  <si>
-    <t>NIABLE A LA MAIRIE</t>
-  </si>
-  <si>
-    <t>xxxxx</t>
-  </si>
-  <si>
-    <t>TAABO LAMTO</t>
-  </si>
-  <si>
-    <t>xxxxxx</t>
-  </si>
-  <si>
-    <t>KONG</t>
-  </si>
-  <si>
-    <t>Responsable Zone: Validation pour intervention</t>
-  </si>
-  <si>
-    <t>MFI CI (SODEXAM)</t>
-  </si>
-  <si>
-    <t>PORT POUET ZONE AEROPORTUAIRE</t>
-  </si>
-  <si>
-    <t>ZENITH BANK COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>ABIDJAN PLATEAU</t>
-  </si>
-  <si>
-    <t>BUVPN260078</t>
-  </si>
-  <si>
-    <t>Principale (avec backup)</t>
-  </si>
-  <si>
-    <t>DIRECTION GENERALE DES DOUANES</t>
-  </si>
-  <si>
-    <t>DJIGUI SHIPPING SITE TREICHVILLE CHU</t>
-  </si>
-  <si>
-    <t>BUVPN260070</t>
-  </si>
-  <si>
-    <t>OCI PCCI 2</t>
-  </si>
-  <si>
-    <t>ABIDJAN TREICHVILLE</t>
-  </si>
-  <si>
-    <t>BUVPN250061</t>
-  </si>
-  <si>
-    <t>DEMANDE INTERNE FRANCHISE MANKONO</t>
-  </si>
-  <si>
-    <t>MONKONO</t>
-  </si>
-  <si>
-    <t>VPNLL</t>
-  </si>
-  <si>
-    <t>OCI</t>
-  </si>
-  <si>
-    <t>Franchise Gagnoa</t>
-  </si>
-  <si>
-    <t>BUVPN260077</t>
-  </si>
-  <si>
-    <t>MAIRIE DE OUELLE</t>
-  </si>
-  <si>
-    <t>XXXXXXXXXXXXX</t>
-  </si>
-  <si>
-    <t>OUELLE QT MAIRIE</t>
-  </si>
-  <si>
-    <t>AGL</t>
-  </si>
-  <si>
-    <t>TREICHVILLE ZONE 3 EN FACE DE CFAO</t>
-  </si>
-  <si>
-    <t>SYTHD260133</t>
-  </si>
-  <si>
-    <t>Responsable Zone: Coordination etude et travaux</t>
-  </si>
-  <si>
-    <t>SYTHD260093</t>
-  </si>
-  <si>
-    <t>UBA</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>STE SIB</t>
-  </si>
-  <si>
-    <t>cuivre</t>
-  </si>
-  <si>
-    <t>AIR CI</t>
-  </si>
-  <si>
-    <t>TREICHVILLE ZONE AEROPORTUAIRE</t>
-  </si>
-  <si>
-    <t>xxxxxxxxxxxxxxx</t>
-  </si>
-  <si>
-    <t>Etude Suspendu</t>
-  </si>
-  <si>
-    <t>CORIS BANK (BACKUP DU 2722223530 )</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY 2 PLATEAUX</t>
-  </si>
-  <si>
-    <t>BICICI PLATEAU (BACKUP DU 2720242424 )</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PLATEAU</t>
-  </si>
-  <si>
-    <t>XXXXXXXXXXXX</t>
-  </si>
-  <si>
-    <t>GRAND BASSAM</t>
-  </si>
-  <si>
-    <t>PLANETPHARMA EXPORT CI</t>
-  </si>
-  <si>
-    <t>SYTHD260122</t>
-  </si>
-  <si>
-    <t>Responsable Zone: Validation intervention</t>
-  </si>
-  <si>
-    <t>SUD COMOE CAOUTCHOU</t>
-  </si>
-  <si>
-    <t>ABOISSO</t>
-  </si>
-  <si>
-    <t>Ingenieur Projet: Suspension Travaux DOB</t>
-  </si>
-  <si>
-    <t>OFI, OLAM IVOIRE</t>
-  </si>
-  <si>
-    <t>ANYAMA</t>
-  </si>
-  <si>
-    <t>OLAM AGRI RUBBER COTE D'IVOIRE ANIASSUE</t>
-  </si>
-  <si>
-    <t>ANIASSUE//VOIE INCONNUE/M. N'GUESSAN THIERRY0556331131</t>
-  </si>
-  <si>
-    <t>radio_fh</t>
-  </si>
-  <si>
-    <t>SYTHD260100</t>
-  </si>
-  <si>
-    <t>STE MANTRA IVOIRE SA VRIDI</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PORT BOUET VRIDI</t>
-  </si>
-  <si>
-    <t>FO</t>
-  </si>
-  <si>
-    <t>SYTHD260131</t>
-  </si>
-  <si>
-    <t>OLAM COCOA PROCESSING CI SAN PEDRO</t>
-  </si>
-  <si>
-    <t>SAN-PEDRO//VOIE INCONNUE/ZONE INDUSTRIELLE 0708454305</t>
-  </si>
-  <si>
-    <t>SYTHD260102</t>
-  </si>
-  <si>
-    <t>CADESA</t>
-  </si>
-  <si>
-    <t>SASSANDRA SAGO ADEBEM</t>
-  </si>
-  <si>
-    <t>GNX</t>
-  </si>
-  <si>
-    <t>DIA 20Mbps Ext A : PoP ICA REPUBLIQUE Ext B : 7,avenue Nogues,Immeuble BSIC,5eme et Abidjan 01 BP 5754 7 AV.Nogues 8X8J+QX Abidjan, COTE D IVOIRE</t>
-  </si>
-  <si>
-    <t>OFI OLAM IVOIRE</t>
-  </si>
-  <si>
-    <t>SECO OUANGOLO (BACKUP DU SYTHD220080)</t>
-  </si>
-  <si>
-    <t>SECO OUANGOLO</t>
-  </si>
-  <si>
-    <t>SECO DIAWALA (BACKUP DU SYTHD220089   )</t>
-  </si>
-  <si>
-    <t>DIAWALA//VOIE INCONNUE/SECO DIAWALA 05 06 72 72 87</t>
-  </si>
-  <si>
-    <t>SECO FERKE (BACKUP DU SYTHD220118 )</t>
-  </si>
-  <si>
-    <t>SECO FERKE</t>
-  </si>
-  <si>
-    <t>SECO TREICHVILLE (BACKUP DU SYTHD230357 )</t>
-  </si>
-  <si>
-    <t>SECO TREICHVILLE</t>
-  </si>
-  <si>
-    <t>MAXAM CI</t>
-  </si>
-  <si>
-    <t>BOUAKE</t>
-  </si>
-  <si>
-    <t>SYTHD260101</t>
-  </si>
-  <si>
-    <t>RIMCO</t>
-  </si>
-  <si>
-    <t>TREICHVILLE ZONE 3</t>
-  </si>
-  <si>
-    <t>1.000.000</t>
-  </si>
-  <si>
-    <t>ECOTI SA</t>
-  </si>
-  <si>
-    <t>YOPOUGON</t>
-  </si>
-  <si>
-    <t>XXXXXXXXXXXXXXXX</t>
-  </si>
-  <si>
-    <t>BGFIBANK</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PORT BOUET BGFIBANK AEROPORT</t>
-  </si>
-  <si>
-    <t>SOLIBRA</t>
-  </si>
-  <si>
-    <t>YOPOUGON PK26</t>
-  </si>
-  <si>
-    <t>STE LONACI</t>
-  </si>
-  <si>
-    <t>Siège MARCORY BIETRY</t>
-  </si>
-  <si>
-    <t>ftto_virage</t>
-  </si>
-  <si>
-    <t>2721599900B</t>
-  </si>
-  <si>
-    <t>CNPS</t>
-  </si>
-  <si>
-    <t>2720252050B</t>
-  </si>
-  <si>
-    <t>STE COMPAGNIE IVOIRIENNE D'ELECTRICITE DTET</t>
-  </si>
-  <si>
-    <t>TREICHVILLE</t>
-  </si>
-  <si>
-    <t>STE CFAO RETAIL</t>
-  </si>
-  <si>
-    <t>PORT_BOUET_ZONE_AEROPORTUAIRE</t>
-  </si>
-  <si>
-    <t>AFG BANK</t>
-  </si>
-  <si>
-    <t>2720306200B</t>
-  </si>
-  <si>
-    <t>MARCORY</t>
-  </si>
-  <si>
-    <t>XXXXXXXXXXXXXXX</t>
-  </si>
-  <si>
-    <t>xxxxxxx</t>
-  </si>
-  <si>
-    <t>MILLENIUM INDUSTRIE</t>
-  </si>
-  <si>
-    <t>BONOUA ZONE INDUSTRIELLE</t>
-  </si>
-  <si>
-    <t>CONNECTED NETWORKS SERVICES LTD</t>
-  </si>
-  <si>
-    <t>BANQUE ATLANTIQUE PLATEAU AVENUE NOGUES PLATEAU</t>
-  </si>
-  <si>
-    <t>SYTHD260097</t>
-  </si>
-  <si>
-    <t>Wholesale : Mise en service GAIA</t>
-  </si>
-  <si>
-    <t>MILLENIUM INDUSTRIE CI</t>
-  </si>
-  <si>
-    <t>CFAO RETAIL</t>
-  </si>
-  <si>
-    <t>SDA_RCI_MARCORY</t>
-  </si>
-  <si>
-    <t>COCODY_LAS_PALMAS</t>
-  </si>
-  <si>
-    <t>BO Homologation: Saisie GAIA LSI</t>
-  </si>
-  <si>
-    <t>SDA_RCI_ANGRE</t>
-  </si>
-  <si>
-    <t>ECOBANK COCODY RIVIERA</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/RIVIERA 0708448800</t>
-  </si>
-  <si>
-    <t>BUVPN260088</t>
-  </si>
-  <si>
-    <t>SODEXAM</t>
-  </si>
-  <si>
-    <t>TABOU Aérodrome</t>
-  </si>
-  <si>
-    <t>SODEXAM BONDOUKOU STATION METEOROLOGIQUE</t>
-  </si>
-  <si>
-    <t>BONDOUKOU STATION METEOROLOGIQUE</t>
-  </si>
-  <si>
-    <t>SYTHD260115</t>
-  </si>
-  <si>
-    <t>INSTITUT HOTELIER FEH KESSE</t>
-  </si>
-  <si>
-    <t>MAN SAINTE THERESE EXTENTION</t>
-  </si>
-  <si>
     <t>NETCYBER CONSULTING</t>
   </si>
   <si>
@@ -776,7 +779,7 @@
     <t>NESKAO</t>
   </si>
   <si>
-    <t>PORT-POUET VRIDI ZONE INDUSTRIELLE RUE DES TEXTILES</t>
+    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/VRIDI ZONE INDUSTRIELLE</t>
   </si>
   <si>
     <t>SYTHD260129</t>
@@ -794,9 +797,6 @@
     <t>UNION INVESTISSEMENT</t>
   </si>
   <si>
-    <t>BO Homologation: Saisie GAIA</t>
-  </si>
-  <si>
     <t>SIB</t>
   </si>
   <si>
@@ -815,6 +815,9 @@
     <t>ABIDJAN-TREICHVILLE AU DC DU KM4 AU SEINDE LA SALLEHOSTING</t>
   </si>
   <si>
+    <t>BBF : Validation Etude</t>
+  </si>
+  <si>
     <t>MITSPA CALL SARL</t>
   </si>
   <si>
@@ -830,9 +833,6 @@
     <t>XXXXXXXXXXXXXXXXX</t>
   </si>
   <si>
-    <t>BBF : Validation Etude</t>
-  </si>
-  <si>
     <t>AROLI GROUPE</t>
   </si>
   <si>
@@ -908,7 +908,16 @@
     <t>BRIDGE MICROFINANCE</t>
   </si>
   <si>
+    <t>GIABA</t>
+  </si>
+  <si>
     <t>Parametrage facturation</t>
+  </si>
+  <si>
+    <t>ALS COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>YAMOUSSOUKRO QUARTIER RESIDENTIEL</t>
   </si>
   <si>
     <t>ID DOSSIER</t>
@@ -982,7 +991,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1419,75 +1428,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76AAFD7B-AF0D-4C07-A193-5ED21C49A69A}">
-  <dimension ref="A1:Q123"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEA6B63F-CC06-4AE4-99D5-8F3B8C81168B}">
+  <dimension ref="A1:Q124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6328125" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>44970444</v>
       </c>
@@ -1538,7 +1546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>52778382</v>
       </c>
@@ -1591,7 +1599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="91" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>52808171</v>
       </c>
@@ -1644,7 +1652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>53702282</v>
       </c>
@@ -1697,7 +1705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>53749839</v>
       </c>
@@ -1750,7 +1758,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>53790357</v>
       </c>
@@ -1803,7 +1811,7 @@
         <v>4430307</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>53899369</v>
       </c>
@@ -1856,7 +1864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>54449048</v>
       </c>
@@ -1909,7 +1917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>55104019</v>
       </c>
@@ -1962,7 +1970,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>55636282</v>
       </c>
@@ -2015,7 +2023,7 @@
         <v>918681</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>55694485</v>
       </c>
@@ -2068,7 +2076,7 @@
         <v>638462</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>56181778</v>
       </c>
@@ -2121,7 +2129,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>56601140</v>
       </c>
@@ -2174,7 +2182,7 @@
         <v>7103410</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>56601982</v>
       </c>
@@ -2182,13 +2190,13 @@
         <v>46035.393611111111</v>
       </c>
       <c r="C15" s="3">
-        <v>62438942</v>
+        <v>62985668</v>
       </c>
       <c r="D15" s="4">
-        <v>46141.325057870374</v>
+        <v>46150.795983796299</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>33</v>
@@ -2218,7 +2226,7 @@
         <v>14</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>2</v>
@@ -2227,7 +2235,7 @@
         <v>7103410</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>56603495</v>
       </c>
@@ -2241,7 +2249,7 @@
         <v>46113.726909722223</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>33</v>
@@ -2250,7 +2258,7 @@
         <v>707003126</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>2</v>
@@ -2271,7 +2279,7 @@
         <v>14</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P16" s="3" t="s">
         <v>2</v>
@@ -2280,7 +2288,7 @@
         <v>7103410</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>56606469</v>
       </c>
@@ -2294,16 +2302,16 @@
         <v>46099.427060185182</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="G17" s="3">
         <v>504041812</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>2</v>
@@ -2333,7 +2341,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>56607988</v>
       </c>
@@ -2347,16 +2355,16 @@
         <v>46141.570902777778</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G18" s="3">
         <v>504041812</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>2</v>
@@ -2377,7 +2385,7 @@
         <v>14</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>2</v>
@@ -2386,7 +2394,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>56611212</v>
       </c>
@@ -2400,16 +2408,16 @@
         <v>46136.681342592594</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G19" s="3">
         <v>504041812</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>2</v>
@@ -2430,7 +2438,7 @@
         <v>14</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>2</v>
@@ -2439,7 +2447,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>56618123</v>
       </c>
@@ -2456,13 +2464,13 @@
         <v>46</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G20" s="3">
         <v>504041812</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I20" s="3">
         <v>1775236</v>
@@ -2483,7 +2491,7 @@
         <v>14</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>2</v>
@@ -2492,7 +2500,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>56675050</v>
       </c>
@@ -2506,22 +2514,22 @@
         <v>46149.704629629632</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G21" s="3">
         <v>748512613</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>2</v>
+        <v>76</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1781606</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>11</v>
@@ -2530,13 +2538,13 @@
         <v>27</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>2</v>
@@ -2545,7 +2553,7 @@
         <v>4362401</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="91" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>56970346</v>
       </c>
@@ -2562,13 +2570,13 @@
         <v>16</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G22" s="3">
         <v>708667658</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>2</v>
@@ -2598,7 +2606,7 @@
         <v>2871414</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>57398181</v>
       </c>
@@ -2615,13 +2623,13 @@
         <v>16</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G23" s="3">
         <v>720631500</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>2</v>
@@ -2642,7 +2650,7 @@
         <v>14</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>2</v>
@@ -2651,7 +2659,7 @@
         <v>4406780</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>57651441</v>
       </c>
@@ -2668,13 +2676,13 @@
         <v>46</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G24" s="3">
         <v>707079088</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>2</v>
@@ -2701,10 +2709,10 @@
         <v>2</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>57706849</v>
       </c>
@@ -2718,16 +2726,16 @@
         <v>46148.703194444446</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G25" s="3">
         <v>708086472</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>2</v>
@@ -2745,7 +2753,7 @@
         <v>19</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O25" s="3" t="s">
         <v>23</v>
@@ -2757,7 +2765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>58055656</v>
       </c>
@@ -2774,13 +2782,13 @@
         <v>46</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G26" s="3">
         <v>758224257</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>2</v>
@@ -2801,7 +2809,7 @@
         <v>14</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>2</v>
@@ -2810,7 +2818,7 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>58093827</v>
       </c>
@@ -2824,7 +2832,7 @@
         <v>46135.713287037041</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>8</v>
@@ -2833,7 +2841,7 @@
         <v>708086759</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>2</v>
@@ -2851,10 +2859,10 @@
         <v>19</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>2</v>
@@ -2863,7 +2871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>58166885</v>
       </c>
@@ -2877,16 +2885,16 @@
         <v>46128.679085648146</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G28" s="3">
         <v>504041812</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>2</v>
@@ -2904,7 +2912,7 @@
         <v>6</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>28</v>
@@ -2916,7 +2924,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>58626822</v>
       </c>
@@ -2933,13 +2941,13 @@
         <v>16</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G29" s="3">
         <v>709574114</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>2</v>
@@ -2969,7 +2977,7 @@
         <v>445307</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>58635645</v>
       </c>
@@ -2983,16 +2991,16 @@
         <v>46133.49863425926</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G30" s="3">
         <v>759250737</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>2</v>
@@ -3013,7 +3021,7 @@
         <v>14</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>2</v>
@@ -3022,7 +3030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>58635674</v>
       </c>
@@ -3036,16 +3044,16 @@
         <v>46133.487384259257</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G31" s="3">
         <v>759250737</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>2</v>
@@ -3060,7 +3068,7 @@
         <v>12</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N31" s="3" t="s">
         <v>14</v>
@@ -3075,7 +3083,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>58797846</v>
       </c>
@@ -3083,22 +3091,22 @@
         <v>46076.510104166664</v>
       </c>
       <c r="C32" s="3">
-        <v>61338699</v>
+        <v>62970260</v>
       </c>
       <c r="D32" s="4">
-        <v>46122.390069444446</v>
+        <v>46150.654166666667</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G32" s="3">
         <v>102224907</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>2</v>
@@ -3119,7 +3127,7 @@
         <v>14</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>2</v>
@@ -3128,7 +3136,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>58856498</v>
       </c>
@@ -3145,13 +3153,13 @@
         <v>46</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G33" s="3">
         <v>748377555</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>2</v>
@@ -3172,7 +3180,7 @@
         <v>14</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>2</v>
@@ -3181,7 +3189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>58860538</v>
       </c>
@@ -3189,28 +3197,28 @@
         <v>46077.446666666663</v>
       </c>
       <c r="C34" s="3">
-        <v>62771302</v>
+        <v>62950864</v>
       </c>
       <c r="D34" s="4">
-        <v>46147.631678240738</v>
+        <v>46150.491238425922</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G34" s="3">
         <v>748377555</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>11</v>
@@ -3219,7 +3227,7 @@
         <v>12</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>14</v>
@@ -3234,7 +3242,7 @@
         <v>5324000</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>58868849</v>
       </c>
@@ -3251,13 +3259,13 @@
         <v>46</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G35" s="3">
         <v>748377555</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>2</v>
@@ -3278,7 +3286,7 @@
         <v>14</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>2</v>
@@ -3287,7 +3295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>58925987</v>
       </c>
@@ -3304,13 +3312,13 @@
         <v>16</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G36" s="3">
         <v>708641473</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>2</v>
@@ -3331,7 +3339,7 @@
         <v>14</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P36" s="3" t="s">
         <v>2</v>
@@ -3340,7 +3348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>58959238</v>
       </c>
@@ -3357,13 +3365,13 @@
         <v>16</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G37" s="3">
         <v>708641473</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>2</v>
@@ -3393,7 +3401,7 @@
         <v>850000</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>58963630</v>
       </c>
@@ -3401,22 +3409,22 @@
         <v>46078.697002314817</v>
       </c>
       <c r="C38" s="3">
-        <v>62943162</v>
+        <v>62956098</v>
       </c>
       <c r="D38" s="4">
-        <v>46150.434062499997</v>
+        <v>46150.531597222223</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="G38" s="3">
         <v>747726344</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>2</v>
@@ -3437,7 +3445,7 @@
         <v>14</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>2</v>
@@ -3446,7 +3454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>58963646</v>
       </c>
@@ -3463,13 +3471,13 @@
         <v>46</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G39" s="3">
         <v>747726344</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>2</v>
@@ -3484,13 +3492,13 @@
         <v>27</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>2</v>
@@ -3513,22 +3521,22 @@
         <v>46147.6247337963</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G40" s="3">
         <v>709136702</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>11</v>
@@ -3540,10 +3548,10 @@
         <v>6</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P40" s="3" t="s">
         <v>2</v>
@@ -3552,7 +3560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>59410212</v>
       </c>
@@ -3566,25 +3574,25 @@
         <v>46132.511064814818</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G41" s="3">
         <v>789018789</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>5</v>
@@ -3593,10 +3601,10 @@
         <v>19</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>2</v>
@@ -3605,7 +3613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>59410843</v>
       </c>
@@ -3619,22 +3627,22 @@
         <v>46107.452592592592</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G42" s="3">
         <v>758700193</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
@@ -3649,7 +3657,7 @@
         <v>14</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>2</v>
@@ -3658,7 +3666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>59414411</v>
       </c>
@@ -3672,22 +3680,22 @@
         <v>46147.610937500001</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G43" s="3">
         <v>566473307</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
@@ -3699,7 +3707,7 @@
         <v>6</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>42</v>
@@ -3711,7 +3719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>59417066</v>
       </c>
@@ -3725,22 +3733,22 @@
         <v>46147.623831018522</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G44" s="3">
         <v>709565662</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
@@ -3752,10 +3760,10 @@
         <v>6</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>2</v>
@@ -3764,7 +3772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>59465071</v>
       </c>
@@ -3778,16 +3786,16 @@
         <v>46107.489861111113</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G45" s="3">
         <v>554235979</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>2</v>
@@ -3817,7 +3825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>59466514</v>
       </c>
@@ -3825,22 +3833,22 @@
         <v>46087.436643518522</v>
       </c>
       <c r="C46" s="3">
-        <v>62942952</v>
+        <v>62971588</v>
       </c>
       <c r="D46" s="4">
-        <v>46150.432476851849</v>
+        <v>46150.664074074077</v>
       </c>
       <c r="E46" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="G46" s="3">
         <v>141679210</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>2</v>
@@ -3861,7 +3869,7 @@
         <v>14</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>2</v>
@@ -3870,7 +3878,7 @@
         <v>3213390</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>59480507</v>
       </c>
@@ -3878,22 +3886,22 @@
         <v>46087.544247685182</v>
       </c>
       <c r="C47" s="3">
-        <v>60564140</v>
+        <v>62965526</v>
       </c>
       <c r="D47" s="4">
-        <v>46107.723194444443</v>
+        <v>46150.615069444444</v>
       </c>
       <c r="E47" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="G47" s="3">
         <v>708547070</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>2</v>
@@ -3911,10 +3919,10 @@
         <v>6</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>134</v>
+        <v>14</v>
+      </c>
+      <c r="O47" s="3">
+        <v>2721712020</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>2</v>
@@ -3923,7 +3931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>59495473</v>
       </c>
@@ -3937,16 +3945,16 @@
         <v>46136.426828703705</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G48" s="3">
         <v>506727287</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>2</v>
@@ -3976,7 +3984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="91" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="72" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>59537755</v>
       </c>
@@ -3993,13 +4001,13 @@
         <v>46</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G49" s="3">
         <v>556331131</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I49" s="3">
         <v>1843236</v>
@@ -4008,7 +4016,7 @@
         <v>51</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>27</v>
@@ -4020,7 +4028,7 @@
         <v>14</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>2</v>
@@ -4029,7 +4037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>59541145</v>
       </c>
@@ -4043,37 +4051,37 @@
         <v>46150.432847222219</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G50" s="3">
         <v>546008131</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>2</v>
+        <v>150</v>
+      </c>
+      <c r="I50" s="3">
+        <v>1842216</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N50" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P50" s="3" t="s">
         <v>2</v>
@@ -4082,7 +4090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="91" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="72" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>59606122</v>
       </c>
@@ -4099,13 +4107,13 @@
         <v>46</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G51" s="3">
         <v>708454305</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I51" s="3">
         <v>1842206</v>
@@ -4114,7 +4122,7 @@
         <v>51</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>27</v>
@@ -4126,7 +4134,7 @@
         <v>14</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P51" s="3" t="s">
         <v>2</v>
@@ -4135,7 +4143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>59615935</v>
       </c>
@@ -4152,13 +4160,13 @@
         <v>16</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G52" s="3">
         <v>767081456</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>2</v>
@@ -4188,7 +4196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="208" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" ht="144" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>59684312</v>
       </c>
@@ -4205,19 +4213,19 @@
         <v>16</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G53" s="3">
         <v>3130227350</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K53" s="3" t="s">
         <v>11</v>
@@ -4241,7 +4249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>59793967</v>
       </c>
@@ -4255,16 +4263,16 @@
         <v>46132.513668981483</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G54" s="3">
         <v>506727287</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>2</v>
@@ -4294,7 +4302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>59813505</v>
       </c>
@@ -4308,16 +4316,16 @@
         <v>46099.71303240741</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G55" s="3">
         <v>706727287</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>2</v>
@@ -4326,7 +4334,7 @@
         <v>26</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>27</v>
@@ -4335,7 +4343,7 @@
         <v>19</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O55" s="3" t="s">
         <v>2</v>
@@ -4347,7 +4355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="78" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>59816396</v>
       </c>
@@ -4361,16 +4369,16 @@
         <v>46099.711053240739</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G56" s="3">
         <v>506727287</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I56" s="3">
         <v>1848446</v>
@@ -4379,7 +4387,7 @@
         <v>51</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>27</v>
@@ -4388,10 +4396,10 @@
         <v>19</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P56" s="3" t="s">
         <v>2</v>
@@ -4400,7 +4408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>59820678</v>
       </c>
@@ -4414,16 +4422,16 @@
         <v>46100.766909722224</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G57" s="3">
         <v>506727287</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>2</v>
@@ -4432,7 +4440,7 @@
         <v>26</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>27</v>
@@ -4441,7 +4449,7 @@
         <v>19</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>2</v>
@@ -4453,7 +4461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <v>59824550</v>
       </c>
@@ -4470,13 +4478,13 @@
         <v>16</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G58" s="3">
         <v>506727287</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>2</v>
@@ -4497,7 +4505,7 @@
         <v>14</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>2</v>
@@ -4506,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>59894743</v>
       </c>
@@ -4514,22 +4522,22 @@
         <v>46094.687673611108</v>
       </c>
       <c r="C59" s="3">
-        <v>62944535</v>
+        <v>62976769</v>
       </c>
       <c r="D59" s="4">
-        <v>46150.444351851853</v>
+        <v>46150.705763888887</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G59" s="3">
         <v>759668146</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>2</v>
@@ -4559,7 +4567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>60026486</v>
       </c>
@@ -4573,16 +4581,16 @@
         <v>46147.43304398148</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G60" s="3">
         <v>506727287</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>2</v>
@@ -4591,7 +4599,7 @@
         <v>26</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>27</v>
@@ -4603,7 +4611,7 @@
         <v>14</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>2</v>
@@ -4612,7 +4620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>60356605</v>
       </c>
@@ -4629,13 +4637,13 @@
         <v>16</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G61" s="3">
         <v>504001081</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>2</v>
@@ -4656,16 +4664,16 @@
         <v>14</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P61" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <v>60748674</v>
       </c>
@@ -4682,13 +4690,13 @@
         <v>16</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G62" s="3">
         <v>767791237</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>2</v>
@@ -4709,7 +4717,7 @@
         <v>14</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>2</v>
@@ -4718,7 +4726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <v>60972166</v>
       </c>
@@ -4726,22 +4734,22 @@
         <v>46114.708020833335</v>
       </c>
       <c r="C63" s="3">
-        <v>62482351</v>
+        <v>62949578</v>
       </c>
       <c r="D63" s="4">
-        <v>46141.675706018519</v>
+        <v>46150.482407407406</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G63" s="3">
         <v>160128782</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>2</v>
@@ -4771,7 +4779,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <v>61220160</v>
       </c>
@@ -4779,28 +4787,28 @@
         <v>46120.483368055553</v>
       </c>
       <c r="C64" s="3">
-        <v>61742545</v>
+        <v>62977466</v>
       </c>
       <c r="D64" s="4">
-        <v>46129.436898148146</v>
+        <v>46150.711793981478</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G64" s="3">
         <v>102571205</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>11</v>
@@ -4812,7 +4820,7 @@
         <v>6</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="O64" s="3" t="s">
         <v>23</v>
@@ -4824,7 +4832,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>61239047</v>
       </c>
@@ -4841,22 +4849,22 @@
         <v>46</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G65" s="3">
         <v>103381121</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>5</v>
@@ -4868,7 +4876,7 @@
         <v>14</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P65" s="3" t="s">
         <v>2</v>
@@ -4877,7 +4885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
         <v>61240327</v>
       </c>
@@ -4891,22 +4899,22 @@
         <v>46128.415625000001</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G66" s="3">
         <v>103381121</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
@@ -4921,7 +4929,7 @@
         <v>14</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>2</v>
@@ -4930,7 +4938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <v>61240462</v>
       </c>
@@ -4947,22 +4955,22 @@
         <v>46</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G67" s="3">
         <v>769218598</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>5</v>
@@ -4974,7 +4982,7 @@
         <v>14</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="P67" s="3" t="s">
         <v>2</v>
@@ -4983,7 +4991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
         <v>61242033</v>
       </c>
@@ -4991,28 +4999,28 @@
         <v>46120.643912037034</v>
       </c>
       <c r="C68" s="3">
-        <v>61743482</v>
+        <v>62945857</v>
       </c>
       <c r="D68" s="4">
-        <v>46129.442071759258</v>
+        <v>46150.456064814818</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G68" s="3">
         <v>747636152</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>4</v>
@@ -5027,7 +5035,7 @@
         <v>14</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P68" s="3" t="s">
         <v>2</v>
@@ -5036,7 +5044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
         <v>61243441</v>
       </c>
@@ -5053,19 +5061,19 @@
         <v>16</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G69" s="3">
         <v>747636152</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K69" s="3" t="s">
         <v>4</v>
@@ -5089,7 +5097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <v>61243727</v>
       </c>
@@ -5103,16 +5111,16 @@
         <v>46128.349027777775</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G70" s="3">
         <v>707974053</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>2</v>
@@ -5142,7 +5150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
         <v>61244524</v>
       </c>
@@ -5159,22 +5167,22 @@
         <v>46</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G71" s="3">
         <v>757818829</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="L71" s="3" t="s">
         <v>5</v>
@@ -5186,7 +5194,7 @@
         <v>14</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="P71" s="3" t="s">
         <v>2</v>
@@ -5195,7 +5203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
         <v>61248751</v>
       </c>
@@ -5209,22 +5217,22 @@
         <v>46147.656886574077</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G72" s="3">
         <v>747636152</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
@@ -5237,7 +5245,7 @@
       </c>
       <c r="N72" s="3"/>
       <c r="O72" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>2</v>
@@ -5246,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
         <v>61254924</v>
       </c>
@@ -5254,22 +5262,22 @@
         <v>46120.74763888889</v>
       </c>
       <c r="C73" s="3">
-        <v>62483616</v>
+        <v>62986121</v>
       </c>
       <c r="D73" s="4">
-        <v>46141.683842592596</v>
+        <v>46150.811145833337</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G73" s="3">
         <v>757818829</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>2</v>
@@ -5299,7 +5307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
         <v>61255381</v>
       </c>
@@ -5307,22 +5315,22 @@
         <v>46120.752291666664</v>
       </c>
       <c r="C74" s="3">
-        <v>62483305</v>
+        <v>62986133</v>
       </c>
       <c r="D74" s="4">
-        <v>46141.682210648149</v>
+        <v>46150.811967592592</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G74" s="3">
         <v>757818829</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>2</v>
@@ -5352,7 +5360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
         <v>61255901</v>
       </c>
@@ -5360,22 +5368,22 @@
         <v>46120.75712962963</v>
       </c>
       <c r="C75" s="3">
-        <v>62484265</v>
+        <v>62951388</v>
       </c>
       <c r="D75" s="4">
-        <v>46141.689074074071</v>
+        <v>46150.494675925926</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G75" s="3">
         <v>757818829</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>2</v>
@@ -5396,7 +5404,7 @@
         <v>14</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="P75" s="3" t="s">
         <v>2</v>
@@ -5405,7 +5413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <v>61315991</v>
       </c>
@@ -5419,16 +5427,16 @@
         <v>46148.392731481479</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G76" s="3">
         <v>778495680</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>2</v>
@@ -5449,7 +5457,7 @@
         <v>14</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>2</v>
@@ -5458,30 +5466,30 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="78" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
-        <v>61317028</v>
+        <v>61336527</v>
       </c>
       <c r="B77" s="4">
-        <v>46121.753101851849</v>
+        <v>46122.368761574071</v>
       </c>
       <c r="C77" s="3">
-        <v>62747944</v>
+        <v>62807025</v>
       </c>
       <c r="D77" s="4">
-        <v>46147.471585648149</v>
+        <v>46148.392222222225</v>
       </c>
       <c r="E77" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G77" s="3">
+        <v>778495680</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G77" s="3">
-        <v>4414839740</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>2</v>
@@ -5490,7 +5498,7 @@
         <v>26</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="L77" s="3" t="s">
         <v>27</v>
@@ -5502,39 +5510,39 @@
         <v>14</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="P77" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q77" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="Q77" s="5">
+        <v>1679940</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
-        <v>61336527</v>
+        <v>61474571</v>
       </c>
       <c r="B78" s="4">
-        <v>46122.368761574071</v>
+        <v>46125.437488425923</v>
       </c>
       <c r="C78" s="3">
-        <v>62807025</v>
+        <v>62114470</v>
       </c>
       <c r="D78" s="4">
-        <v>46148.392222222225</v>
+        <v>46135.476550925923</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G78" s="3">
-        <v>778495680</v>
+        <v>707974053</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>2</v>
@@ -5549,36 +5557,36 @@
         <v>27</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="N78" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="P78" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q78" s="5">
-        <v>1679940</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q78" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
-        <v>61474571</v>
+        <v>61475299</v>
       </c>
       <c r="B79" s="4">
-        <v>46125.437488425923</v>
+        <v>46125.442372685182</v>
       </c>
       <c r="C79" s="3">
-        <v>62114470</v>
+        <v>62772255</v>
       </c>
       <c r="D79" s="4">
-        <v>46135.476550925923</v>
+        <v>46147.638368055559</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>203</v>
@@ -5587,7 +5595,7 @@
         <v>707974053</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>2</v>
@@ -5605,7 +5613,7 @@
         <v>19</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="O79" s="3" t="s">
         <v>39</v>
@@ -5617,21 +5625,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
-        <v>61475299</v>
+        <v>61475818</v>
       </c>
       <c r="B80" s="4">
-        <v>46125.442372685182</v>
+        <v>46125.445914351854</v>
       </c>
       <c r="C80" s="3">
-        <v>61578769</v>
+        <v>62772416</v>
       </c>
       <c r="D80" s="4">
-        <v>46126.756122685183</v>
+        <v>46147.639189814814</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>206</v>
+        <v>65</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>203</v>
@@ -5640,7 +5648,7 @@
         <v>707974053</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>2</v>
@@ -5658,7 +5666,7 @@
         <v>19</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O80" s="3" t="s">
         <v>39</v>
@@ -5670,95 +5678,95 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" ht="72" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
-        <v>61475818</v>
+        <v>61481328</v>
       </c>
       <c r="B81" s="4">
-        <v>46125.445914351854</v>
+        <v>46125.483310185184</v>
       </c>
       <c r="C81" s="3">
-        <v>62772416</v>
+        <v>62173555</v>
       </c>
       <c r="D81" s="4">
-        <v>46147.639189814814</v>
+        <v>46136.44263888889</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G81" s="3">
-        <v>707974053</v>
+        <v>708448800</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>2</v>
+        <v>209</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1891736</v>
       </c>
       <c r="J81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q81" s="5">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="24" x14ac:dyDescent="0.35">
+      <c r="A82" s="3">
+        <v>61504448</v>
+      </c>
+      <c r="B82" s="4">
+        <v>46125.648935185185</v>
+      </c>
+      <c r="C82" s="3">
+        <v>62115179</v>
+      </c>
+      <c r="D82" s="4">
+        <v>46135.481111111112</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G82" s="3">
+        <v>707234610</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J82" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="K82" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L81" s="3" t="s">
+      <c r="L82" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" ht="78" x14ac:dyDescent="0.35">
-      <c r="A82" s="3">
-        <v>61481328</v>
-      </c>
-      <c r="B82" s="4">
-        <v>46125.483310185184</v>
-      </c>
-      <c r="C82" s="3">
-        <v>62173555</v>
-      </c>
-      <c r="D82" s="4">
-        <v>46136.44263888889</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="G82" s="3">
-        <v>708448800</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="I82" s="3">
-        <v>1891736</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="M82" s="3" t="s">
         <v>6</v>
@@ -5767,39 +5775,39 @@
         <v>14</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="P82" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q82" s="5">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+        <v>3070672</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
-        <v>61504448</v>
+        <v>61507701</v>
       </c>
       <c r="B83" s="4">
-        <v>46125.648935185185</v>
+        <v>46125.672951388886</v>
       </c>
       <c r="C83" s="3">
-        <v>62115179</v>
+        <v>62020006</v>
       </c>
       <c r="D83" s="4">
-        <v>46135.481111111112</v>
+        <v>46133.777349537035</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G83" s="3">
-        <v>707234610</v>
+        <v>707906003</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>2</v>
@@ -5820,51 +5828,51 @@
         <v>14</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>28</v>
+        <v>215</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q83" s="5">
-        <v>3070672</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+        <v>596888</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
-        <v>61507701</v>
+        <v>61509953</v>
       </c>
       <c r="B84" s="4">
-        <v>46125.672951388886</v>
+        <v>46125.694004629629</v>
       </c>
       <c r="C84" s="3">
-        <v>62020006</v>
+        <v>62751418</v>
       </c>
       <c r="D84" s="4">
-        <v>46133.777349537035</v>
+        <v>46147.490636574075</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G84" s="3">
-        <v>707906003</v>
+        <v>759379440</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="M84" s="3" t="s">
         <v>6</v>
@@ -5872,52 +5880,52 @@
       <c r="N84" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O84" s="3" t="s">
-        <v>215</v>
+      <c r="O84" s="3">
+        <v>2732780110</v>
       </c>
       <c r="P84" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q84" s="5">
-        <v>596888</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q84" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
-        <v>61509953</v>
+        <v>61560663</v>
       </c>
       <c r="B85" s="4">
-        <v>46125.694004629629</v>
+        <v>46126.615729166668</v>
       </c>
       <c r="C85" s="3">
-        <v>62751418</v>
+        <v>62946623</v>
       </c>
       <c r="D85" s="4">
-        <v>46147.490636574075</v>
+        <v>46150.461550925924</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="G85" s="3">
-        <v>759379440</v>
+        <v>707984429</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M85" s="3" t="s">
         <v>6</v>
@@ -5925,52 +5933,52 @@
       <c r="N85" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O85" s="3">
-        <v>2732780110</v>
+      <c r="O85" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="P85" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q85" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q85" s="5">
+        <v>2984038</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
-        <v>61560663</v>
+        <v>61608637</v>
       </c>
       <c r="B86" s="4">
-        <v>46126.615729166668</v>
+        <v>46127.491550925923</v>
       </c>
       <c r="C86" s="3">
-        <v>62044900</v>
+        <v>61677257</v>
       </c>
       <c r="D86" s="4">
-        <v>46134.432083333333</v>
+        <v>46128.483958333331</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="G86" s="3">
-        <v>707984429</v>
+        <v>702455701</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M86" s="3" t="s">
         <v>6</v>
@@ -5979,51 +5987,51 @@
         <v>14</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>2</v>
+        <v>220</v>
       </c>
       <c r="P86" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q86" s="5">
-        <v>2984038</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q86" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
-        <v>61608637</v>
+        <v>61620138</v>
       </c>
       <c r="B87" s="4">
-        <v>46127.491550925923</v>
+        <v>46127.578287037039</v>
       </c>
       <c r="C87" s="3">
-        <v>61677257</v>
+        <v>62163793</v>
       </c>
       <c r="D87" s="4">
-        <v>46128.483958333331</v>
+        <v>46136.340428240743</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G87" s="3">
-        <v>702455701</v>
+        <v>758051301</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>62</v>
+        <v>222</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="M87" s="3" t="s">
         <v>6</v>
@@ -6032,51 +6040,51 @@
         <v>14</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>219</v>
+        <v>2</v>
       </c>
       <c r="P87" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q87" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
-        <v>61620138</v>
+        <v>61644382</v>
       </c>
       <c r="B88" s="4">
-        <v>46127.578287037039</v>
+        <v>46127.754131944443</v>
       </c>
       <c r="C88" s="3">
-        <v>62163793</v>
+        <v>61977733</v>
       </c>
       <c r="D88" s="4">
-        <v>46136.340428240743</v>
+        <v>46133.466458333336</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="G88" s="3">
-        <v>758051301</v>
+        <v>759250737</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M88" s="3" t="s">
         <v>6</v>
@@ -6085,51 +6093,51 @@
         <v>14</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>2</v>
+        <v>224</v>
       </c>
       <c r="P88" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q88" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="Q88" s="5">
+        <v>1680307</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
-        <v>61644382</v>
+        <v>61700587</v>
       </c>
       <c r="B89" s="4">
-        <v>46127.754131944443</v>
+        <v>46128.642256944448</v>
       </c>
       <c r="C89" s="3">
-        <v>61977733</v>
+        <v>62975253</v>
       </c>
       <c r="D89" s="4">
-        <v>46133.466458333336</v>
+        <v>46150.696006944447</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="G89" s="3">
-        <v>759250737</v>
+        <v>747568798</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>31</v>
+        <v>187</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>6</v>
@@ -6137,40 +6145,40 @@
       <c r="N89" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>223</v>
+      <c r="O89" s="3">
+        <v>2722419000</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q89" s="5">
-        <v>1680307</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q89" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
-        <v>61700587</v>
+        <v>61702838</v>
       </c>
       <c r="B90" s="4">
-        <v>46128.642256944448</v>
+        <v>46128.658946759257</v>
       </c>
       <c r="C90" s="3">
-        <v>61957533</v>
+        <v>62874984</v>
       </c>
       <c r="D90" s="4">
-        <v>46132.804351851853</v>
+        <v>46149.406423611108</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G90" s="3">
         <v>747568798</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>2</v>
@@ -6179,7 +6187,7 @@
         <v>3</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>4</v>
+        <v>187</v>
       </c>
       <c r="L90" s="3" t="s">
         <v>5</v>
@@ -6188,10 +6196,10 @@
         <v>6</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O90" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
+      </c>
+      <c r="O90" s="3">
+        <v>2734710371</v>
       </c>
       <c r="P90" s="3" t="s">
         <v>2</v>
@@ -6200,39 +6208,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
-        <v>61702838</v>
+        <v>61710072</v>
       </c>
       <c r="B91" s="4">
-        <v>46128.658946759257</v>
+        <v>46128.708032407405</v>
       </c>
       <c r="C91" s="3">
-        <v>62874984</v>
+        <v>62110207</v>
       </c>
       <c r="D91" s="4">
-        <v>46149.406423611108</v>
+        <v>46135.445254629631</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G91" s="3">
-        <v>747568798</v>
+        <v>584425796</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>2</v>
+        <v>229</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>183</v>
+        <v>4</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>5</v>
@@ -6241,10 +6249,10 @@
         <v>6</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="O91" s="3">
-        <v>2734710371</v>
+        <v>2721711717</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>2</v>
@@ -6253,42 +6261,42 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A92" s="3">
-        <v>61710072</v>
+        <v>61828334</v>
       </c>
       <c r="B92" s="4">
-        <v>46128.708032407405</v>
+        <v>46130.562754629631</v>
       </c>
       <c r="C92" s="3">
-        <v>62110207</v>
+        <v>62208296</v>
       </c>
       <c r="D92" s="4">
-        <v>46135.445254629631</v>
+        <v>46136.716527777775</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G92" s="3">
-        <v>584425796</v>
+        <v>747309803</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I92" s="3">
-        <v>0</v>
+        <v>231</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="M92" s="3" t="s">
         <v>6</v>
@@ -6296,40 +6304,40 @@
       <c r="N92" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O92" s="3">
-        <v>2721711717</v>
+      <c r="O92" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="P92" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q92" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q92" s="5">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
-        <v>61828334</v>
+        <v>61946442</v>
       </c>
       <c r="B93" s="4">
-        <v>46130.562754629631</v>
+        <v>46132.704247685186</v>
       </c>
       <c r="C93" s="3">
-        <v>62208296</v>
+        <v>62946744</v>
       </c>
       <c r="D93" s="4">
-        <v>46136.716527777775</v>
+        <v>46150.462650462963</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G93" s="3">
-        <v>747309803</v>
+        <v>504041812</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>2</v>
@@ -6338,7 +6346,7 @@
         <v>26</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>27</v>
@@ -6350,7 +6358,7 @@
         <v>14</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>231</v>
+        <v>39</v>
       </c>
       <c r="P93" s="3" t="s">
         <v>2</v>
@@ -6359,45 +6367,45 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
-        <v>61946442</v>
+        <v>61972088</v>
       </c>
       <c r="B94" s="4">
-        <v>46132.704247685186</v>
+        <v>46133.422569444447</v>
       </c>
       <c r="C94" s="3">
-        <v>62214354</v>
+        <v>62868217</v>
       </c>
       <c r="D94" s="4">
-        <v>46136.781145833331</v>
+        <v>46149.240729166668</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>59</v>
+        <v>236</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G94" s="3">
         <v>504041812</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>14</v>
@@ -6408,34 +6416,34 @@
       <c r="P94" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q94" s="5">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q94" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
-        <v>61972088</v>
+        <v>61972108</v>
       </c>
       <c r="B95" s="4">
-        <v>46133.422569444447</v>
+        <v>46133.422662037039</v>
       </c>
       <c r="C95" s="3">
-        <v>62868217</v>
+        <v>62946845</v>
       </c>
       <c r="D95" s="4">
-        <v>46149.240729166668</v>
+        <v>46150.463449074072</v>
       </c>
       <c r="E95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="G95" s="3">
         <v>504041812</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>2</v>
@@ -6450,163 +6458,163 @@
         <v>12</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="N95" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="P95" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q95" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q95" s="5">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" ht="84" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
-        <v>61972108</v>
+        <v>62014200</v>
       </c>
       <c r="B96" s="4">
-        <v>46133.422662037039</v>
+        <v>46133.721585648149</v>
       </c>
       <c r="C96" s="3">
-        <v>62214514</v>
+        <v>62170861</v>
       </c>
       <c r="D96" s="4">
-        <v>46136.783449074072</v>
+        <v>46136.425300925926</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G96" s="3">
-        <v>504041812</v>
+        <v>709837321</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>101</v>
+        <v>239</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="P96" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q96" s="5">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" ht="104" x14ac:dyDescent="0.35">
+        <v>1644000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
-        <v>62014200</v>
+        <v>62170297</v>
       </c>
       <c r="B97" s="4">
-        <v>46133.721585648149</v>
+        <v>46136.420717592591</v>
       </c>
       <c r="C97" s="3">
-        <v>62170861</v>
+        <v>62868231</v>
       </c>
       <c r="D97" s="4">
-        <v>46136.425300925926</v>
+        <v>46149.242083333331</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G97" s="3">
-        <v>709837321</v>
+        <v>546016502</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K97" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L97" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N97" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O97" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P97" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q97" s="5">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="36" x14ac:dyDescent="0.35">
+      <c r="A98" s="3">
+        <v>62241651</v>
+      </c>
+      <c r="B98" s="4">
+        <v>46137.593402777777</v>
+      </c>
+      <c r="C98" s="3">
+        <v>62915074</v>
+      </c>
+      <c r="D98" s="4">
+        <v>46149.715150462966</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G98" s="3">
+        <v>707678205</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L98" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="N97" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P97" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q97" s="5">
-        <v>1644000</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" ht="52" x14ac:dyDescent="0.35">
-      <c r="A98" s="3">
-        <v>62170297</v>
-      </c>
-      <c r="B98" s="4">
-        <v>46136.420717592591</v>
-      </c>
-      <c r="C98" s="3">
-        <v>62868231</v>
-      </c>
-      <c r="D98" s="4">
-        <v>46149.242083333331</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G98" s="3">
-        <v>546016502</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J98" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K98" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L98" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="M98" s="3" t="s">
         <v>6</v>
@@ -6615,45 +6623,45 @@
         <v>14</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>39</v>
+        <v>243</v>
       </c>
       <c r="P98" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q98" s="5">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
-        <v>62241651</v>
+        <v>62243628</v>
       </c>
       <c r="B99" s="4">
-        <v>46137.593402777777</v>
+        <v>46137.617604166669</v>
       </c>
       <c r="C99" s="3">
-        <v>62915074</v>
+        <v>62916092</v>
       </c>
       <c r="D99" s="4">
-        <v>46149.715150462966</v>
+        <v>46149.721608796295</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G99" s="3">
-        <v>707678205</v>
+        <v>779191985</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>2</v>
+        <v>245</v>
+      </c>
+      <c r="I99" s="3">
+        <v>1894446</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="K99" s="3" t="s">
         <v>31</v>
@@ -6662,13 +6670,13 @@
         <v>27</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="P99" s="3" t="s">
         <v>2</v>
@@ -6677,42 +6685,42 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
-        <v>62243628</v>
+        <v>62249046</v>
       </c>
       <c r="B100" s="4">
-        <v>46137.617604166669</v>
+        <v>46137.688391203701</v>
       </c>
       <c r="C100" s="3">
-        <v>62916092</v>
+        <v>62868237</v>
       </c>
       <c r="D100" s="4">
-        <v>46149.721608796295</v>
+        <v>46149.242812500001</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G100" s="3">
-        <v>779191985</v>
+        <v>708946683</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>6</v>
@@ -6721,51 +6729,51 @@
         <v>14</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q100" s="5">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q100" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
-        <v>62249046</v>
+        <v>62420329</v>
       </c>
       <c r="B101" s="4">
-        <v>46137.688391203701</v>
+        <v>46140.709513888891</v>
       </c>
       <c r="C101" s="3">
-        <v>62868237</v>
+        <v>62868242</v>
       </c>
       <c r="D101" s="4">
-        <v>46149.242812500001</v>
+        <v>46149.243807870371</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G101" s="3">
-        <v>708946683</v>
+        <v>777621987</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>6</v>
@@ -6774,51 +6782,51 @@
         <v>14</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q101" s="5">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
-        <v>62420329</v>
+        <v>62497009</v>
       </c>
       <c r="B102" s="4">
-        <v>46140.709513888891</v>
+        <v>46141.808842592596</v>
       </c>
       <c r="C102" s="3">
-        <v>62868242</v>
+        <v>62985374</v>
       </c>
       <c r="D102" s="4">
-        <v>46149.243807870371</v>
+        <v>46150.791493055556</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G102" s="3">
-        <v>777621987</v>
+        <v>702495660</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>6</v>
@@ -6827,51 +6835,51 @@
         <v>14</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q102" s="5">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="Q102" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
-        <v>62497009</v>
+        <v>62544794</v>
       </c>
       <c r="B103" s="4">
-        <v>46141.808842592596</v>
+        <v>46142.662094907406</v>
       </c>
       <c r="C103" s="3">
-        <v>62942793</v>
+        <v>62986109</v>
       </c>
       <c r="D103" s="4">
-        <v>46150.431400462963</v>
+        <v>46150.810706018521</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G103" s="3">
-        <v>702495660</v>
+        <v>142128888</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>62</v>
+        <v>252</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M103" s="3" t="s">
         <v>6</v>
@@ -6880,101 +6888,101 @@
         <v>14</v>
       </c>
       <c r="O103" s="3" t="s">
-        <v>219</v>
+        <v>39</v>
       </c>
       <c r="P103" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q103" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="Q103" s="5">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
-        <v>62544794</v>
+        <v>62546484</v>
       </c>
       <c r="B104" s="4">
-        <v>46142.662094907406</v>
+        <v>46142.674293981479</v>
       </c>
       <c r="C104" s="3">
-        <v>62943024</v>
+        <v>62882881</v>
       </c>
       <c r="D104" s="4">
-        <v>46150.432986111111</v>
+        <v>46149.471701388888</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>251</v>
+        <v>33</v>
       </c>
       <c r="G104" s="3">
-        <v>142128888</v>
+        <v>768204550</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>252</v>
+        <v>88</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="K104" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M104" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N104" s="3" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="O104" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P104" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q104" s="5">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="Q104" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" ht="72" x14ac:dyDescent="0.35">
       <c r="A105" s="3">
-        <v>62546484</v>
+        <v>62551370</v>
       </c>
       <c r="B105" s="4">
-        <v>46142.674293981479</v>
+        <v>46142.717349537037</v>
       </c>
       <c r="C105" s="3">
-        <v>62882881</v>
+        <v>62899958</v>
       </c>
       <c r="D105" s="4">
-        <v>46149.471701388888</v>
+        <v>46149.608275462961</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>33</v>
+        <v>253</v>
       </c>
       <c r="G105" s="3">
-        <v>768204550</v>
+        <v>576382850</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>86</v>
+        <v>254</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L105" s="3" t="s">
         <v>5</v>
@@ -6983,10 +6991,10 @@
         <v>6</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="O105" s="3" t="s">
-        <v>42</v>
+        <v>220</v>
       </c>
       <c r="P105" s="3" t="s">
         <v>2</v>
@@ -6995,51 +7003,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="91" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" ht="72" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
-        <v>62551370</v>
+        <v>62672227</v>
       </c>
       <c r="B106" s="4">
-        <v>46142.717349537037</v>
+        <v>46146.403935185182</v>
       </c>
       <c r="C106" s="3">
-        <v>62899958</v>
+        <v>62980356</v>
       </c>
       <c r="D106" s="4">
-        <v>46149.608275462961</v>
+        <v>46150.72997685185</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>88</v>
+        <v>257</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G106" s="3">
-        <v>576382850</v>
+        <v>707169322</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="N106" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O106" s="3" t="s">
-        <v>219</v>
+        <v>23</v>
       </c>
       <c r="P106" s="3" t="s">
         <v>2</v>
@@ -7048,21 +7056,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="91" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" ht="72" x14ac:dyDescent="0.35">
       <c r="A107" s="3">
-        <v>62672227</v>
+        <v>62672234</v>
       </c>
       <c r="B107" s="4">
-        <v>46146.403935185182</v>
+        <v>46146.403969907406</v>
       </c>
       <c r="C107" s="3">
-        <v>62754365</v>
+        <v>62980413</v>
       </c>
       <c r="D107" s="4">
-        <v>46147.504826388889</v>
+        <v>46150.730520833335</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>235</v>
+        <v>60</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>255</v>
@@ -7080,110 +7088,110 @@
         <v>26</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="L107" s="3" t="s">
         <v>27</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="N107" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O107" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="P107" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q107" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" ht="91" x14ac:dyDescent="0.35">
+      <c r="Q107" s="5">
+        <v>1644000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" ht="96" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
-        <v>62672234</v>
+        <v>62680657</v>
       </c>
       <c r="B108" s="4">
-        <v>46146.403969907406</v>
+        <v>46146.475763888891</v>
       </c>
       <c r="C108" s="3">
-        <v>62753946</v>
+        <v>62868238</v>
       </c>
       <c r="D108" s="4">
-        <v>46147.502928240741</v>
+        <v>46149.243171296293</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>235</v>
+        <v>62</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G108" s="3">
-        <v>707169322</v>
+        <v>778096389</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="N108" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O108" s="3" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="P108" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q108" s="5">
-        <v>1644000</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" ht="104" x14ac:dyDescent="0.35">
+      <c r="Q108" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A109" s="3">
-        <v>62680657</v>
+        <v>62682536</v>
       </c>
       <c r="B109" s="4">
-        <v>46146.475763888891</v>
+        <v>46146.490057870367</v>
       </c>
       <c r="C109" s="3">
-        <v>62868238</v>
+        <v>62885918</v>
       </c>
       <c r="D109" s="4">
-        <v>46149.243171296293</v>
+        <v>46149.494571759256</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G109" s="3">
-        <v>778096389</v>
+        <v>789817770</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="K109" s="3" t="s">
         <v>4</v>
@@ -7198,39 +7206,39 @@
         <v>14</v>
       </c>
       <c r="O109" s="3" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="P109" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q109" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q109" s="5">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A110" s="3">
-        <v>62682536</v>
+        <v>62715782</v>
       </c>
       <c r="B110" s="4">
-        <v>46146.490057870367</v>
+        <v>46146.73746527778</v>
       </c>
       <c r="C110" s="3">
-        <v>62885918</v>
+        <v>62715928</v>
       </c>
       <c r="D110" s="4">
-        <v>46149.494571759256</v>
+        <v>46146.738587962966</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>262</v>
+        <v>184</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G110" s="3">
-        <v>789817770</v>
+        <v>707366919</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>260</v>
+        <v>64</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>2</v>
@@ -7248,42 +7256,42 @@
         <v>6</v>
       </c>
       <c r="N110" s="3" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="O110" s="3" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="P110" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q110" s="5">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q110" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" ht="72" x14ac:dyDescent="0.35">
       <c r="A111" s="3">
-        <v>62715782</v>
+        <v>62722805</v>
       </c>
       <c r="B111" s="4">
-        <v>46146.73746527778</v>
+        <v>46146.81181712963</v>
       </c>
       <c r="C111" s="3">
-        <v>62715928</v>
+        <v>62886458</v>
       </c>
       <c r="D111" s="4">
-        <v>46146.738587962966</v>
+        <v>46149.498113425929</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G111" s="3">
-        <v>707366919</v>
+        <v>708131488</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>62</v>
+        <v>265</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>2</v>
@@ -7301,10 +7309,10 @@
         <v>6</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="O111" s="3" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="P111" s="3" t="s">
         <v>2</v>
@@ -7313,74 +7321,74 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="78" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A112" s="3">
-        <v>62722805</v>
+        <v>62742919</v>
       </c>
       <c r="B112" s="4">
-        <v>46146.81181712963</v>
+        <v>46147.438668981478</v>
       </c>
       <c r="C112" s="3">
-        <v>62886458</v>
+        <v>62940803</v>
       </c>
       <c r="D112" s="4">
-        <v>46149.498113425929</v>
+        <v>46150.411296296297</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>262</v>
+        <v>89</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G112" s="3">
-        <v>708131488</v>
+        <v>757750210</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="K112" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="M112" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N112" s="3" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="O112" s="3" t="s">
-        <v>176</v>
+        <v>268</v>
       </c>
       <c r="P112" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q112" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="Q112" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A113" s="3">
-        <v>62742919</v>
+        <v>62746621</v>
       </c>
       <c r="B113" s="4">
-        <v>46147.438668981478</v>
+        <v>46147.463020833333</v>
       </c>
       <c r="C113" s="3">
-        <v>62940803</v>
+        <v>62900765</v>
       </c>
       <c r="D113" s="4">
-        <v>46150.411296296297</v>
+        <v>46149.615798611114</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>266</v>
@@ -7389,13 +7397,13 @@
         <v>757750210</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>2</v>
+        <v>269</v>
+      </c>
+      <c r="I113" s="3">
+        <v>1941026</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="K113" s="3" t="s">
         <v>11</v>
@@ -7404,13 +7412,13 @@
         <v>27</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="O113" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P113" s="3" t="s">
         <v>2</v>
@@ -7419,21 +7427,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A114" s="3">
-        <v>62746621</v>
+        <v>62748443</v>
       </c>
       <c r="B114" s="4">
-        <v>46147.463020833333</v>
+        <v>46147.475057870368</v>
       </c>
       <c r="C114" s="3">
-        <v>62900765</v>
+        <v>62943615</v>
       </c>
       <c r="D114" s="4">
-        <v>46149.615798611114</v>
+        <v>46150.437337962961</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>266</v>
@@ -7442,28 +7450,28 @@
         <v>757750210</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="I114" s="3">
-        <v>1941026</v>
+        <v>64</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="K114" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="N114" s="3" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="O114" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P114" s="3" t="s">
         <v>2</v>
@@ -7472,42 +7480,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A115" s="3">
-        <v>62748443</v>
+        <v>62760027</v>
       </c>
       <c r="B115" s="4">
-        <v>46147.475057870368</v>
+        <v>46147.546493055554</v>
       </c>
       <c r="C115" s="3">
-        <v>62943615</v>
+        <v>62902869</v>
       </c>
       <c r="D115" s="4">
-        <v>46150.437337962961</v>
+        <v>46149.631921296299</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="G115" s="3">
-        <v>757750210</v>
+        <v>777699799</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>62</v>
+        <v>273</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="K115" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M115" s="3" t="s">
         <v>6</v>
@@ -7516,51 +7524,51 @@
         <v>14</v>
       </c>
       <c r="O115" s="3" t="s">
-        <v>271</v>
+        <v>220</v>
       </c>
       <c r="P115" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q115" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="Q115" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" ht="48" x14ac:dyDescent="0.35">
       <c r="A116" s="3">
-        <v>62760027</v>
+        <v>62768013</v>
       </c>
       <c r="B116" s="4">
-        <v>46147.546493055554</v>
+        <v>46147.609988425924</v>
       </c>
       <c r="C116" s="3">
-        <v>62902869</v>
+        <v>62871386</v>
       </c>
       <c r="D116" s="4">
-        <v>46149.631921296299</v>
+        <v>46149.364837962959</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G116" s="3">
-        <v>777699799</v>
+        <v>143270405</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K116" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M116" s="3" t="s">
         <v>6</v>
@@ -7569,7 +7577,7 @@
         <v>14</v>
       </c>
       <c r="O116" s="3" t="s">
-        <v>219</v>
+        <v>39</v>
       </c>
       <c r="P116" s="3" t="s">
         <v>2</v>
@@ -7578,42 +7586,42 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" ht="72" x14ac:dyDescent="0.35">
       <c r="A117" s="3">
-        <v>62768013</v>
+        <v>62840921</v>
       </c>
       <c r="B117" s="4">
-        <v>46147.609988425924</v>
+        <v>46148.636331018519</v>
       </c>
       <c r="C117" s="3">
-        <v>62871386</v>
+        <v>62941498</v>
       </c>
       <c r="D117" s="4">
-        <v>46149.364837962959</v>
+        <v>46150.418506944443</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G117" s="3">
-        <v>143270405</v>
+        <v>707551377</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="K117" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="M117" s="3" t="s">
         <v>6</v>
@@ -7622,7 +7630,7 @@
         <v>14</v>
       </c>
       <c r="O117" s="3" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
       <c r="P117" s="3" t="s">
         <v>2</v>
@@ -7631,30 +7639,30 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="78" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" ht="60" x14ac:dyDescent="0.35">
       <c r="A118" s="3">
-        <v>62840921</v>
+        <v>62852675</v>
       </c>
       <c r="B118" s="4">
-        <v>46148.636331018519</v>
+        <v>46148.714444444442</v>
       </c>
       <c r="C118" s="3">
-        <v>62941498</v>
+        <v>62871524</v>
       </c>
       <c r="D118" s="4">
-        <v>46150.418506944443</v>
+        <v>46149.366689814815</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>66</v>
+        <v>281</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G118" s="3">
-        <v>707551377</v>
+        <v>777589587</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>2</v>
@@ -7669,45 +7677,45 @@
         <v>27</v>
       </c>
       <c r="M118" s="3" t="s">
-        <v>6</v>
+        <v>239</v>
       </c>
       <c r="N118" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O118" s="3" t="s">
-        <v>278</v>
+        <v>2</v>
       </c>
       <c r="P118" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q118" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+      <c r="Q118" s="5">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A119" s="3">
-        <v>62852675</v>
+        <v>62880594</v>
       </c>
       <c r="B119" s="4">
-        <v>46148.714444444442</v>
+        <v>46149.454710648148</v>
       </c>
       <c r="C119" s="3">
-        <v>62871524</v>
+        <v>62941351</v>
       </c>
       <c r="D119" s="4">
-        <v>46149.366689814815</v>
+        <v>46150.416979166665</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>281</v>
+        <v>68</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G119" s="3">
-        <v>777589587</v>
+        <v>709565662</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>2</v>
@@ -7722,36 +7730,36 @@
         <v>27</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>238</v>
+        <v>19</v>
       </c>
       <c r="N119" s="3" t="s">
         <v>14</v>
       </c>
       <c r="O119" s="3" t="s">
-        <v>2</v>
+        <v>284</v>
       </c>
       <c r="P119" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q119" s="5">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q119" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" ht="36" x14ac:dyDescent="0.35">
       <c r="A120" s="3">
-        <v>62880594</v>
+        <v>62880628</v>
       </c>
       <c r="B120" s="4">
-        <v>46149.454710648148</v>
+        <v>46149.45484953704</v>
       </c>
       <c r="C120" s="3">
-        <v>62941351</v>
+        <v>62941416</v>
       </c>
       <c r="D120" s="4">
-        <v>46150.416979166665</v>
+        <v>46150.417719907404</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>282</v>
@@ -7775,7 +7783,7 @@
         <v>27</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="N120" s="3" t="s">
         <v>14</v>
@@ -7786,99 +7794,99 @@
       <c r="P120" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q120" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q120" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" ht="96" x14ac:dyDescent="0.35">
       <c r="A121" s="3">
-        <v>62880628</v>
+        <v>62880812</v>
       </c>
       <c r="B121" s="4">
-        <v>46149.45484953704</v>
+        <v>46149.456157407411</v>
       </c>
       <c r="C121" s="3">
-        <v>62941416</v>
+        <v>62882154</v>
       </c>
       <c r="D121" s="4">
-        <v>46150.417719907404</v>
+        <v>46149.465740740743</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>66</v>
+        <v>281</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G121" s="3">
-        <v>709565662</v>
+        <v>707672487</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>2</v>
+        <v>286</v>
+      </c>
+      <c r="I121" s="3">
+        <v>0</v>
       </c>
       <c r="J121" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K121" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L121" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M121" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N121" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O121" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P121" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q121" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" ht="36" x14ac:dyDescent="0.35">
+      <c r="A122" s="3">
+        <v>62937923</v>
+      </c>
+      <c r="B122" s="4">
+        <v>46150.381145833337</v>
+      </c>
+      <c r="C122" s="3">
+        <v>62968387</v>
+      </c>
+      <c r="D122" s="4">
+        <v>46150.639861111114</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G122" s="3">
+        <v>565811689</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J122" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K121" s="3" t="s">
+      <c r="K122" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L121" s="3" t="s">
+      <c r="L122" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="M121" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="N121" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O121" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="P121" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q121" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" ht="130" x14ac:dyDescent="0.35">
-      <c r="A122" s="3">
-        <v>62880812</v>
-      </c>
-      <c r="B122" s="4">
-        <v>46149.456157407411</v>
-      </c>
-      <c r="C122" s="3">
-        <v>62882154</v>
-      </c>
-      <c r="D122" s="4">
-        <v>46149.465740740743</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G122" s="3">
-        <v>707672487</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="I122" s="3">
-        <v>0</v>
-      </c>
-      <c r="J122" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K122" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L122" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="M122" s="3" t="s">
         <v>6</v>
@@ -7892,34 +7900,34 @@
       <c r="P122" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q122" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q122" s="5">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" ht="24" x14ac:dyDescent="0.35">
       <c r="A123" s="3">
-        <v>62937923</v>
+        <v>62968196</v>
       </c>
       <c r="B123" s="4">
-        <v>46150.381145833337</v>
+        <v>46150.638715277775</v>
       </c>
       <c r="C123" s="3">
-        <v>62937976</v>
+        <v>63018932</v>
       </c>
       <c r="D123" s="4">
-        <v>46150.381585648145</v>
+        <v>46151.651284722226</v>
       </c>
       <c r="E123" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="F123" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="F123" s="3" t="s">
-        <v>287</v>
-      </c>
       <c r="G123" s="3">
-        <v>565811689</v>
+        <v>758177759</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>2</v>
@@ -7934,23 +7942,76 @@
         <v>27</v>
       </c>
       <c r="M123" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="N123" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O123" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P123" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q123" s="5">
+        <v>2881416</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" ht="36" x14ac:dyDescent="0.35">
+      <c r="A124" s="3">
+        <v>63025600</v>
+      </c>
+      <c r="B124" s="4">
+        <v>46151.740983796299</v>
+      </c>
+      <c r="C124" s="3">
+        <v>63025649</v>
+      </c>
+      <c r="D124" s="4">
+        <v>46151.741284722222</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G124" s="3">
+        <v>758237461</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L124" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M124" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="N123" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O123" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P123" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q123" s="5">
-        <v>250000</v>
+      <c r="N124" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O124" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P124" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q124" s="5">
+        <v>850000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q123" xr:uid="{76AAFD7B-AF0D-4C07-A193-5ED21C49A69A}"/>
+  <autoFilter ref="A1:Q124" xr:uid="{CEA6B63F-CC06-4AE4-99D5-8F3B8C81168B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/Attachments/Bureau/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="407" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2A02E91-EAB6-480D-BE57-F40080CB5CEC}"/>
+  <xr:revisionPtr revIDLastSave="451" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86184E87-553E-4F89-9AFC-41CBB263610D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil2" sheetId="44" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="45" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil2!$A$1:$Q$122</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="283">
   <si>
     <t>-</t>
   </si>
@@ -341,15 +338,6 @@
     <t>M'BRAGO</t>
   </si>
   <si>
-    <t>NSIA BANQUE</t>
-  </si>
-  <si>
-    <t>BONDOUKOU</t>
-  </si>
-  <si>
-    <t>1.635.147</t>
-  </si>
-  <si>
     <t>STE MUGEFCI</t>
   </si>
   <si>
@@ -359,9 +347,6 @@
     <t>TAABO LAMTO</t>
   </si>
   <si>
-    <t>Ingenieur Projet: Suspension Travaux DOB</t>
-  </si>
-  <si>
     <t>MFI CI (SODEXAM)</t>
   </si>
   <si>
@@ -434,45 +419,12 @@
     <t>XXXXXXXXXXXXXX</t>
   </si>
   <si>
-    <t>UBA</t>
-  </si>
-  <si>
-    <t>STE SIB</t>
-  </si>
-  <si>
-    <t>cuivre</t>
-  </si>
-  <si>
-    <t>AIR CI</t>
-  </si>
-  <si>
-    <t>TREICHVILLE ZONE AEROPORTUAIRE</t>
-  </si>
-  <si>
-    <t>CORIS BANK (BACKUP DU 2722223530 )</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY 2 PLATEAUX</t>
-  </si>
-  <si>
-    <t>BICICI PLATEAU (BACKUP DU 2720242424 )</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PLATEAU</t>
-  </si>
-  <si>
     <t>GRAND BASSAM</t>
   </si>
   <si>
     <t>SUD COMOE CAOUTCHOU</t>
   </si>
   <si>
-    <t>OFI, OLAM IVOIRE</t>
-  </si>
-  <si>
-    <t>ANYAMA</t>
-  </si>
-  <si>
     <t>radio_fh</t>
   </si>
   <si>
@@ -494,36 +446,12 @@
     <t>OFI OLAM IVOIRE</t>
   </si>
   <si>
-    <t>SECO OUANGOLO (BACKUP DU SYTHD220080)</t>
-  </si>
-  <si>
-    <t>SECO OUANGOLO</t>
-  </si>
-  <si>
-    <t>SECO DIAWALA (BACKUP DU SYTHD220089   )</t>
-  </si>
-  <si>
-    <t>SECO FERKE (BACKUP DU SYTHD220118 )</t>
-  </si>
-  <si>
-    <t>SECO FERKE</t>
-  </si>
-  <si>
-    <t>SECO TREICHVILLE (BACKUP DU SYTHD230357 )</t>
-  </si>
-  <si>
-    <t>SECO TREICHVILLE</t>
-  </si>
-  <si>
     <t>MAXAM CI</t>
   </si>
   <si>
     <t>BUVPN250061</t>
   </si>
   <si>
-    <t>DIAWALA//VOIE INCONNUE/SECO DIAWALA 05 06 72 72 87</t>
-  </si>
-  <si>
     <t>RIMCO</t>
   </si>
   <si>
@@ -539,9 +467,6 @@
     <t>xxxxxx</t>
   </si>
   <si>
-    <t>xxxxxxxxxxxxxxx</t>
-  </si>
-  <si>
     <t>Etude Suspendu</t>
   </si>
   <si>
@@ -587,12 +512,6 @@
     <t>STE COMPAGNIE IVOIRIENNE D'ELECTRICITE DTET</t>
   </si>
   <si>
-    <t>STE CFAO RETAIL</t>
-  </si>
-  <si>
-    <t>PORT_BOUET_ZONE_AEROPORTUAIRE</t>
-  </si>
-  <si>
     <t>AFG BANK</t>
   </si>
   <si>
@@ -605,18 +524,6 @@
     <t>MILLENIUM INDUSTRIE CI</t>
   </si>
   <si>
-    <t>CFAO RETAIL</t>
-  </si>
-  <si>
-    <t>SDA_RCI_MARCORY</t>
-  </si>
-  <si>
-    <t>COCODY_LAS_PALMAS</t>
-  </si>
-  <si>
-    <t>SDA_RCI_ANGRE</t>
-  </si>
-  <si>
     <t>ECOBANK COCODY RIVIERA</t>
   </si>
   <si>
@@ -671,12 +578,6 @@
     <t>NETCYBER CONSULTING</t>
   </si>
   <si>
-    <t>SGCI</t>
-  </si>
-  <si>
-    <t>DEUX PLATEAUX</t>
-  </si>
-  <si>
     <t>ABIDJAN-PLATEAU BATIMENT WALL STREET</t>
   </si>
   <si>
@@ -770,9 +671,6 @@
     <t>COCODY RIVIERA 2</t>
   </si>
   <si>
-    <t>IP Delivery: Validation information</t>
-  </si>
-  <si>
     <t>MANKALA</t>
   </si>
   <si>
@@ -809,18 +707,9 @@
     <t>ANSSI</t>
   </si>
   <si>
-    <t>ABIDJAN</t>
-  </si>
-  <si>
     <t>NOM</t>
   </si>
   <si>
-    <t>MOTA ENGIL MINING LAFIGUE</t>
-  </si>
-  <si>
-    <t>DABAKALA//VOIE INCONNUE/M. AKOUE 07 48 51 26 13</t>
-  </si>
-  <si>
     <t>SYTHD260132</t>
   </si>
   <si>
@@ -836,12 +725,6 @@
     <t>PLANETPHARMA EXPORT CI</t>
   </si>
   <si>
-    <t>MANTRA IVOIRE SA</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/VRIDI 05 46 00 81 31</t>
-  </si>
-  <si>
     <t>SYTHD260131</t>
   </si>
   <si>
@@ -854,12 +737,6 @@
     <t>SYTHD260136</t>
   </si>
   <si>
-    <t>SYTHD260128</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PORT-BOUET//VOIE INCONNUE/VRIDI ZONE INDUSTRIELLE</t>
-  </si>
-  <si>
     <t>SYTHD260129</t>
   </si>
   <si>
@@ -872,15 +749,6 @@
     <t>XXXXXXXXXXXXXXXXX</t>
   </si>
   <si>
-    <t>SYTHD260125</t>
-  </si>
-  <si>
-    <t>YAMOUSSOUKRO//VOIE INCONNUE/</t>
-  </si>
-  <si>
-    <t>SYTHD260124</t>
-  </si>
-  <si>
     <t>SYTHD260130</t>
   </si>
   <si>
@@ -905,12 +773,6 @@
     <t>SYTHD190044</t>
   </si>
   <si>
-    <t>SOFITEL ABIDJAN HOTEL IVOIRE</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY AU SEIN DE SOFITEL BLOC C</t>
-  </si>
-  <si>
     <t>STE BICICI</t>
   </si>
   <si>
@@ -942,6 +804,87 @@
   </si>
   <si>
     <t>COCODY IMMEUBLE TRIDEM PHARMA RDC</t>
+  </si>
+  <si>
+    <t>ODIENNE//VOIE INCONNUE/GBELEBAN</t>
+  </si>
+  <si>
+    <t>BUVPN260049</t>
+  </si>
+  <si>
+    <t>Prestataire : Correction Conformite Travaux</t>
+  </si>
+  <si>
+    <t>GOULIA</t>
+  </si>
+  <si>
+    <t>BUVPN260089</t>
+  </si>
+  <si>
+    <t>MOTA ENGIL COTE D'IVOIRE MINING</t>
+  </si>
+  <si>
+    <t>STE MANTRA IVOIRE SA VRIDI</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT BOUET VRIDI</t>
+  </si>
+  <si>
+    <t>SYTHD260137</t>
+  </si>
+  <si>
+    <t>SODEXAM BONDOUKOU STATION METEOROLOGIQUE</t>
+  </si>
+  <si>
+    <t>BONDOUKOU STATION METEOROLOGIQUE</t>
+  </si>
+  <si>
+    <t>SYTHD260115</t>
+  </si>
+  <si>
+    <t>SIE : Affectation des ressources</t>
+  </si>
+  <si>
+    <t>PORT-POUET VRIDI ZONE INDUSTRIELLE RUE DES TEXTILES</t>
+  </si>
+  <si>
+    <t>Suspendu</t>
+  </si>
+  <si>
+    <t>Create Gestion RdvEtude</t>
+  </si>
+  <si>
+    <t>SYTHD260134</t>
+  </si>
+  <si>
+    <t>BO Homologation: Mise en service GAIA</t>
+  </si>
+  <si>
+    <t>Parametrage facturation</t>
+  </si>
+  <si>
+    <t>AGENCE EMPLOI JEUNE</t>
+  </si>
+  <si>
+    <t>TREICHVILLE PALAIS DES SPORTS</t>
+  </si>
+  <si>
+    <t>SONGON</t>
+  </si>
+  <si>
+    <t>DOUANES</t>
+  </si>
+  <si>
+    <t>SITE CNTCI TREICHVILLE TERMINUS DU 222</t>
+  </si>
+  <si>
+    <t>SITE SESOCOM TRANSIT TREICHVILLE AVENUE 21 RUE 15</t>
+  </si>
+  <si>
+    <t>STE BGFI BANK</t>
+  </si>
+  <si>
+    <t>COCODY DANGA</t>
   </si>
 </sst>
 </file>
@@ -1007,10 +950,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1329,20 +1268,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E99D2217-19B7-48F6-AA0C-663745521120}">
-  <dimension ref="A1:Q122"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3F1327-EEF1-4F7B-8988-4F1DB9CBD7F5}">
+  <dimension ref="A1:Q108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" customWidth="1"/>
-    <col min="9" max="9" width="10.1796875" customWidth="1"/>
-    <col min="10" max="10" width="10.81640625" customWidth="1"/>
-    <col min="11" max="11" width="8.54296875" customWidth="1"/>
-    <col min="12" max="12" width="9.26953125" customWidth="1"/>
-    <col min="13" max="13" width="9.1796875" customWidth="1"/>
-    <col min="14" max="14" width="6.6328125" customWidth="1"/>
-    <col min="15" max="15" width="9.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.453125" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
@@ -1386,7 +1319,7 @@
         <v>53</v>
       </c>
       <c r="N1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="O1" t="s">
         <v>54</v>
@@ -1489,7 +1422,7 @@
         <v>17</v>
       </c>
       <c r="N3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O3" t="s">
         <v>0</v>
@@ -1542,7 +1475,7 @@
         <v>7</v>
       </c>
       <c r="N4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O4" t="s">
         <v>0</v>
@@ -1595,7 +1528,7 @@
         <v>3</v>
       </c>
       <c r="N5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O5" t="s">
         <v>0</v>
@@ -1648,7 +1581,7 @@
         <v>3</v>
       </c>
       <c r="N6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O6" t="s">
         <v>0</v>
@@ -1701,7 +1634,7 @@
         <v>3</v>
       </c>
       <c r="N7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O7" t="s">
         <v>0</v>
@@ -1754,7 +1687,7 @@
         <v>7</v>
       </c>
       <c r="N8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O8" t="s">
         <v>0</v>
@@ -1807,7 +1740,7 @@
         <v>7</v>
       </c>
       <c r="N9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O9" t="s">
         <v>0</v>
@@ -1860,7 +1793,7 @@
         <v>3</v>
       </c>
       <c r="N10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O10" t="s">
         <v>0</v>
@@ -1913,7 +1846,7 @@
         <v>3</v>
       </c>
       <c r="N11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O11" t="s">
         <v>0</v>
@@ -1966,7 +1899,7 @@
         <v>3</v>
       </c>
       <c r="N12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O12" t="s">
         <v>0</v>
@@ -2019,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="N13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O13" t="s">
         <v>0</v>
@@ -2033,19 +1966,19 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>56603495</v>
+        <v>56601140</v>
       </c>
       <c r="B14" s="2">
-        <v>46035.408518518518</v>
+        <v>46035.385555555556</v>
       </c>
       <c r="C14">
-        <v>60907737</v>
+        <v>59442988</v>
       </c>
       <c r="D14" s="2">
-        <v>46113.726909722223</v>
+        <v>46086.814479166664</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>258</v>
       </c>
       <c r="F14" t="s">
         <v>29</v>
@@ -2054,13 +1987,13 @@
         <v>707003126</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
-      </c>
-      <c r="I14" t="s">
-        <v>0</v>
+        <v>256</v>
+      </c>
+      <c r="I14">
+        <v>1778026</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -2069,10 +2002,10 @@
         <v>8</v>
       </c>
       <c r="M14" t="s">
-        <v>3</v>
+        <v>223</v>
       </c>
       <c r="N14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O14" t="s">
         <v>0</v>
@@ -2081,33 +2014,33 @@
         <v>7103410</v>
       </c>
       <c r="Q14" t="s">
-        <v>20</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>56606469</v>
+        <v>56601982</v>
       </c>
       <c r="B15" s="2">
-        <v>46035.43072916667</v>
+        <v>46035.393611111111</v>
       </c>
       <c r="C15">
-        <v>60100048</v>
+        <v>63227381</v>
       </c>
       <c r="D15" s="2">
-        <v>46099.427060185182</v>
+        <v>46155.633634259262</v>
       </c>
       <c r="E15" t="s">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G15">
-        <v>504041812</v>
+        <v>707003126</v>
       </c>
       <c r="H15" t="s">
-        <v>37</v>
+        <v>259</v>
       </c>
       <c r="I15" t="s">
         <v>0</v>
@@ -2125,42 +2058,42 @@
         <v>3</v>
       </c>
       <c r="N15" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O15" t="s">
         <v>0</v>
       </c>
       <c r="P15" s="1">
-        <v>1000000</v>
+        <v>7103410</v>
       </c>
       <c r="Q15" t="s">
-        <v>34</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>56607988</v>
+        <v>56603495</v>
       </c>
       <c r="B16" s="2">
-        <v>46035.443668981483</v>
+        <v>46035.408518518518</v>
       </c>
       <c r="C16">
-        <v>62467448</v>
+        <v>60907737</v>
       </c>
       <c r="D16" s="2">
-        <v>46141.570902777778</v>
+        <v>46113.726909722223</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="G16">
-        <v>504041812</v>
+        <v>707003126</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I16" t="s">
         <v>0</v>
@@ -2178,42 +2111,42 @@
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O16" t="s">
         <v>0</v>
       </c>
       <c r="P16" s="1">
-        <v>2000000</v>
+        <v>7103410</v>
       </c>
       <c r="Q16" t="s">
-        <v>221</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>56611212</v>
+        <v>56606469</v>
       </c>
       <c r="B17" s="2">
-        <v>46035.471886574072</v>
+        <v>46035.43072916667</v>
       </c>
       <c r="C17">
-        <v>62203808</v>
+        <v>60100048</v>
       </c>
       <c r="D17" s="2">
-        <v>46136.681342592594</v>
+        <v>46099.427060185182</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="F17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G17">
         <v>504041812</v>
       </c>
       <c r="H17" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="I17" t="s">
         <v>0</v>
@@ -2231,48 +2164,48 @@
         <v>3</v>
       </c>
       <c r="N17" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O17" t="s">
         <v>0</v>
       </c>
       <c r="P17" s="1">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q17" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>56618123</v>
+        <v>56607988</v>
       </c>
       <c r="B18" s="2">
-        <v>46035.520821759259</v>
+        <v>46035.443668981483</v>
       </c>
       <c r="C18">
-        <v>59311833</v>
+        <v>62467448</v>
       </c>
       <c r="D18" s="2">
-        <v>46084.811782407407</v>
+        <v>46141.570902777778</v>
       </c>
       <c r="E18" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G18">
         <v>504041812</v>
       </c>
       <c r="H18" t="s">
-        <v>128</v>
-      </c>
-      <c r="I18">
-        <v>1775236</v>
+        <v>88</v>
+      </c>
+      <c r="I18" t="s">
+        <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -2284,7 +2217,7 @@
         <v>3</v>
       </c>
       <c r="N18" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O18" t="s">
         <v>0</v>
@@ -2293,139 +2226,139 @@
         <v>2000000</v>
       </c>
       <c r="Q18" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>56675050</v>
+        <v>56611212</v>
       </c>
       <c r="B19" s="2">
-        <v>46036.516423611109</v>
+        <v>46035.471886574072</v>
       </c>
       <c r="C19">
-        <v>62913355</v>
+        <v>62203808</v>
       </c>
       <c r="D19" s="2">
-        <v>46149.704629629632</v>
+        <v>46136.681342592594</v>
       </c>
       <c r="E19" t="s">
-        <v>261</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="G19">
-        <v>748512613</v>
+        <v>504041812</v>
       </c>
       <c r="H19" t="s">
-        <v>259</v>
-      </c>
-      <c r="I19">
-        <v>1781606</v>
+        <v>90</v>
+      </c>
+      <c r="I19" t="s">
+        <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
       </c>
       <c r="L19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M19" t="s">
-        <v>257</v>
+        <v>3</v>
       </c>
       <c r="N19" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O19" t="s">
         <v>0</v>
       </c>
       <c r="P19" s="1">
-        <v>4362401</v>
+        <v>2000000</v>
       </c>
       <c r="Q19" t="s">
-        <v>260</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>56970346</v>
+        <v>56618123</v>
       </c>
       <c r="B20" s="2">
-        <v>46042.557280092595</v>
+        <v>46035.520821759259</v>
       </c>
       <c r="C20">
-        <v>59242054</v>
+        <v>59311833</v>
       </c>
       <c r="D20" s="2">
-        <v>46083.719525462962</v>
+        <v>46084.811782407407</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G20">
-        <v>708667658</v>
+        <v>504041812</v>
       </c>
       <c r="H20" t="s">
-        <v>94</v>
-      </c>
-      <c r="I20" t="s">
-        <v>0</v>
+        <v>124</v>
+      </c>
+      <c r="I20">
+        <v>1775236</v>
       </c>
       <c r="J20" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M20" t="s">
         <v>3</v>
       </c>
       <c r="N20" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O20" t="s">
         <v>0</v>
       </c>
       <c r="P20" s="1">
-        <v>2871414</v>
+        <v>2000000</v>
       </c>
       <c r="Q20" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>57398181</v>
+        <v>56675050</v>
       </c>
       <c r="B21" s="2">
-        <v>46050.584374999999</v>
+        <v>46036.516423611109</v>
       </c>
       <c r="C21">
-        <v>60344342</v>
+        <v>63140730</v>
       </c>
       <c r="D21" s="2">
-        <v>46104.528900462959</v>
+        <v>46154.429652777777</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>98</v>
+        <v>261</v>
       </c>
       <c r="G21">
-        <v>720631500</v>
+        <v>748512613</v>
       </c>
       <c r="H21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I21" t="s">
         <v>0</v>
@@ -2443,66 +2376,66 @@
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O21" t="s">
         <v>0</v>
       </c>
       <c r="P21" s="1">
-        <v>4406780</v>
+        <v>4362401</v>
       </c>
       <c r="Q21" t="s">
-        <v>35</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>57651441</v>
+        <v>56970346</v>
       </c>
       <c r="B22" s="2">
-        <v>46055.58011574074</v>
+        <v>46042.557280092595</v>
       </c>
       <c r="C22">
-        <v>58955875</v>
+        <v>59242054</v>
       </c>
       <c r="D22" s="2">
-        <v>46078.639594907407</v>
+        <v>46083.719525462962</v>
       </c>
       <c r="E22" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="G22">
-        <v>707079088</v>
+        <v>708667658</v>
       </c>
       <c r="H22" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I22" t="s">
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K22" t="s">
         <v>5</v>
       </c>
       <c r="L22" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M22" t="s">
         <v>3</v>
       </c>
       <c r="N22" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O22" t="s">
         <v>0</v>
       </c>
-      <c r="P22" t="s">
-        <v>102</v>
+      <c r="P22" s="1">
+        <v>2871414</v>
       </c>
       <c r="Q22" t="s">
         <v>34</v>
@@ -2510,28 +2443,28 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>57706849</v>
+        <v>57398181</v>
       </c>
       <c r="B23" s="2">
-        <v>46056.499166666668</v>
+        <v>46050.584374999999</v>
       </c>
       <c r="C23">
-        <v>62851094</v>
+        <v>60344342</v>
       </c>
       <c r="D23" s="2">
-        <v>46148.703194444446</v>
+        <v>46104.528900462959</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G23">
-        <v>708086472</v>
+        <v>720631500</v>
       </c>
       <c r="H23" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="I23" t="s">
         <v>0</v>
@@ -2546,45 +2479,45 @@
         <v>6</v>
       </c>
       <c r="M23" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N23" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O23" t="s">
         <v>0</v>
       </c>
-      <c r="P23">
-        <v>0</v>
+      <c r="P23" s="1">
+        <v>4406780</v>
       </c>
       <c r="Q23" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>58055656</v>
+        <v>57706849</v>
       </c>
       <c r="B24" s="2">
-        <v>46062.760023148148</v>
+        <v>46056.499166666668</v>
       </c>
       <c r="C24">
-        <v>61269237</v>
+        <v>62851094</v>
       </c>
       <c r="D24" s="2">
-        <v>46121.376689814817</v>
+        <v>46148.703194444446</v>
       </c>
       <c r="E24" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="F24" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G24">
-        <v>758224257</v>
+        <v>708086472</v>
       </c>
       <c r="H24" t="s">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="I24" t="s">
         <v>0</v>
@@ -2599,45 +2532,45 @@
         <v>6</v>
       </c>
       <c r="M24" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N24" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O24" t="s">
         <v>0</v>
       </c>
-      <c r="P24" s="1">
-        <v>1800000</v>
+      <c r="P24">
+        <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>58093827</v>
+        <v>58055656</v>
       </c>
       <c r="B25" s="2">
-        <v>46063.583402777775</v>
+        <v>46062.760023148148</v>
       </c>
       <c r="C25">
-        <v>62146534</v>
+        <v>61269237</v>
       </c>
       <c r="D25" s="2">
-        <v>46135.713287037041</v>
+        <v>46121.376689814817</v>
       </c>
       <c r="E25" t="s">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="G25">
-        <v>708086759</v>
+        <v>758224257</v>
       </c>
       <c r="H25" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="I25" t="s">
         <v>0</v>
@@ -2652,198 +2585,198 @@
         <v>6</v>
       </c>
       <c r="M25" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N25" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O25" t="s">
         <v>0</v>
       </c>
-      <c r="P25" t="s">
-        <v>0</v>
+      <c r="P25" s="1">
+        <v>1800000</v>
       </c>
       <c r="Q25" t="s">
-        <v>165</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>58166885</v>
+        <v>58093827</v>
       </c>
       <c r="B26" s="2">
-        <v>46064.649965277778</v>
+        <v>46063.583402777775</v>
       </c>
       <c r="C26">
-        <v>63079695</v>
+        <v>62146534</v>
       </c>
       <c r="D26" s="2">
-        <v>46153.448425925926</v>
+        <v>46135.713287037041</v>
       </c>
       <c r="E26" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="G26">
-        <v>504041812</v>
+        <v>708086759</v>
       </c>
       <c r="H26" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I26" t="s">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
       </c>
       <c r="L26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M26" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N26" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O26" t="s">
         <v>0</v>
       </c>
-      <c r="P26" s="1">
-        <v>2000000</v>
+      <c r="P26" t="s">
+        <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>262</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>58626822</v>
+        <v>58166885</v>
       </c>
       <c r="B27" s="2">
-        <v>46072.810324074075</v>
+        <v>46064.649965277778</v>
       </c>
       <c r="C27">
-        <v>59811821</v>
+        <v>63079695</v>
       </c>
       <c r="D27" s="2">
-        <v>46093.543773148151</v>
+        <v>46153.448425925926</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="F27" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="G27">
-        <v>709574114</v>
+        <v>504041812</v>
       </c>
       <c r="H27" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="I27" t="s">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
       </c>
       <c r="L27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M27" t="s">
         <v>3</v>
       </c>
       <c r="N27" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O27" t="s">
         <v>0</v>
       </c>
       <c r="P27" s="1">
-        <v>445307</v>
+        <v>2000000</v>
       </c>
       <c r="Q27" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>58635645</v>
+        <v>58626822</v>
       </c>
       <c r="B28" s="2">
-        <v>46073.372395833336</v>
+        <v>46072.810324074075</v>
       </c>
       <c r="C28">
-        <v>61982536</v>
+        <v>59811821</v>
       </c>
       <c r="D28" s="2">
-        <v>46133.49863425926</v>
+        <v>46093.543773148151</v>
       </c>
       <c r="E28" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G28">
-        <v>759250737</v>
+        <v>709574114</v>
       </c>
       <c r="H28" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="I28" t="s">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K28" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L28" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M28" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N28" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O28" t="s">
         <v>0</v>
       </c>
-      <c r="P28" t="s">
-        <v>0</v>
+      <c r="P28" s="1">
+        <v>445307</v>
       </c>
       <c r="Q28" t="s">
-        <v>171</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>58635674</v>
+        <v>58635645</v>
       </c>
       <c r="B29" s="2">
-        <v>46073.372488425928</v>
+        <v>46073.372395833336</v>
       </c>
       <c r="C29">
-        <v>61980847</v>
+        <v>61982536</v>
       </c>
       <c r="D29" s="2">
-        <v>46133.487384259257</v>
+        <v>46133.49863425926</v>
       </c>
       <c r="E29" t="s">
         <v>16</v>
       </c>
       <c r="F29" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G29">
         <v>759250737</v>
@@ -2858,51 +2791,51 @@
         <v>18</v>
       </c>
       <c r="K29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L29" t="s">
         <v>8</v>
       </c>
       <c r="M29" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N29" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O29" t="s">
         <v>0</v>
       </c>
-      <c r="P29" s="1">
-        <v>500000</v>
+      <c r="P29" t="s">
+        <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>58797846</v>
+        <v>58635674</v>
       </c>
       <c r="B30" s="2">
-        <v>46076.510104166664</v>
+        <v>46073.372488425928</v>
       </c>
       <c r="C30">
-        <v>62970260</v>
+        <v>61980847</v>
       </c>
       <c r="D30" s="2">
-        <v>46150.654166666667</v>
+        <v>46133.487384259257</v>
       </c>
       <c r="E30" t="s">
-        <v>193</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G30">
-        <v>102224907</v>
+        <v>759250737</v>
       </c>
       <c r="H30" t="s">
-        <v>164</v>
+        <v>25</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
@@ -2911,51 +2844,51 @@
         <v>18</v>
       </c>
       <c r="K30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L30" t="s">
         <v>8</v>
       </c>
       <c r="M30" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N30" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O30" t="s">
         <v>0</v>
       </c>
       <c r="P30" s="1">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="Q30" t="s">
-        <v>172</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>58856498</v>
+        <v>58797846</v>
       </c>
       <c r="B31" s="2">
-        <v>46077.418171296296</v>
+        <v>46076.510104166664</v>
       </c>
       <c r="C31">
-        <v>60800011</v>
+        <v>63198672</v>
       </c>
       <c r="D31" s="2">
-        <v>46112.393784722219</v>
+        <v>46155.408773148149</v>
       </c>
       <c r="E31" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G31">
-        <v>748377555</v>
+        <v>102224907</v>
       </c>
       <c r="H31" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="I31" t="s">
         <v>0</v>
@@ -2964,57 +2897,57 @@
         <v>18</v>
       </c>
       <c r="K31" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L31" t="s">
         <v>8</v>
       </c>
       <c r="M31" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N31" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O31" t="s">
         <v>0</v>
       </c>
-      <c r="P31" t="s">
-        <v>0</v>
+      <c r="P31" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q31" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>58860538</v>
+        <v>58856498</v>
       </c>
       <c r="B32" s="2">
-        <v>46077.446666666663</v>
+        <v>46077.418171296296</v>
       </c>
       <c r="C32">
-        <v>62950864</v>
+        <v>60800011</v>
       </c>
       <c r="D32" s="2">
-        <v>46150.491238425922</v>
+        <v>46112.393784722219</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="F32" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G32">
         <v>748377555</v>
       </c>
       <c r="H32" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="I32" t="s">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K32" t="s">
         <v>5</v>
@@ -3023,51 +2956,51 @@
         <v>8</v>
       </c>
       <c r="M32" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N32" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O32" t="s">
         <v>0</v>
       </c>
-      <c r="P32" s="1">
-        <v>5324000</v>
+      <c r="P32" t="s">
+        <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>58868849</v>
+        <v>58860538</v>
       </c>
       <c r="B33" s="2">
-        <v>46077.501203703701</v>
+        <v>46077.446666666663</v>
       </c>
       <c r="C33">
-        <v>62104932</v>
+        <v>62950864</v>
       </c>
       <c r="D33" s="2">
-        <v>46135.396608796298</v>
+        <v>46150.491238425922</v>
       </c>
       <c r="E33" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G33">
         <v>748377555</v>
       </c>
       <c r="H33" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="I33" t="s">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
@@ -3076,63 +3009,63 @@
         <v>8</v>
       </c>
       <c r="M33" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N33" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O33" t="s">
         <v>0</v>
       </c>
-      <c r="P33" t="s">
-        <v>0</v>
+      <c r="P33" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q33" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>58925987</v>
+        <v>58868849</v>
       </c>
       <c r="B34" s="2">
-        <v>46078.434814814813</v>
+        <v>46077.501203703701</v>
       </c>
       <c r="C34">
-        <v>60163873</v>
+        <v>62104932</v>
       </c>
       <c r="D34" s="2">
-        <v>46100.423101851855</v>
+        <v>46135.396608796298</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="F34" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="G34">
-        <v>708641473</v>
+        <v>748377555</v>
       </c>
       <c r="H34" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="I34" t="s">
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K34" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L34" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M34" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N34" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O34" t="s">
         <v>0</v>
@@ -3141,86 +3074,86 @@
         <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>58959238</v>
+        <v>58925987</v>
       </c>
       <c r="B35" s="2">
-        <v>46078.665532407409</v>
+        <v>46078.434814814813</v>
       </c>
       <c r="C35">
-        <v>60163938</v>
+        <v>60163873</v>
       </c>
       <c r="D35" s="2">
-        <v>46100.423773148148</v>
+        <v>46100.423101851855</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G35">
         <v>708641473</v>
       </c>
       <c r="H35" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I35" t="s">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K35" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M35" t="s">
         <v>3</v>
       </c>
       <c r="N35" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O35" t="s">
         <v>0</v>
       </c>
-      <c r="P35" s="1">
-        <v>850000</v>
+      <c r="P35" t="s">
+        <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>58963630</v>
+        <v>58959238</v>
       </c>
       <c r="B36" s="2">
-        <v>46078.697002314817</v>
+        <v>46078.665532407409</v>
       </c>
       <c r="C36">
-        <v>62956098</v>
+        <v>60163938</v>
       </c>
       <c r="D36" s="2">
-        <v>46150.531597222223</v>
+        <v>46100.423773148148</v>
       </c>
       <c r="E36" t="s">
-        <v>261</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="G36">
-        <v>747726344</v>
+        <v>708641473</v>
       </c>
       <c r="H36" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I36" t="s">
         <v>0</v>
@@ -3229,42 +3162,42 @@
         <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L36" t="s">
         <v>6</v>
       </c>
       <c r="M36" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N36" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O36" t="s">
         <v>0</v>
       </c>
-      <c r="P36" t="s">
-        <v>0</v>
+      <c r="P36" s="1">
+        <v>850000</v>
       </c>
       <c r="Q36" t="s">
-        <v>263</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>58963646</v>
+        <v>58963630</v>
       </c>
       <c r="B37" s="2">
-        <v>46078.697048611109</v>
+        <v>46078.697002314817</v>
       </c>
       <c r="C37">
-        <v>61620936</v>
+        <v>63173571</v>
       </c>
       <c r="D37" s="2">
-        <v>46127.58321759259</v>
+        <v>46154.68545138889</v>
       </c>
       <c r="E37" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="F37" t="s">
         <v>40</v>
@@ -3273,7 +3206,7 @@
         <v>747726344</v>
       </c>
       <c r="H37" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I37" t="s">
         <v>0</v>
@@ -3288,63 +3221,63 @@
         <v>6</v>
       </c>
       <c r="M37" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N37" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O37" t="s">
         <v>0</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="s">
         <v>0</v>
       </c>
       <c r="Q37" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>59406146</v>
+        <v>58963646</v>
       </c>
       <c r="B38" s="2">
-        <v>46086.506643518522</v>
+        <v>46078.697048611109</v>
       </c>
       <c r="C38">
-        <v>62770245</v>
+        <v>61620936</v>
       </c>
       <c r="D38" s="2">
-        <v>46147.6247337963</v>
+        <v>46127.58321759259</v>
       </c>
       <c r="E38" t="s">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="F38" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="G38">
-        <v>709136702</v>
+        <v>747726344</v>
       </c>
       <c r="H38" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="I38" t="s">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="K38" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L38" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M38" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N38" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O38" t="s">
         <v>0</v>
@@ -3353,92 +3286,92 @@
         <v>0</v>
       </c>
       <c r="Q38" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>59410212</v>
+        <v>59466514</v>
       </c>
       <c r="B39" s="2">
-        <v>46086.537708333337</v>
+        <v>46087.436643518522</v>
       </c>
       <c r="C39">
-        <v>61919232</v>
+        <v>63070473</v>
       </c>
       <c r="D39" s="2">
-        <v>46132.511064814818</v>
+        <v>46153.32271990741</v>
       </c>
       <c r="E39" t="s">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="F39" t="s">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="G39">
-        <v>789018789</v>
+        <v>141679210</v>
       </c>
       <c r="H39" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="I39" t="s">
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="K39" t="s">
-        <v>133</v>
+        <v>9</v>
       </c>
       <c r="L39" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M39" t="s">
         <v>7</v>
       </c>
       <c r="N39" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O39" t="s">
         <v>0</v>
       </c>
-      <c r="P39" t="s">
-        <v>0</v>
+      <c r="P39" s="1">
+        <v>3213390</v>
       </c>
       <c r="Q39" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>59410843</v>
+        <v>59480507</v>
       </c>
       <c r="B40" s="2">
-        <v>46086.542870370373</v>
+        <v>46087.544247685182</v>
       </c>
       <c r="C40">
-        <v>60526566</v>
+        <v>63178769</v>
       </c>
       <c r="D40" s="2">
-        <v>46107.452592592592</v>
+        <v>46154.730057870373</v>
       </c>
       <c r="E40" t="s">
-        <v>167</v>
+        <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G40">
-        <v>758700193</v>
+        <v>708547070</v>
       </c>
       <c r="H40" t="s">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="I40" t="s">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K40" t="s">
         <v>1</v>
@@ -3450,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="N40" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O40" t="s">
         <v>0</v>
@@ -3458,105 +3391,105 @@
       <c r="P40" t="s">
         <v>0</v>
       </c>
-      <c r="Q40" t="s">
-        <v>166</v>
+      <c r="Q40">
+        <v>2721712020</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>59414411</v>
+        <v>59537755</v>
       </c>
       <c r="B41" s="2">
-        <v>46086.57104166667</v>
+        <v>46088.586631944447</v>
       </c>
       <c r="C41">
-        <v>62768149</v>
+        <v>61591841</v>
       </c>
       <c r="D41" s="2">
-        <v>46147.610937500001</v>
+        <v>46127.35796296296</v>
       </c>
       <c r="E41" t="s">
+        <v>95</v>
+      </c>
+      <c r="F41" t="s">
+        <v>167</v>
+      </c>
+      <c r="G41">
+        <v>556331131</v>
+      </c>
+      <c r="H41" t="s">
+        <v>149</v>
+      </c>
+      <c r="I41">
+        <v>1843236</v>
+      </c>
+      <c r="J41" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" t="s">
+        <v>129</v>
+      </c>
+      <c r="L41" t="s">
+        <v>6</v>
+      </c>
+      <c r="M41" t="s">
+        <v>7</v>
+      </c>
+      <c r="N41" t="s">
+        <v>123</v>
+      </c>
+      <c r="O41" t="s">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="s">
         <v>168</v>
-      </c>
-      <c r="F41" t="s">
-        <v>136</v>
-      </c>
-      <c r="G41">
-        <v>566473307</v>
-      </c>
-      <c r="H41" t="s">
-        <v>137</v>
-      </c>
-      <c r="I41" t="s">
-        <v>0</v>
-      </c>
-      <c r="J41" t="s">
-        <v>70</v>
-      </c>
-      <c r="K41" t="s">
-        <v>1</v>
-      </c>
-      <c r="L41" t="s">
-        <v>2</v>
-      </c>
-      <c r="M41" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" t="s">
-        <v>126</v>
-      </c>
-      <c r="O41" t="s">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>59417066</v>
+        <v>59541145</v>
       </c>
       <c r="B42" s="2">
-        <v>46086.594525462962</v>
+        <v>46088.634837962964</v>
       </c>
       <c r="C42">
-        <v>62770091</v>
+        <v>63179943</v>
       </c>
       <c r="D42" s="2">
-        <v>46147.623831018522</v>
+        <v>46154.7421412037</v>
       </c>
       <c r="E42" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F42" t="s">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="G42">
-        <v>709565662</v>
+        <v>546008131</v>
       </c>
       <c r="H42" t="s">
-        <v>139</v>
+        <v>263</v>
       </c>
       <c r="I42" t="s">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="K42" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L42" t="s">
-        <v>2</v>
+        <v>192</v>
       </c>
       <c r="M42" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N42" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O42" t="s">
         <v>0</v>
@@ -3565,42 +3498,42 @@
         <v>0</v>
       </c>
       <c r="Q42" t="s">
-        <v>116</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>59465071</v>
+        <v>59606122</v>
       </c>
       <c r="B43" s="2">
-        <v>46087.424062500002</v>
+        <v>46090.447604166664</v>
       </c>
       <c r="C43">
-        <v>60531474</v>
+        <v>61897702</v>
       </c>
       <c r="D43" s="2">
-        <v>46107.489861111113</v>
+        <v>46132.349363425928</v>
       </c>
       <c r="E43" t="s">
-        <v>167</v>
+        <v>95</v>
       </c>
       <c r="F43" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="G43">
-        <v>554235979</v>
+        <v>708454305</v>
       </c>
       <c r="H43" t="s">
-        <v>140</v>
-      </c>
-      <c r="I43" t="s">
-        <v>0</v>
+        <v>169</v>
+      </c>
+      <c r="I43">
+        <v>1842206</v>
       </c>
       <c r="J43" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K43" t="s">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="L43" t="s">
         <v>6</v>
@@ -3609,7 +3542,7 @@
         <v>7</v>
       </c>
       <c r="N43" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O43" t="s">
         <v>0</v>
@@ -3618,33 +3551,33 @@
         <v>0</v>
       </c>
       <c r="Q43" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>59466514</v>
+        <v>59615935</v>
       </c>
       <c r="B44" s="2">
-        <v>46087.436643518522</v>
+        <v>46090.512303240743</v>
       </c>
       <c r="C44">
-        <v>63070473</v>
+        <v>60393405</v>
       </c>
       <c r="D44" s="2">
-        <v>46153.32271990741</v>
+        <v>46105.432800925926</v>
       </c>
       <c r="E44" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>264</v>
+        <v>131</v>
       </c>
       <c r="G44">
-        <v>141679210</v>
+        <v>767081456</v>
       </c>
       <c r="H44" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="I44" t="s">
         <v>0</v>
@@ -3653,69 +3586,69 @@
         <v>13</v>
       </c>
       <c r="K44" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L44" t="s">
         <v>6</v>
       </c>
       <c r="M44" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N44" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O44" t="s">
         <v>0</v>
       </c>
-      <c r="P44" s="1">
-        <v>3213390</v>
+      <c r="P44">
+        <v>0</v>
       </c>
       <c r="Q44" t="s">
-        <v>223</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>59480507</v>
+        <v>59684312</v>
       </c>
       <c r="B45" s="2">
-        <v>46087.544247685182</v>
+        <v>46091.557453703703</v>
       </c>
       <c r="C45">
-        <v>62965526</v>
+        <v>63202931</v>
       </c>
       <c r="D45" s="2">
-        <v>46150.615069444444</v>
+        <v>46155.444965277777</v>
       </c>
       <c r="E45" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="F45" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G45">
-        <v>708547070</v>
+        <v>3130227350</v>
       </c>
       <c r="H45" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="I45" t="s">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K45" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L45" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M45" t="s">
         <v>3</v>
       </c>
       <c r="N45" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O45" t="s">
         <v>0</v>
@@ -3723,34 +3656,34 @@
       <c r="P45" t="s">
         <v>0</v>
       </c>
-      <c r="Q45">
-        <v>2721712020</v>
+      <c r="Q45" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>59495473</v>
+        <v>59894743</v>
       </c>
       <c r="B46" s="2">
-        <v>46087.653935185182</v>
+        <v>46094.687673611108</v>
       </c>
       <c r="C46">
-        <v>62171071</v>
+        <v>63114345</v>
       </c>
       <c r="D46" s="2">
-        <v>46136.426828703705</v>
+        <v>46153.703321759262</v>
       </c>
       <c r="E46" t="s">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="F46" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G46">
-        <v>506727287</v>
+        <v>759668146</v>
       </c>
       <c r="H46" t="s">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="I46" t="s">
         <v>0</v>
@@ -3759,7 +3692,7 @@
         <v>13</v>
       </c>
       <c r="K46" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L46" t="s">
         <v>6</v>
@@ -3768,51 +3701,51 @@
         <v>7</v>
       </c>
       <c r="N46" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O46" t="s">
         <v>0</v>
       </c>
-      <c r="P46">
+      <c r="P46" t="s">
         <v>0</v>
       </c>
       <c r="Q46" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>59537755</v>
+        <v>60026486</v>
       </c>
       <c r="B47" s="2">
-        <v>46088.586631944447</v>
+        <v>46098.36173611111</v>
       </c>
       <c r="C47">
-        <v>61591841</v>
+        <v>63232663</v>
       </c>
       <c r="D47" s="2">
-        <v>46127.35796296296</v>
+        <v>46155.672986111109</v>
       </c>
       <c r="E47" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>197</v>
+        <v>135</v>
       </c>
       <c r="G47">
-        <v>556331131</v>
+        <v>506727287</v>
       </c>
       <c r="H47" t="s">
-        <v>173</v>
-      </c>
-      <c r="I47">
-        <v>1843236</v>
+        <v>57</v>
+      </c>
+      <c r="I47" t="s">
+        <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K47" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="L47" t="s">
         <v>6</v>
@@ -3821,7 +3754,7 @@
         <v>7</v>
       </c>
       <c r="N47" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O47" t="s">
         <v>0</v>
@@ -3830,95 +3763,95 @@
         <v>0</v>
       </c>
       <c r="Q47" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>59541145</v>
+        <v>60356605</v>
       </c>
       <c r="B48" s="2">
-        <v>46088.634837962964</v>
+        <v>46104.623726851853</v>
       </c>
       <c r="C48">
-        <v>62943001</v>
+        <v>63216655</v>
       </c>
       <c r="D48" s="2">
-        <v>46150.432847222219</v>
+        <v>46155.55027777778</v>
       </c>
       <c r="E48" t="s">
-        <v>261</v>
+        <v>61</v>
       </c>
       <c r="F48" t="s">
-        <v>265</v>
+        <v>138</v>
       </c>
       <c r="G48">
-        <v>546008131</v>
+        <v>504001081</v>
       </c>
       <c r="H48" t="s">
-        <v>266</v>
-      </c>
-      <c r="I48">
-        <v>1842216</v>
+        <v>139</v>
+      </c>
+      <c r="I48" t="s">
+        <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K48" t="s">
         <v>9</v>
       </c>
       <c r="L48" t="s">
-        <v>224</v>
+        <v>6</v>
       </c>
       <c r="M48" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="N48" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O48" t="s">
         <v>0</v>
       </c>
-      <c r="P48">
-        <v>0</v>
+      <c r="P48" t="s">
+        <v>140</v>
       </c>
       <c r="Q48" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>59606122</v>
+        <v>60748674</v>
       </c>
       <c r="B49" s="2">
-        <v>46090.447604166664</v>
+        <v>46111.511504629627</v>
       </c>
       <c r="C49">
-        <v>61897702</v>
+        <v>62475433</v>
       </c>
       <c r="D49" s="2">
-        <v>46132.349363425928</v>
+        <v>46141.624513888892</v>
       </c>
       <c r="E49" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
         <v>145</v>
       </c>
       <c r="G49">
-        <v>708454305</v>
+        <v>767791237</v>
       </c>
       <c r="H49" t="s">
-        <v>199</v>
-      </c>
-      <c r="I49">
-        <v>1842206</v>
+        <v>146</v>
+      </c>
+      <c r="I49" t="s">
+        <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K49" t="s">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="L49" t="s">
         <v>6</v>
@@ -3927,7 +3860,7 @@
         <v>7</v>
       </c>
       <c r="N49" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O49" t="s">
         <v>0</v>
@@ -3936,86 +3869,86 @@
         <v>0</v>
       </c>
       <c r="Q49" t="s">
-        <v>200</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>59615935</v>
+        <v>60972166</v>
       </c>
       <c r="B50" s="2">
-        <v>46090.512303240743</v>
+        <v>46114.708020833335</v>
       </c>
       <c r="C50">
-        <v>60393405</v>
+        <v>62949578</v>
       </c>
       <c r="D50" s="2">
-        <v>46105.432800925926</v>
+        <v>46150.482407407406</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G50">
-        <v>767081456</v>
+        <v>160128782</v>
       </c>
       <c r="H50" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I50" t="s">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
       </c>
       <c r="L50" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M50" t="s">
         <v>3</v>
       </c>
       <c r="N50" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O50" t="s">
         <v>0</v>
       </c>
-      <c r="P50">
-        <v>0</v>
+      <c r="P50" s="1">
+        <v>800000</v>
       </c>
       <c r="Q50" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>59684312</v>
+        <v>61220160</v>
       </c>
       <c r="B51" s="2">
-        <v>46091.557453703703</v>
+        <v>46120.483368055553</v>
       </c>
       <c r="C51">
-        <v>61372120</v>
+        <v>63199072</v>
       </c>
       <c r="D51" s="2">
-        <v>46122.663078703707</v>
+        <v>46155.413194444445</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>190</v>
       </c>
       <c r="F51" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G51">
-        <v>3130227350</v>
+        <v>102571205</v>
       </c>
       <c r="H51" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I51" t="s">
         <v>0</v>
@@ -4033,13 +3966,13 @@
         <v>3</v>
       </c>
       <c r="N51" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O51" t="s">
         <v>0</v>
       </c>
-      <c r="P51" t="s">
-        <v>0</v>
+      <c r="P51" s="1">
+        <v>5000000</v>
       </c>
       <c r="Q51" t="s">
         <v>31</v>
@@ -4047,46 +3980,46 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>59793967</v>
+        <v>61239047</v>
       </c>
       <c r="B52" s="2">
-        <v>46093.406724537039</v>
+        <v>46120.622071759259</v>
       </c>
       <c r="C52">
-        <v>61919676</v>
+        <v>62739005</v>
       </c>
       <c r="D52" s="2">
-        <v>46132.513668981483</v>
+        <v>46147.407546296294</v>
       </c>
       <c r="E52" t="s">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="F52" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G52">
-        <v>506727287</v>
+        <v>103381121</v>
       </c>
       <c r="H52" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="I52" t="s">
         <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="K52" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L52" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M52" t="s">
         <v>7</v>
       </c>
       <c r="N52" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O52" t="s">
         <v>0</v>
@@ -4095,51 +4028,51 @@
         <v>0</v>
       </c>
       <c r="Q52" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>59813505</v>
+        <v>61240327</v>
       </c>
       <c r="B53" s="2">
-        <v>46093.557256944441</v>
+        <v>46120.631747685184</v>
       </c>
       <c r="C53">
-        <v>60137642</v>
+        <v>61667960</v>
       </c>
       <c r="D53" s="2">
-        <v>46099.71303240741</v>
+        <v>46128.415625000001</v>
       </c>
       <c r="E53" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G53">
-        <v>706727287</v>
+        <v>103381121</v>
       </c>
       <c r="H53" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I53" t="s">
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="K53" t="s">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="L53" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M53" t="s">
         <v>7</v>
       </c>
       <c r="N53" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O53" t="s">
         <v>0</v>
@@ -4148,104 +4081,104 @@
         <v>0</v>
       </c>
       <c r="Q53" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>59816396</v>
+        <v>61240462</v>
       </c>
       <c r="B54" s="2">
-        <v>46093.580590277779</v>
+        <v>46120.632835648146</v>
       </c>
       <c r="C54">
-        <v>60137506</v>
+        <v>62739244</v>
       </c>
       <c r="D54" s="2">
-        <v>46099.711053240739</v>
+        <v>46147.409062500003</v>
       </c>
       <c r="E54" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F54" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G54">
-        <v>506727287</v>
+        <v>769218598</v>
       </c>
       <c r="H54" t="s">
-        <v>160</v>
-      </c>
-      <c r="I54">
-        <v>1848446</v>
+        <v>78</v>
+      </c>
+      <c r="I54" t="s">
+        <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="K54" t="s">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="L54" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M54" t="s">
         <v>7</v>
       </c>
       <c r="N54" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O54" t="s">
         <v>0</v>
       </c>
-      <c r="P54">
+      <c r="P54" t="s">
         <v>0</v>
       </c>
       <c r="Q54" t="s">
-        <v>15</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>59820678</v>
+        <v>61242033</v>
       </c>
       <c r="B55" s="2">
-        <v>46093.612222222226</v>
+        <v>46120.643912037034</v>
       </c>
       <c r="C55">
-        <v>60208764</v>
+        <v>62945857</v>
       </c>
       <c r="D55" s="2">
-        <v>46100.766909722224</v>
+        <v>46150.456064814818</v>
       </c>
       <c r="E55" t="s">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G55">
-        <v>506727287</v>
+        <v>747636152</v>
       </c>
       <c r="H55" t="s">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="I55" t="s">
         <v>0</v>
       </c>
       <c r="J55" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="K55" t="s">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="L55" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M55" t="s">
         <v>7</v>
       </c>
       <c r="N55" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O55" t="s">
         <v>0</v>
@@ -4254,51 +4187,51 @@
         <v>0</v>
       </c>
       <c r="Q55" t="s">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>59824550</v>
+        <v>61243441</v>
       </c>
       <c r="B56" s="2">
-        <v>46093.6405787037</v>
+        <v>46120.652592592596</v>
       </c>
       <c r="C56">
-        <v>61172877</v>
+        <v>62945141</v>
       </c>
       <c r="D56" s="2">
-        <v>46119.586805555555</v>
+        <v>46150.449965277781</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G56">
-        <v>506727287</v>
+        <v>747636152</v>
       </c>
       <c r="H56" t="s">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="I56" t="s">
         <v>0</v>
       </c>
       <c r="J56" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="K56" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L56" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M56" t="s">
         <v>7</v>
       </c>
       <c r="N56" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O56" t="s">
         <v>0</v>
@@ -4307,51 +4240,51 @@
         <v>0</v>
       </c>
       <c r="Q56" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>59894743</v>
+        <v>61244524</v>
       </c>
       <c r="B57" s="2">
-        <v>46094.687673611108</v>
+        <v>46120.66065972222</v>
       </c>
       <c r="C57">
-        <v>62976769</v>
+        <v>62308856</v>
       </c>
       <c r="D57" s="2">
-        <v>46150.705763888887</v>
+        <v>46139.393194444441</v>
       </c>
       <c r="E57" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="F57" t="s">
         <v>158</v>
       </c>
       <c r="G57">
-        <v>759668146</v>
+        <v>757818829</v>
       </c>
       <c r="H57" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="I57" t="s">
         <v>0</v>
       </c>
       <c r="J57" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="K57" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L57" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M57" t="s">
         <v>7</v>
       </c>
       <c r="N57" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O57" t="s">
         <v>0</v>
@@ -4360,52 +4293,49 @@
         <v>0</v>
       </c>
       <c r="Q57" t="s">
-        <v>32</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>60026486</v>
+        <v>61248751</v>
       </c>
       <c r="B58" s="2">
-        <v>46098.36173611111</v>
+        <v>46120.692800925928</v>
       </c>
       <c r="C58">
-        <v>62742384</v>
+        <v>62775261</v>
       </c>
       <c r="D58" s="2">
-        <v>46147.43304398148</v>
+        <v>46147.656886574077</v>
       </c>
       <c r="E58" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F58" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G58">
-        <v>506727287</v>
+        <v>747636152</v>
       </c>
       <c r="H58" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="I58" t="s">
         <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="K58" t="s">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="L58" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M58" t="s">
         <v>7</v>
       </c>
-      <c r="N58" t="s">
-        <v>127</v>
-      </c>
       <c r="O58" t="s">
         <v>0</v>
       </c>
@@ -4413,33 +4343,33 @@
         <v>0</v>
       </c>
       <c r="Q58" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>60356605</v>
+        <v>61254924</v>
       </c>
       <c r="B59" s="2">
-        <v>46104.623726851853</v>
+        <v>46120.74763888889</v>
       </c>
       <c r="C59">
-        <v>63071030</v>
+        <v>63209008</v>
       </c>
       <c r="D59" s="2">
-        <v>46153.347731481481</v>
+        <v>46155.489004629628</v>
       </c>
       <c r="E59" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="F59" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G59">
-        <v>504001081</v>
+        <v>757818829</v>
       </c>
       <c r="H59" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="I59" t="s">
         <v>0</v>
@@ -4448,51 +4378,51 @@
         <v>13</v>
       </c>
       <c r="K59" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L59" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M59" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N59" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O59" t="s">
         <v>0</v>
       </c>
-      <c r="P59" t="s">
-        <v>163</v>
+      <c r="P59">
+        <v>0</v>
       </c>
       <c r="Q59" t="s">
-        <v>111</v>
+        <v>232</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>60748674</v>
+        <v>61255381</v>
       </c>
       <c r="B60" s="2">
-        <v>46111.511504629627</v>
+        <v>46120.752291666664</v>
       </c>
       <c r="C60">
-        <v>62475433</v>
+        <v>62970699</v>
       </c>
       <c r="D60" s="2">
-        <v>46141.624513888892</v>
+        <v>46150.658067129632</v>
       </c>
       <c r="E60" t="s">
-        <v>10</v>
+        <v>231</v>
       </c>
       <c r="F60" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="G60">
-        <v>767791237</v>
+        <v>757818829</v>
       </c>
       <c r="H60" t="s">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="I60" t="s">
         <v>0</v>
@@ -4504,13 +4434,13 @@
         <v>5</v>
       </c>
       <c r="L60" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M60" t="s">
         <v>7</v>
       </c>
       <c r="N60" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O60" t="s">
         <v>0</v>
@@ -4519,39 +4449,39 @@
         <v>0</v>
       </c>
       <c r="Q60" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>60972166</v>
+        <v>61255901</v>
       </c>
       <c r="B61" s="2">
-        <v>46114.708020833335</v>
+        <v>46120.75712962963</v>
       </c>
       <c r="C61">
-        <v>62949578</v>
+        <v>62951388</v>
       </c>
       <c r="D61" s="2">
-        <v>46150.482407407406</v>
+        <v>46150.494675925926</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
       </c>
       <c r="F61" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="G61">
-        <v>160128782</v>
+        <v>757818829</v>
       </c>
       <c r="H61" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="I61" t="s">
         <v>0</v>
       </c>
       <c r="J61" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K61" t="s">
         <v>5</v>
@@ -4560,316 +4490,316 @@
         <v>8</v>
       </c>
       <c r="M61" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N61" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O61" t="s">
         <v>0</v>
       </c>
-      <c r="P61" s="1">
-        <v>800000</v>
+      <c r="P61">
+        <v>0</v>
       </c>
       <c r="Q61" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>61220160</v>
+        <v>61315991</v>
       </c>
       <c r="B62" s="2">
-        <v>46120.483368055553</v>
+        <v>46121.743379629632</v>
       </c>
       <c r="C62">
-        <v>62977466</v>
+        <v>62807088</v>
       </c>
       <c r="D62" s="2">
-        <v>46150.711793981478</v>
+        <v>46148.392731481479</v>
       </c>
       <c r="E62" t="s">
-        <v>261</v>
+        <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="G62">
-        <v>102571205</v>
+        <v>778495680</v>
       </c>
       <c r="H62" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="I62" t="s">
         <v>0</v>
       </c>
       <c r="J62" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K62" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L62" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M62" t="s">
         <v>3</v>
       </c>
       <c r="N62" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O62" t="s">
         <v>0</v>
       </c>
-      <c r="P62" s="1">
-        <v>5000000</v>
+      <c r="P62" t="s">
+        <v>0</v>
       </c>
       <c r="Q62" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>61239047</v>
+        <v>61336527</v>
       </c>
       <c r="B63" s="2">
-        <v>46120.622071759259</v>
+        <v>46122.368761574071</v>
       </c>
       <c r="C63">
-        <v>62739005</v>
+        <v>62807025</v>
       </c>
       <c r="D63" s="2">
-        <v>46147.407546296294</v>
+        <v>46148.392222222225</v>
       </c>
       <c r="E63" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="G63">
-        <v>103381121</v>
+        <v>778495680</v>
       </c>
       <c r="H63" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="I63" t="s">
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="K63" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M63" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N63" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O63" t="s">
         <v>0</v>
       </c>
-      <c r="P63">
-        <v>0</v>
+      <c r="P63" s="1">
+        <v>1679940</v>
       </c>
       <c r="Q63" t="s">
-        <v>201</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>61240327</v>
+        <v>61481328</v>
       </c>
       <c r="B64" s="2">
-        <v>46120.631747685184</v>
+        <v>46125.483310185184</v>
       </c>
       <c r="C64">
-        <v>61667960</v>
+        <v>62173555</v>
       </c>
       <c r="D64" s="2">
-        <v>46128.415625000001</v>
+        <v>46136.44263888889</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="F64" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="G64">
-        <v>103381121</v>
+        <v>708448800</v>
       </c>
       <c r="H64" t="s">
-        <v>179</v>
-      </c>
-      <c r="I64" t="s">
-        <v>0</v>
+        <v>194</v>
+      </c>
+      <c r="I64">
+        <v>1891736</v>
       </c>
       <c r="J64" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M64" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N64" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O64" t="s">
         <v>0</v>
       </c>
-      <c r="P64">
-        <v>0</v>
+      <c r="P64" s="1">
+        <v>500000</v>
       </c>
       <c r="Q64" t="s">
-        <v>35</v>
+        <v>195</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>61240462</v>
+        <v>61504448</v>
       </c>
       <c r="B65" s="2">
-        <v>46120.632835648146</v>
+        <v>46125.648935185185</v>
       </c>
       <c r="C65">
-        <v>62739244</v>
+        <v>62115179</v>
       </c>
       <c r="D65" s="2">
-        <v>46147.409062500003</v>
+        <v>46135.481111111112</v>
       </c>
       <c r="E65" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G65">
-        <v>769218598</v>
+        <v>707234610</v>
       </c>
       <c r="H65" t="s">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="I65" t="s">
         <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="K65" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="L65" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M65" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N65" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O65" t="s">
         <v>0</v>
       </c>
-      <c r="P65" t="s">
-        <v>0</v>
+      <c r="P65" s="1">
+        <v>3070672</v>
       </c>
       <c r="Q65" t="s">
-        <v>202</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>61242033</v>
+        <v>61507701</v>
       </c>
       <c r="B66" s="2">
-        <v>46120.643912037034</v>
+        <v>46125.672951388886</v>
       </c>
       <c r="C66">
-        <v>62945857</v>
+        <v>62020006</v>
       </c>
       <c r="D66" s="2">
-        <v>46150.456064814818</v>
+        <v>46133.777349537035</v>
       </c>
       <c r="E66" t="s">
-        <v>10</v>
+        <v>258</v>
       </c>
       <c r="F66" t="s">
-        <v>181</v>
+        <v>265</v>
       </c>
       <c r="G66">
-        <v>747636152</v>
+        <v>707906003</v>
       </c>
       <c r="H66" t="s">
-        <v>96</v>
+        <v>266</v>
       </c>
       <c r="I66" t="s">
         <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="K66" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L66" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M66" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N66" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O66" t="s">
         <v>0</v>
       </c>
-      <c r="P66">
-        <v>0</v>
+      <c r="P66" s="1">
+        <v>596888</v>
       </c>
       <c r="Q66" t="s">
-        <v>111</v>
+        <v>267</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>61243441</v>
+        <v>61509953</v>
       </c>
       <c r="B67" s="2">
-        <v>46120.652592592596</v>
+        <v>46125.694004629629</v>
       </c>
       <c r="C67">
-        <v>62945141</v>
+        <v>62751418</v>
       </c>
       <c r="D67" s="2">
-        <v>46150.449965277781</v>
+        <v>46147.490636574075</v>
       </c>
       <c r="E67" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="F67" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G67">
-        <v>747636152</v>
+        <v>759379440</v>
       </c>
       <c r="H67" t="s">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="I67" t="s">
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K67" t="s">
         <v>1</v>
@@ -4878,116 +4808,116 @@
         <v>2</v>
       </c>
       <c r="M67" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N67" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O67" t="s">
         <v>0</v>
       </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>32</v>
+      <c r="P67" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>2732780110</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>61243727</v>
+        <v>61560663</v>
       </c>
       <c r="B68" s="2">
-        <v>46120.654999999999</v>
+        <v>46126.615729166668</v>
       </c>
       <c r="C68">
-        <v>61661110</v>
+        <v>62946623</v>
       </c>
       <c r="D68" s="2">
-        <v>46128.349027777775</v>
+        <v>46150.461550925924</v>
       </c>
       <c r="E68" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
       <c r="F68" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="G68">
-        <v>707974053</v>
+        <v>707984429</v>
       </c>
       <c r="H68" t="s">
-        <v>183</v>
+        <v>97</v>
       </c>
       <c r="I68" t="s">
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
       </c>
       <c r="L68" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M68" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N68" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O68" t="s">
         <v>0</v>
       </c>
-      <c r="P68">
-        <v>0</v>
+      <c r="P68" s="1">
+        <v>2984038</v>
       </c>
       <c r="Q68" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>61244524</v>
+        <v>61608637</v>
       </c>
       <c r="B69" s="2">
-        <v>46120.66065972222</v>
+        <v>46127.491550925923</v>
       </c>
       <c r="C69">
-        <v>62308856</v>
+        <v>61677257</v>
       </c>
       <c r="D69" s="2">
-        <v>46139.393194444441</v>
+        <v>46128.483958333331</v>
       </c>
       <c r="E69" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="F69" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G69">
-        <v>757818829</v>
+        <v>702455701</v>
       </c>
       <c r="H69" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="I69" t="s">
         <v>0</v>
       </c>
       <c r="J69" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K69" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L69" t="s">
         <v>2</v>
       </c>
       <c r="M69" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N69" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O69" t="s">
         <v>0</v>
@@ -4996,295 +4926,298 @@
         <v>0</v>
       </c>
       <c r="Q69" t="s">
-        <v>203</v>
+        <v>126</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>61248751</v>
+        <v>61644382</v>
       </c>
       <c r="B70" s="2">
-        <v>46120.692800925928</v>
+        <v>46127.754131944443</v>
       </c>
       <c r="C70">
-        <v>62775261</v>
+        <v>61977733</v>
       </c>
       <c r="D70" s="2">
-        <v>46147.656886574077</v>
+        <v>46133.466458333336</v>
       </c>
       <c r="E70" t="s">
-        <v>269</v>
+        <v>16</v>
       </c>
       <c r="F70" t="s">
+        <v>105</v>
+      </c>
+      <c r="G70">
+        <v>759250737</v>
+      </c>
+      <c r="H70" t="s">
+        <v>180</v>
+      </c>
+      <c r="I70" t="s">
+        <v>0</v>
+      </c>
+      <c r="J70" t="s">
+        <v>18</v>
+      </c>
+      <c r="K70" t="s">
+        <v>9</v>
+      </c>
+      <c r="L70" t="s">
+        <v>8</v>
+      </c>
+      <c r="M70" t="s">
+        <v>3</v>
+      </c>
+      <c r="N70" t="s">
+        <v>123</v>
+      </c>
+      <c r="O70" t="s">
+        <v>0</v>
+      </c>
+      <c r="P70" s="1">
+        <v>1680307</v>
+      </c>
+      <c r="Q70" t="s">
         <v>181</v>
-      </c>
-      <c r="G70">
-        <v>747636152</v>
-      </c>
-      <c r="H70" t="s">
-        <v>124</v>
-      </c>
-      <c r="I70" t="s">
-        <v>0</v>
-      </c>
-      <c r="J70" t="s">
-        <v>70</v>
-      </c>
-      <c r="K70" t="s">
-        <v>1</v>
-      </c>
-      <c r="L70" t="s">
-        <v>2</v>
-      </c>
-      <c r="M70" t="s">
-        <v>7</v>
-      </c>
-      <c r="O70" t="s">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>61254924</v>
+        <v>61700587</v>
       </c>
       <c r="B71" s="2">
-        <v>46120.74763888889</v>
+        <v>46128.642256944448</v>
       </c>
       <c r="C71">
-        <v>63088332</v>
+        <v>63211249</v>
       </c>
       <c r="D71" s="2">
-        <v>46153.51059027778</v>
+        <v>46155.507719907408</v>
       </c>
       <c r="E71" t="s">
-        <v>261</v>
+        <v>61</v>
       </c>
       <c r="F71" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G71">
-        <v>757818829</v>
+        <v>747568798</v>
       </c>
       <c r="H71" t="s">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="I71" t="s">
         <v>0</v>
       </c>
       <c r="J71" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K71" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L71" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M71" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N71" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O71" t="s">
         <v>0</v>
       </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>270</v>
+      <c r="P71" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>2722419000</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>61255381</v>
+        <v>61702838</v>
       </c>
       <c r="B72" s="2">
-        <v>46120.752291666664</v>
+        <v>46128.658946759257</v>
       </c>
       <c r="C72">
-        <v>62970699</v>
+        <v>63177655</v>
       </c>
       <c r="D72" s="2">
-        <v>46150.658067129632</v>
+        <v>46154.719328703701</v>
       </c>
       <c r="E72" t="s">
-        <v>269</v>
+        <v>190</v>
       </c>
       <c r="F72" t="s">
+        <v>182</v>
+      </c>
+      <c r="G72">
+        <v>747568798</v>
+      </c>
+      <c r="H72" t="s">
         <v>184</v>
       </c>
-      <c r="G72">
-        <v>757818829</v>
-      </c>
-      <c r="H72" t="s">
-        <v>78</v>
-      </c>
       <c r="I72" t="s">
         <v>0</v>
       </c>
       <c r="J72" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K72" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L72" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M72" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N72" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O72" t="s">
         <v>0</v>
       </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>31</v>
+      <c r="P72" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>2734710371</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>61255901</v>
+        <v>61710072</v>
       </c>
       <c r="B73" s="2">
-        <v>46120.75712962963</v>
+        <v>46128.708032407405</v>
       </c>
       <c r="C73">
-        <v>62951388</v>
+        <v>62110207</v>
       </c>
       <c r="D73" s="2">
-        <v>46150.494675925926</v>
+        <v>46135.445254629631</v>
       </c>
       <c r="E73" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="F73" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G73">
-        <v>757818829</v>
+        <v>584425796</v>
       </c>
       <c r="H73" t="s">
-        <v>124</v>
-      </c>
-      <c r="I73" t="s">
+        <v>186</v>
+      </c>
+      <c r="I73">
         <v>0</v>
       </c>
       <c r="J73" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K73" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L73" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M73" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N73" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O73" t="s">
         <v>0</v>
       </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>77</v>
+      <c r="P73" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>2721711717</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>61315991</v>
+        <v>61828334</v>
       </c>
       <c r="B74" s="2">
-        <v>46121.743379629632</v>
+        <v>46130.562754629631</v>
       </c>
       <c r="C74">
-        <v>62807088</v>
+        <v>62208296</v>
       </c>
       <c r="D74" s="2">
-        <v>46148.392731481479</v>
+        <v>46136.716527777775</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="F74" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G74">
-        <v>778495680</v>
+        <v>747309803</v>
       </c>
       <c r="H74" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I74" t="s">
         <v>0</v>
       </c>
       <c r="J74" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K74" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L74" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M74" t="s">
         <v>3</v>
       </c>
       <c r="N74" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O74" t="s">
         <v>0</v>
       </c>
-      <c r="P74" t="s">
-        <v>0</v>
+      <c r="P74" s="1">
+        <v>1000000</v>
       </c>
       <c r="Q74" t="s">
-        <v>119</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>61336527</v>
+        <v>61946442</v>
       </c>
       <c r="B75" s="2">
-        <v>46122.368761574071</v>
+        <v>46132.704247685186</v>
       </c>
       <c r="C75">
-        <v>62807025</v>
+        <v>62946744</v>
       </c>
       <c r="D75" s="2">
-        <v>46148.392222222225</v>
+        <v>46150.462650462963</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G75">
-        <v>778495680</v>
+        <v>504041812</v>
       </c>
       <c r="H75" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="I75" t="s">
         <v>0</v>
@@ -5302,65 +5235,65 @@
         <v>3</v>
       </c>
       <c r="N75" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O75" t="s">
         <v>0</v>
       </c>
       <c r="P75" s="1">
-        <v>1679940</v>
+        <v>1000000</v>
       </c>
       <c r="Q75" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>61474571</v>
+        <v>61972088</v>
       </c>
       <c r="B76" s="2">
-        <v>46125.437488425923</v>
+        <v>46133.422569444447</v>
       </c>
       <c r="C76">
-        <v>62114470</v>
+        <v>62868217</v>
       </c>
       <c r="D76" s="2">
-        <v>46135.476550925923</v>
+        <v>46149.240729166668</v>
       </c>
       <c r="E76" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="F76" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="G76">
-        <v>707974053</v>
+        <v>504041812</v>
       </c>
       <c r="H76" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="I76" t="s">
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
       </c>
       <c r="L76" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M76" t="s">
         <v>7</v>
       </c>
       <c r="N76" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O76" t="s">
         <v>0</v>
       </c>
-      <c r="P76">
+      <c r="P76" t="s">
         <v>0</v>
       </c>
       <c r="Q76" t="s">
@@ -5369,81 +5302,81 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>61475299</v>
+        <v>61972108</v>
       </c>
       <c r="B77" s="2">
-        <v>46125.442372685182</v>
+        <v>46133.422662037039</v>
       </c>
       <c r="C77">
-        <v>62772255</v>
+        <v>62946845</v>
       </c>
       <c r="D77" s="2">
-        <v>46147.638368055559</v>
+        <v>46150.463449074072</v>
       </c>
       <c r="E77" t="s">
-        <v>168</v>
+        <v>10</v>
       </c>
       <c r="F77" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="G77">
-        <v>707974053</v>
+        <v>504041812</v>
       </c>
       <c r="H77" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="I77" t="s">
         <v>0</v>
       </c>
       <c r="J77" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
       </c>
       <c r="L77" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M77" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N77" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O77" t="s">
         <v>0</v>
       </c>
-      <c r="P77">
-        <v>0</v>
+      <c r="P77" s="1">
+        <v>1000000</v>
       </c>
       <c r="Q77" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>61475818</v>
+        <v>62014200</v>
       </c>
       <c r="B78" s="2">
-        <v>46125.445914351854</v>
+        <v>46133.721585648149</v>
       </c>
       <c r="C78">
-        <v>62772416</v>
+        <v>63198452</v>
       </c>
       <c r="D78" s="2">
-        <v>46147.639189814814</v>
+        <v>46155.40662037037</v>
       </c>
       <c r="E78" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="F78" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="G78">
-        <v>707974053</v>
+        <v>709837321</v>
       </c>
       <c r="H78" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="I78" t="s">
         <v>0</v>
@@ -5458,54 +5391,54 @@
         <v>6</v>
       </c>
       <c r="M78" t="s">
-        <v>7</v>
+        <v>178</v>
       </c>
       <c r="N78" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O78" t="s">
         <v>0</v>
       </c>
-      <c r="P78">
-        <v>0</v>
+      <c r="P78" s="1">
+        <v>1644000</v>
       </c>
       <c r="Q78" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>61481328</v>
+        <v>62170297</v>
       </c>
       <c r="B79" s="2">
-        <v>46125.483310185184</v>
+        <v>46136.420717592591</v>
       </c>
       <c r="C79">
-        <v>62173555</v>
+        <v>63207480</v>
       </c>
       <c r="D79" s="2">
-        <v>46136.44263888889</v>
+        <v>46155.47861111111</v>
       </c>
       <c r="E79" t="s">
-        <v>95</v>
+        <v>268</v>
       </c>
       <c r="F79" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G79">
-        <v>708448800</v>
+        <v>546016502</v>
       </c>
       <c r="H79" t="s">
-        <v>226</v>
-      </c>
-      <c r="I79">
-        <v>1891736</v>
+        <v>203</v>
+      </c>
+      <c r="I79" t="s">
+        <v>0</v>
       </c>
       <c r="J79" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K79" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L79" t="s">
         <v>8</v>
@@ -5514,42 +5447,42 @@
         <v>3</v>
       </c>
       <c r="N79" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O79" t="s">
         <v>0</v>
       </c>
       <c r="P79" s="1">
-        <v>500000</v>
+        <v>1500000</v>
       </c>
       <c r="Q79" t="s">
-        <v>227</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>61504448</v>
+        <v>62241651</v>
       </c>
       <c r="B80" s="2">
-        <v>46125.648935185185</v>
+        <v>46137.593402777777</v>
       </c>
       <c r="C80">
-        <v>62115179</v>
+        <v>63197022</v>
       </c>
       <c r="D80" s="2">
-        <v>46135.481111111112</v>
+        <v>46155.39166666667</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="F80" t="s">
         <v>204</v>
       </c>
       <c r="G80">
-        <v>707234610</v>
+        <v>707678205</v>
       </c>
       <c r="H80" t="s">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="I80" t="s">
         <v>0</v>
@@ -5567,254 +5500,254 @@
         <v>3</v>
       </c>
       <c r="N80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O80" t="s">
         <v>0</v>
       </c>
       <c r="P80" s="1">
-        <v>3070672</v>
+        <v>500000</v>
       </c>
       <c r="Q80" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>61509953</v>
+        <v>62243628</v>
       </c>
       <c r="B81" s="2">
-        <v>46125.694004629629</v>
+        <v>46137.617604166669</v>
       </c>
       <c r="C81">
-        <v>62751418</v>
+        <v>63197211</v>
       </c>
       <c r="D81" s="2">
-        <v>46147.490636574075</v>
+        <v>46155.393680555557</v>
       </c>
       <c r="E81" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="F81" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G81">
-        <v>759379440</v>
+        <v>779191985</v>
       </c>
       <c r="H81" t="s">
-        <v>207</v>
+        <v>269</v>
       </c>
       <c r="I81" t="s">
         <v>0</v>
       </c>
       <c r="J81" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K81" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L81" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M81" t="s">
         <v>3</v>
       </c>
       <c r="N81" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O81" t="s">
         <v>0</v>
       </c>
-      <c r="P81" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q81">
-        <v>2732780110</v>
+      <c r="P81" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>61560663</v>
+        <v>62249046</v>
       </c>
       <c r="B82" s="2">
-        <v>46126.615729166668</v>
+        <v>46137.688391203701</v>
       </c>
       <c r="C82">
-        <v>62946623</v>
+        <v>63174891</v>
       </c>
       <c r="D82" s="2">
-        <v>46150.461550925924</v>
+        <v>46154.695729166669</v>
       </c>
       <c r="E82" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="F82" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="G82">
-        <v>707984429</v>
+        <v>708946683</v>
       </c>
       <c r="H82" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="I82" t="s">
         <v>0</v>
       </c>
       <c r="J82" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K82" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L82" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M82" t="s">
         <v>3</v>
       </c>
       <c r="N82" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O82" t="s">
         <v>0</v>
       </c>
-      <c r="P82" s="1">
-        <v>2984038</v>
+      <c r="P82" t="s">
+        <v>0</v>
       </c>
       <c r="Q82" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>61608637</v>
+        <v>62420329</v>
       </c>
       <c r="B83" s="2">
-        <v>46127.491550925923</v>
+        <v>46140.709513888891</v>
       </c>
       <c r="C83">
-        <v>61677257</v>
+        <v>62868242</v>
       </c>
       <c r="D83" s="2">
-        <v>46128.483958333331</v>
+        <v>46149.243807870371</v>
       </c>
       <c r="E83" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G83">
-        <v>702455701</v>
+        <v>777621987</v>
       </c>
       <c r="H83" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="I83" t="s">
         <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K83" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L83" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M83" t="s">
         <v>3</v>
       </c>
       <c r="N83" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O83" t="s">
         <v>0</v>
       </c>
-      <c r="P83" t="s">
-        <v>0</v>
+      <c r="P83" s="1">
+        <v>1500000</v>
       </c>
       <c r="Q83" t="s">
-        <v>130</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>61620138</v>
+        <v>62497009</v>
       </c>
       <c r="B84" s="2">
-        <v>46127.578287037039</v>
+        <v>46141.808842592596</v>
       </c>
       <c r="C84">
-        <v>62163793</v>
+        <v>63232906</v>
       </c>
       <c r="D84" s="2">
-        <v>46136.340428240743</v>
+        <v>46155.674166666664</v>
       </c>
       <c r="E84" t="s">
-        <v>167</v>
+        <v>271</v>
       </c>
       <c r="F84" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G84">
-        <v>758051301</v>
+        <v>702495660</v>
       </c>
       <c r="H84" t="s">
-        <v>211</v>
+        <v>37</v>
       </c>
       <c r="I84" t="s">
         <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K84" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L84" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M84" t="s">
         <v>3</v>
       </c>
       <c r="N84" t="s">
-        <v>127</v>
+        <v>270</v>
       </c>
       <c r="O84" t="s">
         <v>0</v>
       </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="s">
-        <v>0</v>
+      <c r="P84" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>2722560060</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>61644382</v>
+        <v>62544794</v>
       </c>
       <c r="B85" s="2">
-        <v>46127.754131944443</v>
+        <v>46142.662094907406</v>
       </c>
       <c r="C85">
-        <v>61977733</v>
+        <v>63208263</v>
       </c>
       <c r="D85" s="2">
-        <v>46133.466458333336</v>
+        <v>46155.483206018522</v>
       </c>
       <c r="E85" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="F85" t="s">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="G85">
-        <v>759250737</v>
+        <v>142128888</v>
       </c>
       <c r="H85" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I85" t="s">
         <v>0</v>
@@ -5832,42 +5765,42 @@
         <v>3</v>
       </c>
       <c r="N85" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O85" t="s">
         <v>0</v>
       </c>
       <c r="P85" s="1">
-        <v>1680307</v>
+        <v>500000</v>
       </c>
       <c r="Q85" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>61700587</v>
+        <v>62551370</v>
       </c>
       <c r="B86" s="2">
-        <v>46128.642256944448</v>
+        <v>46142.717349537037</v>
       </c>
       <c r="C86">
-        <v>62975253</v>
+        <v>63134483</v>
       </c>
       <c r="D86" s="2">
-        <v>46150.696006944447</v>
+        <v>46154.380196759259</v>
       </c>
       <c r="E86" t="s">
-        <v>261</v>
+        <v>23</v>
       </c>
       <c r="F86" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G86">
-        <v>747568798</v>
+        <v>576382850</v>
       </c>
       <c r="H86" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I86" t="s">
         <v>0</v>
@@ -5876,7 +5809,7 @@
         <v>22</v>
       </c>
       <c r="K86" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L86" t="s">
         <v>2</v>
@@ -5884,61 +5817,58 @@
       <c r="M86" t="s">
         <v>3</v>
       </c>
-      <c r="N86" t="s">
-        <v>127</v>
-      </c>
       <c r="O86" t="s">
         <v>0</v>
       </c>
       <c r="P86" t="s">
         <v>0</v>
       </c>
-      <c r="Q86">
-        <v>2722419000</v>
+      <c r="Q86" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>61702838</v>
+        <v>62672227</v>
       </c>
       <c r="B87" s="2">
-        <v>46128.658946759257</v>
+        <v>46146.403935185182</v>
       </c>
       <c r="C87">
-        <v>62874984</v>
+        <v>63060135</v>
       </c>
       <c r="D87" s="2">
-        <v>46149.406423611108</v>
+        <v>46152.917256944442</v>
       </c>
       <c r="E87" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F87" t="s">
+        <v>213</v>
+      </c>
+      <c r="G87">
+        <v>707169322</v>
+      </c>
+      <c r="H87" t="s">
         <v>214</v>
       </c>
-      <c r="G87">
-        <v>747568798</v>
-      </c>
-      <c r="H87" t="s">
-        <v>216</v>
-      </c>
       <c r="I87" t="s">
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K87" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="L87" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M87" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N87" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O87" t="s">
         <v>0</v>
@@ -5946,211 +5876,211 @@
       <c r="P87" t="s">
         <v>0</v>
       </c>
-      <c r="Q87">
-        <v>2734710371</v>
+      <c r="Q87" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>61710072</v>
+        <v>62672234</v>
       </c>
       <c r="B88" s="2">
-        <v>46128.708032407405</v>
+        <v>46146.403969907406</v>
       </c>
       <c r="C88">
-        <v>62110207</v>
+        <v>63175077</v>
       </c>
       <c r="D88" s="2">
-        <v>46135.445254629631</v>
+        <v>46154.696747685186</v>
       </c>
       <c r="E88" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="F88" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G88">
-        <v>584425796</v>
+        <v>707169322</v>
       </c>
       <c r="H88" t="s">
-        <v>218</v>
-      </c>
-      <c r="I88">
+        <v>214</v>
+      </c>
+      <c r="I88" t="s">
         <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K88" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L88" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M88" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N88" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O88" t="s">
         <v>0</v>
       </c>
-      <c r="P88" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <v>2721711717</v>
+      <c r="P88" s="1">
+        <v>1644000</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>61828334</v>
+        <v>62680657</v>
       </c>
       <c r="B89" s="2">
-        <v>46130.562754629631</v>
+        <v>46146.475763888891</v>
       </c>
       <c r="C89">
-        <v>62208296</v>
+        <v>63209384</v>
       </c>
       <c r="D89" s="2">
-        <v>46136.716527777775</v>
+        <v>46155.492199074077</v>
       </c>
       <c r="E89" t="s">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="F89" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G89">
-        <v>747309803</v>
+        <v>778096389</v>
       </c>
       <c r="H89" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I89" t="s">
         <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="K89" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L89" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M89" t="s">
         <v>3</v>
       </c>
       <c r="N89" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O89" t="s">
         <v>0</v>
       </c>
-      <c r="P89" s="1">
-        <v>1000000</v>
+      <c r="P89" t="s">
+        <v>0</v>
       </c>
       <c r="Q89" t="s">
-        <v>228</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>61946442</v>
+        <v>62682536</v>
       </c>
       <c r="B90" s="2">
-        <v>46132.704247685186</v>
+        <v>46146.490057870367</v>
       </c>
       <c r="C90">
-        <v>62946744</v>
+        <v>63060102</v>
       </c>
       <c r="D90" s="2">
-        <v>46150.462650462963</v>
+        <v>46152.915081018517</v>
       </c>
       <c r="E90" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="G90">
-        <v>504041812</v>
+        <v>789817770</v>
       </c>
       <c r="H90" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="I90" t="s">
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K90" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M90" t="s">
         <v>3</v>
       </c>
       <c r="N90" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O90" t="s">
         <v>0</v>
       </c>
       <c r="P90" s="1">
-        <v>1000000</v>
+        <v>150000</v>
       </c>
       <c r="Q90" t="s">
-        <v>24</v>
+        <v>236</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>61972088</v>
+        <v>62715782</v>
       </c>
       <c r="B91" s="2">
-        <v>46133.422569444447</v>
+        <v>46146.73746527778</v>
       </c>
       <c r="C91">
-        <v>62868217</v>
+        <v>63177364</v>
       </c>
       <c r="D91" s="2">
-        <v>46149.240729166668</v>
+        <v>46154.716550925928</v>
       </c>
       <c r="E91" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="F91" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="G91">
-        <v>504041812</v>
+        <v>707366919</v>
       </c>
       <c r="H91" t="s">
-        <v>230</v>
+        <v>37</v>
       </c>
       <c r="I91" t="s">
         <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K91" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L91" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M91" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N91" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O91" t="s">
         <v>0</v>
@@ -6159,316 +6089,316 @@
         <v>0</v>
       </c>
       <c r="Q91" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>61972108</v>
+        <v>62722805</v>
       </c>
       <c r="B92" s="2">
-        <v>46133.422662037039</v>
+        <v>46146.81181712963</v>
       </c>
       <c r="C92">
-        <v>62946845</v>
+        <v>63060104</v>
       </c>
       <c r="D92" s="2">
-        <v>46150.463449074072</v>
+        <v>46152.916122685187</v>
       </c>
       <c r="E92" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F92" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="G92">
-        <v>504041812</v>
+        <v>708131488</v>
       </c>
       <c r="H92" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="I92" t="s">
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K92" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L92" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M92" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N92" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O92" t="s">
         <v>0</v>
       </c>
-      <c r="P92" s="1">
-        <v>1000000</v>
+      <c r="P92" t="s">
+        <v>0</v>
       </c>
       <c r="Q92" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>62014200</v>
+        <v>62748443</v>
       </c>
       <c r="B93" s="2">
-        <v>46133.721585648149</v>
+        <v>46147.475057870368</v>
       </c>
       <c r="C93">
-        <v>62170861</v>
+        <v>63118824</v>
       </c>
       <c r="D93" s="2">
-        <v>46136.425300925926</v>
+        <v>46153.739791666667</v>
       </c>
       <c r="E93" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="F93" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="G93">
-        <v>709837321</v>
+        <v>757750210</v>
       </c>
       <c r="H93" t="s">
-        <v>233</v>
+        <v>37</v>
       </c>
       <c r="I93" t="s">
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
       </c>
       <c r="L93" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M93" t="s">
-        <v>208</v>
+        <v>3</v>
       </c>
       <c r="N93" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O93" t="s">
         <v>0</v>
       </c>
-      <c r="P93" s="1">
-        <v>1644000</v>
+      <c r="P93">
+        <v>0</v>
       </c>
       <c r="Q93" t="s">
-        <v>31</v>
+        <v>237</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>62170297</v>
+        <v>62760027</v>
       </c>
       <c r="B94" s="2">
-        <v>46136.420717592591</v>
+        <v>46147.546493055554</v>
       </c>
       <c r="C94">
-        <v>62868231</v>
+        <v>62902869</v>
       </c>
       <c r="D94" s="2">
-        <v>46149.242083333331</v>
+        <v>46149.631921296299</v>
       </c>
       <c r="E94" t="s">
-        <v>19</v>
+        <v>143</v>
       </c>
       <c r="F94" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G94">
-        <v>546016502</v>
+        <v>777699799</v>
       </c>
       <c r="H94" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="I94" t="s">
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K94" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L94" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M94" t="s">
         <v>3</v>
       </c>
       <c r="N94" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O94" t="s">
         <v>0</v>
       </c>
-      <c r="P94" s="1">
-        <v>1500000</v>
+      <c r="P94" t="s">
+        <v>0</v>
       </c>
       <c r="Q94" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>62241651</v>
+        <v>62768013</v>
       </c>
       <c r="B95" s="2">
-        <v>46137.593402777777</v>
+        <v>46147.609988425924</v>
       </c>
       <c r="C95">
-        <v>62915074</v>
+        <v>62871386</v>
       </c>
       <c r="D95" s="2">
-        <v>46149.715150462966</v>
+        <v>46149.364837962959</v>
       </c>
       <c r="E95" t="s">
-        <v>261</v>
+        <v>143</v>
       </c>
       <c r="F95" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G95">
-        <v>707678205</v>
+        <v>143270405</v>
       </c>
       <c r="H95" t="s">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="I95" t="s">
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K95" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L95" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M95" t="s">
         <v>3</v>
       </c>
       <c r="N95" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O95" t="s">
         <v>0</v>
       </c>
-      <c r="P95" s="1">
-        <v>500000</v>
+      <c r="P95" t="s">
+        <v>0</v>
       </c>
       <c r="Q95" t="s">
-        <v>271</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>62243628</v>
+        <v>62840921</v>
       </c>
       <c r="B96" s="2">
-        <v>46137.617604166669</v>
+        <v>46148.636331018519</v>
       </c>
       <c r="C96">
-        <v>62916092</v>
+        <v>63101235</v>
       </c>
       <c r="D96" s="2">
-        <v>46149.721608796295</v>
+        <v>46153.608599537038</v>
       </c>
       <c r="E96" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="F96" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="G96">
-        <v>779191985</v>
+        <v>707551377</v>
       </c>
       <c r="H96" t="s">
-        <v>272</v>
-      </c>
-      <c r="I96">
-        <v>1894446</v>
+        <v>243</v>
+      </c>
+      <c r="I96" t="s">
+        <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K96" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L96" t="s">
         <v>6</v>
       </c>
       <c r="M96" t="s">
-        <v>257</v>
+        <v>3</v>
       </c>
       <c r="N96" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="O96" t="s">
         <v>0</v>
       </c>
-      <c r="P96" s="1">
-        <v>500000</v>
+      <c r="P96" t="s">
+        <v>0</v>
       </c>
       <c r="Q96" t="s">
-        <v>273</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>62249046</v>
+        <v>62880594</v>
       </c>
       <c r="B97" s="2">
-        <v>46137.688391203701</v>
+        <v>46149.454710648148</v>
       </c>
       <c r="C97">
-        <v>62868237</v>
+        <v>62941351</v>
       </c>
       <c r="D97" s="2">
-        <v>46149.242812500001</v>
+        <v>46150.416979166665</v>
       </c>
       <c r="E97" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F97" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="G97">
-        <v>708946683</v>
+        <v>709565662</v>
       </c>
       <c r="H97" t="s">
-        <v>37</v>
+        <v>246</v>
       </c>
       <c r="I97" t="s">
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K97" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L97" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M97" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N97" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O97" t="s">
         <v>0</v>
@@ -6477,86 +6407,86 @@
         <v>0</v>
       </c>
       <c r="Q97" t="s">
-        <v>130</v>
+        <v>247</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>62420329</v>
+        <v>62880628</v>
       </c>
       <c r="B98" s="2">
-        <v>46140.709513888891</v>
+        <v>46149.45484953704</v>
       </c>
       <c r="C98">
-        <v>62868242</v>
+        <v>62941416</v>
       </c>
       <c r="D98" s="2">
-        <v>46149.243807870371</v>
+        <v>46150.417719907404</v>
       </c>
       <c r="E98" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F98" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G98">
-        <v>777621987</v>
+        <v>709565662</v>
       </c>
       <c r="H98" t="s">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="I98" t="s">
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
       </c>
       <c r="L98" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M98" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N98" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O98" t="s">
         <v>0</v>
       </c>
-      <c r="P98" s="1">
-        <v>1500000</v>
+      <c r="P98">
+        <v>0</v>
       </c>
       <c r="Q98" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>62497009</v>
+        <v>62880812</v>
       </c>
       <c r="B99" s="2">
-        <v>46141.808842592596</v>
+        <v>46149.456157407411</v>
       </c>
       <c r="C99">
-        <v>63079092</v>
+        <v>63224093</v>
       </c>
       <c r="D99" s="2">
-        <v>46153.44425925926</v>
+        <v>46155.609270833331</v>
       </c>
       <c r="E99" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="F99" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="G99">
-        <v>702495660</v>
+        <v>707672487</v>
       </c>
       <c r="H99" t="s">
-        <v>37</v>
+        <v>249</v>
       </c>
       <c r="I99" t="s">
         <v>0</v>
@@ -6574,7 +6504,7 @@
         <v>3</v>
       </c>
       <c r="N99" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O99" t="s">
         <v>0</v>
@@ -6582,211 +6512,211 @@
       <c r="P99" t="s">
         <v>0</v>
       </c>
-      <c r="Q99">
-        <v>2722560060</v>
+      <c r="Q99" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>62544794</v>
+        <v>62937923</v>
       </c>
       <c r="B100" s="2">
-        <v>46142.662094907406</v>
+        <v>46150.381145833337</v>
       </c>
       <c r="C100">
-        <v>63079395</v>
+        <v>63214161</v>
       </c>
       <c r="D100" s="2">
-        <v>46153.446099537039</v>
+        <v>46155.526944444442</v>
       </c>
       <c r="E100" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="F100" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="G100">
-        <v>142128888</v>
+        <v>565811689</v>
       </c>
       <c r="H100" t="s">
-        <v>242</v>
+        <v>37</v>
       </c>
       <c r="I100" t="s">
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K100" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L100" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M100" t="s">
         <v>3</v>
       </c>
       <c r="N100" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O100" t="s">
         <v>0</v>
       </c>
       <c r="P100" s="1">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="Q100" t="s">
-        <v>275</v>
+        <v>31</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>62546484</v>
+        <v>62968196</v>
       </c>
       <c r="B101" s="2">
-        <v>46142.674293981479</v>
+        <v>46150.638715277775</v>
       </c>
       <c r="C101">
-        <v>63090853</v>
+        <v>63089942</v>
       </c>
       <c r="D101" s="2">
-        <v>46153.527557870373</v>
+        <v>46153.521840277775</v>
       </c>
       <c r="E101" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F101" t="s">
-        <v>29</v>
+        <v>251</v>
       </c>
       <c r="G101">
-        <v>768204550</v>
+        <v>758177759</v>
       </c>
       <c r="H101" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="I101" t="s">
         <v>0</v>
       </c>
       <c r="J101" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="K101" t="s">
         <v>5</v>
       </c>
       <c r="L101" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M101" t="s">
-        <v>3</v>
+        <v>178</v>
       </c>
       <c r="N101" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O101" t="s">
         <v>0</v>
       </c>
-      <c r="P101" t="s">
-        <v>0</v>
+      <c r="P101" s="1">
+        <v>2881416</v>
       </c>
       <c r="Q101" t="s">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>62551370</v>
+        <v>63025600</v>
       </c>
       <c r="B102" s="2">
-        <v>46142.717349537037</v>
+        <v>46151.740983796299</v>
       </c>
       <c r="C102">
-        <v>62899958</v>
+        <v>63092455</v>
       </c>
       <c r="D102" s="2">
-        <v>46149.608275462961</v>
+        <v>46153.539537037039</v>
       </c>
       <c r="E102" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="F102" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="G102">
-        <v>576382850</v>
+        <v>758237461</v>
       </c>
       <c r="H102" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I102" t="s">
         <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K102" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L102" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M102" t="s">
         <v>3</v>
       </c>
       <c r="N102" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O102" t="s">
         <v>0</v>
       </c>
-      <c r="P102" t="s">
-        <v>0</v>
+      <c r="P102" s="1">
+        <v>850000</v>
       </c>
       <c r="Q102" t="s">
-        <v>130</v>
+        <v>230</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>62672227</v>
+        <v>63073782</v>
       </c>
       <c r="B103" s="2">
-        <v>46146.403935185182</v>
+        <v>46153.387870370374</v>
       </c>
       <c r="C103">
-        <v>63060135</v>
+        <v>63115586</v>
       </c>
       <c r="D103" s="2">
-        <v>46152.917256944442</v>
+        <v>46153.713333333333</v>
       </c>
       <c r="E103" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="F103" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="G103">
-        <v>707169322</v>
+        <v>710619970</v>
       </c>
       <c r="H103" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="I103" t="s">
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K103" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L103" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M103" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N103" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O103" t="s">
         <v>0</v>
@@ -6795,33 +6725,33 @@
         <v>0</v>
       </c>
       <c r="Q103" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>62672234</v>
+        <v>63143165</v>
       </c>
       <c r="B104" s="2">
-        <v>46146.403969907406</v>
+        <v>46154.449884259258</v>
       </c>
       <c r="C104">
-        <v>63081306</v>
+        <v>63143198</v>
       </c>
       <c r="D104" s="2">
-        <v>46153.460995370369</v>
+        <v>46154.450150462966</v>
       </c>
       <c r="E104" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="F104" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="G104">
-        <v>707169322</v>
+        <v>708473548</v>
       </c>
       <c r="H104" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="I104" t="s">
         <v>0</v>
@@ -6830,983 +6760,240 @@
         <v>13</v>
       </c>
       <c r="K104" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L104" t="s">
         <v>6</v>
       </c>
       <c r="M104" t="s">
-        <v>14</v>
+        <v>178</v>
       </c>
       <c r="N104" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O104" t="s">
         <v>0</v>
       </c>
       <c r="P104" s="1">
-        <v>1644000</v>
+        <v>7837678</v>
       </c>
       <c r="Q104" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>62680657</v>
+        <v>63168095</v>
       </c>
       <c r="B105" s="2">
-        <v>46146.475763888891</v>
+        <v>46154.647604166668</v>
       </c>
       <c r="C105">
-        <v>62868238</v>
+        <v>63168477</v>
       </c>
       <c r="D105" s="2">
-        <v>46149.243171296293</v>
+        <v>46154.649652777778</v>
       </c>
       <c r="E105" t="s">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="F105" t="s">
-        <v>248</v>
+        <v>29</v>
       </c>
       <c r="G105">
-        <v>778096389</v>
+        <v>747345191</v>
       </c>
       <c r="H105" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="I105" t="s">
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="K105" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L105" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M105" t="s">
         <v>3</v>
       </c>
       <c r="N105" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O105" t="s">
         <v>0</v>
       </c>
-      <c r="P105" t="s">
-        <v>0</v>
+      <c r="P105" s="1">
+        <v>7103410</v>
       </c>
       <c r="Q105" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>62682536</v>
+        <v>63178332</v>
       </c>
       <c r="B106" s="2">
-        <v>46146.490057870367</v>
+        <v>46154.725729166668</v>
       </c>
       <c r="C106">
-        <v>63060102</v>
+        <v>63178359</v>
       </c>
       <c r="D106" s="2">
-        <v>46152.915081018517</v>
+        <v>46154.725960648146</v>
       </c>
       <c r="E106" t="s">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="F106" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="G106">
-        <v>789817770</v>
+        <v>708773097</v>
       </c>
       <c r="H106" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="I106" t="s">
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K106" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M106" t="s">
         <v>3</v>
       </c>
       <c r="N106" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O106" t="s">
         <v>0</v>
       </c>
       <c r="P106" s="1">
-        <v>150000</v>
+        <v>2000000</v>
       </c>
       <c r="Q106" t="s">
-        <v>276</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>62715782</v>
+        <v>63179342</v>
       </c>
       <c r="B107" s="2">
-        <v>46146.73746527778</v>
+        <v>46154.735729166663</v>
       </c>
       <c r="C107">
-        <v>63060166</v>
+        <v>63179372</v>
       </c>
       <c r="D107" s="2">
-        <v>46152.91978009259</v>
+        <v>46154.735960648148</v>
       </c>
       <c r="E107" t="s">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="F107" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="G107">
-        <v>707366919</v>
+        <v>778179203</v>
       </c>
       <c r="H107" t="s">
-        <v>37</v>
+        <v>280</v>
       </c>
       <c r="I107" t="s">
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K107" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L107" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M107" t="s">
         <v>3</v>
       </c>
       <c r="N107" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O107" t="s">
         <v>0</v>
       </c>
-      <c r="P107" t="s">
-        <v>0</v>
+      <c r="P107" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q107" t="s">
-        <v>130</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>62722805</v>
+        <v>63210811</v>
       </c>
       <c r="B108" s="2">
-        <v>46146.81181712963</v>
+        <v>46155.50409722222</v>
       </c>
       <c r="C108">
-        <v>63060104</v>
+        <v>63210839</v>
       </c>
       <c r="D108" s="2">
-        <v>46152.916122685187</v>
+        <v>46155.504328703704</v>
       </c>
       <c r="E108" t="s">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="F108" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="G108">
-        <v>708131488</v>
+        <v>160128782</v>
       </c>
       <c r="H108" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="I108" t="s">
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K108" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L108" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M108" t="s">
         <v>3</v>
       </c>
       <c r="N108" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O108" t="s">
         <v>0</v>
       </c>
-      <c r="P108" t="s">
-        <v>0</v>
+      <c r="P108" s="1">
+        <v>800000</v>
       </c>
       <c r="Q108" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A109">
-        <v>62742919</v>
-      </c>
-      <c r="B109" s="2">
-        <v>46147.438668981478</v>
-      </c>
-      <c r="C109">
-        <v>63078589</v>
-      </c>
-      <c r="D109" s="2">
-        <v>46153.438599537039</v>
-      </c>
-      <c r="E109" t="s">
-        <v>16</v>
-      </c>
-      <c r="F109" t="s">
-        <v>255</v>
-      </c>
-      <c r="G109">
-        <v>757750210</v>
-      </c>
-      <c r="H109" t="s">
-        <v>256</v>
-      </c>
-      <c r="I109" t="s">
-        <v>0</v>
-      </c>
-      <c r="J109" t="s">
-        <v>13</v>
-      </c>
-      <c r="K109" t="s">
-        <v>5</v>
-      </c>
-      <c r="L109" t="s">
-        <v>6</v>
-      </c>
-      <c r="M109" t="s">
-        <v>3</v>
-      </c>
-      <c r="N109" t="s">
-        <v>126</v>
-      </c>
-      <c r="O109" t="s">
-        <v>0</v>
-      </c>
-      <c r="P109">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A110">
-        <v>62746621</v>
-      </c>
-      <c r="B110" s="2">
-        <v>46147.463020833333</v>
-      </c>
-      <c r="C110">
-        <v>62900765</v>
-      </c>
-      <c r="D110" s="2">
-        <v>46149.615798611114</v>
-      </c>
-      <c r="E110" t="s">
-        <v>26</v>
-      </c>
-      <c r="F110" t="s">
-        <v>255</v>
-      </c>
-      <c r="G110">
-        <v>757750210</v>
-      </c>
-      <c r="H110" t="s">
-        <v>278</v>
-      </c>
-      <c r="I110">
-        <v>1941026</v>
-      </c>
-      <c r="J110" t="s">
-        <v>4</v>
-      </c>
-      <c r="K110" t="s">
-        <v>5</v>
-      </c>
-      <c r="L110" t="s">
-        <v>6</v>
-      </c>
-      <c r="M110" t="s">
-        <v>257</v>
-      </c>
-      <c r="N110" t="s">
-        <v>127</v>
-      </c>
-      <c r="O110" t="s">
-        <v>0</v>
-      </c>
-      <c r="P110">
-        <v>0</v>
-      </c>
-      <c r="Q110" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A111">
-        <v>62748443</v>
-      </c>
-      <c r="B111" s="2">
-        <v>46147.475057870368</v>
-      </c>
-      <c r="C111">
-        <v>62943615</v>
-      </c>
-      <c r="D111" s="2">
-        <v>46150.437337962961</v>
-      </c>
-      <c r="E111" t="s">
-        <v>61</v>
-      </c>
-      <c r="F111" t="s">
-        <v>255</v>
-      </c>
-      <c r="G111">
-        <v>757750210</v>
-      </c>
-      <c r="H111" t="s">
-        <v>37</v>
-      </c>
-      <c r="I111" t="s">
-        <v>0</v>
-      </c>
-      <c r="J111" t="s">
-        <v>18</v>
-      </c>
-      <c r="K111" t="s">
-        <v>5</v>
-      </c>
-      <c r="L111" t="s">
-        <v>8</v>
-      </c>
-      <c r="M111" t="s">
-        <v>3</v>
-      </c>
-      <c r="N111" t="s">
-        <v>126</v>
-      </c>
-      <c r="O111" t="s">
-        <v>0</v>
-      </c>
-      <c r="P111">
-        <v>0</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A112">
-        <v>62760027</v>
-      </c>
-      <c r="B112" s="2">
-        <v>46147.546493055554</v>
-      </c>
-      <c r="C112">
-        <v>62902869</v>
-      </c>
-      <c r="D112" s="2">
-        <v>46149.631921296299</v>
-      </c>
-      <c r="E112" t="s">
-        <v>167</v>
-      </c>
-      <c r="F112" t="s">
-        <v>281</v>
-      </c>
-      <c r="G112">
-        <v>777699799</v>
-      </c>
-      <c r="H112" t="s">
-        <v>282</v>
-      </c>
-      <c r="I112" t="s">
-        <v>0</v>
-      </c>
-      <c r="J112" t="s">
-        <v>22</v>
-      </c>
-      <c r="K112" t="s">
-        <v>1</v>
-      </c>
-      <c r="L112" t="s">
-        <v>2</v>
-      </c>
-      <c r="M112" t="s">
-        <v>3</v>
-      </c>
-      <c r="N112" t="s">
-        <v>127</v>
-      </c>
-      <c r="O112" t="s">
-        <v>0</v>
-      </c>
-      <c r="P112" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A113">
-        <v>62768013</v>
-      </c>
-      <c r="B113" s="2">
-        <v>46147.609988425924</v>
-      </c>
-      <c r="C113">
-        <v>62871386</v>
-      </c>
-      <c r="D113" s="2">
-        <v>46149.364837962959</v>
-      </c>
-      <c r="E113" t="s">
-        <v>167</v>
-      </c>
-      <c r="F113" t="s">
-        <v>283</v>
-      </c>
-      <c r="G113">
-        <v>143270405</v>
-      </c>
-      <c r="H113" t="s">
-        <v>284</v>
-      </c>
-      <c r="I113" t="s">
-        <v>0</v>
-      </c>
-      <c r="J113" t="s">
-        <v>18</v>
-      </c>
-      <c r="K113" t="s">
-        <v>1</v>
-      </c>
-      <c r="L113" t="s">
-        <v>8</v>
-      </c>
-      <c r="M113" t="s">
-        <v>3</v>
-      </c>
-      <c r="N113" t="s">
-        <v>127</v>
-      </c>
-      <c r="O113" t="s">
-        <v>0</v>
-      </c>
-      <c r="P113" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A114">
-        <v>62840921</v>
-      </c>
-      <c r="B114" s="2">
-        <v>46148.636331018519</v>
-      </c>
-      <c r="C114">
-        <v>62941498</v>
-      </c>
-      <c r="D114" s="2">
-        <v>46150.418506944443</v>
-      </c>
-      <c r="E114" t="s">
-        <v>16</v>
-      </c>
-      <c r="F114" t="s">
-        <v>285</v>
-      </c>
-      <c r="G114">
-        <v>707551377</v>
-      </c>
-      <c r="H114" t="s">
-        <v>286</v>
-      </c>
-      <c r="I114" t="s">
-        <v>0</v>
-      </c>
-      <c r="J114" t="s">
-        <v>13</v>
-      </c>
-      <c r="K114" t="s">
-        <v>5</v>
-      </c>
-      <c r="L114" t="s">
-        <v>6</v>
-      </c>
-      <c r="M114" t="s">
-        <v>3</v>
-      </c>
-      <c r="N114" t="s">
-        <v>127</v>
-      </c>
-      <c r="O114" t="s">
-        <v>0</v>
-      </c>
-      <c r="P114" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A115">
-        <v>62852675</v>
-      </c>
-      <c r="B115" s="2">
-        <v>46148.714444444442</v>
-      </c>
-      <c r="C115">
-        <v>63080215</v>
-      </c>
-      <c r="D115" s="2">
-        <v>46153.4528587963</v>
-      </c>
-      <c r="E115" t="s">
-        <v>269</v>
-      </c>
-      <c r="F115" t="s">
-        <v>288</v>
-      </c>
-      <c r="G115">
-        <v>777589587</v>
-      </c>
-      <c r="H115" t="s">
-        <v>289</v>
-      </c>
-      <c r="I115" t="s">
-        <v>0</v>
-      </c>
-      <c r="J115" t="s">
-        <v>13</v>
-      </c>
-      <c r="K115" t="s">
-        <v>5</v>
-      </c>
-      <c r="L115" t="s">
-        <v>6</v>
-      </c>
-      <c r="M115" t="s">
-        <v>208</v>
-      </c>
-      <c r="N115" t="s">
-        <v>127</v>
-      </c>
-      <c r="O115" t="s">
-        <v>0</v>
-      </c>
-      <c r="P115" s="1">
-        <v>1200000</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A116">
-        <v>62880594</v>
-      </c>
-      <c r="B116" s="2">
-        <v>46149.454710648148</v>
-      </c>
-      <c r="C116">
-        <v>62941351</v>
-      </c>
-      <c r="D116" s="2">
-        <v>46150.416979166665</v>
-      </c>
-      <c r="E116" t="s">
-        <v>16</v>
-      </c>
-      <c r="F116" t="s">
-        <v>290</v>
-      </c>
-      <c r="G116">
-        <v>709565662</v>
-      </c>
-      <c r="H116" t="s">
-        <v>291</v>
-      </c>
-      <c r="I116" t="s">
-        <v>0</v>
-      </c>
-      <c r="J116" t="s">
-        <v>13</v>
-      </c>
-      <c r="K116" t="s">
-        <v>5</v>
-      </c>
-      <c r="L116" t="s">
-        <v>6</v>
-      </c>
-      <c r="M116" t="s">
-        <v>7</v>
-      </c>
-      <c r="N116" t="s">
-        <v>127</v>
-      </c>
-      <c r="O116" t="s">
-        <v>0</v>
-      </c>
-      <c r="P116" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A117">
-        <v>62880628</v>
-      </c>
-      <c r="B117" s="2">
-        <v>46149.45484953704</v>
-      </c>
-      <c r="C117">
-        <v>62941416</v>
-      </c>
-      <c r="D117" s="2">
-        <v>46150.417719907404</v>
-      </c>
-      <c r="E117" t="s">
-        <v>16</v>
-      </c>
-      <c r="F117" t="s">
-        <v>290</v>
-      </c>
-      <c r="G117">
-        <v>709565662</v>
-      </c>
-      <c r="H117" t="s">
-        <v>291</v>
-      </c>
-      <c r="I117" t="s">
-        <v>0</v>
-      </c>
-      <c r="J117" t="s">
-        <v>13</v>
-      </c>
-      <c r="K117" t="s">
-        <v>5</v>
-      </c>
-      <c r="L117" t="s">
-        <v>6</v>
-      </c>
-      <c r="M117" t="s">
-        <v>14</v>
-      </c>
-      <c r="N117" t="s">
-        <v>127</v>
-      </c>
-      <c r="O117" t="s">
-        <v>0</v>
-      </c>
-      <c r="P117">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A118">
-        <v>62880812</v>
-      </c>
-      <c r="B118" s="2">
-        <v>46149.456157407411</v>
-      </c>
-      <c r="C118">
-        <v>63072435</v>
-      </c>
-      <c r="D118" s="2">
-        <v>46153.371168981481</v>
-      </c>
-      <c r="E118" t="s">
-        <v>123</v>
-      </c>
-      <c r="F118" t="s">
-        <v>293</v>
-      </c>
-      <c r="G118">
-        <v>707672487</v>
-      </c>
-      <c r="H118" t="s">
-        <v>294</v>
-      </c>
-      <c r="I118" t="s">
-        <v>0</v>
-      </c>
-      <c r="J118" t="s">
-        <v>22</v>
-      </c>
-      <c r="K118" t="s">
-        <v>1</v>
-      </c>
-      <c r="L118" t="s">
-        <v>2</v>
-      </c>
-      <c r="M118" t="s">
-        <v>3</v>
-      </c>
-      <c r="N118" t="s">
-        <v>127</v>
-      </c>
-      <c r="O118" t="s">
-        <v>0</v>
-      </c>
-      <c r="P118" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A119">
-        <v>62937923</v>
-      </c>
-      <c r="B119" s="2">
-        <v>46150.381145833337</v>
-      </c>
-      <c r="C119">
-        <v>63089746</v>
-      </c>
-      <c r="D119" s="2">
-        <v>46153.520532407405</v>
-      </c>
-      <c r="E119" t="s">
-        <v>123</v>
-      </c>
-      <c r="F119" t="s">
-        <v>295</v>
-      </c>
-      <c r="G119">
-        <v>565811689</v>
-      </c>
-      <c r="H119" t="s">
-        <v>37</v>
-      </c>
-      <c r="I119" t="s">
-        <v>0</v>
-      </c>
-      <c r="J119" t="s">
-        <v>13</v>
-      </c>
-      <c r="K119" t="s">
-        <v>5</v>
-      </c>
-      <c r="L119" t="s">
-        <v>6</v>
-      </c>
-      <c r="M119" t="s">
-        <v>3</v>
-      </c>
-      <c r="N119" t="s">
-        <v>127</v>
-      </c>
-      <c r="O119" t="s">
-        <v>0</v>
-      </c>
-      <c r="P119" s="1">
-        <v>250000</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A120">
-        <v>62968196</v>
-      </c>
-      <c r="B120" s="2">
-        <v>46150.638715277775</v>
-      </c>
-      <c r="C120">
-        <v>63089942</v>
-      </c>
-      <c r="D120" s="2">
-        <v>46153.521840277775</v>
-      </c>
-      <c r="E120" t="s">
-        <v>269</v>
-      </c>
-      <c r="F120" t="s">
-        <v>296</v>
-      </c>
-      <c r="G120">
-        <v>758177759</v>
-      </c>
-      <c r="H120" t="s">
-        <v>37</v>
-      </c>
-      <c r="I120" t="s">
-        <v>0</v>
-      </c>
-      <c r="J120" t="s">
-        <v>13</v>
-      </c>
-      <c r="K120" t="s">
-        <v>5</v>
-      </c>
-      <c r="L120" t="s">
-        <v>6</v>
-      </c>
-      <c r="M120" t="s">
-        <v>208</v>
-      </c>
-      <c r="N120" t="s">
-        <v>127</v>
-      </c>
-      <c r="O120" t="s">
-        <v>0</v>
-      </c>
-      <c r="P120" s="1">
-        <v>2881416</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A121">
-        <v>63025600</v>
-      </c>
-      <c r="B121" s="2">
-        <v>46151.740983796299</v>
-      </c>
-      <c r="C121">
-        <v>63090146</v>
-      </c>
-      <c r="D121" s="2">
-        <v>46153.522766203707</v>
-      </c>
-      <c r="E121" t="s">
-        <v>269</v>
-      </c>
-      <c r="F121" t="s">
-        <v>297</v>
-      </c>
-      <c r="G121">
-        <v>758237461</v>
-      </c>
-      <c r="H121" t="s">
-        <v>298</v>
-      </c>
-      <c r="I121" t="s">
-        <v>0</v>
-      </c>
-      <c r="J121" t="s">
-        <v>13</v>
-      </c>
-      <c r="K121" t="s">
-        <v>5</v>
-      </c>
-      <c r="L121" t="s">
-        <v>6</v>
-      </c>
-      <c r="M121" t="s">
-        <v>3</v>
-      </c>
-      <c r="N121" t="s">
-        <v>126</v>
-      </c>
-      <c r="O121" t="s">
-        <v>0</v>
-      </c>
-      <c r="P121" s="1">
-        <v>850000</v>
-      </c>
-      <c r="Q121" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A122">
-        <v>63073782</v>
-      </c>
-      <c r="B122" s="2">
-        <v>46153.387870370374</v>
-      </c>
-      <c r="C122">
-        <v>63086952</v>
-      </c>
-      <c r="D122" s="2">
-        <v>46153.499490740738</v>
-      </c>
-      <c r="E122" t="s">
-        <v>243</v>
-      </c>
-      <c r="F122" t="s">
-        <v>299</v>
-      </c>
-      <c r="G122">
-        <v>710619970</v>
-      </c>
-      <c r="H122" t="s">
-        <v>300</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122" t="s">
-        <v>22</v>
-      </c>
-      <c r="K122" t="s">
-        <v>1</v>
-      </c>
-      <c r="L122" t="s">
-        <v>2</v>
-      </c>
-      <c r="M122" t="s">
-        <v>3</v>
-      </c>
-      <c r="N122" t="s">
-        <v>127</v>
-      </c>
-      <c r="O122" t="s">
-        <v>0</v>
-      </c>
-      <c r="P122" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q122" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q122" xr:uid="{E99D2217-19B7-48F6-AA0C-663745521120}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/Attachments/Bureau/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="451" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86184E87-553E-4F89-9AFC-41CBB263610D}"/>
+  <xr:revisionPtr revIDLastSave="487" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1D2D3C0-A6A3-429A-AE0B-B5BB58734133}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="45" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="46" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil2!$A$1:$Q$109</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="283">
   <si>
     <t>-</t>
   </si>
@@ -209,9 +212,6 @@
     <t>REFERENCE</t>
   </si>
   <si>
-    <t>BOUAKE</t>
-  </si>
-  <si>
     <t>AERIA BUVPN 2 AEROPORT</t>
   </si>
   <si>
@@ -338,9 +338,6 @@
     <t>M'BRAGO</t>
   </si>
   <si>
-    <t>STE MUGEFCI</t>
-  </si>
-  <si>
     <t>MAIRIE DE NIABLE</t>
   </si>
   <si>
@@ -443,9 +440,6 @@
     <t>DIA 20Mbps Ext A : PoP ICA REPUBLIQUE Ext B : 7,avenue Nogues,Immeuble BSIC,5eme et Abidjan 01 BP 5754 7 AV.Nogues 8X8J+QX Abidjan, COTE D IVOIRE</t>
   </si>
   <si>
-    <t>OFI OLAM IVOIRE</t>
-  </si>
-  <si>
     <t>MAXAM CI</t>
   </si>
   <si>
@@ -590,9 +584,6 @@
     <t>COCODY VALLON</t>
   </si>
   <si>
-    <t>SAN-PEDRO</t>
-  </si>
-  <si>
     <t>STE SICPA CI</t>
   </si>
   <si>
@@ -617,9 +608,6 @@
     <t>FO</t>
   </si>
   <si>
-    <t>SYTHD260101</t>
-  </si>
-  <si>
     <t>ABIDJAN-COCODY//VOIE INCONNUE/RIVIERA 0708448800</t>
   </si>
   <si>
@@ -650,9 +638,6 @@
     <t>COCODY ANGRE NOUVEAU CHU</t>
   </si>
   <si>
-    <t>XPERIENCE GLOBAL SERVICES</t>
-  </si>
-  <si>
     <t>NESKAO</t>
   </si>
   <si>
@@ -707,9 +692,6 @@
     <t>ANSSI</t>
   </si>
   <si>
-    <t>NOM</t>
-  </si>
-  <si>
     <t>SYTHD260132</t>
   </si>
   <si>
@@ -719,24 +701,15 @@
     <t>BUVPN260086</t>
   </si>
   <si>
-    <t>SYTHD260133</t>
-  </si>
-  <si>
     <t>PLANETPHARMA EXPORT CI</t>
   </si>
   <si>
     <t>SYTHD260131</t>
   </si>
   <si>
-    <t>XXXXXXXXXXXXXXX</t>
-  </si>
-  <si>
     <t>Responsable Zone: Coordination etude et travaux</t>
   </si>
   <si>
-    <t>SYTHD260136</t>
-  </si>
-  <si>
     <t>SYTHD260129</t>
   </si>
   <si>
@@ -806,21 +779,9 @@
     <t>COCODY IMMEUBLE TRIDEM PHARMA RDC</t>
   </si>
   <si>
-    <t>ODIENNE//VOIE INCONNUE/GBELEBAN</t>
-  </si>
-  <si>
-    <t>BUVPN260049</t>
-  </si>
-  <si>
-    <t>Prestataire : Correction Conformite Travaux</t>
-  </si>
-  <si>
     <t>GOULIA</t>
   </si>
   <si>
-    <t>BUVPN260089</t>
-  </si>
-  <si>
     <t>MOTA ENGIL COTE D'IVOIRE MINING</t>
   </si>
   <si>
@@ -833,27 +794,9 @@
     <t>SYTHD260137</t>
   </si>
   <si>
-    <t>SODEXAM BONDOUKOU STATION METEOROLOGIQUE</t>
-  </si>
-  <si>
-    <t>BONDOUKOU STATION METEOROLOGIQUE</t>
-  </si>
-  <si>
-    <t>SYTHD260115</t>
-  </si>
-  <si>
-    <t>SIE : Affectation des ressources</t>
-  </si>
-  <si>
     <t>PORT-POUET VRIDI ZONE INDUSTRIELLE RUE DES TEXTILES</t>
   </si>
   <si>
-    <t>Suspendu</t>
-  </si>
-  <si>
-    <t>Create Gestion RdvEtude</t>
-  </si>
-  <si>
     <t>SYTHD260134</t>
   </si>
   <si>
@@ -885,6 +828,66 @@
   </si>
   <si>
     <t>COCODY DANGA</t>
+  </si>
+  <si>
+    <t>BBF : Validation Etude</t>
+  </si>
+  <si>
+    <t>Technicien zone: Intervention</t>
+  </si>
+  <si>
+    <t>BUVPN260092</t>
+  </si>
+  <si>
+    <t>SYTHD260140</t>
+  </si>
+  <si>
+    <t>ARTCI</t>
+  </si>
+  <si>
+    <t>PORT BOUET PARC DES EXPOSITIONS.</t>
+  </si>
+  <si>
+    <t>SYTHD260141</t>
+  </si>
+  <si>
+    <t>PORT BOUET PARC DES EXPOSITIONS RADISON BLUE.</t>
+  </si>
+  <si>
+    <t>SYTHD260142</t>
+  </si>
+  <si>
+    <t>DEMANDE INTERNE LSI ABIDJAN CINÉ SCRATC 2026</t>
+  </si>
+  <si>
+    <t>Cocody Terrain d'Anono</t>
+  </si>
+  <si>
+    <t>AGT</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie GAIA</t>
+  </si>
+  <si>
+    <t>CALIXT S.A.R.L</t>
+  </si>
+  <si>
+    <t>DANANE</t>
+  </si>
+  <si>
+    <t>AFRICURE PHARMACEUTICAL COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>GRAND BASSAM VITIB ZONE FRANCHE PARC TECHNOLOGIQUE MAHATMA GHANDI.</t>
+  </si>
+  <si>
+    <t>TIOBLI</t>
+  </si>
+  <si>
+    <t>IVOIRE ACIER SARL U</t>
+  </si>
+  <si>
+    <t>ABIDJAN-YOPOUGON AUTOROUTE DU NORD PK 24</t>
   </si>
 </sst>
 </file>
@@ -928,7 +931,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1268,14 +1291,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3F1327-EEF1-4F7B-8988-4F1DB9CBD7F5}">
-  <dimension ref="A1:Q108"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33B89436-3C62-48B9-A287-E4DCE0428514}">
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.453125" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8.7265625" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
@@ -1319,7 +1339,7 @@
         <v>53</v>
       </c>
       <c r="N1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="O1" t="s">
         <v>54</v>
@@ -1348,13 +1368,13 @@
         <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G2">
         <v>777545168</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
@@ -1404,7 +1424,7 @@
         <v>708086759</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I3">
         <v>2788625</v>
@@ -1422,7 +1442,7 @@
         <v>17</v>
       </c>
       <c r="N3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O3" t="s">
         <v>0</v>
@@ -1451,13 +1471,13 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>709738605</v>
       </c>
       <c r="H4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I4">
         <v>2793645</v>
@@ -1475,7 +1495,7 @@
         <v>7</v>
       </c>
       <c r="N4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O4" t="s">
         <v>0</v>
@@ -1484,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
@@ -1510,7 +1530,7 @@
         <v>778036533</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I5" t="s">
         <v>0</v>
@@ -1528,7 +1548,7 @@
         <v>3</v>
       </c>
       <c r="N5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O5" t="s">
         <v>0</v>
@@ -1557,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>703333988</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
         <v>0</v>
@@ -1581,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="N6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O6" t="s">
         <v>0</v>
@@ -1610,13 +1630,13 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>708336404</v>
       </c>
       <c r="H7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
         <v>0</v>
@@ -1634,7 +1654,7 @@
         <v>3</v>
       </c>
       <c r="N7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O7" t="s">
         <v>0</v>
@@ -1669,7 +1689,7 @@
         <v>707003126</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
@@ -1687,7 +1707,7 @@
         <v>7</v>
       </c>
       <c r="N8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O8" t="s">
         <v>0</v>
@@ -1722,7 +1742,7 @@
         <v>708086759</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I9" t="s">
         <v>0</v>
@@ -1740,7 +1760,7 @@
         <v>7</v>
       </c>
       <c r="N9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O9" t="s">
         <v>0</v>
@@ -1769,7 +1789,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G10">
         <v>504033918</v>
@@ -1793,7 +1813,7 @@
         <v>3</v>
       </c>
       <c r="N10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O10" t="s">
         <v>0</v>
@@ -1802,7 +1822,7 @@
         <v>4000000</v>
       </c>
       <c r="Q10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
@@ -1819,10 +1839,10 @@
         <v>46049.856261574074</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G11">
         <v>759003900</v>
@@ -1846,7 +1866,7 @@
         <v>3</v>
       </c>
       <c r="N11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O11" t="s">
         <v>0</v>
@@ -1855,7 +1875,7 @@
         <v>918681</v>
       </c>
       <c r="Q11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -1875,13 +1895,13 @@
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G12">
         <v>749338073</v>
       </c>
       <c r="H12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s">
         <v>0</v>
@@ -1899,7 +1919,7 @@
         <v>3</v>
       </c>
       <c r="N12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O12" t="s">
         <v>0</v>
@@ -1908,7 +1928,7 @@
         <v>638462</v>
       </c>
       <c r="Q12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
@@ -1925,16 +1945,16 @@
         <v>46083.492881944447</v>
       </c>
       <c r="E13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G13">
         <v>585990976</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I13">
         <v>1765416</v>
@@ -1952,7 +1972,7 @@
         <v>3</v>
       </c>
       <c r="N13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O13" t="s">
         <v>0</v>
@@ -1961,24 +1981,24 @@
         <v>3000000</v>
       </c>
       <c r="Q13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>56601140</v>
+        <v>56601982</v>
       </c>
       <c r="B14" s="2">
-        <v>46035.385555555556</v>
+        <v>46035.393611111111</v>
       </c>
       <c r="C14">
-        <v>59442988</v>
+        <v>63317758</v>
       </c>
       <c r="D14" s="2">
-        <v>46086.814479166664</v>
+        <v>46157.506435185183</v>
       </c>
       <c r="E14" t="s">
-        <v>258</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
         <v>29</v>
@@ -1987,13 +2007,13 @@
         <v>707003126</v>
       </c>
       <c r="H14" t="s">
-        <v>256</v>
-      </c>
-      <c r="I14">
-        <v>1778026</v>
+        <v>246</v>
+      </c>
+      <c r="I14" t="s">
+        <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -2002,10 +2022,10 @@
         <v>8</v>
       </c>
       <c r="M14" t="s">
-        <v>223</v>
+        <v>3</v>
       </c>
       <c r="N14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O14" t="s">
         <v>0</v>
@@ -2014,24 +2034,24 @@
         <v>7103410</v>
       </c>
       <c r="Q14" t="s">
-        <v>257</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>56601982</v>
+        <v>56603495</v>
       </c>
       <c r="B15" s="2">
-        <v>46035.393611111111</v>
+        <v>46035.408518518518</v>
       </c>
       <c r="C15">
-        <v>63227381</v>
+        <v>60907737</v>
       </c>
       <c r="D15" s="2">
-        <v>46155.633634259262</v>
+        <v>46113.726909722223</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
         <v>29</v>
@@ -2040,7 +2060,7 @@
         <v>707003126</v>
       </c>
       <c r="H15" t="s">
-        <v>259</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
         <v>0</v>
@@ -2058,7 +2078,7 @@
         <v>3</v>
       </c>
       <c r="N15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O15" t="s">
         <v>0</v>
@@ -2067,33 +2087,33 @@
         <v>7103410</v>
       </c>
       <c r="Q15" t="s">
-        <v>260</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>56603495</v>
+        <v>56606469</v>
       </c>
       <c r="B16" s="2">
-        <v>46035.408518518518</v>
+        <v>46035.43072916667</v>
       </c>
       <c r="C16">
-        <v>60907737</v>
+        <v>60100048</v>
       </c>
       <c r="D16" s="2">
-        <v>46113.726909722223</v>
+        <v>46099.427060185182</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G16">
-        <v>707003126</v>
+        <v>504041812</v>
       </c>
       <c r="H16" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="I16" t="s">
         <v>0</v>
@@ -2111,42 +2131,42 @@
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O16" t="s">
         <v>0</v>
       </c>
       <c r="P16" s="1">
-        <v>7103410</v>
+        <v>1000000</v>
       </c>
       <c r="Q16" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>56606469</v>
+        <v>56607988</v>
       </c>
       <c r="B17" s="2">
-        <v>46035.43072916667</v>
+        <v>46035.443668981483</v>
       </c>
       <c r="C17">
-        <v>60100048</v>
+        <v>62467448</v>
       </c>
       <c r="D17" s="2">
-        <v>46099.427060185182</v>
+        <v>46141.570902777778</v>
       </c>
       <c r="E17" t="s">
-        <v>144</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G17">
         <v>504041812</v>
       </c>
       <c r="H17" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="I17" t="s">
         <v>0</v>
@@ -2164,42 +2184,42 @@
         <v>3</v>
       </c>
       <c r="N17" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O17" t="s">
         <v>0</v>
       </c>
       <c r="P17" s="1">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="Q17" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>56607988</v>
+        <v>56611212</v>
       </c>
       <c r="B18" s="2">
-        <v>46035.443668981483</v>
+        <v>46035.471886574072</v>
       </c>
       <c r="C18">
-        <v>62467448</v>
+        <v>62203808</v>
       </c>
       <c r="D18" s="2">
-        <v>46141.570902777778</v>
+        <v>46136.681342592594</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G18">
         <v>504041812</v>
       </c>
       <c r="H18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s">
         <v>0</v>
@@ -2217,7 +2237,7 @@
         <v>3</v>
       </c>
       <c r="N18" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O18" t="s">
         <v>0</v>
@@ -2226,39 +2246,39 @@
         <v>2000000</v>
       </c>
       <c r="Q18" t="s">
-        <v>189</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>56611212</v>
+        <v>56618123</v>
       </c>
       <c r="B19" s="2">
-        <v>46035.471886574072</v>
+        <v>46035.520821759259</v>
       </c>
       <c r="C19">
-        <v>62203808</v>
+        <v>59311833</v>
       </c>
       <c r="D19" s="2">
-        <v>46136.681342592594</v>
+        <v>46084.811782407407</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G19">
         <v>504041812</v>
       </c>
       <c r="H19" t="s">
-        <v>90</v>
-      </c>
-      <c r="I19" t="s">
-        <v>0</v>
+        <v>122</v>
+      </c>
+      <c r="I19">
+        <v>1775236</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -2270,7 +2290,7 @@
         <v>3</v>
       </c>
       <c r="N19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O19" t="s">
         <v>0</v>
@@ -2279,86 +2299,86 @@
         <v>2000000</v>
       </c>
       <c r="Q19" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>56618123</v>
+        <v>56675050</v>
       </c>
       <c r="B20" s="2">
-        <v>46035.520821759259</v>
+        <v>46036.516423611109</v>
       </c>
       <c r="C20">
-        <v>59311833</v>
+        <v>63302732</v>
       </c>
       <c r="D20" s="2">
-        <v>46084.811782407407</v>
+        <v>46157.396793981483</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s">
-        <v>92</v>
+        <v>247</v>
       </c>
       <c r="G20">
-        <v>504041812</v>
+        <v>748512613</v>
       </c>
       <c r="H20" t="s">
-        <v>124</v>
-      </c>
-      <c r="I20">
-        <v>1775236</v>
+        <v>96</v>
+      </c>
+      <c r="I20" t="s">
+        <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M20" t="s">
         <v>3</v>
       </c>
       <c r="N20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O20" t="s">
         <v>0</v>
       </c>
       <c r="P20" s="1">
-        <v>2000000</v>
+        <v>4362401</v>
       </c>
       <c r="Q20" t="s">
-        <v>125</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>56675050</v>
+        <v>56970346</v>
       </c>
       <c r="B21" s="2">
-        <v>46036.516423611109</v>
+        <v>46042.557280092595</v>
       </c>
       <c r="C21">
-        <v>63140730</v>
+        <v>59242054</v>
       </c>
       <c r="D21" s="2">
-        <v>46154.429652777777</v>
+        <v>46083.719525462962</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>261</v>
+        <v>92</v>
       </c>
       <c r="G21">
-        <v>748512613</v>
+        <v>708667658</v>
       </c>
       <c r="H21" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I21" t="s">
         <v>0</v>
@@ -2376,42 +2396,42 @@
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O21" t="s">
         <v>0</v>
       </c>
       <c r="P21" s="1">
-        <v>4362401</v>
+        <v>2871414</v>
       </c>
       <c r="Q21" t="s">
-        <v>224</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>56970346</v>
+        <v>57398181</v>
       </c>
       <c r="B22" s="2">
-        <v>46042.557280092595</v>
+        <v>46050.584374999999</v>
       </c>
       <c r="C22">
-        <v>59242054</v>
+        <v>60344342</v>
       </c>
       <c r="D22" s="2">
-        <v>46083.719525462962</v>
+        <v>46104.528900462959</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G22">
-        <v>708667658</v>
+        <v>720631500</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I22" t="s">
         <v>0</v>
@@ -2429,42 +2449,42 @@
         <v>3</v>
       </c>
       <c r="N22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O22" t="s">
         <v>0</v>
       </c>
       <c r="P22" s="1">
-        <v>2871414</v>
+        <v>4406780</v>
       </c>
       <c r="Q22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>57398181</v>
+        <v>58055656</v>
       </c>
       <c r="B23" s="2">
-        <v>46050.584374999999</v>
+        <v>46062.760023148148</v>
       </c>
       <c r="C23">
-        <v>60344342</v>
+        <v>61269237</v>
       </c>
       <c r="D23" s="2">
-        <v>46104.528900462959</v>
+        <v>46121.376689814817</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G23">
-        <v>720631500</v>
+        <v>758224257</v>
       </c>
       <c r="H23" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="I23" t="s">
         <v>0</v>
@@ -2482,42 +2502,42 @@
         <v>3</v>
       </c>
       <c r="N23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O23" t="s">
         <v>0</v>
       </c>
       <c r="P23" s="1">
-        <v>4406780</v>
+        <v>1800000</v>
       </c>
       <c r="Q23" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>57706849</v>
+        <v>58093827</v>
       </c>
       <c r="B24" s="2">
-        <v>46056.499166666668</v>
+        <v>46063.583402777775</v>
       </c>
       <c r="C24">
-        <v>62851094</v>
+        <v>62146534</v>
       </c>
       <c r="D24" s="2">
-        <v>46148.703194444446</v>
+        <v>46135.713287037041</v>
       </c>
       <c r="E24" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="F24" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24">
+        <v>708086759</v>
+      </c>
+      <c r="H24" t="s">
         <v>100</v>
-      </c>
-      <c r="G24">
-        <v>708086472</v>
-      </c>
-      <c r="H24" t="s">
-        <v>78</v>
       </c>
       <c r="I24" t="s">
         <v>0</v>
@@ -2535,92 +2555,92 @@
         <v>7</v>
       </c>
       <c r="N24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O24" t="s">
         <v>0</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="s">
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>31</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>58055656</v>
+        <v>58166885</v>
       </c>
       <c r="B25" s="2">
-        <v>46062.760023148148</v>
+        <v>46064.649965277778</v>
       </c>
       <c r="C25">
-        <v>61269237</v>
+        <v>63079695</v>
       </c>
       <c r="D25" s="2">
-        <v>46121.376689814817</v>
+        <v>46153.448425925926</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="G25">
-        <v>758224257</v>
+        <v>504041812</v>
       </c>
       <c r="H25" t="s">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="I25" t="s">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M25" t="s">
         <v>3</v>
       </c>
       <c r="N25" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O25" t="s">
         <v>0</v>
       </c>
       <c r="P25" s="1">
-        <v>1800000</v>
+        <v>2000000</v>
       </c>
       <c r="Q25" t="s">
-        <v>15</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>58093827</v>
+        <v>58626822</v>
       </c>
       <c r="B26" s="2">
-        <v>46063.583402777775</v>
+        <v>46072.810324074075</v>
       </c>
       <c r="C26">
-        <v>62146534</v>
+        <v>59811821</v>
       </c>
       <c r="D26" s="2">
-        <v>46135.713287037041</v>
+        <v>46093.543773148151</v>
       </c>
       <c r="E26" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="G26">
-        <v>708086759</v>
+        <v>709574114</v>
       </c>
       <c r="H26" t="s">
         <v>102</v>
@@ -2638,45 +2658,45 @@
         <v>6</v>
       </c>
       <c r="M26" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O26" t="s">
         <v>0</v>
       </c>
-      <c r="P26" t="s">
-        <v>0</v>
+      <c r="P26" s="1">
+        <v>445307</v>
       </c>
       <c r="Q26" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>58166885</v>
+        <v>58635645</v>
       </c>
       <c r="B27" s="2">
-        <v>46064.649965277778</v>
+        <v>46073.372395833336</v>
       </c>
       <c r="C27">
-        <v>63079695</v>
+        <v>61982536</v>
       </c>
       <c r="D27" s="2">
-        <v>46153.448425925926</v>
+        <v>46133.49863425926</v>
       </c>
       <c r="E27" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="G27">
-        <v>504041812</v>
+        <v>759250737</v>
       </c>
       <c r="H27" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="I27" t="s">
         <v>0</v>
@@ -2685,104 +2705,104 @@
         <v>18</v>
       </c>
       <c r="K27" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L27" t="s">
         <v>8</v>
       </c>
       <c r="M27" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O27" t="s">
         <v>0</v>
       </c>
-      <c r="P27" s="1">
-        <v>2000000</v>
+      <c r="P27" t="s">
+        <v>0</v>
       </c>
       <c r="Q27" t="s">
-        <v>226</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>58626822</v>
+        <v>58635674</v>
       </c>
       <c r="B28" s="2">
-        <v>46072.810324074075</v>
+        <v>46073.372488425928</v>
       </c>
       <c r="C28">
-        <v>59811821</v>
+        <v>61980847</v>
       </c>
       <c r="D28" s="2">
-        <v>46093.543773148151</v>
+        <v>46133.487384259257</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s">
         <v>103</v>
       </c>
       <c r="G28">
-        <v>709574114</v>
+        <v>759250737</v>
       </c>
       <c r="H28" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="I28" t="s">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
       </c>
       <c r="L28" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M28" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O28" t="s">
         <v>0</v>
       </c>
       <c r="P28" s="1">
-        <v>445307</v>
+        <v>500000</v>
       </c>
       <c r="Q28" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>58635645</v>
+        <v>58797846</v>
       </c>
       <c r="B29" s="2">
-        <v>46073.372395833336</v>
+        <v>46076.510104166664</v>
       </c>
       <c r="C29">
-        <v>61982536</v>
+        <v>63198672</v>
       </c>
       <c r="D29" s="2">
-        <v>46133.49863425926</v>
+        <v>46155.408773148149</v>
       </c>
       <c r="E29" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="F29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G29">
-        <v>759250737</v>
+        <v>102224907</v>
       </c>
       <c r="H29" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="I29" t="s">
         <v>0</v>
@@ -2797,45 +2817,45 @@
         <v>8</v>
       </c>
       <c r="M29" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N29" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O29" t="s">
         <v>0</v>
       </c>
-      <c r="P29" t="s">
-        <v>0</v>
+      <c r="P29" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q29" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>58635674</v>
+        <v>58856498</v>
       </c>
       <c r="B30" s="2">
-        <v>46073.372488425928</v>
+        <v>46077.418171296296</v>
       </c>
       <c r="C30">
-        <v>61980847</v>
+        <v>60800011</v>
       </c>
       <c r="D30" s="2">
-        <v>46133.487384259257</v>
+        <v>46112.393784722219</v>
       </c>
       <c r="E30" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="F30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G30">
-        <v>759250737</v>
+        <v>748377555</v>
       </c>
       <c r="H30" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
@@ -2850,98 +2870,98 @@
         <v>8</v>
       </c>
       <c r="M30" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O30" t="s">
         <v>0</v>
       </c>
-      <c r="P30" s="1">
-        <v>500000</v>
+      <c r="P30" t="s">
+        <v>0</v>
       </c>
       <c r="Q30" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>58797846</v>
+        <v>58860538</v>
       </c>
       <c r="B31" s="2">
-        <v>46076.510104166664</v>
+        <v>46077.446666666663</v>
       </c>
       <c r="C31">
-        <v>63198672</v>
+        <v>62950864</v>
       </c>
       <c r="D31" s="2">
-        <v>46155.408773148149</v>
+        <v>46150.491238425922</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G31">
-        <v>102224907</v>
+        <v>748377555</v>
       </c>
       <c r="H31" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="I31" t="s">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K31" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L31" t="s">
         <v>8</v>
       </c>
       <c r="M31" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O31" t="s">
         <v>0</v>
       </c>
       <c r="P31" s="1">
-        <v>2000000</v>
+        <v>5324000</v>
       </c>
       <c r="Q31" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>58856498</v>
+        <v>58868849</v>
       </c>
       <c r="B32" s="2">
-        <v>46077.418171296296</v>
+        <v>46077.501203703701</v>
       </c>
       <c r="C32">
-        <v>60800011</v>
+        <v>62104932</v>
       </c>
       <c r="D32" s="2">
-        <v>46112.393784722219</v>
+        <v>46135.396608796298</v>
       </c>
       <c r="E32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F32" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G32">
         <v>748377555</v>
       </c>
       <c r="H32" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I32" t="s">
         <v>0</v>
@@ -2959,7 +2979,7 @@
         <v>7</v>
       </c>
       <c r="N32" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O32" t="s">
         <v>0</v>
@@ -2968,136 +2988,136 @@
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>58860538</v>
+        <v>58925987</v>
       </c>
       <c r="B33" s="2">
-        <v>46077.446666666663</v>
+        <v>46078.434814814813</v>
       </c>
       <c r="C33">
-        <v>62950864</v>
+        <v>60163873</v>
       </c>
       <c r="D33" s="2">
-        <v>46150.491238425922</v>
+        <v>46100.423101851855</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G33">
-        <v>748377555</v>
+        <v>708641473</v>
       </c>
       <c r="H33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I33" t="s">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K33" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L33" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M33" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N33" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O33" t="s">
         <v>0</v>
       </c>
-      <c r="P33" s="1">
-        <v>5324000</v>
+      <c r="P33" t="s">
+        <v>0</v>
       </c>
       <c r="Q33" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>58868849</v>
+        <v>58959238</v>
       </c>
       <c r="B34" s="2">
-        <v>46077.501203703701</v>
+        <v>46078.665532407409</v>
       </c>
       <c r="C34">
-        <v>62104932</v>
+        <v>60163938</v>
       </c>
       <c r="D34" s="2">
-        <v>46135.396608796298</v>
+        <v>46100.423773148148</v>
       </c>
       <c r="E34" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G34">
-        <v>748377555</v>
+        <v>708641473</v>
       </c>
       <c r="H34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I34" t="s">
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
       </c>
       <c r="L34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M34" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N34" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O34" t="s">
         <v>0</v>
       </c>
-      <c r="P34" t="s">
-        <v>0</v>
+      <c r="P34" s="1">
+        <v>850000</v>
       </c>
       <c r="Q34" t="s">
-        <v>165</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>58925987</v>
+        <v>58963630</v>
       </c>
       <c r="B35" s="2">
-        <v>46078.434814814813</v>
+        <v>46078.697002314817</v>
       </c>
       <c r="C35">
-        <v>60163873</v>
+        <v>63236831</v>
       </c>
       <c r="D35" s="2">
-        <v>46100.423101851855</v>
+        <v>46155.699733796297</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="G35">
-        <v>708641473</v>
+        <v>747726344</v>
       </c>
       <c r="H35" t="s">
         <v>116</v>
@@ -3106,19 +3126,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K35" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L35" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M35" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N35" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O35" t="s">
         <v>0</v>
@@ -3127,33 +3147,33 @@
         <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>58959238</v>
+        <v>58963646</v>
       </c>
       <c r="B36" s="2">
-        <v>46078.665532407409</v>
+        <v>46078.697048611109</v>
       </c>
       <c r="C36">
-        <v>60163938</v>
+        <v>61620936</v>
       </c>
       <c r="D36" s="2">
-        <v>46100.423773148148</v>
+        <v>46127.58321759259</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="F36" t="s">
+        <v>40</v>
+      </c>
+      <c r="G36">
+        <v>747726344</v>
+      </c>
+      <c r="H36" t="s">
         <v>116</v>
-      </c>
-      <c r="G36">
-        <v>708641473</v>
-      </c>
-      <c r="H36" t="s">
-        <v>117</v>
       </c>
       <c r="I36" t="s">
         <v>0</v>
@@ -3162,51 +3182,51 @@
         <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L36" t="s">
         <v>6</v>
       </c>
       <c r="M36" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O36" t="s">
         <v>0</v>
       </c>
-      <c r="P36" s="1">
-        <v>850000</v>
+      <c r="P36">
+        <v>0</v>
       </c>
       <c r="Q36" t="s">
-        <v>31</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>58963630</v>
+        <v>59466514</v>
       </c>
       <c r="B37" s="2">
-        <v>46078.697002314817</v>
+        <v>46087.436643518522</v>
       </c>
       <c r="C37">
-        <v>63173571</v>
+        <v>63070473</v>
       </c>
       <c r="D37" s="2">
-        <v>46154.68545138889</v>
+        <v>46153.32271990741</v>
       </c>
       <c r="E37" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="F37" t="s">
-        <v>40</v>
+        <v>220</v>
       </c>
       <c r="G37">
-        <v>747726344</v>
+        <v>141679210</v>
       </c>
       <c r="H37" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="I37" t="s">
         <v>0</v>
@@ -3224,104 +3244,104 @@
         <v>7</v>
       </c>
       <c r="N37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O37" t="s">
         <v>0</v>
       </c>
-      <c r="P37" t="s">
-        <v>0</v>
+      <c r="P37" s="1">
+        <v>3213390</v>
       </c>
       <c r="Q37" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>58963646</v>
+        <v>59480507</v>
       </c>
       <c r="B38" s="2">
-        <v>46078.697048611109</v>
+        <v>46087.544247685182</v>
       </c>
       <c r="C38">
-        <v>61620936</v>
+        <v>63301042</v>
       </c>
       <c r="D38" s="2">
-        <v>46127.58321759259</v>
+        <v>46157.380254629628</v>
       </c>
       <c r="E38" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="G38">
-        <v>747726344</v>
+        <v>708547070</v>
       </c>
       <c r="H38" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="I38" t="s">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K38" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L38" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M38" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N38" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O38" t="s">
         <v>0</v>
       </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>166</v>
+      <c r="P38" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>2721712020</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>59466514</v>
+        <v>59537755</v>
       </c>
       <c r="B39" s="2">
-        <v>46087.436643518522</v>
+        <v>46088.586631944447</v>
       </c>
       <c r="C39">
-        <v>63070473</v>
+        <v>61591841</v>
       </c>
       <c r="D39" s="2">
-        <v>46153.32271990741</v>
+        <v>46127.35796296296</v>
       </c>
       <c r="E39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F39" t="s">
-        <v>228</v>
+        <v>164</v>
       </c>
       <c r="G39">
-        <v>141679210</v>
+        <v>556331131</v>
       </c>
       <c r="H39" t="s">
+        <v>146</v>
+      </c>
+      <c r="I39">
+        <v>1843236</v>
+      </c>
+      <c r="J39" t="s">
+        <v>4</v>
+      </c>
+      <c r="K39" t="s">
         <v>127</v>
-      </c>
-      <c r="I39" t="s">
-        <v>0</v>
-      </c>
-      <c r="J39" t="s">
-        <v>13</v>
-      </c>
-      <c r="K39" t="s">
-        <v>9</v>
       </c>
       <c r="L39" t="s">
         <v>6</v>
@@ -3330,104 +3350,104 @@
         <v>7</v>
       </c>
       <c r="N39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O39" t="s">
         <v>0</v>
       </c>
-      <c r="P39" s="1">
-        <v>3213390</v>
+      <c r="P39">
+        <v>0</v>
       </c>
       <c r="Q39" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>59480507</v>
+        <v>59541145</v>
       </c>
       <c r="B40" s="2">
-        <v>46087.544247685182</v>
+        <v>46088.634837962964</v>
       </c>
       <c r="C40">
-        <v>63178769</v>
+        <v>63319529</v>
       </c>
       <c r="D40" s="2">
-        <v>46154.730057870373</v>
+        <v>46157.520046296297</v>
       </c>
       <c r="E40" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F40" t="s">
-        <v>128</v>
+        <v>248</v>
       </c>
       <c r="G40">
-        <v>708547070</v>
+        <v>546008131</v>
       </c>
       <c r="H40" t="s">
-        <v>73</v>
+        <v>249</v>
       </c>
       <c r="I40" t="s">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K40" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L40" t="s">
-        <v>2</v>
+        <v>188</v>
       </c>
       <c r="M40" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N40" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O40" t="s">
         <v>0</v>
       </c>
-      <c r="P40" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>2721712020</v>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>59537755</v>
+        <v>59606122</v>
       </c>
       <c r="B41" s="2">
-        <v>46088.586631944447</v>
+        <v>46090.447604166664</v>
       </c>
       <c r="C41">
-        <v>61591841</v>
+        <v>61897702</v>
       </c>
       <c r="D41" s="2">
-        <v>46127.35796296296</v>
+        <v>46132.349363425928</v>
       </c>
       <c r="E41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="G41">
-        <v>556331131</v>
+        <v>708454305</v>
       </c>
       <c r="H41" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="I41">
-        <v>1843236</v>
+        <v>1842206</v>
       </c>
       <c r="J41" t="s">
         <v>4</v>
       </c>
       <c r="K41" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L41" t="s">
         <v>6</v>
@@ -3436,7 +3456,7 @@
         <v>7</v>
       </c>
       <c r="N41" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O41" t="s">
         <v>0</v>
@@ -3445,33 +3465,33 @@
         <v>0</v>
       </c>
       <c r="Q41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>59541145</v>
+        <v>59615935</v>
       </c>
       <c r="B42" s="2">
-        <v>46088.634837962964</v>
+        <v>46090.512303240743</v>
       </c>
       <c r="C42">
-        <v>63179943</v>
+        <v>60393405</v>
       </c>
       <c r="D42" s="2">
-        <v>46154.7421412037</v>
+        <v>46105.432800925926</v>
       </c>
       <c r="E42" t="s">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>262</v>
+        <v>129</v>
       </c>
       <c r="G42">
-        <v>546008131</v>
+        <v>767081456</v>
       </c>
       <c r="H42" t="s">
-        <v>263</v>
+        <v>130</v>
       </c>
       <c r="I42" t="s">
         <v>0</v>
@@ -3480,16 +3500,16 @@
         <v>13</v>
       </c>
       <c r="K42" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L42" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="M42" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O42" t="s">
         <v>0</v>
@@ -3498,86 +3518,86 @@
         <v>0</v>
       </c>
       <c r="Q42" t="s">
-        <v>229</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>59606122</v>
+        <v>59684312</v>
       </c>
       <c r="B43" s="2">
-        <v>46090.447604166664</v>
+        <v>46091.557453703703</v>
       </c>
       <c r="C43">
-        <v>61897702</v>
+        <v>63319047</v>
       </c>
       <c r="D43" s="2">
-        <v>46132.349363425928</v>
+        <v>46157.516157407408</v>
       </c>
       <c r="E43" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F43" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G43">
-        <v>708454305</v>
+        <v>3130227350</v>
       </c>
       <c r="H43" t="s">
-        <v>169</v>
-      </c>
-      <c r="I43">
-        <v>1842206</v>
+        <v>132</v>
+      </c>
+      <c r="I43" t="s">
+        <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K43" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="L43" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M43" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N43" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O43" t="s">
         <v>0</v>
       </c>
-      <c r="P43">
+      <c r="P43" t="s">
         <v>0</v>
       </c>
       <c r="Q43" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>59615935</v>
+        <v>59894743</v>
       </c>
       <c r="B44" s="2">
-        <v>46090.512303240743</v>
+        <v>46094.687673611108</v>
       </c>
       <c r="C44">
-        <v>60393405</v>
+        <v>63466178</v>
       </c>
       <c r="D44" s="2">
-        <v>46105.432800925926</v>
+        <v>46160.561516203707</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>263</v>
       </c>
       <c r="F44" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G44">
-        <v>767081456</v>
+        <v>759668146</v>
       </c>
       <c r="H44" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="I44" t="s">
         <v>0</v>
@@ -3592,98 +3612,98 @@
         <v>6</v>
       </c>
       <c r="M44" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N44" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O44" t="s">
         <v>0</v>
       </c>
-      <c r="P44">
+      <c r="P44" t="s">
         <v>0</v>
       </c>
       <c r="Q44" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>59684312</v>
+        <v>60356605</v>
       </c>
       <c r="B45" s="2">
-        <v>46091.557453703703</v>
+        <v>46104.623726851853</v>
       </c>
       <c r="C45">
-        <v>63202931</v>
+        <v>63346092</v>
       </c>
       <c r="D45" s="2">
-        <v>46155.444965277777</v>
+        <v>46157.73097222222</v>
       </c>
       <c r="E45" t="s">
-        <v>225</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G45">
-        <v>3130227350</v>
+        <v>504001081</v>
       </c>
       <c r="H45" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I45" t="s">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L45" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M45" t="s">
         <v>3</v>
       </c>
       <c r="N45" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O45" t="s">
         <v>0</v>
       </c>
       <c r="P45" t="s">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="Q45" t="s">
-        <v>31</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>59894743</v>
+        <v>60748674</v>
       </c>
       <c r="B46" s="2">
-        <v>46094.687673611108</v>
+        <v>46111.511504629627</v>
       </c>
       <c r="C46">
-        <v>63114345</v>
+        <v>62475433</v>
       </c>
       <c r="D46" s="2">
-        <v>46153.703321759262</v>
+        <v>46141.624513888892</v>
       </c>
       <c r="E46" t="s">
-        <v>231</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G46">
-        <v>759668146</v>
+        <v>767791237</v>
       </c>
       <c r="H46" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="I46" t="s">
         <v>0</v>
@@ -3701,166 +3721,166 @@
         <v>7</v>
       </c>
       <c r="N46" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O46" t="s">
         <v>0</v>
       </c>
-      <c r="P46" t="s">
+      <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>60026486</v>
+        <v>60972166</v>
       </c>
       <c r="B47" s="2">
-        <v>46098.36173611111</v>
+        <v>46114.708020833335</v>
       </c>
       <c r="C47">
-        <v>63232663</v>
+        <v>62949578</v>
       </c>
       <c r="D47" s="2">
-        <v>46155.672986111109</v>
+        <v>46150.482407407406</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G47">
-        <v>506727287</v>
+        <v>160128782</v>
       </c>
       <c r="H47" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="I47" t="s">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K47" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="L47" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M47" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N47" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O47" t="s">
         <v>0</v>
       </c>
-      <c r="P47">
-        <v>0</v>
+      <c r="P47" s="1">
+        <v>800000</v>
       </c>
       <c r="Q47" t="s">
-        <v>193</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>60356605</v>
+        <v>61220160</v>
       </c>
       <c r="B48" s="2">
-        <v>46104.623726851853</v>
+        <v>46120.483368055553</v>
       </c>
       <c r="C48">
-        <v>63216655</v>
+        <v>63331281</v>
       </c>
       <c r="D48" s="2">
-        <v>46155.55027777778</v>
+        <v>46157.621018518519</v>
       </c>
       <c r="E48" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="F48" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G48">
-        <v>504001081</v>
+        <v>102571205</v>
       </c>
       <c r="H48" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="I48" t="s">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K48" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L48" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M48" t="s">
         <v>3</v>
       </c>
       <c r="N48" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O48" t="s">
         <v>0</v>
       </c>
-      <c r="P48" t="s">
-        <v>140</v>
+      <c r="P48" s="1">
+        <v>5000000</v>
       </c>
       <c r="Q48" t="s">
-        <v>264</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>60748674</v>
+        <v>61239047</v>
       </c>
       <c r="B49" s="2">
-        <v>46111.511504629627</v>
+        <v>46120.622071759259</v>
       </c>
       <c r="C49">
-        <v>62475433</v>
+        <v>63445965</v>
       </c>
       <c r="D49" s="2">
-        <v>46141.624513888892</v>
+        <v>46160.400810185187</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
+        <v>264</v>
       </c>
       <c r="F49" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G49">
-        <v>767791237</v>
+        <v>103381121</v>
       </c>
       <c r="H49" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I49" t="s">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="K49" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L49" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M49" t="s">
         <v>7</v>
       </c>
       <c r="N49" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O49" t="s">
         <v>0</v>
@@ -3869,148 +3889,148 @@
         <v>0</v>
       </c>
       <c r="Q49" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>60972166</v>
+        <v>61240327</v>
       </c>
       <c r="B50" s="2">
-        <v>46114.708020833335</v>
+        <v>46120.631747685184</v>
       </c>
       <c r="C50">
-        <v>62949578</v>
+        <v>61667960</v>
       </c>
       <c r="D50" s="2">
-        <v>46150.482407407406</v>
+        <v>46128.415625000001</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G50">
-        <v>160128782</v>
+        <v>103381121</v>
       </c>
       <c r="H50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I50" t="s">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="K50" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L50" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M50" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N50" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O50" t="s">
         <v>0</v>
       </c>
-      <c r="P50" s="1">
-        <v>800000</v>
+      <c r="P50">
+        <v>0</v>
       </c>
       <c r="Q50" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>61220160</v>
+        <v>61240462</v>
       </c>
       <c r="B51" s="2">
-        <v>46120.483368055553</v>
+        <v>46120.632835648146</v>
       </c>
       <c r="C51">
-        <v>63199072</v>
+        <v>63458663</v>
       </c>
       <c r="D51" s="2">
-        <v>46155.413194444445</v>
+        <v>46160.499895833331</v>
       </c>
       <c r="E51" t="s">
-        <v>190</v>
+        <v>264</v>
       </c>
       <c r="F51" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G51">
-        <v>102571205</v>
+        <v>769218598</v>
       </c>
       <c r="H51" t="s">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="I51" t="s">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="K51" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L51" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M51" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O51" t="s">
         <v>0</v>
       </c>
-      <c r="P51" s="1">
-        <v>5000000</v>
+      <c r="P51" t="s">
+        <v>0</v>
       </c>
       <c r="Q51" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>61239047</v>
+        <v>61242033</v>
       </c>
       <c r="B52" s="2">
-        <v>46120.622071759259</v>
+        <v>46120.643912037034</v>
       </c>
       <c r="C52">
-        <v>62739005</v>
+        <v>62945857</v>
       </c>
       <c r="D52" s="2">
-        <v>46147.407546296294</v>
+        <v>46150.456064814818</v>
       </c>
       <c r="E52" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
         <v>154</v>
       </c>
       <c r="G52">
-        <v>103381121</v>
+        <v>747636152</v>
       </c>
       <c r="H52" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="I52" t="s">
         <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K52" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L52" t="s">
         <v>2</v>
@@ -4019,7 +4039,7 @@
         <v>7</v>
       </c>
       <c r="N52" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O52" t="s">
         <v>0</v>
@@ -4028,39 +4048,39 @@
         <v>0</v>
       </c>
       <c r="Q52" t="s">
-        <v>171</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>61240327</v>
+        <v>61243441</v>
       </c>
       <c r="B53" s="2">
-        <v>46120.631747685184</v>
+        <v>46120.652592592596</v>
       </c>
       <c r="C53">
-        <v>61667960</v>
+        <v>62945141</v>
       </c>
       <c r="D53" s="2">
-        <v>46128.415625000001</v>
+        <v>46150.449965277781</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
         <v>154</v>
       </c>
       <c r="G53">
-        <v>103381121</v>
+        <v>747636152</v>
       </c>
       <c r="H53" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="I53" t="s">
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K53" t="s">
         <v>1</v>
@@ -4072,7 +4092,7 @@
         <v>7</v>
       </c>
       <c r="N53" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O53" t="s">
         <v>0</v>
@@ -4081,39 +4101,39 @@
         <v>0</v>
       </c>
       <c r="Q53" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>61240462</v>
+        <v>61244524</v>
       </c>
       <c r="B54" s="2">
-        <v>46120.632835648146</v>
+        <v>46120.66065972222</v>
       </c>
       <c r="C54">
-        <v>62739244</v>
+        <v>62308856</v>
       </c>
       <c r="D54" s="2">
-        <v>46147.409062500003</v>
+        <v>46139.393194444441</v>
       </c>
       <c r="E54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F54" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G54">
-        <v>769218598</v>
+        <v>757818829</v>
       </c>
       <c r="H54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I54" t="s">
         <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K54" t="s">
         <v>27</v>
@@ -4125,7 +4145,7 @@
         <v>7</v>
       </c>
       <c r="N54" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O54" t="s">
         <v>0</v>
@@ -4134,39 +4154,39 @@
         <v>0</v>
       </c>
       <c r="Q54" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>61242033</v>
+        <v>61248751</v>
       </c>
       <c r="B55" s="2">
-        <v>46120.643912037034</v>
+        <v>46120.692800925928</v>
       </c>
       <c r="C55">
-        <v>62945857</v>
+        <v>63444825</v>
       </c>
       <c r="D55" s="2">
-        <v>46150.456064814818</v>
+        <v>46160.387303240743</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="F55" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G55">
         <v>747636152</v>
       </c>
       <c r="H55" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="I55" t="s">
         <v>0</v>
       </c>
       <c r="J55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K55" t="s">
         <v>1</v>
@@ -4178,7 +4198,7 @@
         <v>7</v>
       </c>
       <c r="N55" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O55" t="s">
         <v>0</v>
@@ -4187,51 +4207,51 @@
         <v>0</v>
       </c>
       <c r="Q55" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>61243441</v>
+        <v>61255901</v>
       </c>
       <c r="B56" s="2">
-        <v>46120.652592592596</v>
+        <v>46120.75712962963</v>
       </c>
       <c r="C56">
-        <v>62945141</v>
+        <v>62951388</v>
       </c>
       <c r="D56" s="2">
-        <v>46150.449965277781</v>
+        <v>46150.494675925926</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G56">
-        <v>747636152</v>
+        <v>757818829</v>
       </c>
       <c r="H56" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="I56" t="s">
         <v>0</v>
       </c>
       <c r="J56" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="K56" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L56" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M56" t="s">
         <v>7</v>
       </c>
       <c r="N56" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O56" t="s">
         <v>0</v>
@@ -4240,51 +4260,51 @@
         <v>0</v>
       </c>
       <c r="Q56" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>61244524</v>
+        <v>61315991</v>
       </c>
       <c r="B57" s="2">
-        <v>46120.66065972222</v>
+        <v>46121.743379629632</v>
       </c>
       <c r="C57">
-        <v>62308856</v>
+        <v>62807088</v>
       </c>
       <c r="D57" s="2">
-        <v>46139.393194444441</v>
+        <v>46148.392731481479</v>
       </c>
       <c r="E57" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G57">
-        <v>757818829</v>
+        <v>778495680</v>
       </c>
       <c r="H57" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="I57" t="s">
         <v>0</v>
       </c>
       <c r="J57" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K57" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L57" t="s">
         <v>2</v>
       </c>
       <c r="M57" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N57" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O57" t="s">
         <v>0</v>
@@ -4293,89 +4313,92 @@
         <v>0</v>
       </c>
       <c r="Q57" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>61248751</v>
+        <v>61336527</v>
       </c>
       <c r="B58" s="2">
-        <v>46120.692800925928</v>
+        <v>46122.368761574071</v>
       </c>
       <c r="C58">
-        <v>62775261</v>
+        <v>62807025</v>
       </c>
       <c r="D58" s="2">
-        <v>46147.656886574077</v>
+        <v>46148.392222222225</v>
       </c>
       <c r="E58" t="s">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="F58" t="s">
+        <v>158</v>
+      </c>
+      <c r="G58">
+        <v>778495680</v>
+      </c>
+      <c r="H58" t="s">
         <v>157</v>
       </c>
-      <c r="G58">
-        <v>747636152</v>
-      </c>
-      <c r="H58" t="s">
-        <v>120</v>
-      </c>
       <c r="I58" t="s">
         <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="K58" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L58" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M58" t="s">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="N58" t="s">
+        <v>121</v>
       </c>
       <c r="O58" t="s">
         <v>0</v>
       </c>
-      <c r="P58">
-        <v>0</v>
+      <c r="P58" s="1">
+        <v>1679940</v>
       </c>
       <c r="Q58" t="s">
-        <v>230</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>61254924</v>
+        <v>61481328</v>
       </c>
       <c r="B59" s="2">
-        <v>46120.74763888889</v>
+        <v>46125.483310185184</v>
       </c>
       <c r="C59">
-        <v>63209008</v>
+        <v>62173555</v>
       </c>
       <c r="D59" s="2">
-        <v>46155.489004629628</v>
+        <v>46136.44263888889</v>
       </c>
       <c r="E59" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="F59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G59">
-        <v>757818829</v>
+        <v>708448800</v>
       </c>
       <c r="H59" t="s">
-        <v>78</v>
-      </c>
-      <c r="I59" t="s">
-        <v>0</v>
+        <v>189</v>
+      </c>
+      <c r="I59">
+        <v>1891736</v>
       </c>
       <c r="J59" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s">
         <v>9</v>
@@ -4384,45 +4407,45 @@
         <v>8</v>
       </c>
       <c r="M59" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N59" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O59" t="s">
         <v>0</v>
       </c>
-      <c r="P59">
-        <v>0</v>
+      <c r="P59" s="1">
+        <v>500000</v>
       </c>
       <c r="Q59" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>61255381</v>
+        <v>61504448</v>
       </c>
       <c r="B60" s="2">
-        <v>46120.752291666664</v>
+        <v>46125.648935185185</v>
       </c>
       <c r="C60">
-        <v>62970699</v>
+        <v>62115179</v>
       </c>
       <c r="D60" s="2">
-        <v>46150.658067129632</v>
+        <v>46135.481111111112</v>
       </c>
       <c r="E60" t="s">
-        <v>231</v>
+        <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="G60">
-        <v>757818829</v>
+        <v>707234610</v>
       </c>
       <c r="H60" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="I60" t="s">
         <v>0</v>
@@ -4434,213 +4457,213 @@
         <v>5</v>
       </c>
       <c r="L60" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M60" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N60" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O60" t="s">
         <v>0</v>
       </c>
-      <c r="P60">
-        <v>0</v>
+      <c r="P60" s="1">
+        <v>3070672</v>
       </c>
       <c r="Q60" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>61255901</v>
+        <v>61509953</v>
       </c>
       <c r="B61" s="2">
-        <v>46120.75712962963</v>
+        <v>46125.694004629629</v>
       </c>
       <c r="C61">
-        <v>62951388</v>
+        <v>62751418</v>
       </c>
       <c r="D61" s="2">
-        <v>46150.494675925926</v>
+        <v>46147.490636574075</v>
       </c>
       <c r="E61" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="F61" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G61">
-        <v>757818829</v>
+        <v>759379440</v>
       </c>
       <c r="H61" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="I61" t="s">
         <v>0</v>
       </c>
       <c r="J61" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K61" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L61" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M61" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N61" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O61" t="s">
         <v>0</v>
       </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>77</v>
+      <c r="P61" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>2732780110</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>61315991</v>
+        <v>61560663</v>
       </c>
       <c r="B62" s="2">
-        <v>46121.743379629632</v>
+        <v>46126.615729166668</v>
       </c>
       <c r="C62">
-        <v>62807088</v>
+        <v>62946623</v>
       </c>
       <c r="D62" s="2">
-        <v>46148.392731481479</v>
+        <v>46150.461550925924</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G62">
-        <v>778495680</v>
+        <v>707984429</v>
       </c>
       <c r="H62" t="s">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="I62" t="s">
         <v>0</v>
       </c>
       <c r="J62" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K62" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L62" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M62" t="s">
         <v>3</v>
       </c>
       <c r="N62" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O62" t="s">
         <v>0</v>
       </c>
-      <c r="P62" t="s">
-        <v>0</v>
+      <c r="P62" s="1">
+        <v>2984038</v>
       </c>
       <c r="Q62" t="s">
-        <v>115</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>61336527</v>
+        <v>61608637</v>
       </c>
       <c r="B63" s="2">
-        <v>46122.368761574071</v>
+        <v>46127.491550925923</v>
       </c>
       <c r="C63">
-        <v>62807025</v>
+        <v>61677257</v>
       </c>
       <c r="D63" s="2">
-        <v>46148.392222222225</v>
+        <v>46128.483958333331</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="F63" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="G63">
-        <v>778495680</v>
+        <v>702455701</v>
       </c>
       <c r="H63" t="s">
-        <v>160</v>
+        <v>37</v>
       </c>
       <c r="I63" t="s">
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K63" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L63" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M63" t="s">
         <v>3</v>
       </c>
       <c r="N63" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O63" t="s">
         <v>0</v>
       </c>
-      <c r="P63" s="1">
-        <v>1679940</v>
+      <c r="P63" t="s">
+        <v>0</v>
       </c>
       <c r="Q63" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>61481328</v>
+        <v>61644382</v>
       </c>
       <c r="B64" s="2">
-        <v>46125.483310185184</v>
+        <v>46127.754131944443</v>
       </c>
       <c r="C64">
-        <v>62173555</v>
+        <v>61977733</v>
       </c>
       <c r="D64" s="2">
-        <v>46136.44263888889</v>
+        <v>46133.466458333336</v>
       </c>
       <c r="E64" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="G64">
-        <v>708448800</v>
+        <v>759250737</v>
       </c>
       <c r="H64" t="s">
-        <v>194</v>
-      </c>
-      <c r="I64">
-        <v>1891736</v>
+        <v>177</v>
+      </c>
+      <c r="I64" t="s">
+        <v>0</v>
       </c>
       <c r="J64" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K64" t="s">
         <v>9</v>
@@ -4652,225 +4675,225 @@
         <v>3</v>
       </c>
       <c r="N64" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O64" t="s">
         <v>0</v>
       </c>
       <c r="P64" s="1">
-        <v>500000</v>
+        <v>1680307</v>
       </c>
       <c r="Q64" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>61504448</v>
+        <v>61700587</v>
       </c>
       <c r="B65" s="2">
-        <v>46125.648935185185</v>
+        <v>46128.642256944448</v>
       </c>
       <c r="C65">
-        <v>62115179</v>
+        <v>63460926</v>
       </c>
       <c r="D65" s="2">
-        <v>46135.481111111112</v>
+        <v>46160.51457175926</v>
       </c>
       <c r="E65" t="s">
-        <v>10</v>
+        <v>186</v>
       </c>
       <c r="F65" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G65">
-        <v>707234610</v>
+        <v>747568798</v>
       </c>
       <c r="H65" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="I65" t="s">
         <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K65" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L65" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M65" t="s">
         <v>3</v>
       </c>
       <c r="N65" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O65" t="s">
         <v>0</v>
       </c>
-      <c r="P65" s="1">
-        <v>3070672</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>12</v>
+      <c r="P65" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>2722419000</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>61507701</v>
+        <v>61710072</v>
       </c>
       <c r="B66" s="2">
-        <v>46125.672951388886</v>
+        <v>46128.708032407405</v>
       </c>
       <c r="C66">
-        <v>62020006</v>
+        <v>62110207</v>
       </c>
       <c r="D66" s="2">
-        <v>46133.777349537035</v>
+        <v>46135.445254629631</v>
       </c>
       <c r="E66" t="s">
-        <v>258</v>
+        <v>94</v>
       </c>
       <c r="F66" t="s">
-        <v>265</v>
+        <v>181</v>
       </c>
       <c r="G66">
-        <v>707906003</v>
+        <v>584425796</v>
       </c>
       <c r="H66" t="s">
-        <v>266</v>
-      </c>
-      <c r="I66" t="s">
+        <v>182</v>
+      </c>
+      <c r="I66">
         <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K66" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L66" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M66" t="s">
         <v>3</v>
       </c>
       <c r="N66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O66" t="s">
         <v>0</v>
       </c>
-      <c r="P66" s="1">
-        <v>596888</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>267</v>
+      <c r="P66" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>2721711717</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>61509953</v>
+        <v>61828334</v>
       </c>
       <c r="B67" s="2">
-        <v>46125.694004629629</v>
+        <v>46130.562754629631</v>
       </c>
       <c r="C67">
-        <v>62751418</v>
+        <v>62208296</v>
       </c>
       <c r="D67" s="2">
-        <v>46147.490636574075</v>
+        <v>46136.716527777775</v>
       </c>
       <c r="E67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F67" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G67">
-        <v>759379440</v>
+        <v>747309803</v>
       </c>
       <c r="H67" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="I67" t="s">
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K67" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L67" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M67" t="s">
         <v>3</v>
       </c>
       <c r="N67" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O67" t="s">
         <v>0</v>
       </c>
-      <c r="P67" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>2732780110</v>
+      <c r="P67" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>61560663</v>
+        <v>61946442</v>
       </c>
       <c r="B68" s="2">
-        <v>46126.615729166668</v>
+        <v>46132.704247685186</v>
       </c>
       <c r="C68">
-        <v>62946623</v>
+        <v>62946744</v>
       </c>
       <c r="D68" s="2">
-        <v>46150.461550925924</v>
+        <v>46150.462650462963</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
       </c>
       <c r="F68" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="G68">
-        <v>707984429</v>
+        <v>504041812</v>
       </c>
       <c r="H68" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="I68" t="s">
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
       </c>
       <c r="L68" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M68" t="s">
         <v>3</v>
       </c>
       <c r="N68" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O68" t="s">
         <v>0</v>
       </c>
       <c r="P68" s="1">
-        <v>2984038</v>
+        <v>1000000</v>
       </c>
       <c r="Q68" t="s">
         <v>24</v>
@@ -4878,46 +4901,46 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>61608637</v>
+        <v>61972088</v>
       </c>
       <c r="B69" s="2">
-        <v>46127.491550925923</v>
+        <v>46133.422569444447</v>
       </c>
       <c r="C69">
-        <v>61677257</v>
+        <v>62868217</v>
       </c>
       <c r="D69" s="2">
-        <v>46128.483958333331</v>
+        <v>46149.240729166668</v>
       </c>
       <c r="E69" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="F69" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="G69">
-        <v>702455701</v>
+        <v>504041812</v>
       </c>
       <c r="H69" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="I69" t="s">
         <v>0</v>
       </c>
       <c r="J69" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K69" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L69" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M69" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N69" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O69" t="s">
         <v>0</v>
@@ -4926,33 +4949,33 @@
         <v>0</v>
       </c>
       <c r="Q69" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>61644382</v>
+        <v>61972108</v>
       </c>
       <c r="B70" s="2">
-        <v>46127.754131944443</v>
+        <v>46133.422662037039</v>
       </c>
       <c r="C70">
-        <v>61977733</v>
+        <v>62946845</v>
       </c>
       <c r="D70" s="2">
-        <v>46133.466458333336</v>
+        <v>46150.463449074072</v>
       </c>
       <c r="E70" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="G70">
-        <v>759250737</v>
+        <v>504041812</v>
       </c>
       <c r="H70" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="I70" t="s">
         <v>0</v>
@@ -4961,334 +4984,334 @@
         <v>18</v>
       </c>
       <c r="K70" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L70" t="s">
         <v>8</v>
       </c>
       <c r="M70" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N70" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O70" t="s">
         <v>0</v>
       </c>
       <c r="P70" s="1">
-        <v>1680307</v>
+        <v>1000000</v>
       </c>
       <c r="Q70" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>61700587</v>
+        <v>62014200</v>
       </c>
       <c r="B71" s="2">
-        <v>46128.642256944448</v>
+        <v>46133.721585648149</v>
       </c>
       <c r="C71">
-        <v>63211249</v>
+        <v>63390600</v>
       </c>
       <c r="D71" s="2">
-        <v>46155.507719907408</v>
+        <v>46158.757106481484</v>
       </c>
       <c r="E71" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="F71" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="G71">
-        <v>747568798</v>
+        <v>709837321</v>
       </c>
       <c r="H71" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="I71" t="s">
         <v>0</v>
       </c>
       <c r="J71" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K71" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="L71" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M71" t="s">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="N71" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O71" t="s">
         <v>0</v>
       </c>
-      <c r="P71" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>2722419000</v>
+      <c r="P71" s="1">
+        <v>1644000</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>61702838</v>
+        <v>62170297</v>
       </c>
       <c r="B72" s="2">
-        <v>46128.658946759257</v>
+        <v>46136.420717592591</v>
       </c>
       <c r="C72">
-        <v>63177655</v>
+        <v>63338150</v>
       </c>
       <c r="D72" s="2">
-        <v>46154.719328703701</v>
+        <v>46157.670335648145</v>
       </c>
       <c r="E72" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="F72" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="G72">
-        <v>747568798</v>
+        <v>546016502</v>
       </c>
       <c r="H72" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="I72" t="s">
         <v>0</v>
       </c>
       <c r="J72" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K72" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="L72" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M72" t="s">
         <v>3</v>
       </c>
       <c r="N72" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O72" t="s">
         <v>0</v>
       </c>
-      <c r="P72" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>2734710371</v>
+      <c r="P72" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>61710072</v>
+        <v>62243628</v>
       </c>
       <c r="B73" s="2">
-        <v>46128.708032407405</v>
+        <v>46137.617604166669</v>
       </c>
       <c r="C73">
-        <v>62110207</v>
+        <v>63197211</v>
       </c>
       <c r="D73" s="2">
-        <v>46135.445254629631</v>
+        <v>46155.393680555557</v>
       </c>
       <c r="E73" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F73" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G73">
-        <v>584425796</v>
+        <v>779191985</v>
       </c>
       <c r="H73" t="s">
-        <v>186</v>
-      </c>
-      <c r="I73">
+        <v>251</v>
+      </c>
+      <c r="I73" t="s">
         <v>0</v>
       </c>
       <c r="J73" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K73" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L73" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M73" t="s">
         <v>3</v>
       </c>
       <c r="N73" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O73" t="s">
         <v>0</v>
       </c>
-      <c r="P73" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>2721711717</v>
+      <c r="P73" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>61828334</v>
+        <v>62249046</v>
       </c>
       <c r="B74" s="2">
-        <v>46130.562754629631</v>
+        <v>46137.688391203701</v>
       </c>
       <c r="C74">
-        <v>62208296</v>
+        <v>63239713</v>
       </c>
       <c r="D74" s="2">
-        <v>46136.716527777775</v>
+        <v>46155.72347222222</v>
       </c>
       <c r="E74" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F74" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="G74">
-        <v>747309803</v>
+        <v>708946683</v>
       </c>
       <c r="H74" t="s">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="I74" t="s">
         <v>0</v>
       </c>
       <c r="J74" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K74" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L74" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M74" t="s">
         <v>3</v>
       </c>
       <c r="N74" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O74" t="s">
         <v>0</v>
       </c>
-      <c r="P74" s="1">
-        <v>1000000</v>
+      <c r="P74" t="s">
+        <v>0</v>
       </c>
       <c r="Q74" t="s">
-        <v>196</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>61946442</v>
+        <v>62420329</v>
       </c>
       <c r="B75" s="2">
-        <v>46132.704247685186</v>
+        <v>46140.709513888891</v>
       </c>
       <c r="C75">
-        <v>62946744</v>
+        <v>63331641</v>
       </c>
       <c r="D75" s="2">
-        <v>46150.462650462963</v>
+        <v>46157.623310185183</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G75">
-        <v>504041812</v>
+        <v>777621987</v>
       </c>
       <c r="H75" t="s">
-        <v>198</v>
+        <v>125</v>
       </c>
       <c r="I75" t="s">
         <v>0</v>
       </c>
       <c r="J75" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
       </c>
       <c r="L75" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M75" t="s">
         <v>3</v>
       </c>
       <c r="N75" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O75" t="s">
         <v>0</v>
       </c>
       <c r="P75" s="1">
-        <v>1000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q75" t="s">
-        <v>24</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>61972088</v>
+        <v>62497009</v>
       </c>
       <c r="B76" s="2">
-        <v>46133.422569444447</v>
+        <v>46141.808842592596</v>
       </c>
       <c r="C76">
-        <v>62868217</v>
+        <v>63458983</v>
       </c>
       <c r="D76" s="2">
-        <v>46149.240729166668</v>
+        <v>46160.501875000002</v>
       </c>
       <c r="E76" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="F76" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G76">
-        <v>504041812</v>
+        <v>702495660</v>
       </c>
       <c r="H76" t="s">
-        <v>198</v>
+        <v>37</v>
       </c>
       <c r="I76" t="s">
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K76" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L76" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M76" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N76" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O76" t="s">
         <v>0</v>
@@ -5296,34 +5319,34 @@
       <c r="P76" t="s">
         <v>0</v>
       </c>
-      <c r="Q76" t="s">
-        <v>24</v>
+      <c r="Q76">
+        <v>2722560060</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>61972108</v>
+        <v>62544794</v>
       </c>
       <c r="B77" s="2">
-        <v>46133.422662037039</v>
+        <v>46142.662094907406</v>
       </c>
       <c r="C77">
-        <v>62946845</v>
+        <v>63208263</v>
       </c>
       <c r="D77" s="2">
-        <v>46150.463449074072</v>
+        <v>46155.483206018522</v>
       </c>
       <c r="E77" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F77" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G77">
-        <v>504041812</v>
+        <v>142128888</v>
       </c>
       <c r="H77" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I77" t="s">
         <v>0</v>
@@ -5332,157 +5355,154 @@
         <v>18</v>
       </c>
       <c r="K77" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L77" t="s">
         <v>8</v>
       </c>
       <c r="M77" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N77" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O77" t="s">
         <v>0</v>
       </c>
       <c r="P77" s="1">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="Q77" t="s">
-        <v>112</v>
+        <v>225</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>62014200</v>
+        <v>62551370</v>
       </c>
       <c r="B78" s="2">
-        <v>46133.721585648149</v>
+        <v>46142.717349537037</v>
       </c>
       <c r="C78">
-        <v>63198452</v>
+        <v>63134483</v>
       </c>
       <c r="D78" s="2">
-        <v>46155.40662037037</v>
+        <v>46154.380196759259</v>
       </c>
       <c r="E78" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="F78" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G78">
-        <v>709837321</v>
+        <v>576382850</v>
       </c>
       <c r="H78" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="I78" t="s">
         <v>0</v>
       </c>
       <c r="J78" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K78" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>178</v>
-      </c>
-      <c r="N78" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="O78" t="s">
         <v>0</v>
       </c>
-      <c r="P78" s="1">
-        <v>1644000</v>
+      <c r="P78" t="s">
+        <v>0</v>
       </c>
       <c r="Q78" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>62170297</v>
+        <v>62672227</v>
       </c>
       <c r="B79" s="2">
-        <v>46136.420717592591</v>
+        <v>46146.403935185182</v>
       </c>
       <c r="C79">
-        <v>63207480</v>
+        <v>63331081</v>
       </c>
       <c r="D79" s="2">
-        <v>46155.47861111111</v>
+        <v>46157.619120370371</v>
       </c>
       <c r="E79" t="s">
-        <v>268</v>
+        <v>10</v>
       </c>
       <c r="F79" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G79">
-        <v>546016502</v>
+        <v>707169322</v>
       </c>
       <c r="H79" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I79" t="s">
         <v>0</v>
       </c>
       <c r="J79" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
       </c>
       <c r="L79" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M79" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N79" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O79" t="s">
         <v>0</v>
       </c>
-      <c r="P79" s="1">
-        <v>1500000</v>
+      <c r="P79" t="s">
+        <v>0</v>
       </c>
       <c r="Q79" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>62241651</v>
+        <v>62672234</v>
       </c>
       <c r="B80" s="2">
-        <v>46137.593402777777</v>
+        <v>46146.403969907406</v>
       </c>
       <c r="C80">
-        <v>63197022</v>
+        <v>63346032</v>
       </c>
       <c r="D80" s="2">
-        <v>46155.39166666667</v>
+        <v>46157.730034722219</v>
       </c>
       <c r="E80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F80" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G80">
-        <v>707678205</v>
+        <v>707169322</v>
       </c>
       <c r="H80" t="s">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="I80" t="s">
         <v>0</v>
@@ -5491,104 +5511,104 @@
         <v>13</v>
       </c>
       <c r="K80" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L80" t="s">
         <v>6</v>
       </c>
       <c r="M80" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N80" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O80" t="s">
         <v>0</v>
       </c>
       <c r="P80" s="1">
-        <v>500000</v>
+        <v>1644000</v>
       </c>
       <c r="Q80" t="s">
-        <v>34</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>62243628</v>
+        <v>62680657</v>
       </c>
       <c r="B81" s="2">
-        <v>46137.617604166669</v>
+        <v>46146.475763888891</v>
       </c>
       <c r="C81">
-        <v>63197211</v>
+        <v>63316862</v>
       </c>
       <c r="D81" s="2">
-        <v>46155.393680555557</v>
+        <v>46157.500787037039</v>
       </c>
       <c r="E81" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F81" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G81">
-        <v>779191985</v>
+        <v>778096389</v>
       </c>
       <c r="H81" t="s">
-        <v>269</v>
+        <v>210</v>
       </c>
       <c r="I81" t="s">
         <v>0</v>
       </c>
       <c r="J81" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="K81" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M81" t="s">
         <v>3</v>
       </c>
       <c r="N81" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O81" t="s">
         <v>0</v>
       </c>
-      <c r="P81" s="1">
-        <v>500000</v>
+      <c r="P81" t="s">
+        <v>0</v>
       </c>
       <c r="Q81" t="s">
-        <v>233</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>62249046</v>
+        <v>62682536</v>
       </c>
       <c r="B82" s="2">
-        <v>46137.688391203701</v>
+        <v>46146.490057870367</v>
       </c>
       <c r="C82">
-        <v>63174891</v>
+        <v>63060102</v>
       </c>
       <c r="D82" s="2">
-        <v>46154.695729166669</v>
+        <v>46152.915081018517</v>
       </c>
       <c r="E82" t="s">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="F82" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G82">
-        <v>708946683</v>
+        <v>789817770</v>
       </c>
       <c r="H82" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="I82" t="s">
         <v>0</v>
@@ -5606,95 +5626,95 @@
         <v>3</v>
       </c>
       <c r="N82" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O82" t="s">
         <v>0</v>
       </c>
-      <c r="P82" t="s">
-        <v>0</v>
+      <c r="P82" s="1">
+        <v>150000</v>
       </c>
       <c r="Q82" t="s">
-        <v>126</v>
+        <v>226</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>62420329</v>
+        <v>62715782</v>
       </c>
       <c r="B83" s="2">
-        <v>46140.709513888891</v>
+        <v>46146.73746527778</v>
       </c>
       <c r="C83">
-        <v>62868242</v>
+        <v>63315259</v>
       </c>
       <c r="D83" s="2">
-        <v>46149.243807870371</v>
+        <v>46157.490590277775</v>
       </c>
       <c r="E83" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="F83" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="G83">
-        <v>777621987</v>
+        <v>707366919</v>
       </c>
       <c r="H83" t="s">
-        <v>127</v>
+        <v>37</v>
       </c>
       <c r="I83" t="s">
         <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K83" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L83" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M83" t="s">
         <v>3</v>
       </c>
       <c r="N83" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O83" t="s">
         <v>0</v>
       </c>
-      <c r="P83" s="1">
-        <v>1500000</v>
+      <c r="P83" t="s">
+        <v>0</v>
       </c>
       <c r="Q83" t="s">
-        <v>234</v>
+        <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>62497009</v>
+        <v>62722805</v>
       </c>
       <c r="B84" s="2">
-        <v>46141.808842592596</v>
+        <v>46146.81181712963</v>
       </c>
       <c r="C84">
-        <v>63232906</v>
+        <v>63060104</v>
       </c>
       <c r="D84" s="2">
-        <v>46155.674166666664</v>
+        <v>46152.916122685187</v>
       </c>
       <c r="E84" t="s">
-        <v>271</v>
+        <v>19</v>
       </c>
       <c r="F84" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G84">
-        <v>702495660</v>
+        <v>708131488</v>
       </c>
       <c r="H84" t="s">
-        <v>37</v>
+        <v>215</v>
       </c>
       <c r="I84" t="s">
         <v>0</v>
@@ -5703,7 +5723,7 @@
         <v>22</v>
       </c>
       <c r="K84" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L84" t="s">
         <v>2</v>
@@ -5712,7 +5732,7 @@
         <v>3</v>
       </c>
       <c r="N84" t="s">
-        <v>270</v>
+        <v>121</v>
       </c>
       <c r="O84" t="s">
         <v>0</v>
@@ -5720,34 +5740,34 @@
       <c r="P84" t="s">
         <v>0</v>
       </c>
-      <c r="Q84">
-        <v>2722560060</v>
+      <c r="Q84" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>62544794</v>
+        <v>62748443</v>
       </c>
       <c r="B85" s="2">
-        <v>46142.662094907406</v>
+        <v>46147.475057870368</v>
       </c>
       <c r="C85">
-        <v>63208263</v>
+        <v>63451636</v>
       </c>
       <c r="D85" s="2">
-        <v>46155.483206018522</v>
+        <v>46160.451273148145</v>
       </c>
       <c r="E85" t="s">
-        <v>61</v>
+        <v>186</v>
       </c>
       <c r="F85" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="G85">
-        <v>142128888</v>
+        <v>757750210</v>
       </c>
       <c r="H85" t="s">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c r="I85" t="s">
         <v>0</v>
@@ -5756,7 +5776,7 @@
         <v>18</v>
       </c>
       <c r="K85" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L85" t="s">
         <v>8</v>
@@ -5765,42 +5785,42 @@
         <v>3</v>
       </c>
       <c r="N85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O85" t="s">
         <v>0</v>
       </c>
-      <c r="P85" s="1">
-        <v>500000</v>
+      <c r="P85">
+        <v>0</v>
       </c>
       <c r="Q85" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>62551370</v>
+        <v>62760027</v>
       </c>
       <c r="B86" s="2">
-        <v>46142.717349537037</v>
+        <v>46147.546493055554</v>
       </c>
       <c r="C86">
-        <v>63134483</v>
+        <v>62902869</v>
       </c>
       <c r="D86" s="2">
-        <v>46154.380196759259</v>
+        <v>46149.631921296299</v>
       </c>
       <c r="E86" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="F86" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="G86">
-        <v>576382850</v>
+        <v>777699799</v>
       </c>
       <c r="H86" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I86" t="s">
         <v>0</v>
@@ -5817,6 +5837,9 @@
       <c r="M86" t="s">
         <v>3</v>
       </c>
+      <c r="N86" t="s">
+        <v>121</v>
+      </c>
       <c r="O86" t="s">
         <v>0</v>
       </c>
@@ -5824,51 +5847,51 @@
         <v>0</v>
       </c>
       <c r="Q86" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>62672227</v>
+        <v>62768013</v>
       </c>
       <c r="B87" s="2">
-        <v>46146.403935185182</v>
+        <v>46147.609988425924</v>
       </c>
       <c r="C87">
-        <v>63060135</v>
+        <v>62871386</v>
       </c>
       <c r="D87" s="2">
-        <v>46152.917256944442</v>
+        <v>46149.364837962959</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="F87" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="G87">
-        <v>707169322</v>
+        <v>143270405</v>
       </c>
       <c r="H87" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="I87" t="s">
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K87" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L87" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M87" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N87" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O87" t="s">
         <v>0</v>
@@ -5877,33 +5900,33 @@
         <v>0</v>
       </c>
       <c r="Q87" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>62672234</v>
+        <v>62840921</v>
       </c>
       <c r="B88" s="2">
-        <v>46146.403969907406</v>
+        <v>46148.636331018519</v>
       </c>
       <c r="C88">
-        <v>63175077</v>
+        <v>63101235</v>
       </c>
       <c r="D88" s="2">
-        <v>46154.696747685186</v>
+        <v>46153.608599537038</v>
       </c>
       <c r="E88" t="s">
-        <v>119</v>
+        <v>253</v>
       </c>
       <c r="F88" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="G88">
-        <v>707169322</v>
+        <v>707551377</v>
       </c>
       <c r="H88" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="I88" t="s">
         <v>0</v>
@@ -5918,63 +5941,63 @@
         <v>6</v>
       </c>
       <c r="M88" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N88" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O88" t="s">
         <v>0</v>
       </c>
-      <c r="P88" s="1">
-        <v>1644000</v>
+      <c r="P88" t="s">
+        <v>0</v>
       </c>
       <c r="Q88" t="s">
-        <v>272</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>62680657</v>
+        <v>62880594</v>
       </c>
       <c r="B89" s="2">
-        <v>46146.475763888891</v>
+        <v>46149.454710648148</v>
       </c>
       <c r="C89">
-        <v>63209384</v>
+        <v>62941351</v>
       </c>
       <c r="D89" s="2">
-        <v>46155.492199074077</v>
+        <v>46150.416979166665</v>
       </c>
       <c r="E89" t="s">
-        <v>225</v>
+        <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="G89">
-        <v>778096389</v>
+        <v>709565662</v>
       </c>
       <c r="H89" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="I89" t="s">
         <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="K89" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L89" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M89" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N89" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O89" t="s">
         <v>0</v>
@@ -5983,86 +6006,86 @@
         <v>0</v>
       </c>
       <c r="Q89" t="s">
-        <v>60</v>
+        <v>237</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>62682536</v>
+        <v>62880628</v>
       </c>
       <c r="B90" s="2">
-        <v>46146.490057870367</v>
+        <v>46149.45484953704</v>
       </c>
       <c r="C90">
-        <v>63060102</v>
+        <v>62941416</v>
       </c>
       <c r="D90" s="2">
-        <v>46152.915081018517</v>
+        <v>46150.417719907404</v>
       </c>
       <c r="E90" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F90" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="G90">
-        <v>789817770</v>
+        <v>709565662</v>
       </c>
       <c r="H90" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I90" t="s">
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K90" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L90" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M90" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N90" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O90" t="s">
         <v>0</v>
       </c>
-      <c r="P90" s="1">
-        <v>150000</v>
+      <c r="P90">
+        <v>0</v>
       </c>
       <c r="Q90" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>62715782</v>
+        <v>62880812</v>
       </c>
       <c r="B91" s="2">
-        <v>46146.73746527778</v>
+        <v>46149.456157407411</v>
       </c>
       <c r="C91">
-        <v>63177364</v>
+        <v>63224093</v>
       </c>
       <c r="D91" s="2">
-        <v>46154.716550925928</v>
+        <v>46155.609270833331</v>
       </c>
       <c r="E91" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="F91" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="G91">
-        <v>707366919</v>
+        <v>707672487</v>
       </c>
       <c r="H91" t="s">
-        <v>37</v>
+        <v>239</v>
       </c>
       <c r="I91" t="s">
         <v>0</v>
@@ -6080,7 +6103,7 @@
         <v>3</v>
       </c>
       <c r="N91" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O91" t="s">
         <v>0</v>
@@ -6089,83 +6112,83 @@
         <v>0</v>
       </c>
       <c r="Q91" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>62722805</v>
+        <v>62937923</v>
       </c>
       <c r="B92" s="2">
-        <v>46146.81181712963</v>
+        <v>46150.381145833337</v>
       </c>
       <c r="C92">
-        <v>63060104</v>
+        <v>63342821</v>
       </c>
       <c r="D92" s="2">
-        <v>46152.916122685187</v>
+        <v>46157.705046296294</v>
       </c>
       <c r="E92" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F92" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="G92">
-        <v>708131488</v>
+        <v>565811689</v>
       </c>
       <c r="H92" t="s">
-        <v>221</v>
+        <v>37</v>
       </c>
       <c r="I92" t="s">
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K92" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L92" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M92" t="s">
         <v>3</v>
       </c>
       <c r="N92" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O92" t="s">
         <v>0</v>
       </c>
-      <c r="P92" t="s">
-        <v>0</v>
+      <c r="P92" s="1">
+        <v>250000</v>
       </c>
       <c r="Q92" t="s">
-        <v>115</v>
+        <v>266</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>62748443</v>
+        <v>62968196</v>
       </c>
       <c r="B93" s="2">
-        <v>46147.475057870368</v>
+        <v>46150.638715277775</v>
       </c>
       <c r="C93">
-        <v>63118824</v>
+        <v>63089942</v>
       </c>
       <c r="D93" s="2">
-        <v>46153.739791666667</v>
+        <v>46153.521840277775</v>
       </c>
       <c r="E93" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="F93" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="G93">
-        <v>757750210</v>
+        <v>758177759</v>
       </c>
       <c r="H93" t="s">
         <v>37</v>
@@ -6174,125 +6197,125 @@
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K93" t="s">
         <v>5</v>
       </c>
       <c r="L93" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M93" t="s">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="N93" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O93" t="s">
         <v>0</v>
       </c>
-      <c r="P93">
-        <v>0</v>
+      <c r="P93" s="1">
+        <v>2881416</v>
       </c>
       <c r="Q93" t="s">
-        <v>237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>62760027</v>
+        <v>63025600</v>
       </c>
       <c r="B94" s="2">
-        <v>46147.546493055554</v>
+        <v>46151.740983796299</v>
       </c>
       <c r="C94">
-        <v>62902869</v>
+        <v>63408272</v>
       </c>
       <c r="D94" s="2">
-        <v>46149.631921296299</v>
+        <v>46159.533958333333</v>
       </c>
       <c r="E94" t="s">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="F94" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G94">
-        <v>777699799</v>
+        <v>758237461</v>
       </c>
       <c r="H94" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I94" t="s">
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K94" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L94" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M94" t="s">
         <v>3</v>
       </c>
       <c r="N94" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O94" t="s">
         <v>0</v>
       </c>
-      <c r="P94" t="s">
-        <v>0</v>
+      <c r="P94" s="1">
+        <v>850000</v>
       </c>
       <c r="Q94" t="s">
-        <v>126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>62768013</v>
+        <v>63073782</v>
       </c>
       <c r="B95" s="2">
-        <v>46147.609988425924</v>
+        <v>46153.387870370374</v>
       </c>
       <c r="C95">
-        <v>62871386</v>
+        <v>63389964</v>
       </c>
       <c r="D95" s="2">
-        <v>46149.364837962959</v>
+        <v>46158.743206018517</v>
       </c>
       <c r="E95" t="s">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G95">
-        <v>143270405</v>
+        <v>710619970</v>
       </c>
       <c r="H95" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I95" t="s">
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K95" t="s">
         <v>1</v>
       </c>
       <c r="L95" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M95" t="s">
         <v>3</v>
       </c>
       <c r="N95" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O95" t="s">
         <v>0</v>
@@ -6301,33 +6324,33 @@
         <v>0</v>
       </c>
       <c r="Q95" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>62840921</v>
+        <v>63143165</v>
       </c>
       <c r="B96" s="2">
-        <v>46148.636331018519</v>
+        <v>46154.449884259258</v>
       </c>
       <c r="C96">
-        <v>63101235</v>
+        <v>63143198</v>
       </c>
       <c r="D96" s="2">
-        <v>46153.608599537038</v>
+        <v>46154.450150462966</v>
       </c>
       <c r="E96" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="F96" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="G96">
-        <v>707551377</v>
+        <v>708473548</v>
       </c>
       <c r="H96" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="I96" t="s">
         <v>0</v>
@@ -6342,228 +6365,228 @@
         <v>6</v>
       </c>
       <c r="M96" t="s">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="N96" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O96" t="s">
         <v>0</v>
       </c>
-      <c r="P96" t="s">
-        <v>0</v>
+      <c r="P96" s="1">
+        <v>7837678</v>
       </c>
       <c r="Q96" t="s">
-        <v>244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>62880594</v>
+        <v>63168095</v>
       </c>
       <c r="B97" s="2">
-        <v>46149.454710648148</v>
+        <v>46154.647604166668</v>
       </c>
       <c r="C97">
-        <v>62941351</v>
+        <v>63168477</v>
       </c>
       <c r="D97" s="2">
-        <v>46150.416979166665</v>
+        <v>46154.649652777778</v>
       </c>
       <c r="E97" t="s">
-        <v>16</v>
+        <v>254</v>
       </c>
       <c r="F97" t="s">
-        <v>245</v>
+        <v>29</v>
       </c>
       <c r="G97">
-        <v>709565662</v>
+        <v>747345191</v>
       </c>
       <c r="H97" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="I97" t="s">
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K97" t="s">
         <v>5</v>
       </c>
       <c r="L97" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M97" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N97" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O97" t="s">
         <v>0</v>
       </c>
-      <c r="P97" t="s">
-        <v>0</v>
+      <c r="P97" s="1">
+        <v>7103410</v>
       </c>
       <c r="Q97" t="s">
-        <v>247</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>62880628</v>
+        <v>63178332</v>
       </c>
       <c r="B98" s="2">
-        <v>46149.45484953704</v>
+        <v>46154.725729166668</v>
       </c>
       <c r="C98">
-        <v>62941416</v>
+        <v>63466467</v>
       </c>
       <c r="D98" s="2">
-        <v>46150.417719907404</v>
+        <v>46160.564699074072</v>
       </c>
       <c r="E98" t="s">
-        <v>16</v>
+        <v>263</v>
       </c>
       <c r="F98" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="G98">
-        <v>709565662</v>
+        <v>708773097</v>
       </c>
       <c r="H98" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="I98" t="s">
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K98" t="s">
         <v>5</v>
       </c>
       <c r="L98" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M98" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N98" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O98" t="s">
         <v>0</v>
       </c>
-      <c r="P98">
-        <v>0</v>
+      <c r="P98" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q98" t="s">
-        <v>247</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>62880812</v>
+        <v>63179342</v>
       </c>
       <c r="B99" s="2">
-        <v>46149.456157407411</v>
+        <v>46154.735729166663</v>
       </c>
       <c r="C99">
-        <v>63224093</v>
+        <v>63466705</v>
       </c>
       <c r="D99" s="2">
-        <v>46155.609270833331</v>
+        <v>46160.566377314812</v>
       </c>
       <c r="E99" t="s">
-        <v>119</v>
+        <v>263</v>
       </c>
       <c r="F99" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G99">
-        <v>707672487</v>
+        <v>778179203</v>
       </c>
       <c r="H99" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="I99" t="s">
         <v>0</v>
       </c>
       <c r="J99" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K99" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="L99" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M99" t="s">
         <v>3</v>
       </c>
       <c r="N99" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O99" t="s">
         <v>0</v>
       </c>
-      <c r="P99" t="s">
-        <v>0</v>
+      <c r="P99" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q99" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>62937923</v>
+        <v>63210811</v>
       </c>
       <c r="B100" s="2">
-        <v>46150.381145833337</v>
+        <v>46155.50409722222</v>
       </c>
       <c r="C100">
-        <v>63214161</v>
+        <v>63210839</v>
       </c>
       <c r="D100" s="2">
-        <v>46155.526944444442</v>
+        <v>46155.504328703704</v>
       </c>
       <c r="E100" t="s">
-        <v>119</v>
+        <v>254</v>
       </c>
       <c r="F100" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="G100">
-        <v>565811689</v>
+        <v>160128782</v>
       </c>
       <c r="H100" t="s">
-        <v>37</v>
+        <v>262</v>
       </c>
       <c r="I100" t="s">
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M100" t="s">
         <v>3</v>
       </c>
       <c r="N100" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O100" t="s">
         <v>0</v>
       </c>
       <c r="P100" s="1">
-        <v>250000</v>
+        <v>800000</v>
       </c>
       <c r="Q100" t="s">
         <v>31</v>
@@ -6571,28 +6594,28 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>62968196</v>
+        <v>63302106</v>
       </c>
       <c r="B101" s="2">
-        <v>46150.638715277775</v>
+        <v>46157.389525462961</v>
       </c>
       <c r="C101">
-        <v>63089942</v>
+        <v>63302124</v>
       </c>
       <c r="D101" s="2">
-        <v>46153.521840277775</v>
+        <v>46157.389907407407</v>
       </c>
       <c r="E101" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="F101" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="G101">
-        <v>758177759</v>
+        <v>707282722</v>
       </c>
       <c r="H101" t="s">
-        <v>37</v>
+        <v>268</v>
       </c>
       <c r="I101" t="s">
         <v>0</v>
@@ -6601,51 +6624,51 @@
         <v>13</v>
       </c>
       <c r="K101" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L101" t="s">
         <v>6</v>
       </c>
       <c r="M101" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N101" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O101" t="s">
         <v>0</v>
       </c>
       <c r="P101" s="1">
-        <v>2881416</v>
+        <v>946304</v>
       </c>
       <c r="Q101" t="s">
-        <v>0</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>63025600</v>
+        <v>63303380</v>
       </c>
       <c r="B102" s="2">
-        <v>46151.740983796299</v>
+        <v>46157.402731481481</v>
       </c>
       <c r="C102">
-        <v>63092455</v>
+        <v>63303417</v>
       </c>
       <c r="D102" s="2">
-        <v>46153.539537037039</v>
+        <v>46157.402997685182</v>
       </c>
       <c r="E102" t="s">
-        <v>119</v>
+        <v>254</v>
       </c>
       <c r="F102" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="G102">
-        <v>758237461</v>
+        <v>707282722</v>
       </c>
       <c r="H102" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="I102" t="s">
         <v>0</v>
@@ -6660,122 +6683,122 @@
         <v>6</v>
       </c>
       <c r="M102" t="s">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="N102" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O102" t="s">
         <v>0</v>
       </c>
       <c r="P102" s="1">
-        <v>850000</v>
+        <v>4053290</v>
       </c>
       <c r="Q102" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>63073782</v>
+        <v>63330974</v>
       </c>
       <c r="B103" s="2">
-        <v>46153.387870370374</v>
+        <v>46157.61818287037</v>
       </c>
       <c r="C103">
-        <v>63115586</v>
+        <v>63331008</v>
       </c>
       <c r="D103" s="2">
-        <v>46153.713333333333</v>
+        <v>46157.61855324074</v>
       </c>
       <c r="E103" t="s">
-        <v>119</v>
+        <v>254</v>
       </c>
       <c r="F103" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="G103">
-        <v>710619970</v>
+        <v>759530809</v>
       </c>
       <c r="H103" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="I103" t="s">
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K103" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L103" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M103" t="s">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="N103" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O103" t="s">
         <v>0</v>
       </c>
-      <c r="P103" t="s">
-        <v>0</v>
+      <c r="P103" s="1">
+        <v>1644000</v>
       </c>
       <c r="Q103" t="s">
-        <v>107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>63143165</v>
+        <v>63443742</v>
       </c>
       <c r="B104" s="2">
-        <v>46154.449884259258</v>
+        <v>46160.375115740739</v>
       </c>
       <c r="C104">
-        <v>63143198</v>
+        <v>63443769</v>
       </c>
       <c r="D104" s="2">
-        <v>46154.450150462966</v>
+        <v>46160.375509259262</v>
       </c>
       <c r="E104" t="s">
+        <v>275</v>
+      </c>
+      <c r="F104" t="s">
         <v>274</v>
       </c>
-      <c r="F104" t="s">
-        <v>275</v>
-      </c>
       <c r="G104">
-        <v>708473548</v>
+        <v>798886434</v>
       </c>
       <c r="H104" t="s">
-        <v>276</v>
+        <v>118</v>
       </c>
       <c r="I104" t="s">
         <v>0</v>
       </c>
       <c r="J104" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K104" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L104" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M104" t="s">
-        <v>178</v>
+        <v>3</v>
       </c>
       <c r="N104" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O104" t="s">
         <v>0</v>
       </c>
-      <c r="P104" s="1">
-        <v>7837678</v>
+      <c r="P104" t="s">
+        <v>0</v>
       </c>
       <c r="Q104" t="s">
         <v>0</v>
@@ -6783,81 +6806,81 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>63168095</v>
+        <v>63449095</v>
       </c>
       <c r="B105" s="2">
-        <v>46154.647604166668</v>
+        <v>46160.428668981483</v>
       </c>
       <c r="C105">
-        <v>63168477</v>
+        <v>63449152</v>
       </c>
       <c r="D105" s="2">
-        <v>46154.649652777778</v>
+        <v>46160.429050925923</v>
       </c>
       <c r="E105" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F105" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
       <c r="G105">
-        <v>747345191</v>
+        <v>768420441</v>
       </c>
       <c r="H105" t="s">
-        <v>277</v>
+        <v>37</v>
       </c>
       <c r="I105" t="s">
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K105" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L105" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M105" t="s">
         <v>3</v>
       </c>
       <c r="N105" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O105" t="s">
         <v>0</v>
       </c>
-      <c r="P105" s="1">
-        <v>7103410</v>
+      <c r="P105" t="s">
+        <v>0</v>
       </c>
       <c r="Q105" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>63178332</v>
+        <v>63451685</v>
       </c>
       <c r="B106" s="2">
-        <v>46154.725729166668</v>
+        <v>46160.45171296296</v>
       </c>
       <c r="C106">
-        <v>63178359</v>
+        <v>63451731</v>
       </c>
       <c r="D106" s="2">
-        <v>46154.725960648146</v>
+        <v>46160.451956018522</v>
       </c>
       <c r="E106" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="F106" t="s">
-        <v>278</v>
+        <v>104</v>
       </c>
       <c r="G106">
-        <v>708773097</v>
+        <v>707407425</v>
       </c>
       <c r="H106" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I106" t="s">
         <v>0</v>
@@ -6875,7 +6898,7 @@
         <v>3</v>
       </c>
       <c r="N106" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O106" t="s">
         <v>0</v>
@@ -6884,86 +6907,86 @@
         <v>2000000</v>
       </c>
       <c r="Q106" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>63179342</v>
+        <v>63453142</v>
       </c>
       <c r="B107" s="2">
-        <v>46154.735729166663</v>
+        <v>46160.461238425924</v>
       </c>
       <c r="C107">
-        <v>63179372</v>
+        <v>63453202</v>
       </c>
       <c r="D107" s="2">
-        <v>46154.735960648148</v>
+        <v>46160.461481481485</v>
       </c>
       <c r="E107" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="F107" t="s">
         <v>278</v>
       </c>
       <c r="G107">
-        <v>778179203</v>
+        <v>507828407</v>
       </c>
       <c r="H107" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I107" t="s">
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K107" t="s">
         <v>5</v>
       </c>
       <c r="L107" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M107" t="s">
         <v>3</v>
       </c>
       <c r="N107" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O107" t="s">
         <v>0</v>
       </c>
       <c r="P107" s="1">
-        <v>2000000</v>
+        <v>1009545</v>
       </c>
       <c r="Q107" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>63210811</v>
+        <v>63453475</v>
       </c>
       <c r="B108" s="2">
-        <v>46155.50409722222</v>
+        <v>46160.463773148149</v>
       </c>
       <c r="C108">
-        <v>63210839</v>
+        <v>63453534</v>
       </c>
       <c r="D108" s="2">
-        <v>46155.504328703704</v>
+        <v>46160.464131944442</v>
       </c>
       <c r="E108" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="F108" t="s">
-        <v>281</v>
+        <v>104</v>
       </c>
       <c r="G108">
-        <v>160128782</v>
+        <v>708343014</v>
       </c>
       <c r="H108" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I108" t="s">
         <v>0</v>
@@ -6972,7 +6995,7 @@
         <v>18</v>
       </c>
       <c r="K108" t="s">
-        <v>5</v>
+        <v>127</v>
       </c>
       <c r="L108" t="s">
         <v>8</v>
@@ -6981,19 +7004,76 @@
         <v>3</v>
       </c>
       <c r="N108" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O108" t="s">
         <v>0</v>
       </c>
       <c r="P108" s="1">
-        <v>800000</v>
+        <v>3940384</v>
       </c>
       <c r="Q108" t="s">
         <v>0</v>
       </c>
     </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>63462158</v>
+      </c>
+      <c r="B109" s="2">
+        <v>46160.525254629632</v>
+      </c>
+      <c r="C109">
+        <v>63462196</v>
+      </c>
+      <c r="D109" s="2">
+        <v>46160.525601851848</v>
+      </c>
+      <c r="E109" t="s">
+        <v>254</v>
+      </c>
+      <c r="F109" t="s">
+        <v>281</v>
+      </c>
+      <c r="G109">
+        <v>768231346</v>
+      </c>
+      <c r="H109" t="s">
+        <v>282</v>
+      </c>
+      <c r="I109" t="s">
+        <v>0</v>
+      </c>
+      <c r="J109" t="s">
+        <v>13</v>
+      </c>
+      <c r="K109" t="s">
+        <v>127</v>
+      </c>
+      <c r="L109" t="s">
+        <v>6</v>
+      </c>
+      <c r="M109" t="s">
+        <v>3</v>
+      </c>
+      <c r="N109" t="s">
+        <v>121</v>
+      </c>
+      <c r="O109" t="s">
+        <v>0</v>
+      </c>
+      <c r="P109" s="1">
+        <v>518450</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:Q109" xr:uid="{33B89436-3C62-48B9-A287-E4DCE0428514}"/>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/Attachments/Bureau/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="487" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1D2D3C0-A6A3-429A-AE0B-B5BB58734133}"/>
+  <xr:revisionPtr revIDLastSave="521" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F915418-16CF-4F80-990E-C3E7EC19EFBF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil2" sheetId="46" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="47" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil2!$A$1:$Q$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$Q$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="286">
   <si>
     <t>-</t>
   </si>
@@ -257,9 +257,6 @@
     <t>HUAWEI</t>
   </si>
   <si>
-    <t>ABOISSO</t>
-  </si>
-  <si>
     <t>AGILITY BUSINESS PARKS COTE D’IVOIRE</t>
   </si>
   <si>
@@ -341,9 +338,6 @@
     <t>MAIRIE DE NIABLE</t>
   </si>
   <si>
-    <t>TAABO LAMTO</t>
-  </si>
-  <si>
     <t>MFI CI (SODEXAM)</t>
   </si>
   <si>
@@ -359,18 +353,6 @@
     <t>XXXXXXXXXXXXX</t>
   </si>
   <si>
-    <t>OCI PCCI 2</t>
-  </si>
-  <si>
-    <t>ABIDJAN TREICHVILLE</t>
-  </si>
-  <si>
-    <t>DEMANDE INTERNE FRANCHISE MANKONO</t>
-  </si>
-  <si>
-    <t>MONKONO</t>
-  </si>
-  <si>
     <t>XXXXXXXXXXXX</t>
   </si>
   <si>
@@ -419,9 +401,6 @@
     <t>GRAND BASSAM</t>
   </si>
   <si>
-    <t>SUD COMOE CAOUTCHOU</t>
-  </si>
-  <si>
     <t>radio_fh</t>
   </si>
   <si>
@@ -443,30 +422,12 @@
     <t>MAXAM CI</t>
   </si>
   <si>
-    <t>BUVPN250061</t>
-  </si>
-  <si>
-    <t>RIMCO</t>
-  </si>
-  <si>
-    <t>TREICHVILLE ZONE 3</t>
-  </si>
-  <si>
-    <t>1.000.000</t>
-  </si>
-  <si>
     <t>DJIGUI SHIPPING SITE TREICHVILLE CHU</t>
   </si>
   <si>
-    <t>xxxxxx</t>
-  </si>
-  <si>
     <t>Etude Suspendu</t>
   </si>
   <si>
-    <t>Saisie ASCOM</t>
-  </si>
-  <si>
     <t>ECOTI SA</t>
   </si>
   <si>
@@ -521,9 +482,6 @@
     <t>ECOBANK COCODY RIVIERA</t>
   </si>
   <si>
-    <t>Support IP: Config Eq Acces</t>
-  </si>
-  <si>
     <t>NIABLE A LA MAIRIE</t>
   </si>
   <si>
@@ -578,12 +536,6 @@
     <t>BUVPN260082</t>
   </si>
   <si>
-    <t>ASCOMA</t>
-  </si>
-  <si>
-    <t>COCODY VALLON</t>
-  </si>
-  <si>
     <t>STE SICPA CI</t>
   </si>
   <si>
@@ -641,21 +593,12 @@
     <t>NESKAO</t>
   </si>
   <si>
-    <t>IVOIRE TECHNO COM</t>
-  </si>
-  <si>
     <t>UNITED BANK OF AFRICA</t>
   </si>
   <si>
     <t>UNION INVESTISSEMENT</t>
   </si>
   <si>
-    <t>SIB</t>
-  </si>
-  <si>
-    <t>COCODY RIVIERA 2</t>
-  </si>
-  <si>
     <t>MANKALA</t>
   </si>
   <si>
@@ -689,9 +632,6 @@
     <t>ABIDJAN-COCODY ANGRE NOUVEAU GOUDRON CHU</t>
   </si>
   <si>
-    <t>ANSSI</t>
-  </si>
-  <si>
     <t>SYTHD260132</t>
   </si>
   <si>
@@ -716,15 +656,6 @@
     <t>xxxxxxxxxxx</t>
   </si>
   <si>
-    <t>BUVPN260091</t>
-  </si>
-  <si>
-    <t>XXXXXXXXXXXXXXXXX</t>
-  </si>
-  <si>
-    <t>SYTHD260130</t>
-  </si>
-  <si>
     <t>STE NAVITRANS COTE D'IVOIRE</t>
   </si>
   <si>
@@ -791,9 +722,6 @@
     <t>ABIDJAN-PORT BOUET VRIDI</t>
   </si>
   <si>
-    <t>SYTHD260137</t>
-  </si>
-  <si>
     <t>PORT-POUET VRIDI ZONE INDUSTRIELLE RUE DES TEXTILES</t>
   </si>
   <si>
@@ -803,15 +731,6 @@
     <t>BO Homologation: Mise en service GAIA</t>
   </si>
   <si>
-    <t>Parametrage facturation</t>
-  </si>
-  <si>
-    <t>AGENCE EMPLOI JEUNE</t>
-  </si>
-  <si>
-    <t>TREICHVILLE PALAIS DES SPORTS</t>
-  </si>
-  <si>
     <t>SONGON</t>
   </si>
   <si>
@@ -845,12 +764,6 @@
     <t>ARTCI</t>
   </si>
   <si>
-    <t>PORT BOUET PARC DES EXPOSITIONS.</t>
-  </si>
-  <si>
-    <t>SYTHD260141</t>
-  </si>
-  <si>
     <t>PORT BOUET PARC DES EXPOSITIONS RADISON BLUE.</t>
   </si>
   <si>
@@ -888,6 +801,102 @@
   </si>
   <si>
     <t>ABIDJAN-YOPOUGON AUTOROUTE DU NORD PK 24</t>
+  </si>
+  <si>
+    <t>NOM</t>
+  </si>
+  <si>
+    <t>BUVPN260089</t>
+  </si>
+  <si>
+    <t>2721230250B</t>
+  </si>
+  <si>
+    <t>SYTHD260145</t>
+  </si>
+  <si>
+    <t>SYTHD260143</t>
+  </si>
+  <si>
+    <t>BO Homologation: Mise en service BSCS</t>
+  </si>
+  <si>
+    <t>L'Agence Emploi Jeunes</t>
+  </si>
+  <si>
+    <t>ABIDJAN-TREICHVILLE//VOIE INCONNUE/PALAIS DES SPORTS</t>
+  </si>
+  <si>
+    <t>SYTHD260144</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie BSCS</t>
+  </si>
+  <si>
+    <t>BUVPN260094</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>KALIMBA</t>
+  </si>
+  <si>
+    <t>MARCORY IMMEUBLE BATICHO</t>
+  </si>
+  <si>
+    <t>ASSISTANCE AUTOMOBILE ABIDJANAISE</t>
+  </si>
+  <si>
+    <t>COCODY BATIM A</t>
+  </si>
+  <si>
+    <t>EGLISE VASE D'HONNEUR</t>
+  </si>
+  <si>
+    <t>PORT BOUET PARC DES EXPOSITION</t>
+  </si>
+  <si>
+    <t>NSIA BANQUE COCODY MERMOZ INADES</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY MERMOZ INADES</t>
+  </si>
+  <si>
+    <t>BANQUE NATIONAL D'INVESTISSEMENT DABAKALA</t>
+  </si>
+  <si>
+    <t>DABAKALA EN FACE DE L'HOPITAL ET STATION TOTAL</t>
+  </si>
+  <si>
+    <t>ORANGE BUSNESS SERVICES</t>
+  </si>
+  <si>
+    <t>CREDAFRICA</t>
+  </si>
+  <si>
+    <t>COCODY CARREFOUR DUNCAN</t>
+  </si>
+  <si>
+    <t>BANQUE DE L'HABITAT DE COTE D'IVOIRE PLATEAU</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie GAIA LSI</t>
+  </si>
+  <si>
+    <t>ADKONTACT</t>
+  </si>
+  <si>
+    <t>MAIRIE DE DJEBONOUA</t>
+  </si>
+  <si>
+    <t>DJEBONOUA</t>
+  </si>
+  <si>
+    <t>LSI Elite</t>
   </si>
 </sst>
 </file>
@@ -931,27 +940,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1291,12 +1280,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33B89436-3C62-48B9-A287-E4DCE0428514}">
-  <dimension ref="A1:Q109"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B883F859-51AD-4911-81A4-A2400EFBC314}">
+  <dimension ref="A1:Q108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="3" max="3" width="8.7265625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1339,7 +1325,7 @@
         <v>53</v>
       </c>
       <c r="N1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="O1" t="s">
         <v>54</v>
@@ -1368,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G2">
         <v>777545168</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
@@ -1442,7 +1428,7 @@
         <v>17</v>
       </c>
       <c r="N3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O3" t="s">
         <v>0</v>
@@ -1495,7 +1481,7 @@
         <v>7</v>
       </c>
       <c r="N4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O4" t="s">
         <v>0</v>
@@ -1548,7 +1534,7 @@
         <v>3</v>
       </c>
       <c r="N5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O5" t="s">
         <v>0</v>
@@ -1601,7 +1587,7 @@
         <v>3</v>
       </c>
       <c r="N6" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O6" t="s">
         <v>0</v>
@@ -1654,7 +1640,7 @@
         <v>3</v>
       </c>
       <c r="N7" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O7" t="s">
         <v>0</v>
@@ -1707,7 +1693,7 @@
         <v>7</v>
       </c>
       <c r="N8" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O8" t="s">
         <v>0</v>
@@ -1760,7 +1746,7 @@
         <v>7</v>
       </c>
       <c r="N9" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O9" t="s">
         <v>0</v>
@@ -1813,7 +1799,7 @@
         <v>3</v>
       </c>
       <c r="N10" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O10" t="s">
         <v>0</v>
@@ -1839,10 +1825,10 @@
         <v>46049.856261574074</v>
       </c>
       <c r="E11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G11">
         <v>759003900</v>
@@ -1866,7 +1852,7 @@
         <v>3</v>
       </c>
       <c r="N11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O11" t="s">
         <v>0</v>
@@ -1875,7 +1861,7 @@
         <v>918681</v>
       </c>
       <c r="Q11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -1895,13 +1881,13 @@
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G12">
         <v>749338073</v>
       </c>
       <c r="H12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s">
         <v>0</v>
@@ -1919,7 +1905,7 @@
         <v>3</v>
       </c>
       <c r="N12" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O12" t="s">
         <v>0</v>
@@ -1928,7 +1914,7 @@
         <v>638462</v>
       </c>
       <c r="Q12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
@@ -1945,16 +1931,16 @@
         <v>46083.492881944447</v>
       </c>
       <c r="E13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G13">
         <v>585990976</v>
       </c>
       <c r="H13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I13">
         <v>1765416</v>
@@ -1972,7 +1958,7 @@
         <v>3</v>
       </c>
       <c r="N13" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O13" t="s">
         <v>0</v>
@@ -1981,7 +1967,7 @@
         <v>3000000</v>
       </c>
       <c r="Q13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
@@ -1992,13 +1978,13 @@
         <v>46035.393611111111</v>
       </c>
       <c r="C14">
-        <v>63317758</v>
+        <v>63572836</v>
       </c>
       <c r="D14" s="2">
-        <v>46157.506435185183</v>
+        <v>46162.418113425927</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
         <v>29</v>
@@ -2007,7 +1993,7 @@
         <v>707003126</v>
       </c>
       <c r="H14" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="I14" t="s">
         <v>0</v>
@@ -2025,7 +2011,7 @@
         <v>3</v>
       </c>
       <c r="N14" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O14" t="s">
         <v>0</v>
@@ -2034,7 +2020,7 @@
         <v>7103410</v>
       </c>
       <c r="Q14" t="s">
-        <v>20</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
@@ -2060,7 +2046,7 @@
         <v>707003126</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I15" t="s">
         <v>0</v>
@@ -2078,7 +2064,7 @@
         <v>3</v>
       </c>
       <c r="N15" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O15" t="s">
         <v>0</v>
@@ -2092,28 +2078,28 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>56606469</v>
+        <v>56607988</v>
       </c>
       <c r="B16" s="2">
-        <v>46035.43072916667</v>
+        <v>46035.443668981483</v>
       </c>
       <c r="C16">
-        <v>60100048</v>
+        <v>62467448</v>
       </c>
       <c r="D16" s="2">
-        <v>46099.427060185182</v>
+        <v>46141.570902777778</v>
       </c>
       <c r="E16" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G16">
         <v>504041812</v>
       </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="I16" t="s">
         <v>0</v>
@@ -2131,42 +2117,42 @@
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O16" t="s">
         <v>0</v>
       </c>
       <c r="P16" s="1">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="Q16" t="s">
-        <v>34</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>56607988</v>
+        <v>56611212</v>
       </c>
       <c r="B17" s="2">
-        <v>46035.443668981483</v>
+        <v>46035.471886574072</v>
       </c>
       <c r="C17">
-        <v>62467448</v>
+        <v>62203808</v>
       </c>
       <c r="D17" s="2">
-        <v>46141.570902777778</v>
+        <v>46136.681342592594</v>
       </c>
       <c r="E17" t="s">
         <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G17">
         <v>504041812</v>
       </c>
       <c r="H17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s">
         <v>0</v>
@@ -2184,7 +2170,7 @@
         <v>3</v>
       </c>
       <c r="N17" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O17" t="s">
         <v>0</v>
@@ -2193,39 +2179,39 @@
         <v>2000000</v>
       </c>
       <c r="Q17" t="s">
-        <v>185</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>56611212</v>
+        <v>56618123</v>
       </c>
       <c r="B18" s="2">
-        <v>46035.471886574072</v>
+        <v>46035.520821759259</v>
       </c>
       <c r="C18">
-        <v>62203808</v>
+        <v>63588969</v>
       </c>
       <c r="D18" s="2">
-        <v>46136.681342592594</v>
+        <v>46162.539305555554</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>237</v>
       </c>
       <c r="F18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G18">
         <v>504041812</v>
       </c>
       <c r="H18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I18" t="s">
-        <v>0</v>
+        <v>116</v>
+      </c>
+      <c r="I18">
+        <v>1775236</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -2237,7 +2223,7 @@
         <v>3</v>
       </c>
       <c r="N18" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O18" t="s">
         <v>0</v>
@@ -2246,86 +2232,86 @@
         <v>2000000</v>
       </c>
       <c r="Q18" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>56618123</v>
+        <v>56675050</v>
       </c>
       <c r="B19" s="2">
-        <v>46035.520821759259</v>
+        <v>46036.516423611109</v>
       </c>
       <c r="C19">
-        <v>59311833</v>
+        <v>63302732</v>
       </c>
       <c r="D19" s="2">
-        <v>46084.811782407407</v>
+        <v>46157.396793981483</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="G19">
-        <v>504041812</v>
+        <v>748512613</v>
       </c>
       <c r="H19" t="s">
-        <v>122</v>
-      </c>
-      <c r="I19">
-        <v>1775236</v>
+        <v>95</v>
+      </c>
+      <c r="I19" t="s">
+        <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
       </c>
       <c r="L19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M19" t="s">
         <v>3</v>
       </c>
       <c r="N19" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O19" t="s">
         <v>0</v>
       </c>
       <c r="P19" s="1">
-        <v>2000000</v>
+        <v>4362401</v>
       </c>
       <c r="Q19" t="s">
-        <v>123</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>56675050</v>
+        <v>56970346</v>
       </c>
       <c r="B20" s="2">
-        <v>46036.516423611109</v>
+        <v>46042.557280092595</v>
       </c>
       <c r="C20">
-        <v>63302732</v>
+        <v>59242054</v>
       </c>
       <c r="D20" s="2">
-        <v>46157.396793981483</v>
+        <v>46083.719525462962</v>
       </c>
       <c r="E20" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>247</v>
+        <v>91</v>
       </c>
       <c r="G20">
-        <v>748512613</v>
+        <v>708667658</v>
       </c>
       <c r="H20" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s">
         <v>0</v>
@@ -2343,42 +2329,42 @@
         <v>3</v>
       </c>
       <c r="N20" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O20" t="s">
         <v>0</v>
       </c>
       <c r="P20" s="1">
-        <v>4362401</v>
+        <v>2871414</v>
       </c>
       <c r="Q20" t="s">
-        <v>217</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>56970346</v>
+        <v>57398181</v>
       </c>
       <c r="B21" s="2">
-        <v>46042.557280092595</v>
+        <v>46050.584374999999</v>
       </c>
       <c r="C21">
-        <v>59242054</v>
+        <v>60344342</v>
       </c>
       <c r="D21" s="2">
-        <v>46083.719525462962</v>
+        <v>46104.528900462959</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G21">
-        <v>708667658</v>
+        <v>720631500</v>
       </c>
       <c r="H21" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I21" t="s">
         <v>0</v>
@@ -2396,42 +2382,42 @@
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O21" t="s">
         <v>0</v>
       </c>
       <c r="P21" s="1">
-        <v>2871414</v>
+        <v>4406780</v>
       </c>
       <c r="Q21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>57398181</v>
+        <v>58055656</v>
       </c>
       <c r="B22" s="2">
-        <v>46050.584374999999</v>
+        <v>46062.760023148148</v>
       </c>
       <c r="C22">
-        <v>60344342</v>
+        <v>61269237</v>
       </c>
       <c r="D22" s="2">
-        <v>46104.528900462959</v>
+        <v>46121.376689814817</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G22">
-        <v>720631500</v>
+        <v>758224257</v>
       </c>
       <c r="H22" t="s">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="I22" t="s">
         <v>0</v>
@@ -2449,92 +2435,92 @@
         <v>3</v>
       </c>
       <c r="N22" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O22" t="s">
         <v>0</v>
       </c>
       <c r="P22" s="1">
-        <v>4406780</v>
+        <v>1800000</v>
       </c>
       <c r="Q22" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>58055656</v>
+        <v>58166885</v>
       </c>
       <c r="B23" s="2">
-        <v>46062.760023148148</v>
+        <v>46064.649965277778</v>
       </c>
       <c r="C23">
-        <v>61269237</v>
+        <v>63079695</v>
       </c>
       <c r="D23" s="2">
-        <v>46121.376689814817</v>
+        <v>46153.448425925926</v>
       </c>
       <c r="E23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="G23">
-        <v>758224257</v>
+        <v>504041812</v>
       </c>
       <c r="H23" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="I23" t="s">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K23" t="s">
         <v>5</v>
       </c>
       <c r="L23" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M23" t="s">
         <v>3</v>
       </c>
       <c r="N23" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O23" t="s">
         <v>0</v>
       </c>
       <c r="P23" s="1">
-        <v>1800000</v>
+        <v>2000000</v>
       </c>
       <c r="Q23" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>58093827</v>
+        <v>58626822</v>
       </c>
       <c r="B24" s="2">
-        <v>46063.583402777775</v>
+        <v>46072.810324074075</v>
       </c>
       <c r="C24">
-        <v>62146534</v>
+        <v>59811821</v>
       </c>
       <c r="D24" s="2">
-        <v>46135.713287037041</v>
+        <v>46093.543773148151</v>
       </c>
       <c r="E24" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G24">
-        <v>708086759</v>
+        <v>709574114</v>
       </c>
       <c r="H24" t="s">
         <v>100</v>
@@ -2552,45 +2538,45 @@
         <v>6</v>
       </c>
       <c r="M24" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N24" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O24" t="s">
         <v>0</v>
       </c>
-      <c r="P24" t="s">
-        <v>0</v>
+      <c r="P24" s="1">
+        <v>445307</v>
       </c>
       <c r="Q24" t="s">
-        <v>139</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>58166885</v>
+        <v>58635645</v>
       </c>
       <c r="B25" s="2">
-        <v>46064.649965277778</v>
+        <v>46073.372395833336</v>
       </c>
       <c r="C25">
-        <v>63079695</v>
+        <v>61982536</v>
       </c>
       <c r="D25" s="2">
-        <v>46153.448425925926</v>
+        <v>46133.49863425926</v>
       </c>
       <c r="E25" t="s">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="G25">
-        <v>504041812</v>
+        <v>759250737</v>
       </c>
       <c r="H25" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="I25" t="s">
         <v>0</v>
@@ -2599,104 +2585,104 @@
         <v>18</v>
       </c>
       <c r="K25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L25" t="s">
         <v>8</v>
       </c>
       <c r="M25" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N25" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O25" t="s">
         <v>0</v>
       </c>
-      <c r="P25" s="1">
-        <v>2000000</v>
+      <c r="P25" t="s">
+        <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>219</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>58626822</v>
+        <v>58635674</v>
       </c>
       <c r="B26" s="2">
-        <v>46072.810324074075</v>
+        <v>46073.372488425928</v>
       </c>
       <c r="C26">
-        <v>59811821</v>
+        <v>61980847</v>
       </c>
       <c r="D26" s="2">
-        <v>46093.543773148151</v>
+        <v>46133.487384259257</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F26" t="s">
         <v>101</v>
       </c>
       <c r="G26">
-        <v>709574114</v>
+        <v>759250737</v>
       </c>
       <c r="H26" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="I26" t="s">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K26" t="s">
         <v>5</v>
       </c>
       <c r="L26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M26" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N26" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O26" t="s">
         <v>0</v>
       </c>
       <c r="P26" s="1">
-        <v>445307</v>
+        <v>500000</v>
       </c>
       <c r="Q26" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>58635645</v>
+        <v>58797846</v>
       </c>
       <c r="B27" s="2">
-        <v>46073.372395833336</v>
+        <v>46076.510104166664</v>
       </c>
       <c r="C27">
-        <v>61982536</v>
+        <v>63585491</v>
       </c>
       <c r="D27" s="2">
-        <v>46133.49863425926</v>
+        <v>46162.510451388887</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G27">
-        <v>759250737</v>
+        <v>102224907</v>
       </c>
       <c r="H27" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="I27" t="s">
         <v>0</v>
@@ -2711,45 +2697,45 @@
         <v>8</v>
       </c>
       <c r="M27" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N27" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O27" t="s">
         <v>0</v>
       </c>
-      <c r="P27" t="s">
-        <v>0</v>
+      <c r="P27" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q27" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>58635674</v>
+        <v>58868849</v>
       </c>
       <c r="B28" s="2">
-        <v>46073.372488425928</v>
+        <v>46077.501203703701</v>
       </c>
       <c r="C28">
-        <v>61980847</v>
+        <v>62104932</v>
       </c>
       <c r="D28" s="2">
-        <v>46133.487384259257</v>
+        <v>46135.396608796298</v>
       </c>
       <c r="E28" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G28">
-        <v>759250737</v>
+        <v>748377555</v>
       </c>
       <c r="H28" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="I28" t="s">
         <v>0</v>
@@ -2764,363 +2750,363 @@
         <v>8</v>
       </c>
       <c r="M28" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N28" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O28" t="s">
         <v>0</v>
       </c>
-      <c r="P28" s="1">
-        <v>500000</v>
+      <c r="P28" t="s">
+        <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>59</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>58797846</v>
+        <v>58925987</v>
       </c>
       <c r="B29" s="2">
-        <v>46076.510104166664</v>
+        <v>46078.434814814813</v>
       </c>
       <c r="C29">
-        <v>63198672</v>
+        <v>60163873</v>
       </c>
       <c r="D29" s="2">
-        <v>46155.408773148149</v>
+        <v>46100.423101851855</v>
       </c>
       <c r="E29" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G29">
-        <v>102224907</v>
+        <v>708641473</v>
       </c>
       <c r="H29" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="I29" t="s">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K29" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M29" t="s">
         <v>3</v>
       </c>
       <c r="N29" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O29" t="s">
         <v>0</v>
       </c>
-      <c r="P29" s="1">
-        <v>2000000</v>
+      <c r="P29" t="s">
+        <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>58856498</v>
+        <v>58959238</v>
       </c>
       <c r="B30" s="2">
-        <v>46077.418171296296</v>
+        <v>46078.665532407409</v>
       </c>
       <c r="C30">
-        <v>60800011</v>
+        <v>60163938</v>
       </c>
       <c r="D30" s="2">
-        <v>46112.393784722219</v>
+        <v>46100.423773148148</v>
       </c>
       <c r="E30" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G30">
-        <v>748377555</v>
+        <v>708641473</v>
       </c>
       <c r="H30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
       </c>
       <c r="L30" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M30" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N30" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O30" t="s">
         <v>0</v>
       </c>
-      <c r="P30" t="s">
-        <v>0</v>
+      <c r="P30" s="1">
+        <v>850000</v>
       </c>
       <c r="Q30" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>58860538</v>
+        <v>58963630</v>
       </c>
       <c r="B31" s="2">
-        <v>46077.446666666663</v>
+        <v>46078.697002314817</v>
       </c>
       <c r="C31">
-        <v>62950864</v>
+        <v>63476600</v>
       </c>
       <c r="D31" s="2">
-        <v>46150.491238425922</v>
+        <v>46160.642951388887</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F31" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="G31">
-        <v>748377555</v>
+        <v>747726344</v>
       </c>
       <c r="H31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I31" t="s">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K31" t="s">
         <v>5</v>
       </c>
       <c r="L31" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M31" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N31" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O31" t="s">
         <v>0</v>
       </c>
-      <c r="P31" s="1">
-        <v>5324000</v>
+      <c r="P31" t="s">
+        <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>58868849</v>
+        <v>58963646</v>
       </c>
       <c r="B32" s="2">
-        <v>46077.501203703701</v>
+        <v>46078.697048611109</v>
       </c>
       <c r="C32">
-        <v>62104932</v>
+        <v>63570032</v>
       </c>
       <c r="D32" s="2">
-        <v>46135.396608796298</v>
+        <v>46162.387326388889</v>
       </c>
       <c r="E32" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="F32" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="G32">
-        <v>748377555</v>
+        <v>747726344</v>
       </c>
       <c r="H32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I32" t="s">
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K32" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M32" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N32" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O32" t="s">
         <v>0</v>
       </c>
-      <c r="P32" t="s">
+      <c r="P32">
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>58925987</v>
+        <v>59466514</v>
       </c>
       <c r="B33" s="2">
-        <v>46078.434814814813</v>
+        <v>46087.436643518522</v>
       </c>
       <c r="C33">
-        <v>60163873</v>
+        <v>63070473</v>
       </c>
       <c r="D33" s="2">
-        <v>46100.423101851855</v>
+        <v>46153.32271990741</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="F33" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="G33">
-        <v>708641473</v>
+        <v>141679210</v>
       </c>
       <c r="H33" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I33" t="s">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K33" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L33" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M33" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N33" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O33" t="s">
         <v>0</v>
       </c>
-      <c r="P33" t="s">
-        <v>0</v>
+      <c r="P33" s="1">
+        <v>3213390</v>
       </c>
       <c r="Q33" t="s">
-        <v>105</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>58959238</v>
+        <v>59537755</v>
       </c>
       <c r="B34" s="2">
-        <v>46078.665532407409</v>
+        <v>46088.586631944447</v>
       </c>
       <c r="C34">
-        <v>60163938</v>
+        <v>61591841</v>
       </c>
       <c r="D34" s="2">
-        <v>46100.423773148148</v>
+        <v>46127.35796296296</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="F34" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="G34">
-        <v>708641473</v>
+        <v>556331131</v>
       </c>
       <c r="H34" t="s">
-        <v>115</v>
-      </c>
-      <c r="I34" t="s">
-        <v>0</v>
+        <v>133</v>
+      </c>
+      <c r="I34">
+        <v>1843236</v>
       </c>
       <c r="J34" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K34" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L34" t="s">
         <v>6</v>
       </c>
       <c r="M34" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N34" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O34" t="s">
         <v>0</v>
       </c>
-      <c r="P34" s="1">
-        <v>850000</v>
+      <c r="P34">
+        <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>58963630</v>
+        <v>59541145</v>
       </c>
       <c r="B35" s="2">
-        <v>46078.697002314817</v>
+        <v>46088.634837962964</v>
       </c>
       <c r="C35">
-        <v>63236831</v>
+        <v>63573765</v>
       </c>
       <c r="D35" s="2">
-        <v>46155.699733796297</v>
+        <v>46162.424571759257</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>40</v>
+        <v>225</v>
       </c>
       <c r="G35">
-        <v>747726344</v>
+        <v>546008131</v>
       </c>
       <c r="H35" t="s">
-        <v>116</v>
+        <v>226</v>
       </c>
       <c r="I35" t="s">
         <v>0</v>
@@ -3129,69 +3115,69 @@
         <v>13</v>
       </c>
       <c r="K35" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L35" t="s">
-        <v>6</v>
+        <v>172</v>
       </c>
       <c r="M35" t="s">
         <v>7</v>
       </c>
       <c r="N35" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O35" t="s">
         <v>0</v>
       </c>
-      <c r="P35" t="s">
+      <c r="P35">
         <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>24</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>58963646</v>
+        <v>59606122</v>
       </c>
       <c r="B36" s="2">
-        <v>46078.697048611109</v>
+        <v>46090.447604166664</v>
       </c>
       <c r="C36">
-        <v>61620936</v>
+        <v>61897702</v>
       </c>
       <c r="D36" s="2">
-        <v>46127.58321759259</v>
+        <v>46132.349363425928</v>
       </c>
       <c r="E36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="G36">
-        <v>747726344</v>
+        <v>708454305</v>
       </c>
       <c r="H36" t="s">
-        <v>116</v>
-      </c>
-      <c r="I36" t="s">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="I36">
+        <v>1842206</v>
       </c>
       <c r="J36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K36" t="s">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="L36" t="s">
         <v>6</v>
       </c>
       <c r="M36" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N36" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O36" t="s">
         <v>0</v>
@@ -3200,33 +3186,33 @@
         <v>0</v>
       </c>
       <c r="Q36" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>59466514</v>
+        <v>59615935</v>
       </c>
       <c r="B37" s="2">
-        <v>46087.436643518522</v>
+        <v>46090.512303240743</v>
       </c>
       <c r="C37">
-        <v>63070473</v>
+        <v>60393405</v>
       </c>
       <c r="D37" s="2">
-        <v>46153.32271990741</v>
+        <v>46105.432800925926</v>
       </c>
       <c r="E37" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>220</v>
+        <v>122</v>
       </c>
       <c r="G37">
-        <v>141679210</v>
+        <v>767081456</v>
       </c>
       <c r="H37" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I37" t="s">
         <v>0</v>
@@ -3235,69 +3221,69 @@
         <v>13</v>
       </c>
       <c r="K37" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L37" t="s">
         <v>6</v>
       </c>
       <c r="M37" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N37" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O37" t="s">
         <v>0</v>
       </c>
-      <c r="P37" s="1">
-        <v>3213390</v>
+      <c r="P37">
+        <v>0</v>
       </c>
       <c r="Q37" t="s">
-        <v>187</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>59480507</v>
+        <v>59684312</v>
       </c>
       <c r="B38" s="2">
-        <v>46087.544247685182</v>
+        <v>46091.557453703703</v>
       </c>
       <c r="C38">
-        <v>63301042</v>
+        <v>63319047</v>
       </c>
       <c r="D38" s="2">
-        <v>46157.380254629628</v>
+        <v>46157.516157407408</v>
       </c>
       <c r="E38" t="s">
         <v>60</v>
       </c>
       <c r="F38" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G38">
-        <v>708547070</v>
+        <v>3130227350</v>
       </c>
       <c r="H38" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="I38" t="s">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K38" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L38" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M38" t="s">
         <v>3</v>
       </c>
       <c r="N38" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="O38" t="s">
         <v>0</v>
@@ -3305,43 +3291,43 @@
       <c r="P38" t="s">
         <v>0</v>
       </c>
-      <c r="Q38">
-        <v>2721712020</v>
+      <c r="Q38" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>59537755</v>
+        <v>59894743</v>
       </c>
       <c r="B39" s="2">
-        <v>46088.586631944447</v>
+        <v>46094.687673611108</v>
       </c>
       <c r="C39">
-        <v>61591841</v>
+        <v>63587812</v>
       </c>
       <c r="D39" s="2">
-        <v>46127.35796296296</v>
+        <v>46162.52847222222</v>
       </c>
       <c r="E39" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="G39">
-        <v>556331131</v>
+        <v>759668146</v>
       </c>
       <c r="H39" t="s">
-        <v>146</v>
-      </c>
-      <c r="I39">
-        <v>1843236</v>
+        <v>37</v>
+      </c>
+      <c r="I39" t="s">
+        <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K39" t="s">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="L39" t="s">
         <v>6</v>
@@ -3350,42 +3336,42 @@
         <v>7</v>
       </c>
       <c r="N39" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O39" t="s">
         <v>0</v>
       </c>
-      <c r="P39">
+      <c r="P39" t="s">
         <v>0</v>
       </c>
       <c r="Q39" t="s">
-        <v>165</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>59541145</v>
+        <v>60748674</v>
       </c>
       <c r="B40" s="2">
-        <v>46088.634837962964</v>
+        <v>46111.511504629627</v>
       </c>
       <c r="C40">
-        <v>63319529</v>
+        <v>62475433</v>
       </c>
       <c r="D40" s="2">
-        <v>46157.520046296297</v>
+        <v>46141.624513888892</v>
       </c>
       <c r="E40" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>248</v>
+        <v>129</v>
       </c>
       <c r="G40">
-        <v>546008131</v>
+        <v>767791237</v>
       </c>
       <c r="H40" t="s">
-        <v>249</v>
+        <v>130</v>
       </c>
       <c r="I40" t="s">
         <v>0</v>
@@ -3394,16 +3380,16 @@
         <v>13</v>
       </c>
       <c r="K40" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L40" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="M40" t="s">
         <v>7</v>
       </c>
       <c r="N40" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O40" t="s">
         <v>0</v>
@@ -3412,316 +3398,316 @@
         <v>0</v>
       </c>
       <c r="Q40" t="s">
-        <v>221</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>59606122</v>
+        <v>60972166</v>
       </c>
       <c r="B41" s="2">
-        <v>46090.447604166664</v>
+        <v>46114.708020833335</v>
       </c>
       <c r="C41">
-        <v>61897702</v>
+        <v>62949578</v>
       </c>
       <c r="D41" s="2">
-        <v>46132.349363425928</v>
+        <v>46150.482407407406</v>
       </c>
       <c r="E41" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G41">
-        <v>708454305</v>
+        <v>160128782</v>
       </c>
       <c r="H41" t="s">
-        <v>166</v>
-      </c>
-      <c r="I41">
-        <v>1842206</v>
+        <v>135</v>
+      </c>
+      <c r="I41" t="s">
+        <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K41" t="s">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="L41" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M41" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N41" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O41" t="s">
         <v>0</v>
       </c>
-      <c r="P41">
-        <v>0</v>
+      <c r="P41" s="1">
+        <v>800000</v>
       </c>
       <c r="Q41" t="s">
-        <v>167</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>59615935</v>
+        <v>61220160</v>
       </c>
       <c r="B42" s="2">
-        <v>46090.512303240743</v>
+        <v>46120.483368055553</v>
       </c>
       <c r="C42">
-        <v>60393405</v>
+        <v>63331281</v>
       </c>
       <c r="D42" s="2">
-        <v>46105.432800925926</v>
+        <v>46157.621018518519</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G42">
-        <v>767081456</v>
+        <v>102571205</v>
       </c>
       <c r="H42" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I42" t="s">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K42" t="s">
         <v>5</v>
       </c>
       <c r="L42" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M42" t="s">
         <v>3</v>
       </c>
       <c r="N42" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O42" t="s">
         <v>0</v>
       </c>
-      <c r="P42">
-        <v>0</v>
+      <c r="P42" s="1">
+        <v>5000000</v>
       </c>
       <c r="Q42" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>59684312</v>
+        <v>61239047</v>
       </c>
       <c r="B43" s="2">
-        <v>46091.557453703703</v>
+        <v>46120.622071759259</v>
       </c>
       <c r="C43">
-        <v>63319047</v>
+        <v>63586097</v>
       </c>
       <c r="D43" s="2">
-        <v>46157.516157407408</v>
+        <v>46162.51457175926</v>
       </c>
       <c r="E43" t="s">
         <v>60</v>
       </c>
       <c r="F43" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G43">
-        <v>3130227350</v>
+        <v>103381121</v>
       </c>
       <c r="H43" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="I43" t="s">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="K43" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L43" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M43" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N43" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="O43" t="s">
         <v>0</v>
       </c>
-      <c r="P43" t="s">
+      <c r="P43">
         <v>0</v>
       </c>
       <c r="Q43" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>59894743</v>
+        <v>61240327</v>
       </c>
       <c r="B44" s="2">
-        <v>46094.687673611108</v>
+        <v>46120.631747685184</v>
       </c>
       <c r="C44">
-        <v>63466178</v>
+        <v>61667960</v>
       </c>
       <c r="D44" s="2">
-        <v>46160.561516203707</v>
+        <v>46128.415625000001</v>
       </c>
       <c r="E44" t="s">
-        <v>263</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G44">
-        <v>759668146</v>
+        <v>103381121</v>
       </c>
       <c r="H44" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="I44" t="s">
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="K44" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L44" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M44" t="s">
         <v>7</v>
       </c>
       <c r="N44" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O44" t="s">
         <v>0</v>
       </c>
-      <c r="P44" t="s">
+      <c r="P44">
         <v>0</v>
       </c>
       <c r="Q44" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>60356605</v>
+        <v>61240462</v>
       </c>
       <c r="B45" s="2">
-        <v>46104.623726851853</v>
+        <v>46120.632835648146</v>
       </c>
       <c r="C45">
-        <v>63346092</v>
+        <v>63588593</v>
       </c>
       <c r="D45" s="2">
-        <v>46157.73097222222</v>
+        <v>46162.53564814815</v>
       </c>
       <c r="E45" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="F45" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G45">
-        <v>504001081</v>
+        <v>769218598</v>
       </c>
       <c r="H45" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="I45" t="s">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="K45" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L45" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M45" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N45" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O45" t="s">
         <v>0</v>
       </c>
       <c r="P45" t="s">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="s">
-        <v>250</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>60748674</v>
+        <v>61242033</v>
       </c>
       <c r="B46" s="2">
-        <v>46111.511504629627</v>
+        <v>46120.643912037034</v>
       </c>
       <c r="C46">
-        <v>62475433</v>
+        <v>62945857</v>
       </c>
       <c r="D46" s="2">
-        <v>46141.624513888892</v>
+        <v>46150.456064814818</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G46">
-        <v>767791237</v>
+        <v>747636152</v>
       </c>
       <c r="H46" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="I46" t="s">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="K46" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L46" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M46" t="s">
         <v>7</v>
       </c>
       <c r="N46" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O46" t="s">
         <v>0</v>
@@ -3730,157 +3716,157 @@
         <v>0</v>
       </c>
       <c r="Q46" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>60972166</v>
+        <v>61244524</v>
       </c>
       <c r="B47" s="2">
-        <v>46114.708020833335</v>
+        <v>46120.66065972222</v>
       </c>
       <c r="C47">
-        <v>62949578</v>
+        <v>62308856</v>
       </c>
       <c r="D47" s="2">
-        <v>46150.482407407406</v>
+        <v>46139.393194444441</v>
       </c>
       <c r="E47" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="F47" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G47">
-        <v>160128782</v>
+        <v>757818829</v>
       </c>
       <c r="H47" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="I47" t="s">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="K47" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L47" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M47" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N47" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O47" t="s">
         <v>0</v>
       </c>
-      <c r="P47" s="1">
-        <v>800000</v>
+      <c r="P47" t="s">
+        <v>0</v>
       </c>
       <c r="Q47" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>61220160</v>
+        <v>61248751</v>
       </c>
       <c r="B48" s="2">
-        <v>46120.483368055553</v>
+        <v>46120.692800925928</v>
       </c>
       <c r="C48">
-        <v>63331281</v>
+        <v>63581455</v>
       </c>
       <c r="D48" s="2">
-        <v>46157.621018518519</v>
+        <v>46162.481759259259</v>
       </c>
       <c r="E48" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="G48">
-        <v>102571205</v>
+        <v>747636152</v>
       </c>
       <c r="H48" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="I48" t="s">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="K48" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L48" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N48" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O48" t="s">
         <v>0</v>
       </c>
-      <c r="P48" s="1">
-        <v>5000000</v>
+      <c r="P48">
+        <v>0</v>
       </c>
       <c r="Q48" t="s">
-        <v>31</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>61239047</v>
+        <v>61255901</v>
       </c>
       <c r="B49" s="2">
-        <v>46120.622071759259</v>
+        <v>46120.75712962963</v>
       </c>
       <c r="C49">
-        <v>63445965</v>
+        <v>62951388</v>
       </c>
       <c r="D49" s="2">
-        <v>46160.400810185187</v>
+        <v>46150.494675925926</v>
       </c>
       <c r="E49" t="s">
-        <v>264</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="G49">
-        <v>103381121</v>
+        <v>757818829</v>
       </c>
       <c r="H49" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="I49" t="s">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="K49" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="L49" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M49" t="s">
         <v>7</v>
       </c>
       <c r="N49" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O49" t="s">
         <v>0</v>
@@ -3889,39 +3875,39 @@
         <v>0</v>
       </c>
       <c r="Q49" t="s">
-        <v>168</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>61240327</v>
+        <v>61315991</v>
       </c>
       <c r="B50" s="2">
-        <v>46120.631747685184</v>
+        <v>46121.743379629632</v>
       </c>
       <c r="C50">
-        <v>61667960</v>
+        <v>62807088</v>
       </c>
       <c r="D50" s="2">
-        <v>46128.415625000001</v>
+        <v>46148.392731481479</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G50">
-        <v>103381121</v>
+        <v>778495680</v>
       </c>
       <c r="H50" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I50" t="s">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="K50" t="s">
         <v>1</v>
@@ -3930,222 +3916,222 @@
         <v>2</v>
       </c>
       <c r="M50" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N50" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O50" t="s">
         <v>0</v>
       </c>
-      <c r="P50">
+      <c r="P50" t="s">
         <v>0</v>
       </c>
       <c r="Q50" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>61240462</v>
+        <v>61336527</v>
       </c>
       <c r="B51" s="2">
-        <v>46120.632835648146</v>
+        <v>46122.368761574071</v>
       </c>
       <c r="C51">
-        <v>63458663</v>
+        <v>62807025</v>
       </c>
       <c r="D51" s="2">
-        <v>46160.499895833331</v>
+        <v>46148.392222222225</v>
       </c>
       <c r="E51" t="s">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G51">
-        <v>769218598</v>
+        <v>778495680</v>
       </c>
       <c r="H51" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="I51" t="s">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="K51" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="L51" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M51" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N51" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O51" t="s">
         <v>0</v>
       </c>
-      <c r="P51" t="s">
-        <v>0</v>
+      <c r="P51" s="1">
+        <v>1679940</v>
       </c>
       <c r="Q51" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>61242033</v>
+        <v>61481328</v>
       </c>
       <c r="B52" s="2">
-        <v>46120.643912037034</v>
+        <v>46125.483310185184</v>
       </c>
       <c r="C52">
-        <v>62945857</v>
+        <v>62173555</v>
       </c>
       <c r="D52" s="2">
-        <v>46150.456064814818</v>
+        <v>46136.44263888889</v>
       </c>
       <c r="E52" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="F52" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G52">
-        <v>747636152</v>
+        <v>708448800</v>
       </c>
       <c r="H52" t="s">
-        <v>95</v>
-      </c>
-      <c r="I52" t="s">
-        <v>0</v>
+        <v>173</v>
+      </c>
+      <c r="I52">
+        <v>1891736</v>
       </c>
       <c r="J52" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L52" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M52" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N52" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O52" t="s">
         <v>0</v>
       </c>
-      <c r="P52">
-        <v>0</v>
+      <c r="P52" s="1">
+        <v>500000</v>
       </c>
       <c r="Q52" t="s">
-        <v>105</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>61243441</v>
+        <v>61504448</v>
       </c>
       <c r="B53" s="2">
-        <v>46120.652592592596</v>
+        <v>46125.648935185185</v>
       </c>
       <c r="C53">
-        <v>62945141</v>
+        <v>62115179</v>
       </c>
       <c r="D53" s="2">
-        <v>46150.449965277781</v>
+        <v>46135.481111111112</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G53">
-        <v>747636152</v>
+        <v>707234610</v>
       </c>
       <c r="H53" t="s">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="I53" t="s">
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="K53" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L53" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M53" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N53" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O53" t="s">
         <v>0</v>
       </c>
-      <c r="P53">
-        <v>0</v>
+      <c r="P53" s="1">
+        <v>3070672</v>
       </c>
       <c r="Q53" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>61244524</v>
+        <v>61509953</v>
       </c>
       <c r="B54" s="2">
-        <v>46120.66065972222</v>
+        <v>46125.694004629629</v>
       </c>
       <c r="C54">
-        <v>62308856</v>
+        <v>62751418</v>
       </c>
       <c r="D54" s="2">
-        <v>46139.393194444441</v>
+        <v>46147.490636574075</v>
       </c>
       <c r="E54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F54" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G54">
-        <v>757818829</v>
+        <v>759379440</v>
       </c>
       <c r="H54" t="s">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="I54" t="s">
         <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="K54" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L54" t="s">
         <v>2</v>
       </c>
       <c r="M54" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N54" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O54" t="s">
         <v>0</v>
@@ -4153,299 +4139,299 @@
       <c r="P54" t="s">
         <v>0</v>
       </c>
-      <c r="Q54" t="s">
-        <v>170</v>
+      <c r="Q54">
+        <v>2732780110</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>61248751</v>
+        <v>61560663</v>
       </c>
       <c r="B55" s="2">
-        <v>46120.692800925928</v>
+        <v>46126.615729166668</v>
       </c>
       <c r="C55">
-        <v>63444825</v>
+        <v>62946623</v>
       </c>
       <c r="D55" s="2">
-        <v>46160.387303240743</v>
+        <v>46150.461550925924</v>
       </c>
       <c r="E55" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="G55">
-        <v>747636152</v>
+        <v>707984429</v>
       </c>
       <c r="H55" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="I55" t="s">
         <v>0</v>
       </c>
       <c r="J55" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="K55" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L55" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M55" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N55" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O55" t="s">
         <v>0</v>
       </c>
-      <c r="P55">
-        <v>0</v>
+      <c r="P55" s="1">
+        <v>2984038</v>
       </c>
       <c r="Q55" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>61255901</v>
+        <v>61608637</v>
       </c>
       <c r="B56" s="2">
-        <v>46120.75712962963</v>
+        <v>46127.491550925923</v>
       </c>
       <c r="C56">
-        <v>62951388</v>
+        <v>61677257</v>
       </c>
       <c r="D56" s="2">
-        <v>46150.494675925926</v>
+        <v>46128.483958333331</v>
       </c>
       <c r="E56" t="s">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="F56" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G56">
-        <v>757818829</v>
+        <v>702455701</v>
       </c>
       <c r="H56" t="s">
+        <v>37</v>
+      </c>
+      <c r="I56" t="s">
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>22</v>
+      </c>
+      <c r="K56" t="s">
+        <v>1</v>
+      </c>
+      <c r="L56" t="s">
+        <v>2</v>
+      </c>
+      <c r="M56" t="s">
+        <v>3</v>
+      </c>
+      <c r="N56" t="s">
+        <v>115</v>
+      </c>
+      <c r="O56" t="s">
+        <v>0</v>
+      </c>
+      <c r="P56" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="s">
         <v>118</v>
-      </c>
-      <c r="I56" t="s">
-        <v>0</v>
-      </c>
-      <c r="J56" t="s">
-        <v>13</v>
-      </c>
-      <c r="K56" t="s">
-        <v>5</v>
-      </c>
-      <c r="L56" t="s">
-        <v>8</v>
-      </c>
-      <c r="M56" t="s">
-        <v>7</v>
-      </c>
-      <c r="N56" t="s">
-        <v>121</v>
-      </c>
-      <c r="O56" t="s">
-        <v>0</v>
-      </c>
-      <c r="P56">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>61315991</v>
+        <v>61644382</v>
       </c>
       <c r="B57" s="2">
-        <v>46121.743379629632</v>
+        <v>46127.754131944443</v>
       </c>
       <c r="C57">
-        <v>62807088</v>
+        <v>61977733</v>
       </c>
       <c r="D57" s="2">
-        <v>46148.392731481479</v>
+        <v>46133.466458333336</v>
       </c>
       <c r="E57" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="G57">
-        <v>778495680</v>
+        <v>759250737</v>
       </c>
       <c r="H57" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I57" t="s">
         <v>0</v>
       </c>
       <c r="J57" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K57" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L57" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M57" t="s">
         <v>3</v>
       </c>
       <c r="N57" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O57" t="s">
         <v>0</v>
       </c>
-      <c r="P57" t="s">
-        <v>0</v>
+      <c r="P57" s="1">
+        <v>1680307</v>
       </c>
       <c r="Q57" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>61336527</v>
+        <v>61710072</v>
       </c>
       <c r="B58" s="2">
-        <v>46122.368761574071</v>
+        <v>46128.708032407405</v>
       </c>
       <c r="C58">
-        <v>62807025</v>
+        <v>62110207</v>
       </c>
       <c r="D58" s="2">
-        <v>46148.392222222225</v>
+        <v>46135.445254629631</v>
       </c>
       <c r="E58" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="F58" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G58">
-        <v>778495680</v>
+        <v>584425796</v>
       </c>
       <c r="H58" t="s">
-        <v>157</v>
-      </c>
-      <c r="I58" t="s">
+        <v>166</v>
+      </c>
+      <c r="I58">
         <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K58" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L58" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M58" t="s">
         <v>3</v>
       </c>
       <c r="N58" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O58" t="s">
         <v>0</v>
       </c>
-      <c r="P58" s="1">
-        <v>1679940</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>110</v>
+      <c r="P58" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>2721711717</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>61481328</v>
+        <v>61828334</v>
       </c>
       <c r="B59" s="2">
-        <v>46125.483310185184</v>
+        <v>46130.562754629631</v>
       </c>
       <c r="C59">
-        <v>62173555</v>
+        <v>62208296</v>
       </c>
       <c r="D59" s="2">
-        <v>46136.44263888889</v>
+        <v>46136.716527777775</v>
       </c>
       <c r="E59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F59" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G59">
-        <v>708448800</v>
+        <v>747309803</v>
       </c>
       <c r="H59" t="s">
-        <v>189</v>
-      </c>
-      <c r="I59">
-        <v>1891736</v>
+        <v>168</v>
+      </c>
+      <c r="I59" t="s">
+        <v>0</v>
       </c>
       <c r="J59" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K59" t="s">
         <v>9</v>
       </c>
       <c r="L59" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M59" t="s">
         <v>3</v>
       </c>
       <c r="N59" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O59" t="s">
         <v>0</v>
       </c>
       <c r="P59" s="1">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="Q59" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>61504448</v>
+        <v>61946442</v>
       </c>
       <c r="B60" s="2">
-        <v>46125.648935185185</v>
+        <v>46132.704247685186</v>
       </c>
       <c r="C60">
-        <v>62115179</v>
+        <v>62946744</v>
       </c>
       <c r="D60" s="2">
-        <v>46135.481111111112</v>
+        <v>46150.462650462963</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="G60">
-        <v>707234610</v>
+        <v>504041812</v>
       </c>
       <c r="H60" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I60" t="s">
         <v>0</v>
@@ -4463,60 +4449,60 @@
         <v>3</v>
       </c>
       <c r="N60" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O60" t="s">
         <v>0</v>
       </c>
       <c r="P60" s="1">
-        <v>3070672</v>
+        <v>1000000</v>
       </c>
       <c r="Q60" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>61509953</v>
+        <v>61972088</v>
       </c>
       <c r="B61" s="2">
-        <v>46125.694004629629</v>
+        <v>46133.422569444447</v>
       </c>
       <c r="C61">
-        <v>62751418</v>
+        <v>63486318</v>
       </c>
       <c r="D61" s="2">
-        <v>46147.490636574075</v>
+        <v>46160.711261574077</v>
       </c>
       <c r="E61" t="s">
-        <v>94</v>
+        <v>236</v>
       </c>
       <c r="F61" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G61">
-        <v>759379440</v>
+        <v>504041812</v>
       </c>
       <c r="H61" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I61" t="s">
         <v>0</v>
       </c>
       <c r="J61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K61" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L61" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M61" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N61" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O61" t="s">
         <v>0</v>
@@ -4524,34 +4510,34 @@
       <c r="P61" t="s">
         <v>0</v>
       </c>
-      <c r="Q61">
-        <v>2732780110</v>
+      <c r="Q61" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>61560663</v>
+        <v>61972108</v>
       </c>
       <c r="B62" s="2">
-        <v>46126.615729166668</v>
+        <v>46133.422662037039</v>
       </c>
       <c r="C62">
-        <v>62946623</v>
+        <v>62946845</v>
       </c>
       <c r="D62" s="2">
-        <v>46150.461550925924</v>
+        <v>46150.463449074072</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G62">
-        <v>707984429</v>
+        <v>504041812</v>
       </c>
       <c r="H62" t="s">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="I62" t="s">
         <v>0</v>
@@ -4566,98 +4552,98 @@
         <v>8</v>
       </c>
       <c r="M62" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N62" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O62" t="s">
         <v>0</v>
       </c>
       <c r="P62" s="1">
-        <v>2984038</v>
+        <v>1000000</v>
       </c>
       <c r="Q62" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>61608637</v>
+        <v>62014200</v>
       </c>
       <c r="B63" s="2">
-        <v>46127.491550925923</v>
+        <v>46133.721585648149</v>
       </c>
       <c r="C63">
-        <v>61677257</v>
+        <v>63591596</v>
       </c>
       <c r="D63" s="2">
-        <v>46128.483958333331</v>
+        <v>46162.559629629628</v>
       </c>
       <c r="E63" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="F63" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G63">
-        <v>702455701</v>
+        <v>709837321</v>
       </c>
       <c r="H63" t="s">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="I63" t="s">
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K63" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L63" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M63" t="s">
-        <v>3</v>
+        <v>161</v>
       </c>
       <c r="N63" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O63" t="s">
         <v>0</v>
       </c>
-      <c r="P63" t="s">
-        <v>0</v>
+      <c r="P63" s="1">
+        <v>1644000</v>
       </c>
       <c r="Q63" t="s">
-        <v>124</v>
+        <v>257</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>61644382</v>
+        <v>62170297</v>
       </c>
       <c r="B64" s="2">
-        <v>46127.754131944443</v>
+        <v>46136.420717592591</v>
       </c>
       <c r="C64">
-        <v>61977733</v>
+        <v>63515119</v>
       </c>
       <c r="D64" s="2">
-        <v>46133.466458333336</v>
+        <v>46161.464548611111</v>
       </c>
       <c r="E64" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="F64" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="G64">
-        <v>759250737</v>
+        <v>546016502</v>
       </c>
       <c r="H64" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="I64" t="s">
         <v>0</v>
@@ -4675,272 +4661,266 @@
         <v>3</v>
       </c>
       <c r="N64" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O64" t="s">
         <v>0</v>
       </c>
       <c r="P64" s="1">
-        <v>1680307</v>
+        <v>1500000</v>
       </c>
       <c r="Q64" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>61700587</v>
+        <v>62243628</v>
       </c>
       <c r="B65" s="2">
-        <v>46128.642256944448</v>
+        <v>46137.617604166669</v>
       </c>
       <c r="C65">
-        <v>63460926</v>
+        <v>63573687</v>
       </c>
       <c r="D65" s="2">
-        <v>46160.51457175926</v>
+        <v>46162.424050925925</v>
       </c>
       <c r="E65" t="s">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="F65" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G65">
-        <v>747568798</v>
+        <v>779191985</v>
       </c>
       <c r="H65" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="I65" t="s">
         <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K65" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="L65" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M65" t="s">
         <v>3</v>
       </c>
       <c r="N65" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O65" t="s">
         <v>0</v>
       </c>
-      <c r="P65" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>2722419000</v>
+      <c r="P65" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>61710072</v>
+        <v>62420329</v>
       </c>
       <c r="B66" s="2">
-        <v>46128.708032407405</v>
+        <v>46140.709513888891</v>
       </c>
       <c r="C66">
-        <v>62110207</v>
+        <v>63331641</v>
       </c>
       <c r="D66" s="2">
-        <v>46135.445254629631</v>
+        <v>46157.623310185183</v>
       </c>
       <c r="E66" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="F66" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G66">
-        <v>584425796</v>
+        <v>777621987</v>
       </c>
       <c r="H66" t="s">
-        <v>182</v>
-      </c>
-      <c r="I66">
+        <v>119</v>
+      </c>
+      <c r="I66" t="s">
         <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K66" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L66" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M66" t="s">
         <v>3</v>
       </c>
       <c r="N66" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O66" t="s">
         <v>0</v>
       </c>
-      <c r="P66" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>2721711717</v>
+      <c r="P66" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>61828334</v>
+        <v>62497009</v>
       </c>
       <c r="B67" s="2">
-        <v>46130.562754629631</v>
+        <v>46141.808842592596</v>
       </c>
       <c r="C67">
-        <v>62208296</v>
+        <v>63458983</v>
       </c>
       <c r="D67" s="2">
-        <v>46136.716527777775</v>
+        <v>46160.501875000002</v>
       </c>
       <c r="E67" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="F67" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G67">
-        <v>747309803</v>
+        <v>702495660</v>
       </c>
       <c r="H67" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="I67" t="s">
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K67" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L67" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M67" t="s">
         <v>3</v>
       </c>
-      <c r="N67" t="s">
-        <v>121</v>
-      </c>
       <c r="O67" t="s">
         <v>0</v>
       </c>
-      <c r="P67" s="1">
-        <v>1000000</v>
+      <c r="P67" t="s">
+        <v>0</v>
       </c>
       <c r="Q67" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>61946442</v>
+        <v>62551370</v>
       </c>
       <c r="B68" s="2">
-        <v>46132.704247685186</v>
+        <v>46142.717349537037</v>
       </c>
       <c r="C68">
-        <v>62946744</v>
+        <v>63134483</v>
       </c>
       <c r="D68" s="2">
-        <v>46150.462650462963</v>
+        <v>46154.380196759259</v>
       </c>
       <c r="E68" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F68" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G68">
-        <v>504041812</v>
+        <v>576382850</v>
       </c>
       <c r="H68" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I68" t="s">
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K68" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L68" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M68" t="s">
         <v>3</v>
       </c>
-      <c r="N68" t="s">
-        <v>121</v>
-      </c>
       <c r="O68" t="s">
         <v>0</v>
       </c>
-      <c r="P68" s="1">
-        <v>1000000</v>
+      <c r="P68" t="s">
+        <v>0</v>
       </c>
       <c r="Q68" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>61972088</v>
+        <v>62672227</v>
       </c>
       <c r="B69" s="2">
-        <v>46133.422569444447</v>
+        <v>46146.403935185182</v>
       </c>
       <c r="C69">
-        <v>62868217</v>
+        <v>63331081</v>
       </c>
       <c r="D69" s="2">
-        <v>46149.240729166668</v>
+        <v>46157.619120370371</v>
       </c>
       <c r="E69" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="F69" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G69">
-        <v>504041812</v>
+        <v>707169322</v>
       </c>
       <c r="H69" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I69" t="s">
         <v>0</v>
       </c>
       <c r="J69" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K69" t="s">
         <v>5</v>
       </c>
       <c r="L69" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M69" t="s">
         <v>7</v>
       </c>
       <c r="N69" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O69" t="s">
         <v>0</v>
@@ -4949,245 +4929,242 @@
         <v>0</v>
       </c>
       <c r="Q69" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>61972108</v>
+        <v>62672234</v>
       </c>
       <c r="B70" s="2">
-        <v>46133.422662037039</v>
+        <v>46146.403969907406</v>
       </c>
       <c r="C70">
-        <v>62946845</v>
+        <v>63487207</v>
       </c>
       <c r="D70" s="2">
-        <v>46150.463449074072</v>
+        <v>46160.717349537037</v>
       </c>
       <c r="E70" t="s">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="F70" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G70">
-        <v>504041812</v>
+        <v>707169322</v>
       </c>
       <c r="H70" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I70" t="s">
         <v>0</v>
       </c>
       <c r="J70" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K70" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L70" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M70" t="s">
         <v>14</v>
       </c>
       <c r="N70" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O70" t="s">
         <v>0</v>
       </c>
       <c r="P70" s="1">
-        <v>1000000</v>
+        <v>1644000</v>
       </c>
       <c r="Q70" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>62014200</v>
+        <v>62680657</v>
       </c>
       <c r="B71" s="2">
-        <v>46133.721585648149</v>
+        <v>46146.475763888891</v>
       </c>
       <c r="C71">
-        <v>63390600</v>
+        <v>63485029</v>
       </c>
       <c r="D71" s="2">
-        <v>46158.757106481484</v>
+        <v>46160.702488425923</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F71" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G71">
-        <v>709837321</v>
+        <v>778096389</v>
       </c>
       <c r="H71" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I71" t="s">
         <v>0</v>
       </c>
       <c r="J71" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="K71" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="L71" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M71" t="s">
-        <v>175</v>
-      </c>
-      <c r="N71" t="s">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c r="O71" t="s">
         <v>0</v>
       </c>
-      <c r="P71" s="1">
-        <v>1644000</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>31</v>
+      <c r="P71" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>2722560110</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>62170297</v>
+        <v>62682536</v>
       </c>
       <c r="B72" s="2">
-        <v>46136.420717592591</v>
+        <v>46146.490057870367</v>
       </c>
       <c r="C72">
-        <v>63338150</v>
+        <v>63584329</v>
       </c>
       <c r="D72" s="2">
-        <v>46157.670335648145</v>
+        <v>46162.501944444448</v>
       </c>
       <c r="E72" t="s">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="F72" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="G72">
-        <v>546016502</v>
+        <v>789817770</v>
       </c>
       <c r="H72" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I72" t="s">
         <v>0</v>
       </c>
       <c r="J72" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K72" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L72" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M72" t="s">
         <v>3</v>
       </c>
       <c r="N72" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O72" t="s">
         <v>0</v>
       </c>
       <c r="P72" s="1">
-        <v>1500000</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>265</v>
+        <v>150000</v>
+      </c>
+      <c r="Q72">
+        <v>2722560160</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>62243628</v>
+        <v>62715782</v>
       </c>
       <c r="B73" s="2">
-        <v>46137.617604166669</v>
+        <v>46146.73746527778</v>
       </c>
       <c r="C73">
-        <v>63197211</v>
+        <v>63567780</v>
       </c>
       <c r="D73" s="2">
-        <v>46155.393680555557</v>
+        <v>46162.358761574076</v>
       </c>
       <c r="E73" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="F73" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G73">
-        <v>779191985</v>
+        <v>707366919</v>
       </c>
       <c r="H73" t="s">
-        <v>251</v>
-      </c>
-      <c r="I73" t="s">
+        <v>37</v>
+      </c>
+      <c r="I73">
         <v>0</v>
       </c>
       <c r="J73" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K73" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L73" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M73" t="s">
         <v>3</v>
       </c>
       <c r="N73" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O73" t="s">
         <v>0</v>
       </c>
-      <c r="P73" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>223</v>
+      <c r="P73" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>2722520200</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>62249046</v>
+        <v>62722805</v>
       </c>
       <c r="B74" s="2">
-        <v>46137.688391203701</v>
+        <v>46146.81181712963</v>
       </c>
       <c r="C74">
-        <v>63239713</v>
+        <v>63060104</v>
       </c>
       <c r="D74" s="2">
-        <v>46155.72347222222</v>
+        <v>46152.916122685187</v>
       </c>
       <c r="E74" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G74">
-        <v>708946683</v>
+        <v>708131488</v>
       </c>
       <c r="H74" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="I74" t="s">
         <v>0</v>
@@ -5205,7 +5182,7 @@
         <v>3</v>
       </c>
       <c r="N74" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O74" t="s">
         <v>0</v>
@@ -5214,104 +5191,104 @@
         <v>0</v>
       </c>
       <c r="Q74" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>62420329</v>
+        <v>62760027</v>
       </c>
       <c r="B75" s="2">
-        <v>46140.709513888891</v>
+        <v>46147.546493055554</v>
       </c>
       <c r="C75">
-        <v>63331641</v>
+        <v>62902869</v>
       </c>
       <c r="D75" s="2">
-        <v>46157.623310185183</v>
+        <v>46149.631921296299</v>
       </c>
       <c r="E75" t="s">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="F75" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G75">
-        <v>777621987</v>
+        <v>777699799</v>
       </c>
       <c r="H75" t="s">
-        <v>125</v>
+        <v>206</v>
       </c>
       <c r="I75" t="s">
         <v>0</v>
       </c>
       <c r="J75" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K75" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L75" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M75" t="s">
         <v>3</v>
       </c>
       <c r="N75" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O75" t="s">
         <v>0</v>
       </c>
-      <c r="P75" s="1">
-        <v>1500000</v>
+      <c r="P75" t="s">
+        <v>0</v>
       </c>
       <c r="Q75" t="s">
-        <v>224</v>
+        <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>62497009</v>
+        <v>62768013</v>
       </c>
       <c r="B76" s="2">
-        <v>46141.808842592596</v>
+        <v>46147.609988425924</v>
       </c>
       <c r="C76">
-        <v>63458983</v>
+        <v>62871386</v>
       </c>
       <c r="D76" s="2">
-        <v>46160.501875000002</v>
+        <v>46149.364837962959</v>
       </c>
       <c r="E76" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="F76" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G76">
-        <v>702495660</v>
+        <v>143270405</v>
       </c>
       <c r="H76" t="s">
-        <v>37</v>
+        <v>208</v>
       </c>
       <c r="I76" t="s">
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K76" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M76" t="s">
         <v>3</v>
       </c>
       <c r="N76" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O76" t="s">
         <v>0</v>
@@ -5319,102 +5296,105 @@
       <c r="P76" t="s">
         <v>0</v>
       </c>
-      <c r="Q76">
-        <v>2722560060</v>
+      <c r="Q76" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>62544794</v>
+        <v>62840921</v>
       </c>
       <c r="B77" s="2">
-        <v>46142.662094907406</v>
+        <v>46148.636331018519</v>
       </c>
       <c r="C77">
-        <v>63208263</v>
+        <v>63101235</v>
       </c>
       <c r="D77" s="2">
-        <v>46155.483206018522</v>
+        <v>46153.608599537038</v>
       </c>
       <c r="E77" t="s">
-        <v>60</v>
+        <v>229</v>
       </c>
       <c r="F77" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G77">
-        <v>142128888</v>
+        <v>707551377</v>
       </c>
       <c r="H77" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I77" t="s">
         <v>0</v>
       </c>
       <c r="J77" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K77" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L77" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M77" t="s">
         <v>3</v>
       </c>
       <c r="N77" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="O77" t="s">
         <v>0</v>
       </c>
-      <c r="P77" s="1">
-        <v>500000</v>
+      <c r="P77" t="s">
+        <v>0</v>
       </c>
       <c r="Q77" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>62551370</v>
+        <v>62880594</v>
       </c>
       <c r="B78" s="2">
-        <v>46142.717349537037</v>
+        <v>46149.454710648148</v>
       </c>
       <c r="C78">
-        <v>63134483</v>
+        <v>62941351</v>
       </c>
       <c r="D78" s="2">
-        <v>46154.380196759259</v>
+        <v>46150.416979166665</v>
       </c>
       <c r="E78" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="G78">
-        <v>576382850</v>
+        <v>709565662</v>
       </c>
       <c r="H78" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="I78" t="s">
         <v>0</v>
       </c>
       <c r="J78" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K78" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M78" t="s">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="N78" t="s">
+        <v>115</v>
       </c>
       <c r="O78" t="s">
         <v>0</v>
@@ -5423,33 +5403,33 @@
         <v>0</v>
       </c>
       <c r="Q78" t="s">
-        <v>124</v>
+        <v>214</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>62672227</v>
+        <v>62880628</v>
       </c>
       <c r="B79" s="2">
-        <v>46146.403935185182</v>
+        <v>46149.45484953704</v>
       </c>
       <c r="C79">
-        <v>63331081</v>
+        <v>62941416</v>
       </c>
       <c r="D79" s="2">
-        <v>46157.619120370371</v>
+        <v>46150.417719907404</v>
       </c>
       <c r="E79" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F79" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G79">
-        <v>707169322</v>
+        <v>709565662</v>
       </c>
       <c r="H79" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="I79" t="s">
         <v>0</v>
@@ -5464,257 +5444,257 @@
         <v>6</v>
       </c>
       <c r="M79" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N79" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O79" t="s">
         <v>0</v>
       </c>
-      <c r="P79" t="s">
+      <c r="P79">
         <v>0</v>
       </c>
       <c r="Q79" t="s">
-        <v>31</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>62672234</v>
+        <v>62880812</v>
       </c>
       <c r="B80" s="2">
-        <v>46146.403969907406</v>
+        <v>46149.456157407411</v>
       </c>
       <c r="C80">
-        <v>63346032</v>
+        <v>63518739</v>
       </c>
       <c r="D80" s="2">
-        <v>46157.730034722219</v>
+        <v>46161.489374999997</v>
       </c>
       <c r="E80" t="s">
-        <v>60</v>
+        <v>202</v>
       </c>
       <c r="F80" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="G80">
-        <v>707169322</v>
+        <v>707672487</v>
       </c>
       <c r="H80" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="I80" t="s">
         <v>0</v>
       </c>
       <c r="J80" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K80" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L80" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M80" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N80" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O80" t="s">
         <v>0</v>
       </c>
-      <c r="P80" s="1">
-        <v>1644000</v>
+      <c r="P80" t="s">
+        <v>0</v>
       </c>
       <c r="Q80" t="s">
-        <v>252</v>
+        <v>118</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>62680657</v>
+        <v>62937923</v>
       </c>
       <c r="B81" s="2">
-        <v>46146.475763888891</v>
+        <v>46150.381145833337</v>
       </c>
       <c r="C81">
-        <v>63316862</v>
+        <v>63523789</v>
       </c>
       <c r="D81" s="2">
-        <v>46157.500787037039</v>
+        <v>46161.526226851849</v>
       </c>
       <c r="E81" t="s">
         <v>60</v>
       </c>
       <c r="F81" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G81">
-        <v>778096389</v>
+        <v>565811689</v>
       </c>
       <c r="H81" t="s">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c r="I81" t="s">
         <v>0</v>
       </c>
       <c r="J81" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="K81" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L81" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M81" t="s">
         <v>3</v>
       </c>
       <c r="N81" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="O81" t="s">
         <v>0</v>
       </c>
-      <c r="P81" t="s">
-        <v>0</v>
+      <c r="P81" s="1">
+        <v>250000</v>
       </c>
       <c r="Q81" t="s">
-        <v>59</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>62682536</v>
+        <v>62968196</v>
       </c>
       <c r="B82" s="2">
-        <v>46146.490057870367</v>
+        <v>46150.638715277775</v>
       </c>
       <c r="C82">
-        <v>63060102</v>
+        <v>63584773</v>
       </c>
       <c r="D82" s="2">
-        <v>46152.915081018517</v>
+        <v>46162.505300925928</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>259</v>
       </c>
       <c r="F82" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="G82">
-        <v>789817770</v>
+        <v>758177759</v>
       </c>
       <c r="H82" t="s">
-        <v>212</v>
+        <v>37</v>
       </c>
       <c r="I82" t="s">
         <v>0</v>
       </c>
       <c r="J82" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K82" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L82" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M82" t="s">
-        <v>3</v>
+        <v>161</v>
       </c>
       <c r="N82" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O82" t="s">
         <v>0</v>
       </c>
       <c r="P82" s="1">
-        <v>150000</v>
+        <v>2881416</v>
       </c>
       <c r="Q82" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>62715782</v>
+        <v>63025600</v>
       </c>
       <c r="B83" s="2">
-        <v>46146.73746527778</v>
+        <v>46151.740983796299</v>
       </c>
       <c r="C83">
-        <v>63315259</v>
+        <v>63408272</v>
       </c>
       <c r="D83" s="2">
-        <v>46157.490590277775</v>
+        <v>46159.533958333333</v>
       </c>
       <c r="E83" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G83">
-        <v>707366919</v>
+        <v>758237461</v>
       </c>
       <c r="H83" t="s">
-        <v>37</v>
+        <v>220</v>
       </c>
       <c r="I83" t="s">
         <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K83" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L83" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M83" t="s">
         <v>3</v>
       </c>
       <c r="N83" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O83" t="s">
         <v>0</v>
       </c>
-      <c r="P83" t="s">
-        <v>0</v>
+      <c r="P83" s="1">
+        <v>850000</v>
       </c>
       <c r="Q83" t="s">
-        <v>124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>62722805</v>
+        <v>63073782</v>
       </c>
       <c r="B84" s="2">
-        <v>46146.81181712963</v>
+        <v>46153.387870370374</v>
       </c>
       <c r="C84">
-        <v>63060104</v>
+        <v>63389964</v>
       </c>
       <c r="D84" s="2">
-        <v>46152.916122685187</v>
+        <v>46158.743206018517</v>
       </c>
       <c r="E84" t="s">
         <v>19</v>
       </c>
       <c r="F84" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="G84">
-        <v>708131488</v>
+        <v>710619970</v>
       </c>
       <c r="H84" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="I84" t="s">
         <v>0</v>
@@ -5732,7 +5712,7 @@
         <v>3</v>
       </c>
       <c r="N84" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O84" t="s">
         <v>0</v>
@@ -5741,139 +5721,139 @@
         <v>0</v>
       </c>
       <c r="Q84" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>62748443</v>
+        <v>63143165</v>
       </c>
       <c r="B85" s="2">
-        <v>46147.475057870368</v>
+        <v>46154.449884259258</v>
       </c>
       <c r="C85">
-        <v>63451636</v>
+        <v>63542681</v>
       </c>
       <c r="D85" s="2">
-        <v>46160.451273148145</v>
+        <v>46161.670798611114</v>
       </c>
       <c r="E85" t="s">
-        <v>186</v>
+        <v>263</v>
       </c>
       <c r="F85" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G85">
-        <v>757750210</v>
+        <v>708473548</v>
       </c>
       <c r="H85" t="s">
-        <v>37</v>
-      </c>
-      <c r="I85" t="s">
-        <v>0</v>
+        <v>261</v>
+      </c>
+      <c r="I85">
+        <v>1942866</v>
       </c>
       <c r="J85" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K85" t="s">
         <v>5</v>
       </c>
       <c r="L85" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M85" t="s">
-        <v>3</v>
+        <v>254</v>
       </c>
       <c r="N85" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O85" t="s">
         <v>0</v>
       </c>
-      <c r="P85">
-        <v>0</v>
+      <c r="P85" s="1">
+        <v>7837678</v>
       </c>
       <c r="Q85" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>62760027</v>
+        <v>63168095</v>
       </c>
       <c r="B86" s="2">
-        <v>46147.546493055554</v>
+        <v>46154.647604166668</v>
       </c>
       <c r="C86">
-        <v>62902869</v>
+        <v>63408293</v>
       </c>
       <c r="D86" s="2">
-        <v>46149.631921296299</v>
+        <v>46159.53460648148</v>
       </c>
       <c r="E86" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>228</v>
+        <v>29</v>
       </c>
       <c r="G86">
-        <v>777699799</v>
+        <v>747345191</v>
       </c>
       <c r="H86" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I86" t="s">
         <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K86" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L86" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M86" t="s">
         <v>3</v>
       </c>
       <c r="N86" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O86" t="s">
         <v>0</v>
       </c>
-      <c r="P86" t="s">
-        <v>0</v>
+      <c r="P86" s="1">
+        <v>7103410</v>
       </c>
       <c r="Q86" t="s">
-        <v>124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>62768013</v>
+        <v>63178332</v>
       </c>
       <c r="B87" s="2">
-        <v>46147.609988425924</v>
+        <v>46154.725729166668</v>
       </c>
       <c r="C87">
-        <v>62871386</v>
+        <v>63586939</v>
       </c>
       <c r="D87" s="2">
-        <v>46149.364837962959</v>
+        <v>46162.520671296297</v>
       </c>
       <c r="E87" t="s">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="F87" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G87">
-        <v>143270405</v>
+        <v>708773097</v>
       </c>
       <c r="H87" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I87" t="s">
         <v>0</v>
@@ -5882,7 +5862,7 @@
         <v>18</v>
       </c>
       <c r="K87" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L87" t="s">
         <v>8</v>
@@ -5891,13 +5871,13 @@
         <v>3</v>
       </c>
       <c r="N87" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O87" t="s">
         <v>0</v>
       </c>
-      <c r="P87" t="s">
-        <v>0</v>
+      <c r="P87" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q87" t="s">
         <v>24</v>
@@ -5905,25 +5885,25 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>62840921</v>
+        <v>63179342</v>
       </c>
       <c r="B88" s="2">
-        <v>46148.636331018519</v>
+        <v>46154.735729166663</v>
       </c>
       <c r="C88">
-        <v>63101235</v>
+        <v>63588203</v>
       </c>
       <c r="D88" s="2">
-        <v>46153.608599537038</v>
+        <v>46162.532152777778</v>
       </c>
       <c r="E88" t="s">
-        <v>253</v>
+        <v>198</v>
       </c>
       <c r="F88" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G88">
-        <v>707551377</v>
+        <v>778179203</v>
       </c>
       <c r="H88" t="s">
         <v>233</v>
@@ -5932,107 +5912,107 @@
         <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K88" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L88" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M88" t="s">
         <v>3</v>
       </c>
       <c r="N88" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O88" t="s">
         <v>0</v>
       </c>
-      <c r="P88" t="s">
-        <v>0</v>
+      <c r="P88" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q88" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>62880594</v>
+        <v>63210811</v>
       </c>
       <c r="B89" s="2">
-        <v>46149.454710648148</v>
+        <v>46155.50409722222</v>
       </c>
       <c r="C89">
-        <v>62941351</v>
+        <v>63564036</v>
       </c>
       <c r="D89" s="2">
-        <v>46150.416979166665</v>
+        <v>46162.028981481482</v>
       </c>
       <c r="E89" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F89" t="s">
+        <v>234</v>
+      </c>
+      <c r="G89">
+        <v>160128782</v>
+      </c>
+      <c r="H89" t="s">
         <v>235</v>
       </c>
-      <c r="G89">
-        <v>709565662</v>
-      </c>
-      <c r="H89" t="s">
-        <v>236</v>
-      </c>
       <c r="I89" t="s">
         <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K89" t="s">
         <v>5</v>
       </c>
       <c r="L89" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M89" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N89" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O89" t="s">
         <v>0</v>
       </c>
-      <c r="P89" t="s">
-        <v>0</v>
+      <c r="P89" s="1">
+        <v>800000</v>
       </c>
       <c r="Q89" t="s">
-        <v>237</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>62880628</v>
+        <v>63303380</v>
       </c>
       <c r="B90" s="2">
-        <v>46149.45484953704</v>
+        <v>46157.402731481481</v>
       </c>
       <c r="C90">
-        <v>62941416</v>
+        <v>63577434</v>
       </c>
       <c r="D90" s="2">
-        <v>46150.417719907404</v>
+        <v>46162.453518518516</v>
       </c>
       <c r="E90" t="s">
-        <v>16</v>
+        <v>259</v>
       </c>
       <c r="F90" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="G90">
-        <v>709565662</v>
+        <v>707282722</v>
       </c>
       <c r="H90" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="I90" t="s">
         <v>0</v>
@@ -6047,148 +6027,148 @@
         <v>6</v>
       </c>
       <c r="M90" t="s">
-        <v>14</v>
+        <v>161</v>
       </c>
       <c r="N90" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O90" t="s">
         <v>0</v>
       </c>
-      <c r="P90">
-        <v>0</v>
+      <c r="P90" s="1">
+        <v>4053290</v>
       </c>
       <c r="Q90" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>62880812</v>
+        <v>63330974</v>
       </c>
       <c r="B91" s="2">
-        <v>46149.456157407411</v>
+        <v>46157.61818287037</v>
       </c>
       <c r="C91">
-        <v>63224093</v>
+        <v>63513801</v>
       </c>
       <c r="D91" s="2">
-        <v>46155.609270833331</v>
+        <v>46161.454861111109</v>
       </c>
       <c r="E91" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="F91" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G91">
-        <v>707672487</v>
+        <v>759530809</v>
       </c>
       <c r="H91" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I91" t="s">
         <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K91" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L91" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M91" t="s">
-        <v>3</v>
+        <v>161</v>
       </c>
       <c r="N91" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="O91" t="s">
         <v>0</v>
       </c>
-      <c r="P91" t="s">
-        <v>0</v>
+      <c r="P91" s="1">
+        <v>1644000</v>
       </c>
       <c r="Q91" t="s">
-        <v>59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>62937923</v>
+        <v>63443742</v>
       </c>
       <c r="B92" s="2">
-        <v>46150.381145833337</v>
+        <v>46160.375115740739</v>
       </c>
       <c r="C92">
-        <v>63342821</v>
+        <v>63443769</v>
       </c>
       <c r="D92" s="2">
-        <v>46157.705046296294</v>
+        <v>46160.375509259262</v>
       </c>
       <c r="E92" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="F92" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G92">
-        <v>565811689</v>
+        <v>798886434</v>
       </c>
       <c r="H92" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="I92" t="s">
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K92" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L92" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M92" t="s">
         <v>3</v>
       </c>
       <c r="N92" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O92" t="s">
         <v>0</v>
       </c>
-      <c r="P92" s="1">
-        <v>250000</v>
+      <c r="P92" t="s">
+        <v>0</v>
       </c>
       <c r="Q92" t="s">
-        <v>266</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>62968196</v>
+        <v>63449095</v>
       </c>
       <c r="B93" s="2">
-        <v>46150.638715277775</v>
+        <v>46160.428668981483</v>
       </c>
       <c r="C93">
-        <v>63089942</v>
+        <v>63449152</v>
       </c>
       <c r="D93" s="2">
-        <v>46153.521840277775</v>
+        <v>46160.429050925923</v>
       </c>
       <c r="E93" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="F93" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="G93">
-        <v>758177759</v>
+        <v>768420441</v>
       </c>
       <c r="H93" t="s">
         <v>37</v>
@@ -6197,184 +6177,184 @@
         <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K93" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L93" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M93" t="s">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="N93" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O93" t="s">
         <v>0</v>
       </c>
-      <c r="P93" s="1">
-        <v>2881416</v>
+      <c r="P93" t="s">
+        <v>0</v>
       </c>
       <c r="Q93" t="s">
-        <v>0</v>
+        <v>265</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>63025600</v>
+        <v>63451685</v>
       </c>
       <c r="B94" s="2">
-        <v>46151.740983796299</v>
+        <v>46160.45171296296</v>
       </c>
       <c r="C94">
-        <v>63408272</v>
+        <v>63580027</v>
       </c>
       <c r="D94" s="2">
-        <v>46159.533958333333</v>
+        <v>46162.471990740742</v>
       </c>
       <c r="E94" t="s">
-        <v>19</v>
+        <v>236</v>
       </c>
       <c r="F94" t="s">
-        <v>242</v>
+        <v>102</v>
       </c>
       <c r="G94">
-        <v>758237461</v>
+        <v>707407425</v>
       </c>
       <c r="H94" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="I94" t="s">
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K94" t="s">
         <v>5</v>
       </c>
       <c r="L94" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M94" t="s">
         <v>3</v>
       </c>
       <c r="N94" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O94" t="s">
         <v>0</v>
       </c>
       <c r="P94" s="1">
-        <v>850000</v>
+        <v>2000000</v>
       </c>
       <c r="Q94" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>63073782</v>
+        <v>63453142</v>
       </c>
       <c r="B95" s="2">
-        <v>46153.387870370374</v>
+        <v>46160.461238425924</v>
       </c>
       <c r="C95">
-        <v>63389964</v>
+        <v>63498358</v>
       </c>
       <c r="D95" s="2">
-        <v>46158.743206018517</v>
+        <v>46160.906828703701</v>
       </c>
       <c r="E95" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="F95" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G95">
-        <v>710619970</v>
+        <v>507828407</v>
       </c>
       <c r="H95" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I95" t="s">
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K95" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L95" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M95" t="s">
         <v>3</v>
       </c>
       <c r="N95" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O95" t="s">
         <v>0</v>
       </c>
-      <c r="P95" t="s">
-        <v>0</v>
+      <c r="P95" s="1">
+        <v>1009545</v>
       </c>
       <c r="Q95" t="s">
-        <v>105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>63143165</v>
+        <v>63453475</v>
       </c>
       <c r="B96" s="2">
-        <v>46154.449884259258</v>
+        <v>46160.463773148149</v>
       </c>
       <c r="C96">
-        <v>63143198</v>
+        <v>63498333</v>
       </c>
       <c r="D96" s="2">
-        <v>46154.450150462966</v>
+        <v>46160.904537037037</v>
       </c>
       <c r="E96" t="s">
-        <v>254</v>
+        <v>202</v>
       </c>
       <c r="F96" t="s">
-        <v>255</v>
+        <v>102</v>
       </c>
       <c r="G96">
-        <v>708473548</v>
+        <v>708343014</v>
       </c>
       <c r="H96" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I96" t="s">
         <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K96" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L96" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M96" t="s">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="N96" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="O96" t="s">
         <v>0</v>
       </c>
       <c r="P96" s="1">
-        <v>7837678</v>
+        <v>3940384</v>
       </c>
       <c r="Q96" t="s">
         <v>0</v>
@@ -6382,240 +6362,240 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>63168095</v>
+        <v>63462158</v>
       </c>
       <c r="B97" s="2">
-        <v>46154.647604166668</v>
+        <v>46160.525254629632</v>
       </c>
       <c r="C97">
-        <v>63168477</v>
+        <v>63498261</v>
       </c>
       <c r="D97" s="2">
-        <v>46154.649652777778</v>
+        <v>46160.901041666664</v>
       </c>
       <c r="E97" t="s">
-        <v>254</v>
+        <v>202</v>
       </c>
       <c r="F97" t="s">
-        <v>29</v>
+        <v>252</v>
       </c>
       <c r="G97">
-        <v>747345191</v>
+        <v>768231346</v>
       </c>
       <c r="H97" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I97" t="s">
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K97" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="L97" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M97" t="s">
         <v>3</v>
       </c>
       <c r="N97" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="O97" t="s">
         <v>0</v>
       </c>
       <c r="P97" s="1">
-        <v>7103410</v>
+        <v>518450</v>
       </c>
       <c r="Q97" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>63178332</v>
+        <v>63477655</v>
       </c>
       <c r="B98" s="2">
-        <v>46154.725729166668</v>
+        <v>46160.651041666664</v>
       </c>
       <c r="C98">
-        <v>63466467</v>
+        <v>63567909</v>
       </c>
       <c r="D98" s="2">
-        <v>46160.564699074072</v>
+        <v>46162.360648148147</v>
       </c>
       <c r="E98" t="s">
-        <v>263</v>
+        <v>128</v>
       </c>
       <c r="F98" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="G98">
-        <v>708773097</v>
+        <v>709528212</v>
       </c>
       <c r="H98" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I98" t="s">
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K98" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M98" t="s">
         <v>3</v>
       </c>
       <c r="N98" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O98" t="s">
         <v>0</v>
       </c>
-      <c r="P98" s="1">
-        <v>2000000</v>
+      <c r="P98" t="s">
+        <v>0</v>
       </c>
       <c r="Q98" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>63179342</v>
+        <v>63495969</v>
       </c>
       <c r="B99" s="2">
-        <v>46154.735729166663</v>
+        <v>46160.82644675926</v>
       </c>
       <c r="C99">
-        <v>63466705</v>
+        <v>63592456</v>
       </c>
       <c r="D99" s="2">
-        <v>46160.566377314812</v>
+        <v>46162.567696759259</v>
       </c>
       <c r="E99" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="F99" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="G99">
-        <v>778179203</v>
+        <v>747777575</v>
       </c>
       <c r="H99" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="I99" t="s">
         <v>0</v>
       </c>
       <c r="J99" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K99" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L99" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M99" t="s">
         <v>3</v>
       </c>
       <c r="N99" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O99" t="s">
         <v>0</v>
       </c>
-      <c r="P99" s="1">
-        <v>2000000</v>
+      <c r="P99" t="s">
+        <v>0</v>
       </c>
       <c r="Q99" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>63210811</v>
+        <v>63518010</v>
       </c>
       <c r="B100" s="2">
-        <v>46155.50409722222</v>
+        <v>46161.484699074077</v>
       </c>
       <c r="C100">
-        <v>63210839</v>
+        <v>63520643</v>
       </c>
       <c r="D100" s="2">
-        <v>46155.504328703704</v>
+        <v>46161.502881944441</v>
       </c>
       <c r="E100" t="s">
-        <v>254</v>
+        <v>202</v>
       </c>
       <c r="F100" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="G100">
-        <v>160128782</v>
+        <v>758276318</v>
       </c>
       <c r="H100" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="I100" t="s">
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M100" t="s">
-        <v>3</v>
+        <v>161</v>
       </c>
       <c r="N100" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O100" t="s">
         <v>0</v>
       </c>
       <c r="P100" s="1">
-        <v>800000</v>
+        <v>200000</v>
       </c>
       <c r="Q100" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>63302106</v>
+        <v>63518049</v>
       </c>
       <c r="B101" s="2">
-        <v>46157.389525462961</v>
+        <v>46161.484918981485</v>
       </c>
       <c r="C101">
-        <v>63302124</v>
+        <v>63520839</v>
       </c>
       <c r="D101" s="2">
-        <v>46157.389907407407</v>
+        <v>46161.504050925927</v>
       </c>
       <c r="E101" t="s">
-        <v>254</v>
+        <v>202</v>
       </c>
       <c r="F101" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G101">
-        <v>707282722</v>
+        <v>758276318</v>
       </c>
       <c r="H101" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I101" t="s">
         <v>0</v>
@@ -6624,128 +6604,128 @@
         <v>13</v>
       </c>
       <c r="K101" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L101" t="s">
         <v>6</v>
       </c>
       <c r="M101" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="N101" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O101" t="s">
         <v>0</v>
       </c>
       <c r="P101" s="1">
-        <v>946304</v>
+        <v>200000</v>
       </c>
       <c r="Q101" t="s">
-        <v>269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>63303380</v>
+        <v>63519784</v>
       </c>
       <c r="B102" s="2">
-        <v>46157.402731481481</v>
+        <v>46161.496840277781</v>
       </c>
       <c r="C102">
-        <v>63303417</v>
+        <v>63555124</v>
       </c>
       <c r="D102" s="2">
-        <v>46157.402997685182</v>
+        <v>46161.762708333335</v>
       </c>
       <c r="E102" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F102" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G102">
-        <v>707282722</v>
+        <v>707079088</v>
       </c>
       <c r="H102" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="I102" t="s">
         <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K102" t="s">
         <v>5</v>
       </c>
       <c r="L102" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M102" t="s">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="N102" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O102" t="s">
         <v>0</v>
       </c>
       <c r="P102" s="1">
-        <v>4053290</v>
+        <v>1400000</v>
       </c>
       <c r="Q102" t="s">
-        <v>271</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>63330974</v>
+        <v>63526115</v>
       </c>
       <c r="B103" s="2">
-        <v>46157.61818287037</v>
+        <v>46161.544733796298</v>
       </c>
       <c r="C103">
-        <v>63331008</v>
+        <v>63581111</v>
       </c>
       <c r="D103" s="2">
-        <v>46157.61855324074</v>
+        <v>46162.479467592595</v>
       </c>
       <c r="E103" t="s">
-        <v>254</v>
+        <v>111</v>
       </c>
       <c r="F103" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G103">
-        <v>759530809</v>
+        <v>707722441</v>
       </c>
       <c r="H103" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I103" t="s">
         <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K103" t="s">
         <v>5</v>
       </c>
       <c r="L103" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M103" t="s">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="N103" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O103" t="s">
         <v>0</v>
       </c>
       <c r="P103" s="1">
-        <v>1644000</v>
+        <v>1513624</v>
       </c>
       <c r="Q103" t="s">
         <v>0</v>
@@ -6753,105 +6733,105 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>63443742</v>
+        <v>63529958</v>
       </c>
       <c r="B104" s="2">
-        <v>46160.375115740739</v>
+        <v>46161.577581018515</v>
       </c>
       <c r="C104">
-        <v>63443769</v>
+        <v>63553650</v>
       </c>
       <c r="D104" s="2">
-        <v>46160.375509259262</v>
+        <v>46161.745011574072</v>
       </c>
       <c r="E104" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="F104" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G104">
-        <v>798886434</v>
+        <v>708081052</v>
       </c>
       <c r="H104" t="s">
-        <v>118</v>
+        <v>37</v>
       </c>
       <c r="I104" t="s">
         <v>0</v>
       </c>
       <c r="J104" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K104" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L104" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M104" t="s">
         <v>3</v>
       </c>
       <c r="N104" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="O104" t="s">
         <v>0</v>
       </c>
-      <c r="P104" t="s">
-        <v>0</v>
+      <c r="P104" s="1">
+        <v>655375</v>
       </c>
       <c r="Q104" t="s">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>63449095</v>
+        <v>63535613</v>
       </c>
       <c r="B105" s="2">
-        <v>46160.428668981483</v>
+        <v>46161.623263888891</v>
       </c>
       <c r="C105">
-        <v>63449152</v>
+        <v>63574280</v>
       </c>
       <c r="D105" s="2">
-        <v>46160.429050925923</v>
+        <v>46162.4296412037</v>
       </c>
       <c r="E105" t="s">
-        <v>275</v>
+        <v>111</v>
       </c>
       <c r="F105" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G105">
-        <v>768420441</v>
+        <v>747165047</v>
       </c>
       <c r="H105" t="s">
-        <v>37</v>
+        <v>278</v>
       </c>
       <c r="I105" t="s">
         <v>0</v>
       </c>
       <c r="J105" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K105" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L105" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M105" t="s">
         <v>3</v>
       </c>
       <c r="N105" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="O105" t="s">
         <v>0</v>
       </c>
-      <c r="P105" t="s">
-        <v>0</v>
+      <c r="P105" s="1">
+        <v>277235</v>
       </c>
       <c r="Q105" t="s">
         <v>0</v>
@@ -6859,52 +6839,52 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>63451685</v>
+        <v>63556908</v>
       </c>
       <c r="B106" s="2">
-        <v>46160.45171296296</v>
+        <v>46161.788553240738</v>
       </c>
       <c r="C106">
-        <v>63451731</v>
+        <v>63577836</v>
       </c>
       <c r="D106" s="2">
-        <v>46160.451956018522</v>
+        <v>46162.456759259258</v>
       </c>
       <c r="E106" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="F106" t="s">
-        <v>104</v>
+        <v>279</v>
       </c>
       <c r="G106">
-        <v>707407425</v>
+        <v>711458931</v>
       </c>
       <c r="H106" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I106" t="s">
         <v>0</v>
       </c>
       <c r="J106" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K106" t="s">
         <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M106" t="s">
         <v>3</v>
       </c>
       <c r="N106" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O106" t="s">
         <v>0</v>
       </c>
       <c r="P106" s="1">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q106" t="s">
         <v>0</v>
@@ -6912,28 +6892,28 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>63453142</v>
+        <v>63577039</v>
       </c>
       <c r="B107" s="2">
-        <v>46160.461238425924</v>
+        <v>46162.450127314813</v>
       </c>
       <c r="C107">
-        <v>63453202</v>
+        <v>63580950</v>
       </c>
       <c r="D107" s="2">
-        <v>46160.461481481485</v>
+        <v>46162.47828703704</v>
       </c>
       <c r="E107" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="F107" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G107">
-        <v>507828407</v>
+        <v>716610940</v>
       </c>
       <c r="H107" t="s">
-        <v>279</v>
+        <v>94</v>
       </c>
       <c r="I107" t="s">
         <v>0</v>
@@ -6951,129 +6931,73 @@
         <v>3</v>
       </c>
       <c r="N107" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="O107" t="s">
         <v>0</v>
       </c>
       <c r="P107" s="1">
-        <v>1009545</v>
+        <v>299185</v>
       </c>
       <c r="Q107" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>63453475</v>
+        <v>63578582</v>
       </c>
       <c r="B108" s="2">
-        <v>46160.463773148149</v>
+        <v>46162.462199074071</v>
       </c>
       <c r="C108">
-        <v>63453534</v>
+        <v>63580163</v>
       </c>
       <c r="D108" s="2">
-        <v>46160.464131944442</v>
+        <v>46162.472939814812</v>
       </c>
       <c r="E108" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="F108" t="s">
-        <v>104</v>
+        <v>283</v>
       </c>
       <c r="G108">
-        <v>708343014</v>
+        <v>759974992</v>
       </c>
       <c r="H108" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I108" t="s">
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>18</v>
+        <v>285</v>
       </c>
       <c r="K108" t="s">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="L108" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M108" t="s">
         <v>3</v>
       </c>
       <c r="N108" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O108" t="s">
         <v>0</v>
       </c>
       <c r="P108" s="1">
-        <v>3940384</v>
+        <v>4487314</v>
       </c>
       <c r="Q108" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A109">
-        <v>63462158</v>
-      </c>
-      <c r="B109" s="2">
-        <v>46160.525254629632</v>
-      </c>
-      <c r="C109">
-        <v>63462196</v>
-      </c>
-      <c r="D109" s="2">
-        <v>46160.525601851848</v>
-      </c>
-      <c r="E109" t="s">
-        <v>254</v>
-      </c>
-      <c r="F109" t="s">
-        <v>281</v>
-      </c>
-      <c r="G109">
-        <v>768231346</v>
-      </c>
-      <c r="H109" t="s">
-        <v>282</v>
-      </c>
-      <c r="I109" t="s">
-        <v>0</v>
-      </c>
-      <c r="J109" t="s">
-        <v>13</v>
-      </c>
-      <c r="K109" t="s">
-        <v>127</v>
-      </c>
-      <c r="L109" t="s">
-        <v>6</v>
-      </c>
-      <c r="M109" t="s">
-        <v>3</v>
-      </c>
-      <c r="N109" t="s">
-        <v>121</v>
-      </c>
-      <c r="O109" t="s">
-        <v>0</v>
-      </c>
-      <c r="P109" s="1">
-        <v>518450</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q109" xr:uid="{33B89436-3C62-48B9-A287-E4DCE0428514}"/>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
+  <autoFilter ref="A1:Q108" xr:uid="{B883F859-51AD-4911-81A4-A2400EFBC314}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/blassonni_konan_orange_com/Documents/Documents/PLANIF 2024/PLANIF 2024 -/PLANIF_2025/Planification 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73EC8B04-F7AF-41DA-B005-2A02D5E51D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{016D3E4B-763B-4D9E-9F5E-BBFD3FDCFB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{7E1C3C3D-03CD-46F9-A0BE-2102FBB8297C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{A3780E1A-C455-4FE3-9DB4-C9E9A8BB9E3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$Q$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$Q$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="271">
   <si>
     <t>AGILITY BUSINESS PARKS COTE D’IVOIRE</t>
   </si>
@@ -68,6 +68,30 @@
     <t>SIE : Mise en service GAIA</t>
   </si>
   <si>
+    <t>MOTA ENGIL</t>
+  </si>
+  <si>
+    <t>SEGUELA</t>
+  </si>
+  <si>
+    <t>SYTRAN</t>
+  </si>
+  <si>
+    <t>fo</t>
+  </si>
+  <si>
+    <t>LSI</t>
+  </si>
+  <si>
+    <t>Offert</t>
+  </si>
+  <si>
+    <t>xxxxx</t>
+  </si>
+  <si>
+    <t>Support IP: Config Eq Acces</t>
+  </si>
+  <si>
     <t>SIMDCI SA</t>
   </si>
   <si>
@@ -77,18 +101,12 @@
     <t>IP Connect LL</t>
   </si>
   <si>
-    <t>fo</t>
-  </si>
-  <si>
     <t>LS</t>
   </si>
   <si>
     <t>BCK</t>
   </si>
   <si>
-    <t>Offert</t>
-  </si>
-  <si>
     <t>XXXXXXXXXX</t>
   </si>
   <si>
@@ -122,12 +140,6 @@
     <t>DALOA / DIBLOBLI</t>
   </si>
   <si>
-    <t>SYTRAN</t>
-  </si>
-  <si>
-    <t>LSI</t>
-  </si>
-  <si>
     <t>XXXX</t>
   </si>
   <si>
@@ -167,9 +179,6 @@
     <t>HUAWEI</t>
   </si>
   <si>
-    <t>SEGUELA</t>
-  </si>
-  <si>
     <t>XXXXXXXXXXX</t>
   </si>
   <si>
@@ -203,598 +212,598 @@
     <t>SYTHD260009</t>
   </si>
   <si>
-    <t>ODIENNE//VOIE INCONNUE/GBELEBAN</t>
+    <t>SAMAGO</t>
+  </si>
+  <si>
+    <t>xxxx</t>
+  </si>
+  <si>
+    <t>Prestataire : Travaux</t>
+  </si>
+  <si>
+    <t>QUIPUX AFRIQUE (TOUBA )</t>
+  </si>
+  <si>
+    <t>TOUBA//VOIE INCONNUE/M. LOHI FEH IBRAHIM 0504041812</t>
+  </si>
+  <si>
+    <t>BUVPN260034</t>
+  </si>
+  <si>
+    <t>Technicien zone: Intervention</t>
+  </si>
+  <si>
+    <t>MOTA ENGIL COTE D'IVOIRE MINING</t>
+  </si>
+  <si>
+    <t>DABAKALA</t>
+  </si>
+  <si>
+    <t>SYTHD260132</t>
+  </si>
+  <si>
+    <t>STE INTERNATIONALE D'ASSURANCE MULTIRISQUES</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU AVENUE HOUDAI</t>
+  </si>
+  <si>
+    <t>EMPIRE CIMENT CI</t>
+  </si>
+  <si>
+    <t>M'BRAGO</t>
+  </si>
+  <si>
+    <t>XXXXXXXXX</t>
+  </si>
+  <si>
+    <t>MAIRIE DE NIABLE</t>
+  </si>
+  <si>
+    <t>NIABLE A LA MAIRIE</t>
+  </si>
+  <si>
+    <t>TAABO LAMTO</t>
+  </si>
+  <si>
+    <t>Encours</t>
+  </si>
+  <si>
+    <t>xxxxxx</t>
+  </si>
+  <si>
+    <t>Saisie ASCOM</t>
+  </si>
+  <si>
+    <t>QUIPUX AFRIQUE</t>
+  </si>
+  <si>
+    <t>KONG</t>
+  </si>
+  <si>
+    <t>BUVPN260086</t>
+  </si>
+  <si>
+    <t>MFI CI (SODEXAM)</t>
+  </si>
+  <si>
+    <t>PORT POUET ZONE AEROPORTUAIRE</t>
+  </si>
+  <si>
+    <t>ZENITH BANK COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>ABIDJAN PLATEAU</t>
+  </si>
+  <si>
+    <t>BUVPN260078</t>
+  </si>
+  <si>
+    <t>Test et recette</t>
+  </si>
+  <si>
+    <t>Principale (avec backup)</t>
+  </si>
+  <si>
+    <t>OCI</t>
+  </si>
+  <si>
+    <t>Franchise Gagnoa</t>
+  </si>
+  <si>
+    <t>BUVPN260077</t>
+  </si>
+  <si>
+    <t>MAIRIE DE OUELLE</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>OUELLE QT MAIRIE</t>
+  </si>
+  <si>
+    <t>PLANETPHARMA EXPORT CI</t>
+  </si>
+  <si>
+    <t>GRAND BASSAM</t>
+  </si>
+  <si>
+    <t>SYTHD260122</t>
+  </si>
+  <si>
+    <t>Cordonnateur Prestatataire: Affectation Technicien</t>
+  </si>
+  <si>
+    <t>OLAM AGRI RUBBER COTE D'IVOIRE ANIASSUE</t>
+  </si>
+  <si>
+    <t>ANIASSUE//VOIE INCONNUE/M. N'GUESSAN THIERRY0556331131</t>
+  </si>
+  <si>
+    <t>radio_fh</t>
+  </si>
+  <si>
+    <t>SYTHD260100</t>
+  </si>
+  <si>
+    <t>OLAM COCOA PROCESSING CI SAN PEDRO</t>
+  </si>
+  <si>
+    <t>SAN-PEDRO//VOIE INCONNUE/ZONE INDUSTRIELLE 0708454305</t>
+  </si>
+  <si>
+    <t>SYTHD260102</t>
+  </si>
+  <si>
+    <t>CADESA</t>
+  </si>
+  <si>
+    <t>SASSANDRA SAGO ADEBEM</t>
+  </si>
+  <si>
+    <t>MAXAM CI</t>
+  </si>
+  <si>
+    <t>COCODY</t>
+  </si>
+  <si>
+    <t>ECOTI SA</t>
+  </si>
+  <si>
+    <t>YOPOUGON</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>BGFIBANK</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PORT BOUET BGFIBANK AEROPORT</t>
+  </si>
+  <si>
+    <t>STE LONACI</t>
+  </si>
+  <si>
+    <t>Siège MARCORY BIETRY</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>ftto_virage</t>
+  </si>
+  <si>
+    <t>2721599900B</t>
+  </si>
+  <si>
+    <t>STE COMPAGNIE IVOIRIENNE D'ELECTRICITE DTET</t>
+  </si>
+  <si>
+    <t>TREICHVILLE</t>
+  </si>
+  <si>
+    <t>AFG BANK</t>
+  </si>
+  <si>
+    <t>PLATEAU</t>
+  </si>
+  <si>
+    <t>2720306200B</t>
+  </si>
+  <si>
+    <t>MARCORY</t>
+  </si>
+  <si>
+    <t>2721230250B</t>
+  </si>
+  <si>
+    <t>xxxxxxx</t>
+  </si>
+  <si>
+    <t>MILLENIUM INDUSTRIE</t>
+  </si>
+  <si>
+    <t>BONOUA ZONE INDUSTRIELLE</t>
+  </si>
+  <si>
+    <t>MILLENIUM INDUSTRIE CI</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>ECOBANK COCODY RIVIERA</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/RIVIERA 0708448800</t>
+  </si>
+  <si>
+    <t>BUVPN260088</t>
+  </si>
+  <si>
+    <t>SODEXAM</t>
+  </si>
+  <si>
+    <t>TABOU Aérodrome</t>
+  </si>
+  <si>
+    <t>INSTITUT HOTELIER FEH KESSE</t>
+  </si>
+  <si>
+    <t>MAN SAINTE THERESE EXTENTION</t>
+  </si>
+  <si>
+    <t>NETCYBER CONSULTING</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>Etude Suspendu</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU BATIMENT WALL STREET</t>
+  </si>
+  <si>
+    <t>BUVPN260082</t>
+  </si>
+  <si>
+    <t>QUIPUX AFRIQUE YOPOUGON PK24</t>
+  </si>
+  <si>
+    <t>ABIDJAN-YOPOUGON PK24</t>
+  </si>
+  <si>
+    <t>QUIPUX AFRIQUE LS PK24</t>
+  </si>
+  <si>
+    <t>UNITED BANK OF AFRICA</t>
+  </si>
+  <si>
+    <t>xxxxxxxxxxx</t>
+  </si>
+  <si>
+    <t>UNION INVESTISSEMENT</t>
+  </si>
+  <si>
+    <t>MANKALA</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY DANS LA ZONE DE L'ABASSADE DES ETATS UNIS</t>
+  </si>
+  <si>
+    <t>DEMANDE INTERNE LSI PRINCIPAL ET BACKUP PROJET EVENT</t>
+  </si>
+  <si>
+    <t>ABIDJAN-TREICHVILLE AU DC DU KM4 AU SEINDE LA SALLEHOSTING</t>
+  </si>
+  <si>
+    <t>SYTHD260134</t>
+  </si>
+  <si>
+    <t>Responsable Zone: Validation intervention</t>
+  </si>
+  <si>
+    <t>MITSPA CALL SARL</t>
+  </si>
+  <si>
+    <t>COCODY RIVIERA ABATTA CARREFOUR DROGBA RUE 135 PRES ECOLE VENEZUA.</t>
+  </si>
+  <si>
+    <t>STE FONDATION FONDS D'ENTRETIEN ROUTIER</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY ANGRE NOUVEAU GOUDRON CHU</t>
+  </si>
+  <si>
+    <t>STE NAVITRANS COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>PORT BOUET</t>
+  </si>
+  <si>
+    <t>STE YANGO CI</t>
+  </si>
+  <si>
+    <t>COCODY IVOIRE TRADE CENTER BZAT D 2éETAGE</t>
+  </si>
+  <si>
+    <t>ALS COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>YAMOUSSOUKRO QUARTIER RESIDENTIEL</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t>STE IGUS COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>COCODY IMMEUBLE TRIDEM PHARMA RDC</t>
+  </si>
+  <si>
+    <t>SIE : Affectation des ressources</t>
+  </si>
+  <si>
+    <t>SONGON</t>
+  </si>
+  <si>
+    <t>DOUANES</t>
+  </si>
+  <si>
+    <t>SITE SESOCOM TRANSIT TREICHVILLE AVENUE 21 RUE 15</t>
+  </si>
+  <si>
+    <t>BUVPN260094</t>
+  </si>
+  <si>
+    <t>STE BGFI BANK</t>
+  </si>
+  <si>
+    <t>COCODY DANGA</t>
+  </si>
+  <si>
+    <t>AGT</t>
+  </si>
+  <si>
+    <t>DIRECTION GENERALE DES DOUANES</t>
+  </si>
+  <si>
+    <t>DANANE</t>
+  </si>
+  <si>
+    <t>BUVPN260095</t>
+  </si>
+  <si>
+    <t>AFRICURE PHARMACEUTICAL COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>GRAND BASSAM VITIB ZONE FRANCHE PARC TECHNOLOGIQUE MAHATMA GHANDI.</t>
+  </si>
+  <si>
+    <t>TIOBLI</t>
+  </si>
+  <si>
+    <t>IVOIRE ACIER SARL U</t>
+  </si>
+  <si>
+    <t>ABIDJAN-YOPOUGON AUTOROUTE DU NORD PK 24</t>
+  </si>
+  <si>
+    <t>Responsable Zone: Coordination etude et travaux</t>
+  </si>
+  <si>
+    <t>KALIMBA</t>
+  </si>
+  <si>
+    <t>MARCORY IMMEUBLE BATICHO</t>
+  </si>
+  <si>
+    <t>NSIA BANQUE COCODY MERMOZ INADES</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY MERMOZ INADES</t>
+  </si>
+  <si>
+    <t>BUVPN260097</t>
+  </si>
+  <si>
+    <t>BANQUE NATIONAL D'INVESTISSEMENT DABAKALA</t>
+  </si>
+  <si>
+    <t>DABAKALA EN FACE DE L'HOPITAL ET STATION TOTAL</t>
+  </si>
+  <si>
+    <t>ORANGE BUSNESS SERVICES</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY</t>
+  </si>
+  <si>
+    <t>SYTHD260149</t>
+  </si>
+  <si>
+    <t>CREDAFRICA</t>
+  </si>
+  <si>
+    <t>COCODY CARREFOUR DUNCAN</t>
+  </si>
+  <si>
+    <t>SYTHD260151</t>
+  </si>
+  <si>
+    <t>BANQUE DE L'HABITAT DE COTE D'IVOIRE PLATEAU</t>
+  </si>
+  <si>
+    <t>ABIDJAN-PLATEAU</t>
+  </si>
+  <si>
+    <t>ADKONTACT</t>
+  </si>
+  <si>
+    <t>SYTHD260150</t>
+  </si>
+  <si>
+    <t>MAIRIE DE DJEBONOUA</t>
+  </si>
+  <si>
+    <t>DJEBONOUA</t>
+  </si>
+  <si>
+    <t>LSI Elite</t>
+  </si>
+  <si>
+    <t>VIPNET</t>
+  </si>
+  <si>
+    <t>EXTA: VIPNET HQ 2PLATEAUX LATRILLE EXT B; AMBASSADE D'ESPAGNE COCODY 2 PLATEAUX VALLONS LIAISON FO 4 Mbps</t>
+  </si>
+  <si>
+    <t>Responsable Trafic et Projet : Validation informations</t>
+  </si>
+  <si>
+    <t>FONDATION LA FEE RIMA</t>
+  </si>
+  <si>
+    <t>COCODY 2 PLATEAUX VALLON</t>
+  </si>
+  <si>
+    <t>COCODY 2 PLATEAU VALLON</t>
+  </si>
+  <si>
+    <t>INALCA</t>
+  </si>
+  <si>
+    <t>MARCORY ZONE 4</t>
+  </si>
+  <si>
+    <t>EPHR AGBOVILLE</t>
+  </si>
+  <si>
+    <t>AGBOVILLE</t>
+  </si>
+  <si>
+    <t>STE UCP SANTE MONDIALE</t>
+  </si>
+  <si>
+    <t>COCODY RUE J6 VALLON FACE A LA PHARMACIE ST GILE</t>
+  </si>
+  <si>
+    <t>COCODY VALLON RUE J6 FACE A LA PHARMACIE ST GILE</t>
+  </si>
+  <si>
+    <t>NPSP</t>
+  </si>
+  <si>
+    <t>Extrémité A : ABIDJAN Extrémité B : BOUAKE</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>Extrémité A : BOUAKE Extrémité B : ABIDJAN</t>
+  </si>
+  <si>
+    <t>AGBOVILLE//VOIE INCONNUE/AGBOVILLE</t>
   </si>
   <si>
     <t>NOM</t>
   </si>
   <si>
-    <t>BUVPN260049</t>
-  </si>
-  <si>
-    <t>Prestataire : Correction Conformite Travaux</t>
-  </si>
-  <si>
-    <t>SAMAGO</t>
-  </si>
-  <si>
-    <t>xxxx</t>
-  </si>
-  <si>
-    <t>Prestataire : Travaux</t>
-  </si>
-  <si>
-    <t>QUIPUX AFRIQUE (TOUBA )</t>
-  </si>
-  <si>
-    <t>TOUBA//VOIE INCONNUE/M. LOHI FEH IBRAHIM 0504041812</t>
-  </si>
-  <si>
-    <t>BUVPN260034</t>
-  </si>
-  <si>
-    <t>Technicien zone: Intervention</t>
-  </si>
-  <si>
-    <t>MOTA ENGIL COTE D'IVOIRE MINING</t>
-  </si>
-  <si>
-    <t>DABAKALA</t>
-  </si>
-  <si>
-    <t>SYTHD260132</t>
-  </si>
-  <si>
-    <t>STE INTERNATIONALE D'ASSURANCE MULTIRISQUES</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PLATEAU AVENUE HOUDAI</t>
-  </si>
-  <si>
-    <t>EMPIRE CIMENT CI</t>
-  </si>
-  <si>
-    <t>M'BRAGO</t>
-  </si>
-  <si>
-    <t>XXXXXXXXX</t>
-  </si>
-  <si>
-    <t>MAIRIE DE NIABLE</t>
-  </si>
-  <si>
-    <t>NIABLE A LA MAIRIE</t>
-  </si>
-  <si>
-    <t>xxxxx</t>
-  </si>
-  <si>
-    <t>TAABO LAMTO</t>
-  </si>
-  <si>
-    <t>Encours</t>
-  </si>
-  <si>
-    <t>xxxxxx</t>
-  </si>
-  <si>
-    <t>Saisie ASCOM</t>
-  </si>
-  <si>
-    <t>QUIPUX AFRIQUE</t>
-  </si>
-  <si>
-    <t>KONG</t>
-  </si>
-  <si>
-    <t>BUVPN260086</t>
-  </si>
-  <si>
-    <t>MFI CI (SODEXAM)</t>
-  </si>
-  <si>
-    <t>PORT POUET ZONE AEROPORTUAIRE</t>
-  </si>
-  <si>
-    <t>ZENITH BANK COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>ABIDJAN PLATEAU</t>
-  </si>
-  <si>
-    <t>BUVPN260078</t>
-  </si>
-  <si>
-    <t>Test et recette</t>
-  </si>
-  <si>
-    <t>Principale (avec backup)</t>
-  </si>
-  <si>
-    <t>OCI</t>
-  </si>
-  <si>
-    <t>Franchise Gagnoa</t>
-  </si>
-  <si>
-    <t>BUVPN260077</t>
-  </si>
-  <si>
-    <t>MAIRIE DE OUELLE</t>
-  </si>
-  <si>
-    <t>XXXXXXXXXXXXX</t>
-  </si>
-  <si>
-    <t>OUELLE QT MAIRIE</t>
-  </si>
-  <si>
-    <t>PLANETPHARMA EXPORT CI</t>
-  </si>
-  <si>
-    <t>GRAND BASSAM</t>
-  </si>
-  <si>
-    <t>SYTHD260122</t>
-  </si>
-  <si>
-    <t>Cordonnateur Prestatataire: Affectation Technicien</t>
-  </si>
-  <si>
-    <t>OLAM AGRI RUBBER COTE D'IVOIRE ANIASSUE</t>
-  </si>
-  <si>
-    <t>ANIASSUE//VOIE INCONNUE/M. N'GUESSAN THIERRY0556331131</t>
-  </si>
-  <si>
-    <t>radio_fh</t>
-  </si>
-  <si>
-    <t>SYTHD260100</t>
-  </si>
-  <si>
-    <t>OLAM COCOA PROCESSING CI SAN PEDRO</t>
-  </si>
-  <si>
-    <t>SAN-PEDRO//VOIE INCONNUE/ZONE INDUSTRIELLE 0708454305</t>
-  </si>
-  <si>
-    <t>SYTHD260102</t>
-  </si>
-  <si>
-    <t>CADESA</t>
-  </si>
-  <si>
-    <t>SASSANDRA SAGO ADEBEM</t>
-  </si>
-  <si>
-    <t>MAXAM CI</t>
-  </si>
-  <si>
-    <t>COCODY</t>
-  </si>
-  <si>
-    <t>ECOTI SA</t>
-  </si>
-  <si>
-    <t>YOPOUGON</t>
-  </si>
-  <si>
-    <t>XXXXXXXXXXXXXXXX</t>
-  </si>
-  <si>
-    <t>BGFIBANK</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PORT BOUET BGFIBANK AEROPORT</t>
-  </si>
-  <si>
-    <t>SOLIBRA</t>
-  </si>
-  <si>
-    <t>YOPOUGON PK26</t>
-  </si>
-  <si>
-    <t>VPNLL</t>
-  </si>
-  <si>
-    <t>STE LONACI</t>
-  </si>
-  <si>
-    <t>Siège MARCORY BIETRY</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>ftto_virage</t>
-  </si>
-  <si>
-    <t>2721599900B</t>
-  </si>
-  <si>
-    <t>Responsable Zone: Validation intervention</t>
-  </si>
-  <si>
-    <t>STE COMPAGNIE IVOIRIENNE D'ELECTRICITE DTET</t>
-  </si>
-  <si>
-    <t>TREICHVILLE</t>
-  </si>
-  <si>
-    <t>AFG BANK</t>
-  </si>
-  <si>
-    <t>PLATEAU</t>
-  </si>
-  <si>
-    <t>2720306200B</t>
-  </si>
-  <si>
-    <t>MARCORY</t>
-  </si>
-  <si>
-    <t>2721230250B</t>
-  </si>
-  <si>
-    <t>xxxxxxx</t>
-  </si>
-  <si>
-    <t>MILLENIUM INDUSTRIE</t>
-  </si>
-  <si>
-    <t>BONOUA ZONE INDUSTRIELLE</t>
-  </si>
-  <si>
-    <t>MILLENIUM INDUSTRIE CI</t>
-  </si>
-  <si>
-    <t>XXXXXXXXXXXX</t>
-  </si>
-  <si>
-    <t>ECOBANK COCODY RIVIERA</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/RIVIERA 0708448800</t>
-  </si>
-  <si>
-    <t>BUVPN260088</t>
-  </si>
-  <si>
-    <t>SODEXAM</t>
-  </si>
-  <si>
-    <t>TABOU Aérodrome</t>
-  </si>
-  <si>
-    <t>INSTITUT HOTELIER FEH KESSE</t>
-  </si>
-  <si>
-    <t>MAN SAINTE THERESE EXTENTION</t>
-  </si>
-  <si>
-    <t>NETCYBER CONSULTING</t>
-  </si>
-  <si>
-    <t>XXXXXXXXXXXXXX</t>
-  </si>
-  <si>
-    <t>Etude Suspendu</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PLATEAU BATIMENT WALL STREET</t>
-  </si>
-  <si>
-    <t>BUVPN260082</t>
-  </si>
-  <si>
-    <t>QUIPUX AFRIQUE YOPOUGON PK24</t>
-  </si>
-  <si>
-    <t>ABIDJAN-YOPOUGON PK24</t>
-  </si>
-  <si>
-    <t>QUIPUX AFRIQUE LS PK24</t>
-  </si>
-  <si>
-    <t>UNITED BANK OF AFRICA</t>
-  </si>
-  <si>
-    <t>xxxxxxxxxxx</t>
-  </si>
-  <si>
-    <t>UNION INVESTISSEMENT</t>
-  </si>
-  <si>
-    <t>MANKALA</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY DANS LA ZONE DE L'ABASSADE DES ETATS UNIS</t>
-  </si>
-  <si>
-    <t>DEMANDE INTERNE LSI PRINCIPAL ET BACKUP PROJET EVENT</t>
-  </si>
-  <si>
-    <t>ABIDJAN-TREICHVILLE AU DC DU KM4 AU SEINDE LA SALLEHOSTING</t>
-  </si>
-  <si>
-    <t>SYTHD260134</t>
-  </si>
-  <si>
-    <t>MITSPA CALL SARL</t>
-  </si>
-  <si>
-    <t>COCODY RIVIERA ABATTA CARREFOUR DROGBA RUE 135 PRES ECOLE VENEZUA.</t>
-  </si>
-  <si>
-    <t>STE FONDATION FONDS D'ENTRETIEN ROUTIER</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY ANGRE NOUVEAU GOUDRON CHU</t>
-  </si>
-  <si>
-    <t>STE NAVITRANS COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>PORT BOUET</t>
+    <t>SYTHD250043</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie BSCS</t>
+  </si>
+  <si>
+    <t>FONDS D'ENTRETIEN ROUTIER</t>
+  </si>
+  <si>
+    <t>ABOBO</t>
   </si>
   <si>
     <t>Prestataire : Etude</t>
   </si>
   <si>
-    <t>STE YANGO CI</t>
-  </si>
-  <si>
-    <t>COCODY IVOIRE TRADE CENTER BZAT D 2éETAGE</t>
-  </si>
-  <si>
-    <t>ALS COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>YAMOUSSOUKRO QUARTIER RESIDENTIEL</t>
-  </si>
-  <si>
-    <t>XXXXXXXXXXXXXXX</t>
-  </si>
-  <si>
-    <t>STE IGUS COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>COCODY IMMEUBLE TRIDEM PHARMA RDC</t>
-  </si>
-  <si>
-    <t>SONGON</t>
-  </si>
-  <si>
-    <t>DOUANES</t>
-  </si>
-  <si>
-    <t>SITE SESOCOM TRANSIT TREICHVILLE AVENUE 21 RUE 15</t>
-  </si>
-  <si>
-    <t>BUVPN260094</t>
-  </si>
-  <si>
-    <t>STE BGFI BANK</t>
-  </si>
-  <si>
-    <t>COCODY DANGA</t>
-  </si>
-  <si>
-    <t>AGT</t>
-  </si>
-  <si>
-    <t>CALIXT S.A.R.L</t>
-  </si>
-  <si>
-    <t>DIRECTION GENERALE DES DOUANES</t>
-  </si>
-  <si>
-    <t>DANANE</t>
-  </si>
-  <si>
-    <t>AFRICURE PHARMACEUTICAL COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>GRAND BASSAM VITIB ZONE FRANCHE PARC TECHNOLOGIQUE MAHATMA GHANDI.</t>
-  </si>
-  <si>
-    <t>TIOBLI</t>
-  </si>
-  <si>
-    <t>Responsable Zone: Coordination etude et travaux</t>
-  </si>
-  <si>
-    <t>IVOIRE ACIER SARL U</t>
-  </si>
-  <si>
-    <t>ABIDJAN-YOPOUGON AUTOROUTE DU NORD PK 24</t>
-  </si>
-  <si>
-    <t>KALIMBA</t>
-  </si>
-  <si>
-    <t>MARCORY IMMEUBLE BATICHO</t>
-  </si>
-  <si>
-    <t>ASSISTANCE AUTOMOBILE ABIDJANAISE</t>
-  </si>
-  <si>
-    <t>COCODY BATIM A</t>
-  </si>
-  <si>
-    <t>Support IP: Config Eq Acces</t>
-  </si>
-  <si>
-    <t>NSIA BANQUE COCODY MERMOZ INADES</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY MERMOZ INADES</t>
-  </si>
-  <si>
-    <t>BANQUE NATIONAL D'INVESTISSEMENT DABAKALA</t>
-  </si>
-  <si>
-    <t>DABAKALA EN FACE DE L'HOPITAL ET STATION TOTAL</t>
-  </si>
-  <si>
-    <t>ORANGE BUSNESS SERVICES</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY</t>
-  </si>
-  <si>
-    <t>SYTHD260149</t>
-  </si>
-  <si>
-    <t>CREDAFRICA</t>
-  </si>
-  <si>
-    <t>COCODY CARREFOUR DUNCAN</t>
-  </si>
-  <si>
-    <t>SYTHD260151</t>
+    <t>CORIS BANK</t>
+  </si>
+  <si>
+    <t>Marcory</t>
+  </si>
+  <si>
+    <t>BUVPN240107</t>
+  </si>
+  <si>
+    <t>ANGRE CHU</t>
+  </si>
+  <si>
+    <t>BUVPN240108</t>
+  </si>
+  <si>
+    <t>CMC INVESTMENTS LIMITED</t>
+  </si>
+  <si>
+    <t>EXTA: POP CMC KM4 EXTB: NSIA BANQUE MERMOZ COCODY Débit : 2Mbps</t>
+  </si>
+  <si>
+    <t>YAMOUSSOUKRO Kick-off</t>
+  </si>
+  <si>
+    <t>SYTHD260158</t>
   </si>
   <si>
     <t>Responsable Zone: Validation pour intervention</t>
   </si>
   <si>
-    <t>BANQUE DE L'HABITAT DE COTE D'IVOIRE PLATEAU</t>
-  </si>
-  <si>
-    <t>ABIDJAN-PLATEAU</t>
-  </si>
-  <si>
-    <t>ADKONTACT</t>
-  </si>
-  <si>
-    <t>SYTHD260150</t>
-  </si>
-  <si>
-    <t>MAIRIE DE DJEBONOUA</t>
-  </si>
-  <si>
-    <t>DJEBONOUA</t>
-  </si>
-  <si>
-    <t>LSI Elite</t>
-  </si>
-  <si>
-    <t>VIPNET</t>
-  </si>
-  <si>
-    <t>EXTA: VIPNET HQ 2PLATEAUX LATRILLE EXT B; AMBASSADE D'ESPAGNE COCODY 2 PLATEAUX VALLONS LIAISON FO 4 Mbps</t>
-  </si>
-  <si>
-    <t>Responsable Trafic et Projet : Validation informations</t>
-  </si>
-  <si>
-    <t>FONDATION LA FEE RIMA</t>
-  </si>
-  <si>
-    <t>COCODY 2 PLATEAUX VALLON</t>
-  </si>
-  <si>
-    <t>COCODY 2 PLATEAU VALLON</t>
-  </si>
-  <si>
-    <t>INALCA</t>
-  </si>
-  <si>
-    <t>MARCORY ZONE 4</t>
-  </si>
-  <si>
-    <t>EPHR AGBOVILLE</t>
-  </si>
-  <si>
-    <t>AGBOVILLE</t>
-  </si>
-  <si>
-    <t>STE UCP SANTE MONDIALE</t>
-  </si>
-  <si>
-    <t>COCODY RUE J6 VALLON FACE A LA PHARMACIE ST GILE</t>
-  </si>
-  <si>
-    <t>Parametrage facturation</t>
-  </si>
-  <si>
-    <t>COCODY VALLON RUE J6 FACE A LA PHARMACIE ST GILE</t>
-  </si>
-  <si>
-    <t>NPSP</t>
-  </si>
-  <si>
-    <t>Extrémité A : ABIDJAN Extrémité B : BOUAKE</t>
-  </si>
-  <si>
-    <t>XXX</t>
-  </si>
-  <si>
-    <t>Extrémité A : BOUAKE Extrémité B : ABIDJAN</t>
-  </si>
-  <si>
-    <t>SYTHD250043</t>
-  </si>
-  <si>
-    <t>Support IP: Correction</t>
-  </si>
-  <si>
-    <t>FONDS D'ENTRETIEN ROUTIER</t>
-  </si>
-  <si>
-    <t>ABOBO</t>
-  </si>
-  <si>
-    <t>ORANGE COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>RIVIERA GOLF</t>
-  </si>
-  <si>
-    <t>SYTHD260153</t>
-  </si>
-  <si>
-    <t>SYTHD260152</t>
-  </si>
-  <si>
-    <t>CORIS BANK INTERNATIONAL</t>
-  </si>
-  <si>
-    <t>ABIDJAN-MARCORY//VOIE INCONNUE/MARCORY</t>
-  </si>
-  <si>
-    <t>BUVPN240107</t>
-  </si>
-  <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/ANGRE CHU</t>
-  </si>
-  <si>
-    <t>BUVPN240108</t>
-  </si>
-  <si>
-    <t>CMC INVESTMENTS LIMITED</t>
-  </si>
-  <si>
-    <t>EXTA: POP CMC KM4 EXTB: NSIA BANQUE MERMOZ COCODY Débit : 2Mbps</t>
-  </si>
-  <si>
-    <t>Manager Trafic et Projets : Affectation responsable projet</t>
-  </si>
-  <si>
-    <t>CENTRAL TRADING</t>
-  </si>
-  <si>
-    <t>SYTHD260154</t>
-  </si>
-  <si>
-    <t>COCODY African Digital Week au Sofitel Hôtel Ivoire</t>
-  </si>
-  <si>
-    <t>YAMOUSSOUKRO Kick-off</t>
-  </si>
-  <si>
     <t>COCODY Budweiser Fan Festival Playce Palmeraie</t>
+  </si>
+  <si>
+    <t>BBF : Validation Etude</t>
+  </si>
+  <si>
+    <t>FOND D'ENTRETIEN ROUTIER</t>
+  </si>
+  <si>
+    <t>MECATECH CONCEPT EL JIRE</t>
+  </si>
+  <si>
+    <t>STE ARANDAN HOLDING</t>
+  </si>
+  <si>
+    <t>COCODY LA CITADELLE PORTE 02/01</t>
+  </si>
+  <si>
+    <t>STE OFFICE D'AIDE A LA COMMERCIALISATION DES PRODUITS VIVRIERS</t>
+  </si>
+  <si>
+    <t>ABOBO PK18 AGRIPAC</t>
+  </si>
+  <si>
+    <t>SOCACI</t>
+  </si>
+  <si>
+    <t>MINISTERE EMPLOI ET PROTECTIONSOCIALE</t>
+  </si>
+  <si>
+    <t>PLATEAU TOUR A 11e ETAGE</t>
+  </si>
+  <si>
+    <t>ACTIVA</t>
+  </si>
+  <si>
+    <t>STE AGENCE OCI 2PLTX ENA DEMANDE INTERNE</t>
+  </si>
+  <si>
+    <t>PLATEAU BUREAU RI RP</t>
+  </si>
+  <si>
+    <t>COMITE NATIONAL DE PILOTAGE DES PARTENARIATS PUBLIC PRIVE</t>
+  </si>
+  <si>
+    <t>PLATEAU IMMEUBLE NZARAMA AU 4EME ETAGE</t>
   </si>
   <si>
     <t>ID DOSSIER</t>
@@ -937,7 +946,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -945,6 +954,24 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1287,8 +1314,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD3779C-7CB1-4222-BF19-E0D2FB3081A6}">
-  <dimension ref="A1:Q103"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D0A148-9DB7-45FC-B27B-D5D1079BE330}">
+  <dimension ref="A1:Q106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -1303,55 +1330,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="52" x14ac:dyDescent="0.35">
@@ -1405,33 +1432,33 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
-        <v>52778382</v>
+        <v>49660008</v>
       </c>
       <c r="B3" s="4">
-        <v>45959.67696759259</v>
+        <v>45897.665000000001</v>
       </c>
       <c r="C3" s="3">
-        <v>55073470</v>
+        <v>64382695</v>
       </c>
       <c r="D3" s="4">
-        <v>46003.678194444445</v>
+        <v>46178.470011574071</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="3">
-        <v>708086759</v>
+        <v>748512613</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3">
-        <v>2788625</v>
+      <c r="I3" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>10</v>
@@ -1443,222 +1470,222 @@
         <v>12</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="P3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="91" x14ac:dyDescent="0.35">
+      <c r="Q3" s="5">
+        <v>2538822</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="52" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
-        <v>52808171</v>
+        <v>52778382</v>
       </c>
       <c r="B4" s="4">
-        <v>45960.452361111114</v>
+        <v>45959.67696759259</v>
       </c>
       <c r="C4" s="3">
-        <v>59829408</v>
+        <v>55073470</v>
       </c>
       <c r="D4" s="4">
-        <v>46093.677152777775</v>
+        <v>46003.678194444445</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3">
+        <v>708086759</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="3">
-        <v>709738605</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3">
+        <v>2788625</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2793645</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="91" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>52808171</v>
+      </c>
+      <c r="B5" s="4">
+        <v>45960.452361111114</v>
+      </c>
+      <c r="C5" s="3">
+        <v>59829408</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46093.677152777775</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="3">
+        <v>709738605</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="3">
+        <v>2793645</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="52" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+      <c r="M5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
         <v>53702282</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B6" s="4">
         <v>45978.671550925923</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C6" s="3">
         <v>54614316</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D6" s="4">
         <v>45995.632673611108</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="3">
         <v>778036533</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="26" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
-        <v>53749839</v>
-      </c>
-      <c r="B6" s="4">
-        <v>45979.600694444445</v>
-      </c>
-      <c r="C6" s="3">
-        <v>62944786</v>
-      </c>
-      <c r="D6" s="4">
-        <v>46150.446296296293</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="3">
-        <v>703333988</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="M6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q6" s="5">
-        <v>10000000</v>
+      <c r="Q6" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="26" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
-        <v>53790357</v>
+        <v>53749839</v>
       </c>
       <c r="B7" s="4">
-        <v>45980.438298611109</v>
+        <v>45979.600694444445</v>
       </c>
       <c r="C7" s="3">
-        <v>61385261</v>
+        <v>62944786</v>
       </c>
       <c r="D7" s="4">
-        <v>46122.774224537039</v>
+        <v>46150.446296296293</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7" s="3">
-        <v>708336404</v>
+        <v>703333988</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>32</v>
@@ -1667,30 +1694,30 @@
         <v>2</v>
       </c>
       <c r="Q7" s="5">
-        <v>4430307</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="26" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
-        <v>53899369</v>
+        <v>53790357</v>
       </c>
       <c r="B8" s="4">
-        <v>45981.827430555553</v>
+        <v>45980.438298611109</v>
       </c>
       <c r="C8" s="3">
-        <v>55146678</v>
+        <v>61385261</v>
       </c>
       <c r="D8" s="4">
-        <v>46005.762916666667</v>
+        <v>46122.774224537039</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="G8" s="3">
-        <v>707003126</v>
+        <v>708336404</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>34</v>
@@ -1699,60 +1726,60 @@
         <v>2</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q8" s="5">
+        <v>4430307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
-        <v>54449048</v>
+        <v>53899369</v>
       </c>
       <c r="B9" s="4">
-        <v>45992.706157407411</v>
+        <v>45981.827430555553</v>
       </c>
       <c r="C9" s="3">
-        <v>56341749</v>
+        <v>55146678</v>
       </c>
       <c r="D9" s="4">
-        <v>46029.685115740744</v>
+        <v>46005.762916666667</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9" s="3">
-        <v>708086759</v>
+        <v>707003126</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>11</v>
@@ -1761,10 +1788,10 @@
         <v>12</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>39</v>
@@ -1772,31 +1799,31 @@
       <c r="P9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>2</v>
+      <c r="Q9" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="26" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
-        <v>55104019</v>
+        <v>54449048</v>
       </c>
       <c r="B10" s="4">
-        <v>46004.469606481478</v>
+        <v>45992.706157407411</v>
       </c>
       <c r="C10" s="3">
-        <v>56566265</v>
+        <v>56341749</v>
       </c>
       <c r="D10" s="4">
-        <v>46034.582673611112</v>
+        <v>46029.685115740744</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>40</v>
       </c>
       <c r="G10" s="3">
-        <v>504033918</v>
+        <v>708086759</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>41</v>
@@ -1805,72 +1832,72 @@
         <v>2</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>55104019</v>
+      </c>
+      <c r="B11" s="4">
+        <v>46004.469606481478</v>
+      </c>
+      <c r="C11" s="3">
+        <v>56566265</v>
+      </c>
+      <c r="D11" s="4">
+        <v>46034.582673611112</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="3">
+        <v>504033918</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>4000000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="52" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
-        <v>55636282</v>
-      </c>
-      <c r="B11" s="4">
-        <v>46014.435729166667</v>
-      </c>
-      <c r="C11" s="3">
-        <v>57367586</v>
-      </c>
-      <c r="D11" s="4">
-        <v>46049.856261574074</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="3">
-        <v>759003900</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>45</v>
@@ -1879,145 +1906,145 @@
         <v>2</v>
       </c>
       <c r="Q11" s="5">
-        <v>918681</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="52" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
-        <v>55694485</v>
+        <v>55636282</v>
       </c>
       <c r="B12" s="4">
-        <v>46015.420092592591</v>
+        <v>46014.435729166667</v>
       </c>
       <c r="C12" s="3">
-        <v>56752240</v>
+        <v>57367586</v>
       </c>
       <c r="D12" s="4">
-        <v>46037.705520833333</v>
+        <v>46049.856261574074</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="3">
+        <v>759003900</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="3">
-        <v>749338073</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q12" s="5">
-        <v>638462</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+        <v>918681</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
-        <v>56181778</v>
+        <v>55694485</v>
       </c>
       <c r="B13" s="4">
-        <v>46027.499212962961</v>
+        <v>46015.420092592591</v>
       </c>
       <c r="C13" s="3">
-        <v>59210339</v>
+        <v>56752240</v>
       </c>
       <c r="D13" s="4">
-        <v>46083.492881944447</v>
+        <v>46037.705520833333</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G13" s="3">
-        <v>585990976</v>
+        <v>749338073</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="3">
-        <v>1765416</v>
+        <v>51</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>638462</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>56181778</v>
+      </c>
+      <c r="B14" s="4">
+        <v>46027.499212962961</v>
+      </c>
+      <c r="C14" s="3">
+        <v>59210339</v>
+      </c>
+      <c r="D14" s="4">
+        <v>46083.492881944447</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="P13" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="5">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="52" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
-        <v>56601140</v>
-      </c>
-      <c r="B14" s="4">
-        <v>46035.385555555556</v>
-      </c>
-      <c r="C14" s="3">
-        <v>59442988</v>
-      </c>
-      <c r="D14" s="4">
-        <v>46086.814479166664</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="G14" s="3">
-        <v>707003126</v>
+        <v>585990976</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I14" s="3">
-        <v>1778026</v>
+        <v>1765416</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>11</v>
@@ -2026,10 +2053,10 @@
         <v>12</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>55</v>
@@ -2038,7 +2065,7 @@
         <v>2</v>
       </c>
       <c r="Q14" s="5">
-        <v>7103410</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="26" x14ac:dyDescent="0.35">
@@ -2055,37 +2082,37 @@
         <v>46113.726909722223</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G15" s="3">
         <v>707003126</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>2</v>
@@ -2108,37 +2135,37 @@
         <v>46162.539305555554</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G16" s="3">
         <v>504041812</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I16" s="3">
         <v>1775236</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P16" s="3" t="s">
         <v>2</v>
@@ -2161,37 +2188,37 @@
         <v>46157.396793981483</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G17" s="3">
         <v>748512613</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>2</v>
@@ -2214,37 +2241,37 @@
         <v>46083.719525462962</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" s="3">
         <v>708667658</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>2</v>
@@ -2267,37 +2294,37 @@
         <v>46104.528900462959</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="3">
         <v>720631500</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>2</v>
@@ -2320,37 +2347,37 @@
         <v>46121.376689814817</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G20" s="3">
         <v>758224257</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>2</v>
@@ -2373,37 +2400,37 @@
         <v>46162.626145833332</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G21" s="3">
         <v>708086759</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>2</v>
@@ -2426,37 +2453,37 @@
         <v>46153.448425925926</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G22" s="3">
         <v>504041812</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>2</v>
@@ -2479,37 +2506,37 @@
         <v>46093.543773148151</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G23" s="3">
         <v>709574114</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>2</v>
@@ -2532,37 +2559,37 @@
         <v>46133.49863425926</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G24" s="3">
         <v>759250737</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>2</v>
@@ -2585,37 +2612,37 @@
         <v>46133.487384259257</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G25" s="3">
         <v>759250737</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>2</v>
@@ -2638,37 +2665,37 @@
         <v>46135.396608796298</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G26" s="3">
         <v>748377555</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>2</v>
@@ -2691,16 +2718,16 @@
         <v>46100.423101851855</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G27" s="3">
         <v>708641473</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>2</v>
@@ -2718,10 +2745,10 @@
         <v>6</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>2</v>
@@ -2744,37 +2771,37 @@
         <v>46100.423773148148</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G28" s="3">
         <v>708641473</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>2</v>
@@ -2791,43 +2818,43 @@
         <v>46087.436643518522</v>
       </c>
       <c r="C29" s="3">
-        <v>64055931</v>
+        <v>64373724</v>
       </c>
       <c r="D29" s="4">
-        <v>46172.333738425928</v>
+        <v>46178.388506944444</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G29" s="3">
         <v>141679210</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>2</v>
@@ -2850,37 +2877,37 @@
         <v>46127.35796296296</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G30" s="3">
         <v>556331131</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I30" s="3">
         <v>1843236</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>2</v>
@@ -2903,37 +2930,37 @@
         <v>46132.349363425928</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G31" s="3">
         <v>708454305</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I31" s="3">
         <v>1842206</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P31" s="3" t="s">
         <v>2</v>
@@ -2956,37 +2983,37 @@
         <v>46105.432800925926</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G32" s="3">
         <v>767081456</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>2</v>
@@ -3009,37 +3036,37 @@
         <v>46162.52847222222</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G33" s="3">
         <v>759668146</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>2</v>
@@ -3062,37 +3089,37 @@
         <v>46141.624513888892</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G34" s="3">
         <v>767791237</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P34" s="3" t="s">
         <v>2</v>
@@ -3115,37 +3142,37 @@
         <v>46150.482407407406</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G35" s="3">
         <v>160128782</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>2</v>
@@ -3154,104 +3181,104 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
-        <v>61220160</v>
+        <v>61239047</v>
       </c>
       <c r="B36" s="4">
-        <v>46120.483368055553</v>
+        <v>46120.622071759259</v>
       </c>
       <c r="C36" s="3">
-        <v>63331281</v>
+        <v>64373945</v>
       </c>
       <c r="D36" s="4">
-        <v>46157.621018518519</v>
+        <v>46178.391516203701</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="F36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G36" s="3">
+        <v>103381121</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G36" s="3">
-        <v>102571205</v>
-      </c>
-      <c r="H36" s="3" t="s">
+      <c r="K36" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J36" s="3" t="s">
+      <c r="L36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O36" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="K36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="P36" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q36" s="5">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="Q36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
-        <v>61239047</v>
+        <v>61240327</v>
       </c>
       <c r="B37" s="4">
-        <v>46120.622071759259</v>
+        <v>46120.631747685184</v>
       </c>
       <c r="C37" s="3">
-        <v>63973941</v>
+        <v>63643159</v>
       </c>
       <c r="D37" s="4">
-        <v>46170.640798611108</v>
+        <v>46163.479432870372</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G37" s="3">
         <v>103381121</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="P37" s="3" t="s">
         <v>2</v>
@@ -3260,27 +3287,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
-        <v>61240327</v>
+        <v>61242033</v>
       </c>
       <c r="B38" s="4">
-        <v>46120.631747685184</v>
+        <v>46120.643912037034</v>
       </c>
       <c r="C38" s="3">
-        <v>63643159</v>
+        <v>62945857</v>
       </c>
       <c r="D38" s="4">
-        <v>46163.479432870372</v>
+        <v>46150.456064814818</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>118</v>
       </c>
       <c r="G38" s="3">
-        <v>103381121</v>
+        <v>747636152</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>119</v>
@@ -3289,7 +3316,7 @@
         <v>2</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>4</v>
@@ -3298,13 +3325,13 @@
         <v>5</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>2</v>
@@ -3313,157 +3340,157 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="26" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
-        <v>61242033</v>
+        <v>61244524</v>
       </c>
       <c r="B39" s="4">
-        <v>46120.643912037034</v>
+        <v>46120.66065972222</v>
       </c>
       <c r="C39" s="3">
-        <v>62945857</v>
+        <v>62308856</v>
       </c>
       <c r="D39" s="4">
-        <v>46150.456064814818</v>
+        <v>46139.393194444441</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G39" s="3">
-        <v>747636152</v>
+        <v>757818829</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q39" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q39" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
-        <v>61244524</v>
+        <v>61248751</v>
       </c>
       <c r="B40" s="4">
-        <v>46120.66065972222</v>
+        <v>46120.692800925928</v>
       </c>
       <c r="C40" s="3">
-        <v>62308856</v>
+        <v>64319807</v>
       </c>
       <c r="D40" s="4">
-        <v>46139.393194444441</v>
+        <v>46177.419872685183</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="G40" s="3">
-        <v>757818829</v>
+        <v>747636152</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="A41" s="3">
+        <v>61255901</v>
+      </c>
+      <c r="B41" s="4">
+        <v>46120.75712962963</v>
+      </c>
+      <c r="C41" s="3">
+        <v>62951388</v>
+      </c>
+      <c r="D41" s="4">
+        <v>46150.494675925926</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G41" s="3">
+        <v>757818829</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q40" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="65" x14ac:dyDescent="0.35">
-      <c r="A41" s="3">
-        <v>61248751</v>
-      </c>
-      <c r="B41" s="4">
-        <v>46120.692800925928</v>
-      </c>
-      <c r="C41" s="3">
-        <v>63688864</v>
-      </c>
-      <c r="D41" s="4">
-        <v>46164.347442129627</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G41" s="3">
-        <v>747636152</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M41" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>2</v>
@@ -3472,198 +3499,198 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="52" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
-        <v>61255901</v>
+        <v>61315991</v>
       </c>
       <c r="B42" s="4">
-        <v>46120.75712962963</v>
+        <v>46121.743379629632</v>
       </c>
       <c r="C42" s="3">
-        <v>62951388</v>
+        <v>63689089</v>
       </c>
       <c r="D42" s="4">
-        <v>46150.494675925926</v>
+        <v>46164.351643518516</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>126</v>
       </c>
       <c r="G42" s="3">
-        <v>757818829</v>
+        <v>778495680</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="52" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
-        <v>61315991</v>
+        <v>61336527</v>
       </c>
       <c r="B43" s="4">
-        <v>46121.743379629632</v>
+        <v>46122.368761574071</v>
       </c>
       <c r="C43" s="3">
-        <v>63689089</v>
+        <v>63643262</v>
       </c>
       <c r="D43" s="4">
-        <v>46164.351643518516</v>
+        <v>46163.480023148149</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G43" s="3">
         <v>778495680</v>
       </c>
       <c r="H43" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q43" s="5">
+        <v>1679940</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="78" x14ac:dyDescent="0.35">
+      <c r="A44" s="3">
+        <v>61481328</v>
+      </c>
+      <c r="B44" s="4">
+        <v>46125.483310185184</v>
+      </c>
+      <c r="C44" s="3">
+        <v>62173555</v>
+      </c>
+      <c r="D44" s="4">
+        <v>46136.44263888889</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G44" s="3">
+        <v>708448800</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1891736</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="A45" s="3">
+        <v>61504448</v>
+      </c>
+      <c r="B45" s="4">
+        <v>46125.648935185185</v>
+      </c>
+      <c r="C45" s="3">
+        <v>62115179</v>
+      </c>
+      <c r="D45" s="4">
+        <v>46135.481111111112</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="52" x14ac:dyDescent="0.35">
-      <c r="A44" s="3">
-        <v>61336527</v>
-      </c>
-      <c r="B44" s="4">
-        <v>46122.368761574071</v>
-      </c>
-      <c r="C44" s="3">
-        <v>63643262</v>
-      </c>
-      <c r="D44" s="4">
-        <v>46163.480023148149</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F44" s="3" t="s">
+      <c r="G45" s="3">
+        <v>707234610</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G44" s="3">
-        <v>778495680</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>1679940</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="78" x14ac:dyDescent="0.35">
-      <c r="A45" s="3">
-        <v>61481328</v>
-      </c>
-      <c r="B45" s="4">
-        <v>46125.483310185184</v>
-      </c>
-      <c r="C45" s="3">
-        <v>62173555</v>
-      </c>
-      <c r="D45" s="4">
-        <v>46136.44263888889</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G45" s="3">
-        <v>708448800</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1891736</v>
+      <c r="I45" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>10</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>12</v>
@@ -3672,263 +3699,263 @@
         <v>6</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>138</v>
+        <v>32</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q45" s="5">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+        <v>3070672</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
-        <v>61504448</v>
+        <v>61509953</v>
       </c>
       <c r="B46" s="4">
-        <v>46125.648935185185</v>
+        <v>46125.694004629629</v>
       </c>
       <c r="C46" s="3">
-        <v>62115179</v>
+        <v>62751418</v>
       </c>
       <c r="D46" s="4">
-        <v>46135.481111111112</v>
+        <v>46147.490636574075</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G46" s="3">
-        <v>707234610</v>
+        <v>759379440</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O46" s="3">
+        <v>2732780110</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="A47" s="3">
+        <v>61560663</v>
+      </c>
+      <c r="B47" s="4">
+        <v>46126.615729166668</v>
+      </c>
+      <c r="C47" s="3">
+        <v>62946623</v>
+      </c>
+      <c r="D47" s="4">
+        <v>46150.461550925924</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G47" s="3">
+        <v>707984429</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q46" s="5">
-        <v>3070672</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="39" x14ac:dyDescent="0.35">
-      <c r="A47" s="3">
-        <v>61509953</v>
-      </c>
-      <c r="B47" s="4">
-        <v>46125.694004629629</v>
-      </c>
-      <c r="C47" s="3">
-        <v>62751418</v>
-      </c>
-      <c r="D47" s="4">
-        <v>46147.490636574075</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G47" s="3">
-        <v>759379440</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L47" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O47" s="3">
-        <v>2732780110</v>
+        <v>13</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>2</v>
+      <c r="Q47" s="5">
+        <v>2984038</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="26" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
-        <v>61560663</v>
+        <v>61608637</v>
       </c>
       <c r="B48" s="4">
-        <v>46126.615729166668</v>
+        <v>46127.491550925923</v>
       </c>
       <c r="C48" s="3">
-        <v>62946623</v>
+        <v>61677257</v>
       </c>
       <c r="D48" s="4">
-        <v>46150.461550925924</v>
+        <v>46128.483958333331</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="G48" s="3">
-        <v>707984429</v>
+        <v>702455701</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>39</v>
+        <v>138</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q48" s="5">
-        <v>2984038</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q48" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="52" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
-        <v>61608637</v>
+        <v>61644382</v>
       </c>
       <c r="B49" s="4">
-        <v>46127.491550925923</v>
+        <v>46127.754131944443</v>
       </c>
       <c r="C49" s="3">
-        <v>61677257</v>
+        <v>61977733</v>
       </c>
       <c r="D49" s="4">
-        <v>46128.483958333331</v>
+        <v>46133.466458333336</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="G49" s="3">
-        <v>702455701</v>
+        <v>759250737</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>2</v>
+      <c r="Q49" s="5">
+        <v>1680307</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="52" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
-        <v>61644382</v>
+        <v>61946442</v>
       </c>
       <c r="B50" s="4">
-        <v>46127.754131944443</v>
+        <v>46132.704247685186</v>
       </c>
       <c r="C50" s="3">
-        <v>61977733</v>
+        <v>62946744</v>
       </c>
       <c r="D50" s="4">
-        <v>46133.466458333336</v>
+        <v>46150.462650462963</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="G50" s="3">
-        <v>759250737</v>
+        <v>504041812</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>12</v>
@@ -3937,254 +3964,252 @@
         <v>6</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>147</v>
+        <v>43</v>
       </c>
       <c r="P50" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q50" s="5">
-        <v>1680307</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
-        <v>61946442</v>
+        <v>61972088</v>
       </c>
       <c r="B51" s="4">
-        <v>46132.704247685186</v>
+        <v>46133.422569444447</v>
       </c>
       <c r="C51" s="3">
-        <v>62946744</v>
+        <v>64146321</v>
       </c>
       <c r="D51" s="4">
-        <v>46150.462650462963</v>
+        <v>46174.477534722224</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G51" s="3">
         <v>504041812</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P51" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q51" s="5">
-        <v>1000000</v>
+      <c r="Q51" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
-        <v>61972088</v>
+        <v>61972108</v>
       </c>
       <c r="B52" s="4">
-        <v>46133.422569444447</v>
+        <v>46133.422662037039</v>
       </c>
       <c r="C52" s="3">
-        <v>63706807</v>
+        <v>62946845</v>
       </c>
       <c r="D52" s="4">
-        <v>46164.50849537037</v>
+        <v>46150.463449074072</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G52" s="3">
         <v>504041812</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q52" s="5">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="26" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
-        <v>61972108</v>
+        <v>62420329</v>
       </c>
       <c r="B53" s="4">
-        <v>46133.422662037039</v>
+        <v>46140.709513888891</v>
       </c>
       <c r="C53" s="3">
-        <v>62946845</v>
+        <v>63331641</v>
       </c>
       <c r="D53" s="4">
-        <v>46150.463449074072</v>
+        <v>46157.623310185183</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G53" s="3">
-        <v>504041812</v>
+        <v>777621987</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K53" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="P53" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q53" s="5">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
-        <v>62420329</v>
+        <v>62497009</v>
       </c>
       <c r="B54" s="4">
-        <v>46140.709513888891</v>
+        <v>46141.808842592596</v>
       </c>
       <c r="C54" s="3">
-        <v>63331641</v>
+        <v>63458983</v>
       </c>
       <c r="D54" s="4">
-        <v>46157.623310185183</v>
+        <v>46160.501875000002</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G54" s="3">
-        <v>777621987</v>
+        <v>702495660</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="N54" s="3"/>
       <c r="O54" s="3" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q54" s="5">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q54" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" ht="91" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
-        <v>62497009</v>
+        <v>62551370</v>
       </c>
       <c r="B55" s="4">
-        <v>46141.808842592596</v>
+        <v>46142.717349537037</v>
       </c>
       <c r="C55" s="3">
-        <v>63458983</v>
+        <v>63134483</v>
       </c>
       <c r="D55" s="4">
-        <v>46160.501875000002</v>
+        <v>46154.380196759259</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G55" s="3">
-        <v>702495660</v>
+        <v>576382850</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>2</v>
@@ -4203,7 +4228,7 @@
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="P55" s="3" t="s">
         <v>2</v>
@@ -4214,47 +4239,49 @@
     </row>
     <row r="56" spans="1:17" ht="91" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
-        <v>62551370</v>
+        <v>62672227</v>
       </c>
       <c r="B56" s="4">
-        <v>46142.717349537037</v>
+        <v>46146.403935185182</v>
       </c>
       <c r="C56" s="3">
-        <v>63134483</v>
+        <v>63331081</v>
       </c>
       <c r="D56" s="4">
-        <v>46154.380196759259</v>
+        <v>46157.619120370371</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G56" s="3">
-        <v>576382850</v>
+        <v>707169322</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N56" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="O56" s="3" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="P56" s="3" t="s">
         <v>2</v>
@@ -4265,143 +4292,141 @@
     </row>
     <row r="57" spans="1:17" ht="91" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
-        <v>62672227</v>
+        <v>62672234</v>
       </c>
       <c r="B57" s="4">
-        <v>46146.403935185182</v>
+        <v>46146.403969907406</v>
       </c>
       <c r="C57" s="3">
-        <v>63331081</v>
+        <v>63487207</v>
       </c>
       <c r="D57" s="4">
-        <v>46157.619120370371</v>
+        <v>46160.717349537037</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G57" s="3">
         <v>707169322</v>
       </c>
       <c r="H57" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q57" s="5">
+        <v>1644000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="104" x14ac:dyDescent="0.35">
+      <c r="A58" s="3">
+        <v>62680657</v>
+      </c>
+      <c r="B58" s="4">
+        <v>46146.475763888891</v>
+      </c>
+      <c r="C58" s="3">
+        <v>63485029</v>
+      </c>
+      <c r="D58" s="4">
+        <v>46160.702488425923</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G58" s="3">
+        <v>778096389</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3">
+        <v>2722560110</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="78" x14ac:dyDescent="0.35">
+      <c r="A59" s="3">
+        <v>62722805</v>
+      </c>
+      <c r="B59" s="4">
+        <v>46146.81181712963</v>
+      </c>
+      <c r="C59" s="3">
+        <v>64261496</v>
+      </c>
+      <c r="D59" s="4">
+        <v>46176.409166666665</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G59" s="3">
+        <v>708131488</v>
+      </c>
+      <c r="H59" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="91" x14ac:dyDescent="0.35">
-      <c r="A58" s="3">
-        <v>62672234</v>
-      </c>
-      <c r="B58" s="4">
-        <v>46146.403969907406</v>
-      </c>
-      <c r="C58" s="3">
-        <v>63487207</v>
-      </c>
-      <c r="D58" s="4">
-        <v>46160.717349537037</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G58" s="3">
-        <v>707169322</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q58" s="5">
-        <v>1644000</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" ht="104" x14ac:dyDescent="0.35">
-      <c r="A59" s="3">
-        <v>62680657</v>
-      </c>
-      <c r="B59" s="4">
-        <v>46146.475763888891</v>
-      </c>
-      <c r="C59" s="3">
-        <v>63485029</v>
-      </c>
-      <c r="D59" s="4">
-        <v>46160.702488425923</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G59" s="3">
-        <v>778096389</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>5</v>
@@ -4409,9 +4434,11 @@
       <c r="M59" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3">
-        <v>2722560110</v>
+      <c r="N59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>2</v>
@@ -4420,30 +4447,30 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="78" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="52" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
-        <v>62722805</v>
+        <v>62760027</v>
       </c>
       <c r="B60" s="4">
-        <v>46146.81181712963</v>
+        <v>46147.546493055554</v>
       </c>
       <c r="C60" s="3">
-        <v>63060104</v>
+        <v>64366142</v>
       </c>
       <c r="D60" s="4">
-        <v>46152.916122685187</v>
+        <v>46177.935208333336</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G60" s="3">
-        <v>708131488</v>
+        <v>777699799</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>2</v>
@@ -4461,10 +4488,10 @@
         <v>6</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>2</v>
@@ -4473,51 +4500,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
-        <v>62760027</v>
+        <v>62768013</v>
       </c>
       <c r="B61" s="4">
-        <v>46147.546493055554</v>
+        <v>46147.609988425924</v>
       </c>
       <c r="C61" s="3">
-        <v>64043744</v>
+        <v>62871386</v>
       </c>
       <c r="D61" s="4">
-        <v>46171.740902777776</v>
+        <v>46149.364837962959</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G61" s="3">
-        <v>777699799</v>
+        <v>143270405</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="M61" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="P61" s="3" t="s">
         <v>2</v>
@@ -4526,39 +4553,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="52" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
-        <v>62768013</v>
+        <v>63025600</v>
       </c>
       <c r="B62" s="4">
-        <v>46147.609988425924</v>
+        <v>46151.740983796299</v>
       </c>
       <c r="C62" s="3">
-        <v>62871386</v>
+        <v>63981861</v>
       </c>
       <c r="D62" s="4">
-        <v>46149.364837962959</v>
+        <v>46170.692743055559</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G62" s="3">
-        <v>143270405</v>
+        <v>758237461</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>12</v>
@@ -4567,516 +4594,516 @@
         <v>6</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>39</v>
+        <v>164</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="Q62" s="5">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
-        <v>63025600</v>
+        <v>63073782</v>
       </c>
       <c r="B63" s="4">
-        <v>46151.740983796299</v>
+        <v>46153.387870370374</v>
       </c>
       <c r="C63" s="3">
-        <v>63981861</v>
+        <v>64400935</v>
       </c>
       <c r="D63" s="4">
-        <v>46170.692743055559</v>
+        <v>46178.6247337963</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>16</v>
+        <v>167</v>
       </c>
       <c r="F63" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G63" s="3">
+        <v>710619970</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O63" s="3">
+        <v>2722220590</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q63" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="A64" s="3">
+        <v>63168095</v>
+      </c>
+      <c r="B64" s="4">
+        <v>46154.647604166668</v>
+      </c>
+      <c r="C64" s="3">
+        <v>64148362</v>
+      </c>
+      <c r="D64" s="4">
+        <v>46174.49119212963</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G64" s="3">
+        <v>747345191</v>
+      </c>
+      <c r="H64" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G63" s="3">
-        <v>758237461</v>
-      </c>
-      <c r="H63" s="3" t="s">
+      <c r="I64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>7103410</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="78" x14ac:dyDescent="0.35">
+      <c r="A65" s="3">
+        <v>63179342</v>
+      </c>
+      <c r="B65" s="4">
+        <v>46154.735729166663</v>
+      </c>
+      <c r="C65" s="3">
+        <v>64340204</v>
+      </c>
+      <c r="D65" s="4">
+        <v>46177.61341435185</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="I63" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K63" s="3" t="s">
+      <c r="G65" s="3">
+        <v>778179203</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q65" s="5">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="A66" s="3">
+        <v>63210811</v>
+      </c>
+      <c r="B66" s="4">
+        <v>46155.50409722222</v>
+      </c>
+      <c r="C66" s="3">
+        <v>63691538</v>
+      </c>
+      <c r="D66" s="4">
+        <v>46164.383981481478</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G66" s="3">
+        <v>160128782</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K66" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L63" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M63" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N63" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O63" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="P63" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q63" s="5">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" ht="65" x14ac:dyDescent="0.35">
-      <c r="A64" s="3">
-        <v>63073782</v>
-      </c>
-      <c r="B64" s="4">
-        <v>46153.387870370374</v>
-      </c>
-      <c r="C64" s="3">
-        <v>63689865</v>
-      </c>
-      <c r="D64" s="4">
-        <v>46164.36314814815</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G64" s="3">
-        <v>710619970</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J64" s="3" t="s">
+      <c r="L66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="A67" s="3">
+        <v>63443742</v>
+      </c>
+      <c r="B67" s="4">
+        <v>46160.375115740739</v>
+      </c>
+      <c r="C67" s="3">
+        <v>64299081</v>
+      </c>
+      <c r="D67" s="4">
+        <v>46176.702152777776</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G67" s="3">
+        <v>798886434</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K64" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L64" s="3" t="s">
+      <c r="K67" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L67" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M64" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N64" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O64" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="P64" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q64" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" ht="26" x14ac:dyDescent="0.35">
-      <c r="A65" s="3">
-        <v>63168095</v>
-      </c>
-      <c r="B65" s="4">
-        <v>46154.647604166668</v>
-      </c>
-      <c r="C65" s="3">
-        <v>63408293</v>
-      </c>
-      <c r="D65" s="4">
-        <v>46159.53460648148</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G65" s="3">
-        <v>747345191</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K65" s="3" t="s">
+      <c r="M67" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O67" s="3">
+        <v>2721712140</v>
+      </c>
+      <c r="P67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q67" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="A68" s="3">
+        <v>63451685</v>
+      </c>
+      <c r="B68" s="4">
+        <v>46160.45171296296</v>
+      </c>
+      <c r="C68" s="3">
+        <v>64380756</v>
+      </c>
+      <c r="D68" s="4">
+        <v>46178.45417824074</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G68" s="3">
+        <v>707407425</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L65" s="3" t="s">
+      <c r="L68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" ht="117" x14ac:dyDescent="0.35">
+      <c r="A69" s="3">
+        <v>63453142</v>
+      </c>
+      <c r="B69" s="4">
+        <v>46160.461238425924</v>
+      </c>
+      <c r="C69" s="3">
+        <v>63982556</v>
+      </c>
+      <c r="D69" s="4">
+        <v>46170.697962962964</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G69" s="3">
+        <v>507828407</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M65" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O65" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P65" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q65" s="5">
-        <v>7103410</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="78" x14ac:dyDescent="0.35">
-      <c r="A66" s="3">
-        <v>63179342</v>
-      </c>
-      <c r="B66" s="4">
-        <v>46154.735729166663</v>
-      </c>
-      <c r="C66" s="3">
-        <v>63888488</v>
-      </c>
-      <c r="D66" s="4">
-        <v>46168.647303240738</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G66" s="3">
-        <v>778179203</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q66" s="5">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="26" x14ac:dyDescent="0.35">
-      <c r="A67" s="3">
-        <v>63210811</v>
-      </c>
-      <c r="B67" s="4">
-        <v>46155.50409722222</v>
-      </c>
-      <c r="C67" s="3">
-        <v>63691538</v>
-      </c>
-      <c r="D67" s="4">
-        <v>46164.383981481478</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G67" s="3">
-        <v>160128782</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q67" s="5">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" ht="26" x14ac:dyDescent="0.35">
-      <c r="A68" s="3">
-        <v>63443742</v>
-      </c>
-      <c r="B68" s="4">
-        <v>46160.375115740739</v>
-      </c>
-      <c r="C68" s="3">
-        <v>63686966</v>
-      </c>
-      <c r="D68" s="4">
-        <v>46164.123784722222</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G68" s="3">
-        <v>798886434</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N68" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O68" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="P68" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q68" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" ht="52" x14ac:dyDescent="0.35">
-      <c r="A69" s="3">
-        <v>63449095</v>
-      </c>
-      <c r="B69" s="4">
-        <v>46160.428668981483</v>
-      </c>
-      <c r="C69" s="3">
-        <v>64055920</v>
-      </c>
-      <c r="D69" s="4">
-        <v>46172.333344907405</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G69" s="3">
-        <v>768420441</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M69" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="O69" s="3">
-        <v>2722560090</v>
+        <v>13</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="P69" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q69" s="3" t="s">
-        <v>2</v>
+      <c r="Q69" s="5">
+        <v>1009545</v>
       </c>
     </row>
     <row r="70" spans="1:17" ht="52" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
-        <v>63451685</v>
+        <v>63453475</v>
       </c>
       <c r="B70" s="4">
-        <v>46160.45171296296</v>
+        <v>46160.463773148149</v>
       </c>
       <c r="C70" s="3">
-        <v>63706707</v>
+        <v>64331438</v>
       </c>
       <c r="D70" s="4">
-        <v>46164.507638888892</v>
+        <v>46177.53229166667</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="F70" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" s="3">
+        <v>708343014</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q70" s="5">
+        <v>3940384</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+      <c r="A71" s="3">
+        <v>63462158</v>
+      </c>
+      <c r="B71" s="4">
+        <v>46160.525254629632</v>
+      </c>
+      <c r="C71" s="3">
+        <v>63498261</v>
+      </c>
+      <c r="D71" s="4">
+        <v>46160.901041666664</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F71" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G70" s="3">
-        <v>707407425</v>
-      </c>
-      <c r="H70" s="3" t="s">
+      <c r="G71" s="3">
+        <v>768231346</v>
+      </c>
+      <c r="H71" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="I70" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L70" s="3" t="s">
+      <c r="I71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L71" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M70" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N70" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O70" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P70" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q70" s="5">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" ht="117" x14ac:dyDescent="0.35">
-      <c r="A71" s="3">
-        <v>63453142</v>
-      </c>
-      <c r="B71" s="4">
-        <v>46160.461238425924</v>
-      </c>
-      <c r="C71" s="3">
-        <v>63982556</v>
-      </c>
-      <c r="D71" s="4">
-        <v>46170.697962962964</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G71" s="3">
-        <v>507828407</v>
-      </c>
-      <c r="H71" s="3" t="s">
+      <c r="M71" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N71" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q71" s="5">
+        <v>518450</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="A72" s="3">
+        <v>63477655</v>
+      </c>
+      <c r="B72" s="4">
+        <v>46160.651041666664</v>
+      </c>
+      <c r="C72" s="3">
+        <v>64070326</v>
+      </c>
+      <c r="D72" s="4">
+        <v>46172.530532407407</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F72" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I71" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M71" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N71" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O71" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P71" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q71" s="5">
-        <v>1009545</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" ht="65" x14ac:dyDescent="0.35">
-      <c r="A72" s="3">
-        <v>63453475</v>
-      </c>
-      <c r="B72" s="4">
-        <v>46160.463773148149</v>
-      </c>
-      <c r="C72" s="3">
-        <v>63498333</v>
-      </c>
-      <c r="D72" s="4">
-        <v>46160.904537037037</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="G72" s="3">
-        <v>708343014</v>
+        <v>709528212</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>185</v>
@@ -5085,104 +5112,104 @@
         <v>2</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q72" s="5">
-        <v>3940384</v>
+      <c r="Q72" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
-        <v>63462158</v>
+        <v>63519784</v>
       </c>
       <c r="B73" s="4">
-        <v>46160.525254629632</v>
+        <v>46161.496840277781</v>
       </c>
       <c r="C73" s="3">
-        <v>63498261</v>
+        <v>64376626</v>
       </c>
       <c r="D73" s="4">
-        <v>46160.901041666664</v>
+        <v>46178.418437499997</v>
       </c>
       <c r="E73" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="G73" s="3">
+        <v>707079088</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G73" s="3">
-        <v>768231346</v>
-      </c>
-      <c r="H73" s="3" t="s">
+      <c r="I73" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N73" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O73" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="I73" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K73" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="L73" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M73" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N73" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="O73" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="P73" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q73" s="5">
-        <v>518450</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
-        <v>63477655</v>
+        <v>63526115</v>
       </c>
       <c r="B74" s="4">
-        <v>46160.651041666664</v>
+        <v>46161.544733796298</v>
       </c>
       <c r="C74" s="3">
-        <v>64070326</v>
+        <v>64146684</v>
       </c>
       <c r="D74" s="4">
-        <v>46172.530532407407</v>
+        <v>46174.480104166665</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G74" s="3">
-        <v>709528212</v>
+        <v>707722441</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>190</v>
@@ -5191,104 +5218,104 @@
         <v>2</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="M74" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="P74" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q74" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q74" s="5">
+        <v>1513624</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
-        <v>63495969</v>
+        <v>63529958</v>
       </c>
       <c r="B75" s="4">
-        <v>46160.82644675926</v>
+        <v>46161.577581018515</v>
       </c>
       <c r="C75" s="3">
-        <v>64009175</v>
+        <v>64330956</v>
       </c>
       <c r="D75" s="4">
-        <v>46171.450324074074</v>
+        <v>46177.528310185182</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>191</v>
       </c>
       <c r="G75" s="3">
-        <v>747777575</v>
+        <v>708081052</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="I75" s="3" t="s">
-        <v>2</v>
+      <c r="I75" s="3">
+        <v>1943146</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="M75" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="P75" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q75" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+      <c r="Q75" s="5">
+        <v>655375</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
-        <v>63519784</v>
+        <v>63535613</v>
       </c>
       <c r="B76" s="4">
-        <v>46161.496840277781</v>
+        <v>46161.623263888891</v>
       </c>
       <c r="C76" s="3">
-        <v>63931997</v>
+        <v>64322028</v>
       </c>
       <c r="D76" s="4">
-        <v>46169.771377314813</v>
+        <v>46177.444884259261</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>194</v>
       </c>
       <c r="G76" s="3">
-        <v>707079088</v>
+        <v>747165047</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>195</v>
@@ -5297,10 +5324,10 @@
         <v>2</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>12</v>
@@ -5309,48 +5336,48 @@
         <v>6</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>32</v>
+        <v>196</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q76" s="5">
-        <v>1400000</v>
+        <v>277235</v>
       </c>
     </row>
     <row r="77" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
-        <v>63526115</v>
+        <v>63556908</v>
       </c>
       <c r="B77" s="4">
-        <v>46161.544733796298</v>
+        <v>46161.788553240738</v>
       </c>
       <c r="C77" s="3">
-        <v>63834594</v>
+        <v>64260259</v>
       </c>
       <c r="D77" s="4">
-        <v>46167.705752314818</v>
+        <v>46176.402372685188</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G77" s="3">
-        <v>707722441</v>
+        <v>711458931</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K77" s="3" t="s">
         <v>11</v>
@@ -5362,51 +5389,51 @@
         <v>6</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="P77" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q77" s="5">
-        <v>1513624</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" ht="26" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
-        <v>63529958</v>
+        <v>63577039</v>
       </c>
       <c r="B78" s="4">
-        <v>46161.577581018515</v>
+        <v>46162.450127314813</v>
       </c>
       <c r="C78" s="3">
-        <v>63960740</v>
+        <v>64222245</v>
       </c>
       <c r="D78" s="4">
-        <v>46170.539502314816</v>
+        <v>46175.601759259262</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G78" s="3">
-        <v>708081052</v>
+        <v>716610940</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="I78" s="3">
-        <v>1943146</v>
+        <v>119</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="J78" s="3" t="s">
         <v>10</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="L78" s="3" t="s">
         <v>12</v>
@@ -5415,7 +5442,7 @@
         <v>6</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="O78" s="3" t="s">
         <v>200</v>
@@ -5424,30 +5451,30 @@
         <v>2</v>
       </c>
       <c r="Q78" s="5">
-        <v>655375</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+        <v>299185</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" ht="26" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
-        <v>63535613</v>
+        <v>63578582</v>
       </c>
       <c r="B79" s="4">
-        <v>46161.623263888891</v>
+        <v>46162.462199074071</v>
       </c>
       <c r="C79" s="3">
-        <v>64118436</v>
+        <v>63834278</v>
       </c>
       <c r="D79" s="4">
-        <v>46173.720347222225</v>
+        <v>46167.701192129629</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>204</v>
+        <v>58</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>201</v>
       </c>
       <c r="G79" s="3">
-        <v>747165047</v>
+        <v>759974992</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>202</v>
@@ -5456,219 +5483,219 @@
         <v>2</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>26</v>
+        <v>203</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M79" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>203</v>
+        <v>45</v>
       </c>
       <c r="P79" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q79" s="5">
-        <v>277235</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+        <v>4487314</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" ht="156" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
-        <v>63556908</v>
+        <v>63595239</v>
       </c>
       <c r="B80" s="4">
-        <v>46161.788553240738</v>
+        <v>46162.588333333333</v>
       </c>
       <c r="C80" s="3">
-        <v>63931844</v>
+        <v>63641944</v>
       </c>
       <c r="D80" s="4">
-        <v>46169.76798611111</v>
+        <v>46163.471006944441</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>59</v>
+        <v>206</v>
       </c>
       <c r="F80" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G80" s="3">
+        <v>749194205</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G80" s="3">
-        <v>711458931</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="I80" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K80" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="M80" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="P80" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q80" s="5">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="Q80" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
-        <v>63577039</v>
+        <v>63610581</v>
       </c>
       <c r="B81" s="4">
-        <v>46162.450127314813</v>
+        <v>46162.70239583333</v>
       </c>
       <c r="C81" s="3">
-        <v>64122544</v>
+        <v>64387146</v>
       </c>
       <c r="D81" s="4">
-        <v>46173.810034722221</v>
+        <v>46178.506365740737</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G81" s="3">
-        <v>716610940</v>
+        <v>799642361</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>208</v>
+        <v>29</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q81" s="5">
-        <v>299185</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="Q81" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
-        <v>63578582</v>
+        <v>63611129</v>
       </c>
       <c r="B82" s="4">
-        <v>46162.462199074071</v>
+        <v>46162.70616898148</v>
       </c>
       <c r="C82" s="3">
-        <v>63834278</v>
+        <v>64386946</v>
       </c>
       <c r="D82" s="4">
-        <v>46167.701192129629</v>
+        <v>46178.504861111112</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F82" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G82" s="3">
+        <v>799642361</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G82" s="3">
-        <v>759974992</v>
-      </c>
-      <c r="H82" s="3" t="s">
+      <c r="I82" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="P82" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q82" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="A83" s="3">
+        <v>63643964</v>
+      </c>
+      <c r="B83" s="4">
+        <v>46163.485543981478</v>
+      </c>
+      <c r="C83" s="3">
+        <v>64327360</v>
+      </c>
+      <c r="D83" s="4">
+        <v>46177.494872685187</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F83" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="I82" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J82" s="3" t="s">
+      <c r="G83" s="3">
+        <v>718824404</v>
+      </c>
+      <c r="H83" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="K82" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M82" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N82" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O82" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P82" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q82" s="5">
-        <v>4487314</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" ht="156" x14ac:dyDescent="0.35">
-      <c r="A83" s="3">
-        <v>63595239</v>
-      </c>
-      <c r="B83" s="4">
-        <v>46162.588333333333</v>
-      </c>
-      <c r="C83" s="3">
-        <v>63641944</v>
-      </c>
-      <c r="D83" s="4">
-        <v>46163.471006944441</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G83" s="3">
-        <v>749194205</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>11</v>
@@ -5680,42 +5707,42 @@
         <v>6</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q83" s="5">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="52" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
-        <v>63610581</v>
+        <v>63674987</v>
       </c>
       <c r="B84" s="4">
-        <v>46162.70239583333</v>
+        <v>46163.735543981478</v>
       </c>
       <c r="C84" s="3">
-        <v>64069294</v>
+        <v>64233133</v>
       </c>
       <c r="D84" s="4">
-        <v>46172.521064814813</v>
+        <v>46175.681793981479</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G84" s="3">
-        <v>799642361</v>
+        <v>707479292</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>2</v>
@@ -5733,10 +5760,10 @@
         <v>6</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O84" s="3" t="s">
-        <v>23</v>
+        <v>74</v>
+      </c>
+      <c r="O84" s="3">
+        <v>2723540540</v>
       </c>
       <c r="P84" s="3" t="s">
         <v>2</v>
@@ -5745,51 +5772,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" ht="78" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
-        <v>63611129</v>
+        <v>63688978</v>
       </c>
       <c r="B85" s="4">
-        <v>46162.70616898148</v>
+        <v>46164.349548611113</v>
       </c>
       <c r="C85" s="3">
-        <v>64069270</v>
+        <v>64069688</v>
       </c>
       <c r="D85" s="4">
-        <v>46172.520821759259</v>
+        <v>46172.524756944447</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F85" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G85" s="3">
+        <v>709513411</v>
+      </c>
+      <c r="H85" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G85" s="3">
-        <v>799642361</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="I85" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="P85" s="3" t="s">
         <v>2</v>
@@ -5798,83 +5825,83 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" ht="78" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
-        <v>63643964</v>
+        <v>63688990</v>
       </c>
       <c r="B86" s="4">
-        <v>46163.485543981478</v>
+        <v>46164.349618055552</v>
       </c>
       <c r="C86" s="3">
-        <v>64069963</v>
+        <v>64366272</v>
       </c>
       <c r="D86" s="4">
-        <v>46172.527037037034</v>
+        <v>46177.963703703703</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G86" s="3">
-        <v>718824404</v>
+        <v>709513411</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P86" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q86" s="5">
-        <v>1000000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="87" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
-        <v>63674987</v>
+        <v>63689992</v>
       </c>
       <c r="B87" s="4">
-        <v>46163.735543981478</v>
+        <v>46164.364722222221</v>
       </c>
       <c r="C87" s="3">
-        <v>64025954</v>
+        <v>64366288</v>
       </c>
       <c r="D87" s="4">
-        <v>46171.6018287037</v>
+        <v>46177.965694444443</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>186</v>
+        <v>58</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G87" s="3">
-        <v>707479292</v>
+        <v>709513411</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>2</v>
@@ -5892,10 +5919,10 @@
         <v>6</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="P87" s="3" t="s">
         <v>2</v>
@@ -5904,239 +5931,239 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="78" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
-        <v>63688978</v>
+        <v>63693483</v>
       </c>
       <c r="B88" s="4">
-        <v>46164.349548611113</v>
+        <v>46164.404108796298</v>
       </c>
       <c r="C88" s="3">
-        <v>63852938</v>
+        <v>63998411</v>
       </c>
       <c r="D88" s="4">
-        <v>46168.365914351853</v>
+        <v>46171.337291666663</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G88" s="3">
-        <v>709513411</v>
+        <v>556999292</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K88" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>23</v>
+        <v>219</v>
       </c>
       <c r="P88" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q88" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" ht="78" x14ac:dyDescent="0.35">
+      <c r="Q88" s="5">
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
-        <v>63688990</v>
+        <v>63695475</v>
       </c>
       <c r="B89" s="4">
-        <v>46164.349618055552</v>
+        <v>46164.422708333332</v>
       </c>
       <c r="C89" s="3">
-        <v>63931910</v>
+        <v>64018151</v>
       </c>
       <c r="D89" s="4">
-        <v>46169.769421296296</v>
+        <v>46171.524953703702</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G89" s="3">
-        <v>709513411</v>
+        <v>556999292</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q89" s="5">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="52" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
-        <v>63689992</v>
+        <v>63702675</v>
       </c>
       <c r="B90" s="4">
-        <v>46164.364722222221</v>
+        <v>46164.47996527778</v>
       </c>
       <c r="C90" s="3">
-        <v>63931951</v>
+        <v>64371605</v>
       </c>
       <c r="D90" s="4">
-        <v>46169.770127314812</v>
+        <v>46178.364108796297</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="F90" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G90" s="3">
+        <v>707479292</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I90" s="3">
+        <v>1944406</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M90" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G90" s="3">
-        <v>709513411</v>
-      </c>
-      <c r="H90" s="3" t="s">
+      <c r="N90" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="P90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q90" s="5">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="A91" s="3">
+        <v>63705970</v>
+      </c>
+      <c r="B91" s="4">
+        <v>46164.501944444448</v>
+      </c>
+      <c r="C91" s="3">
+        <v>64371847</v>
+      </c>
+      <c r="D91" s="4">
+        <v>46178.367905092593</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F91" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="I90" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M90" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N90" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O90" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="P90" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q90" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" ht="65" x14ac:dyDescent="0.35">
-      <c r="A91" s="3">
-        <v>63693483</v>
-      </c>
-      <c r="B91" s="4">
-        <v>46164.404108796298</v>
-      </c>
-      <c r="C91" s="3">
-        <v>63998411</v>
-      </c>
-      <c r="D91" s="4">
-        <v>46171.337291666663</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F91" s="3" t="s">
+      <c r="G91" s="3">
+        <v>707361318</v>
+      </c>
+      <c r="H91" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G91" s="3">
-        <v>556999292</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O91" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q91" s="5">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" ht="26" x14ac:dyDescent="0.35">
+      <c r="A92" s="3">
+        <v>63967008</v>
+      </c>
+      <c r="B92" s="4">
+        <v>46170.591331018521</v>
+      </c>
+      <c r="C92" s="3">
+        <v>64369398</v>
+      </c>
+      <c r="D92" s="4">
+        <v>46178.347060185188</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F92" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q91" s="5">
-        <v>2200000</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" ht="65" x14ac:dyDescent="0.35">
-      <c r="A92" s="3">
-        <v>63695475</v>
-      </c>
-      <c r="B92" s="4">
-        <v>46164.422708333332</v>
-      </c>
-      <c r="C92" s="3">
-        <v>64018151</v>
-      </c>
-      <c r="D92" s="4">
-        <v>46171.524953703702</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="G92" s="3">
-        <v>556999292</v>
+        <v>566473307</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>229</v>
@@ -6145,157 +6172,157 @@
         <v>2</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K92" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M92" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>28</v>
+        <v>230</v>
       </c>
       <c r="P92" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q92" s="5">
-        <v>2200000</v>
+      <c r="Q92" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:17" ht="26" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
-        <v>63702675</v>
+        <v>63967605</v>
       </c>
       <c r="B93" s="4">
-        <v>46164.47996527778</v>
+        <v>46170.596550925926</v>
       </c>
       <c r="C93" s="3">
-        <v>64044084</v>
+        <v>64369796</v>
       </c>
       <c r="D93" s="4">
-        <v>46171.744710648149</v>
+        <v>46178.349293981482</v>
       </c>
       <c r="E93" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G93" s="3">
+        <v>566473307</v>
+      </c>
+      <c r="H93" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="G93" s="3">
-        <v>707479292</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="I93" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K93" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="M93" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P93" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q93" s="5">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" ht="91" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
-        <v>63705970</v>
+        <v>64005644</v>
       </c>
       <c r="B94" s="4">
-        <v>46164.501944444448</v>
+        <v>46171.424525462964</v>
       </c>
       <c r="C94" s="3">
-        <v>64043770</v>
+        <v>64228385</v>
       </c>
       <c r="D94" s="4">
-        <v>46171.741157407407</v>
+        <v>46175.64534722222</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G94" s="3">
-        <v>707361318</v>
+        <v>707109668</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q94" s="5">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q94" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
-        <v>63720018</v>
+        <v>64028024</v>
       </c>
       <c r="B95" s="4">
-        <v>46164.627627314818</v>
+        <v>46171.618414351855</v>
       </c>
       <c r="C95" s="3">
-        <v>64014179</v>
+        <v>64356650</v>
       </c>
       <c r="D95" s="4">
-        <v>46171.491574074076</v>
+        <v>46177.753333333334</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>234</v>
+        <v>87</v>
       </c>
       <c r="G95" s="3">
-        <v>707070080</v>
+        <v>709837321</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>235</v>
@@ -6304,19 +6331,19 @@
         <v>2</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O95" s="3" t="s">
         <v>236</v>
@@ -6324,370 +6351,370 @@
       <c r="P95" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q95" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="Q95" s="5">
+        <v>5324000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" ht="65" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
-        <v>63720023</v>
+        <v>64029495</v>
       </c>
       <c r="B96" s="4">
-        <v>46164.627650462964</v>
+        <v>46171.630046296297</v>
       </c>
       <c r="C96" s="3">
-        <v>64013878</v>
+        <v>64372758</v>
       </c>
       <c r="D96" s="4">
-        <v>46171.488518518519</v>
+        <v>46178.378113425926</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>193</v>
+        <v>239</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>234</v>
+        <v>87</v>
       </c>
       <c r="G96" s="3">
-        <v>707070080</v>
+        <v>708335225</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>237</v>
+        <v>129</v>
       </c>
       <c r="P96" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q96" s="5">
-        <v>814800</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+        <v>5324000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
-        <v>63967008</v>
+        <v>64145330</v>
       </c>
       <c r="B97" s="4">
-        <v>46170.591331018521</v>
+        <v>46174.470370370371</v>
       </c>
       <c r="C97" s="3">
-        <v>64003457</v>
+        <v>64366225</v>
       </c>
       <c r="D97" s="4">
-        <v>46171.404895833337</v>
+        <v>46177.954687500001</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G97" s="3">
-        <v>566473307</v>
+        <v>707361318</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="I97" s="3">
-        <v>1945296</v>
+        <v>107</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="K97" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>240</v>
+        <v>29</v>
       </c>
       <c r="P97" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="Q97" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+      <c r="Q97" s="5">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
-        <v>63967605</v>
+        <v>64149984</v>
       </c>
       <c r="B98" s="4">
-        <v>46170.596550925926</v>
+        <v>46174.503194444442</v>
       </c>
       <c r="C98" s="3">
-        <v>64003314</v>
+        <v>64366089</v>
       </c>
       <c r="D98" s="4">
-        <v>46171.403703703705</v>
+        <v>46177.931805555556</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G98" s="3">
-        <v>566473307</v>
+        <v>718151543</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="I98" s="3">
-        <v>1945306</v>
+        <v>107</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K98" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O98" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P98" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q98" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="A99" s="3">
+        <v>64159836</v>
+      </c>
+      <c r="B99" s="4">
+        <v>46174.578506944446</v>
+      </c>
+      <c r="C99" s="3">
+        <v>64366295</v>
+      </c>
+      <c r="D99" s="4">
+        <v>46177.967395833337</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F99" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="P98" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" ht="91" x14ac:dyDescent="0.35">
-      <c r="A99" s="3">
-        <v>64005644</v>
-      </c>
-      <c r="B99" s="4">
-        <v>46171.424525462964</v>
-      </c>
-      <c r="C99" s="3">
-        <v>64009001</v>
-      </c>
-      <c r="D99" s="4">
-        <v>46171.448877314811</v>
-      </c>
-      <c r="E99" s="3" t="s">
+      <c r="G99" s="3">
+        <v>788987805</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N99" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P99" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q99" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" ht="91" x14ac:dyDescent="0.35">
+      <c r="A100" s="3">
+        <v>64168091</v>
+      </c>
+      <c r="B100" s="4">
+        <v>46174.65016203704</v>
+      </c>
+      <c r="C100" s="3">
+        <v>64366297</v>
+      </c>
+      <c r="D100" s="4">
+        <v>46177.96769675926</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G100" s="3">
+        <v>777378597</v>
+      </c>
+      <c r="H100" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F99" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G99" s="3">
-        <v>707109668</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J99" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K99" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L99" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N99" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O99" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="P99" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q99" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" ht="52" x14ac:dyDescent="0.35">
-      <c r="A100" s="3">
-        <v>64023674</v>
-      </c>
-      <c r="B100" s="4">
-        <v>46171.581018518518</v>
-      </c>
-      <c r="C100" s="3">
-        <v>64036834</v>
-      </c>
-      <c r="D100" s="4">
-        <v>46171.685567129629</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F100" s="3" t="s">
+      <c r="I100" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="39" x14ac:dyDescent="0.35">
+      <c r="A101" s="3">
+        <v>64204580</v>
+      </c>
+      <c r="B101" s="4">
+        <v>46175.463912037034</v>
+      </c>
+      <c r="C101" s="3">
+        <v>64372229</v>
+      </c>
+      <c r="D101" s="4">
+        <v>46178.373935185184</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="G100" s="3">
-        <v>777989663</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="O100" s="3" t="s">
+      <c r="G101" s="3">
+        <v>779885779</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="52" x14ac:dyDescent="0.35">
+      <c r="A102" s="3">
+        <v>64257153</v>
+      </c>
+      <c r="B102" s="4">
+        <v>46176.363680555558</v>
+      </c>
+      <c r="C102" s="3">
+        <v>64351413</v>
+      </c>
+      <c r="D102" s="4">
+        <v>46177.702152777776</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F102" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q100" s="5">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" ht="65" x14ac:dyDescent="0.35">
-      <c r="A101" s="3">
-        <v>64027227</v>
-      </c>
-      <c r="B101" s="4">
-        <v>46171.611979166664</v>
-      </c>
-      <c r="C101" s="3">
-        <v>64038585</v>
-      </c>
-      <c r="D101" s="4">
-        <v>46171.698159722226</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G101" s="3">
-        <v>709837321</v>
-      </c>
-      <c r="H101" s="3" t="s">
+      <c r="G102" s="3">
+        <v>749574805</v>
+      </c>
+      <c r="H102" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q101" s="5">
-        <v>1644000</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="26" x14ac:dyDescent="0.35">
-      <c r="A102" s="3">
-        <v>64028024</v>
-      </c>
-      <c r="B102" s="4">
-        <v>46171.618414351855</v>
-      </c>
-      <c r="C102" s="3">
-        <v>64028053</v>
-      </c>
-      <c r="D102" s="4">
-        <v>46171.618645833332</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G102" s="3">
-        <v>709837321</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="I102" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>2</v>
@@ -6696,64 +6723,223 @@
         <v>2</v>
       </c>
       <c r="Q102" s="5">
-        <v>5324000</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" ht="39" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
-        <v>64029495</v>
+        <v>64298334</v>
       </c>
       <c r="B103" s="4">
-        <v>46171.630046296297</v>
+        <v>46176.697557870371</v>
       </c>
       <c r="C103" s="3">
-        <v>64038754</v>
+        <v>64372353</v>
       </c>
       <c r="D103" s="4">
-        <v>46171.699479166666</v>
+        <v>46178.375613425924</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>165</v>
+        <v>239</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>89</v>
+        <v>249</v>
       </c>
       <c r="G103" s="3">
-        <v>708335225</v>
+        <v>102435520</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>250</v>
+        <v>121</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K103" s="3" t="s">
         <v>11</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M103" s="3" t="s">
         <v>6</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O103" s="3" t="s">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="P103" s="3" t="s">
         <v>2</v>
       </c>
       <c r="Q103" s="5">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+      <c r="A104" s="3">
+        <v>64299624</v>
+      </c>
+      <c r="B104" s="4">
+        <v>46176.705578703702</v>
+      </c>
+      <c r="C104" s="3">
+        <v>64337058</v>
+      </c>
+      <c r="D104" s="4">
+        <v>46177.582615740743</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G104" s="3">
+        <v>789196850</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M104" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N104" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O104" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P104" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q104" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" ht="65" x14ac:dyDescent="0.35">
+      <c r="A105" s="3">
+        <v>64299644</v>
+      </c>
+      <c r="B105" s="4">
+        <v>46176.705625000002</v>
+      </c>
+      <c r="C105" s="3">
+        <v>64337134</v>
+      </c>
+      <c r="D105" s="4">
+        <v>46177.583553240744</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G105" s="3">
+        <v>789196850</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J105" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K105" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L105" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M105" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N105" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O105" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P105" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q105" s="5">
         <v>5324000</v>
       </c>
     </row>
+    <row r="106" spans="1:17" ht="91" x14ac:dyDescent="0.35">
+      <c r="A106" s="3">
+        <v>64327001</v>
+      </c>
+      <c r="B106" s="4">
+        <v>46177.491620370369</v>
+      </c>
+      <c r="C106" s="3">
+        <v>64386240</v>
+      </c>
+      <c r="D106" s="4">
+        <v>46178.499872685185</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G106" s="3">
+        <v>747103333</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M106" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N106" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O106" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P106" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q106" s="5">
+        <v>2371414</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q103" xr:uid="{CBD3779C-7CB1-4222-BF19-E0D2FB3081A6}"/>
+  <autoFilter ref="A1:Q106" xr:uid="{F8D0A148-9DB7-45FC-B27B-D5D1079BE330}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/Attachments/Bureau/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="577" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDBE5EC4-AA16-48B9-A0C8-6F9B1A0A0531}"/>
+  <xr:revisionPtr revIDLastSave="584" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8265E2E9-1733-4438-812D-3C55790FE46D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="49" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="50" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$S$99</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="280">
   <si>
     <t>-</t>
   </si>
@@ -329,9 +326,6 @@
     <t>ZENITH BANK COTE D'IVOIRE</t>
   </si>
   <si>
-    <t>DIRECTION GENERALE DES DOUANES</t>
-  </si>
-  <si>
     <t>XXXXXXXXXXXXX</t>
   </si>
   <si>
@@ -488,9 +482,6 @@
     <t>Responsable Zone: Validation intervention</t>
   </si>
   <si>
-    <t>SYTHD260122</t>
-  </si>
-  <si>
     <t>ABIDJAN-COCODY//VOIE INCONNUE/RIVIERA 0708448800</t>
   </si>
   <si>
@@ -539,9 +530,6 @@
     <t>BUVPN260086</t>
   </si>
   <si>
-    <t>PLANETPHARMA EXPORT CI</t>
-  </si>
-  <si>
     <t>Responsable Zone: Coordination etude et travaux</t>
   </si>
   <si>
@@ -578,18 +566,9 @@
     <t>SITE SESOCOM TRANSIT TREICHVILLE AVENUE 21 RUE 15</t>
   </si>
   <si>
-    <t>STE BGFI BANK</t>
-  </si>
-  <si>
-    <t>COCODY DANGA</t>
-  </si>
-  <si>
     <t>Technicien zone: Intervention</t>
   </si>
   <si>
-    <t>DANANE</t>
-  </si>
-  <si>
     <t>AFRICURE PHARMACEUTICAL COTE D'IVOIRE</t>
   </si>
   <si>
@@ -665,12 +644,6 @@
     <t>MARCORY ZONE 4</t>
   </si>
   <si>
-    <t>EPHR AGBOVILLE</t>
-  </si>
-  <si>
-    <t>AGBOVILLE</t>
-  </si>
-  <si>
     <t>STE UCP SANTE MONDIALE</t>
   </si>
   <si>
@@ -701,21 +674,6 @@
     <t>ABOBO</t>
   </si>
   <si>
-    <t>MOTA-ENGIL COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>SEGUELA//VOIE INCONNUE/CT: M AKOUE AU 0748512613</t>
-  </si>
-  <si>
-    <t>SYTHD260159</t>
-  </si>
-  <si>
-    <t>BO Homologation: Saisie BSCS</t>
-  </si>
-  <si>
-    <t>BUVPN260095</t>
-  </si>
-  <si>
     <t>ORANGE BUSNESS SERVICES</t>
   </si>
   <si>
@@ -794,15 +752,6 @@
     <t>ORANGE VILLAGE / PIA SALLE REUNION DG</t>
   </si>
   <si>
-    <t>ORANGE BUSINESS SERVICES</t>
-  </si>
-  <si>
-    <t>SYTHD160170</t>
-  </si>
-  <si>
-    <t>BO Homologation: Saisie GAIA</t>
-  </si>
-  <si>
     <t>COMPAGNIE DE CONTROLE TECHNIQUE AUTOMOBILE (CCTA)</t>
   </si>
   <si>
@@ -813,6 +762,120 @@
   </si>
   <si>
     <t>COCODY DEUX PLATEAUX IMMEUBLE NOLA</t>
+  </si>
+  <si>
+    <t>MOTA ENGIL</t>
+  </si>
+  <si>
+    <t>Planification Ctrl Conformite</t>
+  </si>
+  <si>
+    <t>Prestataire : Correction Conformite Travaux</t>
+  </si>
+  <si>
+    <t>TAABO LAMTO</t>
+  </si>
+  <si>
+    <t>xxxxxx</t>
+  </si>
+  <si>
+    <t>Saisie ASCOM</t>
+  </si>
+  <si>
+    <t>ABIDJAN-TREICHVILLE//VOIE INCONNUE/RIVIERA PALMERAIE RESIDENTIEL</t>
+  </si>
+  <si>
+    <t>SYTHD260162</t>
+  </si>
+  <si>
+    <t>Support IP: Config Eq Acces</t>
+  </si>
+  <si>
+    <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY DANGA</t>
+  </si>
+  <si>
+    <t>BUVPN260101</t>
+  </si>
+  <si>
+    <t>Transmission Plans Equipe Numerisation</t>
+  </si>
+  <si>
+    <t>YAMOUSSOUKRO Kick-off</t>
+  </si>
+  <si>
+    <t>SYTHD260164</t>
+  </si>
+  <si>
+    <t>BUVPN260100</t>
+  </si>
+  <si>
+    <t>BBF : Validation Etude</t>
+  </si>
+  <si>
+    <t>ORANGE BUSINESS SERVICES COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>Realisation Ctrl Conformite</t>
+  </si>
+  <si>
+    <t>COCODY RIVIERA GOLF</t>
+  </si>
+  <si>
+    <t>AGENCE OCI 2PLTX ENA</t>
+  </si>
+  <si>
+    <t>RIVIERA GOLF</t>
+  </si>
+  <si>
+    <t>OCI VILLAGE</t>
+  </si>
+  <si>
+    <t>LIGNE TEST LSI ASSURANCE</t>
+  </si>
+  <si>
+    <t>ORANGE FAB COCODY</t>
+  </si>
+  <si>
+    <t>LIGNES TESTS LSI ASSURANCE</t>
+  </si>
+  <si>
+    <t>COCODY ORANGE FAB</t>
+  </si>
+  <si>
+    <t>TOUCHPOINT FINANCIAL SERVICE</t>
+  </si>
+  <si>
+    <t>COCODY 2 PLATEAU</t>
+  </si>
+  <si>
+    <t>BRIDGEBANK</t>
+  </si>
+  <si>
+    <t>GRAND-BASSAM</t>
+  </si>
+  <si>
+    <t>FRANCHISE TTS</t>
+  </si>
+  <si>
+    <t>RIVIERA PALMERAIE</t>
+  </si>
+  <si>
+    <t>IP Delivery: Validation information</t>
+  </si>
+  <si>
+    <t>FRANCHISE MANKONO</t>
+  </si>
+  <si>
+    <t>MANKONO</t>
+  </si>
+  <si>
+    <t>SAN PEDRO</t>
+  </si>
+  <si>
+    <t>SYTHD260165</t>
+  </si>
+  <si>
+    <t>MINISTERE DE L’ENVIRONNEMENT</t>
   </si>
 </sst>
 </file>
@@ -856,18 +919,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1196,8 +1248,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2053CF0E-53A2-4CAA-A484-0CECB27DEFAC}">
-  <dimension ref="A1:Q99"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B09768A0-915F-4D98-A6E3-373DEF20CD6F}">
+  <dimension ref="A1:Q142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
@@ -1241,7 +1293,7 @@
         <v>51</v>
       </c>
       <c r="N1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O1" t="s">
         <v>52</v>
@@ -1311,28 +1363,28 @@
         <v>45897.665000000001</v>
       </c>
       <c r="C3">
-        <v>64509394</v>
+        <v>64741602</v>
       </c>
       <c r="D3" s="2">
-        <v>46181.36378472222</v>
+        <v>46184.710358796299</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="F3" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="G3">
         <v>748512613</v>
       </c>
       <c r="H3" t="s">
-        <v>221</v>
-      </c>
-      <c r="I3">
-        <v>2743575</v>
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K3" t="s">
         <v>5</v>
@@ -1341,7 +1393,7 @@
         <v>6</v>
       </c>
       <c r="M3" t="s">
-        <v>187</v>
+        <v>3</v>
       </c>
       <c r="N3" t="s">
         <v>107</v>
@@ -1353,89 +1405,89 @@
         <v>2538822</v>
       </c>
       <c r="Q3" t="s">
-        <v>222</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>52778382</v>
+        <v>49660008</v>
       </c>
       <c r="B4" s="2">
-        <v>45959.67696759259</v>
+        <v>45897.665000000001</v>
       </c>
       <c r="C4">
-        <v>55073470</v>
+        <v>64800088</v>
       </c>
       <c r="D4" s="2">
-        <v>46003.678194444445</v>
+        <v>46185.684594907405</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>243</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>242</v>
       </c>
       <c r="G4">
-        <v>708086759</v>
+        <v>748512613</v>
       </c>
       <c r="H4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4">
-        <v>2788625</v>
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="N4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O4" t="s">
         <v>0</v>
       </c>
-      <c r="P4" t="s">
-        <v>0</v>
+      <c r="P4" s="1">
+        <v>2538822</v>
       </c>
       <c r="Q4" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>52808171</v>
+        <v>52778382</v>
       </c>
       <c r="B5" s="2">
-        <v>45960.452361111114</v>
+        <v>45959.67696759259</v>
       </c>
       <c r="C5">
-        <v>59829408</v>
+        <v>55073470</v>
       </c>
       <c r="D5" s="2">
-        <v>46093.677152777775</v>
+        <v>46003.678194444445</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>709738605</v>
+        <v>708086759</v>
       </c>
       <c r="H5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I5">
-        <v>2793645</v>
+        <v>2788625</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
@@ -1447,10 +1499,10 @@
         <v>8</v>
       </c>
       <c r="M5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="N5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O5" t="s">
         <v>0</v>
@@ -1459,51 +1511,51 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>53702282</v>
+        <v>52808171</v>
       </c>
       <c r="B6" s="2">
-        <v>45978.671550925923</v>
+        <v>45960.452361111114</v>
       </c>
       <c r="C6">
-        <v>54614316</v>
+        <v>59829408</v>
       </c>
       <c r="D6" s="2">
-        <v>45995.632673611108</v>
+        <v>46093.677152777775</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="G6">
-        <v>778036533</v>
+        <v>709738605</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" t="s">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="I6">
+        <v>2793645</v>
       </c>
       <c r="J6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O6" t="s">
         <v>0</v>
@@ -1512,139 +1564,139 @@
         <v>0</v>
       </c>
       <c r="Q6" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>53749839</v>
+        <v>53702282</v>
       </c>
       <c r="B7" s="2">
-        <v>45979.600694444445</v>
+        <v>45978.671550925923</v>
       </c>
       <c r="C7">
-        <v>62944786</v>
+        <v>64748163</v>
       </c>
       <c r="D7" s="2">
-        <v>46150.446296296293</v>
+        <v>46184.76871527778</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>244</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>703333988</v>
+        <v>778036533</v>
       </c>
       <c r="H7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I7" t="s">
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M7" t="s">
         <v>3</v>
       </c>
       <c r="N7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O7" t="s">
         <v>0</v>
       </c>
-      <c r="P7" s="1">
-        <v>10000000</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>11</v>
+      <c r="P7" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>2720301240</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>53790357</v>
+        <v>53702282</v>
       </c>
       <c r="B8" s="2">
-        <v>45980.438298611109</v>
+        <v>45978.671550925923</v>
       </c>
       <c r="C8">
-        <v>61385261</v>
+        <v>64785970</v>
       </c>
       <c r="D8" s="2">
-        <v>46122.774224537039</v>
+        <v>46185.580925925926</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="G8">
-        <v>708336404</v>
+        <v>778036533</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="L8" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M8" t="s">
         <v>3</v>
       </c>
       <c r="N8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O8" t="s">
         <v>0</v>
       </c>
-      <c r="P8" s="1">
-        <v>4430307</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>33</v>
+      <c r="P8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>2720301240</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>53899369</v>
+        <v>53749839</v>
       </c>
       <c r="B9" s="2">
-        <v>45981.827430555553</v>
+        <v>45979.600694444445</v>
       </c>
       <c r="C9">
-        <v>55146678</v>
+        <v>62944786</v>
       </c>
       <c r="D9" s="2">
-        <v>46005.762916666667</v>
+        <v>46150.446296296293</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G9">
-        <v>707003126</v>
+        <v>703333988</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I9" t="s">
         <v>0</v>
@@ -1659,263 +1711,263 @@
         <v>6</v>
       </c>
       <c r="M9" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O9" t="s">
         <v>0</v>
       </c>
-      <c r="P9">
-        <v>0</v>
+      <c r="P9" s="1">
+        <v>10000000</v>
       </c>
       <c r="Q9" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>54449048</v>
+        <v>53790357</v>
       </c>
       <c r="B10" s="2">
-        <v>45992.706157407411</v>
+        <v>45980.438298611109</v>
       </c>
       <c r="C10">
-        <v>56341749</v>
+        <v>61385261</v>
       </c>
       <c r="D10" s="2">
-        <v>46029.685115740744</v>
+        <v>46122.774224537039</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="G10">
-        <v>708086759</v>
+        <v>708336404</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="I10" t="s">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O10" t="s">
         <v>0</v>
       </c>
-      <c r="P10" t="s">
-        <v>0</v>
+      <c r="P10" s="1">
+        <v>4430307</v>
       </c>
       <c r="Q10" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>55104019</v>
+        <v>53899369</v>
       </c>
       <c r="B11" s="2">
-        <v>46004.469606481478</v>
+        <v>45981.827430555553</v>
       </c>
       <c r="C11">
-        <v>56566265</v>
+        <v>55146678</v>
       </c>
       <c r="D11" s="2">
-        <v>46034.582673611112</v>
+        <v>46005.762916666667</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="G11">
-        <v>504033918</v>
+        <v>707003126</v>
       </c>
       <c r="H11" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O11" t="s">
         <v>0</v>
       </c>
-      <c r="P11" s="1">
-        <v>4000000</v>
+      <c r="P11">
+        <v>0</v>
       </c>
       <c r="Q11" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>55636282</v>
+        <v>54449048</v>
       </c>
       <c r="B12" s="2">
-        <v>46014.435729166667</v>
+        <v>45992.706157407411</v>
       </c>
       <c r="C12">
-        <v>57367586</v>
+        <v>56341749</v>
       </c>
       <c r="D12" s="2">
-        <v>46049.856261574074</v>
+        <v>46029.685115740744</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="G12">
-        <v>759003900</v>
+        <v>708086759</v>
       </c>
       <c r="H12" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="I12" t="s">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
         <v>5</v>
       </c>
       <c r="L12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M12" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O12" t="s">
         <v>0</v>
       </c>
-      <c r="P12" s="1">
-        <v>918681</v>
+      <c r="P12" t="s">
+        <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>55694485</v>
+        <v>55104019</v>
       </c>
       <c r="B13" s="2">
-        <v>46015.420092592591</v>
+        <v>46004.469606481478</v>
       </c>
       <c r="C13">
-        <v>56752240</v>
+        <v>56566265</v>
       </c>
       <c r="D13" s="2">
-        <v>46037.705520833333</v>
+        <v>46034.582673611112</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G13">
-        <v>749338073</v>
+        <v>504033918</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I13" t="s">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M13" t="s">
         <v>3</v>
       </c>
       <c r="N13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O13" t="s">
         <v>0</v>
       </c>
       <c r="P13" s="1">
-        <v>638462</v>
+        <v>4000000</v>
       </c>
       <c r="Q13" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>56181778</v>
+        <v>55636282</v>
       </c>
       <c r="B14" s="2">
-        <v>46027.499212962961</v>
+        <v>46014.435729166667</v>
       </c>
       <c r="C14">
-        <v>59210339</v>
+        <v>57367586</v>
       </c>
       <c r="D14" s="2">
-        <v>46083.492881944447</v>
+        <v>46049.856261574074</v>
       </c>
       <c r="E14" t="s">
         <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G14">
-        <v>585990976</v>
+        <v>759003900</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
-      </c>
-      <c r="I14">
-        <v>1765416</v>
+        <v>29</v>
+      </c>
+      <c r="I14" t="s">
+        <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -1927,172 +1979,172 @@
         <v>3</v>
       </c>
       <c r="N14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O14" t="s">
         <v>0</v>
       </c>
       <c r="P14" s="1">
-        <v>3000000</v>
+        <v>918681</v>
       </c>
       <c r="Q14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>56603495</v>
+        <v>55694485</v>
       </c>
       <c r="B15" s="2">
-        <v>46035.408518518518</v>
+        <v>46015.420092592591</v>
       </c>
       <c r="C15">
-        <v>60907737</v>
+        <v>56752240</v>
       </c>
       <c r="D15" s="2">
-        <v>46113.726909722223</v>
+        <v>46037.705520833333</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="G15">
-        <v>707003126</v>
+        <v>749338073</v>
       </c>
       <c r="H15" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M15" t="s">
         <v>3</v>
       </c>
       <c r="N15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O15" t="s">
         <v>0</v>
       </c>
       <c r="P15" s="1">
-        <v>7103410</v>
+        <v>638462</v>
       </c>
       <c r="Q15" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>56618123</v>
+        <v>56181778</v>
       </c>
       <c r="B16" s="2">
-        <v>46035.520821759259</v>
+        <v>46027.499212962961</v>
       </c>
       <c r="C16">
-        <v>63588969</v>
+        <v>59210339</v>
       </c>
       <c r="D16" s="2">
-        <v>46162.539305555554</v>
+        <v>46083.492881944447</v>
       </c>
       <c r="E16" t="s">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G16">
-        <v>504041812</v>
+        <v>585990976</v>
       </c>
       <c r="H16" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="I16">
-        <v>1775236</v>
+        <v>1765416</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M16" t="s">
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O16" t="s">
         <v>0</v>
       </c>
       <c r="P16" s="1">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="Q16" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>56675050</v>
+        <v>56603495</v>
       </c>
       <c r="B17" s="2">
-        <v>46036.516423611109</v>
+        <v>46035.408518518518</v>
       </c>
       <c r="C17">
-        <v>63302732</v>
+        <v>60907737</v>
       </c>
       <c r="D17" s="2">
-        <v>46157.396793981483</v>
+        <v>46113.726909722223</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>175</v>
+        <v>28</v>
       </c>
       <c r="G17">
-        <v>748512613</v>
+        <v>707003126</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I17" t="s">
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
       </c>
       <c r="L17" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M17" t="s">
         <v>3</v>
       </c>
       <c r="N17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O17" t="s">
         <v>0</v>
       </c>
       <c r="P17" s="1">
-        <v>4362401</v>
+        <v>7103410</v>
       </c>
       <c r="Q17" t="s">
         <v>19</v>
@@ -2100,81 +2152,81 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>56970346</v>
+        <v>56618123</v>
       </c>
       <c r="B18" s="2">
-        <v>46042.557280092595</v>
+        <v>46035.520821759259</v>
       </c>
       <c r="C18">
-        <v>59242054</v>
+        <v>63588969</v>
       </c>
       <c r="D18" s="2">
-        <v>46083.719525462962</v>
+        <v>46162.539305555554</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G18">
-        <v>708667658</v>
+        <v>504041812</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" t="s">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="I18">
+        <v>1775236</v>
       </c>
       <c r="J18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
       </c>
       <c r="L18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M18" t="s">
         <v>3</v>
       </c>
       <c r="N18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O18" t="s">
         <v>0</v>
       </c>
       <c r="P18" s="1">
-        <v>2871414</v>
+        <v>2000000</v>
       </c>
       <c r="Q18" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>57398181</v>
+        <v>56675050</v>
       </c>
       <c r="B19" s="2">
-        <v>46050.584374999999</v>
+        <v>46036.516423611109</v>
       </c>
       <c r="C19">
-        <v>60344342</v>
+        <v>63302732</v>
       </c>
       <c r="D19" s="2">
-        <v>46104.528900462959</v>
+        <v>46157.396793981483</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="G19">
-        <v>720631500</v>
+        <v>748512613</v>
       </c>
       <c r="H19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s">
         <v>0</v>
@@ -2192,42 +2244,42 @@
         <v>3</v>
       </c>
       <c r="N19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O19" t="s">
         <v>0</v>
       </c>
       <c r="P19" s="1">
-        <v>4406780</v>
+        <v>4362401</v>
       </c>
       <c r="Q19" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>58055656</v>
+        <v>56970346</v>
       </c>
       <c r="B20" s="2">
-        <v>46062.760023148148</v>
+        <v>46042.557280092595</v>
       </c>
       <c r="C20">
-        <v>61269237</v>
+        <v>59242054</v>
       </c>
       <c r="D20" s="2">
-        <v>46121.376689814817</v>
+        <v>46083.719525462962</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G20">
-        <v>758224257</v>
+        <v>708667658</v>
       </c>
       <c r="H20" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="I20" t="s">
         <v>0</v>
@@ -2245,95 +2297,95 @@
         <v>3</v>
       </c>
       <c r="N20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O20" t="s">
         <v>0</v>
       </c>
       <c r="P20" s="1">
-        <v>1800000</v>
+        <v>2871414</v>
       </c>
       <c r="Q20" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>58166885</v>
+        <v>57398181</v>
       </c>
       <c r="B21" s="2">
-        <v>46064.649965277778</v>
+        <v>46050.584374999999</v>
       </c>
       <c r="C21">
-        <v>63079695</v>
+        <v>60344342</v>
       </c>
       <c r="D21" s="2">
-        <v>46153.448425925926</v>
+        <v>46104.528900462959</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G21">
-        <v>504041812</v>
+        <v>720631500</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
       </c>
       <c r="L21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M21" t="s">
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O21" t="s">
         <v>0</v>
       </c>
       <c r="P21" s="1">
-        <v>2000000</v>
+        <v>4406780</v>
       </c>
       <c r="Q21" t="s">
-        <v>165</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>58626822</v>
+        <v>58055656</v>
       </c>
       <c r="B22" s="2">
-        <v>46072.810324074075</v>
+        <v>46062.760023148148</v>
       </c>
       <c r="C22">
-        <v>59811821</v>
+        <v>61269237</v>
       </c>
       <c r="D22" s="2">
-        <v>46093.543773148151</v>
+        <v>46121.376689814817</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G22">
-        <v>709574114</v>
+        <v>758224257</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="I22" t="s">
         <v>0</v>
@@ -2351,60 +2403,60 @@
         <v>3</v>
       </c>
       <c r="N22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O22" t="s">
         <v>0</v>
       </c>
       <c r="P22" s="1">
-        <v>445307</v>
+        <v>1800000</v>
       </c>
       <c r="Q22" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>58635645</v>
+        <v>58093827</v>
       </c>
       <c r="B23" s="2">
-        <v>46073.372395833336</v>
+        <v>46063.583402777775</v>
       </c>
       <c r="C23">
-        <v>61982536</v>
+        <v>63599943</v>
       </c>
       <c r="D23" s="2">
-        <v>46133.49863425926</v>
+        <v>46162.626145833332</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="F23" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="G23">
-        <v>759250737</v>
+        <v>708086759</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
+        <v>245</v>
       </c>
       <c r="I23" t="s">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K23" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L23" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M23" t="s">
         <v>7</v>
       </c>
       <c r="N23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O23" t="s">
         <v>0</v>
@@ -2413,33 +2465,33 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>121</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>58635674</v>
+        <v>58166885</v>
       </c>
       <c r="B24" s="2">
-        <v>46073.372488425928</v>
+        <v>46064.649965277778</v>
       </c>
       <c r="C24">
-        <v>61980847</v>
+        <v>63079695</v>
       </c>
       <c r="D24" s="2">
-        <v>46133.487384259257</v>
+        <v>46153.448425925926</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G24">
-        <v>759250737</v>
+        <v>504041812</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="I24" t="s">
         <v>0</v>
@@ -2454,116 +2506,116 @@
         <v>8</v>
       </c>
       <c r="M24" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O24" t="s">
         <v>0</v>
       </c>
       <c r="P24" s="1">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="Q24" t="s">
-        <v>57</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>58868849</v>
+        <v>58626822</v>
       </c>
       <c r="B25" s="2">
-        <v>46077.501203703701</v>
+        <v>46072.810324074075</v>
       </c>
       <c r="C25">
-        <v>62104932</v>
+        <v>59811821</v>
       </c>
       <c r="D25" s="2">
-        <v>46135.396608796298</v>
+        <v>46093.543773148151</v>
       </c>
       <c r="E25" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G25">
-        <v>748377555</v>
+        <v>709574114</v>
       </c>
       <c r="H25" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I25" t="s">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M25" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O25" t="s">
         <v>0</v>
       </c>
-      <c r="P25" t="s">
-        <v>0</v>
+      <c r="P25" s="1">
+        <v>445307</v>
       </c>
       <c r="Q25" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>58925987</v>
+        <v>58635645</v>
       </c>
       <c r="B26" s="2">
-        <v>46078.434814814813</v>
+        <v>46073.372395833336</v>
       </c>
       <c r="C26">
-        <v>60163873</v>
+        <v>61982536</v>
       </c>
       <c r="D26" s="2">
-        <v>46100.423101851855</v>
+        <v>46133.49863425926</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G26">
-        <v>708641473</v>
+        <v>759250737</v>
       </c>
       <c r="H26" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="I26" t="s">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K26" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L26" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M26" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O26" t="s">
         <v>0</v>
@@ -2572,98 +2624,98 @@
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>58959238</v>
+        <v>58635674</v>
       </c>
       <c r="B27" s="2">
-        <v>46078.665532407409</v>
+        <v>46073.372488425928</v>
       </c>
       <c r="C27">
-        <v>60163938</v>
+        <v>61980847</v>
       </c>
       <c r="D27" s="2">
-        <v>46100.423773148148</v>
+        <v>46133.487384259257</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F27" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G27">
-        <v>708641473</v>
+        <v>759250737</v>
       </c>
       <c r="H27" t="s">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="I27" t="s">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
       </c>
       <c r="L27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M27" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O27" t="s">
         <v>0</v>
       </c>
       <c r="P27" s="1">
-        <v>850000</v>
+        <v>500000</v>
       </c>
       <c r="Q27" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>59466514</v>
+        <v>58868849</v>
       </c>
       <c r="B28" s="2">
-        <v>46087.436643518522</v>
+        <v>46077.501203703701</v>
       </c>
       <c r="C28">
-        <v>64672988</v>
+        <v>62104932</v>
       </c>
       <c r="D28" s="2">
-        <v>46183.651747685188</v>
+        <v>46135.396608796298</v>
       </c>
       <c r="E28" t="s">
-        <v>223</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>166</v>
+        <v>98</v>
       </c>
       <c r="G28">
-        <v>141679210</v>
+        <v>748377555</v>
       </c>
       <c r="H28" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="I28" t="s">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L28" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M28" t="s">
         <v>7</v>
@@ -2674,161 +2726,161 @@
       <c r="O28" t="s">
         <v>0</v>
       </c>
-      <c r="P28" s="1">
-        <v>3213390</v>
+      <c r="P28" t="s">
+        <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>59537755</v>
+        <v>58925987</v>
       </c>
       <c r="B29" s="2">
-        <v>46088.586631944447</v>
+        <v>46078.434814814813</v>
       </c>
       <c r="C29">
-        <v>61591841</v>
+        <v>60163873</v>
       </c>
       <c r="D29" s="2">
-        <v>46127.35796296296</v>
+        <v>46100.423101851855</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="G29">
-        <v>556331131</v>
+        <v>708641473</v>
       </c>
       <c r="H29" t="s">
-        <v>122</v>
-      </c>
-      <c r="I29">
-        <v>1843236</v>
+        <v>101</v>
+      </c>
+      <c r="I29" t="s">
+        <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M29" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O29" t="s">
         <v>0</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="s">
         <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>59606122</v>
+        <v>58959238</v>
       </c>
       <c r="B30" s="2">
-        <v>46090.447604166664</v>
+        <v>46078.665532407409</v>
       </c>
       <c r="C30">
-        <v>61897702</v>
+        <v>60163938</v>
       </c>
       <c r="D30" s="2">
-        <v>46132.349363425928</v>
+        <v>46100.423773148148</v>
       </c>
       <c r="E30" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="G30">
-        <v>708454305</v>
+        <v>708641473</v>
       </c>
       <c r="H30" t="s">
-        <v>137</v>
-      </c>
-      <c r="I30">
-        <v>1842206</v>
+        <v>102</v>
+      </c>
+      <c r="I30" t="s">
+        <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K30" t="s">
-        <v>113</v>
+        <v>5</v>
       </c>
       <c r="L30" t="s">
         <v>6</v>
       </c>
       <c r="M30" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O30" t="s">
         <v>0</v>
       </c>
-      <c r="P30">
-        <v>0</v>
+      <c r="P30" s="1">
+        <v>850000</v>
       </c>
       <c r="Q30" t="s">
-        <v>138</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>59615935</v>
+        <v>59537755</v>
       </c>
       <c r="B31" s="2">
-        <v>46090.512303240743</v>
+        <v>46088.586631944447</v>
       </c>
       <c r="C31">
-        <v>60393405</v>
+        <v>61591841</v>
       </c>
       <c r="D31" s="2">
-        <v>46105.432800925926</v>
+        <v>46127.35796296296</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F31" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="G31">
-        <v>767081456</v>
+        <v>556331131</v>
       </c>
       <c r="H31" t="s">
-        <v>116</v>
-      </c>
-      <c r="I31" t="s">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="I31">
+        <v>1843236</v>
       </c>
       <c r="J31" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K31" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="L31" t="s">
         <v>6</v>
       </c>
       <c r="M31" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O31" t="s">
         <v>0</v>
@@ -2837,42 +2889,42 @@
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>59894743</v>
+        <v>59606122</v>
       </c>
       <c r="B32" s="2">
-        <v>46094.687673611108</v>
+        <v>46090.447604166664</v>
       </c>
       <c r="C32">
-        <v>64675881</v>
+        <v>61897702</v>
       </c>
       <c r="D32" s="2">
-        <v>46183.674537037034</v>
+        <v>46132.349363425928</v>
       </c>
       <c r="E32" t="s">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G32">
-        <v>759668146</v>
+        <v>708454305</v>
       </c>
       <c r="H32" t="s">
-        <v>36</v>
-      </c>
-      <c r="I32" t="s">
-        <v>0</v>
+        <v>136</v>
+      </c>
+      <c r="I32">
+        <v>1842206</v>
       </c>
       <c r="J32" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K32" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="L32" t="s">
         <v>6</v>
@@ -2881,42 +2933,42 @@
         <v>7</v>
       </c>
       <c r="N32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O32" t="s">
         <v>0</v>
       </c>
-      <c r="P32" t="s">
+      <c r="P32">
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>60748674</v>
+        <v>59615935</v>
       </c>
       <c r="B33" s="2">
-        <v>46111.511504629627</v>
+        <v>46090.512303240743</v>
       </c>
       <c r="C33">
-        <v>62475433</v>
+        <v>60393405</v>
       </c>
       <c r="D33" s="2">
-        <v>46141.624513888892</v>
+        <v>46105.432800925926</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G33">
-        <v>767791237</v>
+        <v>767081456</v>
       </c>
       <c r="H33" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I33" t="s">
         <v>0</v>
@@ -2931,10 +2983,10 @@
         <v>6</v>
       </c>
       <c r="M33" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O33" t="s">
         <v>0</v>
@@ -2943,104 +2995,104 @@
         <v>0</v>
       </c>
       <c r="Q33" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>60972166</v>
+        <v>59894743</v>
       </c>
       <c r="B34" s="2">
-        <v>46114.708020833335</v>
+        <v>46094.687673611108</v>
       </c>
       <c r="C34">
-        <v>62949578</v>
+        <v>64800213</v>
       </c>
       <c r="D34" s="2">
-        <v>46150.482407407406</v>
+        <v>46185.685624999998</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="F34" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G34">
-        <v>160128782</v>
+        <v>759668146</v>
       </c>
       <c r="H34" t="s">
-        <v>124</v>
-      </c>
-      <c r="I34" t="s">
-        <v>0</v>
+        <v>248</v>
+      </c>
+      <c r="I34">
+        <v>1849226</v>
       </c>
       <c r="J34" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K34" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M34" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O34" t="s">
         <v>0</v>
       </c>
-      <c r="P34" s="1">
-        <v>800000</v>
+      <c r="P34" t="s">
+        <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>30</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>61239047</v>
+        <v>60748674</v>
       </c>
       <c r="B35" s="2">
-        <v>46120.622071759259</v>
+        <v>46111.511504629627</v>
       </c>
       <c r="C35">
-        <v>64373945</v>
+        <v>62475433</v>
       </c>
       <c r="D35" s="2">
-        <v>46178.391516203701</v>
+        <v>46141.624513888892</v>
       </c>
       <c r="E35" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G35">
-        <v>103381121</v>
+        <v>767791237</v>
       </c>
       <c r="H35" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="I35" t="s">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K35" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L35" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M35" t="s">
         <v>7</v>
       </c>
       <c r="N35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O35" t="s">
         <v>0</v>
@@ -3049,86 +3101,86 @@
         <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>61240327</v>
+        <v>60972166</v>
       </c>
       <c r="B36" s="2">
-        <v>46120.631747685184</v>
+        <v>46114.708020833335</v>
       </c>
       <c r="C36">
-        <v>63643159</v>
+        <v>62949578</v>
       </c>
       <c r="D36" s="2">
-        <v>46163.479432870372</v>
+        <v>46150.482407407406</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G36">
-        <v>103381121</v>
+        <v>160128782</v>
       </c>
       <c r="H36" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I36" t="s">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="K36" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L36" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M36" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O36" t="s">
         <v>0</v>
       </c>
-      <c r="P36">
-        <v>0</v>
+      <c r="P36" s="1">
+        <v>800000</v>
       </c>
       <c r="Q36" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>61242033</v>
+        <v>61239047</v>
       </c>
       <c r="B37" s="2">
-        <v>46120.643912037034</v>
+        <v>46120.622071759259</v>
       </c>
       <c r="C37">
-        <v>62945857</v>
+        <v>64795668</v>
       </c>
       <c r="D37" s="2">
-        <v>46150.456064814818</v>
+        <v>46185.651990740742</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F37" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G37">
-        <v>747636152</v>
+        <v>103381121</v>
       </c>
       <c r="H37" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="I37" t="s">
         <v>0</v>
@@ -3137,7 +3189,7 @@
         <v>67</v>
       </c>
       <c r="K37" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L37" t="s">
         <v>2</v>
@@ -3146,7 +3198,7 @@
         <v>7</v>
       </c>
       <c r="N37" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O37" t="s">
         <v>0</v>
@@ -3155,33 +3207,33 @@
         <v>0</v>
       </c>
       <c r="Q37" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>61244524</v>
+        <v>61240327</v>
       </c>
       <c r="B38" s="2">
-        <v>46120.66065972222</v>
+        <v>46120.631747685184</v>
       </c>
       <c r="C38">
-        <v>62308856</v>
+        <v>63643159</v>
       </c>
       <c r="D38" s="2">
-        <v>46139.393194444441</v>
+        <v>46163.479432870372</v>
       </c>
       <c r="E38" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G38">
-        <v>757818829</v>
+        <v>103381121</v>
       </c>
       <c r="H38" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="I38" t="s">
         <v>0</v>
@@ -3190,7 +3242,7 @@
         <v>67</v>
       </c>
       <c r="K38" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L38" t="s">
         <v>2</v>
@@ -3199,42 +3251,42 @@
         <v>7</v>
       </c>
       <c r="N38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O38" t="s">
         <v>0</v>
       </c>
-      <c r="P38" t="s">
+      <c r="P38">
         <v>0</v>
       </c>
       <c r="Q38" t="s">
-        <v>140</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>61248751</v>
+        <v>61242033</v>
       </c>
       <c r="B39" s="2">
-        <v>46120.692800925928</v>
+        <v>46120.643912037034</v>
       </c>
       <c r="C39">
-        <v>64627389</v>
+        <v>62945857</v>
       </c>
       <c r="D39" s="2">
-        <v>46182.89912037037</v>
+        <v>46150.456064814818</v>
       </c>
       <c r="E39" t="s">
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G39">
         <v>747636152</v>
       </c>
       <c r="H39" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s">
         <v>0</v>
@@ -3243,7 +3295,7 @@
         <v>67</v>
       </c>
       <c r="K39" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L39" t="s">
         <v>2</v>
@@ -3261,139 +3313,139 @@
         <v>0</v>
       </c>
       <c r="Q39" t="s">
-        <v>188</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>61255901</v>
+        <v>61244524</v>
       </c>
       <c r="B40" s="2">
-        <v>46120.75712962963</v>
+        <v>46120.66065972222</v>
       </c>
       <c r="C40">
-        <v>62951388</v>
+        <v>64793029</v>
       </c>
       <c r="D40" s="2">
-        <v>46150.494675925926</v>
+        <v>46185.633090277777</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="F40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G40">
         <v>757818829</v>
       </c>
       <c r="H40" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="I40" t="s">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="K40" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L40" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M40" t="s">
         <v>7</v>
       </c>
       <c r="N40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O40" t="s">
         <v>0</v>
       </c>
-      <c r="P40">
+      <c r="P40" t="s">
         <v>0</v>
       </c>
       <c r="Q40" t="s">
-        <v>73</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>61315991</v>
+        <v>61248751</v>
       </c>
       <c r="B41" s="2">
-        <v>46121.743379629632</v>
+        <v>46120.692800925928</v>
       </c>
       <c r="C41">
-        <v>63689089</v>
+        <v>64698839</v>
       </c>
       <c r="D41" s="2">
-        <v>46164.351643518516</v>
+        <v>46184.382604166669</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G41">
-        <v>778495680</v>
+        <v>747636152</v>
       </c>
       <c r="H41" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="I41" t="s">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="K41" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L41" t="s">
         <v>2</v>
       </c>
       <c r="M41" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O41" t="s">
         <v>0</v>
       </c>
-      <c r="P41" t="s">
+      <c r="P41">
         <v>0</v>
       </c>
       <c r="Q41" t="s">
-        <v>101</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>61336527</v>
+        <v>61255901</v>
       </c>
       <c r="B42" s="2">
-        <v>46122.368761574071</v>
+        <v>46120.75712962963</v>
       </c>
       <c r="C42">
-        <v>63643262</v>
+        <v>62951388</v>
       </c>
       <c r="D42" s="2">
-        <v>46163.480023148149</v>
+        <v>46150.494675925926</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G42">
-        <v>778495680</v>
+        <v>757818829</v>
       </c>
       <c r="H42" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="I42" t="s">
         <v>0</v>
@@ -3405,101 +3457,101 @@
         <v>5</v>
       </c>
       <c r="L42" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M42" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O42" t="s">
         <v>0</v>
       </c>
-      <c r="P42" s="1">
-        <v>1679940</v>
+      <c r="P42">
+        <v>0</v>
       </c>
       <c r="Q42" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>61481328</v>
+        <v>61315991</v>
       </c>
       <c r="B43" s="2">
-        <v>46125.483310185184</v>
+        <v>46121.743379629632</v>
       </c>
       <c r="C43">
-        <v>62173555</v>
+        <v>63689089</v>
       </c>
       <c r="D43" s="2">
-        <v>46136.44263888889</v>
+        <v>46164.351643518516</v>
       </c>
       <c r="E43" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G43">
-        <v>708448800</v>
+        <v>778495680</v>
       </c>
       <c r="H43" t="s">
-        <v>150</v>
-      </c>
-      <c r="I43">
-        <v>1891736</v>
+        <v>129</v>
+      </c>
+      <c r="I43" t="s">
+        <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L43" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M43" t="s">
         <v>3</v>
       </c>
       <c r="N43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O43" t="s">
         <v>0</v>
       </c>
-      <c r="P43" s="1">
-        <v>500000</v>
+      <c r="P43" t="s">
+        <v>0</v>
       </c>
       <c r="Q43" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>61504448</v>
+        <v>61336527</v>
       </c>
       <c r="B44" s="2">
-        <v>46125.648935185185</v>
+        <v>46122.368761574071</v>
       </c>
       <c r="C44">
-        <v>62115179</v>
+        <v>63643262</v>
       </c>
       <c r="D44" s="2">
-        <v>46135.481111111112</v>
+        <v>46163.480023148149</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G44">
-        <v>707234610</v>
+        <v>778495680</v>
       </c>
       <c r="H44" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="I44" t="s">
         <v>0</v>
@@ -3517,148 +3569,148 @@
         <v>3</v>
       </c>
       <c r="N44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O44" t="s">
         <v>0</v>
       </c>
       <c r="P44" s="1">
-        <v>3070672</v>
+        <v>1679940</v>
       </c>
       <c r="Q44" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>61509953</v>
+        <v>61481328</v>
       </c>
       <c r="B45" s="2">
-        <v>46125.694004629629</v>
+        <v>46125.483310185184</v>
       </c>
       <c r="C45">
-        <v>62751418</v>
+        <v>62173555</v>
       </c>
       <c r="D45" s="2">
-        <v>46147.490636574075</v>
+        <v>46136.44263888889</v>
       </c>
       <c r="E45" t="s">
         <v>87</v>
       </c>
       <c r="F45" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="G45">
-        <v>759379440</v>
+        <v>708448800</v>
       </c>
       <c r="H45" t="s">
-        <v>144</v>
-      </c>
-      <c r="I45" t="s">
-        <v>0</v>
+        <v>148</v>
+      </c>
+      <c r="I45">
+        <v>1891736</v>
       </c>
       <c r="J45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K45" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L45" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M45" t="s">
         <v>3</v>
       </c>
       <c r="N45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O45" t="s">
         <v>0</v>
       </c>
-      <c r="P45" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>2732780110</v>
+      <c r="P45" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>61560663</v>
+        <v>61504448</v>
       </c>
       <c r="B46" s="2">
-        <v>46126.615729166668</v>
+        <v>46125.648935185185</v>
       </c>
       <c r="C46">
-        <v>62946623</v>
+        <v>62115179</v>
       </c>
       <c r="D46" s="2">
-        <v>46150.461550925924</v>
+        <v>46135.481111111112</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G46">
-        <v>707984429</v>
+        <v>707234610</v>
       </c>
       <c r="H46" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="I46" t="s">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
       </c>
       <c r="L46" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M46" t="s">
         <v>3</v>
       </c>
       <c r="N46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O46" t="s">
         <v>0</v>
       </c>
       <c r="P46" s="1">
-        <v>2984038</v>
+        <v>3070672</v>
       </c>
       <c r="Q46" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>61608637</v>
+        <v>61509953</v>
       </c>
       <c r="B47" s="2">
-        <v>46127.491550925923</v>
+        <v>46125.694004629629</v>
       </c>
       <c r="C47">
-        <v>61677257</v>
+        <v>62751418</v>
       </c>
       <c r="D47" s="2">
-        <v>46128.483958333331</v>
+        <v>46147.490636574075</v>
       </c>
       <c r="E47" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="F47" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G47">
-        <v>702455701</v>
+        <v>759379440</v>
       </c>
       <c r="H47" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="I47" t="s">
         <v>0</v>
@@ -3676,7 +3728,7 @@
         <v>3</v>
       </c>
       <c r="N47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O47" t="s">
         <v>0</v>
@@ -3684,34 +3736,34 @@
       <c r="P47" t="s">
         <v>0</v>
       </c>
-      <c r="Q47" t="s">
-        <v>111</v>
+      <c r="Q47">
+        <v>2732780110</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>61644382</v>
+        <v>61560663</v>
       </c>
       <c r="B48" s="2">
-        <v>46127.754131944443</v>
+        <v>46126.615729166668</v>
       </c>
       <c r="C48">
-        <v>61977733</v>
+        <v>62946623</v>
       </c>
       <c r="D48" s="2">
-        <v>46133.466458333336</v>
+        <v>46150.461550925924</v>
       </c>
       <c r="E48" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="G48">
-        <v>759250737</v>
+        <v>707984429</v>
       </c>
       <c r="H48" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="I48" t="s">
         <v>0</v>
@@ -3720,7 +3772,7 @@
         <v>17</v>
       </c>
       <c r="K48" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L48" t="s">
         <v>8</v>
@@ -3729,95 +3781,95 @@
         <v>3</v>
       </c>
       <c r="N48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O48" t="s">
         <v>0</v>
       </c>
       <c r="P48" s="1">
-        <v>1680307</v>
+        <v>2984038</v>
       </c>
       <c r="Q48" t="s">
-        <v>147</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>61946442</v>
+        <v>61608637</v>
       </c>
       <c r="B49" s="2">
-        <v>46132.704247685186</v>
+        <v>46127.491550925923</v>
       </c>
       <c r="C49">
-        <v>62946744</v>
+        <v>61677257</v>
       </c>
       <c r="D49" s="2">
-        <v>46150.462650462963</v>
+        <v>46128.483958333331</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F49" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G49">
-        <v>504041812</v>
+        <v>702455701</v>
       </c>
       <c r="H49" t="s">
-        <v>153</v>
+        <v>36</v>
       </c>
       <c r="I49" t="s">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L49" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M49" t="s">
         <v>3</v>
       </c>
       <c r="N49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O49" t="s">
         <v>0</v>
       </c>
-      <c r="P49" s="1">
-        <v>1000000</v>
+      <c r="P49" t="s">
+        <v>0</v>
       </c>
       <c r="Q49" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>61972088</v>
+        <v>61644382</v>
       </c>
       <c r="B50" s="2">
-        <v>46133.422569444447</v>
+        <v>46127.754131944443</v>
       </c>
       <c r="C50">
-        <v>64146321</v>
+        <v>61977733</v>
       </c>
       <c r="D50" s="2">
-        <v>46174.477534722224</v>
+        <v>46133.466458333336</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F50" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="G50">
-        <v>504041812</v>
+        <v>759250737</v>
       </c>
       <c r="H50" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I50" t="s">
         <v>0</v>
@@ -3826,69 +3878,69 @@
         <v>17</v>
       </c>
       <c r="K50" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L50" t="s">
         <v>8</v>
       </c>
       <c r="M50" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O50" t="s">
         <v>0</v>
       </c>
-      <c r="P50" t="s">
-        <v>0</v>
+      <c r="P50" s="1">
+        <v>1680307</v>
       </c>
       <c r="Q50" t="s">
-        <v>23</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>61972108</v>
+        <v>61946442</v>
       </c>
       <c r="B51" s="2">
-        <v>46133.422662037039</v>
+        <v>46132.704247685186</v>
       </c>
       <c r="C51">
-        <v>62946845</v>
+        <v>62946744</v>
       </c>
       <c r="D51" s="2">
-        <v>46150.463449074072</v>
+        <v>46150.462650462963</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G51">
         <v>504041812</v>
       </c>
       <c r="H51" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I51" t="s">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M51" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O51" t="s">
         <v>0</v>
@@ -3897,33 +3949,33 @@
         <v>1000000</v>
       </c>
       <c r="Q51" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>62420329</v>
+        <v>61972088</v>
       </c>
       <c r="B52" s="2">
-        <v>46140.709513888891</v>
+        <v>46133.422569444447</v>
       </c>
       <c r="C52">
-        <v>64675456</v>
+        <v>64146321</v>
       </c>
       <c r="D52" s="2">
-        <v>46183.671956018516</v>
+        <v>46174.477534722224</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G52">
-        <v>777621987</v>
+        <v>504041812</v>
       </c>
       <c r="H52" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="I52" t="s">
         <v>0</v>
@@ -3938,163 +3990,166 @@
         <v>8</v>
       </c>
       <c r="M52" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O52" t="s">
         <v>0</v>
       </c>
-      <c r="P52" s="1">
-        <v>1500000</v>
+      <c r="P52" t="s">
+        <v>0</v>
       </c>
       <c r="Q52" t="s">
-        <v>168</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>62497009</v>
+        <v>61972108</v>
       </c>
       <c r="B53" s="2">
-        <v>46141.808842592596</v>
+        <v>46133.422662037039</v>
       </c>
       <c r="C53">
-        <v>63458983</v>
+        <v>62946845</v>
       </c>
       <c r="D53" s="2">
-        <v>46160.501875000002</v>
+        <v>46150.463449074072</v>
       </c>
       <c r="E53" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G53">
-        <v>702495660</v>
+        <v>504041812</v>
       </c>
       <c r="H53" t="s">
-        <v>36</v>
+        <v>151</v>
       </c>
       <c r="I53" t="s">
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K53" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L53" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M53" t="s">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="N53" t="s">
+        <v>107</v>
       </c>
       <c r="O53" t="s">
         <v>0</v>
       </c>
-      <c r="P53" t="s">
-        <v>0</v>
+      <c r="P53" s="1">
+        <v>1000000</v>
       </c>
       <c r="Q53" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>62551370</v>
+        <v>62420329</v>
       </c>
       <c r="B54" s="2">
-        <v>46142.717349537037</v>
+        <v>46140.709513888891</v>
       </c>
       <c r="C54">
-        <v>63134483</v>
+        <v>64675456</v>
       </c>
       <c r="D54" s="2">
-        <v>46154.380196759259</v>
+        <v>46183.671956018516</v>
       </c>
       <c r="E54" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G54">
-        <v>576382850</v>
+        <v>777621987</v>
       </c>
       <c r="H54" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="I54" t="s">
         <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K54" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L54" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M54" t="s">
         <v>3</v>
       </c>
+      <c r="N54" t="s">
+        <v>107</v>
+      </c>
       <c r="O54" t="s">
         <v>0</v>
       </c>
-      <c r="P54" t="s">
-        <v>0</v>
+      <c r="P54" s="1">
+        <v>1500000</v>
       </c>
       <c r="Q54" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>62672227</v>
+        <v>62497009</v>
       </c>
       <c r="B55" s="2">
-        <v>46146.403935185182</v>
+        <v>46141.808842592596</v>
       </c>
       <c r="C55">
-        <v>63331081</v>
+        <v>63458983</v>
       </c>
       <c r="D55" s="2">
-        <v>46157.619120370371</v>
+        <v>46160.501875000002</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F55" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G55">
-        <v>707169322</v>
+        <v>702495660</v>
       </c>
       <c r="H55" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="I55" t="s">
         <v>0</v>
       </c>
       <c r="J55" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K55" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L55" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M55" t="s">
-        <v>7</v>
-      </c>
-      <c r="N55" t="s">
-        <v>108</v>
+        <v>3</v>
       </c>
       <c r="O55" t="s">
         <v>0</v>
@@ -4103,42 +4158,42 @@
         <v>0</v>
       </c>
       <c r="Q55" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>62680657</v>
+        <v>62551370</v>
       </c>
       <c r="B56" s="2">
-        <v>46146.475763888891</v>
+        <v>46142.717349537037</v>
       </c>
       <c r="C56">
-        <v>63485029</v>
+        <v>63134483</v>
       </c>
       <c r="D56" s="2">
-        <v>46160.702488425923</v>
+        <v>46154.380196759259</v>
       </c>
       <c r="E56" t="s">
         <v>22</v>
       </c>
       <c r="F56" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G56">
-        <v>778096389</v>
+        <v>576382850</v>
       </c>
       <c r="H56" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I56" t="s">
         <v>0</v>
       </c>
       <c r="J56" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L56" t="s">
         <v>2</v>
@@ -4152,52 +4207,52 @@
       <c r="P56" t="s">
         <v>0</v>
       </c>
-      <c r="Q56">
-        <v>2722560110</v>
+      <c r="Q56" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>62722805</v>
+        <v>62672227</v>
       </c>
       <c r="B57" s="2">
-        <v>46146.81181712963</v>
+        <v>46146.403935185182</v>
       </c>
       <c r="C57">
-        <v>64261496</v>
+        <v>63331081</v>
       </c>
       <c r="D57" s="2">
-        <v>46176.409166666665</v>
+        <v>46157.619120370371</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G57">
-        <v>708131488</v>
+        <v>707169322</v>
       </c>
       <c r="H57" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I57" t="s">
         <v>0</v>
       </c>
       <c r="J57" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K57" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L57" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M57" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O57" t="s">
         <v>0</v>
@@ -4206,39 +4261,39 @@
         <v>0</v>
       </c>
       <c r="Q57" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>62760027</v>
+        <v>62680657</v>
       </c>
       <c r="B58" s="2">
-        <v>46147.546493055554</v>
+        <v>46146.475763888891</v>
       </c>
       <c r="C58">
-        <v>64614114</v>
+        <v>63485029</v>
       </c>
       <c r="D58" s="2">
-        <v>46182.695092592592</v>
+        <v>46160.702488425923</v>
       </c>
       <c r="E58" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="F58" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="G58">
-        <v>777699799</v>
+        <v>778096389</v>
       </c>
       <c r="H58" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="I58" t="s">
         <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="K58" t="s">
         <v>26</v>
@@ -4249,9 +4304,6 @@
       <c r="M58" t="s">
         <v>3</v>
       </c>
-      <c r="N58" t="s">
-        <v>107</v>
-      </c>
       <c r="O58" t="s">
         <v>0</v>
       </c>
@@ -4259,51 +4311,51 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>2721710915</v>
+        <v>2722560110</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>62768013</v>
+        <v>62722805</v>
       </c>
       <c r="B59" s="2">
-        <v>46147.609988425924</v>
+        <v>46146.81181712963</v>
       </c>
       <c r="C59">
-        <v>62871386</v>
+        <v>64261496</v>
       </c>
       <c r="D59" s="2">
-        <v>46149.364837962959</v>
+        <v>46176.409166666665</v>
       </c>
       <c r="E59" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G59">
-        <v>143270405</v>
+        <v>708131488</v>
       </c>
       <c r="H59" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="I59" t="s">
         <v>0</v>
       </c>
       <c r="J59" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s">
         <v>1</v>
       </c>
       <c r="L59" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M59" t="s">
         <v>3</v>
       </c>
       <c r="N59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O59" t="s">
         <v>0</v>
@@ -4312,86 +4364,86 @@
         <v>0</v>
       </c>
       <c r="Q59" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>63025600</v>
+        <v>62760027</v>
       </c>
       <c r="B60" s="2">
-        <v>46151.740983796299</v>
+        <v>46147.546493055554</v>
       </c>
       <c r="C60">
-        <v>63981861</v>
+        <v>64614114</v>
       </c>
       <c r="D60" s="2">
-        <v>46170.692743055559</v>
+        <v>46182.695092592592</v>
       </c>
       <c r="E60" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F60" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="G60">
-        <v>758237461</v>
+        <v>777699799</v>
       </c>
       <c r="H60" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="I60" t="s">
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K60" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M60" t="s">
         <v>3</v>
       </c>
       <c r="N60" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O60" t="s">
         <v>0</v>
       </c>
-      <c r="P60" s="1">
-        <v>850000</v>
+      <c r="P60" t="s">
+        <v>0</v>
       </c>
       <c r="Q60" t="s">
-        <v>190</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>63168095</v>
+        <v>62768013</v>
       </c>
       <c r="B61" s="2">
-        <v>46154.647604166668</v>
+        <v>46147.609988425924</v>
       </c>
       <c r="C61">
-        <v>64649156</v>
+        <v>62871386</v>
       </c>
       <c r="D61" s="2">
-        <v>46183.463506944441</v>
+        <v>46149.364837962959</v>
       </c>
       <c r="E61" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="F61" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="G61">
-        <v>747345191</v>
+        <v>143270405</v>
       </c>
       <c r="H61" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="I61" t="s">
         <v>0</v>
@@ -4400,7 +4452,7 @@
         <v>17</v>
       </c>
       <c r="K61" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L61" t="s">
         <v>8</v>
@@ -4409,13 +4461,13 @@
         <v>3</v>
       </c>
       <c r="N61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O61" t="s">
         <v>0</v>
       </c>
-      <c r="P61" s="1">
-        <v>7103410</v>
+      <c r="P61" t="s">
+        <v>0</v>
       </c>
       <c r="Q61" t="s">
         <v>23</v>
@@ -4423,81 +4475,81 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>63179342</v>
+        <v>63025600</v>
       </c>
       <c r="B62" s="2">
-        <v>46154.735729166663</v>
+        <v>46151.740983796299</v>
       </c>
       <c r="C62">
-        <v>64526824</v>
+        <v>63981861</v>
       </c>
       <c r="D62" s="2">
-        <v>46181.499490740738</v>
+        <v>46170.692743055559</v>
       </c>
       <c r="E62" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G62">
-        <v>778179203</v>
+        <v>758237461</v>
       </c>
       <c r="H62" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I62" t="s">
         <v>0</v>
       </c>
       <c r="J62" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K62" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L62" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M62" t="s">
         <v>3</v>
       </c>
       <c r="N62" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O62" t="s">
         <v>0</v>
       </c>
       <c r="P62" s="1">
-        <v>2000000</v>
+        <v>850000</v>
       </c>
       <c r="Q62" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>63210811</v>
+        <v>63168095</v>
       </c>
       <c r="B63" s="2">
-        <v>46155.50409722222</v>
+        <v>46154.647604166668</v>
       </c>
       <c r="C63">
-        <v>64678329</v>
+        <v>64649156</v>
       </c>
       <c r="D63" s="2">
-        <v>46183.692442129628</v>
+        <v>46183.463506944441</v>
       </c>
       <c r="E63" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>179</v>
+        <v>28</v>
       </c>
       <c r="G63">
-        <v>160128782</v>
+        <v>747345191</v>
       </c>
       <c r="H63" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I63" t="s">
         <v>0</v>
@@ -4506,7 +4558,7 @@
         <v>17</v>
       </c>
       <c r="K63" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L63" t="s">
         <v>8</v>
@@ -4515,13 +4567,13 @@
         <v>3</v>
       </c>
       <c r="N63" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O63" t="s">
         <v>0</v>
       </c>
       <c r="P63" s="1">
-        <v>800000</v>
+        <v>7103410</v>
       </c>
       <c r="Q63" t="s">
         <v>23</v>
@@ -4529,28 +4581,28 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>63451685</v>
+        <v>63179342</v>
       </c>
       <c r="B64" s="2">
-        <v>46160.45171296296</v>
+        <v>46154.735729166663</v>
       </c>
       <c r="C64">
-        <v>64407207</v>
+        <v>64526824</v>
       </c>
       <c r="D64" s="2">
-        <v>46178.669502314813</v>
+        <v>46181.499490740738</v>
       </c>
       <c r="E64" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="F64" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="G64">
-        <v>707407425</v>
+        <v>778179203</v>
       </c>
       <c r="H64" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="I64" t="s">
         <v>0</v>
@@ -4559,7 +4611,7 @@
         <v>17</v>
       </c>
       <c r="K64" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L64" t="s">
         <v>8</v>
@@ -4567,6 +4619,9 @@
       <c r="M64" t="s">
         <v>3</v>
       </c>
+      <c r="N64" t="s">
+        <v>107</v>
+      </c>
       <c r="O64" t="s">
         <v>0</v>
       </c>
@@ -4574,151 +4629,151 @@
         <v>2000000</v>
       </c>
       <c r="Q64" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>63453142</v>
+        <v>63210811</v>
       </c>
       <c r="B65" s="2">
-        <v>46160.461238425924</v>
+        <v>46155.50409722222</v>
       </c>
       <c r="C65">
-        <v>63982556</v>
+        <v>64685899</v>
       </c>
       <c r="D65" s="2">
-        <v>46170.697962962964</v>
+        <v>46183.762511574074</v>
       </c>
       <c r="E65" t="s">
-        <v>10</v>
+        <v>244</v>
       </c>
       <c r="F65" t="s">
-        <v>183</v>
+        <v>122</v>
       </c>
       <c r="G65">
-        <v>507828407</v>
+        <v>160128782</v>
       </c>
       <c r="H65" t="s">
-        <v>184</v>
-      </c>
-      <c r="I65" t="s">
-        <v>0</v>
+        <v>251</v>
+      </c>
+      <c r="I65">
+        <v>1951416</v>
       </c>
       <c r="J65" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K65" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L65" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M65" t="s">
-        <v>3</v>
+        <v>181</v>
       </c>
       <c r="N65" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O65" t="s">
         <v>0</v>
       </c>
       <c r="P65" s="1">
-        <v>1009545</v>
+        <v>800000</v>
       </c>
       <c r="Q65" t="s">
-        <v>23</v>
+        <v>252</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>63462158</v>
+        <v>63210811</v>
       </c>
       <c r="B66" s="2">
-        <v>46160.525254629632</v>
+        <v>46155.50409722222</v>
       </c>
       <c r="C66">
-        <v>63498261</v>
+        <v>64743989</v>
       </c>
       <c r="D66" s="2">
-        <v>46160.901041666664</v>
+        <v>46184.729155092595</v>
       </c>
       <c r="E66" t="s">
-        <v>167</v>
+        <v>58</v>
       </c>
       <c r="F66" t="s">
-        <v>185</v>
+        <v>122</v>
       </c>
       <c r="G66">
-        <v>768231346</v>
+        <v>160128782</v>
       </c>
       <c r="H66" t="s">
-        <v>186</v>
-      </c>
-      <c r="I66" t="s">
-        <v>0</v>
+        <v>251</v>
+      </c>
+      <c r="I66">
+        <v>1951416</v>
       </c>
       <c r="J66" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K66" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="L66" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M66" t="s">
-        <v>3</v>
+        <v>181</v>
       </c>
       <c r="N66" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O66" t="s">
         <v>0</v>
       </c>
       <c r="P66" s="1">
-        <v>518450</v>
+        <v>800000</v>
       </c>
       <c r="Q66" t="s">
-        <v>0</v>
+        <v>252</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>63477655</v>
+        <v>63453142</v>
       </c>
       <c r="B67" s="2">
-        <v>46160.651041666664</v>
+        <v>46160.461238425924</v>
       </c>
       <c r="C67">
-        <v>64494969</v>
+        <v>63982556</v>
       </c>
       <c r="D67" s="2">
-        <v>46180.831226851849</v>
+        <v>46170.697962962964</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="G67">
-        <v>709528212</v>
+        <v>507828407</v>
       </c>
       <c r="H67" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="I67" t="s">
         <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K67" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L67" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M67" t="s">
         <v>3</v>
@@ -4729,102 +4784,102 @@
       <c r="O67" t="s">
         <v>0</v>
       </c>
-      <c r="P67" t="s">
-        <v>0</v>
+      <c r="P67" s="1">
+        <v>1009545</v>
       </c>
       <c r="Q67" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>63526115</v>
+        <v>63462158</v>
       </c>
       <c r="B68" s="2">
-        <v>46161.544733796298</v>
+        <v>46160.525254629632</v>
       </c>
       <c r="C68">
-        <v>64146684</v>
+        <v>63498261</v>
       </c>
       <c r="D68" s="2">
-        <v>46174.480104166665</v>
+        <v>46160.901041666664</v>
       </c>
       <c r="E68" t="s">
-        <v>10</v>
+        <v>164</v>
       </c>
       <c r="F68" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="G68">
-        <v>707722441</v>
+        <v>768231346</v>
       </c>
       <c r="H68" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="I68" t="s">
         <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K68" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="L68" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M68" t="s">
         <v>3</v>
       </c>
       <c r="N68" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O68" t="s">
         <v>0</v>
       </c>
       <c r="P68" s="1">
-        <v>1513624</v>
+        <v>518450</v>
       </c>
       <c r="Q68" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>63529958</v>
+        <v>63477655</v>
       </c>
       <c r="B69" s="2">
-        <v>46161.577581018515</v>
+        <v>46160.651041666664</v>
       </c>
       <c r="C69">
-        <v>64330956</v>
+        <v>64725398</v>
       </c>
       <c r="D69" s="2">
-        <v>46177.528310185182</v>
+        <v>46184.600763888891</v>
       </c>
       <c r="E69" t="s">
-        <v>58</v>
+        <v>253</v>
       </c>
       <c r="F69" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="G69">
-        <v>708081052</v>
+        <v>709528212</v>
       </c>
       <c r="H69" t="s">
-        <v>226</v>
-      </c>
-      <c r="I69">
-        <v>1943146</v>
+        <v>186</v>
+      </c>
+      <c r="I69" t="s">
+        <v>0</v>
       </c>
       <c r="J69" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K69" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L69" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M69" t="s">
         <v>3</v>
@@ -4835,102 +4890,102 @@
       <c r="O69" t="s">
         <v>0</v>
       </c>
-      <c r="P69" s="1">
-        <v>655375</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>227</v>
+      <c r="P69" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>2721712160</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>63556908</v>
+        <v>63477655</v>
       </c>
       <c r="B70" s="2">
-        <v>46161.788553240738</v>
+        <v>46160.651041666664</v>
       </c>
       <c r="C70">
-        <v>64260259</v>
+        <v>64785597</v>
       </c>
       <c r="D70" s="2">
-        <v>46176.402372685188</v>
+        <v>46185.578194444446</v>
       </c>
       <c r="E70" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F70" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="G70">
-        <v>711458931</v>
+        <v>709528212</v>
       </c>
       <c r="H70" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="I70" t="s">
         <v>0</v>
       </c>
       <c r="J70" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K70" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L70" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M70" t="s">
         <v>3</v>
       </c>
       <c r="N70" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O70" t="s">
         <v>0</v>
       </c>
-      <c r="P70" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>30</v>
+      <c r="P70" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>2721712160</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>63577039</v>
+        <v>63526115</v>
       </c>
       <c r="B71" s="2">
-        <v>46162.450127314813</v>
+        <v>46161.544733796298</v>
       </c>
       <c r="C71">
-        <v>64526747</v>
+        <v>64146684</v>
       </c>
       <c r="D71" s="2">
-        <v>46181.499120370368</v>
+        <v>46174.480104166665</v>
       </c>
       <c r="E71" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="G71">
-        <v>716610940</v>
+        <v>707722441</v>
       </c>
       <c r="H71" t="s">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="I71" t="s">
         <v>0</v>
       </c>
       <c r="J71" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K71" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L71" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M71" t="s">
         <v>3</v>
@@ -4942,257 +4997,257 @@
         <v>0</v>
       </c>
       <c r="P71" s="1">
-        <v>299185</v>
+        <v>1513624</v>
       </c>
       <c r="Q71" t="s">
-        <v>228</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>63578582</v>
+        <v>63529958</v>
       </c>
       <c r="B72" s="2">
-        <v>46162.462199074071</v>
+        <v>46161.577581018515</v>
       </c>
       <c r="C72">
-        <v>63834278</v>
+        <v>64738332</v>
       </c>
       <c r="D72" s="2">
-        <v>46167.701192129629</v>
+        <v>46184.686076388891</v>
       </c>
       <c r="E72" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F72" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="G72">
-        <v>759974992</v>
+        <v>708081052</v>
       </c>
       <c r="H72" t="s">
-        <v>199</v>
-      </c>
-      <c r="I72" t="s">
-        <v>0</v>
+        <v>213</v>
+      </c>
+      <c r="I72">
+        <v>1943146</v>
       </c>
       <c r="J72" t="s">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="K72" t="s">
         <v>5</v>
       </c>
       <c r="L72" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M72" t="s">
         <v>3</v>
       </c>
       <c r="N72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O72" t="s">
         <v>0</v>
       </c>
       <c r="P72" s="1">
-        <v>4487314</v>
+        <v>655375</v>
       </c>
       <c r="Q72" t="s">
-        <v>57</v>
+        <v>214</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>63595239</v>
+        <v>63556908</v>
       </c>
       <c r="B73" s="2">
-        <v>46162.588333333333</v>
+        <v>46161.788553240738</v>
       </c>
       <c r="C73">
-        <v>64589681</v>
+        <v>64260259</v>
       </c>
       <c r="D73" s="2">
-        <v>46182.503379629627</v>
+        <v>46176.402372685188</v>
       </c>
       <c r="E73" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="G73">
-        <v>749194205</v>
+        <v>711458931</v>
       </c>
       <c r="H73" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="I73" t="s">
         <v>0</v>
       </c>
       <c r="J73" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K73" t="s">
         <v>5</v>
       </c>
       <c r="L73" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M73" t="s">
         <v>3</v>
       </c>
       <c r="N73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O73" t="s">
         <v>0</v>
       </c>
-      <c r="P73" t="s">
-        <v>0</v>
+      <c r="P73" s="1">
+        <v>1000000</v>
       </c>
       <c r="Q73" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>63610581</v>
+        <v>63577039</v>
       </c>
       <c r="B74" s="2">
-        <v>46162.70239583333</v>
+        <v>46162.450127314813</v>
       </c>
       <c r="C74">
-        <v>64677326</v>
+        <v>64761677</v>
       </c>
       <c r="D74" s="2">
-        <v>46183.68550925926</v>
+        <v>46185.374467592592</v>
       </c>
       <c r="E74" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F74" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="G74">
-        <v>799642361</v>
+        <v>716610940</v>
       </c>
       <c r="H74" t="s">
-        <v>204</v>
+        <v>88</v>
       </c>
       <c r="I74" t="s">
         <v>0</v>
       </c>
       <c r="J74" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K74" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L74" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M74" t="s">
         <v>3</v>
       </c>
       <c r="N74" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O74" t="s">
         <v>0</v>
       </c>
-      <c r="P74" t="s">
-        <v>0</v>
+      <c r="P74" s="1">
+        <v>299185</v>
       </c>
       <c r="Q74" t="s">
-        <v>30</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>63611129</v>
+        <v>63578582</v>
       </c>
       <c r="B75" s="2">
-        <v>46162.70616898148</v>
+        <v>46162.462199074071</v>
       </c>
       <c r="C75">
-        <v>64607265</v>
+        <v>64770374</v>
       </c>
       <c r="D75" s="2">
-        <v>46182.646550925929</v>
+        <v>46185.457557870373</v>
       </c>
       <c r="E75" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F75" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="G75">
-        <v>799642361</v>
+        <v>759974992</v>
       </c>
       <c r="H75" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="I75" t="s">
         <v>0</v>
       </c>
       <c r="J75" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="K75" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L75" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M75" t="s">
         <v>3</v>
       </c>
       <c r="N75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O75" t="s">
         <v>0</v>
       </c>
-      <c r="P75" t="s">
-        <v>0</v>
+      <c r="P75" s="1">
+        <v>4487314</v>
       </c>
       <c r="Q75" t="s">
-        <v>190</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>63643964</v>
+        <v>63578582</v>
       </c>
       <c r="B76" s="2">
-        <v>46163.485543981478</v>
+        <v>46162.462199074071</v>
       </c>
       <c r="C76">
-        <v>64643943</v>
+        <v>64770893</v>
       </c>
       <c r="D76" s="2">
-        <v>46183.423136574071</v>
+        <v>46185.462025462963</v>
       </c>
       <c r="E76" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="F76" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="G76">
-        <v>718824404</v>
+        <v>759974992</v>
       </c>
       <c r="H76" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="I76" t="s">
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>12</v>
+        <v>194</v>
       </c>
       <c r="K76" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L76" t="s">
         <v>6</v>
@@ -5201,54 +5256,54 @@
         <v>3</v>
       </c>
       <c r="N76" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O76" t="s">
         <v>0</v>
       </c>
       <c r="P76" s="1">
-        <v>1000000</v>
+        <v>4487314</v>
       </c>
       <c r="Q76" t="s">
-        <v>229</v>
+        <v>57</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>63674987</v>
+        <v>63595239</v>
       </c>
       <c r="B77" s="2">
-        <v>46163.735543981478</v>
+        <v>46162.588333333333</v>
       </c>
       <c r="C77">
-        <v>64233133</v>
+        <v>64589681</v>
       </c>
       <c r="D77" s="2">
-        <v>46175.681793981479</v>
+        <v>46182.503379629627</v>
       </c>
       <c r="E77" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="F77" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="G77">
-        <v>707479292</v>
+        <v>749194205</v>
       </c>
       <c r="H77" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="I77" t="s">
         <v>0</v>
       </c>
       <c r="J77" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K77" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L77" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M77" t="s">
         <v>3</v>
@@ -5262,52 +5317,52 @@
       <c r="P77" t="s">
         <v>0</v>
       </c>
-      <c r="Q77">
-        <v>2723540540</v>
+      <c r="Q77" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>63688978</v>
+        <v>63610581</v>
       </c>
       <c r="B78" s="2">
-        <v>46164.349548611113</v>
+        <v>46162.70239583333</v>
       </c>
       <c r="C78">
-        <v>64676394</v>
+        <v>64677326</v>
       </c>
       <c r="D78" s="2">
-        <v>46183.678668981483</v>
+        <v>46183.68550925926</v>
       </c>
       <c r="E78" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F78" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G78">
-        <v>709513411</v>
+        <v>799642361</v>
       </c>
       <c r="H78" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="I78" t="s">
         <v>0</v>
       </c>
       <c r="J78" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K78" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N78" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O78" t="s">
         <v>0</v>
@@ -5316,154 +5371,154 @@
         <v>0</v>
       </c>
       <c r="Q78" t="s">
-        <v>230</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>63688990</v>
+        <v>63611129</v>
       </c>
       <c r="B79" s="2">
-        <v>46164.349618055552</v>
+        <v>46162.70616898148</v>
       </c>
       <c r="C79">
-        <v>64674905</v>
+        <v>64607265</v>
       </c>
       <c r="D79" s="2">
-        <v>46183.667951388888</v>
+        <v>46182.646550925929</v>
       </c>
       <c r="E79" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F79" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G79">
-        <v>709513411</v>
+        <v>799642361</v>
       </c>
       <c r="H79" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="I79" t="s">
         <v>0</v>
       </c>
       <c r="J79" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K79" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L79" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M79" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O79" t="s">
         <v>0</v>
       </c>
-      <c r="P79" s="1">
-        <v>600000</v>
+      <c r="P79" t="s">
+        <v>0</v>
       </c>
       <c r="Q79" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>63689992</v>
+        <v>63643964</v>
       </c>
       <c r="B80" s="2">
-        <v>46164.364722222221</v>
+        <v>46163.485543981478</v>
       </c>
       <c r="C80">
-        <v>64613893</v>
+        <v>64643943</v>
       </c>
       <c r="D80" s="2">
-        <v>46182.693298611113</v>
+        <v>46183.423136574071</v>
       </c>
       <c r="E80" t="s">
-        <v>58</v>
+        <v>204</v>
       </c>
       <c r="F80" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G80">
-        <v>709513411</v>
+        <v>718824404</v>
       </c>
       <c r="H80" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="I80" t="s">
         <v>0</v>
       </c>
       <c r="J80" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K80" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="L80" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M80" t="s">
         <v>3</v>
       </c>
       <c r="N80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O80" t="s">
         <v>0</v>
       </c>
-      <c r="P80" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <v>2722509970</v>
+      <c r="P80" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>63693483</v>
+        <v>63688978</v>
       </c>
       <c r="B81" s="2">
-        <v>46164.404108796298</v>
+        <v>46164.349548611113</v>
       </c>
       <c r="C81">
-        <v>63998411</v>
+        <v>64609515</v>
       </c>
       <c r="D81" s="2">
-        <v>46171.337291666663</v>
+        <v>46182.662824074076</v>
       </c>
       <c r="E81" t="s">
-        <v>167</v>
+        <v>244</v>
       </c>
       <c r="F81" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G81">
-        <v>556999292</v>
+        <v>709513411</v>
       </c>
       <c r="H81" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="I81" t="s">
         <v>0</v>
       </c>
       <c r="J81" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K81" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L81" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M81" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N81" t="s">
         <v>107</v>
@@ -5471,479 +5526,479 @@
       <c r="O81" t="s">
         <v>0</v>
       </c>
-      <c r="P81" s="1">
-        <v>2200000</v>
+      <c r="P81" t="s">
+        <v>0</v>
       </c>
       <c r="Q81" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>63695475</v>
+        <v>63688978</v>
       </c>
       <c r="B82" s="2">
-        <v>46164.422708333332</v>
+        <v>46164.349548611113</v>
       </c>
       <c r="C82">
-        <v>64018151</v>
+        <v>64799410</v>
       </c>
       <c r="D82" s="2">
-        <v>46171.524953703702</v>
+        <v>46185.679247685184</v>
       </c>
       <c r="E82" t="s">
-        <v>167</v>
+        <v>15</v>
       </c>
       <c r="F82" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G82">
-        <v>556999292</v>
+        <v>709513411</v>
       </c>
       <c r="H82" t="s">
+        <v>203</v>
+      </c>
+      <c r="I82" t="s">
+        <v>0</v>
+      </c>
+      <c r="J82" t="s">
+        <v>12</v>
+      </c>
+      <c r="K82" t="s">
+        <v>9</v>
+      </c>
+      <c r="L82" t="s">
+        <v>6</v>
+      </c>
+      <c r="M82" t="s">
+        <v>7</v>
+      </c>
+      <c r="N82" t="s">
+        <v>107</v>
+      </c>
+      <c r="O82" t="s">
+        <v>0</v>
+      </c>
+      <c r="P82" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="s">
         <v>217</v>
-      </c>
-      <c r="I82" t="s">
-        <v>0</v>
-      </c>
-      <c r="J82" t="s">
-        <v>17</v>
-      </c>
-      <c r="K82" t="s">
-        <v>5</v>
-      </c>
-      <c r="L82" t="s">
-        <v>8</v>
-      </c>
-      <c r="M82" t="s">
-        <v>3</v>
-      </c>
-      <c r="N82" t="s">
-        <v>107</v>
-      </c>
-      <c r="O82" t="s">
-        <v>0</v>
-      </c>
-      <c r="P82" s="1">
-        <v>2200000</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>63705970</v>
+        <v>63688990</v>
       </c>
       <c r="B83" s="2">
-        <v>46164.501944444448</v>
+        <v>46164.349618055552</v>
       </c>
       <c r="C83">
-        <v>64590050</v>
+        <v>64609893</v>
       </c>
       <c r="D83" s="2">
-        <v>46182.506643518522</v>
+        <v>46182.66474537037</v>
       </c>
       <c r="E83" t="s">
-        <v>58</v>
+        <v>244</v>
       </c>
       <c r="F83" t="s">
+        <v>202</v>
+      </c>
+      <c r="G83">
+        <v>709513411</v>
+      </c>
+      <c r="H83" t="s">
+        <v>203</v>
+      </c>
+      <c r="I83" t="s">
+        <v>0</v>
+      </c>
+      <c r="J83" t="s">
+        <v>12</v>
+      </c>
+      <c r="K83" t="s">
+        <v>9</v>
+      </c>
+      <c r="L83" t="s">
+        <v>6</v>
+      </c>
+      <c r="M83" t="s">
+        <v>13</v>
+      </c>
+      <c r="N83" t="s">
+        <v>107</v>
+      </c>
+      <c r="O83" t="s">
+        <v>0</v>
+      </c>
+      <c r="P83" s="1">
+        <v>600000</v>
+      </c>
+      <c r="Q83" t="s">
         <v>218</v>
-      </c>
-      <c r="G83">
-        <v>707361318</v>
-      </c>
-      <c r="H83" t="s">
-        <v>219</v>
-      </c>
-      <c r="I83" t="s">
-        <v>0</v>
-      </c>
-      <c r="J83" t="s">
-        <v>17</v>
-      </c>
-      <c r="K83" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" t="s">
-        <v>107</v>
-      </c>
-      <c r="O83" t="s">
-        <v>0</v>
-      </c>
-      <c r="P83" s="1">
-        <v>2500000</v>
-      </c>
-      <c r="Q83" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>64005644</v>
+        <v>63688990</v>
       </c>
       <c r="B84" s="2">
-        <v>46171.424525462964</v>
+        <v>46164.349618055552</v>
       </c>
       <c r="C84">
-        <v>64548235</v>
+        <v>64800733</v>
       </c>
       <c r="D84" s="2">
-        <v>46181.65724537037</v>
+        <v>46185.689884259256</v>
       </c>
       <c r="E84" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="F84" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="G84">
-        <v>707109668</v>
+        <v>709513411</v>
       </c>
       <c r="H84" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="I84" t="s">
         <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K84" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L84" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M84" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N84" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O84" t="s">
         <v>0</v>
       </c>
-      <c r="P84" t="s">
-        <v>0</v>
+      <c r="P84" s="1">
+        <v>600000</v>
       </c>
       <c r="Q84" t="s">
-        <v>23</v>
+        <v>218</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>64029495</v>
+        <v>63689992</v>
       </c>
       <c r="B85" s="2">
-        <v>46171.630046296297</v>
+        <v>46164.364722222221</v>
       </c>
       <c r="C85">
-        <v>64555278</v>
+        <v>64609440</v>
       </c>
       <c r="D85" s="2">
-        <v>46181.706990740742</v>
+        <v>46182.662499999999</v>
       </c>
       <c r="E85" t="s">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="F85" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="G85">
-        <v>708335225</v>
+        <v>709513411</v>
       </c>
       <c r="H85" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="I85" t="s">
         <v>0</v>
       </c>
       <c r="J85" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K85" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L85" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M85" t="s">
         <v>3</v>
       </c>
       <c r="N85" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O85" t="s">
         <v>0</v>
       </c>
-      <c r="P85" s="1">
-        <v>5324000</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>98</v>
+      <c r="P85" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>2722509970</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>64145330</v>
+        <v>63689992</v>
       </c>
       <c r="B86" s="2">
-        <v>46174.470370370371</v>
+        <v>46164.364722222221</v>
       </c>
       <c r="C86">
-        <v>64495125</v>
+        <v>64800881</v>
       </c>
       <c r="D86" s="2">
-        <v>46180.834756944445</v>
+        <v>46185.691354166665</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="F86" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="G86">
-        <v>707361318</v>
+        <v>709513411</v>
       </c>
       <c r="H86" t="s">
-        <v>36</v>
+        <v>205</v>
       </c>
       <c r="I86" t="s">
         <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K86" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L86" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M86" t="s">
         <v>3</v>
       </c>
       <c r="N86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O86" t="s">
         <v>0</v>
       </c>
-      <c r="P86" s="1">
-        <v>2500000</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>30</v>
+      <c r="P86" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>2722509970</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>64149984</v>
+        <v>63693483</v>
       </c>
       <c r="B87" s="2">
-        <v>46174.503194444442</v>
+        <v>46164.404108796298</v>
       </c>
       <c r="C87">
-        <v>64366089</v>
+        <v>63998411</v>
       </c>
       <c r="D87" s="2">
-        <v>46177.931805555556</v>
+        <v>46171.337291666663</v>
       </c>
       <c r="E87" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F87" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="G87">
-        <v>718151543</v>
+        <v>556999292</v>
       </c>
       <c r="H87" t="s">
-        <v>36</v>
+        <v>207</v>
       </c>
       <c r="I87" t="s">
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M87" t="s">
         <v>3</v>
       </c>
       <c r="N87" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O87" t="s">
         <v>0</v>
       </c>
-      <c r="P87" t="s">
-        <v>0</v>
+      <c r="P87" s="1">
+        <v>2200000</v>
       </c>
       <c r="Q87" t="s">
-        <v>33</v>
+        <v>208</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>64159836</v>
+        <v>63695475</v>
       </c>
       <c r="B88" s="2">
-        <v>46174.578506944446</v>
+        <v>46164.422708333332</v>
       </c>
       <c r="C88">
-        <v>64677164</v>
+        <v>64018151</v>
       </c>
       <c r="D88" s="2">
-        <v>46183.684328703705</v>
+        <v>46171.524953703702</v>
       </c>
       <c r="E88" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F88" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="G88">
-        <v>788987805</v>
+        <v>556999292</v>
       </c>
       <c r="H88" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="I88" t="s">
         <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K88" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L88" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M88" t="s">
         <v>3</v>
       </c>
       <c r="N88" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O88" t="s">
         <v>0</v>
       </c>
-      <c r="P88" t="s">
-        <v>0</v>
+      <c r="P88" s="1">
+        <v>2200000</v>
       </c>
       <c r="Q88" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>64168091</v>
+        <v>63705970</v>
       </c>
       <c r="B89" s="2">
-        <v>46174.65016203704</v>
+        <v>46164.501944444448</v>
       </c>
       <c r="C89">
-        <v>64591214</v>
+        <v>64764904</v>
       </c>
       <c r="D89" s="2">
-        <v>46182.516203703701</v>
+        <v>46185.41207175926</v>
       </c>
       <c r="E89" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="F89" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="G89">
-        <v>777378597</v>
+        <v>707361318</v>
       </c>
       <c r="H89" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="I89" t="s">
         <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K89" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L89" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M89" t="s">
         <v>3</v>
       </c>
       <c r="N89" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O89" t="s">
         <v>0</v>
       </c>
-      <c r="P89" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>2724391874</v>
+      <c r="P89" s="1">
+        <v>2500000</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>64204580</v>
+        <v>64005644</v>
       </c>
       <c r="B90" s="2">
-        <v>46175.463912037034</v>
+        <v>46171.424525462964</v>
       </c>
       <c r="C90">
-        <v>64676754</v>
+        <v>64548235</v>
       </c>
       <c r="D90" s="2">
-        <v>46183.681331018517</v>
+        <v>46181.65724537037</v>
       </c>
       <c r="E90" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="F90" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="G90">
-        <v>779885779</v>
+        <v>707109668</v>
       </c>
       <c r="H90" t="s">
-        <v>36</v>
+        <v>221</v>
       </c>
       <c r="I90" t="s">
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K90" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L90" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M90" t="s">
         <v>3</v>
       </c>
       <c r="N90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O90" t="s">
         <v>0</v>
@@ -5951,34 +6006,34 @@
       <c r="P90" t="s">
         <v>0</v>
       </c>
-      <c r="Q90">
-        <v>2722447474</v>
+      <c r="Q90" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>64298334</v>
+        <v>64028024</v>
       </c>
       <c r="B91" s="2">
-        <v>46176.697557870371</v>
+        <v>46171.618414351855</v>
       </c>
       <c r="C91">
-        <v>64494332</v>
+        <v>64736917</v>
       </c>
       <c r="D91" s="2">
-        <v>46180.813113425924</v>
+        <v>46184.67627314815</v>
       </c>
       <c r="E91" t="s">
-        <v>10</v>
+        <v>253</v>
       </c>
       <c r="F91" t="s">
-        <v>243</v>
+        <v>98</v>
       </c>
       <c r="G91">
-        <v>102435520</v>
+        <v>709837321</v>
       </c>
       <c r="H91" t="s">
-        <v>74</v>
+        <v>254</v>
       </c>
       <c r="I91" t="s">
         <v>0</v>
@@ -5996,95 +6051,95 @@
         <v>3</v>
       </c>
       <c r="N91" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O91" t="s">
         <v>0</v>
       </c>
       <c r="P91" s="1">
-        <v>1000000</v>
+        <v>5324000</v>
       </c>
       <c r="Q91" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>64299624</v>
+        <v>64029495</v>
       </c>
       <c r="B92" s="2">
-        <v>46176.705578703702</v>
+        <v>46171.630046296297</v>
       </c>
       <c r="C92">
-        <v>64337058</v>
+        <v>64732208</v>
       </c>
       <c r="D92" s="2">
-        <v>46177.582615740743</v>
+        <v>46184.645787037036</v>
       </c>
       <c r="E92" t="s">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="F92" t="s">
-        <v>244</v>
+        <v>98</v>
       </c>
       <c r="G92">
-        <v>789196850</v>
+        <v>708335225</v>
       </c>
       <c r="H92" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="I92" t="s">
         <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K92" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L92" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M92" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O92" t="s">
         <v>0</v>
       </c>
-      <c r="P92" t="s">
-        <v>0</v>
+      <c r="P92" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q92" t="s">
-        <v>0</v>
+        <v>255</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>64299644</v>
+        <v>64145330</v>
       </c>
       <c r="B93" s="2">
-        <v>46176.705625000002</v>
+        <v>46174.470370370371</v>
       </c>
       <c r="C93">
-        <v>64337134</v>
+        <v>64789041</v>
       </c>
       <c r="D93" s="2">
-        <v>46177.583553240744</v>
+        <v>46185.604502314818</v>
       </c>
       <c r="E93" t="s">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="F93" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="G93">
-        <v>789196850</v>
+        <v>707361318</v>
       </c>
       <c r="H93" t="s">
-        <v>245</v>
+        <v>36</v>
       </c>
       <c r="I93" t="s">
         <v>0</v>
@@ -6093,119 +6148,122 @@
         <v>17</v>
       </c>
       <c r="K93" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L93" t="s">
         <v>8</v>
       </c>
       <c r="M93" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O93" t="s">
         <v>0</v>
       </c>
       <c r="P93" s="1">
-        <v>5324000</v>
+        <v>2500000</v>
       </c>
       <c r="Q93" t="s">
-        <v>0</v>
+        <v>256</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>64327001</v>
+        <v>64145330</v>
       </c>
       <c r="B94" s="2">
-        <v>46177.491620370369</v>
+        <v>46174.470370370371</v>
       </c>
       <c r="C94">
-        <v>64609809</v>
+        <v>64800104</v>
       </c>
       <c r="D94" s="2">
-        <v>46182.664421296293</v>
+        <v>46185.684641203705</v>
       </c>
       <c r="E94" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F94" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="G94">
-        <v>747103333</v>
+        <v>707361318</v>
       </c>
       <c r="H94" t="s">
-        <v>247</v>
+        <v>36</v>
       </c>
       <c r="I94" t="s">
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K94" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L94" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M94" t="s">
         <v>3</v>
       </c>
+      <c r="N94" t="s">
+        <v>107</v>
+      </c>
       <c r="O94" t="s">
         <v>0</v>
       </c>
       <c r="P94" s="1">
-        <v>2371414</v>
+        <v>2500000</v>
       </c>
       <c r="Q94" t="s">
-        <v>111</v>
+        <v>256</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>64402908</v>
+        <v>64149984</v>
       </c>
       <c r="B95" s="2">
-        <v>46178.638472222221</v>
+        <v>46174.503194444442</v>
       </c>
       <c r="C95">
-        <v>64520808</v>
+        <v>64366089</v>
       </c>
       <c r="D95" s="2">
-        <v>46181.458958333336</v>
+        <v>46177.931805555556</v>
       </c>
       <c r="E95" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="F95" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="G95">
-        <v>748377555</v>
+        <v>718151543</v>
       </c>
       <c r="H95" t="s">
-        <v>250</v>
+        <v>36</v>
       </c>
       <c r="I95" t="s">
         <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K95" t="s">
         <v>5</v>
       </c>
       <c r="L95" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M95" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O95" t="s">
         <v>0</v>
@@ -6214,226 +6272,2498 @@
         <v>0</v>
       </c>
       <c r="Q95" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>64402920</v>
+        <v>64159836</v>
       </c>
       <c r="B96" s="2">
-        <v>46178.638506944444</v>
+        <v>46174.578506944446</v>
       </c>
       <c r="C96">
-        <v>64521199</v>
+        <v>64797420</v>
       </c>
       <c r="D96" s="2">
-        <v>46181.461122685185</v>
+        <v>46185.663576388892</v>
       </c>
       <c r="E96" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="F96" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="G96">
-        <v>748377555</v>
+        <v>788987805</v>
       </c>
       <c r="H96" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="I96" t="s">
         <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K96" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L96" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M96" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O96" t="s">
         <v>0</v>
       </c>
-      <c r="P96" s="1">
-        <v>1644000</v>
+      <c r="P96" t="s">
+        <v>0</v>
       </c>
       <c r="Q96" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>64594376</v>
+        <v>64168091</v>
       </c>
       <c r="B97" s="2">
-        <v>46182.54111111111</v>
+        <v>46174.65016203704</v>
       </c>
       <c r="C97">
-        <v>64600865</v>
+        <v>64793736</v>
       </c>
       <c r="D97" s="2">
-        <v>46182.595046296294</v>
+        <v>46185.638784722221</v>
       </c>
       <c r="E97" t="s">
-        <v>253</v>
+        <v>147</v>
       </c>
       <c r="F97" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="G97">
-        <v>708081052</v>
+        <v>777378597</v>
       </c>
       <c r="H97" t="s">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="I97" t="s">
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K97" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L97" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M97" t="s">
         <v>3</v>
       </c>
       <c r="N97" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O97" t="s">
         <v>0</v>
       </c>
-      <c r="P97">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="s">
-        <v>252</v>
+      <c r="P97" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>2724391874</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>64667196</v>
+        <v>64204580</v>
       </c>
       <c r="B98" s="2">
-        <v>46183.609664351854</v>
+        <v>46175.463912037034</v>
       </c>
       <c r="C98">
-        <v>64667221</v>
+        <v>64676754</v>
       </c>
       <c r="D98" s="2">
-        <v>46183.609872685185</v>
+        <v>46183.681331018517</v>
       </c>
       <c r="E98" t="s">
-        <v>212</v>
+        <v>58</v>
       </c>
       <c r="F98" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="G98">
-        <v>778552680</v>
+        <v>779885779</v>
       </c>
       <c r="H98" t="s">
-        <v>255</v>
+        <v>36</v>
       </c>
       <c r="I98" t="s">
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K98" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M98" t="s">
         <v>3</v>
       </c>
       <c r="N98" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="O98" t="s">
         <v>0</v>
       </c>
-      <c r="P98" s="1">
-        <v>1000000</v>
+      <c r="P98" t="s">
+        <v>0</v>
       </c>
       <c r="Q98" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
+        <v>64298334</v>
+      </c>
+      <c r="B99" s="2">
+        <v>46176.697557870371</v>
+      </c>
+      <c r="C99">
+        <v>64494332</v>
+      </c>
+      <c r="D99" s="2">
+        <v>46180.813113425924</v>
+      </c>
+      <c r="E99" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" t="s">
+        <v>230</v>
+      </c>
+      <c r="G99">
+        <v>102435520</v>
+      </c>
+      <c r="H99" t="s">
+        <v>74</v>
+      </c>
+      <c r="I99" t="s">
+        <v>0</v>
+      </c>
+      <c r="J99" t="s">
+        <v>12</v>
+      </c>
+      <c r="K99" t="s">
+        <v>5</v>
+      </c>
+      <c r="L99" t="s">
+        <v>6</v>
+      </c>
+      <c r="M99" t="s">
+        <v>3</v>
+      </c>
+      <c r="N99" t="s">
+        <v>107</v>
+      </c>
+      <c r="O99" t="s">
+        <v>0</v>
+      </c>
+      <c r="P99" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>64299624</v>
+      </c>
+      <c r="B100" s="2">
+        <v>46176.705578703702</v>
+      </c>
+      <c r="C100">
+        <v>64697050</v>
+      </c>
+      <c r="D100" s="2">
+        <v>46184.353541666664</v>
+      </c>
+      <c r="E100" t="s">
+        <v>257</v>
+      </c>
+      <c r="F100" t="s">
+        <v>231</v>
+      </c>
+      <c r="G100">
+        <v>789196850</v>
+      </c>
+      <c r="H100" t="s">
+        <v>232</v>
+      </c>
+      <c r="I100" t="s">
+        <v>0</v>
+      </c>
+      <c r="J100" t="s">
+        <v>17</v>
+      </c>
+      <c r="K100" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" t="s">
+        <v>8</v>
+      </c>
+      <c r="M100" t="s">
+        <v>7</v>
+      </c>
+      <c r="N100" t="s">
+        <v>107</v>
+      </c>
+      <c r="O100" t="s">
+        <v>0</v>
+      </c>
+      <c r="P100" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>64299644</v>
+      </c>
+      <c r="B101" s="2">
+        <v>46176.705625000002</v>
+      </c>
+      <c r="C101">
+        <v>64697118</v>
+      </c>
+      <c r="D101" s="2">
+        <v>46184.354618055557</v>
+      </c>
+      <c r="E101" t="s">
+        <v>257</v>
+      </c>
+      <c r="F101" t="s">
+        <v>231</v>
+      </c>
+      <c r="G101">
+        <v>789196850</v>
+      </c>
+      <c r="H101" t="s">
+        <v>232</v>
+      </c>
+      <c r="I101" t="s">
+        <v>0</v>
+      </c>
+      <c r="J101" t="s">
+        <v>17</v>
+      </c>
+      <c r="K101" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" t="s">
+        <v>13</v>
+      </c>
+      <c r="N101" t="s">
+        <v>107</v>
+      </c>
+      <c r="O101" t="s">
+        <v>0</v>
+      </c>
+      <c r="P101" s="1">
+        <v>5324000</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>64327001</v>
+      </c>
+      <c r="B102" s="2">
+        <v>46177.491620370369</v>
+      </c>
+      <c r="C102">
+        <v>64609809</v>
+      </c>
+      <c r="D102" s="2">
+        <v>46182.664421296293</v>
+      </c>
+      <c r="E102" t="s">
+        <v>235</v>
+      </c>
+      <c r="F102" t="s">
+        <v>233</v>
+      </c>
+      <c r="G102">
+        <v>747103333</v>
+      </c>
+      <c r="H102" t="s">
+        <v>234</v>
+      </c>
+      <c r="I102" t="s">
+        <v>0</v>
+      </c>
+      <c r="J102" t="s">
+        <v>12</v>
+      </c>
+      <c r="K102" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" t="s">
+        <v>6</v>
+      </c>
+      <c r="M102" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" t="s">
+        <v>0</v>
+      </c>
+      <c r="P102" s="1">
+        <v>2371414</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>64327001</v>
+      </c>
+      <c r="B103" s="2">
+        <v>46177.491620370369</v>
+      </c>
+      <c r="C103">
+        <v>64696856</v>
+      </c>
+      <c r="D103" s="2">
+        <v>46184.349166666667</v>
+      </c>
+      <c r="E103" t="s">
+        <v>257</v>
+      </c>
+      <c r="F103" t="s">
+        <v>233</v>
+      </c>
+      <c r="G103">
+        <v>747103333</v>
+      </c>
+      <c r="H103" t="s">
+        <v>234</v>
+      </c>
+      <c r="I103" t="s">
+        <v>0</v>
+      </c>
+      <c r="J103" t="s">
+        <v>12</v>
+      </c>
+      <c r="K103" t="s">
+        <v>5</v>
+      </c>
+      <c r="L103" t="s">
+        <v>6</v>
+      </c>
+      <c r="M103" t="s">
+        <v>3</v>
+      </c>
+      <c r="N103" t="s">
+        <v>107</v>
+      </c>
+      <c r="O103" t="s">
+        <v>0</v>
+      </c>
+      <c r="P103" s="1">
+        <v>2371414</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>64402908</v>
+      </c>
+      <c r="B104" s="2">
+        <v>46178.638472222221</v>
+      </c>
+      <c r="C104">
+        <v>64697303</v>
+      </c>
+      <c r="D104" s="2">
+        <v>46184.357141203705</v>
+      </c>
+      <c r="E104" t="s">
+        <v>257</v>
+      </c>
+      <c r="F104" t="s">
+        <v>236</v>
+      </c>
+      <c r="G104">
+        <v>748377555</v>
+      </c>
+      <c r="H104" t="s">
+        <v>237</v>
+      </c>
+      <c r="I104" t="s">
+        <v>0</v>
+      </c>
+      <c r="J104" t="s">
+        <v>12</v>
+      </c>
+      <c r="K104" t="s">
+        <v>5</v>
+      </c>
+      <c r="L104" t="s">
+        <v>6</v>
+      </c>
+      <c r="M104" t="s">
+        <v>7</v>
+      </c>
+      <c r="N104" t="s">
+        <v>107</v>
+      </c>
+      <c r="O104" t="s">
+        <v>0</v>
+      </c>
+      <c r="P104" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>64402920</v>
+      </c>
+      <c r="B105" s="2">
+        <v>46178.638506944444</v>
+      </c>
+      <c r="C105">
+        <v>64697727</v>
+      </c>
+      <c r="D105" s="2">
+        <v>46184.363796296297</v>
+      </c>
+      <c r="E105" t="s">
+        <v>257</v>
+      </c>
+      <c r="F105" t="s">
+        <v>236</v>
+      </c>
+      <c r="G105">
+        <v>748377555</v>
+      </c>
+      <c r="H105" t="s">
+        <v>237</v>
+      </c>
+      <c r="I105" t="s">
+        <v>0</v>
+      </c>
+      <c r="J105" t="s">
+        <v>12</v>
+      </c>
+      <c r="K105" t="s">
+        <v>5</v>
+      </c>
+      <c r="L105" t="s">
+        <v>6</v>
+      </c>
+      <c r="M105" t="s">
+        <v>13</v>
+      </c>
+      <c r="N105" t="s">
+        <v>107</v>
+      </c>
+      <c r="O105" t="s">
+        <v>0</v>
+      </c>
+      <c r="P105" s="1">
+        <v>1644000</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>64594376</v>
+      </c>
+      <c r="B106" s="2">
+        <v>46182.54111111111</v>
+      </c>
+      <c r="C106">
+        <v>64701063</v>
+      </c>
+      <c r="D106" s="2">
+        <v>46184.409282407411</v>
+      </c>
+      <c r="E106" t="s">
+        <v>15</v>
+      </c>
+      <c r="F106" t="s">
+        <v>258</v>
+      </c>
+      <c r="G106">
+        <v>708081052</v>
+      </c>
+      <c r="H106" t="s">
+        <v>56</v>
+      </c>
+      <c r="I106">
+        <v>1950636</v>
+      </c>
+      <c r="J106" t="s">
+        <v>4</v>
+      </c>
+      <c r="K106" t="s">
+        <v>5</v>
+      </c>
+      <c r="L106" t="s">
+        <v>8</v>
+      </c>
+      <c r="M106" t="s">
+        <v>181</v>
+      </c>
+      <c r="N106" t="s">
+        <v>106</v>
+      </c>
+      <c r="O106" t="s">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>64667196</v>
+      </c>
+      <c r="B107" s="2">
+        <v>46183.609664351854</v>
+      </c>
+      <c r="C107">
+        <v>64667221</v>
+      </c>
+      <c r="D107" s="2">
+        <v>46183.609872685185</v>
+      </c>
+      <c r="E107" t="s">
+        <v>204</v>
+      </c>
+      <c r="F107" t="s">
+        <v>238</v>
+      </c>
+      <c r="G107">
+        <v>778552680</v>
+      </c>
+      <c r="H107" t="s">
+        <v>239</v>
+      </c>
+      <c r="I107" t="s">
+        <v>0</v>
+      </c>
+      <c r="J107" t="s">
+        <v>12</v>
+      </c>
+      <c r="K107" t="s">
+        <v>5</v>
+      </c>
+      <c r="L107" t="s">
+        <v>6</v>
+      </c>
+      <c r="M107" t="s">
+        <v>3</v>
+      </c>
+      <c r="N107" t="s">
+        <v>107</v>
+      </c>
+      <c r="O107" t="s">
+        <v>0</v>
+      </c>
+      <c r="P107" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>64667196</v>
+      </c>
+      <c r="B108" s="2">
+        <v>46183.609664351854</v>
+      </c>
+      <c r="C108">
+        <v>64697935</v>
+      </c>
+      <c r="D108" s="2">
+        <v>46184.367303240739</v>
+      </c>
+      <c r="E108" t="s">
+        <v>257</v>
+      </c>
+      <c r="F108" t="s">
+        <v>238</v>
+      </c>
+      <c r="G108">
+        <v>778552680</v>
+      </c>
+      <c r="H108" t="s">
+        <v>239</v>
+      </c>
+      <c r="I108" t="s">
+        <v>0</v>
+      </c>
+      <c r="J108" t="s">
+        <v>12</v>
+      </c>
+      <c r="K108" t="s">
+        <v>5</v>
+      </c>
+      <c r="L108" t="s">
+        <v>6</v>
+      </c>
+      <c r="M108" t="s">
+        <v>3</v>
+      </c>
+      <c r="N108" t="s">
+        <v>107</v>
+      </c>
+      <c r="O108" t="s">
+        <v>0</v>
+      </c>
+      <c r="P108" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A109">
         <v>64670304</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B109" s="2">
         <v>46183.632245370369</v>
       </c>
-      <c r="C99">
-        <v>64670348</v>
-      </c>
-      <c r="D99" s="2">
-        <v>46183.632476851853</v>
-      </c>
-      <c r="E99" t="s">
-        <v>253</v>
-      </c>
-      <c r="F99" t="s">
-        <v>256</v>
-      </c>
-      <c r="G99">
+      <c r="C109">
+        <v>64795098</v>
+      </c>
+      <c r="D109" s="2">
+        <v>46185.648055555554</v>
+      </c>
+      <c r="E109" t="s">
+        <v>259</v>
+      </c>
+      <c r="F109" t="s">
+        <v>240</v>
+      </c>
+      <c r="G109">
         <v>505499292</v>
       </c>
-      <c r="H99" t="s">
+      <c r="H109" t="s">
+        <v>241</v>
+      </c>
+      <c r="I109" t="s">
+        <v>0</v>
+      </c>
+      <c r="J109" t="s">
+        <v>21</v>
+      </c>
+      <c r="K109" t="s">
+        <v>26</v>
+      </c>
+      <c r="L109" t="s">
+        <v>2</v>
+      </c>
+      <c r="M109" t="s">
+        <v>3</v>
+      </c>
+      <c r="N109" t="s">
+        <v>106</v>
+      </c>
+      <c r="O109" t="s">
+        <v>0</v>
+      </c>
+      <c r="P109" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>64670304</v>
+      </c>
+      <c r="B110" s="2">
+        <v>46183.632245370369</v>
+      </c>
+      <c r="C110">
+        <v>64799962</v>
+      </c>
+      <c r="D110" s="2">
+        <v>46185.68377314815</v>
+      </c>
+      <c r="E110" t="s">
+        <v>164</v>
+      </c>
+      <c r="F110" t="s">
+        <v>240</v>
+      </c>
+      <c r="G110">
+        <v>505499292</v>
+      </c>
+      <c r="H110" t="s">
+        <v>241</v>
+      </c>
+      <c r="I110" t="s">
+        <v>0</v>
+      </c>
+      <c r="J110" t="s">
+        <v>21</v>
+      </c>
+      <c r="K110" t="s">
+        <v>26</v>
+      </c>
+      <c r="L110" t="s">
+        <v>2</v>
+      </c>
+      <c r="M110" t="s">
+        <v>3</v>
+      </c>
+      <c r="N110" t="s">
+        <v>107</v>
+      </c>
+      <c r="O110" t="s">
+        <v>0</v>
+      </c>
+      <c r="P110" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>64681816</v>
+      </c>
+      <c r="B111" s="2">
+        <v>46183.72179398148</v>
+      </c>
+      <c r="C111">
+        <v>64681863</v>
+      </c>
+      <c r="D111" s="2">
+        <v>46183.722037037034</v>
+      </c>
+      <c r="E111" t="s">
+        <v>204</v>
+      </c>
+      <c r="F111" t="s">
+        <v>236</v>
+      </c>
+      <c r="G111">
+        <v>749935631</v>
+      </c>
+      <c r="H111" t="s">
+        <v>260</v>
+      </c>
+      <c r="I111" t="s">
+        <v>0</v>
+      </c>
+      <c r="J111" t="s">
+        <v>12</v>
+      </c>
+      <c r="K111" t="s">
+        <v>5</v>
+      </c>
+      <c r="L111" t="s">
+        <v>6</v>
+      </c>
+      <c r="M111" t="s">
+        <v>3</v>
+      </c>
+      <c r="N111" t="s">
+        <v>107</v>
+      </c>
+      <c r="O111" t="s">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>64681816</v>
+      </c>
+      <c r="B112" s="2">
+        <v>46183.72179398148</v>
+      </c>
+      <c r="C112">
+        <v>64698288</v>
+      </c>
+      <c r="D112" s="2">
+        <v>46184.373344907406</v>
+      </c>
+      <c r="E112" t="s">
+        <v>103</v>
+      </c>
+      <c r="F112" t="s">
+        <v>236</v>
+      </c>
+      <c r="G112">
+        <v>749935631</v>
+      </c>
+      <c r="H112" t="s">
+        <v>260</v>
+      </c>
+      <c r="I112" t="s">
+        <v>0</v>
+      </c>
+      <c r="J112" t="s">
+        <v>12</v>
+      </c>
+      <c r="K112" t="s">
+        <v>5</v>
+      </c>
+      <c r="L112" t="s">
+        <v>6</v>
+      </c>
+      <c r="M112" t="s">
+        <v>3</v>
+      </c>
+      <c r="N112" t="s">
+        <v>107</v>
+      </c>
+      <c r="O112" t="s">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>64682728</v>
+      </c>
+      <c r="B113" s="2">
+        <v>46183.730092592596</v>
+      </c>
+      <c r="C113">
+        <v>64682804</v>
+      </c>
+      <c r="D113" s="2">
+        <v>46183.730451388888</v>
+      </c>
+      <c r="E113" t="s">
+        <v>204</v>
+      </c>
+      <c r="F113" t="s">
+        <v>261</v>
+      </c>
+      <c r="G113">
+        <v>749935631</v>
+      </c>
+      <c r="H113" t="s">
+        <v>260</v>
+      </c>
+      <c r="I113" t="s">
+        <v>0</v>
+      </c>
+      <c r="J113" t="s">
+        <v>12</v>
+      </c>
+      <c r="K113" t="s">
+        <v>5</v>
+      </c>
+      <c r="L113" t="s">
+        <v>6</v>
+      </c>
+      <c r="M113" t="s">
+        <v>3</v>
+      </c>
+      <c r="N113" t="s">
+        <v>107</v>
+      </c>
+      <c r="O113" t="s">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>64682728</v>
+      </c>
+      <c r="B114" s="2">
+        <v>46183.730092592596</v>
+      </c>
+      <c r="C114">
+        <v>64698140</v>
+      </c>
+      <c r="D114" s="2">
+        <v>46184.370219907411</v>
+      </c>
+      <c r="E114" t="s">
+        <v>103</v>
+      </c>
+      <c r="F114" t="s">
+        <v>261</v>
+      </c>
+      <c r="G114">
+        <v>749935631</v>
+      </c>
+      <c r="H114" t="s">
+        <v>260</v>
+      </c>
+      <c r="I114" t="s">
+        <v>0</v>
+      </c>
+      <c r="J114" t="s">
+        <v>12</v>
+      </c>
+      <c r="K114" t="s">
+        <v>5</v>
+      </c>
+      <c r="L114" t="s">
+        <v>6</v>
+      </c>
+      <c r="M114" t="s">
+        <v>3</v>
+      </c>
+      <c r="N114" t="s">
+        <v>107</v>
+      </c>
+      <c r="O114" t="s">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>64704377</v>
+      </c>
+      <c r="B115" s="2">
+        <v>46184.438657407409</v>
+      </c>
+      <c r="C115">
+        <v>64704417</v>
+      </c>
+      <c r="D115" s="2">
+        <v>46184.438969907409</v>
+      </c>
+      <c r="E115" t="s">
+        <v>204</v>
+      </c>
+      <c r="F115" t="s">
+        <v>236</v>
+      </c>
+      <c r="G115">
+        <v>749935631</v>
+      </c>
+      <c r="H115" t="s">
+        <v>262</v>
+      </c>
+      <c r="I115" t="s">
+        <v>0</v>
+      </c>
+      <c r="J115" t="s">
+        <v>12</v>
+      </c>
+      <c r="K115" t="s">
+        <v>5</v>
+      </c>
+      <c r="L115" t="s">
+        <v>6</v>
+      </c>
+      <c r="M115" t="s">
+        <v>3</v>
+      </c>
+      <c r="N115" t="s">
+        <v>107</v>
+      </c>
+      <c r="O115" t="s">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>64704377</v>
+      </c>
+      <c r="B116" s="2">
+        <v>46184.438657407409</v>
+      </c>
+      <c r="C116">
+        <v>64767654</v>
+      </c>
+      <c r="D116" s="2">
+        <v>46185.435648148145</v>
+      </c>
+      <c r="E116" t="s">
+        <v>103</v>
+      </c>
+      <c r="F116" t="s">
+        <v>236</v>
+      </c>
+      <c r="G116">
+        <v>749935631</v>
+      </c>
+      <c r="H116" t="s">
+        <v>262</v>
+      </c>
+      <c r="I116" t="s">
+        <v>0</v>
+      </c>
+      <c r="J116" t="s">
+        <v>12</v>
+      </c>
+      <c r="K116" t="s">
+        <v>5</v>
+      </c>
+      <c r="L116" t="s">
+        <v>6</v>
+      </c>
+      <c r="M116" t="s">
+        <v>3</v>
+      </c>
+      <c r="N116" t="s">
+        <v>107</v>
+      </c>
+      <c r="O116" t="s">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>64704719</v>
+      </c>
+      <c r="B117" s="2">
+        <v>46184.442048611112</v>
+      </c>
+      <c r="C117">
+        <v>64704786</v>
+      </c>
+      <c r="D117" s="2">
+        <v>46184.442291666666</v>
+      </c>
+      <c r="E117" t="s">
+        <v>204</v>
+      </c>
+      <c r="F117" t="s">
+        <v>236</v>
+      </c>
+      <c r="G117">
+        <v>749935631</v>
+      </c>
+      <c r="H117" t="s">
+        <v>262</v>
+      </c>
+      <c r="I117" t="s">
+        <v>0</v>
+      </c>
+      <c r="J117" t="s">
+        <v>12</v>
+      </c>
+      <c r="K117" t="s">
+        <v>5</v>
+      </c>
+      <c r="L117" t="s">
+        <v>6</v>
+      </c>
+      <c r="M117" t="s">
+        <v>3</v>
+      </c>
+      <c r="N117" t="s">
+        <v>107</v>
+      </c>
+      <c r="O117" t="s">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>64704719</v>
+      </c>
+      <c r="B118" s="2">
+        <v>46184.442048611112</v>
+      </c>
+      <c r="C118">
+        <v>64766924</v>
+      </c>
+      <c r="D118" s="2">
+        <v>46185.429074074076</v>
+      </c>
+      <c r="E118" t="s">
+        <v>103</v>
+      </c>
+      <c r="F118" t="s">
+        <v>236</v>
+      </c>
+      <c r="G118">
+        <v>749935631</v>
+      </c>
+      <c r="H118" t="s">
+        <v>262</v>
+      </c>
+      <c r="I118" t="s">
+        <v>0</v>
+      </c>
+      <c r="J118" t="s">
+        <v>12</v>
+      </c>
+      <c r="K118" t="s">
+        <v>5</v>
+      </c>
+      <c r="L118" t="s">
+        <v>6</v>
+      </c>
+      <c r="M118" t="s">
+        <v>3</v>
+      </c>
+      <c r="N118" t="s">
+        <v>107</v>
+      </c>
+      <c r="O118" t="s">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>64705061</v>
+      </c>
+      <c r="B119" s="2">
+        <v>46184.445474537039</v>
+      </c>
+      <c r="C119">
+        <v>64705107</v>
+      </c>
+      <c r="D119" s="2">
+        <v>46184.445694444446</v>
+      </c>
+      <c r="E119" t="s">
+        <v>204</v>
+      </c>
+      <c r="F119" t="s">
+        <v>98</v>
+      </c>
+      <c r="G119">
+        <v>749935631</v>
+      </c>
+      <c r="H119" t="s">
+        <v>262</v>
+      </c>
+      <c r="I119" t="s">
+        <v>0</v>
+      </c>
+      <c r="J119" t="s">
+        <v>12</v>
+      </c>
+      <c r="K119" t="s">
+        <v>5</v>
+      </c>
+      <c r="L119" t="s">
+        <v>6</v>
+      </c>
+      <c r="M119" t="s">
+        <v>3</v>
+      </c>
+      <c r="N119" t="s">
+        <v>107</v>
+      </c>
+      <c r="O119" t="s">
+        <v>0</v>
+      </c>
+      <c r="P119" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>64705061</v>
+      </c>
+      <c r="B120" s="2">
+        <v>46184.445474537039</v>
+      </c>
+      <c r="C120">
+        <v>64767799</v>
+      </c>
+      <c r="D120" s="2">
+        <v>46185.436608796299</v>
+      </c>
+      <c r="E120" t="s">
+        <v>103</v>
+      </c>
+      <c r="F120" t="s">
+        <v>98</v>
+      </c>
+      <c r="G120">
+        <v>749935631</v>
+      </c>
+      <c r="H120" t="s">
+        <v>262</v>
+      </c>
+      <c r="I120" t="s">
+        <v>0</v>
+      </c>
+      <c r="J120" t="s">
+        <v>12</v>
+      </c>
+      <c r="K120" t="s">
+        <v>5</v>
+      </c>
+      <c r="L120" t="s">
+        <v>6</v>
+      </c>
+      <c r="M120" t="s">
+        <v>3</v>
+      </c>
+      <c r="N120" t="s">
+        <v>107</v>
+      </c>
+      <c r="O120" t="s">
+        <v>0</v>
+      </c>
+      <c r="P120" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>64705620</v>
+      </c>
+      <c r="B121" s="2">
+        <v>46184.450127314813</v>
+      </c>
+      <c r="C121">
+        <v>64705667</v>
+      </c>
+      <c r="D121" s="2">
+        <v>46184.45039351852</v>
+      </c>
+      <c r="E121" t="s">
+        <v>204</v>
+      </c>
+      <c r="F121" t="s">
+        <v>98</v>
+      </c>
+      <c r="G121">
+        <v>749935631</v>
+      </c>
+      <c r="H121" t="s">
+        <v>262</v>
+      </c>
+      <c r="I121" t="s">
+        <v>0</v>
+      </c>
+      <c r="J121" t="s">
+        <v>12</v>
+      </c>
+      <c r="K121" t="s">
+        <v>5</v>
+      </c>
+      <c r="L121" t="s">
+        <v>6</v>
+      </c>
+      <c r="M121" t="s">
+        <v>3</v>
+      </c>
+      <c r="N121" t="s">
+        <v>107</v>
+      </c>
+      <c r="O121" t="s">
+        <v>0</v>
+      </c>
+      <c r="P121" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>64705620</v>
+      </c>
+      <c r="B122" s="2">
+        <v>46184.450127314813</v>
+      </c>
+      <c r="C122">
+        <v>64768052</v>
+      </c>
+      <c r="D122" s="2">
+        <v>46185.438449074078</v>
+      </c>
+      <c r="E122" t="s">
+        <v>103</v>
+      </c>
+      <c r="F122" t="s">
+        <v>98</v>
+      </c>
+      <c r="G122">
+        <v>749935631</v>
+      </c>
+      <c r="H122" t="s">
+        <v>262</v>
+      </c>
+      <c r="I122" t="s">
+        <v>0</v>
+      </c>
+      <c r="J122" t="s">
+        <v>12</v>
+      </c>
+      <c r="K122" t="s">
+        <v>5</v>
+      </c>
+      <c r="L122" t="s">
+        <v>6</v>
+      </c>
+      <c r="M122" t="s">
+        <v>3</v>
+      </c>
+      <c r="N122" t="s">
+        <v>107</v>
+      </c>
+      <c r="O122" t="s">
+        <v>0</v>
+      </c>
+      <c r="P122" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>64710297</v>
+      </c>
+      <c r="B123" s="2">
+        <v>46184.486192129632</v>
+      </c>
+      <c r="C123">
+        <v>64710340</v>
+      </c>
+      <c r="D123" s="2">
+        <v>46184.48641203704</v>
+      </c>
+      <c r="E123" t="s">
+        <v>204</v>
+      </c>
+      <c r="F123" t="s">
+        <v>98</v>
+      </c>
+      <c r="G123">
+        <v>749935631</v>
+      </c>
+      <c r="H123" t="s">
+        <v>263</v>
+      </c>
+      <c r="I123" t="s">
+        <v>0</v>
+      </c>
+      <c r="J123" t="s">
+        <v>12</v>
+      </c>
+      <c r="K123" t="s">
+        <v>5</v>
+      </c>
+      <c r="L123" t="s">
+        <v>6</v>
+      </c>
+      <c r="M123" t="s">
+        <v>3</v>
+      </c>
+      <c r="N123" t="s">
+        <v>107</v>
+      </c>
+      <c r="O123" t="s">
+        <v>0</v>
+      </c>
+      <c r="P123" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>64710297</v>
+      </c>
+      <c r="B124" s="2">
+        <v>46184.486192129632</v>
+      </c>
+      <c r="C124">
+        <v>64767053</v>
+      </c>
+      <c r="D124" s="2">
+        <v>46185.430451388886</v>
+      </c>
+      <c r="E124" t="s">
+        <v>103</v>
+      </c>
+      <c r="F124" t="s">
+        <v>98</v>
+      </c>
+      <c r="G124">
+        <v>749935631</v>
+      </c>
+      <c r="H124" t="s">
+        <v>263</v>
+      </c>
+      <c r="I124" t="s">
+        <v>0</v>
+      </c>
+      <c r="J124" t="s">
+        <v>12</v>
+      </c>
+      <c r="K124" t="s">
+        <v>5</v>
+      </c>
+      <c r="L124" t="s">
+        <v>6</v>
+      </c>
+      <c r="M124" t="s">
+        <v>3</v>
+      </c>
+      <c r="N124" t="s">
+        <v>107</v>
+      </c>
+      <c r="O124" t="s">
+        <v>0</v>
+      </c>
+      <c r="P124" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>64710582</v>
+      </c>
+      <c r="B125" s="2">
+        <v>46184.488217592596</v>
+      </c>
+      <c r="C125">
+        <v>64710629</v>
+      </c>
+      <c r="D125" s="2">
+        <v>46184.488449074073</v>
+      </c>
+      <c r="E125" t="s">
+        <v>204</v>
+      </c>
+      <c r="F125" t="s">
+        <v>98</v>
+      </c>
+      <c r="G125">
+        <v>749935631</v>
+      </c>
+      <c r="H125" t="s">
+        <v>263</v>
+      </c>
+      <c r="I125" t="s">
+        <v>0</v>
+      </c>
+      <c r="J125" t="s">
+        <v>12</v>
+      </c>
+      <c r="K125" t="s">
+        <v>5</v>
+      </c>
+      <c r="L125" t="s">
+        <v>6</v>
+      </c>
+      <c r="M125" t="s">
+        <v>3</v>
+      </c>
+      <c r="N125" t="s">
+        <v>107</v>
+      </c>
+      <c r="O125" t="s">
+        <v>0</v>
+      </c>
+      <c r="P125" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>64710582</v>
+      </c>
+      <c r="B126" s="2">
+        <v>46184.488217592596</v>
+      </c>
+      <c r="C126">
+        <v>64767884</v>
+      </c>
+      <c r="D126" s="2">
+        <v>46185.437291666669</v>
+      </c>
+      <c r="E126" t="s">
+        <v>103</v>
+      </c>
+      <c r="F126" t="s">
+        <v>98</v>
+      </c>
+      <c r="G126">
+        <v>749935631</v>
+      </c>
+      <c r="H126" t="s">
+        <v>263</v>
+      </c>
+      <c r="I126" t="s">
+        <v>0</v>
+      </c>
+      <c r="J126" t="s">
+        <v>12</v>
+      </c>
+      <c r="K126" t="s">
+        <v>5</v>
+      </c>
+      <c r="L126" t="s">
+        <v>6</v>
+      </c>
+      <c r="M126" t="s">
+        <v>3</v>
+      </c>
+      <c r="N126" t="s">
+        <v>107</v>
+      </c>
+      <c r="O126" t="s">
+        <v>0</v>
+      </c>
+      <c r="P126" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>64726631</v>
+      </c>
+      <c r="B127" s="2">
+        <v>46184.610069444447</v>
+      </c>
+      <c r="C127">
+        <v>64766778</v>
+      </c>
+      <c r="D127" s="2">
+        <v>46185.427928240744</v>
+      </c>
+      <c r="E127" t="s">
+        <v>103</v>
+      </c>
+      <c r="F127" t="s">
+        <v>264</v>
+      </c>
+      <c r="G127">
+        <v>749935631</v>
+      </c>
+      <c r="H127" t="s">
+        <v>265</v>
+      </c>
+      <c r="I127" t="s">
+        <v>0</v>
+      </c>
+      <c r="J127" t="s">
+        <v>12</v>
+      </c>
+      <c r="K127" t="s">
+        <v>5</v>
+      </c>
+      <c r="L127" t="s">
+        <v>6</v>
+      </c>
+      <c r="M127" t="s">
+        <v>3</v>
+      </c>
+      <c r="N127" t="s">
+        <v>107</v>
+      </c>
+      <c r="O127" t="s">
+        <v>0</v>
+      </c>
+      <c r="P127" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>64726631</v>
+      </c>
+      <c r="B128" s="2">
+        <v>46184.610069444447</v>
+      </c>
+      <c r="C128">
+        <v>64726671</v>
+      </c>
+      <c r="D128" s="2">
+        <v>46184.610312500001</v>
+      </c>
+      <c r="E128" t="s">
+        <v>204</v>
+      </c>
+      <c r="F128" t="s">
+        <v>264</v>
+      </c>
+      <c r="G128">
+        <v>749935631</v>
+      </c>
+      <c r="H128" t="s">
+        <v>265</v>
+      </c>
+      <c r="I128" t="s">
+        <v>0</v>
+      </c>
+      <c r="J128" t="s">
+        <v>12</v>
+      </c>
+      <c r="K128" t="s">
+        <v>5</v>
+      </c>
+      <c r="L128" t="s">
+        <v>6</v>
+      </c>
+      <c r="M128" t="s">
+        <v>3</v>
+      </c>
+      <c r="N128" t="s">
+        <v>107</v>
+      </c>
+      <c r="O128" t="s">
+        <v>0</v>
+      </c>
+      <c r="P128" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>64727926</v>
+      </c>
+      <c r="B129" s="2">
+        <v>46184.618587962963</v>
+      </c>
+      <c r="C129">
+        <v>64766686</v>
+      </c>
+      <c r="D129" s="2">
+        <v>46185.427233796298</v>
+      </c>
+      <c r="E129" t="s">
+        <v>103</v>
+      </c>
+      <c r="F129" t="s">
+        <v>266</v>
+      </c>
+      <c r="G129">
+        <v>749935631</v>
+      </c>
+      <c r="H129" t="s">
+        <v>267</v>
+      </c>
+      <c r="I129" t="s">
+        <v>0</v>
+      </c>
+      <c r="J129" t="s">
+        <v>12</v>
+      </c>
+      <c r="K129" t="s">
+        <v>5</v>
+      </c>
+      <c r="L129" t="s">
+        <v>6</v>
+      </c>
+      <c r="M129" t="s">
+        <v>3</v>
+      </c>
+      <c r="N129" t="s">
+        <v>107</v>
+      </c>
+      <c r="O129" t="s">
+        <v>0</v>
+      </c>
+      <c r="P129" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>64727926</v>
+      </c>
+      <c r="B130" s="2">
+        <v>46184.618587962963</v>
+      </c>
+      <c r="C130">
+        <v>64727981</v>
+      </c>
+      <c r="D130" s="2">
+        <v>46184.618877314817</v>
+      </c>
+      <c r="E130" t="s">
+        <v>204</v>
+      </c>
+      <c r="F130" t="s">
+        <v>266</v>
+      </c>
+      <c r="G130">
+        <v>749935631</v>
+      </c>
+      <c r="H130" t="s">
+        <v>267</v>
+      </c>
+      <c r="I130" t="s">
+        <v>0</v>
+      </c>
+      <c r="J130" t="s">
+        <v>12</v>
+      </c>
+      <c r="K130" t="s">
+        <v>5</v>
+      </c>
+      <c r="L130" t="s">
+        <v>6</v>
+      </c>
+      <c r="M130" t="s">
+        <v>3</v>
+      </c>
+      <c r="N130" t="s">
+        <v>107</v>
+      </c>
+      <c r="O130" t="s">
+        <v>0</v>
+      </c>
+      <c r="P130" s="1">
+        <v>500000</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>64761027</v>
+      </c>
+      <c r="B131" s="2">
+        <v>46185.365057870367</v>
+      </c>
+      <c r="C131">
+        <v>64767232</v>
+      </c>
+      <c r="D131" s="2">
+        <v>46185.431805555556</v>
+      </c>
+      <c r="E131" t="s">
         <v>257</v>
       </c>
-      <c r="I99" t="s">
-        <v>0</v>
-      </c>
-      <c r="J99" t="s">
+      <c r="F131" t="s">
+        <v>268</v>
+      </c>
+      <c r="G131">
+        <v>576617272</v>
+      </c>
+      <c r="H131" t="s">
+        <v>269</v>
+      </c>
+      <c r="I131">
+        <v>1951326</v>
+      </c>
+      <c r="J131" t="s">
         <v>21</v>
       </c>
-      <c r="K99" t="s">
+      <c r="K131" t="s">
         <v>1</v>
       </c>
-      <c r="L99" t="s">
+      <c r="L131" t="s">
         <v>2</v>
       </c>
-      <c r="M99" t="s">
-        <v>3</v>
-      </c>
-      <c r="N99" t="s">
-        <v>107</v>
-      </c>
-      <c r="O99" t="s">
-        <v>0</v>
-      </c>
-      <c r="P99" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="s">
+      <c r="M131" t="s">
+        <v>3</v>
+      </c>
+      <c r="N131" t="s">
+        <v>107</v>
+      </c>
+      <c r="O131" t="s">
+        <v>0</v>
+      </c>
+      <c r="P131" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>64761746</v>
+      </c>
+      <c r="B132" s="2">
+        <v>46185.375196759262</v>
+      </c>
+      <c r="C132">
+        <v>64777663</v>
+      </c>
+      <c r="D132" s="2">
+        <v>46185.514745370368</v>
+      </c>
+      <c r="E132" t="s">
+        <v>103</v>
+      </c>
+      <c r="F132" t="s">
+        <v>270</v>
+      </c>
+      <c r="G132">
+        <v>749503436</v>
+      </c>
+      <c r="H132" t="s">
+        <v>271</v>
+      </c>
+      <c r="I132" t="s">
+        <v>0</v>
+      </c>
+      <c r="J132" t="s">
+        <v>21</v>
+      </c>
+      <c r="K132" t="s">
+        <v>1</v>
+      </c>
+      <c r="L132" t="s">
+        <v>2</v>
+      </c>
+      <c r="M132" t="s">
+        <v>3</v>
+      </c>
+      <c r="N132" t="s">
+        <v>107</v>
+      </c>
+      <c r="O132" t="s">
+        <v>0</v>
+      </c>
+      <c r="P132" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>64775381</v>
+      </c>
+      <c r="B133" s="2">
+        <v>46185.497025462966</v>
+      </c>
+      <c r="C133">
+        <v>64775412</v>
+      </c>
+      <c r="D133" s="2">
+        <v>46185.497256944444</v>
+      </c>
+      <c r="E133" t="s">
+        <v>204</v>
+      </c>
+      <c r="F133" t="s">
+        <v>272</v>
+      </c>
+      <c r="G133">
+        <v>757500782</v>
+      </c>
+      <c r="H133" t="s">
+        <v>273</v>
+      </c>
+      <c r="I133" t="s">
+        <v>0</v>
+      </c>
+      <c r="J133" t="s">
+        <v>17</v>
+      </c>
+      <c r="K133" t="s">
+        <v>5</v>
+      </c>
+      <c r="L133" t="s">
+        <v>8</v>
+      </c>
+      <c r="M133" t="s">
+        <v>7</v>
+      </c>
+      <c r="N133" t="s">
+        <v>107</v>
+      </c>
+      <c r="O133" t="s">
+        <v>0</v>
+      </c>
+      <c r="P133" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>64775381</v>
+      </c>
+      <c r="B134" s="2">
+        <v>46185.497025462966</v>
+      </c>
+      <c r="C134">
+        <v>64795189</v>
+      </c>
+      <c r="D134" s="2">
+        <v>46185.648576388892</v>
+      </c>
+      <c r="E134" t="s">
+        <v>274</v>
+      </c>
+      <c r="F134" t="s">
+        <v>272</v>
+      </c>
+      <c r="G134">
+        <v>757500782</v>
+      </c>
+      <c r="H134" t="s">
+        <v>273</v>
+      </c>
+      <c r="I134" t="s">
+        <v>0</v>
+      </c>
+      <c r="J134" t="s">
+        <v>17</v>
+      </c>
+      <c r="K134" t="s">
+        <v>5</v>
+      </c>
+      <c r="L134" t="s">
+        <v>8</v>
+      </c>
+      <c r="M134" t="s">
+        <v>7</v>
+      </c>
+      <c r="N134" t="s">
+        <v>107</v>
+      </c>
+      <c r="O134" t="s">
+        <v>0</v>
+      </c>
+      <c r="P134" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>64775393</v>
+      </c>
+      <c r="B135" s="2">
+        <v>46185.497060185182</v>
+      </c>
+      <c r="C135">
+        <v>64775424</v>
+      </c>
+      <c r="D135" s="2">
+        <v>46185.49728009259</v>
+      </c>
+      <c r="E135" t="s">
+        <v>204</v>
+      </c>
+      <c r="F135" t="s">
+        <v>272</v>
+      </c>
+      <c r="G135">
+        <v>757500782</v>
+      </c>
+      <c r="H135" t="s">
+        <v>273</v>
+      </c>
+      <c r="I135" t="s">
+        <v>0</v>
+      </c>
+      <c r="J135" t="s">
+        <v>17</v>
+      </c>
+      <c r="K135" t="s">
+        <v>5</v>
+      </c>
+      <c r="L135" t="s">
+        <v>8</v>
+      </c>
+      <c r="M135" t="s">
+        <v>13</v>
+      </c>
+      <c r="N135" t="s">
+        <v>107</v>
+      </c>
+      <c r="O135" t="s">
+        <v>0</v>
+      </c>
+      <c r="P135" s="1">
+        <v>5324000</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>64775393</v>
+      </c>
+      <c r="B136" s="2">
+        <v>46185.497060185182</v>
+      </c>
+      <c r="C136">
+        <v>64795058</v>
+      </c>
+      <c r="D136" s="2">
+        <v>46185.647870370369</v>
+      </c>
+      <c r="E136" t="s">
+        <v>274</v>
+      </c>
+      <c r="F136" t="s">
+        <v>272</v>
+      </c>
+      <c r="G136">
+        <v>757500782</v>
+      </c>
+      <c r="H136" t="s">
+        <v>273</v>
+      </c>
+      <c r="I136" t="s">
+        <v>0</v>
+      </c>
+      <c r="J136" t="s">
+        <v>17</v>
+      </c>
+      <c r="K136" t="s">
+        <v>5</v>
+      </c>
+      <c r="L136" t="s">
+        <v>8</v>
+      </c>
+      <c r="M136" t="s">
+        <v>13</v>
+      </c>
+      <c r="N136" t="s">
+        <v>107</v>
+      </c>
+      <c r="O136" t="s">
+        <v>0</v>
+      </c>
+      <c r="P136" s="1">
+        <v>5324000</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>64776871</v>
+      </c>
+      <c r="B137" s="2">
+        <v>46185.508958333332</v>
+      </c>
+      <c r="C137">
+        <v>64776930</v>
+      </c>
+      <c r="D137" s="2">
+        <v>46185.509189814817</v>
+      </c>
+      <c r="E137" t="s">
+        <v>204</v>
+      </c>
+      <c r="F137" t="s">
+        <v>275</v>
+      </c>
+      <c r="G137">
+        <v>748377555</v>
+      </c>
+      <c r="H137" t="s">
+        <v>276</v>
+      </c>
+      <c r="I137" t="s">
+        <v>0</v>
+      </c>
+      <c r="J137" t="s">
+        <v>17</v>
+      </c>
+      <c r="K137" t="s">
+        <v>5</v>
+      </c>
+      <c r="L137" t="s">
+        <v>8</v>
+      </c>
+      <c r="M137" t="s">
+        <v>7</v>
+      </c>
+      <c r="N137" t="s">
+        <v>107</v>
+      </c>
+      <c r="O137" t="s">
+        <v>0</v>
+      </c>
+      <c r="P137" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>64776871</v>
+      </c>
+      <c r="B138" s="2">
+        <v>46185.508958333332</v>
+      </c>
+      <c r="C138">
+        <v>64795250</v>
+      </c>
+      <c r="D138" s="2">
+        <v>46185.649201388886</v>
+      </c>
+      <c r="E138" t="s">
+        <v>274</v>
+      </c>
+      <c r="F138" t="s">
+        <v>275</v>
+      </c>
+      <c r="G138">
+        <v>748377555</v>
+      </c>
+      <c r="H138" t="s">
+        <v>276</v>
+      </c>
+      <c r="I138" t="s">
+        <v>0</v>
+      </c>
+      <c r="J138" t="s">
+        <v>17</v>
+      </c>
+      <c r="K138" t="s">
+        <v>5</v>
+      </c>
+      <c r="L138" t="s">
+        <v>8</v>
+      </c>
+      <c r="M138" t="s">
+        <v>7</v>
+      </c>
+      <c r="N138" t="s">
+        <v>107</v>
+      </c>
+      <c r="O138" t="s">
+        <v>0</v>
+      </c>
+      <c r="P138" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>64776884</v>
+      </c>
+      <c r="B139" s="2">
+        <v>46185.508993055555</v>
+      </c>
+      <c r="C139">
+        <v>64776942</v>
+      </c>
+      <c r="D139" s="2">
+        <v>46185.509247685186</v>
+      </c>
+      <c r="E139" t="s">
+        <v>204</v>
+      </c>
+      <c r="F139" t="s">
+        <v>275</v>
+      </c>
+      <c r="G139">
+        <v>748377555</v>
+      </c>
+      <c r="H139" t="s">
+        <v>276</v>
+      </c>
+      <c r="I139" t="s">
+        <v>0</v>
+      </c>
+      <c r="J139" t="s">
+        <v>17</v>
+      </c>
+      <c r="K139" t="s">
+        <v>5</v>
+      </c>
+      <c r="L139" t="s">
+        <v>8</v>
+      </c>
+      <c r="M139" t="s">
+        <v>13</v>
+      </c>
+      <c r="N139" t="s">
+        <v>107</v>
+      </c>
+      <c r="O139" t="s">
+        <v>0</v>
+      </c>
+      <c r="P139" s="1">
+        <v>5324000</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>64776884</v>
+      </c>
+      <c r="B140" s="2">
+        <v>46185.508993055555</v>
+      </c>
+      <c r="C140">
+        <v>64794898</v>
+      </c>
+      <c r="D140" s="2">
+        <v>46185.647060185183</v>
+      </c>
+      <c r="E140" t="s">
+        <v>274</v>
+      </c>
+      <c r="F140" t="s">
+        <v>275</v>
+      </c>
+      <c r="G140">
+        <v>748377555</v>
+      </c>
+      <c r="H140" t="s">
+        <v>276</v>
+      </c>
+      <c r="I140" t="s">
+        <v>0</v>
+      </c>
+      <c r="J140" t="s">
+        <v>17</v>
+      </c>
+      <c r="K140" t="s">
+        <v>5</v>
+      </c>
+      <c r="L140" t="s">
+        <v>8</v>
+      </c>
+      <c r="M140" t="s">
+        <v>13</v>
+      </c>
+      <c r="N140" t="s">
+        <v>107</v>
+      </c>
+      <c r="O140" t="s">
+        <v>0</v>
+      </c>
+      <c r="P140" s="1">
+        <v>5324000</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>64785630</v>
+      </c>
+      <c r="B141" s="2">
+        <v>46185.578321759262</v>
+      </c>
+      <c r="C141">
+        <v>64803291</v>
+      </c>
+      <c r="D141" s="2">
+        <v>46185.710648148146</v>
+      </c>
+      <c r="E141" t="s">
+        <v>176</v>
+      </c>
+      <c r="F141" t="s">
+        <v>98</v>
+      </c>
+      <c r="G141">
+        <v>708793132</v>
+      </c>
+      <c r="H141" t="s">
+        <v>277</v>
+      </c>
+      <c r="I141" t="s">
+        <v>0</v>
+      </c>
+      <c r="J141" t="s">
+        <v>12</v>
+      </c>
+      <c r="K141" t="s">
+        <v>5</v>
+      </c>
+      <c r="L141" t="s">
+        <v>6</v>
+      </c>
+      <c r="M141" t="s">
+        <v>3</v>
+      </c>
+      <c r="N141" t="s">
+        <v>107</v>
+      </c>
+      <c r="O141" t="s">
+        <v>0</v>
+      </c>
+      <c r="P141" s="1">
+        <v>293000</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>64791999</v>
+      </c>
+      <c r="B142" s="2">
+        <v>46185.626469907409</v>
+      </c>
+      <c r="C142">
+        <v>64794477</v>
+      </c>
+      <c r="D142" s="2">
+        <v>46185.644490740742</v>
+      </c>
+      <c r="E142" t="s">
+        <v>274</v>
+      </c>
+      <c r="F142" t="s">
+        <v>279</v>
+      </c>
+      <c r="G142">
+        <v>140675694</v>
+      </c>
+      <c r="H142" t="s">
+        <v>36</v>
+      </c>
+      <c r="I142" t="s">
+        <v>0</v>
+      </c>
+      <c r="J142" t="s">
+        <v>67</v>
+      </c>
+      <c r="K142" t="s">
+        <v>1</v>
+      </c>
+      <c r="L142" t="s">
+        <v>2</v>
+      </c>
+      <c r="M142" t="s">
+        <v>3</v>
+      </c>
+      <c r="N142" t="s">
+        <v>107</v>
+      </c>
+      <c r="O142" t="s">
+        <v>0</v>
+      </c>
+      <c r="P142" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S99" xr:uid="{2053CF0E-53A2-4CAA-A484-0CECB27DEFAC}"/>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/Attachments/Bureau/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="584" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8265E2E9-1733-4438-812D-3C55790FE46D}"/>
+  <xr:revisionPtr revIDLastSave="615" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F63E252-9B23-4BFE-96FB-C016DB179D39}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil2" sheetId="50" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil2!$A$1:$Q$113</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="269">
   <si>
     <t>-</t>
   </si>
@@ -704,9 +707,6 @@
     <t>EXTA: POP CMC KM4 EXTB: NSIA BANQUE MERMOZ COCODY Débit : 2Mbps</t>
   </si>
   <si>
-    <t>COCODY Budweiser Fan Festival Playce Palmeraie</t>
-  </si>
-  <si>
     <t>FOND D'ENTRETIEN ROUTIER</t>
   </si>
   <si>
@@ -743,9 +743,6 @@
     <t>PLATEAU IMMEUBLE NZARAMA AU 4EME ETAGE</t>
   </si>
   <si>
-    <t>BO Homologation: Saisie GAIA LSI</t>
-  </si>
-  <si>
     <t>STE AGENCE OCI 2PLTX ENA</t>
   </si>
   <si>
@@ -767,21 +764,6 @@
     <t>MOTA ENGIL</t>
   </si>
   <si>
-    <t>Planification Ctrl Conformite</t>
-  </si>
-  <si>
-    <t>Prestataire : Correction Conformite Travaux</t>
-  </si>
-  <si>
-    <t>TAABO LAMTO</t>
-  </si>
-  <si>
-    <t>xxxxxx</t>
-  </si>
-  <si>
-    <t>Saisie ASCOM</t>
-  </si>
-  <si>
     <t>ABIDJAN-TREICHVILLE//VOIE INCONNUE/RIVIERA PALMERAIE RESIDENTIEL</t>
   </si>
   <si>
@@ -797,15 +779,6 @@
     <t>BUVPN260101</t>
   </si>
   <si>
-    <t>Transmission Plans Equipe Numerisation</t>
-  </si>
-  <si>
-    <t>YAMOUSSOUKRO Kick-off</t>
-  </si>
-  <si>
-    <t>SYTHD260164</t>
-  </si>
-  <si>
     <t>BUVPN260100</t>
   </si>
   <si>
@@ -813,9 +786,6 @@
   </si>
   <si>
     <t>ORANGE BUSINESS SERVICES COTE D'IVOIRE</t>
-  </si>
-  <si>
-    <t>Realisation Ctrl Conformite</t>
   </si>
   <si>
     <t>COCODY RIVIERA GOLF</t>
@@ -919,7 +889,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1249,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B09768A0-915F-4D98-A6E3-373DEF20CD6F}">
-  <dimension ref="A1:Q142"/>
+  <dimension ref="A1:Q113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
@@ -1372,7 +1353,7 @@
         <v>176</v>
       </c>
       <c r="F3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G3">
         <v>748512613</v>
@@ -1410,43 +1391,43 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>49660008</v>
+        <v>52778382</v>
       </c>
       <c r="B4" s="2">
-        <v>45897.665000000001</v>
+        <v>45959.67696759259</v>
       </c>
       <c r="C4">
-        <v>64800088</v>
+        <v>55073470</v>
       </c>
       <c r="D4" s="2">
-        <v>46185.684594907405</v>
+        <v>46003.678194444445</v>
       </c>
       <c r="E4" t="s">
-        <v>243</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>242</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>748512613</v>
+        <v>708086759</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="I4">
+        <v>2788625</v>
       </c>
       <c r="J4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K4" t="s">
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="N4" t="s">
         <v>107</v>
@@ -1454,40 +1435,40 @@
       <c r="O4" t="s">
         <v>0</v>
       </c>
-      <c r="P4" s="1">
-        <v>2538822</v>
+      <c r="P4" t="s">
+        <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>52778382</v>
+        <v>52808171</v>
       </c>
       <c r="B5" s="2">
-        <v>45959.67696759259</v>
+        <v>45960.452361111114</v>
       </c>
       <c r="C5">
-        <v>55073470</v>
+        <v>59829408</v>
       </c>
       <c r="D5" s="2">
-        <v>46003.678194444445</v>
+        <v>46093.677152777775</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="G5">
-        <v>708086759</v>
+        <v>709738605</v>
       </c>
       <c r="H5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I5">
-        <v>2788625</v>
+        <v>2793645</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
@@ -1499,7 +1480,7 @@
         <v>8</v>
       </c>
       <c r="M5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N5" t="s">
         <v>107</v>
@@ -1511,51 +1492,51 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>52808171</v>
+        <v>53702282</v>
       </c>
       <c r="B6" s="2">
-        <v>45960.452361111114</v>
+        <v>45978.671550925923</v>
       </c>
       <c r="C6">
-        <v>59829408</v>
+        <v>64785970</v>
       </c>
       <c r="D6" s="2">
-        <v>46093.677152777775</v>
+        <v>46185.580925925926</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>709738605</v>
+        <v>778036533</v>
       </c>
       <c r="H6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6">
-        <v>2793645</v>
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O6" t="s">
         <v>0</v>
@@ -1563,46 +1544,46 @@
       <c r="P6" t="s">
         <v>0</v>
       </c>
-      <c r="Q6" t="s">
-        <v>60</v>
+      <c r="Q6">
+        <v>2720301240</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>53702282</v>
+        <v>53749839</v>
       </c>
       <c r="B7" s="2">
-        <v>45978.671550925923</v>
+        <v>45979.600694444445</v>
       </c>
       <c r="C7">
-        <v>64748163</v>
+        <v>62944786</v>
       </c>
       <c r="D7" s="2">
-        <v>46184.76871527778</v>
+        <v>46150.446296296293</v>
       </c>
       <c r="E7" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="G7">
-        <v>778036533</v>
+        <v>703333988</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I7" t="s">
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M7" t="s">
         <v>3</v>
@@ -1613,90 +1594,90 @@
       <c r="O7" t="s">
         <v>0</v>
       </c>
-      <c r="P7" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>2720301240</v>
+      <c r="P7" s="1">
+        <v>10000000</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>53702282</v>
+        <v>53790357</v>
       </c>
       <c r="B8" s="2">
-        <v>45978.671550925923</v>
+        <v>45980.438298611109</v>
       </c>
       <c r="C8">
-        <v>64785970</v>
+        <v>61385261</v>
       </c>
       <c r="D8" s="2">
-        <v>46185.580925925926</v>
+        <v>46122.774224537039</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="G8">
-        <v>778036533</v>
+        <v>708336404</v>
       </c>
       <c r="H8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="L8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M8" t="s">
         <v>3</v>
       </c>
       <c r="N8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O8" t="s">
         <v>0</v>
       </c>
-      <c r="P8" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>2720301240</v>
+      <c r="P8" s="1">
+        <v>4430307</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>53749839</v>
+        <v>53899369</v>
       </c>
       <c r="B9" s="2">
-        <v>45979.600694444445</v>
+        <v>45981.827430555553</v>
       </c>
       <c r="C9">
-        <v>62944786</v>
+        <v>55146678</v>
       </c>
       <c r="D9" s="2">
-        <v>46150.446296296293</v>
+        <v>46005.762916666667</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G9">
-        <v>703333988</v>
+        <v>707003126</v>
       </c>
       <c r="H9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I9" t="s">
         <v>0</v>
@@ -1711,7 +1692,7 @@
         <v>6</v>
       </c>
       <c r="M9" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N9" t="s">
         <v>107</v>
@@ -1719,52 +1700,52 @@
       <c r="O9" t="s">
         <v>0</v>
       </c>
-      <c r="P9" s="1">
-        <v>10000000</v>
+      <c r="P9">
+        <v>0</v>
       </c>
       <c r="Q9" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>53790357</v>
+        <v>54449048</v>
       </c>
       <c r="B10" s="2">
-        <v>45980.438298611109</v>
+        <v>45992.706157407411</v>
       </c>
       <c r="C10">
-        <v>61385261</v>
+        <v>56341749</v>
       </c>
       <c r="D10" s="2">
-        <v>46122.774224537039</v>
+        <v>46029.685115740744</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="G10">
-        <v>708336404</v>
+        <v>708086759</v>
       </c>
       <c r="H10" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M10" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N10" t="s">
         <v>107</v>
@@ -1772,52 +1753,52 @@
       <c r="O10" t="s">
         <v>0</v>
       </c>
-      <c r="P10" s="1">
-        <v>4430307</v>
+      <c r="P10" t="s">
+        <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>53899369</v>
+        <v>55104019</v>
       </c>
       <c r="B11" s="2">
-        <v>45981.827430555553</v>
+        <v>46004.469606481478</v>
       </c>
       <c r="C11">
-        <v>55146678</v>
+        <v>56566265</v>
       </c>
       <c r="D11" s="2">
-        <v>46005.762916666667</v>
+        <v>46034.582673611112</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="G11">
-        <v>707003126</v>
+        <v>504033918</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="I11" t="s">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M11" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N11" t="s">
         <v>107</v>
@@ -1825,52 +1806,52 @@
       <c r="O11" t="s">
         <v>0</v>
       </c>
-      <c r="P11">
-        <v>0</v>
+      <c r="P11" s="1">
+        <v>4000000</v>
       </c>
       <c r="Q11" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>54449048</v>
+        <v>55636282</v>
       </c>
       <c r="B12" s="2">
-        <v>45992.706157407411</v>
+        <v>46014.435729166667</v>
       </c>
       <c r="C12">
-        <v>56341749</v>
+        <v>57367586</v>
       </c>
       <c r="D12" s="2">
-        <v>46029.685115740744</v>
+        <v>46049.856261574074</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G12">
-        <v>708086759</v>
+        <v>759003900</v>
       </c>
       <c r="H12" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="I12" t="s">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K12" t="s">
         <v>5</v>
       </c>
       <c r="L12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M12" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N12" t="s">
         <v>107</v>
@@ -1878,49 +1859,49 @@
       <c r="O12" t="s">
         <v>0</v>
       </c>
-      <c r="P12" t="s">
-        <v>0</v>
+      <c r="P12" s="1">
+        <v>918681</v>
       </c>
       <c r="Q12" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>55104019</v>
+        <v>55694485</v>
       </c>
       <c r="B13" s="2">
-        <v>46004.469606481478</v>
+        <v>46015.420092592591</v>
       </c>
       <c r="C13">
-        <v>56566265</v>
+        <v>56752240</v>
       </c>
       <c r="D13" s="2">
-        <v>46034.582673611112</v>
+        <v>46037.705520833333</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G13">
-        <v>504033918</v>
+        <v>749338073</v>
       </c>
       <c r="H13" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I13" t="s">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M13" t="s">
         <v>3</v>
@@ -1932,42 +1913,42 @@
         <v>0</v>
       </c>
       <c r="P13" s="1">
-        <v>4000000</v>
+        <v>638462</v>
       </c>
       <c r="Q13" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>55636282</v>
+        <v>56181778</v>
       </c>
       <c r="B14" s="2">
-        <v>46014.435729166667</v>
+        <v>46027.499212962961</v>
       </c>
       <c r="C14">
-        <v>57367586</v>
+        <v>59210339</v>
       </c>
       <c r="D14" s="2">
-        <v>46049.856261574074</v>
+        <v>46083.492881944447</v>
       </c>
       <c r="E14" t="s">
         <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G14">
-        <v>759003900</v>
+        <v>585990976</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
-      </c>
-      <c r="I14" t="s">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="I14">
+        <v>1765416</v>
       </c>
       <c r="J14" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -1985,48 +1966,48 @@
         <v>0</v>
       </c>
       <c r="P14" s="1">
-        <v>918681</v>
+        <v>3000000</v>
       </c>
       <c r="Q14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>55694485</v>
+        <v>56603495</v>
       </c>
       <c r="B15" s="2">
-        <v>46015.420092592591</v>
+        <v>46035.408518518518</v>
       </c>
       <c r="C15">
-        <v>56752240</v>
+        <v>60907737</v>
       </c>
       <c r="D15" s="2">
-        <v>46037.705520833333</v>
+        <v>46113.726909722223</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="G15">
-        <v>749338073</v>
+        <v>707003126</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I15" t="s">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M15" t="s">
         <v>3</v>
@@ -2038,48 +2019,48 @@
         <v>0</v>
       </c>
       <c r="P15" s="1">
-        <v>638462</v>
+        <v>7103410</v>
       </c>
       <c r="Q15" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>56181778</v>
+        <v>56618123</v>
       </c>
       <c r="B16" s="2">
-        <v>46027.499212962961</v>
+        <v>46035.520821759259</v>
       </c>
       <c r="C16">
-        <v>59210339</v>
+        <v>63588969</v>
       </c>
       <c r="D16" s="2">
-        <v>46083.492881944447</v>
+        <v>46162.539305555554</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>176</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G16">
-        <v>585990976</v>
+        <v>504041812</v>
       </c>
       <c r="H16" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="I16">
-        <v>1765416</v>
+        <v>1775236</v>
       </c>
       <c r="J16" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M16" t="s">
         <v>3</v>
@@ -2091,48 +2072,48 @@
         <v>0</v>
       </c>
       <c r="P16" s="1">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="Q16" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>56603495</v>
+        <v>56675050</v>
       </c>
       <c r="B17" s="2">
-        <v>46035.408518518518</v>
+        <v>46036.516423611109</v>
       </c>
       <c r="C17">
-        <v>60907737</v>
+        <v>63302732</v>
       </c>
       <c r="D17" s="2">
-        <v>46113.726909722223</v>
+        <v>46157.396793981483</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="G17">
-        <v>707003126</v>
+        <v>748512613</v>
       </c>
       <c r="H17" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I17" t="s">
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
       </c>
       <c r="L17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M17" t="s">
         <v>3</v>
@@ -2144,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="1">
-        <v>7103410</v>
+        <v>4362401</v>
       </c>
       <c r="Q17" t="s">
         <v>19</v>
@@ -2152,40 +2133,40 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>56618123</v>
+        <v>56970346</v>
       </c>
       <c r="B18" s="2">
-        <v>46035.520821759259</v>
+        <v>46042.557280092595</v>
       </c>
       <c r="C18">
-        <v>63588969</v>
+        <v>59242054</v>
       </c>
       <c r="D18" s="2">
-        <v>46162.539305555554</v>
+        <v>46083.719525462962</v>
       </c>
       <c r="E18" t="s">
-        <v>176</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18">
-        <v>504041812</v>
+        <v>708667658</v>
       </c>
       <c r="H18" t="s">
-        <v>108</v>
-      </c>
-      <c r="I18">
-        <v>1775236</v>
+        <v>86</v>
+      </c>
+      <c r="I18" t="s">
+        <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
       </c>
       <c r="L18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M18" t="s">
         <v>3</v>
@@ -2197,36 +2178,36 @@
         <v>0</v>
       </c>
       <c r="P18" s="1">
-        <v>2000000</v>
+        <v>2871414</v>
       </c>
       <c r="Q18" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>56675050</v>
+        <v>57398181</v>
       </c>
       <c r="B19" s="2">
-        <v>46036.516423611109</v>
+        <v>46050.584374999999</v>
       </c>
       <c r="C19">
-        <v>63302732</v>
+        <v>60344342</v>
       </c>
       <c r="D19" s="2">
-        <v>46157.396793981483</v>
+        <v>46104.528900462959</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="G19">
-        <v>748512613</v>
+        <v>720631500</v>
       </c>
       <c r="H19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s">
         <v>0</v>
@@ -2250,36 +2231,36 @@
         <v>0</v>
       </c>
       <c r="P19" s="1">
-        <v>4362401</v>
+        <v>4406780</v>
       </c>
       <c r="Q19" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>56970346</v>
+        <v>58055656</v>
       </c>
       <c r="B20" s="2">
-        <v>46042.557280092595</v>
+        <v>46062.760023148148</v>
       </c>
       <c r="C20">
-        <v>59242054</v>
+        <v>61269237</v>
       </c>
       <c r="D20" s="2">
-        <v>46083.719525462962</v>
+        <v>46121.376689814817</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G20">
-        <v>708667658</v>
+        <v>758224257</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="I20" t="s">
         <v>0</v>
@@ -2303,48 +2284,48 @@
         <v>0</v>
       </c>
       <c r="P20" s="1">
-        <v>2871414</v>
+        <v>1800000</v>
       </c>
       <c r="Q20" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>57398181</v>
+        <v>58166885</v>
       </c>
       <c r="B21" s="2">
-        <v>46050.584374999999</v>
+        <v>46064.649965277778</v>
       </c>
       <c r="C21">
-        <v>60344342</v>
+        <v>63079695</v>
       </c>
       <c r="D21" s="2">
-        <v>46104.528900462959</v>
+        <v>46153.448425925926</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G21">
-        <v>720631500</v>
+        <v>504041812</v>
       </c>
       <c r="H21" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="I21" t="s">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
       </c>
       <c r="L21" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M21" t="s">
         <v>3</v>
@@ -2356,36 +2337,36 @@
         <v>0</v>
       </c>
       <c r="P21" s="1">
-        <v>4406780</v>
+        <v>2000000</v>
       </c>
       <c r="Q21" t="s">
-        <v>34</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>58055656</v>
+        <v>58626822</v>
       </c>
       <c r="B22" s="2">
-        <v>46062.760023148148</v>
+        <v>46072.810324074075</v>
       </c>
       <c r="C22">
-        <v>61269237</v>
+        <v>59811821</v>
       </c>
       <c r="D22" s="2">
-        <v>46121.376689814817</v>
+        <v>46093.543773148151</v>
       </c>
       <c r="E22" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G22">
-        <v>758224257</v>
+        <v>709574114</v>
       </c>
       <c r="H22" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="I22" t="s">
         <v>0</v>
@@ -2409,54 +2390,54 @@
         <v>0</v>
       </c>
       <c r="P22" s="1">
-        <v>1800000</v>
+        <v>445307</v>
       </c>
       <c r="Q22" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>58093827</v>
+        <v>58635645</v>
       </c>
       <c r="B23" s="2">
-        <v>46063.583402777775</v>
+        <v>46073.372395833336</v>
       </c>
       <c r="C23">
-        <v>63599943</v>
+        <v>61982536</v>
       </c>
       <c r="D23" s="2">
-        <v>46162.626145833332</v>
+        <v>46133.49863425926</v>
       </c>
       <c r="E23" t="s">
-        <v>247</v>
+        <v>15</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="G23">
-        <v>708086759</v>
+        <v>759250737</v>
       </c>
       <c r="H23" t="s">
-        <v>245</v>
+        <v>24</v>
       </c>
       <c r="I23" t="s">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L23" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M23" t="s">
         <v>7</v>
       </c>
       <c r="N23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O23" t="s">
         <v>0</v>
@@ -2465,33 +2446,33 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>246</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>58166885</v>
+        <v>58635674</v>
       </c>
       <c r="B24" s="2">
-        <v>46064.649965277778</v>
+        <v>46073.372488425928</v>
       </c>
       <c r="C24">
-        <v>63079695</v>
+        <v>61980847</v>
       </c>
       <c r="D24" s="2">
-        <v>46153.448425925926</v>
+        <v>46133.487384259257</v>
       </c>
       <c r="E24" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G24">
-        <v>504041812</v>
+        <v>759250737</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="I24" t="s">
         <v>0</v>
@@ -2506,7 +2487,7 @@
         <v>8</v>
       </c>
       <c r="M24" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N24" t="s">
         <v>107</v>
@@ -2515,51 +2496,51 @@
         <v>0</v>
       </c>
       <c r="P24" s="1">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="Q24" t="s">
-        <v>163</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>58626822</v>
+        <v>58868849</v>
       </c>
       <c r="B25" s="2">
-        <v>46072.810324074075</v>
+        <v>46077.501203703701</v>
       </c>
       <c r="C25">
-        <v>59811821</v>
+        <v>62104932</v>
       </c>
       <c r="D25" s="2">
-        <v>46093.543773148151</v>
+        <v>46135.396608796298</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F25" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G25">
-        <v>709574114</v>
+        <v>748377555</v>
       </c>
       <c r="H25" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I25" t="s">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M25" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N25" t="s">
         <v>107</v>
@@ -2567,52 +2548,52 @@
       <c r="O25" t="s">
         <v>0</v>
       </c>
-      <c r="P25" s="1">
-        <v>445307</v>
+      <c r="P25" t="s">
+        <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>58635645</v>
+        <v>58925987</v>
       </c>
       <c r="B26" s="2">
-        <v>46073.372395833336</v>
+        <v>46078.434814814813</v>
       </c>
       <c r="C26">
-        <v>61982536</v>
+        <v>60163873</v>
       </c>
       <c r="D26" s="2">
-        <v>46133.49863425926</v>
+        <v>46100.423101851855</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G26">
-        <v>759250737</v>
+        <v>708641473</v>
       </c>
       <c r="H26" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="I26" t="s">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L26" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M26" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N26" t="s">
         <v>107</v>
@@ -2624,48 +2605,48 @@
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>58635674</v>
+        <v>58959238</v>
       </c>
       <c r="B27" s="2">
-        <v>46073.372488425928</v>
+        <v>46078.665532407409</v>
       </c>
       <c r="C27">
-        <v>61980847</v>
+        <v>60163938</v>
       </c>
       <c r="D27" s="2">
-        <v>46133.487384259257</v>
+        <v>46100.423773148148</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G27">
-        <v>759250737</v>
+        <v>708641473</v>
       </c>
       <c r="H27" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="I27" t="s">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
       </c>
       <c r="L27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M27" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N27" t="s">
         <v>107</v>
@@ -2674,48 +2655,48 @@
         <v>0</v>
       </c>
       <c r="P27" s="1">
-        <v>500000</v>
+        <v>850000</v>
       </c>
       <c r="Q27" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>58868849</v>
+        <v>59537755</v>
       </c>
       <c r="B28" s="2">
-        <v>46077.501203703701</v>
+        <v>46088.586631944447</v>
       </c>
       <c r="C28">
-        <v>62104932</v>
+        <v>61591841</v>
       </c>
       <c r="D28" s="2">
-        <v>46135.396608796298</v>
+        <v>46127.35796296296</v>
       </c>
       <c r="E28" t="s">
         <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="G28">
-        <v>748377555</v>
+        <v>556331131</v>
       </c>
       <c r="H28" t="s">
-        <v>99</v>
-      </c>
-      <c r="I28" t="s">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="I28">
+        <v>1843236</v>
       </c>
       <c r="J28" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K28" t="s">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="L28" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M28" t="s">
         <v>7</v>
@@ -2726,52 +2707,52 @@
       <c r="O28" t="s">
         <v>0</v>
       </c>
-      <c r="P28" t="s">
+      <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>58925987</v>
+        <v>59606122</v>
       </c>
       <c r="B29" s="2">
-        <v>46078.434814814813</v>
+        <v>46090.447604166664</v>
       </c>
       <c r="C29">
-        <v>60163873</v>
+        <v>61897702</v>
       </c>
       <c r="D29" s="2">
-        <v>46100.423101851855</v>
+        <v>46132.349363425928</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F29" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="G29">
-        <v>708641473</v>
+        <v>708454305</v>
       </c>
       <c r="H29" t="s">
-        <v>101</v>
-      </c>
-      <c r="I29" t="s">
-        <v>0</v>
+        <v>136</v>
+      </c>
+      <c r="I29">
+        <v>1842206</v>
       </c>
       <c r="J29" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K29" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="L29" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M29" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N29" t="s">
         <v>107</v>
@@ -2779,37 +2760,37 @@
       <c r="O29" t="s">
         <v>0</v>
       </c>
-      <c r="P29" t="s">
+      <c r="P29">
         <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>58959238</v>
+        <v>59615935</v>
       </c>
       <c r="B30" s="2">
-        <v>46078.665532407409</v>
+        <v>46090.512303240743</v>
       </c>
       <c r="C30">
-        <v>60163938</v>
+        <v>60393405</v>
       </c>
       <c r="D30" s="2">
-        <v>46100.423773148148</v>
+        <v>46105.432800925926</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="G30">
-        <v>708641473</v>
+        <v>767081456</v>
       </c>
       <c r="H30" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
@@ -2832,46 +2813,46 @@
       <c r="O30" t="s">
         <v>0</v>
       </c>
-      <c r="P30" s="1">
-        <v>850000</v>
+      <c r="P30">
+        <v>0</v>
       </c>
       <c r="Q30" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>59537755</v>
+        <v>59894743</v>
       </c>
       <c r="B31" s="2">
-        <v>46088.586631944447</v>
+        <v>46094.687673611108</v>
       </c>
       <c r="C31">
-        <v>61591841</v>
+        <v>64800213</v>
       </c>
       <c r="D31" s="2">
-        <v>46127.35796296296</v>
+        <v>46185.685624999998</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>243</v>
       </c>
       <c r="F31" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="G31">
-        <v>556331131</v>
+        <v>759668146</v>
       </c>
       <c r="H31" t="s">
-        <v>121</v>
+        <v>241</v>
       </c>
       <c r="I31">
-        <v>1843236</v>
+        <v>1849226</v>
       </c>
       <c r="J31" t="s">
         <v>4</v>
       </c>
       <c r="K31" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="L31" t="s">
         <v>6</v>
@@ -2885,46 +2866,46 @@
       <c r="O31" t="s">
         <v>0</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="s">
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>135</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>59606122</v>
+        <v>60748674</v>
       </c>
       <c r="B32" s="2">
-        <v>46090.447604166664</v>
+        <v>46111.511504629627</v>
       </c>
       <c r="C32">
-        <v>61897702</v>
+        <v>62475433</v>
       </c>
       <c r="D32" s="2">
-        <v>46132.349363425928</v>
+        <v>46141.624513888892</v>
       </c>
       <c r="E32" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G32">
-        <v>708454305</v>
+        <v>767791237</v>
       </c>
       <c r="H32" t="s">
-        <v>136</v>
-      </c>
-      <c r="I32">
-        <v>1842206</v>
+        <v>119</v>
+      </c>
+      <c r="I32" t="s">
+        <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K32" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="L32" t="s">
         <v>6</v>
@@ -2942,45 +2923,45 @@
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>59615935</v>
+        <v>60972166</v>
       </c>
       <c r="B33" s="2">
-        <v>46090.512303240743</v>
+        <v>46114.708020833335</v>
       </c>
       <c r="C33">
-        <v>60393405</v>
+        <v>62949578</v>
       </c>
       <c r="D33" s="2">
-        <v>46105.432800925926</v>
+        <v>46150.482407407406</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G33">
-        <v>767081456</v>
+        <v>160128782</v>
       </c>
       <c r="H33" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I33" t="s">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
       </c>
       <c r="L33" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M33" t="s">
         <v>3</v>
@@ -2991,102 +2972,102 @@
       <c r="O33" t="s">
         <v>0</v>
       </c>
-      <c r="P33">
-        <v>0</v>
+      <c r="P33" s="1">
+        <v>800000</v>
       </c>
       <c r="Q33" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>59894743</v>
+        <v>61239047</v>
       </c>
       <c r="B34" s="2">
-        <v>46094.687673611108</v>
+        <v>46120.622071759259</v>
       </c>
       <c r="C34">
-        <v>64800213</v>
+        <v>64795668</v>
       </c>
       <c r="D34" s="2">
-        <v>46185.685624999998</v>
+        <v>46185.651990740742</v>
       </c>
       <c r="E34" t="s">
-        <v>250</v>
+        <v>58</v>
       </c>
       <c r="F34" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G34">
-        <v>759668146</v>
+        <v>103381121</v>
       </c>
       <c r="H34" t="s">
-        <v>248</v>
-      </c>
-      <c r="I34">
-        <v>1849226</v>
+        <v>125</v>
+      </c>
+      <c r="I34" t="s">
+        <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="K34" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="L34" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M34" t="s">
         <v>7</v>
       </c>
       <c r="N34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O34" t="s">
         <v>0</v>
       </c>
-      <c r="P34" t="s">
+      <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>249</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>60748674</v>
+        <v>61240327</v>
       </c>
       <c r="B35" s="2">
-        <v>46111.511504629627</v>
+        <v>46120.631747685184</v>
       </c>
       <c r="C35">
-        <v>62475433</v>
+        <v>63643159</v>
       </c>
       <c r="D35" s="2">
-        <v>46141.624513888892</v>
+        <v>46163.479432870372</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G35">
-        <v>767791237</v>
+        <v>103381121</v>
       </c>
       <c r="H35" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I35" t="s">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="K35" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M35" t="s">
         <v>7</v>
@@ -3101,48 +3082,48 @@
         <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>60972166</v>
+        <v>61242033</v>
       </c>
       <c r="B36" s="2">
-        <v>46114.708020833335</v>
+        <v>46120.643912037034</v>
       </c>
       <c r="C36">
-        <v>62949578</v>
+        <v>62945857</v>
       </c>
       <c r="D36" s="2">
-        <v>46150.482407407406</v>
+        <v>46150.456064814818</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G36">
-        <v>160128782</v>
+        <v>747636152</v>
       </c>
       <c r="H36" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="I36" t="s">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="K36" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N36" t="s">
         <v>107</v>
@@ -3150,37 +3131,37 @@
       <c r="O36" t="s">
         <v>0</v>
       </c>
-      <c r="P36" s="1">
-        <v>800000</v>
+      <c r="P36">
+        <v>0</v>
       </c>
       <c r="Q36" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>61239047</v>
+        <v>61244524</v>
       </c>
       <c r="B37" s="2">
-        <v>46120.622071759259</v>
+        <v>46120.66065972222</v>
       </c>
       <c r="C37">
-        <v>64795668</v>
+        <v>64793029</v>
       </c>
       <c r="D37" s="2">
-        <v>46185.651990740742</v>
+        <v>46185.633090277777</v>
       </c>
       <c r="E37" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="F37" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G37">
-        <v>103381121</v>
+        <v>757818829</v>
       </c>
       <c r="H37" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="I37" t="s">
         <v>0</v>
@@ -3203,37 +3184,37 @@
       <c r="O37" t="s">
         <v>0</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="s">
         <v>0</v>
       </c>
       <c r="Q37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>61240327</v>
+        <v>61248751</v>
       </c>
       <c r="B38" s="2">
-        <v>46120.631747685184</v>
+        <v>46120.692800925928</v>
       </c>
       <c r="C38">
-        <v>63643159</v>
+        <v>64698839</v>
       </c>
       <c r="D38" s="2">
-        <v>46163.479432870372</v>
+        <v>46184.382604166669</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G38">
-        <v>103381121</v>
+        <v>747636152</v>
       </c>
       <c r="H38" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="I38" t="s">
         <v>0</v>
@@ -3242,7 +3223,7 @@
         <v>67</v>
       </c>
       <c r="K38" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L38" t="s">
         <v>2</v>
@@ -3260,45 +3241,45 @@
         <v>0</v>
       </c>
       <c r="Q38" t="s">
-        <v>34</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>61242033</v>
+        <v>61255901</v>
       </c>
       <c r="B39" s="2">
-        <v>46120.643912037034</v>
+        <v>46120.75712962963</v>
       </c>
       <c r="C39">
-        <v>62945857</v>
+        <v>62951388</v>
       </c>
       <c r="D39" s="2">
-        <v>46150.456064814818</v>
+        <v>46150.494675925926</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G39">
-        <v>747636152</v>
+        <v>757818829</v>
       </c>
       <c r="H39" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="I39" t="s">
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K39" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L39" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M39" t="s">
         <v>7</v>
@@ -3313,51 +3294,51 @@
         <v>0</v>
       </c>
       <c r="Q39" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>61244524</v>
+        <v>61315991</v>
       </c>
       <c r="B40" s="2">
-        <v>46120.66065972222</v>
+        <v>46121.743379629632</v>
       </c>
       <c r="C40">
-        <v>64793029</v>
+        <v>63689089</v>
       </c>
       <c r="D40" s="2">
-        <v>46185.633090277777</v>
+        <v>46164.351643518516</v>
       </c>
       <c r="E40" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G40">
-        <v>757818829</v>
+        <v>778495680</v>
       </c>
       <c r="H40" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="I40" t="s">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L40" t="s">
         <v>2</v>
       </c>
       <c r="M40" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N40" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O40" t="s">
         <v>0</v>
@@ -3366,48 +3347,48 @@
         <v>0</v>
       </c>
       <c r="Q40" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>61248751</v>
+        <v>61336527</v>
       </c>
       <c r="B41" s="2">
-        <v>46120.692800925928</v>
+        <v>46122.368761574071</v>
       </c>
       <c r="C41">
-        <v>64698839</v>
+        <v>63643262</v>
       </c>
       <c r="D41" s="2">
-        <v>46184.382604166669</v>
+        <v>46163.480023148149</v>
       </c>
       <c r="E41" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G41">
-        <v>747636152</v>
+        <v>778495680</v>
       </c>
       <c r="H41" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="I41" t="s">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K41" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L41" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M41" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N41" t="s">
         <v>107</v>
@@ -3415,52 +3396,52 @@
       <c r="O41" t="s">
         <v>0</v>
       </c>
-      <c r="P41">
-        <v>0</v>
+      <c r="P41" s="1">
+        <v>1679940</v>
       </c>
       <c r="Q41" t="s">
-        <v>182</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>61255901</v>
+        <v>61481328</v>
       </c>
       <c r="B42" s="2">
-        <v>46120.75712962963</v>
+        <v>46125.483310185184</v>
       </c>
       <c r="C42">
-        <v>62951388</v>
+        <v>62173555</v>
       </c>
       <c r="D42" s="2">
-        <v>46150.494675925926</v>
+        <v>46136.44263888889</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F42" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G42">
-        <v>757818829</v>
+        <v>708448800</v>
       </c>
       <c r="H42" t="s">
-        <v>104</v>
-      </c>
-      <c r="I42" t="s">
-        <v>0</v>
+        <v>148</v>
+      </c>
+      <c r="I42">
+        <v>1891736</v>
       </c>
       <c r="J42" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L42" t="s">
         <v>8</v>
       </c>
       <c r="M42" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N42" t="s">
         <v>107</v>
@@ -3468,49 +3449,49 @@
       <c r="O42" t="s">
         <v>0</v>
       </c>
-      <c r="P42">
-        <v>0</v>
+      <c r="P42" s="1">
+        <v>500000</v>
       </c>
       <c r="Q42" t="s">
-        <v>73</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>61315991</v>
+        <v>61504448</v>
       </c>
       <c r="B43" s="2">
-        <v>46121.743379629632</v>
+        <v>46125.648935185185</v>
       </c>
       <c r="C43">
-        <v>63689089</v>
+        <v>62115179</v>
       </c>
       <c r="D43" s="2">
-        <v>46164.351643518516</v>
+        <v>46135.481111111112</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G43">
-        <v>778495680</v>
+        <v>707234610</v>
       </c>
       <c r="H43" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="I43" t="s">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K43" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L43" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M43" t="s">
         <v>3</v>
@@ -3521,49 +3502,49 @@
       <c r="O43" t="s">
         <v>0</v>
       </c>
-      <c r="P43" t="s">
-        <v>0</v>
+      <c r="P43" s="1">
+        <v>3070672</v>
       </c>
       <c r="Q43" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>61336527</v>
+        <v>61509953</v>
       </c>
       <c r="B44" s="2">
-        <v>46122.368761574071</v>
+        <v>46125.694004629629</v>
       </c>
       <c r="C44">
-        <v>63643262</v>
+        <v>62751418</v>
       </c>
       <c r="D44" s="2">
-        <v>46163.480023148149</v>
+        <v>46147.490636574075</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="F44" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="G44">
-        <v>778495680</v>
+        <v>759379440</v>
       </c>
       <c r="H44" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="I44" t="s">
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L44" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M44" t="s">
         <v>3</v>
@@ -3574,46 +3555,46 @@
       <c r="O44" t="s">
         <v>0</v>
       </c>
-      <c r="P44" s="1">
-        <v>1679940</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>97</v>
+      <c r="P44" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>2732780110</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>61481328</v>
+        <v>61560663</v>
       </c>
       <c r="B45" s="2">
-        <v>46125.483310185184</v>
+        <v>46126.615729166668</v>
       </c>
       <c r="C45">
-        <v>62173555</v>
+        <v>62946623</v>
       </c>
       <c r="D45" s="2">
-        <v>46136.44263888889</v>
+        <v>46150.461550925924</v>
       </c>
       <c r="E45" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G45">
-        <v>708448800</v>
+        <v>707984429</v>
       </c>
       <c r="H45" t="s">
-        <v>148</v>
-      </c>
-      <c r="I45">
-        <v>1891736</v>
+        <v>89</v>
+      </c>
+      <c r="I45" t="s">
+        <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K45" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L45" t="s">
         <v>8</v>
@@ -3628,48 +3609,48 @@
         <v>0</v>
       </c>
       <c r="P45" s="1">
-        <v>500000</v>
+        <v>2984038</v>
       </c>
       <c r="Q45" t="s">
-        <v>149</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>61504448</v>
+        <v>61608637</v>
       </c>
       <c r="B46" s="2">
-        <v>46125.648935185185</v>
+        <v>46127.491550925923</v>
       </c>
       <c r="C46">
-        <v>62115179</v>
+        <v>61677257</v>
       </c>
       <c r="D46" s="2">
-        <v>46135.481111111112</v>
+        <v>46128.483958333331</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F46" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G46">
-        <v>707234610</v>
+        <v>702455701</v>
       </c>
       <c r="H46" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="I46" t="s">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L46" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M46" t="s">
         <v>3</v>
@@ -3680,49 +3661,49 @@
       <c r="O46" t="s">
         <v>0</v>
       </c>
-      <c r="P46" s="1">
-        <v>3070672</v>
+      <c r="P46" t="s">
+        <v>0</v>
       </c>
       <c r="Q46" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>61509953</v>
+        <v>61644382</v>
       </c>
       <c r="B47" s="2">
-        <v>46125.694004629629</v>
+        <v>46127.754131944443</v>
       </c>
       <c r="C47">
-        <v>62751418</v>
+        <v>61977733</v>
       </c>
       <c r="D47" s="2">
-        <v>46147.490636574075</v>
+        <v>46133.466458333336</v>
       </c>
       <c r="E47" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="G47">
-        <v>759379440</v>
+        <v>759250737</v>
       </c>
       <c r="H47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I47" t="s">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K47" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L47" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M47" t="s">
         <v>3</v>
@@ -3733,49 +3714,49 @@
       <c r="O47" t="s">
         <v>0</v>
       </c>
-      <c r="P47" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>2732780110</v>
+      <c r="P47" s="1">
+        <v>1680307</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>61560663</v>
+        <v>61946442</v>
       </c>
       <c r="B48" s="2">
-        <v>46126.615729166668</v>
+        <v>46132.704247685186</v>
       </c>
       <c r="C48">
-        <v>62946623</v>
+        <v>62946744</v>
       </c>
       <c r="D48" s="2">
-        <v>46150.461550925924</v>
+        <v>46150.462650462963</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="G48">
-        <v>707984429</v>
+        <v>504041812</v>
       </c>
       <c r="H48" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="I48" t="s">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K48" t="s">
         <v>5</v>
       </c>
       <c r="L48" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M48" t="s">
         <v>3</v>
@@ -3787,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="1">
-        <v>2984038</v>
+        <v>1000000</v>
       </c>
       <c r="Q48" t="s">
         <v>23</v>
@@ -3795,43 +3776,43 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>61608637</v>
+        <v>61972088</v>
       </c>
       <c r="B49" s="2">
-        <v>46127.491550925923</v>
+        <v>46133.422569444447</v>
       </c>
       <c r="C49">
-        <v>61677257</v>
+        <v>64146321</v>
       </c>
       <c r="D49" s="2">
-        <v>46128.483958333331</v>
+        <v>46174.477534722224</v>
       </c>
       <c r="E49" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G49">
-        <v>702455701</v>
+        <v>504041812</v>
       </c>
       <c r="H49" t="s">
-        <v>36</v>
+        <v>151</v>
       </c>
       <c r="I49" t="s">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K49" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L49" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M49" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N49" t="s">
         <v>107</v>
@@ -3843,33 +3824,33 @@
         <v>0</v>
       </c>
       <c r="Q49" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>61644382</v>
+        <v>61972108</v>
       </c>
       <c r="B50" s="2">
-        <v>46127.754131944443</v>
+        <v>46133.422662037039</v>
       </c>
       <c r="C50">
-        <v>61977733</v>
+        <v>62946845</v>
       </c>
       <c r="D50" s="2">
-        <v>46133.466458333336</v>
+        <v>46150.463449074072</v>
       </c>
       <c r="E50" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="G50">
-        <v>759250737</v>
+        <v>504041812</v>
       </c>
       <c r="H50" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="I50" t="s">
         <v>0</v>
@@ -3878,13 +3859,13 @@
         <v>17</v>
       </c>
       <c r="K50" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L50" t="s">
         <v>8</v>
       </c>
       <c r="M50" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N50" t="s">
         <v>107</v>
@@ -3893,48 +3874,48 @@
         <v>0</v>
       </c>
       <c r="P50" s="1">
-        <v>1680307</v>
+        <v>1000000</v>
       </c>
       <c r="Q50" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>61946442</v>
+        <v>62420329</v>
       </c>
       <c r="B51" s="2">
-        <v>46132.704247685186</v>
+        <v>46140.709513888891</v>
       </c>
       <c r="C51">
-        <v>62946744</v>
+        <v>64675456</v>
       </c>
       <c r="D51" s="2">
-        <v>46150.462650462963</v>
+        <v>46183.671956018516</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G51">
-        <v>504041812</v>
+        <v>777621987</v>
       </c>
       <c r="H51" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="I51" t="s">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K51" t="s">
         <v>5</v>
       </c>
       <c r="L51" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M51" t="s">
         <v>3</v>
@@ -3946,54 +3927,51 @@
         <v>0</v>
       </c>
       <c r="P51" s="1">
-        <v>1000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q51" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>61972088</v>
+        <v>62497009</v>
       </c>
       <c r="B52" s="2">
-        <v>46133.422569444447</v>
+        <v>46141.808842592596</v>
       </c>
       <c r="C52">
-        <v>64146321</v>
+        <v>63458983</v>
       </c>
       <c r="D52" s="2">
-        <v>46174.477534722224</v>
+        <v>46160.501875000002</v>
       </c>
       <c r="E52" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F52" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G52">
-        <v>504041812</v>
+        <v>702495660</v>
       </c>
       <c r="H52" t="s">
-        <v>151</v>
+        <v>36</v>
       </c>
       <c r="I52" t="s">
         <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L52" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M52" t="s">
-        <v>7</v>
-      </c>
-      <c r="N52" t="s">
-        <v>107</v>
+        <v>3</v>
       </c>
       <c r="O52" t="s">
         <v>0</v>
@@ -4002,101 +3980,98 @@
         <v>0</v>
       </c>
       <c r="Q52" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>61972108</v>
+        <v>62551370</v>
       </c>
       <c r="B53" s="2">
-        <v>46133.422662037039</v>
+        <v>46142.717349537037</v>
       </c>
       <c r="C53">
-        <v>62946845</v>
+        <v>63134483</v>
       </c>
       <c r="D53" s="2">
-        <v>46150.463449074072</v>
+        <v>46154.380196759259</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F53" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G53">
-        <v>504041812</v>
+        <v>576382850</v>
       </c>
       <c r="H53" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I53" t="s">
         <v>0</v>
       </c>
       <c r="J53" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L53" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M53" t="s">
-        <v>13</v>
-      </c>
-      <c r="N53" t="s">
-        <v>107</v>
+        <v>3</v>
       </c>
       <c r="O53" t="s">
         <v>0</v>
       </c>
-      <c r="P53" s="1">
-        <v>1000000</v>
+      <c r="P53" t="s">
+        <v>0</v>
       </c>
       <c r="Q53" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>62420329</v>
+        <v>62672227</v>
       </c>
       <c r="B54" s="2">
-        <v>46140.709513888891</v>
+        <v>46146.403935185182</v>
       </c>
       <c r="C54">
-        <v>64675456</v>
+        <v>63331081</v>
       </c>
       <c r="D54" s="2">
-        <v>46183.671956018516</v>
+        <v>46157.619120370371</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G54">
-        <v>777621987</v>
+        <v>707169322</v>
       </c>
       <c r="H54" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="I54" t="s">
         <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
       </c>
       <c r="L54" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M54" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N54" t="s">
         <v>107</v>
@@ -4104,46 +4079,46 @@
       <c r="O54" t="s">
         <v>0</v>
       </c>
-      <c r="P54" s="1">
-        <v>1500000</v>
+      <c r="P54" t="s">
+        <v>0</v>
       </c>
       <c r="Q54" t="s">
-        <v>165</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>62497009</v>
+        <v>62680657</v>
       </c>
       <c r="B55" s="2">
-        <v>46141.808842592596</v>
+        <v>46146.475763888891</v>
       </c>
       <c r="C55">
-        <v>63458983</v>
+        <v>63485029</v>
       </c>
       <c r="D55" s="2">
-        <v>46160.501875000002</v>
+        <v>46160.702488425923</v>
       </c>
       <c r="E55" t="s">
         <v>22</v>
       </c>
       <c r="F55" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G55">
-        <v>702495660</v>
+        <v>778096389</v>
       </c>
       <c r="H55" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="I55" t="s">
         <v>0</v>
       </c>
       <c r="J55" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="K55" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L55" t="s">
         <v>2</v>
@@ -4157,34 +4132,34 @@
       <c r="P55" t="s">
         <v>0</v>
       </c>
-      <c r="Q55" t="s">
-        <v>110</v>
+      <c r="Q55">
+        <v>2722560110</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>62551370</v>
+        <v>62722805</v>
       </c>
       <c r="B56" s="2">
-        <v>46142.717349537037</v>
+        <v>46146.81181712963</v>
       </c>
       <c r="C56">
-        <v>63134483</v>
+        <v>64261496</v>
       </c>
       <c r="D56" s="2">
-        <v>46154.380196759259</v>
+        <v>46176.409166666665</v>
       </c>
       <c r="E56" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G56">
-        <v>576382850</v>
+        <v>708131488</v>
       </c>
       <c r="H56" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I56" t="s">
         <v>0</v>
@@ -4201,6 +4176,9 @@
       <c r="M56" t="s">
         <v>3</v>
       </c>
+      <c r="N56" t="s">
+        <v>107</v>
+      </c>
       <c r="O56" t="s">
         <v>0</v>
       </c>
@@ -4208,51 +4186,51 @@
         <v>0</v>
       </c>
       <c r="Q56" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>62672227</v>
+        <v>62760027</v>
       </c>
       <c r="B57" s="2">
-        <v>46146.403935185182</v>
+        <v>46147.546493055554</v>
       </c>
       <c r="C57">
-        <v>63331081</v>
+        <v>64614114</v>
       </c>
       <c r="D57" s="2">
-        <v>46157.619120370371</v>
+        <v>46182.695092592592</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F57" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G57">
-        <v>707169322</v>
+        <v>777699799</v>
       </c>
       <c r="H57" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="I57" t="s">
         <v>0</v>
       </c>
       <c r="J57" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K57" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L57" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M57" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O57" t="s">
         <v>0</v>
@@ -4261,95 +4239,98 @@
         <v>0</v>
       </c>
       <c r="Q57" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>62680657</v>
+        <v>62768013</v>
       </c>
       <c r="B58" s="2">
-        <v>46146.475763888891</v>
+        <v>46147.609988425924</v>
       </c>
       <c r="C58">
-        <v>63485029</v>
+        <v>62871386</v>
       </c>
       <c r="D58" s="2">
-        <v>46160.702488425923</v>
+        <v>46149.364837962959</v>
       </c>
       <c r="E58" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="F58" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G58">
-        <v>778096389</v>
+        <v>143270405</v>
       </c>
       <c r="H58" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="I58" t="s">
         <v>0</v>
       </c>
       <c r="J58" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="K58" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L58" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M58" t="s">
         <v>3</v>
       </c>
+      <c r="N58" t="s">
+        <v>107</v>
+      </c>
       <c r="O58" t="s">
         <v>0</v>
       </c>
       <c r="P58" t="s">
         <v>0</v>
       </c>
-      <c r="Q58">
-        <v>2722560110</v>
+      <c r="Q58" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>62722805</v>
+        <v>63025600</v>
       </c>
       <c r="B59" s="2">
-        <v>46146.81181712963</v>
+        <v>46151.740983796299</v>
       </c>
       <c r="C59">
-        <v>64261496</v>
+        <v>63981861</v>
       </c>
       <c r="D59" s="2">
-        <v>46176.409166666665</v>
+        <v>46170.692743055559</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G59">
-        <v>708131488</v>
+        <v>758237461</v>
       </c>
       <c r="H59" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="I59" t="s">
         <v>0</v>
       </c>
       <c r="J59" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K59" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L59" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M59" t="s">
         <v>3</v>
@@ -4360,90 +4341,90 @@
       <c r="O59" t="s">
         <v>0</v>
       </c>
-      <c r="P59" t="s">
-        <v>0</v>
+      <c r="P59" s="1">
+        <v>850000</v>
       </c>
       <c r="Q59" t="s">
-        <v>100</v>
+        <v>184</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>62760027</v>
+        <v>63168095</v>
       </c>
       <c r="B60" s="2">
-        <v>46147.546493055554</v>
+        <v>46154.647604166668</v>
       </c>
       <c r="C60">
-        <v>64614114</v>
+        <v>64649156</v>
       </c>
       <c r="D60" s="2">
-        <v>46182.695092592592</v>
+        <v>46183.463506944441</v>
       </c>
       <c r="E60" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F60" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
       <c r="G60">
-        <v>777699799</v>
+        <v>747345191</v>
       </c>
       <c r="H60" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I60" t="s">
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K60" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L60" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M60" t="s">
         <v>3</v>
       </c>
       <c r="N60" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O60" t="s">
         <v>0</v>
       </c>
-      <c r="P60" t="s">
-        <v>0</v>
+      <c r="P60" s="1">
+        <v>7103410</v>
       </c>
       <c r="Q60" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>62768013</v>
+        <v>63179342</v>
       </c>
       <c r="B61" s="2">
-        <v>46147.609988425924</v>
+        <v>46154.735729166663</v>
       </c>
       <c r="C61">
-        <v>62871386</v>
+        <v>64526824</v>
       </c>
       <c r="D61" s="2">
-        <v>46149.364837962959</v>
+        <v>46181.499490740738</v>
       </c>
       <c r="E61" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="F61" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G61">
-        <v>143270405</v>
+        <v>778179203</v>
       </c>
       <c r="H61" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="I61" t="s">
         <v>0</v>
@@ -4452,7 +4433,7 @@
         <v>17</v>
       </c>
       <c r="K61" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L61" t="s">
         <v>8</v>
@@ -4466,102 +4447,102 @@
       <c r="O61" t="s">
         <v>0</v>
       </c>
-      <c r="P61" t="s">
-        <v>0</v>
+      <c r="P61" s="1">
+        <v>2000000</v>
       </c>
       <c r="Q61" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>63025600</v>
+        <v>63210811</v>
       </c>
       <c r="B62" s="2">
-        <v>46151.740983796299</v>
+        <v>46155.50409722222</v>
       </c>
       <c r="C62">
-        <v>63981861</v>
+        <v>64743989</v>
       </c>
       <c r="D62" s="2">
-        <v>46170.692743055559</v>
+        <v>46184.729155092595</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F62" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="G62">
-        <v>758237461</v>
+        <v>160128782</v>
       </c>
       <c r="H62" t="s">
-        <v>171</v>
-      </c>
-      <c r="I62" t="s">
-        <v>0</v>
+        <v>244</v>
+      </c>
+      <c r="I62">
+        <v>1951416</v>
       </c>
       <c r="J62" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K62" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L62" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M62" t="s">
-        <v>3</v>
+        <v>181</v>
       </c>
       <c r="N62" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O62" t="s">
         <v>0</v>
       </c>
       <c r="P62" s="1">
-        <v>850000</v>
+        <v>800000</v>
       </c>
       <c r="Q62" t="s">
-        <v>184</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>63168095</v>
+        <v>63453142</v>
       </c>
       <c r="B63" s="2">
-        <v>46154.647604166668</v>
+        <v>46160.461238425924</v>
       </c>
       <c r="C63">
-        <v>64649156</v>
+        <v>63982556</v>
       </c>
       <c r="D63" s="2">
-        <v>46183.463506944441</v>
+        <v>46170.697962962964</v>
       </c>
       <c r="E63" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="G63">
-        <v>747345191</v>
+        <v>507828407</v>
       </c>
       <c r="H63" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I63" t="s">
         <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K63" t="s">
         <v>5</v>
       </c>
       <c r="L63" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M63" t="s">
         <v>3</v>
@@ -4573,7 +4554,7 @@
         <v>0</v>
       </c>
       <c r="P63" s="1">
-        <v>7103410</v>
+        <v>1009545</v>
       </c>
       <c r="Q63" t="s">
         <v>23</v>
@@ -4581,199 +4562,199 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>63179342</v>
+        <v>63462158</v>
       </c>
       <c r="B64" s="2">
-        <v>46154.735729166663</v>
+        <v>46160.525254629632</v>
       </c>
       <c r="C64">
-        <v>64526824</v>
+        <v>63498261</v>
       </c>
       <c r="D64" s="2">
-        <v>46181.499490740738</v>
+        <v>46160.901041666664</v>
       </c>
       <c r="E64" t="s">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="F64" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G64">
-        <v>778179203</v>
+        <v>768231346</v>
       </c>
       <c r="H64" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="I64" t="s">
         <v>0</v>
       </c>
       <c r="J64" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K64" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="L64" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M64" t="s">
         <v>3</v>
       </c>
       <c r="N64" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O64" t="s">
         <v>0</v>
       </c>
       <c r="P64" s="1">
-        <v>2000000</v>
+        <v>518450</v>
       </c>
       <c r="Q64" t="s">
-        <v>183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>63210811</v>
+        <v>63477655</v>
       </c>
       <c r="B65" s="2">
-        <v>46155.50409722222</v>
+        <v>46160.651041666664</v>
       </c>
       <c r="C65">
-        <v>64685899</v>
+        <v>64785597</v>
       </c>
       <c r="D65" s="2">
-        <v>46183.762511574074</v>
+        <v>46185.578194444446</v>
       </c>
       <c r="E65" t="s">
-        <v>244</v>
+        <v>58</v>
       </c>
       <c r="F65" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="G65">
-        <v>160128782</v>
+        <v>709528212</v>
       </c>
       <c r="H65" t="s">
-        <v>251</v>
-      </c>
-      <c r="I65">
-        <v>1951416</v>
+        <v>186</v>
+      </c>
+      <c r="I65" t="s">
+        <v>0</v>
       </c>
       <c r="J65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="L65" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M65" t="s">
-        <v>181</v>
+        <v>3</v>
       </c>
       <c r="N65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O65" t="s">
         <v>0</v>
       </c>
-      <c r="P65" s="1">
-        <v>800000</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>252</v>
+      <c r="P65" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>2721712160</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>63210811</v>
+        <v>63526115</v>
       </c>
       <c r="B66" s="2">
-        <v>46155.50409722222</v>
+        <v>46161.544733796298</v>
       </c>
       <c r="C66">
-        <v>64743989</v>
+        <v>64146684</v>
       </c>
       <c r="D66" s="2">
-        <v>46184.729155092595</v>
+        <v>46174.480104166665</v>
       </c>
       <c r="E66" t="s">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="F66" t="s">
-        <v>122</v>
+        <v>187</v>
       </c>
       <c r="G66">
-        <v>160128782</v>
+        <v>707722441</v>
       </c>
       <c r="H66" t="s">
-        <v>251</v>
-      </c>
-      <c r="I66">
-        <v>1951416</v>
+        <v>188</v>
+      </c>
+      <c r="I66" t="s">
+        <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K66" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L66" t="s">
         <v>8</v>
       </c>
       <c r="M66" t="s">
-        <v>181</v>
+        <v>3</v>
       </c>
       <c r="N66" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O66" t="s">
         <v>0</v>
       </c>
       <c r="P66" s="1">
-        <v>800000</v>
+        <v>1513624</v>
       </c>
       <c r="Q66" t="s">
-        <v>252</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>63453142</v>
+        <v>63529958</v>
       </c>
       <c r="B67" s="2">
-        <v>46160.461238425924</v>
+        <v>46161.577581018515</v>
       </c>
       <c r="C67">
-        <v>63982556</v>
+        <v>64738332</v>
       </c>
       <c r="D67" s="2">
-        <v>46170.697962962964</v>
+        <v>46184.686076388891</v>
       </c>
       <c r="E67" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F67" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="G67">
-        <v>507828407</v>
+        <v>708081052</v>
       </c>
       <c r="H67" t="s">
-        <v>178</v>
-      </c>
-      <c r="I67" t="s">
-        <v>0</v>
+        <v>213</v>
+      </c>
+      <c r="I67">
+        <v>1943146</v>
       </c>
       <c r="J67" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K67" t="s">
         <v>5</v>
       </c>
       <c r="L67" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M67" t="s">
         <v>3</v>
@@ -4785,36 +4766,36 @@
         <v>0</v>
       </c>
       <c r="P67" s="1">
-        <v>1009545</v>
+        <v>655375</v>
       </c>
       <c r="Q67" t="s">
-        <v>23</v>
+        <v>214</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>63462158</v>
+        <v>63556908</v>
       </c>
       <c r="B68" s="2">
-        <v>46160.525254629632</v>
+        <v>46161.788553240738</v>
       </c>
       <c r="C68">
-        <v>63498261</v>
+        <v>64260259</v>
       </c>
       <c r="D68" s="2">
-        <v>46160.901041666664</v>
+        <v>46176.402372685188</v>
       </c>
       <c r="E68" t="s">
-        <v>164</v>
+        <v>10</v>
       </c>
       <c r="F68" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G68">
-        <v>768231346</v>
+        <v>711458931</v>
       </c>
       <c r="H68" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I68" t="s">
         <v>0</v>
@@ -4823,7 +4804,7 @@
         <v>12</v>
       </c>
       <c r="K68" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="L68" t="s">
         <v>6</v>
@@ -4832,148 +4813,148 @@
         <v>3</v>
       </c>
       <c r="N68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O68" t="s">
         <v>0</v>
       </c>
       <c r="P68" s="1">
-        <v>518450</v>
+        <v>1000000</v>
       </c>
       <c r="Q68" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>63477655</v>
+        <v>63577039</v>
       </c>
       <c r="B69" s="2">
-        <v>46160.651041666664</v>
+        <v>46162.450127314813</v>
       </c>
       <c r="C69">
-        <v>64725398</v>
+        <v>64761677</v>
       </c>
       <c r="D69" s="2">
-        <v>46184.600763888891</v>
+        <v>46185.374467592592</v>
       </c>
       <c r="E69" t="s">
-        <v>253</v>
+        <v>15</v>
       </c>
       <c r="F69" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G69">
-        <v>709528212</v>
+        <v>716610940</v>
       </c>
       <c r="H69" t="s">
-        <v>186</v>
+        <v>88</v>
       </c>
       <c r="I69" t="s">
         <v>0</v>
       </c>
       <c r="J69" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K69" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="L69" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M69" t="s">
         <v>3</v>
       </c>
       <c r="N69" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O69" t="s">
         <v>0</v>
       </c>
-      <c r="P69" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>2721712160</v>
+      <c r="P69" s="1">
+        <v>299185</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>63477655</v>
+        <v>63578582</v>
       </c>
       <c r="B70" s="2">
-        <v>46160.651041666664</v>
+        <v>46162.462199074071</v>
       </c>
       <c r="C70">
-        <v>64785597</v>
+        <v>64770374</v>
       </c>
       <c r="D70" s="2">
-        <v>46185.578194444446</v>
+        <v>46185.457557870373</v>
       </c>
       <c r="E70" t="s">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="F70" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G70">
-        <v>709528212</v>
+        <v>759974992</v>
       </c>
       <c r="H70" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I70" t="s">
         <v>0</v>
       </c>
       <c r="J70" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="K70" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L70" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M70" t="s">
         <v>3</v>
       </c>
       <c r="N70" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O70" t="s">
         <v>0</v>
       </c>
-      <c r="P70" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>2721712160</v>
+      <c r="P70" s="1">
+        <v>4487314</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>63526115</v>
+        <v>63595239</v>
       </c>
       <c r="B71" s="2">
-        <v>46161.544733796298</v>
+        <v>46162.588333333333</v>
       </c>
       <c r="C71">
-        <v>64146684</v>
+        <v>64589681</v>
       </c>
       <c r="D71" s="2">
-        <v>46174.480104166665</v>
+        <v>46182.503379629627</v>
       </c>
       <c r="E71" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="F71" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="G71">
-        <v>707722441</v>
+        <v>749194205</v>
       </c>
       <c r="H71" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="I71" t="s">
         <v>0</v>
@@ -4996,49 +4977,49 @@
       <c r="O71" t="s">
         <v>0</v>
       </c>
-      <c r="P71" s="1">
-        <v>1513624</v>
+      <c r="P71" t="s">
+        <v>0</v>
       </c>
       <c r="Q71" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>63529958</v>
+        <v>63610581</v>
       </c>
       <c r="B72" s="2">
-        <v>46161.577581018515</v>
+        <v>46162.70239583333</v>
       </c>
       <c r="C72">
-        <v>64738332</v>
+        <v>64677326</v>
       </c>
       <c r="D72" s="2">
-        <v>46184.686076388891</v>
+        <v>46183.68550925926</v>
       </c>
       <c r="E72" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F72" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="G72">
-        <v>708081052</v>
+        <v>799642361</v>
       </c>
       <c r="H72" t="s">
-        <v>213</v>
-      </c>
-      <c r="I72">
-        <v>1943146</v>
+        <v>198</v>
+      </c>
+      <c r="I72" t="s">
+        <v>0</v>
       </c>
       <c r="J72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K72" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L72" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M72" t="s">
         <v>3</v>
@@ -5049,49 +5030,49 @@
       <c r="O72" t="s">
         <v>0</v>
       </c>
-      <c r="P72" s="1">
-        <v>655375</v>
+      <c r="P72" t="s">
+        <v>0</v>
       </c>
       <c r="Q72" t="s">
-        <v>214</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>63556908</v>
+        <v>63611129</v>
       </c>
       <c r="B73" s="2">
-        <v>46161.788553240738</v>
+        <v>46162.70616898148</v>
       </c>
       <c r="C73">
-        <v>64260259</v>
+        <v>64607265</v>
       </c>
       <c r="D73" s="2">
-        <v>46176.402372685188</v>
+        <v>46182.646550925929</v>
       </c>
       <c r="E73" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F73" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="G73">
-        <v>711458931</v>
+        <v>799642361</v>
       </c>
       <c r="H73" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="I73" t="s">
         <v>0</v>
       </c>
       <c r="J73" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K73" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L73" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M73" t="s">
         <v>3</v>
@@ -5102,37 +5083,37 @@
       <c r="O73" t="s">
         <v>0</v>
       </c>
-      <c r="P73" s="1">
-        <v>1000000</v>
+      <c r="P73" t="s">
+        <v>0</v>
       </c>
       <c r="Q73" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>63577039</v>
+        <v>63643964</v>
       </c>
       <c r="B74" s="2">
-        <v>46162.450127314813</v>
+        <v>46163.485543981478</v>
       </c>
       <c r="C74">
-        <v>64761677</v>
+        <v>64643943</v>
       </c>
       <c r="D74" s="2">
-        <v>46185.374467592592</v>
+        <v>46183.423136574071</v>
       </c>
       <c r="E74" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="F74" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="G74">
-        <v>716610940</v>
+        <v>718824404</v>
       </c>
       <c r="H74" t="s">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="I74" t="s">
         <v>0</v>
@@ -5156,51 +5137,51 @@
         <v>0</v>
       </c>
       <c r="P74" s="1">
-        <v>299185</v>
+        <v>1000000</v>
       </c>
       <c r="Q74" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>63578582</v>
+        <v>63688978</v>
       </c>
       <c r="B75" s="2">
-        <v>46162.462199074071</v>
+        <v>46164.349548611113</v>
       </c>
       <c r="C75">
-        <v>64770374</v>
+        <v>64799410</v>
       </c>
       <c r="D75" s="2">
-        <v>46185.457557870373</v>
+        <v>46185.679247685184</v>
       </c>
       <c r="E75" t="s">
-        <v>164</v>
+        <v>15</v>
       </c>
       <c r="F75" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G75">
-        <v>759974992</v>
+        <v>709513411</v>
       </c>
       <c r="H75" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="I75" t="s">
         <v>0</v>
       </c>
       <c r="J75" t="s">
-        <v>194</v>
+        <v>12</v>
       </c>
       <c r="K75" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L75" t="s">
         <v>6</v>
       </c>
       <c r="M75" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N75" t="s">
         <v>107</v>
@@ -5208,52 +5189,52 @@
       <c r="O75" t="s">
         <v>0</v>
       </c>
-      <c r="P75" s="1">
-        <v>4487314</v>
+      <c r="P75" t="s">
+        <v>0</v>
       </c>
       <c r="Q75" t="s">
-        <v>57</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>63578582</v>
+        <v>63688990</v>
       </c>
       <c r="B76" s="2">
-        <v>46162.462199074071</v>
+        <v>46164.349618055552</v>
       </c>
       <c r="C76">
-        <v>64770893</v>
+        <v>64800733</v>
       </c>
       <c r="D76" s="2">
-        <v>46185.462025462963</v>
+        <v>46185.689884259256</v>
       </c>
       <c r="E76" t="s">
-        <v>244</v>
+        <v>15</v>
       </c>
       <c r="F76" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G76">
-        <v>759974992</v>
+        <v>709513411</v>
       </c>
       <c r="H76" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="I76" t="s">
         <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>194</v>
+        <v>12</v>
       </c>
       <c r="K76" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L76" t="s">
         <v>6</v>
       </c>
       <c r="M76" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N76" t="s">
         <v>107</v>
@@ -5262,48 +5243,48 @@
         <v>0</v>
       </c>
       <c r="P76" s="1">
-        <v>4487314</v>
+        <v>600000</v>
       </c>
       <c r="Q76" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>63595239</v>
+        <v>63689992</v>
       </c>
       <c r="B77" s="2">
-        <v>46162.588333333333</v>
+        <v>46164.364722222221</v>
       </c>
       <c r="C77">
-        <v>64589681</v>
+        <v>64800881</v>
       </c>
       <c r="D77" s="2">
-        <v>46182.503379629627</v>
+        <v>46185.691354166665</v>
       </c>
       <c r="E77" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="F77" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="G77">
-        <v>749194205</v>
+        <v>709513411</v>
       </c>
       <c r="H77" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="I77" t="s">
         <v>0</v>
       </c>
       <c r="J77" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K77" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L77" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M77" t="s">
         <v>3</v>
@@ -5317,152 +5298,152 @@
       <c r="P77" t="s">
         <v>0</v>
       </c>
-      <c r="Q77" t="s">
-        <v>23</v>
+      <c r="Q77">
+        <v>2722509970</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>63610581</v>
+        <v>63693483</v>
       </c>
       <c r="B78" s="2">
-        <v>46162.70239583333</v>
+        <v>46164.404108796298</v>
       </c>
       <c r="C78">
-        <v>64677326</v>
+        <v>63998411</v>
       </c>
       <c r="D78" s="2">
-        <v>46183.68550925926</v>
+        <v>46171.337291666663</v>
       </c>
       <c r="E78" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F78" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G78">
-        <v>799642361</v>
+        <v>556999292</v>
       </c>
       <c r="H78" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="I78" t="s">
         <v>0</v>
       </c>
       <c r="J78" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K78" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L78" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M78" t="s">
         <v>3</v>
       </c>
       <c r="N78" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O78" t="s">
         <v>0</v>
       </c>
-      <c r="P78" t="s">
-        <v>0</v>
+      <c r="P78" s="1">
+        <v>2200000</v>
       </c>
       <c r="Q78" t="s">
-        <v>30</v>
+        <v>208</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>63611129</v>
+        <v>63695475</v>
       </c>
       <c r="B79" s="2">
-        <v>46162.70616898148</v>
+        <v>46164.422708333332</v>
       </c>
       <c r="C79">
-        <v>64607265</v>
+        <v>64018151</v>
       </c>
       <c r="D79" s="2">
-        <v>46182.646550925929</v>
+        <v>46171.524953703702</v>
       </c>
       <c r="E79" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F79" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G79">
-        <v>799642361</v>
+        <v>556999292</v>
       </c>
       <c r="H79" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="I79" t="s">
         <v>0</v>
       </c>
       <c r="J79" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K79" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L79" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M79" t="s">
         <v>3</v>
       </c>
       <c r="N79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O79" t="s">
         <v>0</v>
       </c>
-      <c r="P79" t="s">
-        <v>0</v>
+      <c r="P79" s="1">
+        <v>2200000</v>
       </c>
       <c r="Q79" t="s">
-        <v>184</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>63643964</v>
+        <v>63705970</v>
       </c>
       <c r="B80" s="2">
-        <v>46163.485543981478</v>
+        <v>46164.501944444448</v>
       </c>
       <c r="C80">
-        <v>64643943</v>
+        <v>64764904</v>
       </c>
       <c r="D80" s="2">
-        <v>46183.423136574071</v>
+        <v>46185.41207175926</v>
       </c>
       <c r="E80" t="s">
-        <v>204</v>
+        <v>15</v>
       </c>
       <c r="F80" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G80">
-        <v>718824404</v>
+        <v>707361318</v>
       </c>
       <c r="H80" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="I80" t="s">
         <v>0</v>
       </c>
       <c r="J80" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K80" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L80" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M80" t="s">
         <v>3</v>
@@ -5474,51 +5455,51 @@
         <v>0</v>
       </c>
       <c r="P80" s="1">
-        <v>1000000</v>
+        <v>2500000</v>
       </c>
       <c r="Q80" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>63688978</v>
+        <v>64005644</v>
       </c>
       <c r="B81" s="2">
-        <v>46164.349548611113</v>
+        <v>46171.424525462964</v>
       </c>
       <c r="C81">
-        <v>64609515</v>
+        <v>64548235</v>
       </c>
       <c r="D81" s="2">
-        <v>46182.662824074076</v>
+        <v>46181.65724537037</v>
       </c>
       <c r="E81" t="s">
-        <v>244</v>
+        <v>117</v>
       </c>
       <c r="F81" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="G81">
-        <v>709513411</v>
+        <v>707109668</v>
       </c>
       <c r="H81" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="I81" t="s">
         <v>0</v>
       </c>
       <c r="J81" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K81" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L81" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M81" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N81" t="s">
         <v>107</v>
@@ -5530,48 +5511,48 @@
         <v>0</v>
       </c>
       <c r="Q81" t="s">
-        <v>217</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>63688978</v>
+        <v>64145330</v>
       </c>
       <c r="B82" s="2">
-        <v>46164.349548611113</v>
+        <v>46174.470370370371</v>
       </c>
       <c r="C82">
-        <v>64799410</v>
+        <v>64800104</v>
       </c>
       <c r="D82" s="2">
-        <v>46185.679247685184</v>
+        <v>46185.684641203705</v>
       </c>
       <c r="E82" t="s">
-        <v>15</v>
+        <v>243</v>
       </c>
       <c r="F82" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="G82">
-        <v>709513411</v>
+        <v>707361318</v>
       </c>
       <c r="H82" t="s">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="I82" t="s">
         <v>0</v>
       </c>
       <c r="J82" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K82" t="s">
         <v>9</v>
       </c>
       <c r="L82" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M82" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N82" t="s">
         <v>107</v>
@@ -5579,52 +5560,52 @@
       <c r="O82" t="s">
         <v>0</v>
       </c>
-      <c r="P82" t="s">
-        <v>0</v>
+      <c r="P82" s="1">
+        <v>2500000</v>
       </c>
       <c r="Q82" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>63688990</v>
+        <v>64149984</v>
       </c>
       <c r="B83" s="2">
-        <v>46164.349618055552</v>
+        <v>46174.503194444442</v>
       </c>
       <c r="C83">
-        <v>64609893</v>
+        <v>64366089</v>
       </c>
       <c r="D83" s="2">
-        <v>46182.66474537037</v>
+        <v>46177.931805555556</v>
       </c>
       <c r="E83" t="s">
-        <v>244</v>
+        <v>18</v>
       </c>
       <c r="F83" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="G83">
-        <v>709513411</v>
+        <v>718151543</v>
       </c>
       <c r="H83" t="s">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="I83" t="s">
         <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K83" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L83" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M83" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N83" t="s">
         <v>107</v>
@@ -5632,52 +5613,52 @@
       <c r="O83" t="s">
         <v>0</v>
       </c>
-      <c r="P83" s="1">
-        <v>600000</v>
+      <c r="P83" t="s">
+        <v>0</v>
       </c>
       <c r="Q83" t="s">
-        <v>218</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>63688990</v>
+        <v>64159836</v>
       </c>
       <c r="B84" s="2">
-        <v>46164.349618055552</v>
+        <v>46174.578506944446</v>
       </c>
       <c r="C84">
-        <v>64800733</v>
+        <v>64797420</v>
       </c>
       <c r="D84" s="2">
-        <v>46185.689884259256</v>
+        <v>46185.663576388892</v>
       </c>
       <c r="E84" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F84" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="G84">
-        <v>709513411</v>
+        <v>788987805</v>
       </c>
       <c r="H84" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="I84" t="s">
         <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K84" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L84" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M84" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N84" t="s">
         <v>107</v>
@@ -5685,37 +5666,37 @@
       <c r="O84" t="s">
         <v>0</v>
       </c>
-      <c r="P84" s="1">
-        <v>600000</v>
+      <c r="P84" t="s">
+        <v>0</v>
       </c>
       <c r="Q84" t="s">
-        <v>218</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>63689992</v>
+        <v>64168091</v>
       </c>
       <c r="B85" s="2">
-        <v>46164.364722222221</v>
+        <v>46174.65016203704</v>
       </c>
       <c r="C85">
-        <v>64609440</v>
+        <v>64793736</v>
       </c>
       <c r="D85" s="2">
-        <v>46182.662499999999</v>
+        <v>46185.638784722221</v>
       </c>
       <c r="E85" t="s">
-        <v>244</v>
+        <v>147</v>
       </c>
       <c r="F85" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="G85">
-        <v>709513411</v>
+        <v>777378597</v>
       </c>
       <c r="H85" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="I85" t="s">
         <v>0</v>
@@ -5733,7 +5714,7 @@
         <v>3</v>
       </c>
       <c r="N85" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O85" t="s">
         <v>0</v>
@@ -5742,33 +5723,33 @@
         <v>0</v>
       </c>
       <c r="Q85">
-        <v>2722509970</v>
+        <v>2724391874</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>63689992</v>
+        <v>64204580</v>
       </c>
       <c r="B86" s="2">
-        <v>46164.364722222221</v>
+        <v>46175.463912037034</v>
       </c>
       <c r="C86">
-        <v>64800881</v>
+        <v>64676754</v>
       </c>
       <c r="D86" s="2">
-        <v>46185.691354166665</v>
+        <v>46183.681331018517</v>
       </c>
       <c r="E86" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="F86" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="G86">
-        <v>709513411</v>
+        <v>779885779</v>
       </c>
       <c r="H86" t="s">
-        <v>205</v>
+        <v>36</v>
       </c>
       <c r="I86" t="s">
         <v>0</v>
@@ -5777,7 +5758,7 @@
         <v>21</v>
       </c>
       <c r="K86" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L86" t="s">
         <v>2</v>
@@ -5786,7 +5767,7 @@
         <v>3</v>
       </c>
       <c r="N86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O86" t="s">
         <v>0</v>
@@ -5794,87 +5775,87 @@
       <c r="P86" t="s">
         <v>0</v>
       </c>
-      <c r="Q86">
-        <v>2722509970</v>
+      <c r="Q86" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>63693483</v>
+        <v>64298334</v>
       </c>
       <c r="B87" s="2">
-        <v>46164.404108796298</v>
+        <v>46176.697557870371</v>
       </c>
       <c r="C87">
-        <v>63998411</v>
+        <v>64494332</v>
       </c>
       <c r="D87" s="2">
-        <v>46171.337291666663</v>
+        <v>46180.813113425924</v>
       </c>
       <c r="E87" t="s">
-        <v>164</v>
+        <v>10</v>
       </c>
       <c r="F87" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="G87">
-        <v>556999292</v>
+        <v>102435520</v>
       </c>
       <c r="H87" t="s">
-        <v>207</v>
+        <v>74</v>
       </c>
       <c r="I87" t="s">
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K87" t="s">
         <v>5</v>
       </c>
       <c r="L87" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M87" t="s">
         <v>3</v>
       </c>
       <c r="N87" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O87" t="s">
         <v>0</v>
       </c>
       <c r="P87" s="1">
-        <v>2200000</v>
+        <v>1000000</v>
       </c>
       <c r="Q87" t="s">
-        <v>208</v>
+        <v>57</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>63695475</v>
+        <v>64299624</v>
       </c>
       <c r="B88" s="2">
-        <v>46164.422708333332</v>
+        <v>46176.705578703702</v>
       </c>
       <c r="C88">
-        <v>64018151</v>
+        <v>64697050</v>
       </c>
       <c r="D88" s="2">
-        <v>46171.524953703702</v>
+        <v>46184.353541666664</v>
       </c>
       <c r="E88" t="s">
-        <v>164</v>
+        <v>247</v>
       </c>
       <c r="F88" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="G88">
-        <v>556999292</v>
+        <v>789196850</v>
       </c>
       <c r="H88" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="I88" t="s">
         <v>0</v>
@@ -5889,45 +5870,45 @@
         <v>8</v>
       </c>
       <c r="M88" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N88" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O88" t="s">
         <v>0</v>
       </c>
-      <c r="P88" s="1">
-        <v>2200000</v>
+      <c r="P88" t="s">
+        <v>0</v>
       </c>
       <c r="Q88" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>63705970</v>
+        <v>64299644</v>
       </c>
       <c r="B89" s="2">
-        <v>46164.501944444448</v>
+        <v>46176.705625000002</v>
       </c>
       <c r="C89">
-        <v>64764904</v>
+        <v>64697118</v>
       </c>
       <c r="D89" s="2">
-        <v>46185.41207175926</v>
+        <v>46184.354618055557</v>
       </c>
       <c r="E89" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="F89" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="G89">
-        <v>707361318</v>
+        <v>789196850</v>
       </c>
       <c r="H89" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="I89" t="s">
         <v>0</v>
@@ -5942,57 +5923,57 @@
         <v>8</v>
       </c>
       <c r="M89" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N89" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O89" t="s">
         <v>0</v>
       </c>
       <c r="P89" s="1">
-        <v>2500000</v>
+        <v>5324000</v>
       </c>
       <c r="Q89" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>64005644</v>
+        <v>64327001</v>
       </c>
       <c r="B90" s="2">
-        <v>46171.424525462964</v>
+        <v>46177.491620370369</v>
       </c>
       <c r="C90">
-        <v>64548235</v>
+        <v>64696856</v>
       </c>
       <c r="D90" s="2">
-        <v>46181.65724537037</v>
+        <v>46184.349166666667</v>
       </c>
       <c r="E90" t="s">
-        <v>117</v>
+        <v>247</v>
       </c>
       <c r="F90" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="G90">
-        <v>707109668</v>
+        <v>747103333</v>
       </c>
       <c r="H90" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="I90" t="s">
         <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K90" t="s">
         <v>5</v>
       </c>
       <c r="L90" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M90" t="s">
         <v>3</v>
@@ -6003,37 +5984,37 @@
       <c r="O90" t="s">
         <v>0</v>
       </c>
-      <c r="P90" t="s">
-        <v>0</v>
+      <c r="P90" s="1">
+        <v>2371414</v>
       </c>
       <c r="Q90" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>64028024</v>
+        <v>64402908</v>
       </c>
       <c r="B91" s="2">
-        <v>46171.618414351855</v>
+        <v>46178.638472222221</v>
       </c>
       <c r="C91">
-        <v>64736917</v>
+        <v>64697303</v>
       </c>
       <c r="D91" s="2">
-        <v>46184.67627314815</v>
+        <v>46184.357141203705</v>
       </c>
       <c r="E91" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F91" t="s">
-        <v>98</v>
+        <v>234</v>
       </c>
       <c r="G91">
-        <v>709837321</v>
+        <v>748377555</v>
       </c>
       <c r="H91" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="I91" t="s">
         <v>0</v>
@@ -6048,7 +6029,7 @@
         <v>6</v>
       </c>
       <c r="M91" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N91" t="s">
         <v>107</v>
@@ -6056,37 +6037,37 @@
       <c r="O91" t="s">
         <v>0</v>
       </c>
-      <c r="P91" s="1">
-        <v>5324000</v>
+      <c r="P91" t="s">
+        <v>0</v>
       </c>
       <c r="Q91" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>64029495</v>
+        <v>64402920</v>
       </c>
       <c r="B92" s="2">
-        <v>46171.630046296297</v>
+        <v>46178.638506944444</v>
       </c>
       <c r="C92">
-        <v>64732208</v>
+        <v>64697727</v>
       </c>
       <c r="D92" s="2">
-        <v>46184.645787037036</v>
+        <v>46184.363796296297</v>
       </c>
       <c r="E92" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F92" t="s">
-        <v>98</v>
+        <v>234</v>
       </c>
       <c r="G92">
-        <v>708335225</v>
+        <v>748377555</v>
       </c>
       <c r="H92" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="I92" t="s">
         <v>0</v>
@@ -6095,13 +6076,13 @@
         <v>12</v>
       </c>
       <c r="K92" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L92" t="s">
         <v>6</v>
       </c>
       <c r="M92" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N92" t="s">
         <v>107</v>
@@ -6110,101 +6091,101 @@
         <v>0</v>
       </c>
       <c r="P92" s="1">
-        <v>5324000</v>
+        <v>1644000</v>
       </c>
       <c r="Q92" t="s">
-        <v>255</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>64145330</v>
+        <v>64594376</v>
       </c>
       <c r="B93" s="2">
-        <v>46174.470370370371</v>
+        <v>46182.54111111111</v>
       </c>
       <c r="C93">
-        <v>64789041</v>
+        <v>64701063</v>
       </c>
       <c r="D93" s="2">
-        <v>46185.604502314818</v>
+        <v>46184.409282407411</v>
       </c>
       <c r="E93" t="s">
-        <v>253</v>
+        <v>15</v>
       </c>
       <c r="F93" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="G93">
-        <v>707361318</v>
+        <v>708081052</v>
       </c>
       <c r="H93" t="s">
-        <v>36</v>
-      </c>
-      <c r="I93" t="s">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="I93">
+        <v>1950636</v>
       </c>
       <c r="J93" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K93" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L93" t="s">
         <v>8</v>
       </c>
       <c r="M93" t="s">
-        <v>3</v>
+        <v>181</v>
       </c>
       <c r="N93" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O93" t="s">
         <v>0</v>
       </c>
-      <c r="P93" s="1">
-        <v>2500000</v>
+      <c r="P93">
+        <v>0</v>
       </c>
       <c r="Q93" t="s">
-        <v>256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>64145330</v>
+        <v>64667196</v>
       </c>
       <c r="B94" s="2">
-        <v>46174.470370370371</v>
+        <v>46183.609664351854</v>
       </c>
       <c r="C94">
-        <v>64800104</v>
+        <v>64697935</v>
       </c>
       <c r="D94" s="2">
-        <v>46185.684641203705</v>
+        <v>46184.367303240739</v>
       </c>
       <c r="E94" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F94" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="G94">
-        <v>707361318</v>
+        <v>778552680</v>
       </c>
       <c r="H94" t="s">
-        <v>36</v>
+        <v>237</v>
       </c>
       <c r="I94" t="s">
         <v>0</v>
       </c>
       <c r="J94" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K94" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L94" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M94" t="s">
         <v>3</v>
@@ -6216,36 +6197,36 @@
         <v>0</v>
       </c>
       <c r="P94" s="1">
-        <v>2500000</v>
+        <v>1000000</v>
       </c>
       <c r="Q94" t="s">
-        <v>256</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>64149984</v>
+        <v>64670304</v>
       </c>
       <c r="B95" s="2">
-        <v>46174.503194444442</v>
+        <v>46183.632245370369</v>
       </c>
       <c r="C95">
-        <v>64366089</v>
+        <v>64799962</v>
       </c>
       <c r="D95" s="2">
-        <v>46177.931805555556</v>
+        <v>46185.68377314815</v>
       </c>
       <c r="E95" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F95" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="G95">
-        <v>718151543</v>
+        <v>505499292</v>
       </c>
       <c r="H95" t="s">
-        <v>36</v>
+        <v>239</v>
       </c>
       <c r="I95" t="s">
         <v>0</v>
@@ -6254,7 +6235,7 @@
         <v>21</v>
       </c>
       <c r="K95" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L95" t="s">
         <v>2</v>
@@ -6272,45 +6253,45 @@
         <v>0</v>
       </c>
       <c r="Q95" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>64159836</v>
+        <v>64681816</v>
       </c>
       <c r="B96" s="2">
-        <v>46174.578506944446</v>
+        <v>46183.72179398148</v>
       </c>
       <c r="C96">
-        <v>64797420</v>
+        <v>64698288</v>
       </c>
       <c r="D96" s="2">
-        <v>46185.663576388892</v>
+        <v>46184.373344907406</v>
       </c>
       <c r="E96" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="F96" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="G96">
-        <v>788987805</v>
+        <v>749935631</v>
       </c>
       <c r="H96" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="I96" t="s">
         <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K96" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L96" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M96" t="s">
         <v>3</v>
@@ -6321,143 +6302,143 @@
       <c r="O96" t="s">
         <v>0</v>
       </c>
-      <c r="P96" t="s">
+      <c r="P96">
         <v>0</v>
       </c>
       <c r="Q96" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>64168091</v>
+        <v>64682728</v>
       </c>
       <c r="B97" s="2">
-        <v>46174.65016203704</v>
+        <v>46183.730092592596</v>
       </c>
       <c r="C97">
-        <v>64793736</v>
+        <v>64698140</v>
       </c>
       <c r="D97" s="2">
-        <v>46185.638784722221</v>
+        <v>46184.370219907411</v>
       </c>
       <c r="E97" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="F97" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="G97">
-        <v>777378597</v>
+        <v>749935631</v>
       </c>
       <c r="H97" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="I97" t="s">
         <v>0</v>
       </c>
       <c r="J97" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K97" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L97" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M97" t="s">
         <v>3</v>
       </c>
       <c r="N97" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O97" t="s">
         <v>0</v>
       </c>
-      <c r="P97" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q97">
-        <v>2724391874</v>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>64204580</v>
+        <v>64704377</v>
       </c>
       <c r="B98" s="2">
-        <v>46175.463912037034</v>
+        <v>46184.438657407409</v>
       </c>
       <c r="C98">
-        <v>64676754</v>
+        <v>64704417</v>
       </c>
       <c r="D98" s="2">
-        <v>46183.681331018517</v>
+        <v>46184.438969907409</v>
       </c>
       <c r="E98" t="s">
-        <v>58</v>
+        <v>204</v>
       </c>
       <c r="F98" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="G98">
-        <v>779885779</v>
+        <v>749935631</v>
       </c>
       <c r="H98" t="s">
-        <v>36</v>
+        <v>251</v>
       </c>
       <c r="I98" t="s">
         <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K98" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L98" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M98" t="s">
         <v>3</v>
       </c>
       <c r="N98" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O98" t="s">
         <v>0</v>
       </c>
-      <c r="P98" t="s">
+      <c r="P98">
         <v>0</v>
       </c>
       <c r="Q98" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>64298334</v>
+        <v>64704719</v>
       </c>
       <c r="B99" s="2">
-        <v>46176.697557870371</v>
+        <v>46184.442048611112</v>
       </c>
       <c r="C99">
-        <v>64494332</v>
+        <v>64704786</v>
       </c>
       <c r="D99" s="2">
-        <v>46180.813113425924</v>
+        <v>46184.442291666666</v>
       </c>
       <c r="E99" t="s">
-        <v>10</v>
+        <v>204</v>
       </c>
       <c r="F99" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G99">
-        <v>102435520</v>
+        <v>749935631</v>
       </c>
       <c r="H99" t="s">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="I99" t="s">
         <v>0</v>
@@ -6480,52 +6461,52 @@
       <c r="O99" t="s">
         <v>0</v>
       </c>
-      <c r="P99" s="1">
-        <v>1000000</v>
+      <c r="P99">
+        <v>0</v>
       </c>
       <c r="Q99" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>64299624</v>
+        <v>64705061</v>
       </c>
       <c r="B100" s="2">
-        <v>46176.705578703702</v>
+        <v>46184.445474537039</v>
       </c>
       <c r="C100">
-        <v>64697050</v>
+        <v>64767799</v>
       </c>
       <c r="D100" s="2">
-        <v>46184.353541666664</v>
+        <v>46185.436608796299</v>
       </c>
       <c r="E100" t="s">
-        <v>257</v>
+        <v>103</v>
       </c>
       <c r="F100" t="s">
-        <v>231</v>
+        <v>98</v>
       </c>
       <c r="G100">
-        <v>789196850</v>
+        <v>749935631</v>
       </c>
       <c r="H100" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="I100" t="s">
         <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K100" t="s">
         <v>5</v>
       </c>
       <c r="L100" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M100" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N100" t="s">
         <v>107</v>
@@ -6533,52 +6514,52 @@
       <c r="O100" t="s">
         <v>0</v>
       </c>
-      <c r="P100" t="s">
-        <v>0</v>
+      <c r="P100" s="1">
+        <v>500000</v>
       </c>
       <c r="Q100" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>64299644</v>
+        <v>64705620</v>
       </c>
       <c r="B101" s="2">
-        <v>46176.705625000002</v>
+        <v>46184.450127314813</v>
       </c>
       <c r="C101">
-        <v>64697118</v>
+        <v>64768052</v>
       </c>
       <c r="D101" s="2">
-        <v>46184.354618055557</v>
+        <v>46185.438449074078</v>
       </c>
       <c r="E101" t="s">
-        <v>257</v>
+        <v>103</v>
       </c>
       <c r="F101" t="s">
-        <v>231</v>
+        <v>98</v>
       </c>
       <c r="G101">
-        <v>789196850</v>
+        <v>749935631</v>
       </c>
       <c r="H101" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="I101" t="s">
         <v>0</v>
       </c>
       <c r="J101" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K101" t="s">
         <v>5</v>
       </c>
       <c r="L101" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M101" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N101" t="s">
         <v>107</v>
@@ -6587,36 +6568,36 @@
         <v>0</v>
       </c>
       <c r="P101" s="1">
-        <v>5324000</v>
+        <v>500000</v>
       </c>
       <c r="Q101" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>64327001</v>
+        <v>64710297</v>
       </c>
       <c r="B102" s="2">
-        <v>46177.491620370369</v>
+        <v>46184.486192129632</v>
       </c>
       <c r="C102">
-        <v>64609809</v>
+        <v>64767053</v>
       </c>
       <c r="D102" s="2">
-        <v>46182.664421296293</v>
+        <v>46185.430451388886</v>
       </c>
       <c r="E102" t="s">
-        <v>235</v>
+        <v>103</v>
       </c>
       <c r="F102" t="s">
-        <v>233</v>
+        <v>98</v>
       </c>
       <c r="G102">
-        <v>747103333</v>
+        <v>749935631</v>
       </c>
       <c r="H102" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="I102" t="s">
         <v>0</v>
@@ -6633,40 +6614,43 @@
       <c r="M102" t="s">
         <v>3</v>
       </c>
+      <c r="N102" t="s">
+        <v>107</v>
+      </c>
       <c r="O102" t="s">
         <v>0</v>
       </c>
       <c r="P102" s="1">
-        <v>2371414</v>
+        <v>500000</v>
       </c>
       <c r="Q102" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>64327001</v>
+        <v>64710582</v>
       </c>
       <c r="B103" s="2">
-        <v>46177.491620370369</v>
+        <v>46184.488217592596</v>
       </c>
       <c r="C103">
-        <v>64696856</v>
+        <v>64767884</v>
       </c>
       <c r="D103" s="2">
-        <v>46184.349166666667</v>
+        <v>46185.437291666669</v>
       </c>
       <c r="E103" t="s">
-        <v>257</v>
+        <v>103</v>
       </c>
       <c r="F103" t="s">
-        <v>233</v>
+        <v>98</v>
       </c>
       <c r="G103">
-        <v>747103333</v>
+        <v>749935631</v>
       </c>
       <c r="H103" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="I103" t="s">
         <v>0</v>
@@ -6690,36 +6674,36 @@
         <v>0</v>
       </c>
       <c r="P103" s="1">
-        <v>2371414</v>
+        <v>500000</v>
       </c>
       <c r="Q103" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>64402908</v>
+        <v>64726631</v>
       </c>
       <c r="B104" s="2">
-        <v>46178.638472222221</v>
+        <v>46184.610069444447</v>
       </c>
       <c r="C104">
-        <v>64697303</v>
+        <v>64766778</v>
       </c>
       <c r="D104" s="2">
-        <v>46184.357141203705</v>
+        <v>46185.427928240744</v>
       </c>
       <c r="E104" t="s">
-        <v>257</v>
+        <v>103</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="G104">
-        <v>748377555</v>
+        <v>749935631</v>
       </c>
       <c r="H104" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="I104" t="s">
         <v>0</v>
@@ -6734,7 +6718,7 @@
         <v>6</v>
       </c>
       <c r="M104" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N104" t="s">
         <v>107</v>
@@ -6742,37 +6726,37 @@
       <c r="O104" t="s">
         <v>0</v>
       </c>
-      <c r="P104" t="s">
-        <v>0</v>
+      <c r="P104" s="1">
+        <v>500000</v>
       </c>
       <c r="Q104" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>64402920</v>
+        <v>64727926</v>
       </c>
       <c r="B105" s="2">
-        <v>46178.638506944444</v>
+        <v>46184.618587962963</v>
       </c>
       <c r="C105">
-        <v>64697727</v>
+        <v>64766686</v>
       </c>
       <c r="D105" s="2">
-        <v>46184.363796296297</v>
+        <v>46185.427233796298</v>
       </c>
       <c r="E105" t="s">
-        <v>257</v>
+        <v>103</v>
       </c>
       <c r="F105" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="G105">
-        <v>748377555</v>
+        <v>749935631</v>
       </c>
       <c r="H105" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="I105" t="s">
         <v>0</v>
@@ -6787,7 +6771,7 @@
         <v>6</v>
       </c>
       <c r="M105" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N105" t="s">
         <v>107</v>
@@ -6796,59 +6780,59 @@
         <v>0</v>
       </c>
       <c r="P105" s="1">
-        <v>1644000</v>
+        <v>500000</v>
       </c>
       <c r="Q105" t="s">
-        <v>208</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>64594376</v>
+        <v>64761027</v>
       </c>
       <c r="B106" s="2">
-        <v>46182.54111111111</v>
+        <v>46185.365057870367</v>
       </c>
       <c r="C106">
-        <v>64701063</v>
+        <v>64767232</v>
       </c>
       <c r="D106" s="2">
-        <v>46184.409282407411</v>
+        <v>46185.431805555556</v>
       </c>
       <c r="E106" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="F106" t="s">
+        <v>257</v>
+      </c>
+      <c r="G106">
+        <v>576617272</v>
+      </c>
+      <c r="H106" t="s">
         <v>258</v>
       </c>
-      <c r="G106">
-        <v>708081052</v>
-      </c>
-      <c r="H106" t="s">
-        <v>56</v>
-      </c>
       <c r="I106">
-        <v>1950636</v>
+        <v>1951326</v>
       </c>
       <c r="J106" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K106" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L106" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M106" t="s">
-        <v>181</v>
+        <v>3</v>
       </c>
       <c r="N106" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O106" t="s">
         <v>0</v>
       </c>
-      <c r="P106">
+      <c r="P106" t="s">
         <v>0</v>
       </c>
       <c r="Q106" t="s">
@@ -6857,40 +6841,40 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>64667196</v>
+        <v>64761746</v>
       </c>
       <c r="B107" s="2">
-        <v>46183.609664351854</v>
+        <v>46185.375196759262</v>
       </c>
       <c r="C107">
-        <v>64667221</v>
+        <v>64777663</v>
       </c>
       <c r="D107" s="2">
-        <v>46183.609872685185</v>
+        <v>46185.514745370368</v>
       </c>
       <c r="E107" t="s">
-        <v>204</v>
+        <v>103</v>
       </c>
       <c r="F107" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="G107">
-        <v>778552680</v>
+        <v>749503436</v>
       </c>
       <c r="H107" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="I107" t="s">
         <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K107" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L107" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M107" t="s">
         <v>3</v>
@@ -6901,52 +6885,52 @@
       <c r="O107" t="s">
         <v>0</v>
       </c>
-      <c r="P107" s="1">
-        <v>1000000</v>
+      <c r="P107" t="s">
+        <v>0</v>
       </c>
       <c r="Q107" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>64667196</v>
+        <v>64775381</v>
       </c>
       <c r="B108" s="2">
-        <v>46183.609664351854</v>
+        <v>46185.497025462966</v>
       </c>
       <c r="C108">
-        <v>64697935</v>
+        <v>64775412</v>
       </c>
       <c r="D108" s="2">
-        <v>46184.367303240739</v>
+        <v>46185.497256944444</v>
       </c>
       <c r="E108" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="F108" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="G108">
-        <v>778552680</v>
+        <v>757500782</v>
       </c>
       <c r="H108" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="I108" t="s">
         <v>0</v>
       </c>
       <c r="J108" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K108" t="s">
         <v>5</v>
       </c>
       <c r="L108" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M108" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N108" t="s">
         <v>107</v>
@@ -6954,105 +6938,105 @@
       <c r="O108" t="s">
         <v>0</v>
       </c>
-      <c r="P108" s="1">
-        <v>1000000</v>
+      <c r="P108" t="s">
+        <v>0</v>
       </c>
       <c r="Q108" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>64670304</v>
+        <v>64775393</v>
       </c>
       <c r="B109" s="2">
-        <v>46183.632245370369</v>
+        <v>46185.497060185182</v>
       </c>
       <c r="C109">
-        <v>64795098</v>
+        <v>64775424</v>
       </c>
       <c r="D109" s="2">
-        <v>46185.648055555554</v>
+        <v>46185.49728009259</v>
       </c>
       <c r="E109" t="s">
-        <v>259</v>
+        <v>204</v>
       </c>
       <c r="F109" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="G109">
-        <v>505499292</v>
+        <v>757500782</v>
       </c>
       <c r="H109" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="I109" t="s">
         <v>0</v>
       </c>
       <c r="J109" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K109" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L109" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M109" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N109" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O109" t="s">
         <v>0</v>
       </c>
-      <c r="P109" t="s">
-        <v>0</v>
+      <c r="P109" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q109" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110">
-        <v>64670304</v>
+        <v>64776871</v>
       </c>
       <c r="B110" s="2">
-        <v>46183.632245370369</v>
+        <v>46185.508958333332</v>
       </c>
       <c r="C110">
-        <v>64799962</v>
+        <v>64776930</v>
       </c>
       <c r="D110" s="2">
-        <v>46185.68377314815</v>
+        <v>46185.509189814817</v>
       </c>
       <c r="E110" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="F110" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="G110">
-        <v>505499292</v>
+        <v>748377555</v>
       </c>
       <c r="H110" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="I110" t="s">
         <v>0</v>
       </c>
       <c r="J110" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K110" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L110" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M110" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N110" t="s">
         <v>107</v>
@@ -7064,48 +7048,48 @@
         <v>0</v>
       </c>
       <c r="Q110" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111">
-        <v>64681816</v>
+        <v>64776884</v>
       </c>
       <c r="B111" s="2">
-        <v>46183.72179398148</v>
+        <v>46185.508993055555</v>
       </c>
       <c r="C111">
-        <v>64681863</v>
+        <v>64776942</v>
       </c>
       <c r="D111" s="2">
-        <v>46183.722037037034</v>
+        <v>46185.509247685186</v>
       </c>
       <c r="E111" t="s">
         <v>204</v>
       </c>
       <c r="F111" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="G111">
-        <v>749935631</v>
+        <v>748377555</v>
       </c>
       <c r="H111" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="I111" t="s">
         <v>0</v>
       </c>
       <c r="J111" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K111" t="s">
         <v>5</v>
       </c>
       <c r="L111" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M111" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N111" t="s">
         <v>107</v>
@@ -7113,37 +7097,37 @@
       <c r="O111" t="s">
         <v>0</v>
       </c>
-      <c r="P111">
-        <v>0</v>
+      <c r="P111" s="1">
+        <v>5324000</v>
       </c>
       <c r="Q111" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112">
-        <v>64681816</v>
+        <v>64785630</v>
       </c>
       <c r="B112" s="2">
-        <v>46183.72179398148</v>
+        <v>46185.578321759262</v>
       </c>
       <c r="C112">
-        <v>64698288</v>
+        <v>64803291</v>
       </c>
       <c r="D112" s="2">
-        <v>46184.373344907406</v>
+        <v>46185.710648148146</v>
       </c>
       <c r="E112" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="F112" t="s">
-        <v>236</v>
+        <v>98</v>
       </c>
       <c r="G112">
-        <v>749935631</v>
+        <v>708793132</v>
       </c>
       <c r="H112" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="I112" t="s">
         <v>0</v>
@@ -7166,49 +7150,49 @@
       <c r="O112" t="s">
         <v>0</v>
       </c>
-      <c r="P112">
-        <v>0</v>
+      <c r="P112" s="1">
+        <v>293000</v>
       </c>
       <c r="Q112" t="s">
-        <v>11</v>
+        <v>267</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113">
-        <v>64682728</v>
+        <v>64791999</v>
       </c>
       <c r="B113" s="2">
-        <v>46183.730092592596</v>
+        <v>46185.626469907409</v>
       </c>
       <c r="C113">
-        <v>64682804</v>
+        <v>64794477</v>
       </c>
       <c r="D113" s="2">
-        <v>46183.730451388888</v>
+        <v>46185.644490740742</v>
       </c>
       <c r="E113" t="s">
-        <v>204</v>
+        <v>263</v>
       </c>
       <c r="F113" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="G113">
-        <v>749935631</v>
+        <v>140675694</v>
       </c>
       <c r="H113" t="s">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="I113" t="s">
         <v>0</v>
       </c>
       <c r="J113" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="K113" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L113" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M113" t="s">
         <v>3</v>
@@ -7219,1551 +7203,18 @@
       <c r="O113" t="s">
         <v>0</v>
       </c>
-      <c r="P113">
+      <c r="P113" t="s">
         <v>0</v>
       </c>
       <c r="Q113" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A114">
-        <v>64682728</v>
-      </c>
-      <c r="B114" s="2">
-        <v>46183.730092592596</v>
-      </c>
-      <c r="C114">
-        <v>64698140</v>
-      </c>
-      <c r="D114" s="2">
-        <v>46184.370219907411</v>
-      </c>
-      <c r="E114" t="s">
-        <v>103</v>
-      </c>
-      <c r="F114" t="s">
-        <v>261</v>
-      </c>
-      <c r="G114">
-        <v>749935631</v>
-      </c>
-      <c r="H114" t="s">
-        <v>260</v>
-      </c>
-      <c r="I114" t="s">
-        <v>0</v>
-      </c>
-      <c r="J114" t="s">
-        <v>12</v>
-      </c>
-      <c r="K114" t="s">
-        <v>5</v>
-      </c>
-      <c r="L114" t="s">
-        <v>6</v>
-      </c>
-      <c r="M114" t="s">
-        <v>3</v>
-      </c>
-      <c r="N114" t="s">
-        <v>107</v>
-      </c>
-      <c r="O114" t="s">
-        <v>0</v>
-      </c>
-      <c r="P114">
-        <v>0</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A115">
-        <v>64704377</v>
-      </c>
-      <c r="B115" s="2">
-        <v>46184.438657407409</v>
-      </c>
-      <c r="C115">
-        <v>64704417</v>
-      </c>
-      <c r="D115" s="2">
-        <v>46184.438969907409</v>
-      </c>
-      <c r="E115" t="s">
-        <v>204</v>
-      </c>
-      <c r="F115" t="s">
-        <v>236</v>
-      </c>
-      <c r="G115">
-        <v>749935631</v>
-      </c>
-      <c r="H115" t="s">
-        <v>262</v>
-      </c>
-      <c r="I115" t="s">
-        <v>0</v>
-      </c>
-      <c r="J115" t="s">
-        <v>12</v>
-      </c>
-      <c r="K115" t="s">
-        <v>5</v>
-      </c>
-      <c r="L115" t="s">
-        <v>6</v>
-      </c>
-      <c r="M115" t="s">
-        <v>3</v>
-      </c>
-      <c r="N115" t="s">
-        <v>107</v>
-      </c>
-      <c r="O115" t="s">
-        <v>0</v>
-      </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A116">
-        <v>64704377</v>
-      </c>
-      <c r="B116" s="2">
-        <v>46184.438657407409</v>
-      </c>
-      <c r="C116">
-        <v>64767654</v>
-      </c>
-      <c r="D116" s="2">
-        <v>46185.435648148145</v>
-      </c>
-      <c r="E116" t="s">
-        <v>103</v>
-      </c>
-      <c r="F116" t="s">
-        <v>236</v>
-      </c>
-      <c r="G116">
-        <v>749935631</v>
-      </c>
-      <c r="H116" t="s">
-        <v>262</v>
-      </c>
-      <c r="I116" t="s">
-        <v>0</v>
-      </c>
-      <c r="J116" t="s">
-        <v>12</v>
-      </c>
-      <c r="K116" t="s">
-        <v>5</v>
-      </c>
-      <c r="L116" t="s">
-        <v>6</v>
-      </c>
-      <c r="M116" t="s">
-        <v>3</v>
-      </c>
-      <c r="N116" t="s">
-        <v>107</v>
-      </c>
-      <c r="O116" t="s">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A117">
-        <v>64704719</v>
-      </c>
-      <c r="B117" s="2">
-        <v>46184.442048611112</v>
-      </c>
-      <c r="C117">
-        <v>64704786</v>
-      </c>
-      <c r="D117" s="2">
-        <v>46184.442291666666</v>
-      </c>
-      <c r="E117" t="s">
-        <v>204</v>
-      </c>
-      <c r="F117" t="s">
-        <v>236</v>
-      </c>
-      <c r="G117">
-        <v>749935631</v>
-      </c>
-      <c r="H117" t="s">
-        <v>262</v>
-      </c>
-      <c r="I117" t="s">
-        <v>0</v>
-      </c>
-      <c r="J117" t="s">
-        <v>12</v>
-      </c>
-      <c r="K117" t="s">
-        <v>5</v>
-      </c>
-      <c r="L117" t="s">
-        <v>6</v>
-      </c>
-      <c r="M117" t="s">
-        <v>3</v>
-      </c>
-      <c r="N117" t="s">
-        <v>107</v>
-      </c>
-      <c r="O117" t="s">
-        <v>0</v>
-      </c>
-      <c r="P117">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A118">
-        <v>64704719</v>
-      </c>
-      <c r="B118" s="2">
-        <v>46184.442048611112</v>
-      </c>
-      <c r="C118">
-        <v>64766924</v>
-      </c>
-      <c r="D118" s="2">
-        <v>46185.429074074076</v>
-      </c>
-      <c r="E118" t="s">
-        <v>103</v>
-      </c>
-      <c r="F118" t="s">
-        <v>236</v>
-      </c>
-      <c r="G118">
-        <v>749935631</v>
-      </c>
-      <c r="H118" t="s">
-        <v>262</v>
-      </c>
-      <c r="I118" t="s">
-        <v>0</v>
-      </c>
-      <c r="J118" t="s">
-        <v>12</v>
-      </c>
-      <c r="K118" t="s">
-        <v>5</v>
-      </c>
-      <c r="L118" t="s">
-        <v>6</v>
-      </c>
-      <c r="M118" t="s">
-        <v>3</v>
-      </c>
-      <c r="N118" t="s">
-        <v>107</v>
-      </c>
-      <c r="O118" t="s">
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A119">
-        <v>64705061</v>
-      </c>
-      <c r="B119" s="2">
-        <v>46184.445474537039</v>
-      </c>
-      <c r="C119">
-        <v>64705107</v>
-      </c>
-      <c r="D119" s="2">
-        <v>46184.445694444446</v>
-      </c>
-      <c r="E119" t="s">
-        <v>204</v>
-      </c>
-      <c r="F119" t="s">
-        <v>98</v>
-      </c>
-      <c r="G119">
-        <v>749935631</v>
-      </c>
-      <c r="H119" t="s">
-        <v>262</v>
-      </c>
-      <c r="I119" t="s">
-        <v>0</v>
-      </c>
-      <c r="J119" t="s">
-        <v>12</v>
-      </c>
-      <c r="K119" t="s">
-        <v>5</v>
-      </c>
-      <c r="L119" t="s">
-        <v>6</v>
-      </c>
-      <c r="M119" t="s">
-        <v>3</v>
-      </c>
-      <c r="N119" t="s">
-        <v>107</v>
-      </c>
-      <c r="O119" t="s">
-        <v>0</v>
-      </c>
-      <c r="P119" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A120">
-        <v>64705061</v>
-      </c>
-      <c r="B120" s="2">
-        <v>46184.445474537039</v>
-      </c>
-      <c r="C120">
-        <v>64767799</v>
-      </c>
-      <c r="D120" s="2">
-        <v>46185.436608796299</v>
-      </c>
-      <c r="E120" t="s">
-        <v>103</v>
-      </c>
-      <c r="F120" t="s">
-        <v>98</v>
-      </c>
-      <c r="G120">
-        <v>749935631</v>
-      </c>
-      <c r="H120" t="s">
-        <v>262</v>
-      </c>
-      <c r="I120" t="s">
-        <v>0</v>
-      </c>
-      <c r="J120" t="s">
-        <v>12</v>
-      </c>
-      <c r="K120" t="s">
-        <v>5</v>
-      </c>
-      <c r="L120" t="s">
-        <v>6</v>
-      </c>
-      <c r="M120" t="s">
-        <v>3</v>
-      </c>
-      <c r="N120" t="s">
-        <v>107</v>
-      </c>
-      <c r="O120" t="s">
-        <v>0</v>
-      </c>
-      <c r="P120" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A121">
-        <v>64705620</v>
-      </c>
-      <c r="B121" s="2">
-        <v>46184.450127314813</v>
-      </c>
-      <c r="C121">
-        <v>64705667</v>
-      </c>
-      <c r="D121" s="2">
-        <v>46184.45039351852</v>
-      </c>
-      <c r="E121" t="s">
-        <v>204</v>
-      </c>
-      <c r="F121" t="s">
-        <v>98</v>
-      </c>
-      <c r="G121">
-        <v>749935631</v>
-      </c>
-      <c r="H121" t="s">
-        <v>262</v>
-      </c>
-      <c r="I121" t="s">
-        <v>0</v>
-      </c>
-      <c r="J121" t="s">
-        <v>12</v>
-      </c>
-      <c r="K121" t="s">
-        <v>5</v>
-      </c>
-      <c r="L121" t="s">
-        <v>6</v>
-      </c>
-      <c r="M121" t="s">
-        <v>3</v>
-      </c>
-      <c r="N121" t="s">
-        <v>107</v>
-      </c>
-      <c r="O121" t="s">
-        <v>0</v>
-      </c>
-      <c r="P121" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q121" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A122">
-        <v>64705620</v>
-      </c>
-      <c r="B122" s="2">
-        <v>46184.450127314813</v>
-      </c>
-      <c r="C122">
-        <v>64768052</v>
-      </c>
-      <c r="D122" s="2">
-        <v>46185.438449074078</v>
-      </c>
-      <c r="E122" t="s">
-        <v>103</v>
-      </c>
-      <c r="F122" t="s">
-        <v>98</v>
-      </c>
-      <c r="G122">
-        <v>749935631</v>
-      </c>
-      <c r="H122" t="s">
-        <v>262</v>
-      </c>
-      <c r="I122" t="s">
-        <v>0</v>
-      </c>
-      <c r="J122" t="s">
-        <v>12</v>
-      </c>
-      <c r="K122" t="s">
-        <v>5</v>
-      </c>
-      <c r="L122" t="s">
-        <v>6</v>
-      </c>
-      <c r="M122" t="s">
-        <v>3</v>
-      </c>
-      <c r="N122" t="s">
-        <v>107</v>
-      </c>
-      <c r="O122" t="s">
-        <v>0</v>
-      </c>
-      <c r="P122" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A123">
-        <v>64710297</v>
-      </c>
-      <c r="B123" s="2">
-        <v>46184.486192129632</v>
-      </c>
-      <c r="C123">
-        <v>64710340</v>
-      </c>
-      <c r="D123" s="2">
-        <v>46184.48641203704</v>
-      </c>
-      <c r="E123" t="s">
-        <v>204</v>
-      </c>
-      <c r="F123" t="s">
-        <v>98</v>
-      </c>
-      <c r="G123">
-        <v>749935631</v>
-      </c>
-      <c r="H123" t="s">
-        <v>263</v>
-      </c>
-      <c r="I123" t="s">
-        <v>0</v>
-      </c>
-      <c r="J123" t="s">
-        <v>12</v>
-      </c>
-      <c r="K123" t="s">
-        <v>5</v>
-      </c>
-      <c r="L123" t="s">
-        <v>6</v>
-      </c>
-      <c r="M123" t="s">
-        <v>3</v>
-      </c>
-      <c r="N123" t="s">
-        <v>107</v>
-      </c>
-      <c r="O123" t="s">
-        <v>0</v>
-      </c>
-      <c r="P123" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q123" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A124">
-        <v>64710297</v>
-      </c>
-      <c r="B124" s="2">
-        <v>46184.486192129632</v>
-      </c>
-      <c r="C124">
-        <v>64767053</v>
-      </c>
-      <c r="D124" s="2">
-        <v>46185.430451388886</v>
-      </c>
-      <c r="E124" t="s">
-        <v>103</v>
-      </c>
-      <c r="F124" t="s">
-        <v>98</v>
-      </c>
-      <c r="G124">
-        <v>749935631</v>
-      </c>
-      <c r="H124" t="s">
-        <v>263</v>
-      </c>
-      <c r="I124" t="s">
-        <v>0</v>
-      </c>
-      <c r="J124" t="s">
-        <v>12</v>
-      </c>
-      <c r="K124" t="s">
-        <v>5</v>
-      </c>
-      <c r="L124" t="s">
-        <v>6</v>
-      </c>
-      <c r="M124" t="s">
-        <v>3</v>
-      </c>
-      <c r="N124" t="s">
-        <v>107</v>
-      </c>
-      <c r="O124" t="s">
-        <v>0</v>
-      </c>
-      <c r="P124" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q124" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A125">
-        <v>64710582</v>
-      </c>
-      <c r="B125" s="2">
-        <v>46184.488217592596</v>
-      </c>
-      <c r="C125">
-        <v>64710629</v>
-      </c>
-      <c r="D125" s="2">
-        <v>46184.488449074073</v>
-      </c>
-      <c r="E125" t="s">
-        <v>204</v>
-      </c>
-      <c r="F125" t="s">
-        <v>98</v>
-      </c>
-      <c r="G125">
-        <v>749935631</v>
-      </c>
-      <c r="H125" t="s">
-        <v>263</v>
-      </c>
-      <c r="I125" t="s">
-        <v>0</v>
-      </c>
-      <c r="J125" t="s">
-        <v>12</v>
-      </c>
-      <c r="K125" t="s">
-        <v>5</v>
-      </c>
-      <c r="L125" t="s">
-        <v>6</v>
-      </c>
-      <c r="M125" t="s">
-        <v>3</v>
-      </c>
-      <c r="N125" t="s">
-        <v>107</v>
-      </c>
-      <c r="O125" t="s">
-        <v>0</v>
-      </c>
-      <c r="P125" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q125" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A126">
-        <v>64710582</v>
-      </c>
-      <c r="B126" s="2">
-        <v>46184.488217592596</v>
-      </c>
-      <c r="C126">
-        <v>64767884</v>
-      </c>
-      <c r="D126" s="2">
-        <v>46185.437291666669</v>
-      </c>
-      <c r="E126" t="s">
-        <v>103</v>
-      </c>
-      <c r="F126" t="s">
-        <v>98</v>
-      </c>
-      <c r="G126">
-        <v>749935631</v>
-      </c>
-      <c r="H126" t="s">
-        <v>263</v>
-      </c>
-      <c r="I126" t="s">
-        <v>0</v>
-      </c>
-      <c r="J126" t="s">
-        <v>12</v>
-      </c>
-      <c r="K126" t="s">
-        <v>5</v>
-      </c>
-      <c r="L126" t="s">
-        <v>6</v>
-      </c>
-      <c r="M126" t="s">
-        <v>3</v>
-      </c>
-      <c r="N126" t="s">
-        <v>107</v>
-      </c>
-      <c r="O126" t="s">
-        <v>0</v>
-      </c>
-      <c r="P126" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q126" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A127">
-        <v>64726631</v>
-      </c>
-      <c r="B127" s="2">
-        <v>46184.610069444447</v>
-      </c>
-      <c r="C127">
-        <v>64766778</v>
-      </c>
-      <c r="D127" s="2">
-        <v>46185.427928240744</v>
-      </c>
-      <c r="E127" t="s">
-        <v>103</v>
-      </c>
-      <c r="F127" t="s">
-        <v>264</v>
-      </c>
-      <c r="G127">
-        <v>749935631</v>
-      </c>
-      <c r="H127" t="s">
-        <v>265</v>
-      </c>
-      <c r="I127" t="s">
-        <v>0</v>
-      </c>
-      <c r="J127" t="s">
-        <v>12</v>
-      </c>
-      <c r="K127" t="s">
-        <v>5</v>
-      </c>
-      <c r="L127" t="s">
-        <v>6</v>
-      </c>
-      <c r="M127" t="s">
-        <v>3</v>
-      </c>
-      <c r="N127" t="s">
-        <v>107</v>
-      </c>
-      <c r="O127" t="s">
-        <v>0</v>
-      </c>
-      <c r="P127" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q127" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A128">
-        <v>64726631</v>
-      </c>
-      <c r="B128" s="2">
-        <v>46184.610069444447</v>
-      </c>
-      <c r="C128">
-        <v>64726671</v>
-      </c>
-      <c r="D128" s="2">
-        <v>46184.610312500001</v>
-      </c>
-      <c r="E128" t="s">
-        <v>204</v>
-      </c>
-      <c r="F128" t="s">
-        <v>264</v>
-      </c>
-      <c r="G128">
-        <v>749935631</v>
-      </c>
-      <c r="H128" t="s">
-        <v>265</v>
-      </c>
-      <c r="I128" t="s">
-        <v>0</v>
-      </c>
-      <c r="J128" t="s">
-        <v>12</v>
-      </c>
-      <c r="K128" t="s">
-        <v>5</v>
-      </c>
-      <c r="L128" t="s">
-        <v>6</v>
-      </c>
-      <c r="M128" t="s">
-        <v>3</v>
-      </c>
-      <c r="N128" t="s">
-        <v>107</v>
-      </c>
-      <c r="O128" t="s">
-        <v>0</v>
-      </c>
-      <c r="P128" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q128" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A129">
-        <v>64727926</v>
-      </c>
-      <c r="B129" s="2">
-        <v>46184.618587962963</v>
-      </c>
-      <c r="C129">
-        <v>64766686</v>
-      </c>
-      <c r="D129" s="2">
-        <v>46185.427233796298</v>
-      </c>
-      <c r="E129" t="s">
-        <v>103</v>
-      </c>
-      <c r="F129" t="s">
-        <v>266</v>
-      </c>
-      <c r="G129">
-        <v>749935631</v>
-      </c>
-      <c r="H129" t="s">
-        <v>267</v>
-      </c>
-      <c r="I129" t="s">
-        <v>0</v>
-      </c>
-      <c r="J129" t="s">
-        <v>12</v>
-      </c>
-      <c r="K129" t="s">
-        <v>5</v>
-      </c>
-      <c r="L129" t="s">
-        <v>6</v>
-      </c>
-      <c r="M129" t="s">
-        <v>3</v>
-      </c>
-      <c r="N129" t="s">
-        <v>107</v>
-      </c>
-      <c r="O129" t="s">
-        <v>0</v>
-      </c>
-      <c r="P129" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q129" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A130">
-        <v>64727926</v>
-      </c>
-      <c r="B130" s="2">
-        <v>46184.618587962963</v>
-      </c>
-      <c r="C130">
-        <v>64727981</v>
-      </c>
-      <c r="D130" s="2">
-        <v>46184.618877314817</v>
-      </c>
-      <c r="E130" t="s">
-        <v>204</v>
-      </c>
-      <c r="F130" t="s">
-        <v>266</v>
-      </c>
-      <c r="G130">
-        <v>749935631</v>
-      </c>
-      <c r="H130" t="s">
-        <v>267</v>
-      </c>
-      <c r="I130" t="s">
-        <v>0</v>
-      </c>
-      <c r="J130" t="s">
-        <v>12</v>
-      </c>
-      <c r="K130" t="s">
-        <v>5</v>
-      </c>
-      <c r="L130" t="s">
-        <v>6</v>
-      </c>
-      <c r="M130" t="s">
-        <v>3</v>
-      </c>
-      <c r="N130" t="s">
-        <v>107</v>
-      </c>
-      <c r="O130" t="s">
-        <v>0</v>
-      </c>
-      <c r="P130" s="1">
-        <v>500000</v>
-      </c>
-      <c r="Q130" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A131">
-        <v>64761027</v>
-      </c>
-      <c r="B131" s="2">
-        <v>46185.365057870367</v>
-      </c>
-      <c r="C131">
-        <v>64767232</v>
-      </c>
-      <c r="D131" s="2">
-        <v>46185.431805555556</v>
-      </c>
-      <c r="E131" t="s">
-        <v>257</v>
-      </c>
-      <c r="F131" t="s">
-        <v>268</v>
-      </c>
-      <c r="G131">
-        <v>576617272</v>
-      </c>
-      <c r="H131" t="s">
-        <v>269</v>
-      </c>
-      <c r="I131">
-        <v>1951326</v>
-      </c>
-      <c r="J131" t="s">
-        <v>21</v>
-      </c>
-      <c r="K131" t="s">
-        <v>1</v>
-      </c>
-      <c r="L131" t="s">
-        <v>2</v>
-      </c>
-      <c r="M131" t="s">
-        <v>3</v>
-      </c>
-      <c r="N131" t="s">
-        <v>107</v>
-      </c>
-      <c r="O131" t="s">
-        <v>0</v>
-      </c>
-      <c r="P131" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A132">
-        <v>64761746</v>
-      </c>
-      <c r="B132" s="2">
-        <v>46185.375196759262</v>
-      </c>
-      <c r="C132">
-        <v>64777663</v>
-      </c>
-      <c r="D132" s="2">
-        <v>46185.514745370368</v>
-      </c>
-      <c r="E132" t="s">
-        <v>103</v>
-      </c>
-      <c r="F132" t="s">
-        <v>270</v>
-      </c>
-      <c r="G132">
-        <v>749503436</v>
-      </c>
-      <c r="H132" t="s">
-        <v>271</v>
-      </c>
-      <c r="I132" t="s">
-        <v>0</v>
-      </c>
-      <c r="J132" t="s">
-        <v>21</v>
-      </c>
-      <c r="K132" t="s">
-        <v>1</v>
-      </c>
-      <c r="L132" t="s">
-        <v>2</v>
-      </c>
-      <c r="M132" t="s">
-        <v>3</v>
-      </c>
-      <c r="N132" t="s">
-        <v>107</v>
-      </c>
-      <c r="O132" t="s">
-        <v>0</v>
-      </c>
-      <c r="P132" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A133">
-        <v>64775381</v>
-      </c>
-      <c r="B133" s="2">
-        <v>46185.497025462966</v>
-      </c>
-      <c r="C133">
-        <v>64775412</v>
-      </c>
-      <c r="D133" s="2">
-        <v>46185.497256944444</v>
-      </c>
-      <c r="E133" t="s">
-        <v>204</v>
-      </c>
-      <c r="F133" t="s">
-        <v>272</v>
-      </c>
-      <c r="G133">
-        <v>757500782</v>
-      </c>
-      <c r="H133" t="s">
-        <v>273</v>
-      </c>
-      <c r="I133" t="s">
-        <v>0</v>
-      </c>
-      <c r="J133" t="s">
-        <v>17</v>
-      </c>
-      <c r="K133" t="s">
-        <v>5</v>
-      </c>
-      <c r="L133" t="s">
-        <v>8</v>
-      </c>
-      <c r="M133" t="s">
-        <v>7</v>
-      </c>
-      <c r="N133" t="s">
-        <v>107</v>
-      </c>
-      <c r="O133" t="s">
-        <v>0</v>
-      </c>
-      <c r="P133" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q133" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A134">
-        <v>64775381</v>
-      </c>
-      <c r="B134" s="2">
-        <v>46185.497025462966</v>
-      </c>
-      <c r="C134">
-        <v>64795189</v>
-      </c>
-      <c r="D134" s="2">
-        <v>46185.648576388892</v>
-      </c>
-      <c r="E134" t="s">
-        <v>274</v>
-      </c>
-      <c r="F134" t="s">
-        <v>272</v>
-      </c>
-      <c r="G134">
-        <v>757500782</v>
-      </c>
-      <c r="H134" t="s">
-        <v>273</v>
-      </c>
-      <c r="I134" t="s">
-        <v>0</v>
-      </c>
-      <c r="J134" t="s">
-        <v>17</v>
-      </c>
-      <c r="K134" t="s">
-        <v>5</v>
-      </c>
-      <c r="L134" t="s">
-        <v>8</v>
-      </c>
-      <c r="M134" t="s">
-        <v>7</v>
-      </c>
-      <c r="N134" t="s">
-        <v>107</v>
-      </c>
-      <c r="O134" t="s">
-        <v>0</v>
-      </c>
-      <c r="P134" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A135">
-        <v>64775393</v>
-      </c>
-      <c r="B135" s="2">
-        <v>46185.497060185182</v>
-      </c>
-      <c r="C135">
-        <v>64775424</v>
-      </c>
-      <c r="D135" s="2">
-        <v>46185.49728009259</v>
-      </c>
-      <c r="E135" t="s">
-        <v>204</v>
-      </c>
-      <c r="F135" t="s">
-        <v>272</v>
-      </c>
-      <c r="G135">
-        <v>757500782</v>
-      </c>
-      <c r="H135" t="s">
-        <v>273</v>
-      </c>
-      <c r="I135" t="s">
-        <v>0</v>
-      </c>
-      <c r="J135" t="s">
-        <v>17</v>
-      </c>
-      <c r="K135" t="s">
-        <v>5</v>
-      </c>
-      <c r="L135" t="s">
-        <v>8</v>
-      </c>
-      <c r="M135" t="s">
-        <v>13</v>
-      </c>
-      <c r="N135" t="s">
-        <v>107</v>
-      </c>
-      <c r="O135" t="s">
-        <v>0</v>
-      </c>
-      <c r="P135" s="1">
-        <v>5324000</v>
-      </c>
-      <c r="Q135" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A136">
-        <v>64775393</v>
-      </c>
-      <c r="B136" s="2">
-        <v>46185.497060185182</v>
-      </c>
-      <c r="C136">
-        <v>64795058</v>
-      </c>
-      <c r="D136" s="2">
-        <v>46185.647870370369</v>
-      </c>
-      <c r="E136" t="s">
-        <v>274</v>
-      </c>
-      <c r="F136" t="s">
-        <v>272</v>
-      </c>
-      <c r="G136">
-        <v>757500782</v>
-      </c>
-      <c r="H136" t="s">
-        <v>273</v>
-      </c>
-      <c r="I136" t="s">
-        <v>0</v>
-      </c>
-      <c r="J136" t="s">
-        <v>17</v>
-      </c>
-      <c r="K136" t="s">
-        <v>5</v>
-      </c>
-      <c r="L136" t="s">
-        <v>8</v>
-      </c>
-      <c r="M136" t="s">
-        <v>13</v>
-      </c>
-      <c r="N136" t="s">
-        <v>107</v>
-      </c>
-      <c r="O136" t="s">
-        <v>0</v>
-      </c>
-      <c r="P136" s="1">
-        <v>5324000</v>
-      </c>
-      <c r="Q136" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A137">
-        <v>64776871</v>
-      </c>
-      <c r="B137" s="2">
-        <v>46185.508958333332</v>
-      </c>
-      <c r="C137">
-        <v>64776930</v>
-      </c>
-      <c r="D137" s="2">
-        <v>46185.509189814817</v>
-      </c>
-      <c r="E137" t="s">
-        <v>204</v>
-      </c>
-      <c r="F137" t="s">
-        <v>275</v>
-      </c>
-      <c r="G137">
-        <v>748377555</v>
-      </c>
-      <c r="H137" t="s">
-        <v>276</v>
-      </c>
-      <c r="I137" t="s">
-        <v>0</v>
-      </c>
-      <c r="J137" t="s">
-        <v>17</v>
-      </c>
-      <c r="K137" t="s">
-        <v>5</v>
-      </c>
-      <c r="L137" t="s">
-        <v>8</v>
-      </c>
-      <c r="M137" t="s">
-        <v>7</v>
-      </c>
-      <c r="N137" t="s">
-        <v>107</v>
-      </c>
-      <c r="O137" t="s">
-        <v>0</v>
-      </c>
-      <c r="P137" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q137" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A138">
-        <v>64776871</v>
-      </c>
-      <c r="B138" s="2">
-        <v>46185.508958333332</v>
-      </c>
-      <c r="C138">
-        <v>64795250</v>
-      </c>
-      <c r="D138" s="2">
-        <v>46185.649201388886</v>
-      </c>
-      <c r="E138" t="s">
-        <v>274</v>
-      </c>
-      <c r="F138" t="s">
-        <v>275</v>
-      </c>
-      <c r="G138">
-        <v>748377555</v>
-      </c>
-      <c r="H138" t="s">
-        <v>276</v>
-      </c>
-      <c r="I138" t="s">
-        <v>0</v>
-      </c>
-      <c r="J138" t="s">
-        <v>17</v>
-      </c>
-      <c r="K138" t="s">
-        <v>5</v>
-      </c>
-      <c r="L138" t="s">
-        <v>8</v>
-      </c>
-      <c r="M138" t="s">
-        <v>7</v>
-      </c>
-      <c r="N138" t="s">
-        <v>107</v>
-      </c>
-      <c r="O138" t="s">
-        <v>0</v>
-      </c>
-      <c r="P138" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q138" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A139">
-        <v>64776884</v>
-      </c>
-      <c r="B139" s="2">
-        <v>46185.508993055555</v>
-      </c>
-      <c r="C139">
-        <v>64776942</v>
-      </c>
-      <c r="D139" s="2">
-        <v>46185.509247685186</v>
-      </c>
-      <c r="E139" t="s">
-        <v>204</v>
-      </c>
-      <c r="F139" t="s">
-        <v>275</v>
-      </c>
-      <c r="G139">
-        <v>748377555</v>
-      </c>
-      <c r="H139" t="s">
-        <v>276</v>
-      </c>
-      <c r="I139" t="s">
-        <v>0</v>
-      </c>
-      <c r="J139" t="s">
-        <v>17</v>
-      </c>
-      <c r="K139" t="s">
-        <v>5</v>
-      </c>
-      <c r="L139" t="s">
-        <v>8</v>
-      </c>
-      <c r="M139" t="s">
-        <v>13</v>
-      </c>
-      <c r="N139" t="s">
-        <v>107</v>
-      </c>
-      <c r="O139" t="s">
-        <v>0</v>
-      </c>
-      <c r="P139" s="1">
-        <v>5324000</v>
-      </c>
-      <c r="Q139" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A140">
-        <v>64776884</v>
-      </c>
-      <c r="B140" s="2">
-        <v>46185.508993055555</v>
-      </c>
-      <c r="C140">
-        <v>64794898</v>
-      </c>
-      <c r="D140" s="2">
-        <v>46185.647060185183</v>
-      </c>
-      <c r="E140" t="s">
-        <v>274</v>
-      </c>
-      <c r="F140" t="s">
-        <v>275</v>
-      </c>
-      <c r="G140">
-        <v>748377555</v>
-      </c>
-      <c r="H140" t="s">
-        <v>276</v>
-      </c>
-      <c r="I140" t="s">
-        <v>0</v>
-      </c>
-      <c r="J140" t="s">
-        <v>17</v>
-      </c>
-      <c r="K140" t="s">
-        <v>5</v>
-      </c>
-      <c r="L140" t="s">
-        <v>8</v>
-      </c>
-      <c r="M140" t="s">
-        <v>13</v>
-      </c>
-      <c r="N140" t="s">
-        <v>107</v>
-      </c>
-      <c r="O140" t="s">
-        <v>0</v>
-      </c>
-      <c r="P140" s="1">
-        <v>5324000</v>
-      </c>
-      <c r="Q140" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A141">
-        <v>64785630</v>
-      </c>
-      <c r="B141" s="2">
-        <v>46185.578321759262</v>
-      </c>
-      <c r="C141">
-        <v>64803291</v>
-      </c>
-      <c r="D141" s="2">
-        <v>46185.710648148146</v>
-      </c>
-      <c r="E141" t="s">
-        <v>176</v>
-      </c>
-      <c r="F141" t="s">
-        <v>98</v>
-      </c>
-      <c r="G141">
-        <v>708793132</v>
-      </c>
-      <c r="H141" t="s">
-        <v>277</v>
-      </c>
-      <c r="I141" t="s">
-        <v>0</v>
-      </c>
-      <c r="J141" t="s">
-        <v>12</v>
-      </c>
-      <c r="K141" t="s">
-        <v>5</v>
-      </c>
-      <c r="L141" t="s">
-        <v>6</v>
-      </c>
-      <c r="M141" t="s">
-        <v>3</v>
-      </c>
-      <c r="N141" t="s">
-        <v>107</v>
-      </c>
-      <c r="O141" t="s">
-        <v>0</v>
-      </c>
-      <c r="P141" s="1">
-        <v>293000</v>
-      </c>
-      <c r="Q141" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A142">
-        <v>64791999</v>
-      </c>
-      <c r="B142" s="2">
-        <v>46185.626469907409</v>
-      </c>
-      <c r="C142">
-        <v>64794477</v>
-      </c>
-      <c r="D142" s="2">
-        <v>46185.644490740742</v>
-      </c>
-      <c r="E142" t="s">
-        <v>274</v>
-      </c>
-      <c r="F142" t="s">
-        <v>279</v>
-      </c>
-      <c r="G142">
-        <v>140675694</v>
-      </c>
-      <c r="H142" t="s">
-        <v>36</v>
-      </c>
-      <c r="I142" t="s">
-        <v>0</v>
-      </c>
-      <c r="J142" t="s">
-        <v>67</v>
-      </c>
-      <c r="K142" t="s">
-        <v>1</v>
-      </c>
-      <c r="L142" t="s">
-        <v>2</v>
-      </c>
-      <c r="M142" t="s">
-        <v>3</v>
-      </c>
-      <c r="N142" t="s">
-        <v>107</v>
-      </c>
-      <c r="O142" t="s">
-        <v>0</v>
-      </c>
-      <c r="P142" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q113" xr:uid="{B09768A0-915F-4D98-A6E3-373DEF20CD6F}"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/pipe.xlsx
+++ b/pipe.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://orange0-my.sharepoint.com/personal/edith_bah_orange_com/Documents/Attachments/Bureau/Nouveau dossier/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="615" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F63E252-9B23-4BFE-96FB-C016DB179D39}"/>
+  <xr:revisionPtr revIDLastSave="623" documentId="11_65767444480FB77B7A889FE1F7C42529ACCAD36A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BA35E43-E552-4159-9CA7-C8D12E8312B6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil2" sheetId="50" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="51" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil2!$A$1:$Q$113</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="278">
   <si>
     <t>-</t>
   </si>
@@ -116,9 +113,6 @@
     <t>ABIDJAN PLATEAU</t>
   </si>
   <si>
-    <t>Responsable Zone: Validation pour intervention</t>
-  </si>
-  <si>
     <t>ftto_virage</t>
   </si>
   <si>
@@ -482,9 +476,6 @@
     <t>BUVPN260082</t>
   </si>
   <si>
-    <t>Responsable Zone: Validation intervention</t>
-  </si>
-  <si>
     <t>ABIDJAN-COCODY//VOIE INCONNUE/RIVIERA 0708448800</t>
   </si>
   <si>
@@ -614,9 +605,6 @@
     <t>ABIDJAN-PLATEAU</t>
   </si>
   <si>
-    <t>ADKONTACT</t>
-  </si>
-  <si>
     <t>MAIRIE DE DJEBONOUA</t>
   </si>
   <si>
@@ -641,12 +629,6 @@
     <t>COCODY 2 PLATEAU VALLON</t>
   </si>
   <si>
-    <t>INALCA</t>
-  </si>
-  <si>
-    <t>MARCORY ZONE 4</t>
-  </si>
-  <si>
     <t>STE UCP SANTE MONDIALE</t>
   </si>
   <si>
@@ -671,12 +653,6 @@
     <t>Extrémité A : BOUAKE Extrémité B : ABIDJAN</t>
   </si>
   <si>
-    <t>FONDS D'ENTRETIEN ROUTIER</t>
-  </si>
-  <si>
-    <t>ABOBO</t>
-  </si>
-  <si>
     <t>ORANGE BUSNESS SERVICES</t>
   </si>
   <si>
@@ -689,18 +665,9 @@
     <t>SYTHD260150</t>
   </si>
   <si>
-    <t>SYTHD260156</t>
-  </si>
-  <si>
-    <t>SYTHD260160</t>
-  </si>
-  <si>
     <t>SYTHD260161</t>
   </si>
   <si>
-    <t>BUVPN260098</t>
-  </si>
-  <si>
     <t>CMC INVESTMENTS LIMITED</t>
   </si>
   <si>
@@ -773,9 +740,6 @@
     <t>Support IP: Config Eq Acces</t>
   </si>
   <si>
-    <t>ABIDJAN-COCODY//VOIE INCONNUE/COCODY DANGA</t>
-  </si>
-  <si>
     <t>BUVPN260101</t>
   </si>
   <si>
@@ -785,9 +749,6 @@
     <t>BBF : Validation Etude</t>
   </si>
   <si>
-    <t>ORANGE BUSINESS SERVICES COTE D'IVOIRE</t>
-  </si>
-  <si>
     <t>COCODY RIVIERA GOLF</t>
   </si>
   <si>
@@ -830,9 +791,6 @@
     <t>RIVIERA PALMERAIE</t>
   </si>
   <si>
-    <t>IP Delivery: Validation information</t>
-  </si>
-  <si>
     <t>FRANCHISE MANKONO</t>
   </si>
   <si>
@@ -846,6 +804,72 @@
   </si>
   <si>
     <t>MINISTERE DE L’ENVIRONNEMENT</t>
+  </si>
+  <si>
+    <t>Transmission Plans Equipe Numerisation</t>
+  </si>
+  <si>
+    <t>Prestataire : Correction Conformite Travaux</t>
+  </si>
+  <si>
+    <t>TAABO LAMTO</t>
+  </si>
+  <si>
+    <t>xxxxxx</t>
+  </si>
+  <si>
+    <t>Saisie ASCOM</t>
+  </si>
+  <si>
+    <t>STE BGFI BANK</t>
+  </si>
+  <si>
+    <t>COCODY DANGA</t>
+  </si>
+  <si>
+    <t>ADKONTACT COTE D'IVOIRE</t>
+  </si>
+  <si>
+    <t>ABIDJAN-TREICHVILLE//VOIE INCONNUE/TREICHVILLE</t>
+  </si>
+  <si>
+    <t>BO Homologation: Saisie BSCS</t>
+  </si>
+  <si>
+    <t>BO Homologation: Mise en service GAIA</t>
+  </si>
+  <si>
+    <t>YAMOUSSOUKRO Kick-off</t>
+  </si>
+  <si>
+    <t>COCODY Budweiser Fan Festival Playce Palmeraie</t>
+  </si>
+  <si>
+    <t>SYTHD260164</t>
+  </si>
+  <si>
+    <t>UCP SANTE BANQUE MONDIALE</t>
+  </si>
+  <si>
+    <t>SYTHD230029</t>
+  </si>
+  <si>
+    <t>Support IP: Correction</t>
+  </si>
+  <si>
+    <t>NOUVELLE GENERAION DE SERVICE</t>
+  </si>
+  <si>
+    <t>STE OCI DEMANDE INTERNE</t>
+  </si>
+  <si>
+    <t>PORT-BOUET PARC D'EXPOSITION</t>
+  </si>
+  <si>
+    <t>Temporaire</t>
+  </si>
+  <si>
+    <t>SIE: Pilote</t>
   </si>
 </sst>
 </file>
@@ -889,18 +913,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1229,61 +1242,61 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B09768A0-915F-4D98-A6E3-373DEF20CD6F}">
-  <dimension ref="A1:Q113"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF4F71D-0C95-42F8-9350-C44E6AC4639E}">
+  <dimension ref="A1:Q138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>45</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>46</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>47</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>48</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>49</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>50</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O1" t="s">
         <v>51</v>
       </c>
-      <c r="N1" t="s">
-        <v>105</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>52</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>53</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -1303,13 +1316,13 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G2">
         <v>777545168</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
@@ -1350,16 +1363,16 @@
         <v>46184.710358796299</v>
       </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F3" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G3">
         <v>748512613</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
         <v>0</v>
@@ -1377,7 +1390,7 @@
         <v>3</v>
       </c>
       <c r="N3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="O3" t="s">
         <v>0</v>
@@ -1391,84 +1404,84 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>52778382</v>
+        <v>49660008</v>
       </c>
       <c r="B4" s="2">
-        <v>45959.67696759259</v>
+        <v>45897.665000000001</v>
       </c>
       <c r="C4">
-        <v>55073470</v>
+        <v>64920585</v>
       </c>
       <c r="D4" s="2">
-        <v>46003.678194444445</v>
+        <v>46188.554189814815</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>256</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>230</v>
       </c>
       <c r="G4">
-        <v>708086759</v>
+        <v>748512613</v>
       </c>
       <c r="H4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4">
-        <v>2788625</v>
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="N4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O4" t="s">
         <v>0</v>
       </c>
-      <c r="P4" t="s">
-        <v>0</v>
+      <c r="P4" s="1">
+        <v>2538822</v>
       </c>
       <c r="Q4" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>52808171</v>
+        <v>52778382</v>
       </c>
       <c r="B5" s="2">
-        <v>45960.452361111114</v>
+        <v>45959.67696759259</v>
       </c>
       <c r="C5">
-        <v>59829408</v>
+        <v>55073470</v>
       </c>
       <c r="D5" s="2">
-        <v>46093.677152777775</v>
+        <v>46003.678194444445</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5">
+        <v>708086759</v>
+      </c>
+      <c r="H5" t="s">
         <v>55</v>
       </c>
-      <c r="G5">
-        <v>709738605</v>
-      </c>
-      <c r="H5" t="s">
-        <v>59</v>
-      </c>
       <c r="I5">
-        <v>2793645</v>
+        <v>2788625</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
@@ -1480,10 +1493,10 @@
         <v>8</v>
       </c>
       <c r="M5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="N5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O5" t="s">
         <v>0</v>
@@ -1492,48 +1505,48 @@
         <v>0</v>
       </c>
       <c r="Q5" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>53702282</v>
+        <v>52808171</v>
       </c>
       <c r="B6" s="2">
-        <v>45978.671550925923</v>
+        <v>45960.452361111114</v>
       </c>
       <c r="C6">
-        <v>64785970</v>
+        <v>59829408</v>
       </c>
       <c r="D6" s="2">
-        <v>46185.580925925926</v>
+        <v>46093.677152777775</v>
       </c>
       <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6">
+        <v>709738605</v>
+      </c>
+      <c r="H6" t="s">
         <v>58</v>
       </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6">
-        <v>778036533</v>
-      </c>
-      <c r="H6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" t="s">
-        <v>0</v>
+      <c r="I6">
+        <v>2793645</v>
       </c>
       <c r="J6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N6" t="s">
         <v>106</v>
@@ -1544,84 +1557,84 @@
       <c r="P6" t="s">
         <v>0</v>
       </c>
-      <c r="Q6">
-        <v>2720301240</v>
+      <c r="Q6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>53749839</v>
+        <v>53702282</v>
       </c>
       <c r="B7" s="2">
-        <v>45979.600694444445</v>
+        <v>45978.671550925923</v>
       </c>
       <c r="C7">
-        <v>62944786</v>
+        <v>64748163</v>
       </c>
       <c r="D7" s="2">
-        <v>46150.446296296293</v>
+        <v>46184.76871527778</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>257</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>703333988</v>
+        <v>778036533</v>
       </c>
       <c r="H7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I7" t="s">
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M7" t="s">
         <v>3</v>
       </c>
       <c r="N7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O7" t="s">
         <v>0</v>
       </c>
-      <c r="P7" s="1">
-        <v>10000000</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>11</v>
+      <c r="P7" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>2720301240</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>53790357</v>
+        <v>53702282</v>
       </c>
       <c r="B8" s="2">
-        <v>45980.438298611109</v>
+        <v>45978.671550925923</v>
       </c>
       <c r="C8">
-        <v>61385261</v>
+        <v>64785970</v>
       </c>
       <c r="D8" s="2">
-        <v>46122.774224537039</v>
+        <v>46185.580925925926</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>708336404</v>
+        <v>778036533</v>
       </c>
       <c r="H8" t="s">
         <v>61</v>
@@ -1630,54 +1643,54 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M8" t="s">
         <v>3</v>
       </c>
       <c r="N8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="O8" t="s">
         <v>0</v>
       </c>
-      <c r="P8" s="1">
-        <v>4430307</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>33</v>
+      <c r="P8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>2720301240</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>53899369</v>
+        <v>53749839</v>
       </c>
       <c r="B9" s="2">
-        <v>45981.827430555553</v>
+        <v>45979.600694444445</v>
       </c>
       <c r="C9">
-        <v>55146678</v>
+        <v>62944786</v>
       </c>
       <c r="D9" s="2">
-        <v>46005.762916666667</v>
+        <v>46150.446296296293</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="G9">
-        <v>707003126</v>
+        <v>703333988</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
         <v>0</v>
@@ -1692,263 +1705,263 @@
         <v>6</v>
       </c>
       <c r="M9" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O9" t="s">
         <v>0</v>
       </c>
-      <c r="P9">
-        <v>0</v>
+      <c r="P9" s="1">
+        <v>10000000</v>
       </c>
       <c r="Q9" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>54449048</v>
+        <v>53790357</v>
       </c>
       <c r="B10" s="2">
-        <v>45992.706157407411</v>
+        <v>45980.438298611109</v>
       </c>
       <c r="C10">
-        <v>56341749</v>
+        <v>61385261</v>
       </c>
       <c r="D10" s="2">
-        <v>46029.685115740744</v>
+        <v>46122.774224537039</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="G10">
-        <v>708086759</v>
+        <v>708336404</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I10" t="s">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O10" t="s">
         <v>0</v>
       </c>
-      <c r="P10" t="s">
-        <v>0</v>
+      <c r="P10" s="1">
+        <v>4430307</v>
       </c>
       <c r="Q10" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>55104019</v>
+        <v>53899369</v>
       </c>
       <c r="B11" s="2">
-        <v>46004.469606481478</v>
+        <v>45981.827430555553</v>
       </c>
       <c r="C11">
-        <v>56566265</v>
+        <v>55146678</v>
       </c>
       <c r="D11" s="2">
-        <v>46034.582673611112</v>
+        <v>46005.762916666667</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="G11">
-        <v>504033918</v>
+        <v>707003126</v>
       </c>
       <c r="H11" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="I11" t="s">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K11" t="s">
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O11" t="s">
         <v>0</v>
       </c>
-      <c r="P11" s="1">
-        <v>4000000</v>
+      <c r="P11">
+        <v>0</v>
       </c>
       <c r="Q11" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>55636282</v>
+        <v>54449048</v>
       </c>
       <c r="B12" s="2">
-        <v>46014.435729166667</v>
+        <v>45992.706157407411</v>
       </c>
       <c r="C12">
-        <v>57367586</v>
+        <v>56341749</v>
       </c>
       <c r="D12" s="2">
-        <v>46049.856261574074</v>
+        <v>46029.685115740744</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="G12">
-        <v>759003900</v>
+        <v>708086759</v>
       </c>
       <c r="H12" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="I12" t="s">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
         <v>5</v>
       </c>
       <c r="L12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M12" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O12" t="s">
         <v>0</v>
       </c>
-      <c r="P12" s="1">
-        <v>918681</v>
+      <c r="P12" t="s">
+        <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>55694485</v>
+        <v>55104019</v>
       </c>
       <c r="B13" s="2">
-        <v>46015.420092592591</v>
+        <v>46004.469606481478</v>
       </c>
       <c r="C13">
-        <v>56752240</v>
+        <v>56566265</v>
       </c>
       <c r="D13" s="2">
-        <v>46037.705520833333</v>
+        <v>46034.582673611112</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G13">
-        <v>749338073</v>
+        <v>504033918</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="I13" t="s">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K13" t="s">
         <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M13" t="s">
         <v>3</v>
       </c>
       <c r="N13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O13" t="s">
         <v>0</v>
       </c>
       <c r="P13" s="1">
-        <v>638462</v>
+        <v>4000000</v>
       </c>
       <c r="Q13" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>56181778</v>
+        <v>55636282</v>
       </c>
       <c r="B14" s="2">
-        <v>46027.499212962961</v>
+        <v>46014.435729166667</v>
       </c>
       <c r="C14">
-        <v>59210339</v>
+        <v>57367586</v>
       </c>
       <c r="D14" s="2">
-        <v>46083.492881944447</v>
+        <v>46049.856261574074</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G14">
-        <v>585990976</v>
+        <v>759003900</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
-      </c>
-      <c r="I14">
-        <v>1765416</v>
+        <v>28</v>
+      </c>
+      <c r="I14" t="s">
+        <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -1960,172 +1973,172 @@
         <v>3</v>
       </c>
       <c r="N14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O14" t="s">
         <v>0</v>
       </c>
       <c r="P14" s="1">
-        <v>3000000</v>
+        <v>918681</v>
       </c>
       <c r="Q14" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>56603495</v>
+        <v>55694485</v>
       </c>
       <c r="B15" s="2">
-        <v>46035.408518518518</v>
+        <v>46015.420092592591</v>
       </c>
       <c r="C15">
-        <v>60907737</v>
+        <v>56752240</v>
       </c>
       <c r="D15" s="2">
-        <v>46113.726909722223</v>
+        <v>46037.705520833333</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="G15">
-        <v>707003126</v>
+        <v>749338073</v>
       </c>
       <c r="H15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I15" t="s">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K15" t="s">
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M15" t="s">
         <v>3</v>
       </c>
       <c r="N15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O15" t="s">
         <v>0</v>
       </c>
       <c r="P15" s="1">
-        <v>7103410</v>
+        <v>638462</v>
       </c>
       <c r="Q15" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>56618123</v>
+        <v>56181778</v>
       </c>
       <c r="B16" s="2">
-        <v>46035.520821759259</v>
+        <v>46027.499212962961</v>
       </c>
       <c r="C16">
-        <v>63588969</v>
+        <v>59210339</v>
       </c>
       <c r="D16" s="2">
-        <v>46162.539305555554</v>
+        <v>46083.492881944447</v>
       </c>
       <c r="E16" t="s">
-        <v>176</v>
+        <v>86</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G16">
-        <v>504041812</v>
+        <v>585990976</v>
       </c>
       <c r="H16" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="I16">
-        <v>1775236</v>
+        <v>1765416</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M16" t="s">
         <v>3</v>
       </c>
       <c r="N16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O16" t="s">
         <v>0</v>
       </c>
       <c r="P16" s="1">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="Q16" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>56675050</v>
+        <v>56603495</v>
       </c>
       <c r="B17" s="2">
-        <v>46036.516423611109</v>
+        <v>46035.408518518518</v>
       </c>
       <c r="C17">
-        <v>63302732</v>
+        <v>60907737</v>
       </c>
       <c r="D17" s="2">
-        <v>46157.396793981483</v>
+        <v>46113.726909722223</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>172</v>
+        <v>27</v>
       </c>
       <c r="G17">
-        <v>748512613</v>
+        <v>707003126</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I17" t="s">
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K17" t="s">
         <v>5</v>
       </c>
       <c r="L17" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M17" t="s">
         <v>3</v>
       </c>
       <c r="N17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O17" t="s">
         <v>0</v>
       </c>
       <c r="P17" s="1">
-        <v>4362401</v>
+        <v>7103410</v>
       </c>
       <c r="Q17" t="s">
         <v>19</v>
@@ -2133,81 +2146,81 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>56970346</v>
+        <v>56618123</v>
       </c>
       <c r="B18" s="2">
-        <v>46042.557280092595</v>
+        <v>46035.520821759259</v>
       </c>
       <c r="C18">
-        <v>59242054</v>
+        <v>63588969</v>
       </c>
       <c r="D18" s="2">
-        <v>46083.719525462962</v>
+        <v>46162.539305555554</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G18">
-        <v>708667658</v>
+        <v>504041812</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" t="s">
-        <v>0</v>
+        <v>107</v>
+      </c>
+      <c r="I18">
+        <v>1775236</v>
       </c>
       <c r="J18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
       </c>
       <c r="L18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M18" t="s">
         <v>3</v>
       </c>
       <c r="N18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O18" t="s">
         <v>0</v>
       </c>
       <c r="P18" s="1">
-        <v>2871414</v>
+        <v>2000000</v>
       </c>
       <c r="Q18" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>57398181</v>
+        <v>56675050</v>
       </c>
       <c r="B19" s="2">
-        <v>46050.584374999999</v>
+        <v>46036.516423611109</v>
       </c>
       <c r="C19">
-        <v>60344342</v>
+        <v>63302732</v>
       </c>
       <c r="D19" s="2">
-        <v>46104.528900462959</v>
+        <v>46157.396793981483</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="G19">
-        <v>720631500</v>
+        <v>748512613</v>
       </c>
       <c r="H19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s">
         <v>0</v>
@@ -2225,42 +2238,42 @@
         <v>3</v>
       </c>
       <c r="N19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O19" t="s">
         <v>0</v>
       </c>
       <c r="P19" s="1">
-        <v>4406780</v>
+        <v>4362401</v>
       </c>
       <c r="Q19" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>58055656</v>
+        <v>56970346</v>
       </c>
       <c r="B20" s="2">
-        <v>46062.760023148148</v>
+        <v>46042.557280092595</v>
       </c>
       <c r="C20">
-        <v>61269237</v>
+        <v>59242054</v>
       </c>
       <c r="D20" s="2">
-        <v>46121.376689814817</v>
+        <v>46083.719525462962</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G20">
-        <v>758224257</v>
+        <v>708667658</v>
       </c>
       <c r="H20" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="I20" t="s">
         <v>0</v>
@@ -2278,95 +2291,95 @@
         <v>3</v>
       </c>
       <c r="N20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O20" t="s">
         <v>0</v>
       </c>
       <c r="P20" s="1">
-        <v>1800000</v>
+        <v>2871414</v>
       </c>
       <c r="Q20" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>58166885</v>
+        <v>57398181</v>
       </c>
       <c r="B21" s="2">
-        <v>46064.649965277778</v>
+        <v>46050.584374999999</v>
       </c>
       <c r="C21">
-        <v>63079695</v>
+        <v>60344342</v>
       </c>
       <c r="D21" s="2">
-        <v>46153.448425925926</v>
+        <v>46104.528900462959</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G21">
-        <v>504041812</v>
+        <v>720631500</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K21" t="s">
         <v>5</v>
       </c>
       <c r="L21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M21" t="s">
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O21" t="s">
         <v>0</v>
       </c>
       <c r="P21" s="1">
-        <v>2000000</v>
+        <v>4406780</v>
       </c>
       <c r="Q21" t="s">
-        <v>163</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>58626822</v>
+        <v>58055656</v>
       </c>
       <c r="B22" s="2">
-        <v>46072.810324074075</v>
+        <v>46062.760023148148</v>
       </c>
       <c r="C22">
-        <v>59811821</v>
+        <v>61269237</v>
       </c>
       <c r="D22" s="2">
-        <v>46093.543773148151</v>
+        <v>46121.376689814817</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G22">
-        <v>709574114</v>
+        <v>758224257</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="I22" t="s">
         <v>0</v>
@@ -2384,60 +2397,60 @@
         <v>3</v>
       </c>
       <c r="N22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O22" t="s">
         <v>0</v>
       </c>
       <c r="P22" s="1">
-        <v>445307</v>
+        <v>1800000</v>
       </c>
       <c r="Q22" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>58635645</v>
+        <v>58093827</v>
       </c>
       <c r="B23" s="2">
-        <v>46073.372395833336</v>
+        <v>46063.583402777775</v>
       </c>
       <c r="C23">
-        <v>61982536</v>
+        <v>63599943</v>
       </c>
       <c r="D23" s="2">
-        <v>46133.49863425926</v>
+        <v>46162.626145833332</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>260</v>
       </c>
       <c r="F23" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="G23">
-        <v>759250737</v>
+        <v>708086759</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
+        <v>258</v>
       </c>
       <c r="I23" t="s">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K23" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L23" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M23" t="s">
         <v>7</v>
       </c>
       <c r="N23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="O23" t="s">
         <v>0</v>
@@ -2446,33 +2459,33 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>120</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>58635674</v>
+        <v>58166885</v>
       </c>
       <c r="B24" s="2">
-        <v>46073.372488425928</v>
+        <v>46064.649965277778</v>
       </c>
       <c r="C24">
-        <v>61980847</v>
+        <v>63079695</v>
       </c>
       <c r="D24" s="2">
-        <v>46133.487384259257</v>
+        <v>46153.448425925926</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G24">
-        <v>759250737</v>
+        <v>504041812</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="I24" t="s">
         <v>0</v>
@@ -2487,116 +2500,116 @@
         <v>8</v>
       </c>
       <c r="M24" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O24" t="s">
         <v>0</v>
       </c>
       <c r="P24" s="1">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="Q24" t="s">
-        <v>57</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>58868849</v>
+        <v>58626822</v>
       </c>
       <c r="B25" s="2">
-        <v>46077.501203703701</v>
+        <v>46072.810324074075</v>
       </c>
       <c r="C25">
-        <v>62104932</v>
+        <v>59811821</v>
       </c>
       <c r="D25" s="2">
-        <v>46135.396608796298</v>
+        <v>46093.543773148151</v>
       </c>
       <c r="E25" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G25">
-        <v>748377555</v>
+        <v>709574114</v>
       </c>
       <c r="H25" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="I25" t="s">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K25" t="s">
         <v>5</v>
       </c>
       <c r="L25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M25" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O25" t="s">
         <v>0</v>
       </c>
-      <c r="P25" t="s">
-        <v>0</v>
+      <c r="P25" s="1">
+        <v>445307</v>
       </c>
       <c r="Q25" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>58925987</v>
+        <v>58635645</v>
       </c>
       <c r="B26" s="2">
-        <v>46078.434814814813</v>
+        <v>46073.372395833336</v>
       </c>
       <c r="C26">
-        <v>60163873</v>
+        <v>61982536</v>
       </c>
       <c r="D26" s="2">
-        <v>46100.423101851855</v>
+        <v>46133.49863425926</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G26">
-        <v>708641473</v>
+        <v>759250737</v>
       </c>
       <c r="H26" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="I26" t="s">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K26" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L26" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M26" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O26" t="s">
         <v>0</v>
@@ -2605,192 +2618,192 @@
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>58959238</v>
+        <v>58635674</v>
       </c>
       <c r="B27" s="2">
-        <v>46078.665532407409</v>
+        <v>46073.372488425928</v>
       </c>
       <c r="C27">
-        <v>60163938</v>
+        <v>61980847</v>
       </c>
       <c r="D27" s="2">
-        <v>46100.423773148148</v>
+        <v>46133.487384259257</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F27" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G27">
-        <v>708641473</v>
+        <v>759250737</v>
       </c>
       <c r="H27" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="I27" t="s">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K27" t="s">
         <v>5</v>
       </c>
       <c r="L27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M27" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O27" t="s">
         <v>0</v>
       </c>
       <c r="P27" s="1">
-        <v>850000</v>
+        <v>500000</v>
       </c>
       <c r="Q27" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>59537755</v>
+        <v>58868849</v>
       </c>
       <c r="B28" s="2">
-        <v>46088.586631944447</v>
+        <v>46077.501203703701</v>
       </c>
       <c r="C28">
-        <v>61591841</v>
+        <v>62104932</v>
       </c>
       <c r="D28" s="2">
-        <v>46127.35796296296</v>
+        <v>46135.396608796298</v>
       </c>
       <c r="E28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="G28">
-        <v>556331131</v>
+        <v>748377555</v>
       </c>
       <c r="H28" t="s">
-        <v>121</v>
-      </c>
-      <c r="I28">
-        <v>1843236</v>
+        <v>98</v>
+      </c>
+      <c r="I28" t="s">
+        <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="L28" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M28" t="s">
         <v>7</v>
       </c>
       <c r="N28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O28" t="s">
         <v>0</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="s">
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>59606122</v>
+        <v>58925987</v>
       </c>
       <c r="B29" s="2">
-        <v>46090.447604166664</v>
+        <v>46078.434814814813</v>
       </c>
       <c r="C29">
-        <v>61897702</v>
+        <v>60163873</v>
       </c>
       <c r="D29" s="2">
-        <v>46132.349363425928</v>
+        <v>46100.423101851855</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="G29">
-        <v>708454305</v>
+        <v>708641473</v>
       </c>
       <c r="H29" t="s">
-        <v>136</v>
-      </c>
-      <c r="I29">
-        <v>1842206</v>
+        <v>100</v>
+      </c>
+      <c r="I29" t="s">
+        <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M29" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O29" t="s">
         <v>0</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="s">
         <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>59615935</v>
+        <v>58959238</v>
       </c>
       <c r="B30" s="2">
-        <v>46090.512303240743</v>
+        <v>46078.665532407409</v>
       </c>
       <c r="C30">
-        <v>60393405</v>
+        <v>64964038</v>
       </c>
       <c r="D30" s="2">
-        <v>46105.432800925926</v>
+        <v>46189.418923611112</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="G30">
-        <v>767081456</v>
+        <v>708641473</v>
       </c>
       <c r="H30" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="I30" t="s">
         <v>0</v>
@@ -2808,51 +2821,51 @@
         <v>3</v>
       </c>
       <c r="N30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O30" t="s">
         <v>0</v>
       </c>
-      <c r="P30">
-        <v>0</v>
+      <c r="P30" s="1">
+        <v>850000</v>
       </c>
       <c r="Q30" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>59894743</v>
+        <v>59537755</v>
       </c>
       <c r="B31" s="2">
-        <v>46094.687673611108</v>
+        <v>46088.586631944447</v>
       </c>
       <c r="C31">
-        <v>64800213</v>
+        <v>61591841</v>
       </c>
       <c r="D31" s="2">
-        <v>46185.685624999998</v>
+        <v>46127.35796296296</v>
       </c>
       <c r="E31" t="s">
-        <v>243</v>
+        <v>86</v>
       </c>
       <c r="F31" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="G31">
-        <v>759668146</v>
+        <v>556331131</v>
       </c>
       <c r="H31" t="s">
-        <v>241</v>
+        <v>120</v>
       </c>
       <c r="I31">
-        <v>1849226</v>
+        <v>1843236</v>
       </c>
       <c r="J31" t="s">
         <v>4</v>
       </c>
       <c r="K31" t="s">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="L31" t="s">
         <v>6</v>
@@ -2861,51 +2874,51 @@
         <v>7</v>
       </c>
       <c r="N31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O31" t="s">
         <v>0</v>
       </c>
-      <c r="P31" t="s">
+      <c r="P31">
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>242</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>60748674</v>
+        <v>59606122</v>
       </c>
       <c r="B32" s="2">
-        <v>46111.511504629627</v>
+        <v>46090.447604166664</v>
       </c>
       <c r="C32">
-        <v>62475433</v>
+        <v>61897702</v>
       </c>
       <c r="D32" s="2">
-        <v>46141.624513888892</v>
+        <v>46132.349363425928</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G32">
-        <v>767791237</v>
+        <v>708454305</v>
       </c>
       <c r="H32" t="s">
-        <v>119</v>
-      </c>
-      <c r="I32" t="s">
-        <v>0</v>
+        <v>135</v>
+      </c>
+      <c r="I32">
+        <v>1842206</v>
       </c>
       <c r="J32" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K32" t="s">
-        <v>5</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s">
         <v>6</v>
@@ -2914,7 +2927,7 @@
         <v>7</v>
       </c>
       <c r="N32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O32" t="s">
         <v>0</v>
@@ -2923,157 +2936,157 @@
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>60972166</v>
+        <v>59615935</v>
       </c>
       <c r="B33" s="2">
-        <v>46114.708020833335</v>
+        <v>46090.512303240743</v>
       </c>
       <c r="C33">
-        <v>62949578</v>
+        <v>60393405</v>
       </c>
       <c r="D33" s="2">
-        <v>46150.482407407406</v>
+        <v>46105.432800925926</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="G33">
-        <v>160128782</v>
+        <v>767081456</v>
       </c>
       <c r="H33" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="I33" t="s">
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
       </c>
       <c r="L33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M33" t="s">
         <v>3</v>
       </c>
       <c r="N33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O33" t="s">
         <v>0</v>
       </c>
-      <c r="P33" s="1">
-        <v>800000</v>
+      <c r="P33">
+        <v>0</v>
       </c>
       <c r="Q33" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>61239047</v>
+        <v>59894743</v>
       </c>
       <c r="B34" s="2">
-        <v>46120.622071759259</v>
+        <v>46094.687673611108</v>
       </c>
       <c r="C34">
-        <v>64795668</v>
+        <v>64965140</v>
       </c>
       <c r="D34" s="2">
-        <v>46185.651990740742</v>
+        <v>46189